--- a/financas.xlsx
+++ b/financas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{0F9471C2-95A1-4CF9-8CFE-1EF73F0B2DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E956260-8345-44B7-8A5E-CD6CF659F393}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="8_{0F9471C2-95A1-4CF9-8CFE-1EF73F0B2DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FCB1B94-4D65-465E-B673-4DA11AAF26BE}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="247">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -135,6 +135,9 @@
     <t>Status pagamento Stella</t>
   </si>
   <si>
+    <t>Em aberto</t>
+  </si>
+  <si>
     <t>Itaú Total</t>
   </si>
   <si>
@@ -204,6 +207,9 @@
     <t>Modo de Pagamento</t>
   </si>
   <si>
+    <t>Fixo</t>
+  </si>
+  <si>
     <t>Manual</t>
   </si>
   <si>
@@ -216,12 +222,117 @@
     <t>Mensalidade</t>
   </si>
   <si>
+    <t>PS Plus Samuel</t>
+  </si>
+  <si>
+    <t>Produtos</t>
+  </si>
+  <si>
+    <t>Calça Kevlar</t>
+  </si>
+  <si>
+    <t>Equipamentos Grid Motors</t>
+  </si>
+  <si>
+    <t>Racing Rabbit</t>
+  </si>
+  <si>
+    <t>Moto</t>
+  </si>
+  <si>
+    <t>Jogos PSN</t>
+  </si>
+  <si>
+    <t>Estorno Jaqueta Grid Motors</t>
+  </si>
+  <si>
+    <t>Estorno</t>
+  </si>
+  <si>
+    <t>Psiquiatra</t>
+  </si>
+  <si>
+    <t>Saúde</t>
+  </si>
+  <si>
+    <t>Renner Stella</t>
+  </si>
+  <si>
+    <t>Renner - Presente Stella</t>
+  </si>
+  <si>
+    <t>Capacete Stella</t>
+  </si>
+  <si>
+    <t>HDMI Splitter</t>
+  </si>
+  <si>
+    <t>Caderno Azadi Store</t>
+  </si>
+  <si>
+    <t>Blood of the Dawnwalker - Ricardo</t>
+  </si>
+  <si>
+    <t>Indiana Jones A SER ESTORNADO</t>
+  </si>
+  <si>
+    <t>Indiana Jones Premium Edition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estorno Indiana Jones </t>
+  </si>
+  <si>
+    <t>Multiprocessador</t>
+  </si>
+  <si>
+    <t>Wolverine Pré venda</t>
+  </si>
+  <si>
+    <t>Roupa</t>
+  </si>
+  <si>
+    <t>Escapamento JBK</t>
+  </si>
+  <si>
+    <t>Vans Loafer</t>
+  </si>
+  <si>
+    <t>Blood of the Dawnwalker</t>
+  </si>
+  <si>
     <t>Clube Literatura Clássica</t>
   </si>
   <si>
+    <t>Jaqueta Stella</t>
+  </si>
+  <si>
+    <t>Segunda Pele Kevlar</t>
+  </si>
+  <si>
+    <t>Presente Dimitri</t>
+  </si>
+  <si>
+    <t>Pedrinho Bancos</t>
+  </si>
+  <si>
+    <t>Rog Ally Dock</t>
+  </si>
+  <si>
+    <t>Luva Fairtex</t>
+  </si>
+  <si>
     <t>Hostinger Nano</t>
   </si>
   <si>
+    <t>TENTAR ADIATNAR</t>
+  </si>
+  <si>
+    <t>Moletom Brutal Kill</t>
+  </si>
+  <si>
+    <t>Roupas</t>
+  </si>
+  <si>
     <t>HBO</t>
   </si>
   <si>
@@ -246,6 +357,9 @@
     <t>Veroo</t>
   </si>
   <si>
+    <t>Amazon Prime</t>
+  </si>
+  <si>
     <t>Seguro Allianz</t>
   </si>
   <si>
@@ -258,9 +372,6 @@
     <t>Claude</t>
   </si>
   <si>
-    <t>Amazon Prime</t>
-  </si>
-  <si>
     <t>Youtube</t>
   </si>
   <si>
@@ -270,384 +381,288 @@
     <t>Muay Thai personal</t>
   </si>
   <si>
-    <t>Pedrinho Bancos</t>
-  </si>
-  <si>
-    <t>Produtos</t>
-  </si>
-  <si>
-    <t>Ração</t>
-  </si>
-  <si>
-    <t>Fixo</t>
+    <t xml:space="preserve">Pagamento </t>
+  </si>
+  <si>
+    <t>PAGAMENTO</t>
+  </si>
+  <si>
+    <t>Vivo</t>
+  </si>
+  <si>
+    <t>Luz</t>
+  </si>
+  <si>
+    <t>Água</t>
+  </si>
+  <si>
+    <t>Gás</t>
+  </si>
+  <si>
+    <t>Seguranças+Câmera+Seguro Residencial</t>
+  </si>
+  <si>
+    <t>Cartão Itaú da Stella</t>
+  </si>
+  <si>
+    <t>Recolhimento INSS</t>
+  </si>
+  <si>
+    <t>Empréstimo</t>
+  </si>
+  <si>
+    <t>Honorários Edilson</t>
+  </si>
+  <si>
+    <t>Dinheiro guardado para...</t>
+  </si>
+  <si>
+    <t>Saldo inicial</t>
+  </si>
+  <si>
+    <t>Para retirar mês que vem?</t>
+  </si>
+  <si>
+    <t>Movimentação</t>
+  </si>
+  <si>
+    <t>Seu João</t>
+  </si>
+  <si>
+    <t>Seguro Itaú</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Com turbo</t>
+  </si>
+  <si>
+    <t>Caixinha Total</t>
+  </si>
+  <si>
+    <t>Caixinha Stella</t>
+  </si>
+  <si>
+    <t>Detran</t>
+  </si>
+  <si>
+    <t>Sem turbo</t>
+  </si>
+  <si>
+    <t>IPVAs + Licenciamento</t>
+  </si>
+  <si>
+    <t>Tirando da Caixinha Turbo</t>
+  </si>
+  <si>
+    <t>Adiantamento Stella Janeiro</t>
+  </si>
+  <si>
+    <t>Ajuste NuConta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cidadania+Veterinário Brida </t>
+  </si>
+  <si>
+    <t>Devolução Stella</t>
+  </si>
+  <si>
+    <t>Salário afastamento</t>
+  </si>
+  <si>
+    <t>Emergência Geleia+Vurtuoso+Terra Brasa</t>
+  </si>
+  <si>
+    <t>Adiantamento Stella</t>
+  </si>
+  <si>
+    <t>Galpãozin</t>
+  </si>
+  <si>
+    <t>Fisioterapia Stella</t>
+  </si>
+  <si>
+    <t>Pagamento Fasolina + Almoço Shirley + Linkedin+Bonfas</t>
+  </si>
+  <si>
+    <t>INSS</t>
+  </si>
+  <si>
+    <t>Pagamento Superbowl</t>
+  </si>
+  <si>
+    <t>SiSenor</t>
+  </si>
+  <si>
+    <t>Alemão</t>
   </si>
   <si>
     <t>GPS Moto</t>
   </si>
   <si>
-    <t>Roupa</t>
-  </si>
-  <si>
-    <t>Calça Kevlar</t>
-  </si>
-  <si>
-    <t>Equipamentos Grid Motors</t>
-  </si>
-  <si>
-    <t>Racing Rabbit</t>
-  </si>
-  <si>
-    <t>Moto</t>
-  </si>
-  <si>
-    <t>PS Plus Samuel</t>
-  </si>
-  <si>
-    <t>Jogos PSN</t>
-  </si>
-  <si>
-    <t>Renner - Presente Stella</t>
-  </si>
-  <si>
-    <t>Renner Stella</t>
-  </si>
-  <si>
-    <t>Capacete Stella</t>
-  </si>
-  <si>
-    <t>HDMI Splitter</t>
-  </si>
-  <si>
-    <t>Caderno Azadi Store</t>
-  </si>
-  <si>
-    <t>Multiprocessador</t>
-  </si>
-  <si>
-    <t>Wolverine Pré venda</t>
-  </si>
-  <si>
-    <t>Blood of the Dawnwalker</t>
-  </si>
-  <si>
-    <t>Escapamento JBK</t>
-  </si>
-  <si>
-    <t>Jaqueta Stella</t>
-  </si>
-  <si>
-    <t>Segunda Pele Kevlar</t>
-  </si>
-  <si>
-    <t>Rog Ally Dock</t>
-  </si>
-  <si>
-    <t>Luva Fairtex</t>
-  </si>
-  <si>
-    <t>TENTAR ADIATNAR</t>
-  </si>
-  <si>
-    <t>Moletom Brutal Kill</t>
-  </si>
-  <si>
-    <t>Roupas</t>
-  </si>
-  <si>
-    <t>Estorno</t>
-  </si>
-  <si>
-    <t>Estorno Jaqueta Grid Motors</t>
-  </si>
-  <si>
-    <t>Blood of the Dawnwalker - Ricardo</t>
+    <t>Portão</t>
+  </si>
+  <si>
+    <t>Devolução  Stella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonfa's </t>
+  </si>
+  <si>
+    <t>Ilumeo Março - WillBank</t>
+  </si>
+  <si>
+    <t>Remédio e Consulta Stella</t>
   </si>
   <si>
     <t>Pagamentos</t>
   </si>
   <si>
-    <t>Indiana Jones A SER ESTORNADO</t>
-  </si>
-  <si>
-    <t>Indiana Jones Premium Edition</t>
-  </si>
-  <si>
-    <t>Psiquiatra</t>
-  </si>
-  <si>
-    <t>Saúde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estorno Indiana Jones </t>
-  </si>
-  <si>
-    <t>Presente Dimitri</t>
+    <t>Adiantamento INSS</t>
+  </si>
+  <si>
+    <t>Adicional</t>
+  </si>
+  <si>
+    <t>Pagamentos fds Páscoa</t>
+  </si>
+  <si>
+    <t>Portão segunda parte</t>
+  </si>
+  <si>
+    <t>Devolução INSS</t>
+  </si>
+  <si>
+    <t>Páscoa</t>
+  </si>
+  <si>
+    <t>Psicólogo Stella</t>
+  </si>
+  <si>
+    <t>Estadia Lucky</t>
+  </si>
+  <si>
+    <t>Completar INSS Maio</t>
+  </si>
+  <si>
+    <t>PS5 Samuel</t>
+  </si>
+  <si>
+    <t>Madero</t>
+  </si>
+  <si>
+    <t>Monitor Daniel</t>
+  </si>
+  <si>
+    <t>Nano</t>
+  </si>
+  <si>
+    <t>Conserto Meriva</t>
+  </si>
+  <si>
+    <t>Pagamento Capinha e si senor</t>
+  </si>
+  <si>
+    <t>Adiantamento ROG</t>
+  </si>
+  <si>
+    <t>Completar salário Junho</t>
+  </si>
+  <si>
+    <t>Gigio</t>
+  </si>
+  <si>
+    <t>Devolução Stella (325 do PS5)</t>
+  </si>
+  <si>
+    <t>Julho - Bônus</t>
+  </si>
+  <si>
+    <t>Julho - 40% 13º</t>
+  </si>
+  <si>
+    <t>Julho - Pagamentos Necessários</t>
+  </si>
+  <si>
+    <t>Pagamento Edilson</t>
+  </si>
+  <si>
+    <t>Hot Wheels</t>
+  </si>
+  <si>
+    <t>Dinheiro Nano</t>
+  </si>
+  <si>
+    <t>Recolhimento Receita</t>
+  </si>
+  <si>
+    <t>Ilumeo Julho - 1º PPT</t>
+  </si>
+  <si>
+    <t>APC+Puscifer</t>
+  </si>
+  <si>
+    <t>Bar do Alemão</t>
+  </si>
+  <si>
+    <t>Adiantamento reembolso</t>
+  </si>
+  <si>
+    <t>Control+Dawnwalker</t>
+  </si>
+  <si>
+    <t>Retorno reembolso</t>
+  </si>
+  <si>
+    <t>Jogos e Restaurantes</t>
+  </si>
+  <si>
+    <t>INSS Stella</t>
+  </si>
+  <si>
+    <t>INSS Stella + Honorários Edilson</t>
   </si>
   <si>
     <t>Andiamo</t>
   </si>
   <si>
-    <t>Vans Loafer</t>
-  </si>
-  <si>
-    <t>Vivo</t>
-  </si>
-  <si>
-    <t>Luz</t>
-  </si>
-  <si>
-    <t>Água</t>
-  </si>
-  <si>
-    <t>Gás</t>
-  </si>
-  <si>
-    <t>Seguranças+Câmera+Seguro Residencial</t>
-  </si>
-  <si>
-    <t>Cartão Itaú da Stella</t>
-  </si>
-  <si>
-    <t>Recolhimento INSS</t>
-  </si>
-  <si>
-    <t>Empréstimo</t>
-  </si>
-  <si>
-    <t>Honorários Edilson</t>
-  </si>
-  <si>
-    <t>Dinheiro guardado para...</t>
-  </si>
-  <si>
-    <t>Saldo inicial</t>
-  </si>
-  <si>
-    <t>Para retirar mês que vem?</t>
-  </si>
-  <si>
-    <t>Movimentação</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Com turbo</t>
-  </si>
-  <si>
-    <t>Caixinha Total</t>
-  </si>
-  <si>
-    <t>Caixinha Stella</t>
-  </si>
-  <si>
-    <t>Detran</t>
-  </si>
-  <si>
-    <t>Sem turbo</t>
-  </si>
-  <si>
-    <t>IPVAs + Licenciamento</t>
-  </si>
-  <si>
-    <t>Tirando da Caixinha Turbo</t>
-  </si>
-  <si>
-    <t>Adiantamento Stella Janeiro</t>
-  </si>
-  <si>
-    <t>Ajuste NuConta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cidadania+Veterinário Brida </t>
-  </si>
-  <si>
-    <t>Devolução Stella</t>
-  </si>
-  <si>
-    <t>Salário afastamento</t>
-  </si>
-  <si>
-    <t>Emergência Geleia+Vurtuoso+Terra Brasa</t>
-  </si>
-  <si>
-    <t>Adiantamento Stella</t>
-  </si>
-  <si>
-    <t>Galpãozin</t>
-  </si>
-  <si>
-    <t>Fisioterapia Stella</t>
-  </si>
-  <si>
-    <t>Pagamento Fasolina + Almoço Shirley + Linkedin+Bonfas</t>
-  </si>
-  <si>
-    <t>INSS</t>
-  </si>
-  <si>
-    <t>Pagamento Superbowl</t>
-  </si>
-  <si>
-    <t>SiSenor</t>
-  </si>
-  <si>
-    <t>Alemão</t>
-  </si>
-  <si>
-    <t>Portão</t>
-  </si>
-  <si>
-    <t>Devolução  Stella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bonfa's </t>
-  </si>
-  <si>
-    <t>Ilumeo Março - WillBank</t>
-  </si>
-  <si>
-    <t>Remédio e Consulta Stella</t>
-  </si>
-  <si>
-    <t>Adiantamento INSS</t>
-  </si>
-  <si>
-    <t>Adicional</t>
-  </si>
-  <si>
-    <t>Pagamentos fds Páscoa</t>
-  </si>
-  <si>
-    <t>Portão segunda parte</t>
-  </si>
-  <si>
-    <t>Devolução INSS</t>
-  </si>
-  <si>
-    <t>Páscoa</t>
-  </si>
-  <si>
-    <t>Psicólogo Stella</t>
-  </si>
-  <si>
-    <t>Estadia Lucky</t>
-  </si>
-  <si>
-    <t>Completar INSS Maio</t>
-  </si>
-  <si>
-    <t>PS5 Samuel</t>
-  </si>
-  <si>
-    <t>Madero</t>
-  </si>
-  <si>
-    <t>Monitor Daniel</t>
-  </si>
-  <si>
-    <t>Nano</t>
-  </si>
-  <si>
-    <t>Conserto Meriva</t>
-  </si>
-  <si>
-    <t>Pagamento Capinha e si senor</t>
-  </si>
-  <si>
-    <t>Adiantamento ROG</t>
-  </si>
-  <si>
-    <t>Completar salário Junho</t>
-  </si>
-  <si>
-    <t>Gigio</t>
-  </si>
-  <si>
-    <t>Devolução Stella (325 do PS5)</t>
-  </si>
-  <si>
-    <t>Julho - Bônus</t>
-  </si>
-  <si>
-    <t>Julho - 40% 13º</t>
-  </si>
-  <si>
-    <t>Julho - Pagamentos Necessários</t>
-  </si>
-  <si>
-    <t>Pagamento Edilson</t>
-  </si>
-  <si>
-    <t>Hot Wheels</t>
-  </si>
-  <si>
-    <t>Dinheiro Nano</t>
-  </si>
-  <si>
-    <t>Recolhimento Receita</t>
-  </si>
-  <si>
-    <t>Ilumeo Julho - 1º PPT</t>
-  </si>
-  <si>
-    <t>APC+Puscifer</t>
-  </si>
-  <si>
-    <t>Bar do Alemão</t>
-  </si>
-  <si>
-    <t>Adiantamento reembolso</t>
-  </si>
-  <si>
-    <t>Control+Dawnwalker</t>
-  </si>
-  <si>
-    <t>Retorno reembolso</t>
-  </si>
-  <si>
-    <t>Jogos e Restaurantes</t>
+    <t>Passaportes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devolução Stella </t>
+  </si>
+  <si>
+    <t>Devolução Stella + Recolhimento</t>
+  </si>
+  <si>
+    <t>Sanduba do Barba</t>
+  </si>
+  <si>
+    <t>Ilumeo Agosto - 2º PPT</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
+    <t>Passagens - Compradas em agosto</t>
+  </si>
+  <si>
+    <t>Pagamento Control</t>
+  </si>
+  <si>
+    <t>Adiantamento Stella Setembro</t>
   </si>
   <si>
     <t>Restituição IR</t>
   </si>
   <si>
-    <t>INSS Stella</t>
-  </si>
-  <si>
-    <t>Setembro</t>
-  </si>
-  <si>
-    <t>INSS Stella + Honorários Edilson</t>
-  </si>
-  <si>
-    <t>Passagens - Compradas em agosto</t>
-  </si>
-  <si>
-    <t>Passaportes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devolução Stella </t>
-  </si>
-  <si>
-    <t>Sanduba do Barba</t>
-  </si>
-  <si>
-    <t>Ilumeo Agosto - 2º PPT</t>
-  </si>
-  <si>
-    <t>Outubro</t>
-  </si>
-  <si>
-    <t>Pagamento Control</t>
-  </si>
-  <si>
     <t>Novembro</t>
   </si>
   <si>
-    <t>Pagamento Dawnwalker</t>
-  </si>
-  <si>
     <t>Dezembro</t>
   </si>
   <si>
@@ -693,37 +708,85 @@
     <t>Obs.</t>
   </si>
   <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
     <t>Câmeras</t>
   </si>
   <si>
     <t>NuBank</t>
   </si>
   <si>
-    <t>Seu João</t>
+    <t>poupança</t>
   </si>
   <si>
     <t>Dera</t>
   </si>
   <si>
-    <t>Ok</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>poupança</t>
-  </si>
-  <si>
-    <t>Seguro Itaú</t>
-  </si>
-  <si>
-    <t>Adiantamento Stella Setembro</t>
-  </si>
-  <si>
-    <t>Devolução Stella + Recolhimento</t>
-  </si>
-  <si>
-    <t>Em aberto</t>
+    <t>Ração Geleia</t>
+  </si>
+  <si>
+    <t>Ração Brida</t>
+  </si>
+  <si>
+    <t>Silent Hill Townfall</t>
+  </si>
+  <si>
+    <t>Pontual</t>
+  </si>
+  <si>
+    <t>Transporte</t>
+  </si>
+  <si>
+    <t>Uber Paraíso da Cerveja - Ida e Volta</t>
+  </si>
+  <si>
+    <t>Pizza</t>
+  </si>
+  <si>
+    <t>Comida</t>
+  </si>
+  <si>
+    <t>Comida e Bebida Lucky Friends - Os dois dias</t>
+  </si>
+  <si>
+    <t>Muuuushine</t>
+  </si>
+  <si>
+    <t>Touca Cutterman</t>
+  </si>
+  <si>
+    <t>Frango Frito</t>
+  </si>
+  <si>
+    <t>Frango Frito Caio</t>
+  </si>
+  <si>
+    <t>Estacionamento Lucky Friends</t>
+  </si>
+  <si>
+    <t>Estacionamento Lucky Friends Caio</t>
+  </si>
+  <si>
+    <t>Ponto Da Esfiha</t>
+  </si>
+  <si>
+    <t>Gasolina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagamentos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">       Reembolso Psicóloga</t>
+  </si>
+  <si>
+    <t>Psicóloga</t>
+  </si>
+  <si>
+    <t>Psicóloga Atrasada</t>
   </si>
 </sst>
 </file>
@@ -1016,7 +1079,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1195,11 +1258,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1208,12 +1271,23 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="17">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1264,6 +1338,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.79989013336588644"/>
         </patternFill>
       </fill>
@@ -1285,38 +1373,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.79989013336588644"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9E1F2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9E1F2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1577,7 +1633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:F39"/>
+  <dimension ref="B1:F40"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
@@ -1603,13 +1659,13 @@
     <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="76"/>
       <c r="C3" s="6">
-        <f>C5-C8-C10-C11-C24+C25+C7</f>
-        <v>1296.4372380952377</v>
+        <f>C5-C8-C10-C11-C24+C25+C7+C26</f>
+        <v>1727.4614047619039</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E24+E25</f>
-        <v>3083.3875000000007</v>
+        <v>2733.8216666666667</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1618,7 +1674,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="8">
-        <v>9800</v>
+        <v>10000</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="8">
@@ -1631,12 +1687,12 @@
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-6503.5627619047627</v>
+        <v>-7695.0385952380966</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-6916.6124999999993</v>
+        <v>-7266.1783333333333</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -1667,12 +1723,12 @@
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>3947.6610952380952</v>
+        <v>5139.1369285714291</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>1108.8724999999999</v>
+        <v>1458.4383333333335</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -1681,12 +1737,12 @@
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>3947.6610952380952</v>
+        <v>5139.1369285714291</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>1108.8724999999999</v>
+        <v>1458.4383333333335</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
@@ -1849,7 +1905,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="8">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="8"/>
@@ -1859,150 +1915,148 @@
         <v>18</v>
       </c>
       <c r="C25" s="8">
-        <f>SUM(C26:C37)</f>
+        <f>SUM(C27:C38)</f>
         <v>0</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8">
-        <f>SUM(E26:E35)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+        <f>SUM(E27:E36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="14" t="str">
-        <f>IF('NuConta e Poupança'!M5="Sim",'NuConta e Poupança'!N5,"")</f>
-        <v/>
-      </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="14"/>
+        <v>244</v>
+      </c>
+      <c r="C26" s="8">
+        <f>(338/4)*5</f>
+        <v>422.5</v>
+      </c>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B27" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="14" t="str">
+        <f>IF('NuConta e Poupança'!M5="Sim",'NuConta e Poupança'!N5,"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="15"/>
+      <c r="E27" s="14"/>
+    </row>
+    <row r="28" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="21"/>
-    </row>
-    <row r="28" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="13" t="str">
+      <c r="C28" s="14"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="21"/>
+    </row>
+    <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L7</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C28" s="14" t="str">
+      <c r="C29" s="14" t="str">
         <f>IF('NuConta e Poupança'!M7="Sim",'NuConta e Poupança'!N7,"")</f>
         <v/>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="21"/>
-    </row>
-    <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="13" t="str">
+      <c r="D29" s="20"/>
+      <c r="E29" s="21"/>
+    </row>
+    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L8</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C29" s="14" t="str">
+      <c r="C30" s="14" t="str">
         <f>IF('NuConta e Poupança'!M8="Sim",'NuConta e Poupança'!N8,"")</f>
         <v/>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="21"/>
-    </row>
-    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="13" t="str">
+      <c r="D30" s="20"/>
+      <c r="E30" s="21"/>
+    </row>
+    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L9</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C30" s="14" t="str">
+      <c r="C31" s="14" t="str">
         <f>IF('NuConta e Poupança'!M9="Sim",'NuConta e Poupança'!N9,"")</f>
         <v/>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="21"/>
-    </row>
-    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="13" t="str">
+      <c r="D31" s="20"/>
+      <c r="E31" s="21"/>
+    </row>
+    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L10</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C31" s="14" t="str">
+      <c r="C32" s="14" t="str">
         <f>IF('NuConta e Poupança'!M10="Sim",'NuConta e Poupança'!N10,"")</f>
         <v/>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="21"/>
-    </row>
-    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="13" t="str">
+      <c r="D32" s="20"/>
+      <c r="E32" s="21"/>
+    </row>
+    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L12</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C32" s="14" t="str">
+      <c r="C33" s="14" t="str">
         <f>IF('NuConta e Poupança'!M12="Sim",'NuConta e Poupança'!N11,"")</f>
         <v/>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="21"/>
-    </row>
-    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="13" t="str">
+      <c r="D33" s="20"/>
+      <c r="E33" s="21"/>
+    </row>
+    <row r="34" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L13</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C33" s="14" t="str">
+      <c r="C34" s="14" t="str">
         <f>IF('NuConta e Poupança'!M13="Sim",'NuConta e Poupança'!N12,"")</f>
         <v/>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="21"/>
-    </row>
-    <row r="34" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="13" t="str">
+      <c r="D34" s="20"/>
+      <c r="E34" s="21"/>
+    </row>
+    <row r="35" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L14</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C34" s="14" t="str">
+      <c r="C35" s="14" t="str">
         <f>IF('NuConta e Poupança'!M14="Sim",'NuConta e Poupança'!N13,"")</f>
         <v/>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="21"/>
-    </row>
-    <row r="35" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="13" t="str">
+      <c r="D35" s="20"/>
+      <c r="E35" s="21"/>
+    </row>
+    <row r="36" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L15</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C35" s="14" t="str">
+      <c r="C36" s="14" t="str">
         <f>IF('NuConta e Poupança'!M15="Sim",'NuConta e Poupança'!N14,"")</f>
         <v/>
       </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="21"/>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B36" s="13" t="str">
+      <c r="D36" s="20"/>
+      <c r="E36" s="21"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L16</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C36" s="14" t="str">
+      <c r="C37" s="14" t="str">
         <f>IF('NuConta e Poupança'!M16="Sim",'NuConta e Poupança'!N15,"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="16"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="13" t="str">
-        <f>"       "&amp;'NuConta e Poupança'!L17</f>
-        <v xml:space="preserve">       </v>
-      </c>
-      <c r="C37" s="14" t="str">
-        <f>IF('NuConta e Poupança'!M17="Sim",'NuConta e Poupança'!N16,"")</f>
         <v/>
       </c>
       <c r="D37" s="20"/>
@@ -2011,27 +2065,40 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="13" t="str">
+        <f>"       "&amp;'NuConta e Poupança'!L17</f>
+        <v xml:space="preserve">       </v>
+      </c>
+      <c r="C38" s="14" t="str">
+        <f>IF('NuConta e Poupança'!M17="Sim",'NuConta e Poupança'!N16,"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="20"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="16"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L21</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C38" s="14" t="str">
+      <c r="C39" s="14" t="str">
         <f>IF('NuConta e Poupança'!M21="Sim",'NuConta e Poupança'!N20,"")</f>
         <v/>
       </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="21"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="13" t="str">
+      <c r="D39" s="20"/>
+      <c r="E39" s="21"/>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L22</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C39" s="14" t="str">
+      <c r="C40" s="14" t="str">
         <f>IF('NuConta e Poupança'!M22="Sim",'NuConta e Poupança'!N21,"")</f>
         <v/>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="21"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2083,11 +2150,11 @@
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>1108.8724999999999</v>
+        <v>1458.4383333333335</v>
       </c>
       <c r="D4" s="24">
         <f>Saldo!C9+D5</f>
-        <v>3947.6610952380952</v>
+        <v>5139.1369285714291</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
@@ -2206,7 +2273,7 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>4290.2275</v>
+        <v>4639.7933333333331</v>
       </c>
       <c r="D19" s="27"/>
     </row>
@@ -2234,7 +2301,7 @@
         <v>28</v>
       </c>
       <c r="C23" s="71" t="s">
-        <v>225</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2266,7 +2333,7 @@
   <sheetData>
     <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
@@ -2275,7 +2342,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2298,57 +2365,57 @@
     </row>
     <row r="4" spans="3:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M4" s="34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O4" s="33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P4" s="33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q4" s="34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="69" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" s="37" t="s">
         <v>1</v>
@@ -2363,10 +2430,10 @@
         <v>240.97</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L5" s="38">
         <f t="shared" ref="L5:L15" si="1">I5/N5</f>
@@ -2388,7 +2455,7 @@
       </c>
       <c r="Q5" s="37">
         <f ca="1">IF(O5&lt;&gt;"",IFERROR(DATEDIF(O5,TODAY(),"m")+1,""),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2951,7 +3018,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J5:K22">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"Parcelado/Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2983,7 +3050,7 @@
   <sheetData>
     <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
@@ -2992,7 +3059,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" s="43"/>
       <c r="P1" s="2"/>
@@ -3000,15 +3067,15 @@
     <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="45">
         <f>SUM(L6:L268)</f>
-        <v>5056.5335952380947</v>
+        <v>6660.4702619047621</v>
       </c>
       <c r="E2" s="32">
         <f>SUMIF($E$6:$E$268,E1,$M$6:$M$268)</f>
-        <v>3947.6610952380952</v>
+        <v>5139.1369285714291</v>
       </c>
       <c r="F2" s="32">
         <f>SUMIF($F$6:$F$268,F1,$M$6:$M$268)</f>
-        <v>1108.8724999999999</v>
+        <v>1458.4383333333335</v>
       </c>
       <c r="G2" s="32">
         <f>SUMIF($G$6:$G$268,G1,$M$6:$M$268)</f>
@@ -3028,52 +3095,52 @@
     <row r="5" spans="3:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="33"/>
       <c r="D5" s="33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M5" s="34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N5" s="34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O5" s="33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P5" s="33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q5" s="34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C6" s="35"/>
       <c r="D6" s="36" t="s">
-        <v>76</v>
+        <v>226</v>
       </c>
       <c r="E6" s="37" t="s">
         <v>1</v>
@@ -3083,24 +3150,24 @@
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37">
-        <f>COUNTA(E6:G6)</f>
+        <f t="shared" ref="H6:H37" si="0">COUNTA(E6:G6)</f>
         <v>2</v>
       </c>
       <c r="I6" s="38">
         <v>359</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="L6" s="38">
-        <f>I6/N6</f>
+        <f t="shared" ref="L6:L37" si="1">I6/N6</f>
         <v>179.5</v>
       </c>
       <c r="M6" s="38">
-        <f>IFERROR(L6/H6,"")</f>
+        <f t="shared" ref="M6:M37" si="2">IFERROR(L6/H6,"")</f>
         <v>89.75</v>
       </c>
       <c r="N6" s="39">
@@ -3110,18 +3177,18 @@
         <v>46056</v>
       </c>
       <c r="P6" s="64">
-        <f>IF(N6&lt;&gt;1,EDATE(O6,N6-1),"")</f>
+        <f t="shared" ref="P6:P37" si="3">IF(N6&lt;&gt;1,EDATE(O6,N6-1),"")</f>
         <v>46084</v>
       </c>
       <c r="Q6" s="37">
-        <f ca="1">IF(O6&lt;&gt;"",IFERROR(DATEDIF(O6,TODAY(),"m")+1,""),"")</f>
-        <v>7</v>
+        <f t="shared" ref="Q6:Q24" ca="1" si="4">IF(O6&lt;&gt;"",IFERROR(DATEDIF(O6,TODAY(),"m")+1,""),"")</f>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C7" s="35"/>
       <c r="D7" s="36" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E7" s="37" t="s">
         <v>1</v>
@@ -3129,24 +3196,24 @@
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
       <c r="H7" s="37">
-        <f>COUNTA(E7:G7)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I7" s="38">
         <v>258</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L7" s="38">
-        <f>I7/N7</f>
+        <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="M7" s="38">
-        <f>IFERROR(L7/H7,"")</f>
+        <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="N7" s="39">
@@ -3156,18 +3223,18 @@
         <v>46056</v>
       </c>
       <c r="P7" s="64">
-        <f>IF(N7&lt;&gt;1,EDATE(O7,N7-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46115</v>
       </c>
       <c r="Q7" s="37">
-        <f ca="1">IF(O7&lt;&gt;"",IFERROR(DATEDIF(O7,TODAY(),"m")+1,""),"")</f>
-        <v>7</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C8" s="35"/>
       <c r="D8" s="66" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E8" s="37" t="s">
         <v>1</v>
@@ -3175,24 +3242,24 @@
       <c r="F8" s="37"/>
       <c r="G8" s="37"/>
       <c r="H8" s="37">
-        <f>COUNTA(E8:G8)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I8" s="38">
         <v>1909.3</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K8" s="38" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L8" s="38">
-        <f>I8/N8</f>
+        <f t="shared" si="1"/>
         <v>190.93</v>
       </c>
       <c r="M8" s="38">
-        <f>IFERROR(L8/H8,"")</f>
+        <f t="shared" si="2"/>
         <v>190.93</v>
       </c>
       <c r="N8" s="39">
@@ -3202,18 +3269,18 @@
         <v>46025</v>
       </c>
       <c r="P8" s="64">
-        <f>IF(N8&lt;&gt;1,EDATE(O8,N8-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46298</v>
       </c>
       <c r="Q8" s="37">
-        <f ca="1">IF(O8&lt;&gt;"",IFERROR(DATEDIF(O8,TODAY(),"m")+1,""),"")</f>
-        <v>8</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C9" s="35"/>
       <c r="D9" s="66" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="E9" s="37" t="s">
         <v>1</v>
@@ -3223,24 +3290,24 @@
       </c>
       <c r="G9" s="37"/>
       <c r="H9" s="37">
-        <f>COUNTA(E9:G9)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I9" s="38">
         <v>725</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L9" s="38">
-        <f>I9/N9</f>
+        <f t="shared" si="1"/>
         <v>120.83333333333333</v>
       </c>
       <c r="M9" s="38">
-        <f>IFERROR(L9/H9,"")</f>
+        <f t="shared" si="2"/>
         <v>60.416666666666664</v>
       </c>
       <c r="N9" s="39">
@@ -3250,18 +3317,18 @@
         <v>46145</v>
       </c>
       <c r="P9" s="64">
-        <f>IF(N9&lt;&gt;1,EDATE(O9,N9-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46298</v>
       </c>
       <c r="Q9" s="37">
-        <f ca="1">IF(O9&lt;&gt;"",IFERROR(DATEDIF(O9,TODAY(),"m")+1,""),"")</f>
-        <v>4</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C10" s="35"/>
       <c r="D10" s="66" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>1</v>
@@ -3269,24 +3336,24 @@
       <c r="F10" s="37"/>
       <c r="G10" s="37"/>
       <c r="H10" s="37">
-        <f>COUNTA(E10:G10)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I10" s="38">
         <v>659</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L10" s="38">
-        <f>I10/N10</f>
+        <f t="shared" si="1"/>
         <v>54.916666666666664</v>
       </c>
       <c r="M10" s="38">
-        <f>IFERROR(L10/H10,"")</f>
+        <f t="shared" si="2"/>
         <v>54.916666666666664</v>
       </c>
       <c r="N10" s="39">
@@ -3296,18 +3363,18 @@
         <v>45964</v>
       </c>
       <c r="P10" s="64">
-        <f>IF(N10&lt;&gt;1,EDATE(O10,N10-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46298</v>
       </c>
       <c r="Q10" s="37">
-        <f ca="1">IF(O10&lt;&gt;"",IFERROR(DATEDIF(O10,TODAY(),"m")+1,""),"")</f>
-        <v>10</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C11" s="35"/>
       <c r="D11" s="66" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="E11" s="37" t="s">
         <v>1</v>
@@ -3315,24 +3382,24 @@
       <c r="F11" s="37"/>
       <c r="G11" s="37"/>
       <c r="H11" s="37">
-        <f>COUNTA(E11:G11)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I11" s="38">
         <v>2319.3000000000002</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L11" s="38">
-        <f>I11/N11</f>
+        <f t="shared" si="1"/>
         <v>193.27500000000001</v>
       </c>
       <c r="M11" s="38">
-        <f>IFERROR(L11/H11,"")</f>
+        <f t="shared" si="2"/>
         <v>193.27500000000001</v>
       </c>
       <c r="N11" s="39">
@@ -3342,18 +3409,18 @@
         <v>45964</v>
       </c>
       <c r="P11" s="64">
-        <f>IF(N11&lt;&gt;1,EDATE(O11,N11-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46298</v>
       </c>
       <c r="Q11" s="37">
-        <f ca="1">IF(O11&lt;&gt;"",IFERROR(DATEDIF(O11,TODAY(),"m")+1,""),"")</f>
-        <v>10</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C12" s="35"/>
       <c r="D12" s="66" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E12" s="37" t="s">
         <v>1</v>
@@ -3361,24 +3428,24 @@
       <c r="F12" s="37"/>
       <c r="G12" s="37"/>
       <c r="H12" s="37">
-        <f>COUNTA(E12:G12)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I12" s="38">
         <v>2000</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="L12" s="38">
-        <f>I12/N12</f>
+        <f t="shared" si="1"/>
         <v>166.66666666666666</v>
       </c>
       <c r="M12" s="38">
-        <f>IFERROR(L12/H12,"")</f>
+        <f t="shared" si="2"/>
         <v>166.66666666666666</v>
       </c>
       <c r="N12" s="39">
@@ -3388,18 +3455,18 @@
         <v>45964</v>
       </c>
       <c r="P12" s="64">
-        <f>IF(N12&lt;&gt;1,EDATE(O12,N12-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46298</v>
       </c>
       <c r="Q12" s="37">
-        <f ca="1">IF(O12&lt;&gt;"",IFERROR(DATEDIF(O12,TODAY(),"m")+1,""),"")</f>
-        <v>10</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C13" s="35"/>
       <c r="D13" s="66" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="E13" s="37" t="s">
         <v>1</v>
@@ -3407,24 +3474,24 @@
       <c r="F13" s="37"/>
       <c r="G13" s="37"/>
       <c r="H13" s="37">
-        <f>COUNTA(E13:G13)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I13" s="38">
         <v>372.43</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L13" s="38">
-        <f>I13/N13</f>
+        <f t="shared" si="1"/>
         <v>93.107500000000002</v>
       </c>
       <c r="M13" s="38">
-        <f>IFERROR(L13/H13,"")</f>
+        <f t="shared" si="2"/>
         <v>93.107500000000002</v>
       </c>
       <c r="N13" s="39">
@@ -3434,18 +3501,18 @@
         <v>46206</v>
       </c>
       <c r="P13" s="64">
-        <f>IF(N13&lt;&gt;1,EDATE(O13,N13-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46298</v>
       </c>
       <c r="Q13" s="37">
-        <f ca="1">IF(O13&lt;&gt;"",IFERROR(DATEDIF(O13,TODAY(),"m")+1,""),"")</f>
-        <v>2</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C14" s="35"/>
       <c r="D14" s="66" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>1</v>
@@ -3453,7 +3520,7 @@
       <c r="F14" s="37"/>
       <c r="G14" s="37"/>
       <c r="H14" s="37">
-        <f>COUNTA(E14:G14)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I14" s="38">
@@ -3461,17 +3528,17 @@
         <v>-773.04</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="L14" s="38">
-        <f>I14/N14</f>
+        <f t="shared" si="1"/>
         <v>-64.42</v>
       </c>
       <c r="M14" s="38">
-        <f>IFERROR(L14/H14,"")</f>
+        <f t="shared" si="2"/>
         <v>-64.42</v>
       </c>
       <c r="N14" s="39">
@@ -3481,18 +3548,18 @@
         <v>45964</v>
       </c>
       <c r="P14" s="64">
-        <f>IF(N14&lt;&gt;1,EDATE(O14,N14-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46298</v>
       </c>
       <c r="Q14" s="37">
-        <f ca="1">IF(O14&lt;&gt;"",IFERROR(DATEDIF(O14,TODAY(),"m")+1,""),"")</f>
-        <v>10</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C15" s="35"/>
       <c r="D15" s="66" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="E15" s="37" t="s">
         <v>1</v>
@@ -3500,24 +3567,24 @@
       <c r="F15" s="37"/>
       <c r="G15" s="37"/>
       <c r="H15" s="37">
-        <f>COUNTA(E15:G15)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I15" s="38">
         <v>531</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K15" s="38" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="L15" s="38">
-        <f>I15/N15</f>
+        <f t="shared" si="1"/>
         <v>265.5</v>
       </c>
       <c r="M15" s="38">
-        <f>IFERROR(L15/H15,"")</f>
+        <f t="shared" si="2"/>
         <v>265.5</v>
       </c>
       <c r="N15" s="39">
@@ -3527,18 +3594,18 @@
         <v>46268</v>
       </c>
       <c r="P15" s="64">
-        <f>IF(N15&lt;&gt;1,EDATE(O15,N15-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46298</v>
       </c>
-      <c r="Q15" s="37" t="str">
-        <f ca="1">IF(O15&lt;&gt;"",IFERROR(DATEDIF(O15,TODAY(),"m")+1,""),"")</f>
-        <v/>
+      <c r="Q15" s="37">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C16" s="35"/>
       <c r="D16" s="66" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="E16" s="37"/>
       <c r="F16" s="37" t="s">
@@ -3546,24 +3613,24 @@
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
-        <f>COUNTA(E16:G16)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I16" s="38">
         <v>161.72999999999999</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L16" s="38">
-        <f>I16/N16</f>
+        <f t="shared" si="1"/>
         <v>53.91</v>
       </c>
       <c r="M16" s="38">
-        <f>IFERROR(L16/H16,"")</f>
+        <f t="shared" si="2"/>
         <v>53.91</v>
       </c>
       <c r="N16" s="39">
@@ -3573,18 +3640,18 @@
         <v>46240</v>
       </c>
       <c r="P16" s="64">
-        <f>IF(N16&lt;&gt;1,EDATE(O16,N16-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46301</v>
       </c>
       <c r="Q16" s="37">
-        <f ca="1">IF(O16&lt;&gt;"",IFERROR(DATEDIF(O16,TODAY(),"m")+1,""),"")</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C17" s="35"/>
       <c r="D17" s="66" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E17" s="37" t="s">
         <v>1</v>
@@ -3592,24 +3659,24 @@
       <c r="F17" s="37"/>
       <c r="G17" s="37"/>
       <c r="H17" s="37">
-        <f>COUNTA(E17:G17)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I17" s="38">
         <v>72</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K17" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L17" s="38">
-        <f>I17/N17</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="M17" s="38">
-        <f>IFERROR(L17/H17,"")</f>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="N17" s="39">
@@ -3619,18 +3686,18 @@
         <v>46240</v>
       </c>
       <c r="P17" s="64">
-        <f>IF(N17&lt;&gt;1,EDATE(O17,N17-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46301</v>
       </c>
       <c r="Q17" s="37">
-        <f ca="1">IF(O17&lt;&gt;"",IFERROR(DATEDIF(O17,TODAY(),"m")+1,""),"")</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C18" s="35"/>
       <c r="D18" s="65" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="E18" s="37"/>
       <c r="F18" s="37" t="s">
@@ -3638,24 +3705,24 @@
       </c>
       <c r="G18" s="37"/>
       <c r="H18" s="37">
-        <f>COUNTA(E18:G18)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I18" s="38">
         <v>973.02</v>
       </c>
       <c r="J18" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="L18" s="38">
-        <f>I18/N18</f>
+        <f t="shared" si="1"/>
         <v>81.084999999999994</v>
       </c>
       <c r="M18" s="38">
-        <f>IFERROR(L18/H18,"")</f>
+        <f t="shared" si="2"/>
         <v>81.084999999999994</v>
       </c>
       <c r="N18" s="39">
@@ -3665,18 +3732,18 @@
         <v>45994</v>
       </c>
       <c r="P18" s="64">
-        <f>IF(N18&lt;&gt;1,EDATE(O18,N18-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46329</v>
       </c>
       <c r="Q18" s="37">
-        <f ca="1">IF(O18&lt;&gt;"",IFERROR(DATEDIF(O18,TODAY(),"m")+1,""),"")</f>
-        <v>9</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C19" s="35"/>
       <c r="D19" s="65" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E19" s="37" t="s">
         <v>1</v>
@@ -3684,24 +3751,24 @@
       <c r="F19" s="37"/>
       <c r="G19" s="37"/>
       <c r="H19" s="37">
-        <f>COUNTA(E19:G19)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I19" s="38">
         <v>379</v>
       </c>
       <c r="J19" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K19" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L19" s="38">
-        <f>I19/N19</f>
+        <f t="shared" si="1"/>
         <v>54.142857142857146</v>
       </c>
       <c r="M19" s="38">
-        <f>IFERROR(L19/H19,"")</f>
+        <f t="shared" si="2"/>
         <v>54.142857142857146</v>
       </c>
       <c r="N19" s="39">
@@ -3711,18 +3778,18 @@
         <v>46145</v>
       </c>
       <c r="P19" s="64">
-        <f>IF(N19&lt;&gt;1,EDATE(O19,N19-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46329</v>
       </c>
       <c r="Q19" s="37">
-        <f ca="1">IF(O19&lt;&gt;"",IFERROR(DATEDIF(O19,TODAY(),"m")+1,""),"")</f>
-        <v>4</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C20" s="35"/>
       <c r="D20" s="65" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>1</v>
@@ -3730,24 +3797,24 @@
       <c r="F20" s="37"/>
       <c r="G20" s="37"/>
       <c r="H20" s="37">
-        <f>COUNTA(E20:G20)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I20" s="38">
         <v>297</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L20" s="38">
-        <f>I20/N20</f>
+        <f t="shared" si="1"/>
         <v>49.5</v>
       </c>
       <c r="M20" s="38">
-        <f>IFERROR(L20/H20,"")</f>
+        <f t="shared" si="2"/>
         <v>49.5</v>
       </c>
       <c r="N20" s="39">
@@ -3757,18 +3824,18 @@
         <v>46176</v>
       </c>
       <c r="P20" s="64">
-        <f>IF(N20&lt;&gt;1,EDATE(O20,N20-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46329</v>
       </c>
       <c r="Q20" s="37">
-        <f ca="1">IF(O20&lt;&gt;"",IFERROR(DATEDIF(O20,TODAY(),"m")+1,""),"")</f>
-        <v>3</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C21" s="35"/>
       <c r="D21" s="65" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="E21" s="37" t="s">
         <v>1</v>
@@ -3776,24 +3843,24 @@
       <c r="F21" s="37"/>
       <c r="G21" s="37"/>
       <c r="H21" s="37">
-        <f>COUNTA(E21:G21)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I21" s="38">
         <v>326.99</v>
       </c>
       <c r="J21" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L21" s="38">
-        <f>I21/N21</f>
+        <f t="shared" si="1"/>
         <v>108.99666666666667</v>
       </c>
       <c r="M21" s="38">
-        <f>IFERROR(L21/H21,"")</f>
+        <f t="shared" si="2"/>
         <v>108.99666666666667</v>
       </c>
       <c r="N21" s="39">
@@ -3803,18 +3870,18 @@
         <v>46268</v>
       </c>
       <c r="P21" s="64">
-        <f>IF(N21&lt;&gt;1,EDATE(O21,N21-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46329</v>
       </c>
-      <c r="Q21" s="37" t="str">
-        <f ca="1">IF(O21&lt;&gt;"",IFERROR(DATEDIF(O21,TODAY(),"m")+1,""),"")</f>
-        <v/>
+      <c r="Q21" s="37">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C22" s="35"/>
       <c r="D22" s="70" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>1</v>
@@ -3824,24 +3891,24 @@
       </c>
       <c r="G22" s="37"/>
       <c r="H22" s="37">
-        <f>COUNTA(E22:G22)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I22" s="38">
         <v>209.94</v>
       </c>
       <c r="J22" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L22" s="38">
-        <f>I22/N22</f>
+        <f t="shared" si="1"/>
         <v>52.484999999999999</v>
       </c>
       <c r="M22" s="38">
-        <f>IFERROR(L22/H22,"")</f>
+        <f t="shared" si="2"/>
         <v>26.2425</v>
       </c>
       <c r="N22" s="39">
@@ -3851,18 +3918,18 @@
         <v>46268</v>
       </c>
       <c r="P22" s="64">
-        <f>IF(N22&lt;&gt;1,EDATE(O22,N22-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46359</v>
       </c>
-      <c r="Q22" s="37" t="str">
-        <f ca="1">IF(O22&lt;&gt;"",IFERROR(DATEDIF(O22,TODAY(),"m")+1,""),"")</f>
-        <v/>
+      <c r="Q22" s="37">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C23" s="35"/>
       <c r="D23" s="70" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="E23" s="37" t="s">
         <v>1</v>
@@ -3872,24 +3939,24 @@
       </c>
       <c r="G23" s="37"/>
       <c r="H23" s="37">
-        <f>COUNTA(E23:G23)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I23" s="38">
         <v>249.5</v>
       </c>
       <c r="J23" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L23" s="38">
-        <f>I23/N23</f>
+        <f t="shared" si="1"/>
         <v>62.375</v>
       </c>
       <c r="M23" s="38">
-        <f>IFERROR(L23/H23,"")</f>
+        <f t="shared" si="2"/>
         <v>31.1875</v>
       </c>
       <c r="N23" s="39">
@@ -3899,18 +3966,18 @@
         <v>46268</v>
       </c>
       <c r="P23" s="64">
-        <f>IF(N23&lt;&gt;1,EDATE(O23,N23-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46359</v>
       </c>
-      <c r="Q23" s="37" t="str">
-        <f ca="1">IF(O23&lt;&gt;"",IFERROR(DATEDIF(O23,TODAY(),"m")+1,""),"")</f>
-        <v/>
+      <c r="Q23" s="37">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C24" s="35"/>
       <c r="D24" s="70" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E24" s="37" t="s">
         <v>1</v>
@@ -3920,24 +3987,24 @@
       </c>
       <c r="G24" s="37"/>
       <c r="H24" s="37">
-        <f>COUNTA(E24:G24)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I24" s="38">
         <v>-209.94</v>
       </c>
       <c r="J24" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L24" s="38">
-        <f>I24/N24</f>
+        <f t="shared" si="1"/>
         <v>-52.484999999999999</v>
       </c>
       <c r="M24" s="38">
-        <f>IFERROR(L24/H24,"")</f>
+        <f t="shared" si="2"/>
         <v>-26.2425</v>
       </c>
       <c r="N24" s="39">
@@ -3947,18 +4014,18 @@
         <v>46268</v>
       </c>
       <c r="P24" s="64">
-        <f>IF(N24&lt;&gt;1,EDATE(O24,N24-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46359</v>
       </c>
-      <c r="Q24" s="37" t="str">
-        <f ca="1">IF(O24&lt;&gt;"",IFERROR(DATEDIF(O24,TODAY(),"m")+1,""),"")</f>
-        <v/>
+      <c r="Q24" s="37">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C25" s="35"/>
       <c r="D25" s="46" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E25" s="37" t="s">
         <v>1</v>
@@ -3968,24 +4035,24 @@
       </c>
       <c r="G25" s="37"/>
       <c r="H25" s="37">
-        <f>COUNTA(E25:G25)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I25" s="38">
         <v>506</v>
       </c>
       <c r="J25" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L25" s="38">
-        <f>I25/N25</f>
+        <f t="shared" si="1"/>
         <v>50.6</v>
       </c>
       <c r="M25" s="38">
-        <f>IFERROR(L25/H25,"")</f>
+        <f t="shared" si="2"/>
         <v>25.3</v>
       </c>
       <c r="N25" s="39">
@@ -3995,7 +4062,7 @@
         <v>46115</v>
       </c>
       <c r="P25" s="64">
-        <f>IF(N25&lt;&gt;1,EDATE(O25,N25-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46390</v>
       </c>
       <c r="Q25" s="37"/>
@@ -4003,7 +4070,7 @@
     <row r="26" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C26" s="35"/>
       <c r="D26" s="46" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>1</v>
@@ -4011,24 +4078,24 @@
       <c r="F26" s="37"/>
       <c r="G26" s="37"/>
       <c r="H26" s="37">
-        <f>COUNTA(E26:G26)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I26" s="38">
         <v>399.9</v>
       </c>
       <c r="J26" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L26" s="38">
-        <f>I26/N26</f>
+        <f t="shared" si="1"/>
         <v>57.128571428571426</v>
       </c>
       <c r="M26" s="38">
-        <f>IFERROR(L26/H26,"")</f>
+        <f t="shared" si="2"/>
         <v>57.128571428571426</v>
       </c>
       <c r="N26" s="39">
@@ -4038,18 +4105,18 @@
         <v>46206</v>
       </c>
       <c r="P26" s="64">
-        <f>IF(N26&lt;&gt;1,EDATE(O26,N26-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46390</v>
       </c>
       <c r="Q26" s="37">
-        <f ca="1">IF(O26&lt;&gt;"",IFERROR(DATEDIF(O26,TODAY(),"m")+1,""),"")</f>
-        <v>2</v>
+        <f t="shared" ref="Q26:Q47" ca="1" si="5">IF(O26&lt;&gt;"",IFERROR(DATEDIF(O26,TODAY(),"m")+1,""),"")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C27" s="35"/>
       <c r="D27" s="46" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E27" s="37" t="s">
         <v>1</v>
@@ -4057,24 +4124,24 @@
       <c r="F27" s="37"/>
       <c r="G27" s="37"/>
       <c r="H27" s="37">
-        <f>COUNTA(E27:G27)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I27" s="38">
         <v>284</v>
       </c>
       <c r="J27" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="L27" s="38">
-        <f>I27/N27</f>
+        <f t="shared" si="1"/>
         <v>47.333333333333336</v>
       </c>
       <c r="M27" s="38">
-        <f>IFERROR(L27/H27,"")</f>
+        <f t="shared" si="2"/>
         <v>47.333333333333336</v>
       </c>
       <c r="N27" s="39">
@@ -4084,18 +4151,18 @@
         <v>46237</v>
       </c>
       <c r="P27" s="64">
-        <f>IF(N27&lt;&gt;1,EDATE(O27,N27-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46390</v>
       </c>
       <c r="Q27" s="37">
-        <f ca="1">IF(O27&lt;&gt;"",IFERROR(DATEDIF(O27,TODAY(),"m")+1,""),"")</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C28" s="35"/>
       <c r="D28" s="46" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E28" s="37" t="s">
         <v>1</v>
@@ -4103,24 +4170,24 @@
       <c r="F28" s="37"/>
       <c r="G28" s="37"/>
       <c r="H28" s="37">
-        <f>COUNTA(E28:G28)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I28" s="38">
         <v>500</v>
       </c>
       <c r="J28" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L28" s="38">
-        <f>I28/N28</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="M28" s="38">
-        <f>IFERROR(L28/H28,"")</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="N28" s="39">
@@ -4130,18 +4197,18 @@
         <v>46268</v>
       </c>
       <c r="P28" s="64">
-        <f>IF(N28&lt;&gt;1,EDATE(O28,N28-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46390</v>
       </c>
-      <c r="Q28" s="37" t="str">
-        <f ca="1">IF(O28&lt;&gt;"",IFERROR(DATEDIF(O28,TODAY(),"m")+1,""),"")</f>
-        <v/>
+      <c r="Q28" s="37">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C29" s="35"/>
       <c r="D29" s="46" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>1</v>
@@ -4149,24 +4216,24 @@
       <c r="F29" s="37"/>
       <c r="G29" s="37"/>
       <c r="H29" s="37">
-        <f>COUNTA(E29:G29)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I29" s="38">
         <v>300</v>
       </c>
       <c r="J29" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L29" s="38">
-        <f>I29/N29</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="M29" s="38">
-        <f>IFERROR(L29/H29,"")</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="N29" s="39">
@@ -4176,18 +4243,18 @@
         <v>46237</v>
       </c>
       <c r="P29" s="64">
-        <f>IF(N29&lt;&gt;1,EDATE(O29,N29-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46390</v>
       </c>
       <c r="Q29" s="37">
-        <f ca="1">IF(O29&lt;&gt;"",IFERROR(DATEDIF(O29,TODAY(),"m")+1,""),"")</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C30" s="35"/>
       <c r="D30" s="36" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>1</v>
@@ -4197,24 +4264,24 @@
       </c>
       <c r="G30" s="37"/>
       <c r="H30" s="37">
-        <f>COUNTA(E30:G30)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I30" s="38">
         <v>1017.6</v>
       </c>
       <c r="J30" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L30" s="38">
-        <f>I30/N30</f>
+        <f t="shared" si="1"/>
         <v>84.8</v>
       </c>
       <c r="M30" s="38">
-        <f>IFERROR(L30/H30,"")</f>
+        <f t="shared" si="2"/>
         <v>42.4</v>
       </c>
       <c r="N30" s="39">
@@ -4224,18 +4291,18 @@
         <v>46084</v>
       </c>
       <c r="P30" s="64">
-        <f>IF(N30&lt;&gt;1,EDATE(O30,N30-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46421</v>
       </c>
       <c r="Q30" s="37">
-        <f ca="1">IF(O30&lt;&gt;"",IFERROR(DATEDIF(O30,TODAY(),"m")+1,""),"")</f>
-        <v>6</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C31" s="35"/>
       <c r="D31" s="46" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E31" s="37" t="s">
         <v>1</v>
@@ -4243,24 +4310,24 @@
       <c r="F31" s="37"/>
       <c r="G31" s="37"/>
       <c r="H31" s="37">
-        <f>COUNTA(E31:G31)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I31" s="38">
         <v>1900</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L31" s="38">
-        <f>I31/N31</f>
+        <f t="shared" si="1"/>
         <v>190</v>
       </c>
       <c r="M31" s="38">
-        <f>IFERROR(L31/H31,"")</f>
+        <f t="shared" si="2"/>
         <v>190</v>
       </c>
       <c r="N31" s="39">
@@ -4270,18 +4337,18 @@
         <v>46145</v>
       </c>
       <c r="P31" s="64">
-        <f>IF(N31&lt;&gt;1,EDATE(O31,N31-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46421</v>
       </c>
       <c r="Q31" s="37">
-        <f ca="1">IF(O31&lt;&gt;"",IFERROR(DATEDIF(O31,TODAY(),"m")+1,""),"")</f>
-        <v>4</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C32" s="35"/>
       <c r="D32" s="46" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E32" s="37" t="s">
         <v>1</v>
@@ -4289,24 +4356,24 @@
       <c r="F32" s="37"/>
       <c r="G32" s="37"/>
       <c r="H32" s="37">
-        <f>COUNTA(E32:G32)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I32" s="38">
         <v>474.33</v>
       </c>
       <c r="J32" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K32" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L32" s="38">
-        <f>I32/N32</f>
+        <f t="shared" si="1"/>
         <v>52.703333333333333</v>
       </c>
       <c r="M32" s="38">
-        <f>IFERROR(L32/H32,"")</f>
+        <f t="shared" si="2"/>
         <v>52.703333333333333</v>
       </c>
       <c r="N32" s="39">
@@ -4316,18 +4383,18 @@
         <v>46176</v>
       </c>
       <c r="P32" s="64">
-        <f>IF(N32&lt;&gt;1,EDATE(O32,N32-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46421</v>
       </c>
       <c r="Q32" s="37">
-        <f ca="1">IF(O32&lt;&gt;"",IFERROR(DATEDIF(O32,TODAY(),"m")+1,""),"")</f>
-        <v>3</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C33" s="35"/>
       <c r="D33" s="46" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="E33" s="37" t="s">
         <v>1</v>
@@ -4335,24 +4402,24 @@
       <c r="F33" s="37"/>
       <c r="G33" s="37"/>
       <c r="H33" s="37">
-        <f>COUNTA(E33:G33)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I33" s="38">
         <v>330</v>
       </c>
       <c r="J33" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L33" s="38">
-        <f>I33/N33</f>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="M33" s="38">
-        <f>IFERROR(L33/H33,"")</f>
+        <f t="shared" si="2"/>
         <v>55</v>
       </c>
       <c r="N33" s="39">
@@ -4362,18 +4429,18 @@
         <v>46268</v>
       </c>
       <c r="P33" s="64">
-        <f>IF(N33&lt;&gt;1,EDATE(O33,N33-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46421</v>
       </c>
-      <c r="Q33" s="37" t="str">
-        <f ca="1">IF(O33&lt;&gt;"",IFERROR(DATEDIF(O33,TODAY(),"m")+1,""),"")</f>
-        <v/>
+      <c r="Q33" s="37">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C34" s="35"/>
       <c r="D34" s="46" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="E34" s="37" t="s">
         <v>1</v>
@@ -4383,24 +4450,24 @@
       </c>
       <c r="G34" s="37"/>
       <c r="H34" s="37">
-        <f>COUNTA(E34:G34)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I34" s="38">
         <v>1780</v>
       </c>
       <c r="J34" s="68" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K34" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L34" s="38">
-        <f>I34/N34</f>
+        <f t="shared" si="1"/>
         <v>222.5</v>
       </c>
       <c r="M34" s="38">
-        <f>IFERROR(L34/H34,"")</f>
+        <f t="shared" si="2"/>
         <v>111.25</v>
       </c>
       <c r="N34" s="39">
@@ -4410,18 +4477,18 @@
         <v>46237</v>
       </c>
       <c r="P34" s="64">
-        <f>IF(N34&lt;&gt;1,EDATE(O34,N34-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46449</v>
       </c>
       <c r="Q34" s="37">
-        <f ca="1">IF(O34&lt;&gt;"",IFERROR(DATEDIF(O34,TODAY(),"m")+1,""),"")</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C35" s="35"/>
       <c r="D35" s="46" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E35" s="37" t="s">
         <v>1</v>
@@ -4429,24 +4496,24 @@
       <c r="F35" s="37"/>
       <c r="G35" s="37"/>
       <c r="H35" s="37">
-        <f>COUNTA(E35:G35)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I35" s="38">
         <v>286.39</v>
       </c>
       <c r="J35" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L35" s="38">
-        <f>I35/N35</f>
+        <f t="shared" si="1"/>
         <v>28.638999999999999</v>
       </c>
       <c r="M35" s="38">
-        <f>IFERROR(L35/H35,"")</f>
+        <f t="shared" si="2"/>
         <v>28.638999999999999</v>
       </c>
       <c r="N35" s="39">
@@ -4456,18 +4523,18 @@
         <v>46176</v>
       </c>
       <c r="P35" s="64">
-        <f>IF(N35&lt;&gt;1,EDATE(O35,N35-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46449</v>
       </c>
       <c r="Q35" s="37">
-        <f ca="1">IF(O35&lt;&gt;"",IFERROR(DATEDIF(O35,TODAY(),"m")+1,""),"")</f>
-        <v>3</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C36" s="35"/>
       <c r="D36" s="46" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E36" s="37" t="s">
         <v>1</v>
@@ -4475,24 +4542,24 @@
       <c r="F36" s="37"/>
       <c r="G36" s="37"/>
       <c r="H36" s="37">
-        <f>COUNTA(E36:G36)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I36" s="38">
         <v>1181.1400000000001</v>
       </c>
       <c r="J36" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L36" s="38">
-        <f>I36/N36</f>
+        <f t="shared" si="1"/>
         <v>118.114</v>
       </c>
       <c r="M36" s="38">
-        <f>IFERROR(L36/H36,"")</f>
+        <f t="shared" si="2"/>
         <v>118.114</v>
       </c>
       <c r="N36" s="39">
@@ -4502,18 +4569,18 @@
         <v>46206</v>
       </c>
       <c r="P36" s="64">
-        <f>IF(N36&lt;&gt;1,EDATE(O36,N36-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46480</v>
       </c>
       <c r="Q36" s="37">
-        <f ca="1">IF(O36&lt;&gt;"",IFERROR(DATEDIF(O36,TODAY(),"m")+1,""),"")</f>
-        <v>2</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C37" s="35"/>
       <c r="D37" s="46" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="E37" s="37" t="s">
         <v>1</v>
@@ -4523,24 +4590,24 @@
       </c>
       <c r="G37" s="37"/>
       <c r="H37" s="37">
-        <f>COUNTA(E37:G37)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I37" s="38">
         <v>224.24</v>
       </c>
       <c r="J37" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L37" s="38">
-        <f>I37/N37</f>
+        <f t="shared" si="1"/>
         <v>18.686666666666667</v>
       </c>
       <c r="M37" s="38">
-        <f>IFERROR(L37/H37,"")</f>
+        <f t="shared" si="2"/>
         <v>9.3433333333333337</v>
       </c>
       <c r="N37" s="39">
@@ -4550,20 +4617,20 @@
         <v>46176</v>
       </c>
       <c r="P37" s="64">
-        <f>IF(N37&lt;&gt;1,EDATE(O37,N37-1),"")</f>
+        <f t="shared" si="3"/>
         <v>46510</v>
       </c>
       <c r="Q37" s="37">
-        <f ca="1">IF(O37&lt;&gt;"",IFERROR(DATEDIF(O37,TODAY(),"m")+1,""),"")</f>
-        <v>3</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C38" s="35" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D38" s="46" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>1</v>
@@ -4571,24 +4638,24 @@
       <c r="F38" s="37"/>
       <c r="G38" s="37"/>
       <c r="H38" s="37">
-        <f>COUNTA(E38:G38)</f>
+        <f t="shared" ref="H38:H69" si="6">COUNTA(E38:G38)</f>
         <v>1</v>
       </c>
       <c r="I38" s="38">
         <v>279</v>
       </c>
       <c r="J38" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K38" s="38" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="L38" s="38">
-        <f>I38/N38</f>
+        <f t="shared" ref="L38:L69" si="7">I38/N38</f>
         <v>27.9</v>
       </c>
       <c r="M38" s="38">
-        <f>IFERROR(L38/H38,"")</f>
+        <f t="shared" ref="M38:M69" si="8">IFERROR(L38/H38,"")</f>
         <v>27.9</v>
       </c>
       <c r="N38" s="39">
@@ -4598,18 +4665,18 @@
         <v>46237</v>
       </c>
       <c r="P38" s="64">
-        <f>IF(N38&lt;&gt;1,EDATE(O38,N38-1),"")</f>
+        <f t="shared" ref="P38:P69" si="9">IF(N38&lt;&gt;1,EDATE(O38,N38-1),"")</f>
         <v>46510</v>
       </c>
       <c r="Q38" s="37">
-        <f ca="1">IF(O38&lt;&gt;"",IFERROR(DATEDIF(O38,TODAY(),"m")+1,""),"")</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C39" s="35"/>
       <c r="D39" s="36" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="E39" s="37" t="s">
         <v>1</v>
@@ -4619,24 +4686,24 @@
       </c>
       <c r="G39" s="37"/>
       <c r="H39" s="37">
-        <f>COUNTA(E39:G39)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="I39" s="38">
         <v>22.45</v>
       </c>
       <c r="J39" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K39" s="37" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="L39" s="38">
-        <f>I39/N39</f>
+        <f t="shared" si="7"/>
         <v>22.45</v>
       </c>
       <c r="M39" s="38">
-        <f>IFERROR(L39/H39,"")</f>
+        <f t="shared" si="8"/>
         <v>11.225</v>
       </c>
       <c r="N39" s="39">
@@ -4644,18 +4711,18 @@
       </c>
       <c r="O39" s="64"/>
       <c r="P39" s="64" t="str">
-        <f>IF(N39&lt;&gt;1,EDATE(O39,N39-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q39" s="37" t="str">
-        <f ca="1">IF(O39&lt;&gt;"",IFERROR(DATEDIF(O39,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="40" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C40" s="35"/>
       <c r="D40" s="46" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="E40" s="37" t="s">
         <v>1</v>
@@ -4665,24 +4732,24 @@
       </c>
       <c r="G40" s="37"/>
       <c r="H40" s="37">
-        <f>COUNTA(E40:G40)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="I40" s="38">
         <v>60</v>
       </c>
       <c r="J40" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L40" s="38">
-        <f>I40/N40</f>
+        <f t="shared" si="7"/>
         <v>60</v>
       </c>
       <c r="M40" s="38">
-        <f>IFERROR(L40/H40,"")</f>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
       <c r="N40" s="39">
@@ -4690,18 +4757,18 @@
       </c>
       <c r="O40" s="64"/>
       <c r="P40" s="64" t="str">
-        <f>IF(N40&lt;&gt;1,EDATE(O40,N40-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q40" s="37" t="str">
-        <f ca="1">IF(O40&lt;&gt;"",IFERROR(DATEDIF(O40,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="41" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C41" s="35"/>
       <c r="D41" s="36" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="E41" s="37" t="s">
         <v>1</v>
@@ -4711,24 +4778,24 @@
       </c>
       <c r="G41" s="37"/>
       <c r="H41" s="37">
-        <f>COUNTA(E41:G41)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="I41" s="38">
         <v>395.54</v>
       </c>
       <c r="J41" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K41" s="37" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="L41" s="38">
-        <f>I41/N41</f>
+        <f t="shared" si="7"/>
         <v>395.54</v>
       </c>
       <c r="M41" s="38">
-        <f>IFERROR(L41/H41,"")</f>
+        <f t="shared" si="8"/>
         <v>197.77</v>
       </c>
       <c r="N41" s="39">
@@ -4736,18 +4803,18 @@
       </c>
       <c r="O41" s="64"/>
       <c r="P41" s="64" t="str">
-        <f>IF(N41&lt;&gt;1,EDATE(O41,N41-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q41" s="37" t="str">
-        <f ca="1">IF(O41&lt;&gt;"",IFERROR(DATEDIF(O41,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="42" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C42" s="35"/>
       <c r="D42" s="36" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="E42" s="37" t="s">
         <v>1</v>
@@ -4757,24 +4824,24 @@
       </c>
       <c r="G42" s="37"/>
       <c r="H42" s="37">
-        <f>COUNTA(E42:G42)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="I42" s="38">
         <v>319.42</v>
       </c>
       <c r="J42" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L42" s="38">
-        <f>I42/N42</f>
+        <f t="shared" si="7"/>
         <v>319.42</v>
       </c>
       <c r="M42" s="38">
-        <f>IFERROR(L42/H42,"")</f>
+        <f t="shared" si="8"/>
         <v>159.71</v>
       </c>
       <c r="N42" s="39">
@@ -4782,18 +4849,18 @@
       </c>
       <c r="O42" s="64"/>
       <c r="P42" s="64" t="str">
-        <f>IF(N42&lt;&gt;1,EDATE(O42,N42-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q42" s="37" t="str">
-        <f ca="1">IF(O42&lt;&gt;"",IFERROR(DATEDIF(O42,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C43" s="35"/>
       <c r="D43" s="46" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E43" s="37" t="s">
         <v>1</v>
@@ -4803,24 +4870,24 @@
       </c>
       <c r="G43" s="37"/>
       <c r="H43" s="37">
-        <f>COUNTA(E43:G43)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="I43" s="38">
         <v>225</v>
       </c>
       <c r="J43" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K43" s="37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L43" s="38">
-        <f>I43/N43</f>
+        <f t="shared" si="7"/>
         <v>225</v>
       </c>
       <c r="M43" s="38">
-        <f>IFERROR(L43/H43,"")</f>
+        <f t="shared" si="8"/>
         <v>112.5</v>
       </c>
       <c r="N43" s="39">
@@ -4828,18 +4895,18 @@
       </c>
       <c r="O43" s="64"/>
       <c r="P43" s="64" t="str">
-        <f>IF(N43&lt;&gt;1,EDATE(O43,N43-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q43" s="37" t="str">
-        <f ca="1">IF(O43&lt;&gt;"",IFERROR(DATEDIF(O43,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="44" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C44" s="35"/>
       <c r="D44" s="36" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="E44" s="37" t="s">
         <v>1</v>
@@ -4849,24 +4916,24 @@
       </c>
       <c r="G44" s="37"/>
       <c r="H44" s="37">
-        <f>COUNTA(E44:G44)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="I44" s="38">
         <v>166.15</v>
       </c>
       <c r="J44" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L44" s="38">
-        <f>I44/N44</f>
+        <f t="shared" si="7"/>
         <v>166.15</v>
       </c>
       <c r="M44" s="38">
-        <f>IFERROR(L44/H44,"")</f>
+        <f t="shared" si="8"/>
         <v>83.075000000000003</v>
       </c>
       <c r="N44" s="39">
@@ -4874,18 +4941,18 @@
       </c>
       <c r="O44" s="64"/>
       <c r="P44" s="64" t="str">
-        <f>IF(N44&lt;&gt;1,EDATE(O44,N44-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q44" s="37" t="str">
-        <f ca="1">IF(O44&lt;&gt;"",IFERROR(DATEDIF(O44,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="45" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C45" s="35"/>
       <c r="D45" s="36" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="E45" s="37" t="s">
         <v>1</v>
@@ -4895,24 +4962,24 @@
       </c>
       <c r="G45" s="37"/>
       <c r="H45" s="37">
-        <f>COUNTA(E45:G45)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="I45" s="38">
         <v>19.899999999999999</v>
       </c>
       <c r="J45" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K45" s="37" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="L45" s="38">
-        <f>I45/N45</f>
+        <f t="shared" si="7"/>
         <v>19.899999999999999</v>
       </c>
       <c r="M45" s="38">
-        <f>IFERROR(L45/H45,"")</f>
+        <f t="shared" si="8"/>
         <v>9.9499999999999993</v>
       </c>
       <c r="N45" s="39">
@@ -4920,18 +4987,18 @@
       </c>
       <c r="O45" s="64"/>
       <c r="P45" s="64" t="str">
-        <f>IF(N45&lt;&gt;1,EDATE(O45,N45-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q45" s="37" t="str">
-        <f ca="1">IF(O45&lt;&gt;"",IFERROR(DATEDIF(O45,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C46" s="35"/>
       <c r="D46" s="46" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="E46" s="37" t="s">
         <v>1</v>
@@ -4939,24 +5006,24 @@
       <c r="F46" s="37"/>
       <c r="G46" s="37"/>
       <c r="H46" s="37">
-        <f>COUNTA(E46:G46)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I46" s="38">
         <v>284.05</v>
       </c>
       <c r="J46" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="L46" s="38">
-        <f>I46/N46</f>
+        <f t="shared" si="7"/>
         <v>284.05</v>
       </c>
       <c r="M46" s="38">
-        <f>IFERROR(L46/H46,"")</f>
+        <f t="shared" si="8"/>
         <v>284.05</v>
       </c>
       <c r="N46" s="39">
@@ -4964,18 +5031,18 @@
       </c>
       <c r="O46" s="64"/>
       <c r="P46" s="64" t="str">
-        <f>IF(N46&lt;&gt;1,EDATE(O46,N46-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q46" s="37" t="str">
-        <f ca="1">IF(O46&lt;&gt;"",IFERROR(DATEDIF(O46,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="47" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C47" s="35"/>
       <c r="D47" s="46" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="E47" s="37" t="s">
         <v>1</v>
@@ -4983,24 +5050,24 @@
       <c r="F47" s="37"/>
       <c r="G47" s="37"/>
       <c r="H47" s="37">
-        <f>COUNTA(E47:G47)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I47" s="38">
         <v>110</v>
       </c>
       <c r="J47" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K47" s="38" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="L47" s="38">
-        <f>I47/N47</f>
+        <f t="shared" si="7"/>
         <v>110</v>
       </c>
       <c r="M47" s="38">
-        <f>IFERROR(L47/H47,"")</f>
+        <f t="shared" si="8"/>
         <v>110</v>
       </c>
       <c r="N47" s="39">
@@ -5008,18 +5075,18 @@
       </c>
       <c r="O47" s="64"/>
       <c r="P47" s="64" t="str">
-        <f>IF(N47&lt;&gt;1,EDATE(O47,N47-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q47" s="37" t="str">
-        <f ca="1">IF(O47&lt;&gt;"",IFERROR(DATEDIF(O47,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
     </row>
     <row r="48" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C48" s="35"/>
       <c r="D48" s="46" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="E48" s="37" t="s">
         <v>1</v>
@@ -5027,24 +5094,24 @@
       <c r="F48" s="37"/>
       <c r="G48" s="37"/>
       <c r="H48" s="37">
-        <f>COUNTA(E48:G48)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I48" s="38">
         <v>118.4</v>
       </c>
       <c r="J48" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K48" s="38" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="L48" s="38">
-        <f>I48/N48</f>
+        <f t="shared" si="7"/>
         <v>118.4</v>
       </c>
       <c r="M48" s="38">
-        <f>IFERROR(L48/H48,"")</f>
+        <f t="shared" si="8"/>
         <v>118.4</v>
       </c>
       <c r="N48" s="39">
@@ -5052,7 +5119,7 @@
       </c>
       <c r="O48" s="64"/>
       <c r="P48" s="64" t="str">
-        <f>IF(N48&lt;&gt;1,EDATE(O48,N48-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q48" s="37"/>
@@ -5060,7 +5127,7 @@
     <row r="49" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C49" s="35"/>
       <c r="D49" s="36" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="E49" s="37" t="s">
         <v>1</v>
@@ -5068,24 +5135,24 @@
       <c r="F49" s="37"/>
       <c r="G49" s="37"/>
       <c r="H49" s="37">
-        <f>COUNTA(E49:G49)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I49" s="38">
         <v>26.9</v>
       </c>
       <c r="J49" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K49" s="37" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="L49" s="38">
-        <f>I49/N49</f>
+        <f t="shared" si="7"/>
         <v>26.9</v>
       </c>
       <c r="M49" s="38">
-        <f>IFERROR(L49/H49,"")</f>
+        <f t="shared" si="8"/>
         <v>26.9</v>
       </c>
       <c r="N49" s="39">
@@ -5093,7 +5160,7 @@
       </c>
       <c r="O49" s="64"/>
       <c r="P49" s="64" t="str">
-        <f>IF(N49&lt;&gt;1,EDATE(O49,N49-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q49" s="37" t="str">
@@ -5104,7 +5171,7 @@
     <row r="50" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C50" s="35"/>
       <c r="D50" s="46" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="E50" s="37" t="s">
         <v>1</v>
@@ -5112,24 +5179,24 @@
       <c r="F50" s="37"/>
       <c r="G50" s="37"/>
       <c r="H50" s="37">
-        <f>COUNTA(E50:G50)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I50" s="38">
         <v>70</v>
       </c>
       <c r="J50" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K50" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L50" s="38">
-        <f>I50/N50</f>
+        <f t="shared" si="7"/>
         <v>70</v>
       </c>
       <c r="M50" s="38">
-        <f>IFERROR(L50/H50,"")</f>
+        <f t="shared" si="8"/>
         <v>70</v>
       </c>
       <c r="N50" s="39">
@@ -5137,7 +5204,7 @@
       </c>
       <c r="O50" s="64"/>
       <c r="P50" s="64" t="str">
-        <f>IF(N50&lt;&gt;1,EDATE(O50,N50-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q50" s="37"/>
@@ -5145,7 +5212,7 @@
     <row r="51" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C51" s="35"/>
       <c r="D51" s="67" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="E51" s="37" t="s">
         <v>1</v>
@@ -5153,24 +5220,24 @@
       <c r="F51" s="37"/>
       <c r="G51" s="37"/>
       <c r="H51" s="37">
-        <f>COUNTA(E51:G51)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I51" s="38">
         <v>415</v>
       </c>
       <c r="J51" s="38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K51" s="38" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L51" s="38">
-        <f>I51/N51</f>
+        <f t="shared" si="7"/>
         <v>415</v>
       </c>
       <c r="M51" s="38">
-        <f>IFERROR(L51/H51,"")</f>
+        <f t="shared" si="8"/>
         <v>415</v>
       </c>
       <c r="N51" s="39">
@@ -5178,555 +5245,755 @@
       </c>
       <c r="O51" s="64"/>
       <c r="P51" s="64" t="str">
-        <f>IF(N51&lt;&gt;1,EDATE(O51,N51-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q51" s="37" t="str">
-        <f ca="1">IF(O51&lt;&gt;"",IFERROR(DATEDIF(O51,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ref="Q51:Q82" ca="1" si="10">IF(O51&lt;&gt;"",IFERROR(DATEDIF(O51,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="52" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C52" s="35"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
+      <c r="D52" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="E52" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G52" s="37"/>
       <c r="H52" s="37">
-        <f>COUNTA(E52:G52)</f>
-        <v>0</v>
-      </c>
-      <c r="I52" s="38"/>
-      <c r="J52" s="38"/>
-      <c r="K52" s="38"/>
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="I52" s="38">
+        <v>-43</v>
+      </c>
+      <c r="J52" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="K52" s="38" t="s">
+        <v>112</v>
+      </c>
       <c r="L52" s="38">
-        <f>I52/N52</f>
-        <v>0</v>
-      </c>
-      <c r="M52" s="38" t="str">
-        <f>IFERROR(L52/H52,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>-43</v>
+      </c>
+      <c r="M52" s="38">
+        <f t="shared" si="8"/>
+        <v>-21.5</v>
       </c>
       <c r="N52" s="39">
         <v>1</v>
       </c>
       <c r="O52" s="64"/>
       <c r="P52" s="64" t="str">
-        <f>IF(N52&lt;&gt;1,EDATE(O52,N52-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q52" s="37" t="str">
-        <f ca="1">IF(O52&lt;&gt;"",IFERROR(DATEDIF(O52,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="53" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C53" s="35"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
+      <c r="D53" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="E53" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G53" s="37"/>
       <c r="H53" s="37">
-        <f>COUNTA(E53:G53)</f>
-        <v>0</v>
-      </c>
-      <c r="I53" s="38"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="I53" s="38">
+        <v>217.85</v>
+      </c>
+      <c r="J53" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="K53" s="38" t="s">
+        <v>53</v>
+      </c>
       <c r="L53" s="38">
-        <f>I53/N53</f>
-        <v>0</v>
-      </c>
-      <c r="M53" s="38" t="str">
-        <f>IFERROR(L53/H53,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>108.925</v>
+      </c>
+      <c r="M53" s="38">
+        <f t="shared" si="8"/>
+        <v>54.462499999999999</v>
       </c>
       <c r="N53" s="39">
-        <v>1</v>
-      </c>
-      <c r="O53" s="64"/>
-      <c r="P53" s="64" t="str">
-        <f>IF(N53&lt;&gt;1,EDATE(O53,N53-1),"")</f>
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="O53" s="64">
+        <v>46298</v>
+      </c>
+      <c r="P53" s="64">
+        <f t="shared" si="9"/>
+        <v>46329</v>
       </c>
       <c r="Q53" s="37" t="str">
-        <f ca="1">IF(O53&lt;&gt;"",IFERROR(DATEDIF(O53,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="54" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C54" s="35"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="37"/>
+      <c r="D54" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="E54" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F54" s="37"/>
       <c r="G54" s="37"/>
       <c r="H54" s="37">
-        <f>COUNTA(E54:G54)</f>
-        <v>0</v>
-      </c>
-      <c r="I54" s="38"/>
-      <c r="J54" s="38"/>
-      <c r="K54" s="38"/>
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="I54" s="38">
+        <v>300</v>
+      </c>
+      <c r="J54" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="K54" s="38" t="s">
+        <v>59</v>
+      </c>
       <c r="L54" s="38">
-        <f>I54/N54</f>
-        <v>0</v>
-      </c>
-      <c r="M54" s="38" t="str">
-        <f>IFERROR(L54/H54,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>50</v>
+      </c>
+      <c r="M54" s="38">
+        <f t="shared" si="8"/>
+        <v>50</v>
       </c>
       <c r="N54" s="39">
-        <v>1</v>
-      </c>
-      <c r="O54" s="64"/>
-      <c r="P54" s="64" t="str">
-        <f>IF(N54&lt;&gt;1,EDATE(O54,N54-1),"")</f>
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="O54" s="64">
+        <v>46298</v>
+      </c>
+      <c r="P54" s="64">
+        <f t="shared" si="9"/>
+        <v>46449</v>
       </c>
       <c r="Q54" s="37" t="str">
-        <f ca="1">IF(O54&lt;&gt;"",IFERROR(DATEDIF(O54,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="55" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C55" s="35"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="37"/>
+      <c r="D55" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="E55" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F55" s="37"/>
       <c r="G55" s="37"/>
       <c r="H55" s="37">
-        <f>COUNTA(E55:G55)</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="38"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="38"/>
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="I55" s="38">
+        <f>SUM(17.94+19.97)</f>
+        <v>37.909999999999997</v>
+      </c>
+      <c r="J55" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="K55" s="38" t="s">
+        <v>230</v>
+      </c>
       <c r="L55" s="38">
-        <f>I55/N55</f>
-        <v>0</v>
-      </c>
-      <c r="M55" s="38" t="str">
-        <f>IFERROR(L55/H55,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>37.909999999999997</v>
+      </c>
+      <c r="M55" s="38">
+        <f t="shared" si="8"/>
+        <v>37.909999999999997</v>
       </c>
       <c r="N55" s="39">
         <v>1</v>
       </c>
-      <c r="O55" s="64"/>
+      <c r="O55" s="64">
+        <v>46298</v>
+      </c>
       <c r="P55" s="64" t="str">
-        <f>IF(N55&lt;&gt;1,EDATE(O55,N55-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q55" s="37" t="str">
-        <f ca="1">IF(O55&lt;&gt;"",IFERROR(DATEDIF(O55,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="56" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C56" s="35"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
+      <c r="D56" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="E56" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G56" s="37"/>
       <c r="H56" s="37">
-        <f>COUNTA(E56:G56)</f>
-        <v>0</v>
-      </c>
-      <c r="I56" s="38"/>
-      <c r="J56" s="38"/>
-      <c r="K56" s="38"/>
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="I56" s="38">
+        <v>66</v>
+      </c>
+      <c r="J56" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="K56" s="38" t="s">
+        <v>233</v>
+      </c>
       <c r="L56" s="38">
-        <f>I56/N56</f>
-        <v>0</v>
-      </c>
-      <c r="M56" s="38" t="str">
-        <f>IFERROR(L56/H56,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>66</v>
+      </c>
+      <c r="M56" s="38">
+        <f t="shared" si="8"/>
+        <v>33</v>
       </c>
       <c r="N56" s="39">
         <v>1</v>
       </c>
-      <c r="O56" s="64"/>
+      <c r="O56" s="64">
+        <v>46298</v>
+      </c>
       <c r="P56" s="64" t="str">
-        <f>IF(N56&lt;&gt;1,EDATE(O56,N56-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q56" s="37" t="str">
-        <f ca="1">IF(O56&lt;&gt;"",IFERROR(DATEDIF(O56,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="35"/>
-      <c r="D57" s="46"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
+      <c r="D57" s="46" t="s">
+        <v>242</v>
+      </c>
+      <c r="E57" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G57" s="37"/>
       <c r="H57" s="37">
-        <f>COUNTA(E57:G57)</f>
-        <v>0</v>
-      </c>
-      <c r="I57" s="38"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="38"/>
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="I57" s="38">
+        <v>265</v>
+      </c>
+      <c r="J57" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="K57" s="38" t="s">
+        <v>230</v>
+      </c>
       <c r="L57" s="38">
-        <f>I57/N57</f>
-        <v>0</v>
-      </c>
-      <c r="M57" s="38" t="str">
-        <f>IFERROR(L57/H57,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>265</v>
+      </c>
+      <c r="M57" s="38">
+        <f t="shared" si="8"/>
+        <v>132.5</v>
       </c>
       <c r="N57" s="39">
         <v>1</v>
       </c>
-      <c r="O57" s="64"/>
+      <c r="O57" s="64">
+        <v>46298</v>
+      </c>
       <c r="P57" s="64" t="str">
-        <f>IF(N57&lt;&gt;1,EDATE(O57,N57-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q57" s="37" t="str">
-        <f ca="1">IF(O57&lt;&gt;"",IFERROR(DATEDIF(O57,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="58" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C58" s="35"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="37"/>
+      <c r="D58" s="79" t="s">
+        <v>234</v>
+      </c>
+      <c r="E58" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F58" s="37"/>
       <c r="G58" s="37"/>
       <c r="H58" s="37">
-        <f>COUNTA(E58:G58)</f>
-        <v>0</v>
-      </c>
-      <c r="I58" s="38"/>
-      <c r="J58" s="38"/>
-      <c r="K58" s="38"/>
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="I58" s="38">
+        <f>170+199</f>
+        <v>369</v>
+      </c>
+      <c r="J58" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="K58" s="38" t="s">
+        <v>233</v>
+      </c>
       <c r="L58" s="38">
-        <f>I58/N58</f>
-        <v>0</v>
-      </c>
-      <c r="M58" s="38" t="str">
-        <f>IFERROR(L58/H58,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>369</v>
+      </c>
+      <c r="M58" s="38">
+        <f t="shared" si="8"/>
+        <v>369</v>
       </c>
       <c r="N58" s="39">
         <v>1</v>
       </c>
-      <c r="O58" s="64"/>
+      <c r="O58" s="64">
+        <v>46298</v>
+      </c>
       <c r="P58" s="64" t="str">
-        <f>IF(N58&lt;&gt;1,EDATE(O58,N58-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q58" s="37" t="str">
-        <f ca="1">IF(O58&lt;&gt;"",IFERROR(DATEDIF(O58,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="59" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C59" s="35"/>
-      <c r="D59" s="46"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
+      <c r="D59" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G59" s="37"/>
       <c r="H59" s="37">
-        <f>COUNTA(E59:G59)</f>
-        <v>0</v>
-      </c>
-      <c r="I59" s="38"/>
-      <c r="J59" s="38"/>
-      <c r="K59" s="38"/>
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="I59" s="38">
+        <v>120</v>
+      </c>
+      <c r="J59" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="K59" s="38" t="s">
+        <v>233</v>
+      </c>
       <c r="L59" s="38">
-        <f>I59/N59</f>
-        <v>0</v>
-      </c>
-      <c r="M59" s="38" t="str">
-        <f>IFERROR(L59/H59,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>120</v>
+      </c>
+      <c r="M59" s="38">
+        <f t="shared" si="8"/>
+        <v>60</v>
       </c>
       <c r="N59" s="39">
         <v>1</v>
       </c>
-      <c r="O59" s="64"/>
+      <c r="O59" s="64">
+        <v>46298</v>
+      </c>
       <c r="P59" s="64" t="str">
-        <f>IF(N59&lt;&gt;1,EDATE(O59,N59-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q59" s="37" t="str">
-        <f ca="1">IF(O59&lt;&gt;"",IFERROR(DATEDIF(O59,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="60" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C60" s="35"/>
-      <c r="D60" s="46"/>
-      <c r="E60" s="37"/>
+      <c r="D60" s="46" t="s">
+        <v>236</v>
+      </c>
+      <c r="E60" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F60" s="37"/>
       <c r="G60" s="37"/>
       <c r="H60" s="37">
-        <f>COUNTA(E60:G60)</f>
-        <v>0</v>
-      </c>
-      <c r="I60" s="38"/>
-      <c r="J60" s="38"/>
-      <c r="K60" s="38"/>
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="I60" s="38">
+        <v>85</v>
+      </c>
+      <c r="J60" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="K60" s="38" t="s">
+        <v>59</v>
+      </c>
       <c r="L60" s="38">
-        <f>I60/N60</f>
-        <v>0</v>
-      </c>
-      <c r="M60" s="38" t="str">
-        <f>IFERROR(L60/H60,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>85</v>
+      </c>
+      <c r="M60" s="38">
+        <f t="shared" si="8"/>
+        <v>85</v>
       </c>
       <c r="N60" s="39">
         <v>1</v>
       </c>
-      <c r="O60" s="64"/>
+      <c r="O60" s="64">
+        <v>46298</v>
+      </c>
       <c r="P60" s="64" t="str">
-        <f>IF(N60&lt;&gt;1,EDATE(O60,N60-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q60" s="37" t="str">
-        <f ca="1">IF(O60&lt;&gt;"",IFERROR(DATEDIF(O60,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="61" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C61" s="35"/>
-      <c r="D61" s="46"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
+      <c r="D61" s="46" t="s">
+        <v>237</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G61" s="37"/>
       <c r="H61" s="37">
-        <f>COUNTA(E61:G61)</f>
-        <v>0</v>
-      </c>
-      <c r="I61" s="38"/>
-      <c r="J61" s="38"/>
-      <c r="K61" s="38"/>
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="I61" s="38">
+        <f>(128.68/3)*2</f>
+        <v>85.786666666666676</v>
+      </c>
+      <c r="J61" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="K61" s="38" t="s">
+        <v>233</v>
+      </c>
       <c r="L61" s="38">
-        <f>I61/N61</f>
-        <v>0</v>
-      </c>
-      <c r="M61" s="38" t="str">
-        <f>IFERROR(L61/H61,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>85.786666666666676</v>
+      </c>
+      <c r="M61" s="38">
+        <f t="shared" si="8"/>
+        <v>42.893333333333338</v>
       </c>
       <c r="N61" s="39">
         <v>1</v>
       </c>
-      <c r="O61" s="64"/>
+      <c r="O61" s="64">
+        <v>46298</v>
+      </c>
       <c r="P61" s="64" t="str">
-        <f>IF(N61&lt;&gt;1,EDATE(O61,N61-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q61" s="37" t="str">
-        <f ca="1">IF(O61&lt;&gt;"",IFERROR(DATEDIF(O61,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="62" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C62" s="35"/>
-      <c r="D62" s="46"/>
+      <c r="D62" s="46" t="s">
+        <v>238</v>
+      </c>
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
       <c r="G62" s="37"/>
       <c r="H62" s="37">
-        <f>COUNTA(E62:G62)</f>
-        <v>0</v>
-      </c>
-      <c r="I62" s="38"/>
-      <c r="J62" s="38"/>
-      <c r="K62" s="38"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="38">
+        <f>85.79/2</f>
+        <v>42.895000000000003</v>
+      </c>
+      <c r="J62" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="K62" s="38" t="s">
+        <v>233</v>
+      </c>
       <c r="L62" s="38">
-        <f>I62/N62</f>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>42.895000000000003</v>
       </c>
       <c r="M62" s="38" t="str">
-        <f>IFERROR(L62/H62,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="N62" s="39">
         <v>1</v>
       </c>
-      <c r="O62" s="64"/>
+      <c r="O62" s="64">
+        <v>46298</v>
+      </c>
       <c r="P62" s="64" t="str">
-        <f>IF(N62&lt;&gt;1,EDATE(O62,N62-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q62" s="37" t="str">
-        <f ca="1">IF(O62&lt;&gt;"",IFERROR(DATEDIF(O62,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="63" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C63" s="35"/>
-      <c r="D63" s="46"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
+      <c r="D63" s="46" t="s">
+        <v>239</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G63" s="37"/>
       <c r="H63" s="37">
-        <f>COUNTA(E63:G63)</f>
-        <v>0</v>
-      </c>
-      <c r="I63" s="38"/>
-      <c r="J63" s="38"/>
-      <c r="K63" s="38"/>
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="I63" s="38">
+        <v>40</v>
+      </c>
+      <c r="J63" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="K63" s="38" t="s">
+        <v>230</v>
+      </c>
       <c r="L63" s="38">
-        <f>I63/N63</f>
-        <v>0</v>
-      </c>
-      <c r="M63" s="38" t="str">
-        <f>IFERROR(L63/H63,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="M63" s="38">
+        <f t="shared" si="8"/>
+        <v>20</v>
       </c>
       <c r="N63" s="39">
         <v>1</v>
       </c>
-      <c r="O63" s="64"/>
+      <c r="O63" s="64">
+        <v>46298</v>
+      </c>
       <c r="P63" s="64" t="str">
-        <f>IF(N63&lt;&gt;1,EDATE(O63,N63-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q63" s="37" t="str">
-        <f ca="1">IF(O63&lt;&gt;"",IFERROR(DATEDIF(O63,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="64" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C64" s="35"/>
-      <c r="D64" s="46"/>
+      <c r="D64" s="46" t="s">
+        <v>240</v>
+      </c>
       <c r="E64" s="37"/>
       <c r="F64" s="37"/>
       <c r="G64" s="37"/>
       <c r="H64" s="37">
-        <f>COUNTA(E64:G64)</f>
-        <v>0</v>
-      </c>
-      <c r="I64" s="38"/>
-      <c r="J64" s="38"/>
-      <c r="K64" s="38"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I64" s="38">
+        <v>20</v>
+      </c>
+      <c r="J64" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="K64" s="38" t="s">
+        <v>230</v>
+      </c>
       <c r="L64" s="38">
-        <f>I64/N64</f>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="M64" s="38" t="str">
-        <f>IFERROR(L64/H64,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="N64" s="39">
         <v>1</v>
       </c>
-      <c r="O64" s="64"/>
+      <c r="O64" s="64">
+        <v>46298</v>
+      </c>
       <c r="P64" s="64" t="str">
-        <f>IF(N64&lt;&gt;1,EDATE(O64,N64-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q64" s="37" t="str">
-        <f ca="1">IF(O64&lt;&gt;"",IFERROR(DATEDIF(O64,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="65" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C65" s="35"/>
-      <c r="D65" s="46"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="37"/>
+      <c r="D65" s="46" t="s">
+        <v>241</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G65" s="37"/>
       <c r="H65" s="37">
-        <f>COUNTA(E65:G65)</f>
-        <v>0</v>
-      </c>
-      <c r="I65" s="38"/>
-      <c r="J65" s="38"/>
-      <c r="K65" s="38"/>
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="I65" s="38">
+        <v>56.42</v>
+      </c>
+      <c r="J65" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="K65" s="38" t="s">
+        <v>233</v>
+      </c>
       <c r="L65" s="38">
-        <f>I65/N65</f>
-        <v>0</v>
-      </c>
-      <c r="M65" s="38" t="str">
-        <f>IFERROR(L65/H65,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>56.42</v>
+      </c>
+      <c r="M65" s="38">
+        <f t="shared" si="8"/>
+        <v>28.21</v>
       </c>
       <c r="N65" s="39">
         <v>1</v>
       </c>
       <c r="O65" s="64"/>
       <c r="P65" s="64" t="str">
-        <f>IF(N65&lt;&gt;1,EDATE(O65,N65-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q65" s="37" t="str">
-        <f ca="1">IF(O65&lt;&gt;"",IFERROR(DATEDIF(O65,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="66" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C66" s="35"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="37"/>
+      <c r="D66" s="46" t="s">
+        <v>243</v>
+      </c>
+      <c r="E66" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F66" s="37"/>
       <c r="G66" s="37"/>
       <c r="H66" s="37">
-        <f>COUNTA(E66:G66)</f>
-        <v>0</v>
-      </c>
-      <c r="I66" s="38"/>
-      <c r="J66" s="38"/>
-      <c r="K66" s="38"/>
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="I66" s="38">
+        <v>-338</v>
+      </c>
+      <c r="J66" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="K66" s="38" t="s">
+        <v>112</v>
+      </c>
       <c r="L66" s="38">
-        <f>I66/N66</f>
-        <v>0</v>
-      </c>
-      <c r="M66" s="38" t="str">
-        <f>IFERROR(L66/H66,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>-338</v>
+      </c>
+      <c r="M66" s="38">
+        <f t="shared" si="8"/>
+        <v>-338</v>
       </c>
       <c r="N66" s="39">
         <v>1</v>
       </c>
       <c r="O66" s="64"/>
       <c r="P66" s="64" t="str">
-        <f>IF(N66&lt;&gt;1,EDATE(O66,N66-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q66" s="37" t="str">
-        <f ca="1">IF(O66&lt;&gt;"",IFERROR(DATEDIF(O66,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="67" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C67" s="35"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="37"/>
+      <c r="D67" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F67" s="37"/>
       <c r="G67" s="37"/>
       <c r="H67" s="37">
-        <f>COUNTA(E67:G67)</f>
-        <v>0</v>
-      </c>
-      <c r="I67" s="38"/>
-      <c r="J67" s="38"/>
-      <c r="K67" s="38"/>
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="I67" s="38">
+        <v>638</v>
+      </c>
+      <c r="J67" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="K67" s="38" t="s">
+        <v>68</v>
+      </c>
       <c r="L67" s="38">
-        <f>I67/N67</f>
-        <v>0</v>
-      </c>
-      <c r="M67" s="38" t="str">
-        <f>IFERROR(L67/H67,"")</f>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>638</v>
+      </c>
+      <c r="M67" s="38">
+        <f t="shared" si="8"/>
+        <v>638</v>
       </c>
       <c r="N67" s="39">
         <v>1</v>
       </c>
       <c r="O67" s="64"/>
       <c r="P67" s="64" t="str">
-        <f>IF(N67&lt;&gt;1,EDATE(O67,N67-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q67" s="37" t="str">
-        <f ca="1">IF(O67&lt;&gt;"",IFERROR(DATEDIF(O67,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -5737,18 +6004,18 @@
       <c r="F68" s="37"/>
       <c r="G68" s="37"/>
       <c r="H68" s="37">
-        <f>COUNTA(E68:G68)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I68" s="38"/>
       <c r="J68" s="38"/>
       <c r="K68" s="38"/>
       <c r="L68" s="38">
-        <f>I68/N68</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M68" s="38" t="str">
-        <f>IFERROR(L68/H68,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="N68" s="39">
@@ -5756,11 +6023,11 @@
       </c>
       <c r="O68" s="64"/>
       <c r="P68" s="64" t="str">
-        <f>IF(N68&lt;&gt;1,EDATE(O68,N68-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q68" s="37" t="str">
-        <f ca="1">IF(O68&lt;&gt;"",IFERROR(DATEDIF(O68,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -5771,18 +6038,18 @@
       <c r="F69" s="37"/>
       <c r="G69" s="37"/>
       <c r="H69" s="37">
-        <f>COUNTA(E69:G69)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I69" s="38"/>
       <c r="J69" s="38"/>
       <c r="K69" s="38"/>
       <c r="L69" s="38">
-        <f>I69/N69</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M69" s="38" t="str">
-        <f>IFERROR(L69/H69,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="N69" s="39">
@@ -5790,11 +6057,11 @@
       </c>
       <c r="O69" s="64"/>
       <c r="P69" s="64" t="str">
-        <f>IF(N69&lt;&gt;1,EDATE(O69,N69-1),"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q69" s="37" t="str">
-        <f ca="1">IF(O69&lt;&gt;"",IFERROR(DATEDIF(O69,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -5805,18 +6072,18 @@
       <c r="F70" s="37"/>
       <c r="G70" s="37"/>
       <c r="H70" s="37">
-        <f>COUNTA(E70:G70)</f>
+        <f t="shared" ref="H70:H101" si="11">COUNTA(E70:G70)</f>
         <v>0</v>
       </c>
       <c r="I70" s="38"/>
       <c r="J70" s="38"/>
       <c r="K70" s="38"/>
       <c r="L70" s="38">
-        <f>I70/N70</f>
+        <f t="shared" ref="L70:L101" si="12">I70/N70</f>
         <v>0</v>
       </c>
       <c r="M70" s="38" t="str">
-        <f>IFERROR(L70/H70,"")</f>
+        <f t="shared" ref="M70:M101" si="13">IFERROR(L70/H70,"")</f>
         <v/>
       </c>
       <c r="N70" s="39">
@@ -5824,11 +6091,11 @@
       </c>
       <c r="O70" s="64"/>
       <c r="P70" s="64" t="str">
-        <f>IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
+        <f t="shared" ref="P70:P101" si="14">IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
         <v/>
       </c>
       <c r="Q70" s="37" t="str">
-        <f ca="1">IF(O70&lt;&gt;"",IFERROR(DATEDIF(O70,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -5839,18 +6106,18 @@
       <c r="F71" s="37"/>
       <c r="G71" s="37"/>
       <c r="H71" s="37">
-        <f>COUNTA(E71:G71)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I71" s="38"/>
       <c r="J71" s="38"/>
       <c r="K71" s="38"/>
       <c r="L71" s="38">
-        <f>I71/N71</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M71" s="38" t="str">
-        <f>IFERROR(L71/H71,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N71" s="39">
@@ -5858,11 +6125,11 @@
       </c>
       <c r="O71" s="64"/>
       <c r="P71" s="64" t="str">
-        <f>IF(N71&lt;&gt;1,EDATE(O71,N71-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q71" s="37" t="str">
-        <f ca="1">IF(O71&lt;&gt;"",IFERROR(DATEDIF(O71,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -5873,18 +6140,18 @@
       <c r="F72" s="37"/>
       <c r="G72" s="37"/>
       <c r="H72" s="37">
-        <f>COUNTA(E72:G72)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I72" s="38"/>
       <c r="J72" s="38"/>
       <c r="K72" s="38"/>
       <c r="L72" s="38">
-        <f>I72/N72</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M72" s="38" t="str">
-        <f>IFERROR(L72/H72,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N72" s="39">
@@ -5892,11 +6159,11 @@
       </c>
       <c r="O72" s="64"/>
       <c r="P72" s="64" t="str">
-        <f>IF(N72&lt;&gt;1,EDATE(O72,N72-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q72" s="37" t="str">
-        <f ca="1">IF(O72&lt;&gt;"",IFERROR(DATEDIF(O72,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -5907,18 +6174,18 @@
       <c r="F73" s="37"/>
       <c r="G73" s="37"/>
       <c r="H73" s="37">
-        <f>COUNTA(E73:G73)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I73" s="38"/>
       <c r="J73" s="38"/>
       <c r="K73" s="38"/>
       <c r="L73" s="38">
-        <f>I73/N73</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M73" s="38" t="str">
-        <f>IFERROR(L73/H73,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N73" s="39">
@@ -5926,11 +6193,11 @@
       </c>
       <c r="O73" s="64"/>
       <c r="P73" s="64" t="str">
-        <f>IF(N73&lt;&gt;1,EDATE(O73,N73-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q73" s="37" t="str">
-        <f ca="1">IF(O73&lt;&gt;"",IFERROR(DATEDIF(O73,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -5941,18 +6208,18 @@
       <c r="F74" s="37"/>
       <c r="G74" s="37"/>
       <c r="H74" s="37">
-        <f>COUNTA(E74:G74)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I74" s="38"/>
       <c r="J74" s="38"/>
       <c r="K74" s="38"/>
       <c r="L74" s="38">
-        <f>I74/N74</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M74" s="38" t="str">
-        <f>IFERROR(L74/H74,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N74" s="39">
@@ -5960,11 +6227,11 @@
       </c>
       <c r="O74" s="64"/>
       <c r="P74" s="64" t="str">
-        <f>IF(N74&lt;&gt;1,EDATE(O74,N74-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q74" s="37" t="str">
-        <f ca="1">IF(O74&lt;&gt;"",IFERROR(DATEDIF(O74,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -5975,18 +6242,18 @@
       <c r="F75" s="37"/>
       <c r="G75" s="37"/>
       <c r="H75" s="37">
-        <f>COUNTA(E75:G75)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I75" s="38"/>
       <c r="J75" s="38"/>
       <c r="K75" s="38"/>
       <c r="L75" s="38">
-        <f>I75/N75</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M75" s="38" t="str">
-        <f>IFERROR(L75/H75,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N75" s="39">
@@ -5994,11 +6261,11 @@
       </c>
       <c r="O75" s="64"/>
       <c r="P75" s="64" t="str">
-        <f>IF(N75&lt;&gt;1,EDATE(O75,N75-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q75" s="37" t="str">
-        <f ca="1">IF(O75&lt;&gt;"",IFERROR(DATEDIF(O75,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -6009,18 +6276,18 @@
       <c r="F76" s="37"/>
       <c r="G76" s="37"/>
       <c r="H76" s="37">
-        <f>COUNTA(E76:G76)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I76" s="38"/>
       <c r="J76" s="38"/>
       <c r="K76" s="38"/>
       <c r="L76" s="38">
-        <f>I76/N76</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M76" s="38" t="str">
-        <f>IFERROR(L76/H76,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N76" s="39">
@@ -6028,11 +6295,11 @@
       </c>
       <c r="O76" s="64"/>
       <c r="P76" s="64" t="str">
-        <f>IF(N76&lt;&gt;1,EDATE(O76,N76-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q76" s="37" t="str">
-        <f ca="1">IF(O76&lt;&gt;"",IFERROR(DATEDIF(O76,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -6043,18 +6310,18 @@
       <c r="F77" s="37"/>
       <c r="G77" s="37"/>
       <c r="H77" s="37">
-        <f>COUNTA(E77:G77)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I77" s="38"/>
       <c r="J77" s="38"/>
       <c r="K77" s="38"/>
       <c r="L77" s="38">
-        <f>I77/N77</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M77" s="38" t="str">
-        <f>IFERROR(L77/H77,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N77" s="39">
@@ -6062,11 +6329,11 @@
       </c>
       <c r="O77" s="64"/>
       <c r="P77" s="64" t="str">
-        <f>IF(N77&lt;&gt;1,EDATE(O77,N77-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q77" s="37" t="str">
-        <f ca="1">IF(O77&lt;&gt;"",IFERROR(DATEDIF(O77,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -6077,18 +6344,18 @@
       <c r="F78" s="37"/>
       <c r="G78" s="37"/>
       <c r="H78" s="37">
-        <f>COUNTA(E78:G78)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I78" s="38"/>
       <c r="J78" s="38"/>
       <c r="K78" s="38"/>
       <c r="L78" s="38">
-        <f>I78/N78</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M78" s="38" t="str">
-        <f>IFERROR(L78/H78,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N78" s="39">
@@ -6096,11 +6363,11 @@
       </c>
       <c r="O78" s="64"/>
       <c r="P78" s="64" t="str">
-        <f>IF(N78&lt;&gt;1,EDATE(O78,N78-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q78" s="37" t="str">
-        <f ca="1">IF(O78&lt;&gt;"",IFERROR(DATEDIF(O78,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -6111,18 +6378,18 @@
       <c r="F79" s="37"/>
       <c r="G79" s="37"/>
       <c r="H79" s="37">
-        <f>COUNTA(E79:G79)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I79" s="38"/>
       <c r="J79" s="38"/>
       <c r="K79" s="38"/>
       <c r="L79" s="38">
-        <f>I79/N79</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M79" s="38" t="str">
-        <f>IFERROR(L79/H79,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N79" s="39">
@@ -6130,11 +6397,11 @@
       </c>
       <c r="O79" s="64"/>
       <c r="P79" s="64" t="str">
-        <f>IF(N79&lt;&gt;1,EDATE(O79,N79-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q79" s="37" t="str">
-        <f ca="1">IF(O79&lt;&gt;"",IFERROR(DATEDIF(O79,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -6145,18 +6412,18 @@
       <c r="F80" s="37"/>
       <c r="G80" s="37"/>
       <c r="H80" s="37">
-        <f>COUNTA(E80:G80)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I80" s="38"/>
       <c r="J80" s="38"/>
       <c r="K80" s="38"/>
       <c r="L80" s="38">
-        <f>I80/N80</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M80" s="38" t="str">
-        <f>IFERROR(L80/H80,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N80" s="39">
@@ -6164,11 +6431,11 @@
       </c>
       <c r="O80" s="64"/>
       <c r="P80" s="64" t="str">
-        <f>IF(N80&lt;&gt;1,EDATE(O80,N80-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q80" s="37" t="str">
-        <f ca="1">IF(O80&lt;&gt;"",IFERROR(DATEDIF(O80,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -6179,18 +6446,18 @@
       <c r="F81" s="37"/>
       <c r="G81" s="37"/>
       <c r="H81" s="37">
-        <f>COUNTA(E81:G81)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I81" s="38"/>
       <c r="J81" s="38"/>
       <c r="K81" s="38"/>
       <c r="L81" s="38">
-        <f>I81/N81</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M81" s="38" t="str">
-        <f>IFERROR(L81/H81,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N81" s="39">
@@ -6198,11 +6465,11 @@
       </c>
       <c r="O81" s="64"/>
       <c r="P81" s="64" t="str">
-        <f>IF(N81&lt;&gt;1,EDATE(O81,N81-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q81" s="37" t="str">
-        <f ca="1">IF(O81&lt;&gt;"",IFERROR(DATEDIF(O81,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -6213,18 +6480,18 @@
       <c r="F82" s="37"/>
       <c r="G82" s="37"/>
       <c r="H82" s="37">
-        <f>COUNTA(E82:G82)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I82" s="38"/>
       <c r="J82" s="38"/>
       <c r="K82" s="38"/>
       <c r="L82" s="38">
-        <f>I82/N82</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M82" s="38" t="str">
-        <f>IFERROR(L82/H82,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N82" s="39">
@@ -6232,11 +6499,11 @@
       </c>
       <c r="O82" s="64"/>
       <c r="P82" s="64" t="str">
-        <f>IF(N82&lt;&gt;1,EDATE(O82,N82-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q82" s="37" t="str">
-        <f ca="1">IF(O82&lt;&gt;"",IFERROR(DATEDIF(O82,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -6247,18 +6514,18 @@
       <c r="F83" s="37"/>
       <c r="G83" s="37"/>
       <c r="H83" s="37">
-        <f>COUNTA(E83:G83)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I83" s="38"/>
       <c r="J83" s="38"/>
       <c r="K83" s="38"/>
       <c r="L83" s="38">
-        <f>I83/N83</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M83" s="38" t="str">
-        <f>IFERROR(L83/H83,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N83" s="39">
@@ -6266,11 +6533,11 @@
       </c>
       <c r="O83" s="64"/>
       <c r="P83" s="64" t="str">
-        <f>IF(N83&lt;&gt;1,EDATE(O83,N83-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q83" s="37" t="str">
-        <f ca="1">IF(O83&lt;&gt;"",IFERROR(DATEDIF(O83,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ref="Q83:Q114" ca="1" si="15">IF(O83&lt;&gt;"",IFERROR(DATEDIF(O83,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -6281,18 +6548,18 @@
       <c r="F84" s="37"/>
       <c r="G84" s="37"/>
       <c r="H84" s="37">
-        <f>COUNTA(E84:G84)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I84" s="38"/>
       <c r="J84" s="38"/>
       <c r="K84" s="38"/>
       <c r="L84" s="38">
-        <f>I84/N84</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M84" s="38" t="str">
-        <f>IFERROR(L84/H84,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N84" s="39">
@@ -6300,11 +6567,11 @@
       </c>
       <c r="O84" s="64"/>
       <c r="P84" s="64" t="str">
-        <f>IF(N84&lt;&gt;1,EDATE(O84,N84-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q84" s="37" t="str">
-        <f ca="1">IF(O84&lt;&gt;"",IFERROR(DATEDIF(O84,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6315,18 +6582,18 @@
       <c r="F85" s="37"/>
       <c r="G85" s="37"/>
       <c r="H85" s="37">
-        <f>COUNTA(E85:G85)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I85" s="38"/>
       <c r="J85" s="38"/>
       <c r="K85" s="38"/>
       <c r="L85" s="38">
-        <f>I85/N85</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M85" s="38" t="str">
-        <f>IFERROR(L85/H85,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N85" s="39">
@@ -6334,11 +6601,11 @@
       </c>
       <c r="O85" s="35"/>
       <c r="P85" s="35" t="str">
-        <f>IF(N85&lt;&gt;1,EDATE(O85,N85-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q85" s="37" t="str">
-        <f ca="1">IF(O85&lt;&gt;"",IFERROR(DATEDIF(O85,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6349,18 +6616,18 @@
       <c r="F86" s="37"/>
       <c r="G86" s="37"/>
       <c r="H86" s="37">
-        <f>COUNTA(E86:G86)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I86" s="38"/>
       <c r="J86" s="38"/>
       <c r="K86" s="38"/>
       <c r="L86" s="38">
-        <f>I86/N86</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M86" s="38" t="str">
-        <f>IFERROR(L86/H86,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N86" s="39">
@@ -6368,11 +6635,11 @@
       </c>
       <c r="O86" s="35"/>
       <c r="P86" s="35" t="str">
-        <f>IF(N86&lt;&gt;1,EDATE(O86,N86-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q86" s="37" t="str">
-        <f ca="1">IF(O86&lt;&gt;"",IFERROR(DATEDIF(O86,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6383,18 +6650,18 @@
       <c r="F87" s="37"/>
       <c r="G87" s="37"/>
       <c r="H87" s="37">
-        <f>COUNTA(E87:G87)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I87" s="38"/>
       <c r="J87" s="38"/>
       <c r="K87" s="38"/>
       <c r="L87" s="38">
-        <f>I87/N87</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M87" s="38" t="str">
-        <f>IFERROR(L87/H87,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N87" s="39">
@@ -6402,11 +6669,11 @@
       </c>
       <c r="O87" s="35"/>
       <c r="P87" s="35" t="str">
-        <f>IF(N87&lt;&gt;1,EDATE(O87,N87-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q87" s="37" t="str">
-        <f ca="1">IF(O87&lt;&gt;"",IFERROR(DATEDIF(O87,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6417,18 +6684,18 @@
       <c r="F88" s="37"/>
       <c r="G88" s="37"/>
       <c r="H88" s="37">
-        <f>COUNTA(E88:G88)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I88" s="38"/>
       <c r="J88" s="38"/>
       <c r="K88" s="38"/>
       <c r="L88" s="38">
-        <f>I88/N88</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M88" s="38" t="str">
-        <f>IFERROR(L88/H88,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N88" s="39">
@@ -6436,11 +6703,11 @@
       </c>
       <c r="O88" s="35"/>
       <c r="P88" s="35" t="str">
-        <f>IF(N88&lt;&gt;1,EDATE(O88,N88-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q88" s="37" t="str">
-        <f ca="1">IF(O88&lt;&gt;"",IFERROR(DATEDIF(O88,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6451,18 +6718,18 @@
       <c r="F89" s="37"/>
       <c r="G89" s="37"/>
       <c r="H89" s="37">
-        <f>COUNTA(E89:G89)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I89" s="38"/>
       <c r="J89" s="38"/>
       <c r="K89" s="38"/>
       <c r="L89" s="38">
-        <f>I89/N89</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M89" s="38" t="str">
-        <f>IFERROR(L89/H89,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N89" s="39">
@@ -6470,11 +6737,11 @@
       </c>
       <c r="O89" s="35"/>
       <c r="P89" s="35" t="str">
-        <f>IF(N89&lt;&gt;1,EDATE(O89,N89-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q89" s="37" t="str">
-        <f ca="1">IF(O89&lt;&gt;"",IFERROR(DATEDIF(O89,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6485,18 +6752,18 @@
       <c r="F90" s="37"/>
       <c r="G90" s="37"/>
       <c r="H90" s="37">
-        <f>COUNTA(E90:G90)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I90" s="38"/>
       <c r="J90" s="38"/>
       <c r="K90" s="38"/>
       <c r="L90" s="38">
-        <f>I90/N90</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M90" s="38" t="str">
-        <f>IFERROR(L90/H90,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N90" s="39">
@@ -6504,11 +6771,11 @@
       </c>
       <c r="O90" s="35"/>
       <c r="P90" s="35" t="str">
-        <f>IF(N90&lt;&gt;1,EDATE(O90,N90-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q90" s="37" t="str">
-        <f ca="1">IF(O90&lt;&gt;"",IFERROR(DATEDIF(O90,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6519,18 +6786,18 @@
       <c r="F91" s="37"/>
       <c r="G91" s="37"/>
       <c r="H91" s="37">
-        <f>COUNTA(E91:G91)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I91" s="38"/>
       <c r="J91" s="38"/>
       <c r="K91" s="38"/>
       <c r="L91" s="38">
-        <f>I91/N91</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M91" s="38" t="str">
-        <f>IFERROR(L91/H91,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N91" s="39">
@@ -6538,11 +6805,11 @@
       </c>
       <c r="O91" s="35"/>
       <c r="P91" s="35" t="str">
-        <f>IF(N91&lt;&gt;1,EDATE(O91,N91-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q91" s="37" t="str">
-        <f ca="1">IF(O91&lt;&gt;"",IFERROR(DATEDIF(O91,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6553,18 +6820,18 @@
       <c r="F92" s="37"/>
       <c r="G92" s="37"/>
       <c r="H92" s="37">
-        <f>COUNTA(E92:G92)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I92" s="38"/>
       <c r="J92" s="38"/>
       <c r="K92" s="38"/>
       <c r="L92" s="38">
-        <f>I92/N92</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M92" s="38" t="str">
-        <f>IFERROR(L92/H92,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N92" s="39">
@@ -6572,11 +6839,11 @@
       </c>
       <c r="O92" s="35"/>
       <c r="P92" s="35" t="str">
-        <f>IF(N92&lt;&gt;1,EDATE(O92,N92-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q92" s="37" t="str">
-        <f ca="1">IF(O92&lt;&gt;"",IFERROR(DATEDIF(O92,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6587,18 +6854,18 @@
       <c r="F93" s="37"/>
       <c r="G93" s="37"/>
       <c r="H93" s="37">
-        <f>COUNTA(E93:G93)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I93" s="38"/>
       <c r="J93" s="38"/>
       <c r="K93" s="38"/>
       <c r="L93" s="38">
-        <f>I93/N93</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M93" s="38" t="str">
-        <f>IFERROR(L93/H93,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N93" s="39">
@@ -6606,11 +6873,11 @@
       </c>
       <c r="O93" s="35"/>
       <c r="P93" s="35" t="str">
-        <f>IF(N93&lt;&gt;1,EDATE(O93,N93-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q93" s="37" t="str">
-        <f ca="1">IF(O93&lt;&gt;"",IFERROR(DATEDIF(O93,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6621,18 +6888,18 @@
       <c r="F94" s="37"/>
       <c r="G94" s="37"/>
       <c r="H94" s="37">
-        <f>COUNTA(E94:G94)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I94" s="38"/>
       <c r="J94" s="38"/>
       <c r="K94" s="38"/>
       <c r="L94" s="38">
-        <f>I94/N94</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M94" s="38" t="str">
-        <f>IFERROR(L94/H94,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N94" s="39">
@@ -6640,11 +6907,11 @@
       </c>
       <c r="O94" s="35"/>
       <c r="P94" s="35" t="str">
-        <f>IF(N94&lt;&gt;1,EDATE(O94,N94-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q94" s="37" t="str">
-        <f ca="1">IF(O94&lt;&gt;"",IFERROR(DATEDIF(O94,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6655,18 +6922,18 @@
       <c r="F95" s="37"/>
       <c r="G95" s="37"/>
       <c r="H95" s="37">
-        <f>COUNTA(E95:G95)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I95" s="38"/>
       <c r="J95" s="38"/>
       <c r="K95" s="38"/>
       <c r="L95" s="38">
-        <f>I95/N95</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M95" s="38" t="str">
-        <f>IFERROR(L95/H95,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N95" s="39">
@@ -6674,11 +6941,11 @@
       </c>
       <c r="O95" s="35"/>
       <c r="P95" s="35" t="str">
-        <f>IF(N95&lt;&gt;1,EDATE(O95,N95-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q95" s="37" t="str">
-        <f ca="1">IF(O95&lt;&gt;"",IFERROR(DATEDIF(O95,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6689,18 +6956,18 @@
       <c r="F96" s="37"/>
       <c r="G96" s="37"/>
       <c r="H96" s="37">
-        <f>COUNTA(E96:G96)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I96" s="38"/>
       <c r="J96" s="38"/>
       <c r="K96" s="38"/>
       <c r="L96" s="38">
-        <f>I96/N96</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M96" s="38" t="str">
-        <f>IFERROR(L96/H96,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N96" s="39">
@@ -6708,11 +6975,11 @@
       </c>
       <c r="O96" s="35"/>
       <c r="P96" s="35" t="str">
-        <f>IF(N96&lt;&gt;1,EDATE(O96,N96-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q96" s="37" t="str">
-        <f ca="1">IF(O96&lt;&gt;"",IFERROR(DATEDIF(O96,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6723,18 +6990,18 @@
       <c r="F97" s="37"/>
       <c r="G97" s="37"/>
       <c r="H97" s="37">
-        <f>COUNTA(E97:G97)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I97" s="38"/>
       <c r="J97" s="38"/>
       <c r="K97" s="38"/>
       <c r="L97" s="38">
-        <f>I97/N97</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M97" s="38" t="str">
-        <f>IFERROR(L97/H97,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N97" s="39">
@@ -6742,11 +7009,11 @@
       </c>
       <c r="O97" s="35"/>
       <c r="P97" s="35" t="str">
-        <f>IF(N97&lt;&gt;1,EDATE(O97,N97-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q97" s="37" t="str">
-        <f ca="1">IF(O97&lt;&gt;"",IFERROR(DATEDIF(O97,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6757,18 +7024,18 @@
       <c r="F98" s="37"/>
       <c r="G98" s="37"/>
       <c r="H98" s="37">
-        <f>COUNTA(E98:G98)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I98" s="38"/>
       <c r="J98" s="38"/>
       <c r="K98" s="38"/>
       <c r="L98" s="38">
-        <f>I98/N98</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M98" s="38" t="str">
-        <f>IFERROR(L98/H98,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N98" s="39">
@@ -6776,11 +7043,11 @@
       </c>
       <c r="O98" s="35"/>
       <c r="P98" s="35" t="str">
-        <f>IF(N98&lt;&gt;1,EDATE(O98,N98-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q98" s="37" t="str">
-        <f ca="1">IF(O98&lt;&gt;"",IFERROR(DATEDIF(O98,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6791,18 +7058,18 @@
       <c r="F99" s="37"/>
       <c r="G99" s="37"/>
       <c r="H99" s="37">
-        <f>COUNTA(E99:G99)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I99" s="38"/>
       <c r="J99" s="38"/>
       <c r="K99" s="38"/>
       <c r="L99" s="38">
-        <f>I99/N99</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M99" s="38" t="str">
-        <f>IFERROR(L99/H99,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N99" s="39">
@@ -6810,11 +7077,11 @@
       </c>
       <c r="O99" s="35"/>
       <c r="P99" s="35" t="str">
-        <f>IF(N99&lt;&gt;1,EDATE(O99,N99-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q99" s="37" t="str">
-        <f ca="1">IF(O99&lt;&gt;"",IFERROR(DATEDIF(O99,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6825,18 +7092,18 @@
       <c r="F100" s="37"/>
       <c r="G100" s="37"/>
       <c r="H100" s="37">
-        <f>COUNTA(E100:G100)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I100" s="38"/>
       <c r="J100" s="38"/>
       <c r="K100" s="38"/>
       <c r="L100" s="38">
-        <f>I100/N100</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M100" s="38" t="str">
-        <f>IFERROR(L100/H100,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N100" s="39">
@@ -6844,11 +7111,11 @@
       </c>
       <c r="O100" s="35"/>
       <c r="P100" s="35" t="str">
-        <f>IF(N100&lt;&gt;1,EDATE(O100,N100-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q100" s="37" t="str">
-        <f ca="1">IF(O100&lt;&gt;"",IFERROR(DATEDIF(O100,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6859,18 +7126,18 @@
       <c r="F101" s="37"/>
       <c r="G101" s="37"/>
       <c r="H101" s="37">
-        <f>COUNTA(E101:G101)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I101" s="38"/>
       <c r="J101" s="38"/>
       <c r="K101" s="38"/>
       <c r="L101" s="38">
-        <f>I101/N101</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M101" s="38" t="str">
-        <f>IFERROR(L101/H101,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N101" s="39">
@@ -6878,11 +7145,11 @@
       </c>
       <c r="O101" s="35"/>
       <c r="P101" s="35" t="str">
-        <f>IF(N101&lt;&gt;1,EDATE(O101,N101-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q101" s="37" t="str">
-        <f ca="1">IF(O101&lt;&gt;"",IFERROR(DATEDIF(O101,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6893,18 +7160,18 @@
       <c r="F102" s="37"/>
       <c r="G102" s="37"/>
       <c r="H102" s="37">
-        <f>COUNTA(E102:G102)</f>
+        <f t="shared" ref="H102:H133" si="16">COUNTA(E102:G102)</f>
         <v>0</v>
       </c>
       <c r="I102" s="38"/>
       <c r="J102" s="38"/>
       <c r="K102" s="38"/>
       <c r="L102" s="38">
-        <f>I102/N102</f>
+        <f t="shared" ref="L102:L130" si="17">I102/N102</f>
         <v>0</v>
       </c>
       <c r="M102" s="38" t="str">
-        <f>IFERROR(L102/H102,"")</f>
+        <f t="shared" ref="M102:M133" si="18">IFERROR(L102/H102,"")</f>
         <v/>
       </c>
       <c r="N102" s="39">
@@ -6912,11 +7179,11 @@
       </c>
       <c r="O102" s="35"/>
       <c r="P102" s="35" t="str">
-        <f>IF(N102&lt;&gt;1,EDATE(O102,N102-1),"")</f>
+        <f t="shared" ref="P102:P133" si="19">IF(N102&lt;&gt;1,EDATE(O102,N102-1),"")</f>
         <v/>
       </c>
       <c r="Q102" s="37" t="str">
-        <f ca="1">IF(O102&lt;&gt;"",IFERROR(DATEDIF(O102,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6927,18 +7194,18 @@
       <c r="F103" s="37"/>
       <c r="G103" s="37"/>
       <c r="H103" s="37">
-        <f>COUNTA(E103:G103)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I103" s="38"/>
       <c r="J103" s="38"/>
       <c r="K103" s="38"/>
       <c r="L103" s="38">
-        <f>I103/N103</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M103" s="38" t="str">
-        <f>IFERROR(L103/H103,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N103" s="39">
@@ -6946,11 +7213,11 @@
       </c>
       <c r="O103" s="35"/>
       <c r="P103" s="35" t="str">
-        <f>IF(N103&lt;&gt;1,EDATE(O103,N103-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q103" s="37" t="str">
-        <f ca="1">IF(O103&lt;&gt;"",IFERROR(DATEDIF(O103,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6961,18 +7228,18 @@
       <c r="F104" s="37"/>
       <c r="G104" s="37"/>
       <c r="H104" s="37">
-        <f>COUNTA(E104:G104)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I104" s="38"/>
       <c r="J104" s="38"/>
       <c r="K104" s="38"/>
       <c r="L104" s="38">
-        <f>I104/N104</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M104" s="38" t="str">
-        <f>IFERROR(L104/H104,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N104" s="39">
@@ -6980,11 +7247,11 @@
       </c>
       <c r="O104" s="35"/>
       <c r="P104" s="35" t="str">
-        <f>IF(N104&lt;&gt;1,EDATE(O104,N104-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q104" s="37" t="str">
-        <f ca="1">IF(O104&lt;&gt;"",IFERROR(DATEDIF(O104,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -6995,18 +7262,18 @@
       <c r="F105" s="37"/>
       <c r="G105" s="37"/>
       <c r="H105" s="37">
-        <f>COUNTA(E105:G105)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I105" s="38"/>
       <c r="J105" s="38"/>
       <c r="K105" s="38"/>
       <c r="L105" s="38">
-        <f>I105/N105</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M105" s="38" t="str">
-        <f>IFERROR(L105/H105,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N105" s="39">
@@ -7014,11 +7281,11 @@
       </c>
       <c r="O105" s="35"/>
       <c r="P105" s="35" t="str">
-        <f>IF(N105&lt;&gt;1,EDATE(O105,N105-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q105" s="37" t="str">
-        <f ca="1">IF(O105&lt;&gt;"",IFERROR(DATEDIF(O105,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7029,18 +7296,18 @@
       <c r="F106" s="37"/>
       <c r="G106" s="37"/>
       <c r="H106" s="37">
-        <f>COUNTA(E106:G106)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I106" s="38"/>
       <c r="J106" s="38"/>
       <c r="K106" s="38"/>
       <c r="L106" s="38">
-        <f>I106/N106</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M106" s="38" t="str">
-        <f>IFERROR(L106/H106,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N106" s="39">
@@ -7048,11 +7315,11 @@
       </c>
       <c r="O106" s="35"/>
       <c r="P106" s="35" t="str">
-        <f>IF(N106&lt;&gt;1,EDATE(O106,N106-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q106" s="37" t="str">
-        <f ca="1">IF(O106&lt;&gt;"",IFERROR(DATEDIF(O106,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7063,18 +7330,18 @@
       <c r="F107" s="37"/>
       <c r="G107" s="37"/>
       <c r="H107" s="37">
-        <f>COUNTA(E107:G107)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I107" s="38"/>
       <c r="J107" s="38"/>
       <c r="K107" s="38"/>
       <c r="L107" s="38">
-        <f>I107/N107</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M107" s="38" t="str">
-        <f>IFERROR(L107/H107,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N107" s="39">
@@ -7082,11 +7349,11 @@
       </c>
       <c r="O107" s="35"/>
       <c r="P107" s="35" t="str">
-        <f>IF(N107&lt;&gt;1,EDATE(O107,N107-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q107" s="37" t="str">
-        <f ca="1">IF(O107&lt;&gt;"",IFERROR(DATEDIF(O107,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7097,18 +7364,18 @@
       <c r="F108" s="37"/>
       <c r="G108" s="37"/>
       <c r="H108" s="37">
-        <f>COUNTA(E108:G108)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I108" s="38"/>
       <c r="J108" s="38"/>
       <c r="K108" s="38"/>
       <c r="L108" s="38">
-        <f>I108/N108</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M108" s="38" t="str">
-        <f>IFERROR(L108/H108,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N108" s="39">
@@ -7116,11 +7383,11 @@
       </c>
       <c r="O108" s="35"/>
       <c r="P108" s="35" t="str">
-        <f>IF(N108&lt;&gt;1,EDATE(O108,N108-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q108" s="37" t="str">
-        <f ca="1">IF(O108&lt;&gt;"",IFERROR(DATEDIF(O108,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7131,18 +7398,18 @@
       <c r="F109" s="37"/>
       <c r="G109" s="37"/>
       <c r="H109" s="37">
-        <f>COUNTA(E109:G109)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I109" s="38"/>
       <c r="J109" s="38"/>
       <c r="K109" s="38"/>
       <c r="L109" s="38">
-        <f>I109/N109</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M109" s="38" t="str">
-        <f>IFERROR(L109/H109,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N109" s="39">
@@ -7150,11 +7417,11 @@
       </c>
       <c r="O109" s="35"/>
       <c r="P109" s="35" t="str">
-        <f>IF(N109&lt;&gt;1,EDATE(O109,N109-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q109" s="37" t="str">
-        <f ca="1">IF(O109&lt;&gt;"",IFERROR(DATEDIF(O109,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7165,18 +7432,18 @@
       <c r="F110" s="37"/>
       <c r="G110" s="37"/>
       <c r="H110" s="37">
-        <f>COUNTA(E110:G110)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I110" s="38"/>
       <c r="J110" s="38"/>
       <c r="K110" s="38"/>
       <c r="L110" s="38">
-        <f>I110/N110</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M110" s="38" t="str">
-        <f>IFERROR(L110/H110,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N110" s="39">
@@ -7184,11 +7451,11 @@
       </c>
       <c r="O110" s="35"/>
       <c r="P110" s="35" t="str">
-        <f>IF(N110&lt;&gt;1,EDATE(O110,N110-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q110" s="37" t="str">
-        <f ca="1">IF(O110&lt;&gt;"",IFERROR(DATEDIF(O110,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7199,18 +7466,18 @@
       <c r="F111" s="37"/>
       <c r="G111" s="37"/>
       <c r="H111" s="37">
-        <f>COUNTA(E111:G111)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I111" s="38"/>
       <c r="J111" s="38"/>
       <c r="K111" s="38"/>
       <c r="L111" s="38">
-        <f>I111/N111</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M111" s="38" t="str">
-        <f>IFERROR(L111/H111,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N111" s="39">
@@ -7218,11 +7485,11 @@
       </c>
       <c r="O111" s="35"/>
       <c r="P111" s="35" t="str">
-        <f>IF(N111&lt;&gt;1,EDATE(O111,N111-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q111" s="37" t="str">
-        <f ca="1">IF(O111&lt;&gt;"",IFERROR(DATEDIF(O111,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7233,18 +7500,18 @@
       <c r="F112" s="37"/>
       <c r="G112" s="37"/>
       <c r="H112" s="37">
-        <f>COUNTA(E112:G112)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I112" s="38"/>
       <c r="J112" s="38"/>
       <c r="K112" s="38"/>
       <c r="L112" s="38">
-        <f>I112/N112</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M112" s="38" t="str">
-        <f>IFERROR(L112/H112,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N112" s="39">
@@ -7252,11 +7519,11 @@
       </c>
       <c r="O112" s="35"/>
       <c r="P112" s="35" t="str">
-        <f>IF(N112&lt;&gt;1,EDATE(O112,N112-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q112" s="37" t="str">
-        <f ca="1">IF(O112&lt;&gt;"",IFERROR(DATEDIF(O112,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7267,18 +7534,18 @@
       <c r="F113" s="37"/>
       <c r="G113" s="37"/>
       <c r="H113" s="37">
-        <f>COUNTA(E113:G113)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I113" s="38"/>
       <c r="J113" s="38"/>
       <c r="K113" s="38"/>
       <c r="L113" s="38">
-        <f>I113/N113</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M113" s="38" t="str">
-        <f>IFERROR(L113/H113,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N113" s="39">
@@ -7286,11 +7553,11 @@
       </c>
       <c r="O113" s="35"/>
       <c r="P113" s="35" t="str">
-        <f>IF(N113&lt;&gt;1,EDATE(O113,N113-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q113" s="37" t="str">
-        <f ca="1">IF(O113&lt;&gt;"",IFERROR(DATEDIF(O113,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7301,18 +7568,18 @@
       <c r="F114" s="37"/>
       <c r="G114" s="37"/>
       <c r="H114" s="37">
-        <f>COUNTA(E114:G114)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I114" s="38"/>
       <c r="J114" s="38"/>
       <c r="K114" s="38"/>
       <c r="L114" s="38">
-        <f>I114/N114</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M114" s="38" t="str">
-        <f>IFERROR(L114/H114,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N114" s="39">
@@ -7320,11 +7587,11 @@
       </c>
       <c r="O114" s="35"/>
       <c r="P114" s="35" t="str">
-        <f>IF(N114&lt;&gt;1,EDATE(O114,N114-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q114" s="37" t="str">
-        <f ca="1">IF(O114&lt;&gt;"",IFERROR(DATEDIF(O114,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
@@ -7335,18 +7602,18 @@
       <c r="F115" s="37"/>
       <c r="G115" s="37"/>
       <c r="H115" s="37">
-        <f>COUNTA(E115:G115)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I115" s="38"/>
       <c r="J115" s="38"/>
       <c r="K115" s="38"/>
       <c r="L115" s="38">
-        <f>I115/N115</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M115" s="38" t="str">
-        <f>IFERROR(L115/H115,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N115" s="39">
@@ -7354,11 +7621,11 @@
       </c>
       <c r="O115" s="35"/>
       <c r="P115" s="35" t="str">
-        <f>IF(N115&lt;&gt;1,EDATE(O115,N115-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q115" s="37" t="str">
-        <f ca="1">IF(O115&lt;&gt;"",IFERROR(DATEDIF(O115,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ref="Q115:Q130" ca="1" si="20">IF(O115&lt;&gt;"",IFERROR(DATEDIF(O115,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7369,18 +7636,18 @@
       <c r="F116" s="37"/>
       <c r="G116" s="37"/>
       <c r="H116" s="37">
-        <f>COUNTA(E116:G116)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I116" s="38"/>
       <c r="J116" s="38"/>
       <c r="K116" s="38"/>
       <c r="L116" s="38">
-        <f>I116/N116</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M116" s="38" t="str">
-        <f>IFERROR(L116/H116,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N116" s="39">
@@ -7388,11 +7655,11 @@
       </c>
       <c r="O116" s="35"/>
       <c r="P116" s="35" t="str">
-        <f>IF(N116&lt;&gt;1,EDATE(O116,N116-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q116" s="37" t="str">
-        <f ca="1">IF(O116&lt;&gt;"",IFERROR(DATEDIF(O116,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7403,18 +7670,18 @@
       <c r="F117" s="37"/>
       <c r="G117" s="37"/>
       <c r="H117" s="37">
-        <f>COUNTA(E117:G117)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I117" s="38"/>
       <c r="J117" s="38"/>
       <c r="K117" s="38"/>
       <c r="L117" s="38">
-        <f>I117/N117</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M117" s="38" t="str">
-        <f>IFERROR(L117/H117,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N117" s="39">
@@ -7422,11 +7689,11 @@
       </c>
       <c r="O117" s="35"/>
       <c r="P117" s="35" t="str">
-        <f>IF(N117&lt;&gt;1,EDATE(O117,N117-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q117" s="37" t="str">
-        <f ca="1">IF(O117&lt;&gt;"",IFERROR(DATEDIF(O117,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7437,18 +7704,18 @@
       <c r="F118" s="37"/>
       <c r="G118" s="37"/>
       <c r="H118" s="37">
-        <f>COUNTA(E118:G118)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I118" s="38"/>
       <c r="J118" s="38"/>
       <c r="K118" s="38"/>
       <c r="L118" s="38">
-        <f>I118/N118</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M118" s="38" t="str">
-        <f>IFERROR(L118/H118,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N118" s="39">
@@ -7456,11 +7723,11 @@
       </c>
       <c r="O118" s="35"/>
       <c r="P118" s="35" t="str">
-        <f>IF(N118&lt;&gt;1,EDATE(O118,N118-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q118" s="37" t="str">
-        <f ca="1">IF(O118&lt;&gt;"",IFERROR(DATEDIF(O118,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7471,18 +7738,18 @@
       <c r="F119" s="37"/>
       <c r="G119" s="37"/>
       <c r="H119" s="37">
-        <f>COUNTA(E119:G119)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I119" s="38"/>
       <c r="J119" s="38"/>
       <c r="K119" s="38"/>
       <c r="L119" s="38">
-        <f>I119/N119</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M119" s="38" t="str">
-        <f>IFERROR(L119/H119,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N119" s="39">
@@ -7490,11 +7757,11 @@
       </c>
       <c r="O119" s="35"/>
       <c r="P119" s="35" t="str">
-        <f>IF(N119&lt;&gt;1,EDATE(O119,N119-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q119" s="37" t="str">
-        <f ca="1">IF(O119&lt;&gt;"",IFERROR(DATEDIF(O119,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7505,18 +7772,18 @@
       <c r="F120" s="37"/>
       <c r="G120" s="37"/>
       <c r="H120" s="37">
-        <f>COUNTA(E120:G120)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I120" s="38"/>
       <c r="J120" s="38"/>
       <c r="K120" s="38"/>
       <c r="L120" s="38">
-        <f>I120/N120</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M120" s="38" t="str">
-        <f>IFERROR(L120/H120,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N120" s="39">
@@ -7524,11 +7791,11 @@
       </c>
       <c r="O120" s="35"/>
       <c r="P120" s="35" t="str">
-        <f>IF(N120&lt;&gt;1,EDATE(O120,N120-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q120" s="37" t="str">
-        <f ca="1">IF(O120&lt;&gt;"",IFERROR(DATEDIF(O120,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7539,18 +7806,18 @@
       <c r="F121" s="37"/>
       <c r="G121" s="37"/>
       <c r="H121" s="37">
-        <f>COUNTA(E121:G121)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I121" s="38"/>
       <c r="J121" s="38"/>
       <c r="K121" s="38"/>
       <c r="L121" s="38">
-        <f>I121/N121</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M121" s="38" t="str">
-        <f>IFERROR(L121/H121,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N121" s="39">
@@ -7558,11 +7825,11 @@
       </c>
       <c r="O121" s="35"/>
       <c r="P121" s="35" t="str">
-        <f>IF(N121&lt;&gt;1,EDATE(O121,N121-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q121" s="37" t="str">
-        <f ca="1">IF(O121&lt;&gt;"",IFERROR(DATEDIF(O121,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7573,18 +7840,18 @@
       <c r="F122" s="37"/>
       <c r="G122" s="37"/>
       <c r="H122" s="37">
-        <f>COUNTA(E122:G122)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I122" s="38"/>
       <c r="J122" s="38"/>
       <c r="K122" s="38"/>
       <c r="L122" s="38">
-        <f>I122/N122</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M122" s="38" t="str">
-        <f>IFERROR(L122/H122,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N122" s="39">
@@ -7592,11 +7859,11 @@
       </c>
       <c r="O122" s="35"/>
       <c r="P122" s="35" t="str">
-        <f>IF(N122&lt;&gt;1,EDATE(O122,N122-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q122" s="37" t="str">
-        <f ca="1">IF(O122&lt;&gt;"",IFERROR(DATEDIF(O122,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7607,18 +7874,18 @@
       <c r="F123" s="37"/>
       <c r="G123" s="37"/>
       <c r="H123" s="37">
-        <f>COUNTA(E123:G123)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I123" s="38"/>
       <c r="J123" s="38"/>
       <c r="K123" s="38"/>
       <c r="L123" s="38">
-        <f>I123/N123</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M123" s="38" t="str">
-        <f>IFERROR(L123/H123,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N123" s="39">
@@ -7626,11 +7893,11 @@
       </c>
       <c r="O123" s="35"/>
       <c r="P123" s="35" t="str">
-        <f>IF(N123&lt;&gt;1,EDATE(O123,N123-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q123" s="37" t="str">
-        <f ca="1">IF(O123&lt;&gt;"",IFERROR(DATEDIF(O123,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7641,18 +7908,18 @@
       <c r="F124" s="37"/>
       <c r="G124" s="37"/>
       <c r="H124" s="37">
-        <f>COUNTA(E124:G124)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I124" s="38"/>
       <c r="J124" s="38"/>
       <c r="K124" s="38"/>
       <c r="L124" s="38">
-        <f>I124/N124</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M124" s="38" t="str">
-        <f>IFERROR(L124/H124,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N124" s="39">
@@ -7660,11 +7927,11 @@
       </c>
       <c r="O124" s="35"/>
       <c r="P124" s="35" t="str">
-        <f>IF(N124&lt;&gt;1,EDATE(O124,N124-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q124" s="37" t="str">
-        <f ca="1">IF(O124&lt;&gt;"",IFERROR(DATEDIF(O124,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7675,18 +7942,18 @@
       <c r="F125" s="37"/>
       <c r="G125" s="37"/>
       <c r="H125" s="37">
-        <f>COUNTA(E125:G125)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I125" s="38"/>
       <c r="J125" s="38"/>
       <c r="K125" s="38"/>
       <c r="L125" s="38">
-        <f>I125/N125</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M125" s="38" t="str">
-        <f>IFERROR(L125/H125,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N125" s="39">
@@ -7694,11 +7961,11 @@
       </c>
       <c r="O125" s="35"/>
       <c r="P125" s="35" t="str">
-        <f>IF(N125&lt;&gt;1,EDATE(O125,N125-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q125" s="37" t="str">
-        <f ca="1">IF(O125&lt;&gt;"",IFERROR(DATEDIF(O125,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7709,18 +7976,18 @@
       <c r="F126" s="37"/>
       <c r="G126" s="37"/>
       <c r="H126" s="37">
-        <f>COUNTA(E126:G126)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I126" s="38"/>
       <c r="J126" s="38"/>
       <c r="K126" s="38"/>
       <c r="L126" s="38">
-        <f>I126/N126</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M126" s="38" t="str">
-        <f>IFERROR(L126/H126,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N126" s="39">
@@ -7728,11 +7995,11 @@
       </c>
       <c r="O126" s="35"/>
       <c r="P126" s="35" t="str">
-        <f>IF(N126&lt;&gt;1,EDATE(O126,N126-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q126" s="37" t="str">
-        <f ca="1">IF(O126&lt;&gt;"",IFERROR(DATEDIF(O126,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7743,18 +8010,18 @@
       <c r="F127" s="37"/>
       <c r="G127" s="37"/>
       <c r="H127" s="37">
-        <f>COUNTA(E127:G127)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I127" s="38"/>
       <c r="J127" s="38"/>
       <c r="K127" s="38"/>
       <c r="L127" s="38">
-        <f>I127/N127</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M127" s="38" t="str">
-        <f>IFERROR(L127/H127,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N127" s="39">
@@ -7762,11 +8029,11 @@
       </c>
       <c r="O127" s="35"/>
       <c r="P127" s="35" t="str">
-        <f>IF(N127&lt;&gt;1,EDATE(O127,N127-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q127" s="37" t="str">
-        <f ca="1">IF(O127&lt;&gt;"",IFERROR(DATEDIF(O127,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7777,18 +8044,18 @@
       <c r="F128" s="37"/>
       <c r="G128" s="37"/>
       <c r="H128" s="37">
-        <f>COUNTA(E128:G128)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I128" s="38"/>
       <c r="J128" s="38"/>
       <c r="K128" s="38"/>
       <c r="L128" s="38">
-        <f>I128/N128</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M128" s="38" t="str">
-        <f>IFERROR(L128/H128,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N128" s="39">
@@ -7796,11 +8063,11 @@
       </c>
       <c r="O128" s="35"/>
       <c r="P128" s="35" t="str">
-        <f>IF(N128&lt;&gt;1,EDATE(O128,N128-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q128" s="37" t="str">
-        <f ca="1">IF(O128&lt;&gt;"",IFERROR(DATEDIF(O128,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7811,18 +8078,18 @@
       <c r="F129" s="37"/>
       <c r="G129" s="37"/>
       <c r="H129" s="37">
-        <f>COUNTA(E129:G129)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I129" s="38"/>
       <c r="J129" s="38"/>
       <c r="K129" s="38"/>
       <c r="L129" s="38">
-        <f>I129/N129</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M129" s="38" t="str">
-        <f>IFERROR(L129/H129,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N129" s="39">
@@ -7830,11 +8097,11 @@
       </c>
       <c r="O129" s="35"/>
       <c r="P129" s="35" t="str">
-        <f>IF(N129&lt;&gt;1,EDATE(O129,N129-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q129" s="37" t="str">
-        <f ca="1">IF(O129&lt;&gt;"",IFERROR(DATEDIF(O129,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7845,18 +8112,18 @@
       <c r="F130" s="37"/>
       <c r="G130" s="37"/>
       <c r="H130" s="37">
-        <f>COUNTA(E130:G130)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I130" s="38"/>
       <c r="J130" s="38"/>
       <c r="K130" s="38"/>
       <c r="L130" s="38">
-        <f>I130/N130</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M130" s="38" t="str">
-        <f>IFERROR(L130/H130,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N130" s="39">
@@ -7864,11 +8131,11 @@
       </c>
       <c r="O130" s="35"/>
       <c r="P130" s="35" t="str">
-        <f>IF(N130&lt;&gt;1,EDATE(O130,N130-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q130" s="37" t="str">
-        <f ca="1">IF(O130&lt;&gt;"",IFERROR(DATEDIF(O130,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -7879,22 +8146,32 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="I6:I130">
-    <cfRule type="cellIs" dxfId="11" priority="16" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:J130">
-    <cfRule type="cellIs" dxfId="10" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="17" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:K130">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
       <formula>"Parcelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K50">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="10" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K52">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K66">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7921,40 +8198,40 @@
   <sheetData>
     <row r="2" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J2" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K2" s="34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M2" s="33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N2" s="33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O2" s="34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7991,13 +8268,13 @@
       <c r="N3" s="38"/>
       <c r="O3" s="39">
         <f t="shared" ref="O3:O13" ca="1" si="3">IFERROR(DATEDIF(M3,TODAY(),"m")+1,"")</f>
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="R3" s="16"/>
     </row>
     <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="55" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E4" s="56" t="s">
         <v>1</v>
@@ -8029,7 +8306,7 @@
       <c r="N4" s="38"/>
       <c r="O4" s="39">
         <f t="shared" ca="1" si="3"/>
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="R4" s="16"/>
     </row>
@@ -8038,7 +8315,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>1</v>
@@ -8070,7 +8347,7 @@
       <c r="N5" s="38"/>
       <c r="O5" s="39">
         <f t="shared" ca="1" si="3"/>
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="P5" s="59"/>
     </row>
@@ -8080,7 +8357,7 @@
         <v>2515.7400000000002</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>1</v>
@@ -8112,13 +8389,13 @@
       <c r="N6" s="38"/>
       <c r="O6" s="39">
         <f t="shared" ca="1" si="3"/>
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="60"/>
       <c r="D7" s="54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E7" s="36" t="s">
         <v>1</v>
@@ -8150,7 +8427,7 @@
       <c r="N7" s="38"/>
       <c r="O7" s="39">
         <f t="shared" ca="1" si="3"/>
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="8" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8158,7 +8435,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="54" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>1</v>
@@ -8190,7 +8467,7 @@
       <c r="N8" s="38"/>
       <c r="O8" s="39">
         <f t="shared" ca="1" si="3"/>
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="9" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8199,7 +8476,7 @@
         <v>5807.74</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E9" s="36" t="s">
         <v>1</v>
@@ -8232,12 +8509,12 @@
       <c r="N9" s="38"/>
       <c r="O9" s="39">
         <f t="shared" ca="1" si="3"/>
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D10" s="54" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="37" t="s">
@@ -8267,12 +8544,12 @@
       <c r="N10" s="38"/>
       <c r="O10" s="39">
         <f t="shared" ca="1" si="3"/>
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D11" s="54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="37" t="s">
@@ -8302,12 +8579,12 @@
       <c r="N11" s="38"/>
       <c r="O11" s="39">
         <f t="shared" ca="1" si="3"/>
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D12" s="54" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E12" s="36"/>
       <c r="F12" s="37" t="s">
@@ -8337,12 +8614,12 @@
       <c r="N12" s="38"/>
       <c r="O12" s="39">
         <f t="shared" ca="1" si="3"/>
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D13" s="54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E13" s="36" t="s">
         <v>1</v>
@@ -8374,7 +8651,7 @@
       <c r="N13" s="38"/>
       <c r="O13" s="39">
         <f t="shared" ca="1" si="3"/>
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
@@ -8503,7 +8780,7 @@
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" s="2"/>
       <c r="N1" s="47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8513,10 +8790,10 @@
     <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G3" s="2"/>
       <c r="L3" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="M3" s="77" t="s">
         <v>124</v>
-      </c>
-      <c r="M3" s="77" t="s">
-        <v>125</v>
       </c>
       <c r="N3" s="43">
         <f>SUM(N5:N21)</f>
@@ -8527,7 +8804,7 @@
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G4" s="2"/>
       <c r="L4" s="48" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M4" s="78"/>
       <c r="N4" s="49"/>
@@ -8538,7 +8815,7 @@
       <c r="F5" s="16"/>
       <c r="G5" s="28"/>
       <c r="L5" t="s">
-        <v>217</v>
+        <v>126</v>
       </c>
       <c r="N5" s="1">
         <v>100</v>
@@ -8548,7 +8825,7 @@
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G6" s="2"/>
       <c r="L6" t="s">
-        <v>222</v>
+        <v>127</v>
       </c>
       <c r="N6" s="1">
         <f>97+31</f>
@@ -8557,50 +8834,50 @@
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G7" s="2"/>
-      <c r="N7" s="74"/>
+      <c r="N7" s="73"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F8" s="16"/>
       <c r="G8" s="50"/>
-      <c r="N8" s="74"/>
+      <c r="N8" s="73"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F9" s="47" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G9" s="28"/>
-      <c r="N9" s="73"/>
+      <c r="N9" s="72"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F10" s="16">
         <f>SUM(G11:I11)</f>
-        <v>0.62000000000261934</v>
+        <v>4520.0000000000036</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H10" s="51" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I10" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="N10" s="73"/>
+        <v>132</v>
+      </c>
+      <c r="N10" s="72"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F11" s="16">
         <f>SUM(G11:H11)</f>
-        <v>0.62000000000261934</v>
+        <v>4520.0000000000036</v>
       </c>
       <c r="G11" s="1">
         <f>G12+SUM(G14:G496)</f>
-        <v>0.62000000000261934</v>
+        <v>4520.0000000000036</v>
       </c>
       <c r="H11" s="1">
         <f>H12+SUM(H14:H496)</f>
@@ -8610,29 +8887,29 @@
         <f>I12+SUM(I14:I496)</f>
         <v>0</v>
       </c>
-      <c r="N11" s="73"/>
+      <c r="N11" s="72"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G12" s="1">
         <v>15250</v>
       </c>
-      <c r="N12" s="73"/>
+      <c r="N12" s="72"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F13" s="72" t="s">
-        <v>126</v>
+      <c r="F13" s="74" t="s">
+        <v>125</v>
       </c>
       <c r="G13" s="52"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="N13" s="73"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="N13" s="72"/>
     </row>
     <row r="14" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G14" s="53"/>
       <c r="H14" s="53"/>
@@ -8641,7 +8918,7 @@
     </row>
     <row r="15" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G15" s="53">
         <v>773.35</v>
@@ -8652,7 +8929,7 @@
     </row>
     <row r="16" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G16" s="53">
         <v>-5148</v>
@@ -8663,7 +8940,7 @@
     </row>
     <row r="17" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G17" s="53">
         <v>-168</v>
@@ -8674,7 +8951,7 @@
     </row>
     <row r="18" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G18" s="53">
         <v>-1700</v>
@@ -8685,7 +8962,7 @@
     </row>
     <row r="19" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G19" s="53">
         <v>5148</v>
@@ -8696,7 +8973,7 @@
     </row>
     <row r="20" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G20" s="53">
         <v>-4938</v>
@@ -8707,7 +8984,7 @@
     </row>
     <row r="21" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G21" s="53">
         <v>-1595</v>
@@ -8718,7 +8995,7 @@
     </row>
     <row r="22" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G22" s="53">
         <v>-4677</v>
@@ -8729,7 +9006,7 @@
     </row>
     <row r="23" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G23" s="53">
         <v>-200</v>
@@ -8740,7 +9017,7 @@
     </row>
     <row r="24" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G24" s="53">
         <v>4677</v>
@@ -8751,7 +9028,7 @@
     </row>
     <row r="25" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G25" s="53">
         <v>-750</v>
@@ -8762,7 +9039,7 @@
     </row>
     <row r="26" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G26" s="53">
         <v>-652</v>
@@ -8773,7 +9050,7 @@
     </row>
     <row r="27" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G27" s="53">
         <v>11100</v>
@@ -8784,7 +9061,7 @@
     </row>
     <row r="28" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G28" s="53">
         <v>-396</v>
@@ -8795,7 +9072,7 @@
     </row>
     <row r="29" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G29" s="53">
         <v>-4211</v>
@@ -8806,7 +9083,7 @@
     </row>
     <row r="30" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G30" s="53">
         <v>-450</v>
@@ -8817,7 +9094,7 @@
     </row>
     <row r="31" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G31" s="53">
         <v>-1197</v>
@@ -8828,7 +9105,7 @@
     </row>
     <row r="32" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F32" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="G32" s="53">
         <v>-315</v>
@@ -8839,7 +9116,7 @@
     </row>
     <row r="33" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G33" s="53">
         <v>-830</v>
@@ -8850,7 +9127,7 @@
     </row>
     <row r="34" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F34" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G34" s="53">
         <v>4211</v>
@@ -8861,7 +9138,7 @@
     </row>
     <row r="35" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F35" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G35" s="53">
         <v>-200</v>
@@ -8872,7 +9149,7 @@
     </row>
     <row r="36" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F36" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G36" s="53">
         <v>10000</v>
@@ -8883,7 +9160,7 @@
     </row>
     <row r="37" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F37" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G37" s="53">
         <v>-200</v>
@@ -8894,7 +9171,7 @@
     </row>
     <row r="38" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F38" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="G38" s="53">
         <v>-381</v>
@@ -8905,7 +9182,7 @@
     </row>
     <row r="39" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G39" s="53">
         <v>-4911</v>
@@ -8917,7 +9194,7 @@
     <row r="40" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G40" s="53">
         <v>-5700</v>
@@ -8928,7 +9205,7 @@
     </row>
     <row r="41" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F41" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G41" s="53">
         <v>-400</v>
@@ -8939,7 +9216,7 @@
     </row>
     <row r="42" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F42" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G42" s="53">
         <v>-450</v>
@@ -8950,7 +9227,7 @@
     </row>
     <row r="43" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G43" s="53">
         <v>-640</v>
@@ -8962,7 +9239,7 @@
     <row r="44" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G44" s="53">
         <v>5700</v>
@@ -8973,7 +9250,7 @@
     </row>
     <row r="45" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F45" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G45" s="53">
         <v>-130</v>
@@ -8984,7 +9261,7 @@
     </row>
     <row r="46" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F46" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G46" s="53">
         <v>-250</v>
@@ -8995,7 +9272,7 @@
     </row>
     <row r="47" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F47" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G47" s="53">
         <v>-112.2</v>
@@ -9006,7 +9283,7 @@
     </row>
     <row r="48" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F48" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G48" s="53">
         <v>4911</v>
@@ -9017,7 +9294,7 @@
     </row>
     <row r="49" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F49" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G49" s="53">
         <v>-3000</v>
@@ -9028,7 +9305,7 @@
     </row>
     <row r="50" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F50" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G50" s="53">
         <v>-4000</v>
@@ -9039,7 +9316,7 @@
     </row>
     <row r="51" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F51" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G51" s="53">
         <v>-200</v>
@@ -9050,7 +9327,7 @@
     </row>
     <row r="52" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F52" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G52" s="53">
         <v>-4612</v>
@@ -9061,7 +9338,7 @@
     </row>
     <row r="53" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F53" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G53" s="53">
         <v>-700</v>
@@ -9072,7 +9349,7 @@
     </row>
     <row r="54" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F54" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G54" s="53">
         <v>-880</v>
@@ -9083,7 +9360,7 @@
     </row>
     <row r="55" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F55" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G55" s="53">
         <v>-310</v>
@@ -9094,7 +9371,7 @@
     </row>
     <row r="56" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F56" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G56" s="53">
         <v>-250</v>
@@ -9105,7 +9382,7 @@
     </row>
     <row r="57" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F57" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G57" s="53">
         <v>4690</v>
@@ -9116,7 +9393,7 @@
     </row>
     <row r="58" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F58" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G58" s="53">
         <v>-4440</v>
@@ -9127,7 +9404,7 @@
     </row>
     <row r="59" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F59" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G59" s="53">
         <v>-4697</v>
@@ -9137,7 +9414,7 @@
     </row>
     <row r="60" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F60" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G60" s="53">
         <v>-2500</v>
@@ -9147,7 +9424,7 @@
     </row>
     <row r="61" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F61" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G61" s="53">
         <v>-126</v>
@@ -9157,7 +9434,7 @@
     </row>
     <row r="62" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F62" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G62" s="53">
         <v>4742</v>
@@ -9167,7 +9444,7 @@
     </row>
     <row r="63" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F63" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="G63" s="53">
         <v>-410</v>
@@ -9182,7 +9459,7 @@
     </row>
     <row r="65" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F65" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G65" s="53">
         <v>3320</v>
@@ -9192,7 +9469,7 @@
     </row>
     <row r="66" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F66" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G66" s="53">
         <v>4090</v>
@@ -9202,7 +9479,7 @@
     </row>
     <row r="67" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F67" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G67" s="53">
         <v>-5688</v>
@@ -9212,7 +9489,7 @@
     </row>
     <row r="68" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F68" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G68" s="53">
         <v>-4433</v>
@@ -9222,7 +9499,7 @@
     </row>
     <row r="69" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F69" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G69" s="53">
         <v>-250</v>
@@ -9232,7 +9509,7 @@
     </row>
     <row r="70" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F70" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G70" s="53">
         <v>-99</v>
@@ -9242,7 +9519,7 @@
     </row>
     <row r="71" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F71" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G71" s="53">
         <v>320</v>
@@ -9252,7 +9529,7 @@
     </row>
     <row r="72" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F72" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G72" s="53">
         <v>-1572</v>
@@ -9267,7 +9544,7 @@
     </row>
     <row r="74" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F74" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G74" s="53">
         <v>4433</v>
@@ -9277,7 +9554,7 @@
     </row>
     <row r="75" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F75" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G75" s="53">
         <v>8000</v>
@@ -9287,7 +9564,7 @@
     </row>
     <row r="76" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F76" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G76" s="53">
         <v>-1344</v>
@@ -9297,7 +9574,7 @@
     </row>
     <row r="77" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F77" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G77" s="53">
         <v>-308</v>
@@ -9307,7 +9584,7 @@
     </row>
     <row r="78" spans="6:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F78" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G78" s="53">
         <v>-4204</v>
@@ -9317,7 +9594,7 @@
     </row>
     <row r="79" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F79" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G79" s="53">
         <v>-338</v>
@@ -9327,7 +9604,7 @@
     </row>
     <row r="80" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F80" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G80" s="53">
         <v>-50</v>
@@ -9337,7 +9614,7 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F81" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G81" s="53">
         <v>338</v>
@@ -9347,7 +9624,7 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F82" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G82" s="53">
         <v>-540</v>
@@ -9357,7 +9634,7 @@
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F83" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G83" s="53">
         <v>-184.31</v>
@@ -9369,7 +9646,7 @@
       <c r="C84" s="53"/>
       <c r="D84" s="53"/>
       <c r="F84" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G84" s="53">
         <v>-1464.22</v>
@@ -9381,7 +9658,7 @@
       <c r="C85" s="53"/>
       <c r="D85" s="53"/>
       <c r="F85" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G85" s="53">
         <v>1005</v>
@@ -9393,7 +9670,7 @@
       <c r="C86" s="53"/>
       <c r="D86" s="53"/>
       <c r="F86" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G86" s="53">
         <v>-500</v>
@@ -9405,7 +9682,7 @@
       <c r="C87" s="53"/>
       <c r="D87" s="53"/>
       <c r="F87" t="s">
-        <v>112</v>
+        <v>192</v>
       </c>
       <c r="G87" s="53">
         <v>-225</v>
@@ -9417,7 +9694,7 @@
       <c r="C88" s="53"/>
       <c r="D88" s="53"/>
       <c r="F88" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G88" s="53">
         <v>-516</v>
@@ -9426,15 +9703,10 @@
       <c r="I88" s="53"/>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B89" t="s">
-        <v>187</v>
-      </c>
-      <c r="C89" s="53">
-        <v>5170</v>
-      </c>
+      <c r="C89" s="53"/>
       <c r="D89" s="53"/>
       <c r="F89" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G89" s="53">
         <v>4204</v>
@@ -9444,14 +9716,14 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="C90" s="53">
         <v>5556.2</v>
       </c>
       <c r="D90" s="53"/>
       <c r="F90" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G90" s="53">
         <v>-100</v>
@@ -9463,7 +9735,7 @@
       <c r="C91" s="53"/>
       <c r="D91" s="53"/>
       <c r="F91" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G91" s="53">
         <v>8000</v>
@@ -9473,16 +9745,16 @@
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C92" s="53">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D92" s="53">
         <v>300</v>
       </c>
       <c r="F92" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="G92" s="53">
         <v>1000</v>
@@ -9494,7 +9766,7 @@
       <c r="C93" s="53"/>
       <c r="D93" s="53"/>
       <c r="F93" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="G93" s="53">
         <v>-12881</v>
@@ -9504,17 +9776,17 @@
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C94" s="53">
         <v>160</v>
       </c>
       <c r="D94" s="53"/>
       <c r="F94" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="G94" s="53">
-        <v>-4489</v>
+        <v>-4489.62</v>
       </c>
       <c r="H94" s="53"/>
       <c r="I94" s="53"/>
@@ -9522,13 +9794,18 @@
     <row r="95" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C95" s="53"/>
       <c r="D95" s="53"/>
-      <c r="G95" s="53"/>
+      <c r="F95" t="s">
+        <v>203</v>
+      </c>
+      <c r="G95" s="53">
+        <v>5000</v>
+      </c>
       <c r="H95" s="53"/>
       <c r="I95" s="53"/>
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C96" s="53">
         <v>2000</v>
@@ -9536,7 +9813,12 @@
       <c r="D96" s="53">
         <v>300</v>
       </c>
-      <c r="G96" s="53"/>
+      <c r="F96" t="s">
+        <v>246</v>
+      </c>
+      <c r="G96" s="53">
+        <v>-480</v>
+      </c>
       <c r="H96" s="53"/>
       <c r="I96" s="53"/>
     </row>
@@ -9548,12 +9830,7 @@
       <c r="I97" s="53"/>
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B98" t="s">
-        <v>199</v>
-      </c>
-      <c r="C98" s="53">
-        <v>300</v>
-      </c>
+      <c r="C98" s="53"/>
       <c r="D98" s="53"/>
       <c r="G98" s="53"/>
       <c r="H98" s="53"/>
@@ -9568,7 +9845,7 @@
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C100" s="53">
         <v>2000</v>
@@ -9582,7 +9859,7 @@
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C101" s="53">
         <v>8000</v>
@@ -9594,11 +9871,9 @@
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>202</v>
-      </c>
-      <c r="C102" s="53">
-        <v>4180</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="C102" s="53"/>
       <c r="D102" s="53"/>
       <c r="G102" s="53"/>
       <c r="H102" s="53"/>
@@ -9613,7 +9888,7 @@
     </row>
     <row r="104" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C104" s="53">
         <v>2000</v>
@@ -9627,7 +9902,7 @@
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C105" s="53">
         <v>2000</v>
@@ -9641,7 +9916,7 @@
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C106" s="53">
         <v>2000</v>
@@ -9662,7 +9937,7 @@
     </row>
     <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C108" s="53">
         <v>-20000</v>
@@ -9681,7 +9956,7 @@
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C110" s="53">
         <v>2000</v>
@@ -9695,7 +9970,7 @@
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C111" s="53">
         <v>2000</v>
@@ -9709,7 +9984,7 @@
     </row>
     <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C112" s="53">
         <v>8000</v>
@@ -9721,7 +9996,7 @@
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C113" s="53">
         <v>2000</v>
@@ -9735,7 +10010,7 @@
     </row>
     <row r="114" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C114" s="53">
         <v>2000</v>
@@ -9748,73 +10023,73 @@
       <c r="I114" s="53"/>
     </row>
     <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C115" s="53"/>
       <c r="G115" s="53"/>
       <c r="H115" s="53"/>
       <c r="I115" s="53"/>
     </row>
     <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C116" s="53"/>
       <c r="G116" s="53"/>
       <c r="H116" s="53"/>
       <c r="I116" s="53"/>
     </row>
     <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C117" s="53"/>
       <c r="G117" s="53"/>
       <c r="H117" s="53"/>
       <c r="I117" s="53"/>
     </row>
     <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C118" s="53"/>
       <c r="G118" s="53"/>
       <c r="H118" s="53"/>
       <c r="I118" s="53"/>
     </row>
     <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C119" s="53"/>
       <c r="G119" s="53"/>
       <c r="H119" s="53"/>
       <c r="I119" s="53"/>
     </row>
     <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C120" s="53"/>
       <c r="G120" s="53"/>
       <c r="H120" s="53"/>
       <c r="I120" s="53"/>
     </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C121" s="53"/>
       <c r="G121" s="53"/>
       <c r="H121" s="53"/>
       <c r="I121" s="53"/>
     </row>
     <row r="122" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G122" s="53"/>
-      <c r="H122" s="53"/>
       <c r="I122" s="53"/>
     </row>
     <row r="123" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G123" s="53"/>
-      <c r="H123" s="53"/>
       <c r="I123" s="53"/>
     </row>
     <row r="124" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G124" s="53"/>
-      <c r="H124" s="53"/>
       <c r="I124" s="53"/>
     </row>
     <row r="125" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G125" s="53"/>
-      <c r="H125" s="53"/>
       <c r="I125" s="53"/>
     </row>
     <row r="126" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G126" s="53"/>
-      <c r="H126" s="53"/>
       <c r="I126" s="53"/>
     </row>
     <row r="127" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G127" s="53"/>
-      <c r="H127" s="53"/>
       <c r="I127" s="53"/>
     </row>
     <row r="128" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G128" s="53"/>
-      <c r="H128" s="53"/>
       <c r="I128" s="53"/>
     </row>
     <row r="129" spans="7:9" x14ac:dyDescent="0.25">
@@ -10925,35 +11200,43 @@
   <mergeCells count="1">
     <mergeCell ref="M3:M4"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C84:D114">
-    <cfRule type="cellIs" dxfId="7" priority="155" operator="greaterThan">
+  <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C84:D114 C115:C121">
+    <cfRule type="cellIs" dxfId="9" priority="173" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="156" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="174" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G120:G1048576">
-    <cfRule type="cellIs" dxfId="5" priority="151" operator="greaterThan">
+  <conditionalFormatting sqref="G96:H121 G122:G1048576">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="152" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I119">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="G14:I95">
+    <cfRule type="cellIs" dxfId="5" priority="13" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="14" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H120:I266">
-    <cfRule type="cellIs" dxfId="1" priority="153" operator="greaterThan">
+  <conditionalFormatting sqref="H129:I266">
+    <cfRule type="cellIs" dxfId="3" priority="171" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="154" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="172" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I96:I128">
+    <cfRule type="cellIs" dxfId="1" priority="19" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10975,13 +11258,13 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" s="62" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C1" s="63" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
@@ -10995,25 +11278,25 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D3" s="54"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D4" s="54"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="54" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5" s="37" t="s">
         <v>220</v>
@@ -11022,16 +11305,16 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D6" s="54"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="54" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C7" s="37" t="s">
         <v>220</v>
@@ -11040,30 +11323,30 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="54" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D8" s="54"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="54" t="s">
-        <v>217</v>
+        <v>126</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="54" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D10" s="54"/>
     </row>

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="8_{0F9471C2-95A1-4CF9-8CFE-1EF73F0B2DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FCB1B94-4D65-465E-B673-4DA11AAF26BE}"/>
+  <xr:revisionPtr revIDLastSave="378" documentId="8_{0F9471C2-95A1-4CF9-8CFE-1EF73F0B2DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F13926B-4FCC-494B-AAC4-993FF0A8CA9D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" firstSheet="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Itaú!$C$4:$Q$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NuBank!$C$5:$Q$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NuBank!$C$5:$Q$128</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="279">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -93,6 +93,9 @@
     <t xml:space="preserve">        Gás</t>
   </si>
   <si>
+    <t xml:space="preserve">        Verisure</t>
+  </si>
+  <si>
     <t xml:space="preserve">        Seguranças+Câmera+Seguro+Edilson</t>
   </si>
   <si>
@@ -105,6 +108,9 @@
     <t>Dinheiro Guardado na poupança</t>
   </si>
   <si>
+    <t xml:space="preserve">       Reembolso Psicóloga</t>
+  </si>
+  <si>
     <t xml:space="preserve">       Seu João</t>
   </si>
   <si>
@@ -207,6 +213,9 @@
     <t>Modo de Pagamento</t>
   </si>
   <si>
+    <t>Ração Geleia</t>
+  </si>
+  <si>
     <t>Fixo</t>
   </si>
   <si>
@@ -387,6 +396,150 @@
     <t>PAGAMENTO</t>
   </si>
   <si>
+    <t>Ração Brida</t>
+  </si>
+  <si>
+    <t>Silent Hill Townfall</t>
+  </si>
+  <si>
+    <t>Uber Paraíso da Cerveja - Ida e Volta</t>
+  </si>
+  <si>
+    <t>Pontual</t>
+  </si>
+  <si>
+    <t>Transporte</t>
+  </si>
+  <si>
+    <t>Pizza</t>
+  </si>
+  <si>
+    <t>Comida</t>
+  </si>
+  <si>
+    <t>Gasolina</t>
+  </si>
+  <si>
+    <t>Comida e Bebida Lucky Friends - Os dois dias</t>
+  </si>
+  <si>
+    <t>Muuuushine</t>
+  </si>
+  <si>
+    <t>Touca Cutterman</t>
+  </si>
+  <si>
+    <t>Frango Frito</t>
+  </si>
+  <si>
+    <t>Frango Frito Caio</t>
+  </si>
+  <si>
+    <t>Estacionamento Lucky Friends</t>
+  </si>
+  <si>
+    <t>Estacionamento Lucky Friends Caio</t>
+  </si>
+  <si>
+    <t>Ponto Da Esfiha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagamentos </t>
+  </si>
+  <si>
+    <t>Psicóloga</t>
+  </si>
+  <si>
+    <t>GamePass</t>
+  </si>
+  <si>
+    <t>Piralanches</t>
+  </si>
+  <si>
+    <t>Pagamento Piralanches</t>
+  </si>
+  <si>
+    <t>PiraLanances</t>
+  </si>
+  <si>
+    <t>Produtos de Limpeza</t>
+  </si>
+  <si>
+    <t>Baronesa</t>
+  </si>
+  <si>
+    <t>Pagamento Baronesa</t>
+  </si>
+  <si>
+    <t>Gasolina Sorocaba</t>
+  </si>
+  <si>
+    <t>Gasolina Sorocaba Caio</t>
+  </si>
+  <si>
+    <t>Pagamento Gasolina</t>
+  </si>
+  <si>
+    <t>Banho das Cachorras</t>
+  </si>
+  <si>
+    <t>Pets</t>
+  </si>
+  <si>
+    <t>Janta - O Fuxico</t>
+  </si>
+  <si>
+    <t>Pagamento Janta - O Fuxico</t>
+  </si>
+  <si>
+    <t>Produtos Rennala - Xixi Sim</t>
+  </si>
+  <si>
+    <t>Sacos de Lixo</t>
+  </si>
+  <si>
+    <t>Janta Crisma Valentina</t>
+  </si>
+  <si>
+    <t>Pagamento Janta Crisma Valentina</t>
+  </si>
+  <si>
+    <t>Meli+</t>
+  </si>
+  <si>
+    <t>Oak Bier</t>
+  </si>
+  <si>
+    <t>Tapetinho</t>
+  </si>
+  <si>
+    <t>Almoço Mr Jones</t>
+  </si>
+  <si>
+    <t>Pagamento Almoço Mr Jones</t>
+  </si>
+  <si>
+    <t>Airbnb Sorocaba Caio</t>
+  </si>
+  <si>
+    <t>Serviços</t>
+  </si>
+  <si>
+    <t>Airbnb Sorocaba Caio Ajuste</t>
+  </si>
+  <si>
+    <t>Pagamento Airbnb Sorocaba Caio</t>
+  </si>
+  <si>
+    <t>Sapataria</t>
+  </si>
+  <si>
+    <t>Guacolombia</t>
+  </si>
+  <si>
+    <t>Kadalora</t>
+  </si>
+  <si>
     <t>Vivo</t>
   </si>
   <si>
@@ -663,6 +816,12 @@
     <t>Novembro</t>
   </si>
   <si>
+    <t>Psicóloga Atrasada</t>
+  </si>
+  <si>
+    <t>Custos Rennala</t>
+  </si>
+  <si>
     <t>Dezembro</t>
   </si>
   <si>
@@ -724,69 +883,6 @@
   </si>
   <si>
     <t>Dera</t>
-  </si>
-  <si>
-    <t>Ração Geleia</t>
-  </si>
-  <si>
-    <t>Ração Brida</t>
-  </si>
-  <si>
-    <t>Silent Hill Townfall</t>
-  </si>
-  <si>
-    <t>Pontual</t>
-  </si>
-  <si>
-    <t>Transporte</t>
-  </si>
-  <si>
-    <t>Uber Paraíso da Cerveja - Ida e Volta</t>
-  </si>
-  <si>
-    <t>Pizza</t>
-  </si>
-  <si>
-    <t>Comida</t>
-  </si>
-  <si>
-    <t>Comida e Bebida Lucky Friends - Os dois dias</t>
-  </si>
-  <si>
-    <t>Muuuushine</t>
-  </si>
-  <si>
-    <t>Touca Cutterman</t>
-  </si>
-  <si>
-    <t>Frango Frito</t>
-  </si>
-  <si>
-    <t>Frango Frito Caio</t>
-  </si>
-  <si>
-    <t>Estacionamento Lucky Friends</t>
-  </si>
-  <si>
-    <t>Estacionamento Lucky Friends Caio</t>
-  </si>
-  <si>
-    <t>Ponto Da Esfiha</t>
-  </si>
-  <si>
-    <t>Gasolina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagamentos </t>
-  </si>
-  <si>
-    <t xml:space="preserve">       Reembolso Psicóloga</t>
-  </si>
-  <si>
-    <t>Psicóloga</t>
-  </si>
-  <si>
-    <t>Psicóloga Atrasada</t>
   </si>
 </sst>
 </file>
@@ -798,7 +894,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1079,7 +1175,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1266,18 +1362,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="31">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1327,6 +1422,92 @@
       <font>
         <color rgb="FF00B050"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1633,8 +1814,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:F40"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:F41"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
     <col min="3" max="3" width="19.85546875" style="1" customWidth="1"/>
@@ -1643,8 +1824,8 @@
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:6" ht="15.75" customHeight="1"/>
+    <row r="2" spans="2:6" ht="23.25" customHeight="1">
       <c r="B2" s="75" t="s">
         <v>0</v>
       </c>
@@ -1656,46 +1837,46 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="76"/>
+    <row r="3" spans="2:6" ht="24" customHeight="1">
+      <c r="B3" s="77"/>
       <c r="C3" s="6">
-        <f>C5-C8-C10-C11-C24+C25+C7+C26</f>
-        <v>1727.4614047619039</v>
+        <f>C5-C8-C10-C11-C25+C26+C7+C27</f>
+        <v>1631.7072380952386</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
-        <f>E5-E8-E10-E11-E24+E25</f>
-        <v>2733.8216666666667</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+        <f>E5-E8-E10-E11-E25+E26</f>
+        <v>2330.8541666666661</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="7.5" customHeight="1"/>
+    <row r="5" spans="2:6">
       <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="8">
-        <v>10000</v>
+        <v>10400</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="8">
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6">
       <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-7695.0385952380966</v>
+        <v>-8190.7927619047614</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-7266.1783333333333</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+        <v>-7669.1458333333339</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -1703,7 +1884,7 @@
       <c r="D7" s="9"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6">
       <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
@@ -1717,49 +1898,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6">
       <c r="B9" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>5139.1369285714291</v>
+        <v>5580.2910952380944</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>1458.4383333333335</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+        <v>1806.8058333333333</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>5139.1369285714291</v>
+        <v>5580.2910952380944</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>1458.4383333333335</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+        <v>1806.8058333333333</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="8">
         <f>Contas!B6</f>
-        <v>2515.7400000000002</v>
+        <v>2570.34</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="8">
         <f>Contas!B9</f>
-        <v>5807.74</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+        <v>5862.34</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" outlineLevel="1">
       <c r="B12" s="13" t="s">
         <v>10</v>
       </c>
@@ -1773,7 +1954,7 @@
         <v>1617.835</v>
       </c>
     </row>
-    <row r="13" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" outlineLevel="1">
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
@@ -1787,22 +1968,22 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" outlineLevel="1">
       <c r="B14" s="13" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="14">
         <f>Contas!K5</f>
-        <v>165.4</v>
+        <v>220</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="14">
         <f>Contas!K5</f>
-        <v>165.4</v>
+        <v>220</v>
       </c>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" outlineLevel="1">
       <c r="B15" s="13" t="s">
         <v>13</v>
       </c>
@@ -1816,7 +1997,7 @@
         <v>40.619999999999997</v>
       </c>
     </row>
-    <row r="16" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" outlineLevel="1">
       <c r="B16" s="13" t="s">
         <v>14</v>
       </c>
@@ -1830,275 +2011,289 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" outlineLevel="1">
       <c r="B17" s="13" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="14">
+        <f>Contas!K8</f>
+        <v>112.38500000000001</v>
+      </c>
+      <c r="D17" s="15"/>
+      <c r="E17" s="14">
+        <f>Contas!K8</f>
+        <v>112.38500000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" outlineLevel="1">
+      <c r="B18" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="14">
         <f>Contas!$K9+Contas!$K13</f>
         <v>333.5</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="14">
+      <c r="D18" s="15"/>
+      <c r="E18" s="14">
         <f>Contas!$K9+Contas!$K13</f>
         <v>333.5</v>
       </c>
     </row>
-    <row r="18" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="str">
+    <row r="19" spans="2:5" outlineLevel="1">
+      <c r="B19" s="13" t="str">
         <f>Contas!$D10</f>
         <v>Cartão Itaú da Stella</v>
-      </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="14">
-        <f>Contas!K10</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="13" t="str">
-        <f>Contas!$D11</f>
-        <v>Recolhimento INSS</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="15"/>
       <c r="E19" s="14">
-        <f>Contas!K11</f>
+        <f>Contas!K10</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" outlineLevel="1">
       <c r="B20" s="13" t="str">
-        <f>Contas!$D12</f>
-        <v>Empréstimo</v>
+        <f>Contas!$D11</f>
+        <v>Recolhimento INSS</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="15"/>
       <c r="E20" s="14">
+        <f>Contas!K11</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" outlineLevel="1">
+      <c r="B21" s="13" t="str">
+        <f>Contas!$D12</f>
+        <v>Empréstimo</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="14">
         <f>Contas!K12</f>
         <v>1292</v>
       </c>
     </row>
-    <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="18"/>
-    </row>
-    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="14"/>
-    </row>
-    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" outlineLevel="1">
+      <c r="B22" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="2:5" outlineLevel="1">
       <c r="B23" s="13"/>
       <c r="C23" s="14"/>
       <c r="D23" s="15"/>
       <c r="E23" s="14"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="8">
-        <v>1000</v>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="8"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" outlineLevel="1">
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="14"/>
+    </row>
+    <row r="25" spans="2:5">
       <c r="B25" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C25" s="8">
-        <f>SUM(C27:C38)</f>
+        <v>1000</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="8">
+        <f>SUM(C28:C39)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8">
-        <f>SUM(E27:E36)</f>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8">
+        <f>SUM(E28:E37)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B26" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="C26" s="8">
+    <row r="27" spans="2:5">
+      <c r="B27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="8">
         <f>(338/4)*5</f>
         <v>422.5</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-    </row>
-    <row r="27" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="14" t="str">
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" spans="2:5" outlineLevel="1">
+      <c r="B28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="14" t="str">
         <f>IF('NuConta e Poupança'!M5="Sim",'NuConta e Poupança'!N5,"")</f>
         <v/>
       </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="14"/>
-    </row>
-    <row r="28" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="21"/>
-    </row>
-    <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="13" t="str">
+      <c r="D28" s="15"/>
+      <c r="E28" s="14"/>
+    </row>
+    <row r="29" spans="2:5" outlineLevel="1">
+      <c r="B29" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="21"/>
+    </row>
+    <row r="30" spans="2:5" outlineLevel="1">
+      <c r="B30" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L7</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C29" s="14" t="str">
+      <c r="C30" s="14" t="str">
         <f>IF('NuConta e Poupança'!M7="Sim",'NuConta e Poupança'!N7,"")</f>
         <v/>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="21"/>
-    </row>
-    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="13" t="str">
+      <c r="D30" s="20"/>
+      <c r="E30" s="21"/>
+    </row>
+    <row r="31" spans="2:5" outlineLevel="1">
+      <c r="B31" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L8</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C30" s="14" t="str">
+      <c r="C31" s="14" t="str">
         <f>IF('NuConta e Poupança'!M8="Sim",'NuConta e Poupança'!N8,"")</f>
         <v/>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="21"/>
-    </row>
-    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="13" t="str">
+      <c r="D31" s="20"/>
+      <c r="E31" s="21"/>
+    </row>
+    <row r="32" spans="2:5" outlineLevel="1">
+      <c r="B32" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L9</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C31" s="14" t="str">
+      <c r="C32" s="14" t="str">
         <f>IF('NuConta e Poupança'!M9="Sim",'NuConta e Poupança'!N9,"")</f>
         <v/>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="21"/>
-    </row>
-    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="13" t="str">
+      <c r="D32" s="20"/>
+      <c r="E32" s="21"/>
+    </row>
+    <row r="33" spans="2:6" outlineLevel="1">
+      <c r="B33" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L10</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C32" s="14" t="str">
+      <c r="C33" s="14" t="str">
         <f>IF('NuConta e Poupança'!M10="Sim",'NuConta e Poupança'!N10,"")</f>
         <v/>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="21"/>
-    </row>
-    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="13" t="str">
+      <c r="D33" s="20"/>
+      <c r="E33" s="21"/>
+    </row>
+    <row r="34" spans="2:6" outlineLevel="1">
+      <c r="B34" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L12</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C33" s="14" t="str">
+      <c r="C34" s="14" t="str">
         <f>IF('NuConta e Poupança'!M12="Sim",'NuConta e Poupança'!N11,"")</f>
         <v/>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="21"/>
-    </row>
-    <row r="34" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="13" t="str">
+      <c r="D34" s="20"/>
+      <c r="E34" s="21"/>
+    </row>
+    <row r="35" spans="2:6" outlineLevel="1">
+      <c r="B35" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L13</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C34" s="14" t="str">
+      <c r="C35" s="14" t="str">
         <f>IF('NuConta e Poupança'!M13="Sim",'NuConta e Poupança'!N12,"")</f>
         <v/>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="21"/>
-    </row>
-    <row r="35" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="13" t="str">
+      <c r="D35" s="20"/>
+      <c r="E35" s="21"/>
+    </row>
+    <row r="36" spans="2:6" outlineLevel="1">
+      <c r="B36" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L14</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C35" s="14" t="str">
+      <c r="C36" s="14" t="str">
         <f>IF('NuConta e Poupança'!M14="Sim",'NuConta e Poupança'!N13,"")</f>
         <v/>
       </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="21"/>
-    </row>
-    <row r="36" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="13" t="str">
+      <c r="D36" s="20"/>
+      <c r="E36" s="21"/>
+    </row>
+    <row r="37" spans="2:6" outlineLevel="1">
+      <c r="B37" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L15</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C36" s="14" t="str">
+      <c r="C37" s="14" t="str">
         <f>IF('NuConta e Poupança'!M15="Sim",'NuConta e Poupança'!N14,"")</f>
         <v/>
       </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="21"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="13" t="str">
+      <c r="D37" s="20"/>
+      <c r="E37" s="21"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L16</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C37" s="14" t="str">
+      <c r="C38" s="14" t="str">
         <f>IF('NuConta e Poupança'!M16="Sim",'NuConta e Poupança'!N15,"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="16"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="13" t="str">
-        <f>"       "&amp;'NuConta e Poupança'!L17</f>
-        <v xml:space="preserve">       </v>
-      </c>
-      <c r="C38" s="14" t="str">
-        <f>IF('NuConta e Poupança'!M17="Sim",'NuConta e Poupança'!N16,"")</f>
         <v/>
       </c>
       <c r="D38" s="20"/>
       <c r="E38" s="21"/>
       <c r="F38" s="16"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6">
       <c r="B39" s="13" t="str">
+        <f>"       "&amp;'NuConta e Poupança'!L17</f>
+        <v xml:space="preserve">       </v>
+      </c>
+      <c r="C39" s="14" t="str">
+        <f>IF('NuConta e Poupança'!M17="Sim",'NuConta e Poupança'!N16,"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="20"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="16"/>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L21</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C39" s="14" t="str">
+      <c r="C40" s="14" t="str">
         <f>IF('NuConta e Poupança'!M21="Sim",'NuConta e Poupança'!N20,"")</f>
         <v/>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="21"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="13" t="str">
+      <c r="D40" s="20"/>
+      <c r="E40" s="21"/>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L22</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C40" s="14" t="str">
+      <c r="C41" s="14" t="str">
         <f>IF('NuConta e Poupança'!M22="Sim",'NuConta e Poupança'!N21,"")</f>
         <v/>
       </c>
-      <c r="D40" s="20"/>
-      <c r="E40" s="21"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2111,8 +2306,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:D23"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:D24"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="31.42578125" customWidth="1"/>
@@ -2121,8 +2316,8 @@
     <col min="5" max="5" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" ht="39" customHeight="1"/>
+    <row r="2" spans="2:4" ht="18.75" customHeight="1">
       <c r="B2" s="22"/>
       <c r="C2" s="23" t="s">
         <v>2</v>
@@ -2131,7 +2326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4">
       <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
@@ -2144,57 +2339,57 @@
         <v>40.161666666666669</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4">
       <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>1458.4383333333335</v>
+        <v>1806.8058333333333</v>
       </c>
       <c r="D4" s="24">
         <f>Saldo!C9+D5</f>
-        <v>5139.1369285714291</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+        <v>5580.2910952380944</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4">
       <c r="B6" s="13"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4">
       <c r="B7" s="13"/>
       <c r="C7" s="8"/>
       <c r="D7" s="24"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4">
       <c r="B8" s="13"/>
       <c r="C8" s="8"/>
       <c r="D8" s="24"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4">
       <c r="B9" s="13"/>
       <c r="C9" s="8"/>
       <c r="D9" s="24"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4">
       <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="8">
-        <f>SUM(C11,C13:C17)</f>
-        <v>3181.355</v>
+        <f>SUM(C11,C13:C18)</f>
+        <v>3348.34</v>
       </c>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4">
       <c r="B11" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11" s="14">
         <f>Saldo!E12</f>
@@ -2202,9 +2397,9 @@
       </c>
       <c r="D11" s="13"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4">
       <c r="B12" s="25" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" s="26">
         <f>Contas!K4</f>
@@ -2212,17 +2407,17 @@
       </c>
       <c r="D12" s="13"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4">
       <c r="B13" s="13" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="14">
         <f>Contas!K5</f>
-        <v>165.4</v>
+        <v>220</v>
       </c>
       <c r="D13" s="13"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4">
       <c r="B14" s="13" t="s">
         <v>13</v>
       </c>
@@ -2232,7 +2427,7 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4">
       <c r="B15" s="13" t="s">
         <v>14</v>
       </c>
@@ -2242,66 +2437,76 @@
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4">
       <c r="B16" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C16" s="14">
-        <f>Saldo!E17</f>
+        <f>Contas!K8</f>
+        <v>112.38500000000001</v>
+      </c>
+      <c r="D16" s="13"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="14">
+        <f>Saldo!E18</f>
         <v>333.5</v>
       </c>
-      <c r="D16" s="13"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="14">
-        <f>Saldo!E19</f>
+      <c r="D17" s="13"/>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="14">
+        <f>Saldo!E20</f>
         <v>1000</v>
       </c>
-      <c r="D17" s="13"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="13"/>
-      <c r="C18" s="14"/>
       <c r="D18" s="13"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="11">
+    <row r="19" spans="2:4">
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="13"/>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>4639.7933333333331</v>
-      </c>
-      <c r="D19" s="27"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="1"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="11">
+        <v>5155.1458333333339</v>
+      </c>
+      <c r="D20" s="27"/>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="11">
         <v>5556.6183333333338</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="71">
+    <row r="23" spans="2:4">
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="71">
         <v>46262</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="71" t="s">
-        <v>29</v>
+    <row r="24" spans="2:4">
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="71" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2316,7 +2521,7 @@
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
   <dimension ref="C1:Q67"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" style="2" customWidth="1"/>
@@ -2331,9 +2536,9 @@
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1">
       <c r="D1" s="29" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
@@ -2342,10 +2547,10 @@
         <v>2</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="3:17" ht="19.5" customHeight="1">
       <c r="D2" s="31">
         <f>SUM(L5:L21)</f>
         <v>40.161666666666669</v>
@@ -2363,59 +2568,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="3:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:17" ht="30" customHeight="1">
       <c r="C4" s="33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" s="34" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O4" s="33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P4" s="33" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q4" s="34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="3:17" ht="16.5" customHeight="1">
       <c r="C5" s="69" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" s="37" t="s">
         <v>1</v>
@@ -2430,10 +2635,10 @@
         <v>240.97</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L5" s="38">
         <f t="shared" ref="L5:L15" si="1">I5/N5</f>
@@ -2458,7 +2663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:17" ht="16.5" customHeight="1">
       <c r="C6" s="37"/>
       <c r="D6" s="36"/>
       <c r="E6" s="37"/>
@@ -2490,7 +2695,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:17" ht="16.5" customHeight="1">
       <c r="C7" s="35"/>
       <c r="D7" s="36"/>
       <c r="E7" s="37"/>
@@ -2519,7 +2724,7 @@
       <c r="P7" s="35"/>
       <c r="Q7" s="37"/>
     </row>
-    <row r="8" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:17" ht="16.5" customHeight="1">
       <c r="C8" s="35"/>
       <c r="D8" s="36"/>
       <c r="E8" s="37"/>
@@ -2548,7 +2753,7 @@
       <c r="P8" s="35"/>
       <c r="Q8" s="37"/>
     </row>
-    <row r="9" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:17" ht="16.5" customHeight="1">
       <c r="C9" s="35"/>
       <c r="D9" s="36"/>
       <c r="E9" s="37"/>
@@ -2577,7 +2782,7 @@
       <c r="P9" s="35"/>
       <c r="Q9" s="37"/>
     </row>
-    <row r="10" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:17" ht="16.5" customHeight="1">
       <c r="C10" s="35"/>
       <c r="D10" s="36"/>
       <c r="E10" s="37"/>
@@ -2609,7 +2814,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:17" ht="16.5" customHeight="1">
       <c r="C11" s="35"/>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
@@ -2638,7 +2843,7 @@
       <c r="P11" s="35"/>
       <c r="Q11" s="37"/>
     </row>
-    <row r="12" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:17" ht="16.5" customHeight="1">
       <c r="C12" s="37"/>
       <c r="D12" s="36"/>
       <c r="E12" s="37"/>
@@ -2667,7 +2872,7 @@
       <c r="P12" s="35"/>
       <c r="Q12" s="37"/>
     </row>
-    <row r="13" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:17" ht="16.5" customHeight="1">
       <c r="C13" s="37"/>
       <c r="D13" s="36"/>
       <c r="E13" s="37"/>
@@ -2696,7 +2901,7 @@
       <c r="P13" s="35"/>
       <c r="Q13" s="37"/>
     </row>
-    <row r="14" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:17" ht="16.5" customHeight="1">
       <c r="C14" s="37"/>
       <c r="D14" s="36"/>
       <c r="E14" s="37"/>
@@ -2725,7 +2930,7 @@
       <c r="P14" s="35"/>
       <c r="Q14" s="37"/>
     </row>
-    <row r="15" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:17" ht="16.5" customHeight="1">
       <c r="C15" s="37"/>
       <c r="D15" s="36"/>
       <c r="E15" s="37"/>
@@ -2754,7 +2959,7 @@
       <c r="P15" s="35"/>
       <c r="Q15" s="37"/>
     </row>
-    <row r="16" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:17" ht="16.5" customHeight="1">
       <c r="C16" s="37"/>
       <c r="D16" s="36"/>
       <c r="E16" s="37"/>
@@ -2771,7 +2976,7 @@
       <c r="P16" s="35"/>
       <c r="Q16" s="37"/>
     </row>
-    <row r="17" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:17" ht="16.5" customHeight="1">
       <c r="C17" s="35"/>
       <c r="D17" s="36"/>
       <c r="E17" s="37"/>
@@ -2788,7 +2993,7 @@
       <c r="P17" s="35"/>
       <c r="Q17" s="37"/>
     </row>
-    <row r="18" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:17" ht="16.5" customHeight="1">
       <c r="C18" s="35"/>
       <c r="D18" s="36"/>
       <c r="E18" s="37"/>
@@ -2805,7 +3010,7 @@
       <c r="P18" s="35"/>
       <c r="Q18" s="37"/>
     </row>
-    <row r="19" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:17" ht="16.5" customHeight="1">
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -2816,198 +3021,198 @@
       <c r="O19" s="41"/>
       <c r="P19" s="41"/>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:17">
       <c r="H20" s="2"/>
       <c r="O20" s="42"/>
       <c r="P20" s="42"/>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:17">
       <c r="H21" s="2"/>
       <c r="O21" s="42"/>
       <c r="P21" s="42"/>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:17">
       <c r="H22" s="2"/>
       <c r="O22" s="42"/>
       <c r="P22" s="42"/>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:17">
       <c r="O23" s="42"/>
       <c r="P23" s="42"/>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:17">
       <c r="O24" s="42"/>
       <c r="P24" s="42"/>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:17">
       <c r="O25" s="42"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:17">
       <c r="O26" s="42"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:17">
       <c r="O27" s="42"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:17">
       <c r="O28" s="42"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:17">
       <c r="O29" s="42"/>
       <c r="P29" s="42"/>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:17">
       <c r="O30" s="42"/>
       <c r="P30" s="42"/>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:17">
       <c r="O31" s="42"/>
       <c r="P31" s="42"/>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:17">
       <c r="O32" s="42"/>
       <c r="P32" s="42"/>
     </row>
-    <row r="33" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="15:16">
       <c r="O33" s="42"/>
       <c r="P33" s="42"/>
     </row>
-    <row r="34" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="15:16">
       <c r="O34" s="42"/>
       <c r="P34" s="42"/>
     </row>
-    <row r="35" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="15:16">
       <c r="O35" s="42"/>
       <c r="P35" s="42"/>
     </row>
-    <row r="36" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="15:16">
       <c r="O36" s="42"/>
       <c r="P36" s="42"/>
     </row>
-    <row r="37" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="15:16">
       <c r="O37" s="42"/>
       <c r="P37" s="42"/>
     </row>
-    <row r="38" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="15:16">
       <c r="O38" s="42"/>
       <c r="P38" s="42"/>
     </row>
-    <row r="39" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="15:16">
       <c r="O39" s="42"/>
       <c r="P39" s="42"/>
     </row>
-    <row r="40" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="15:16">
       <c r="O40" s="42"/>
       <c r="P40" s="42"/>
     </row>
-    <row r="41" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="15:16">
       <c r="O41" s="42"/>
       <c r="P41" s="42"/>
     </row>
-    <row r="42" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="15:16">
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
     </row>
-    <row r="43" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="15:16">
       <c r="O43" s="42"/>
       <c r="P43" s="42"/>
     </row>
-    <row r="44" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="15:16">
       <c r="O44" s="42"/>
       <c r="P44" s="42"/>
     </row>
-    <row r="45" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="15:16">
       <c r="O45" s="42"/>
       <c r="P45" s="42"/>
     </row>
-    <row r="46" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="15:16">
       <c r="O46" s="42"/>
       <c r="P46" s="42"/>
     </row>
-    <row r="47" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="15:16">
       <c r="O47" s="42"/>
       <c r="P47" s="42"/>
     </row>
-    <row r="48" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="15:16">
       <c r="O48" s="42"/>
       <c r="P48" s="42"/>
     </row>
-    <row r="49" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="15:16">
       <c r="O49" s="42"/>
       <c r="P49" s="42"/>
     </row>
-    <row r="50" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="15:16">
       <c r="O50" s="42"/>
       <c r="P50" s="42"/>
     </row>
-    <row r="51" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="15:16">
       <c r="O51" s="42"/>
       <c r="P51" s="42"/>
     </row>
-    <row r="52" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="15:16">
       <c r="O52" s="42"/>
       <c r="P52" s="42"/>
     </row>
-    <row r="53" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="15:16">
       <c r="O53" s="42"/>
       <c r="P53" s="42"/>
     </row>
-    <row r="54" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="15:16">
       <c r="O54" s="42"/>
       <c r="P54" s="42"/>
     </row>
-    <row r="55" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="15:16">
       <c r="O55" s="42"/>
       <c r="P55" s="42"/>
     </row>
-    <row r="56" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="15:16">
       <c r="O56" s="42"/>
       <c r="P56" s="42"/>
     </row>
-    <row r="57" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="15:16">
       <c r="O57" s="42"/>
       <c r="P57" s="42"/>
     </row>
-    <row r="58" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="15:16">
       <c r="O58" s="42"/>
       <c r="P58" s="42"/>
     </row>
-    <row r="59" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="15:16">
       <c r="O59" s="42"/>
       <c r="P59" s="42"/>
     </row>
-    <row r="60" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="15:16">
       <c r="O60" s="42"/>
       <c r="P60" s="42"/>
     </row>
-    <row r="61" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="15:16">
       <c r="O61" s="42"/>
       <c r="P61" s="42"/>
     </row>
-    <row r="62" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="15:16">
       <c r="O62" s="42"/>
       <c r="P62" s="42"/>
     </row>
-    <row r="63" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="15:16">
       <c r="O63" s="42"/>
       <c r="P63" s="42"/>
     </row>
-    <row r="64" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="15:16">
       <c r="O64" s="42"/>
       <c r="P64" s="42"/>
     </row>
-    <row r="65" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="15:16">
       <c r="O65" s="42"/>
       <c r="P65" s="42"/>
     </row>
-    <row r="66" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="15:16">
       <c r="O66" s="42"/>
       <c r="P66" s="42"/>
     </row>
-    <row r="67" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="15:16">
       <c r="O67" s="42"/>
       <c r="P67" s="42"/>
     </row>
@@ -3018,7 +3223,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J5:K22">
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
       <formula>"Parcelado/Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3032,8 +3237,8 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="C1:Q130"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C1:Q128"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" style="2" customWidth="1"/>
@@ -3048,9 +3253,9 @@
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1">
       <c r="D1" s="44" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
@@ -3059,88 +3264,88 @@
         <v>2</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L1" s="43"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:17" ht="19.5" customHeight="1">
       <c r="D2" s="45">
-        <f>SUM(L6:L268)</f>
-        <v>6660.4702619047621</v>
+        <f>SUM(L6:L266)</f>
+        <v>7733.0669285714293</v>
       </c>
       <c r="E2" s="32">
-        <f>SUMIF($E$6:$E$268,E1,$M$6:$M$268)</f>
-        <v>5139.1369285714291</v>
+        <f>SUMIF($E$6:$E$266,E1,$M$6:$M$266)</f>
+        <v>5580.2910952380944</v>
       </c>
       <c r="F2" s="32">
-        <f>SUMIF($F$6:$F$268,F1,$M$6:$M$268)</f>
-        <v>1458.4383333333335</v>
+        <f>SUMIF($F$6:$F$266,F1,$M$6:$M$266)</f>
+        <v>1806.8058333333333</v>
       </c>
       <c r="G2" s="32">
-        <f>SUMIF($G$6:$G$268,G1,$M$6:$M$268)</f>
-        <v>0</v>
+        <f>SUMIF($G$6:$G$266,G1,$M$6:$M$266)</f>
+        <v>128.845</v>
       </c>
       <c r="H2" s="16"/>
       <c r="L2" s="43"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:17">
       <c r="L3" s="43"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:17">
       <c r="M4" s="43"/>
     </row>
-    <row r="5" spans="3:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:17" ht="32.25" customHeight="1">
       <c r="C5" s="33"/>
       <c r="D5" s="33" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" s="34" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N5" s="34" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O5" s="33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P5" s="33" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q5" s="34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="3:17">
       <c r="C6" s="35"/>
       <c r="D6" s="36" t="s">
-        <v>226</v>
+        <v>55</v>
       </c>
       <c r="E6" s="37" t="s">
         <v>1</v>
@@ -3157,10 +3362,10 @@
         <v>359</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L6" s="38">
         <f t="shared" ref="L6:L37" si="1">I6/N6</f>
@@ -3185,10 +3390,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:17">
       <c r="C7" s="35"/>
       <c r="D7" s="36" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E7" s="37" t="s">
         <v>1</v>
@@ -3203,10 +3408,10 @@
         <v>258</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L7" s="38">
         <f t="shared" si="1"/>
@@ -3231,10 +3436,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:17">
       <c r="C8" s="35"/>
       <c r="D8" s="66" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E8" s="37" t="s">
         <v>1</v>
@@ -3249,10 +3454,10 @@
         <v>1909.3</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K8" s="38" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L8" s="38">
         <f t="shared" si="1"/>
@@ -3277,10 +3482,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:17">
       <c r="C9" s="35"/>
       <c r="D9" s="66" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" s="37" t="s">
         <v>1</v>
@@ -3297,10 +3502,10 @@
         <v>725</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L9" s="38">
         <f t="shared" si="1"/>
@@ -3325,10 +3530,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:17">
       <c r="C10" s="35"/>
       <c r="D10" s="66" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>1</v>
@@ -3343,10 +3548,10 @@
         <v>659</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L10" s="38">
         <f t="shared" si="1"/>
@@ -3371,10 +3576,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:17">
       <c r="C11" s="35"/>
       <c r="D11" s="66" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E11" s="37" t="s">
         <v>1</v>
@@ -3389,10 +3594,10 @@
         <v>2319.3000000000002</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L11" s="38">
         <f t="shared" si="1"/>
@@ -3417,10 +3622,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:17">
       <c r="C12" s="35"/>
       <c r="D12" s="66" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E12" s="37" t="s">
         <v>1</v>
@@ -3435,10 +3640,10 @@
         <v>2000</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L12" s="38">
         <f t="shared" si="1"/>
@@ -3463,10 +3668,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:17">
       <c r="C13" s="35"/>
       <c r="D13" s="66" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E13" s="37" t="s">
         <v>1</v>
@@ -3481,10 +3686,10 @@
         <v>372.43</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L13" s="38">
         <f t="shared" si="1"/>
@@ -3509,10 +3714,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:17">
       <c r="C14" s="35"/>
       <c r="D14" s="66" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>1</v>
@@ -3528,10 +3733,10 @@
         <v>-773.04</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L14" s="38">
         <f t="shared" si="1"/>
@@ -3556,10 +3761,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:17">
       <c r="C15" s="35"/>
       <c r="D15" s="66" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E15" s="37" t="s">
         <v>1</v>
@@ -3574,10 +3779,10 @@
         <v>531</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K15" s="38" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L15" s="38">
         <f t="shared" si="1"/>
@@ -3602,10 +3807,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:17">
       <c r="C16" s="35"/>
       <c r="D16" s="66" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E16" s="37"/>
       <c r="F16" s="37" t="s">
@@ -3620,10 +3825,10 @@
         <v>161.72999999999999</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L16" s="38">
         <f t="shared" si="1"/>
@@ -3648,10 +3853,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:17">
       <c r="C17" s="35"/>
       <c r="D17" s="66" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E17" s="37" t="s">
         <v>1</v>
@@ -3666,10 +3871,10 @@
         <v>72</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K17" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L17" s="38">
         <f t="shared" si="1"/>
@@ -3694,10 +3899,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:17">
       <c r="C18" s="35"/>
       <c r="D18" s="65" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E18" s="37"/>
       <c r="F18" s="37" t="s">
@@ -3712,10 +3917,10 @@
         <v>973.02</v>
       </c>
       <c r="J18" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L18" s="38">
         <f t="shared" si="1"/>
@@ -3740,10 +3945,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:17">
       <c r="C19" s="35"/>
       <c r="D19" s="65" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E19" s="37" t="s">
         <v>1</v>
@@ -3758,10 +3963,10 @@
         <v>379</v>
       </c>
       <c r="J19" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K19" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L19" s="38">
         <f t="shared" si="1"/>
@@ -3786,10 +3991,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:17">
       <c r="C20" s="35"/>
       <c r="D20" s="65" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>1</v>
@@ -3804,10 +4009,10 @@
         <v>297</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L20" s="38">
         <f t="shared" si="1"/>
@@ -3832,10 +4037,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:17">
       <c r="C21" s="35"/>
       <c r="D21" s="65" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E21" s="37" t="s">
         <v>1</v>
@@ -3850,10 +4055,10 @@
         <v>326.99</v>
       </c>
       <c r="J21" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L21" s="38">
         <f t="shared" si="1"/>
@@ -3878,10 +4083,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:17">
       <c r="C22" s="35"/>
       <c r="D22" s="70" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>1</v>
@@ -3898,10 +4103,10 @@
         <v>209.94</v>
       </c>
       <c r="J22" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L22" s="38">
         <f t="shared" si="1"/>
@@ -3926,10 +4131,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:17">
       <c r="C23" s="35"/>
       <c r="D23" s="70" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E23" s="37" t="s">
         <v>1</v>
@@ -3946,10 +4151,10 @@
         <v>249.5</v>
       </c>
       <c r="J23" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L23" s="38">
         <f t="shared" si="1"/>
@@ -3974,10 +4179,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:17">
       <c r="C24" s="35"/>
       <c r="D24" s="70" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E24" s="37" t="s">
         <v>1</v>
@@ -3994,10 +4199,10 @@
         <v>-209.94</v>
       </c>
       <c r="J24" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L24" s="38">
         <f t="shared" si="1"/>
@@ -4022,10 +4227,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:17">
       <c r="C25" s="35"/>
       <c r="D25" s="46" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E25" s="37" t="s">
         <v>1</v>
@@ -4042,10 +4247,10 @@
         <v>506</v>
       </c>
       <c r="J25" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L25" s="38">
         <f t="shared" si="1"/>
@@ -4067,10 +4272,10 @@
       </c>
       <c r="Q25" s="37"/>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:17">
       <c r="C26" s="35"/>
       <c r="D26" s="46" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>1</v>
@@ -4085,10 +4290,10 @@
         <v>399.9</v>
       </c>
       <c r="J26" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L26" s="38">
         <f t="shared" si="1"/>
@@ -4113,10 +4318,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:17">
       <c r="C27" s="35"/>
       <c r="D27" s="46" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E27" s="37" t="s">
         <v>1</v>
@@ -4131,10 +4336,10 @@
         <v>284</v>
       </c>
       <c r="J27" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L27" s="38">
         <f t="shared" si="1"/>
@@ -4159,10 +4364,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:17">
       <c r="C28" s="35"/>
       <c r="D28" s="46" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E28" s="37" t="s">
         <v>1</v>
@@ -4177,10 +4382,10 @@
         <v>500</v>
       </c>
       <c r="J28" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L28" s="38">
         <f t="shared" si="1"/>
@@ -4205,10 +4410,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:17">
       <c r="C29" s="35"/>
       <c r="D29" s="46" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>1</v>
@@ -4223,10 +4428,10 @@
         <v>300</v>
       </c>
       <c r="J29" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L29" s="38">
         <f t="shared" si="1"/>
@@ -4251,10 +4456,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:17">
       <c r="C30" s="35"/>
       <c r="D30" s="36" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>1</v>
@@ -4271,10 +4476,10 @@
         <v>1017.6</v>
       </c>
       <c r="J30" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L30" s="38">
         <f t="shared" si="1"/>
@@ -4299,10 +4504,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:17">
       <c r="C31" s="35"/>
       <c r="D31" s="46" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E31" s="37" t="s">
         <v>1</v>
@@ -4317,10 +4522,10 @@
         <v>1900</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L31" s="38">
         <f t="shared" si="1"/>
@@ -4345,10 +4550,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:17">
       <c r="C32" s="35"/>
       <c r="D32" s="46" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E32" s="37" t="s">
         <v>1</v>
@@ -4363,10 +4568,10 @@
         <v>474.33</v>
       </c>
       <c r="J32" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K32" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L32" s="38">
         <f t="shared" si="1"/>
@@ -4391,10 +4596,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:17">
       <c r="C33" s="35"/>
       <c r="D33" s="46" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E33" s="37" t="s">
         <v>1</v>
@@ -4409,10 +4614,10 @@
         <v>330</v>
       </c>
       <c r="J33" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L33" s="38">
         <f t="shared" si="1"/>
@@ -4437,10 +4642,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:17">
       <c r="C34" s="35"/>
       <c r="D34" s="46" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E34" s="37" t="s">
         <v>1</v>
@@ -4457,10 +4662,10 @@
         <v>1780</v>
       </c>
       <c r="J34" s="68" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K34" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L34" s="38">
         <f t="shared" si="1"/>
@@ -4485,10 +4690,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:17">
       <c r="C35" s="35"/>
       <c r="D35" s="46" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E35" s="37" t="s">
         <v>1</v>
@@ -4503,10 +4708,10 @@
         <v>286.39</v>
       </c>
       <c r="J35" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L35" s="38">
         <f t="shared" si="1"/>
@@ -4531,10 +4736,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:17">
       <c r="C36" s="35"/>
       <c r="D36" s="46" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E36" s="37" t="s">
         <v>1</v>
@@ -4549,10 +4754,10 @@
         <v>1181.1400000000001</v>
       </c>
       <c r="J36" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L36" s="38">
         <f t="shared" si="1"/>
@@ -4577,10 +4782,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:17">
       <c r="C37" s="35"/>
       <c r="D37" s="46" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E37" s="37" t="s">
         <v>1</v>
@@ -4597,10 +4802,10 @@
         <v>224.24</v>
       </c>
       <c r="J37" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L37" s="38">
         <f t="shared" si="1"/>
@@ -4625,12 +4830,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:17">
       <c r="C38" s="35" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D38" s="46" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>1</v>
@@ -4645,10 +4850,10 @@
         <v>279</v>
       </c>
       <c r="J38" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K38" s="38" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L38" s="38">
         <f t="shared" ref="L38:L69" si="7">I38/N38</f>
@@ -4673,10 +4878,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:17">
       <c r="C39" s="35"/>
       <c r="D39" s="36" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E39" s="37" t="s">
         <v>1</v>
@@ -4693,10 +4898,10 @@
         <v>22.45</v>
       </c>
       <c r="J39" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K39" s="37" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L39" s="38">
         <f t="shared" si="7"/>
@@ -4719,10 +4924,10 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:17">
       <c r="C40" s="35"/>
       <c r="D40" s="46" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E40" s="37" t="s">
         <v>1</v>
@@ -4739,10 +4944,10 @@
         <v>60</v>
       </c>
       <c r="J40" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L40" s="38">
         <f t="shared" si="7"/>
@@ -4765,10 +4970,10 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:17">
       <c r="C41" s="35"/>
       <c r="D41" s="36" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E41" s="37" t="s">
         <v>1</v>
@@ -4785,10 +4990,10 @@
         <v>395.54</v>
       </c>
       <c r="J41" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K41" s="37" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L41" s="38">
         <f t="shared" si="7"/>
@@ -4811,10 +5016,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:17">
       <c r="C42" s="35"/>
       <c r="D42" s="36" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E42" s="37" t="s">
         <v>1</v>
@@ -4828,21 +5033,21 @@
         <v>2</v>
       </c>
       <c r="I42" s="38">
-        <v>319.42</v>
+        <v>197</v>
       </c>
       <c r="J42" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L42" s="38">
         <f t="shared" si="7"/>
-        <v>319.42</v>
+        <v>197</v>
       </c>
       <c r="M42" s="38">
         <f t="shared" si="8"/>
-        <v>159.71</v>
+        <v>98.5</v>
       </c>
       <c r="N42" s="39">
         <v>1</v>
@@ -4857,10 +5062,10 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:17">
       <c r="C43" s="35"/>
       <c r="D43" s="46" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E43" s="37" t="s">
         <v>1</v>
@@ -4877,10 +5082,10 @@
         <v>225</v>
       </c>
       <c r="J43" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K43" s="37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L43" s="38">
         <f t="shared" si="7"/>
@@ -4903,10 +5108,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:17">
       <c r="C44" s="35"/>
       <c r="D44" s="36" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E44" s="37" t="s">
         <v>1</v>
@@ -4923,10 +5128,10 @@
         <v>166.15</v>
       </c>
       <c r="J44" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L44" s="38">
         <f t="shared" si="7"/>
@@ -4949,10 +5154,10 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:17">
       <c r="C45" s="35"/>
       <c r="D45" s="36" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E45" s="37" t="s">
         <v>1</v>
@@ -4969,10 +5174,10 @@
         <v>19.899999999999999</v>
       </c>
       <c r="J45" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K45" s="37" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L45" s="38">
         <f t="shared" si="7"/>
@@ -4995,10 +5200,10 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:17">
       <c r="C46" s="35"/>
       <c r="D46" s="46" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E46" s="37" t="s">
         <v>1</v>
@@ -5013,10 +5218,10 @@
         <v>284.05</v>
       </c>
       <c r="J46" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L46" s="38">
         <f t="shared" si="7"/>
@@ -5039,10 +5244,10 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:17">
       <c r="C47" s="35"/>
       <c r="D47" s="46" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E47" s="37" t="s">
         <v>1</v>
@@ -5057,10 +5262,10 @@
         <v>110</v>
       </c>
       <c r="J47" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K47" s="38" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L47" s="38">
         <f t="shared" si="7"/>
@@ -5083,10 +5288,10 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:17">
       <c r="C48" s="35"/>
       <c r="D48" s="46" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E48" s="37" t="s">
         <v>1</v>
@@ -5101,10 +5306,10 @@
         <v>118.4</v>
       </c>
       <c r="J48" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K48" s="38" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L48" s="38">
         <f t="shared" si="7"/>
@@ -5124,10 +5329,10 @@
       </c>
       <c r="Q48" s="37"/>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:17">
       <c r="C49" s="35"/>
       <c r="D49" s="36" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E49" s="37" t="s">
         <v>1</v>
@@ -5142,10 +5347,10 @@
         <v>26.9</v>
       </c>
       <c r="J49" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K49" s="37" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L49" s="38">
         <f t="shared" si="7"/>
@@ -5168,10 +5373,10 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:17">
       <c r="C50" s="35"/>
       <c r="D50" s="46" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E50" s="37" t="s">
         <v>1</v>
@@ -5186,10 +5391,10 @@
         <v>70</v>
       </c>
       <c r="J50" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K50" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L50" s="38">
         <f t="shared" si="7"/>
@@ -5209,10 +5414,10 @@
       </c>
       <c r="Q50" s="37"/>
     </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:17">
       <c r="C51" s="35"/>
       <c r="D51" s="67" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E51" s="37" t="s">
         <v>1</v>
@@ -5224,21 +5429,21 @@
         <v>1</v>
       </c>
       <c r="I51" s="38">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="J51" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K51" s="38" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L51" s="38">
         <f t="shared" si="7"/>
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="M51" s="38">
         <f t="shared" si="8"/>
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="N51" s="39">
         <v>1</v>
@@ -5253,10 +5458,10 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:17">
       <c r="C52" s="35"/>
       <c r="D52" s="46" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E52" s="37" t="s">
         <v>1</v>
@@ -5273,10 +5478,10 @@
         <v>-43</v>
       </c>
       <c r="J52" s="38" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K52" s="38" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L52" s="38">
         <f t="shared" si="7"/>
@@ -5299,10 +5504,10 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:17">
       <c r="C53" s="35"/>
       <c r="D53" s="46" t="s">
-        <v>227</v>
+        <v>116</v>
       </c>
       <c r="E53" s="37" t="s">
         <v>1</v>
@@ -5319,10 +5524,10 @@
         <v>217.85</v>
       </c>
       <c r="J53" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K53" s="38" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L53" s="38">
         <f t="shared" si="7"/>
@@ -5347,10 +5552,10 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:17">
       <c r="C54" s="35"/>
       <c r="D54" s="46" t="s">
-        <v>228</v>
+        <v>117</v>
       </c>
       <c r="E54" s="37" t="s">
         <v>1</v>
@@ -5365,10 +5570,10 @@
         <v>300</v>
       </c>
       <c r="J54" s="38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K54" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L54" s="38">
         <f t="shared" si="7"/>
@@ -5393,10 +5598,10 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:17">
       <c r="C55" s="35"/>
       <c r="D55" s="46" t="s">
-        <v>231</v>
+        <v>118</v>
       </c>
       <c r="E55" s="37" t="s">
         <v>1</v>
@@ -5412,10 +5617,10 @@
         <v>37.909999999999997</v>
       </c>
       <c r="J55" s="38" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="K55" s="38" t="s">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="L55" s="38">
         <f t="shared" si="7"/>
@@ -5440,10 +5645,10 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:17">
       <c r="C56" s="35"/>
       <c r="D56" s="46" t="s">
-        <v>232</v>
+        <v>121</v>
       </c>
       <c r="E56" s="37" t="s">
         <v>1</v>
@@ -5460,10 +5665,10 @@
         <v>66</v>
       </c>
       <c r="J56" s="38" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="K56" s="38" t="s">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="L56" s="38">
         <f t="shared" si="7"/>
@@ -5488,10 +5693,10 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:17">
       <c r="C57" s="35"/>
       <c r="D57" s="46" t="s">
-        <v>242</v>
+        <v>123</v>
       </c>
       <c r="E57" s="37" t="s">
         <v>1</v>
@@ -5508,10 +5713,10 @@
         <v>265</v>
       </c>
       <c r="J57" s="38" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="K57" s="38" t="s">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="L57" s="38">
         <f t="shared" si="7"/>
@@ -5536,10 +5741,10 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:17">
       <c r="C58" s="35"/>
-      <c r="D58" s="79" t="s">
-        <v>234</v>
+      <c r="D58" s="36" t="s">
+        <v>124</v>
       </c>
       <c r="E58" s="37" t="s">
         <v>1</v>
@@ -5555,10 +5760,10 @@
         <v>369</v>
       </c>
       <c r="J58" s="38" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="K58" s="38" t="s">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="L58" s="38">
         <f t="shared" si="7"/>
@@ -5583,10 +5788,10 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:17">
       <c r="C59" s="35"/>
       <c r="D59" s="46" t="s">
-        <v>235</v>
+        <v>125</v>
       </c>
       <c r="E59" s="37" t="s">
         <v>1</v>
@@ -5603,10 +5808,10 @@
         <v>120</v>
       </c>
       <c r="J59" s="38" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="K59" s="38" t="s">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="L59" s="38">
         <f t="shared" si="7"/>
@@ -5631,10 +5836,10 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:17">
       <c r="C60" s="35"/>
       <c r="D60" s="46" t="s">
-        <v>236</v>
+        <v>126</v>
       </c>
       <c r="E60" s="37" t="s">
         <v>1</v>
@@ -5649,10 +5854,10 @@
         <v>85</v>
       </c>
       <c r="J60" s="38" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="K60" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L60" s="38">
         <f t="shared" si="7"/>
@@ -5677,10 +5882,10 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:17">
       <c r="C61" s="35"/>
       <c r="D61" s="46" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
       <c r="E61" s="37" t="s">
         <v>1</v>
@@ -5698,10 +5903,10 @@
         <v>85.786666666666676</v>
       </c>
       <c r="J61" s="38" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="K61" s="38" t="s">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="L61" s="38">
         <f t="shared" si="7"/>
@@ -5726,10 +5931,10 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:17">
       <c r="C62" s="35"/>
       <c r="D62" s="46" t="s">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
@@ -5743,10 +5948,10 @@
         <v>42.895000000000003</v>
       </c>
       <c r="J62" s="38" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="K62" s="38" t="s">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="L62" s="38">
         <f t="shared" si="7"/>
@@ -5771,10 +5976,10 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:17">
       <c r="C63" s="35"/>
       <c r="D63" s="46" t="s">
-        <v>239</v>
+        <v>129</v>
       </c>
       <c r="E63" s="37" t="s">
         <v>1</v>
@@ -5791,10 +5996,10 @@
         <v>40</v>
       </c>
       <c r="J63" s="38" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="K63" s="38" t="s">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="L63" s="38">
         <f t="shared" si="7"/>
@@ -5819,10 +6024,10 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:17">
       <c r="C64" s="35"/>
       <c r="D64" s="46" t="s">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="E64" s="37"/>
       <c r="F64" s="37"/>
@@ -5835,10 +6040,10 @@
         <v>20</v>
       </c>
       <c r="J64" s="38" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="L64" s="38">
         <f t="shared" si="7"/>
@@ -5863,10 +6068,10 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:17">
       <c r="C65" s="35"/>
       <c r="D65" s="46" t="s">
-        <v>241</v>
+        <v>131</v>
       </c>
       <c r="E65" s="37" t="s">
         <v>1</v>
@@ -5883,10 +6088,10 @@
         <v>56.42</v>
       </c>
       <c r="J65" s="38" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="K65" s="38" t="s">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="L65" s="38">
         <f t="shared" si="7"/>
@@ -5899,7 +6104,9 @@
       <c r="N65" s="39">
         <v>1</v>
       </c>
-      <c r="O65" s="64"/>
+      <c r="O65" s="64">
+        <v>46298</v>
+      </c>
       <c r="P65" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5909,10 +6116,10 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:17">
       <c r="C66" s="35"/>
       <c r="D66" s="46" t="s">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="E66" s="37" t="s">
         <v>1</v>
@@ -5927,10 +6134,10 @@
         <v>-338</v>
       </c>
       <c r="J66" s="38" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L66" s="38">
         <f t="shared" si="7"/>
@@ -5943,7 +6150,9 @@
       <c r="N66" s="39">
         <v>1</v>
       </c>
-      <c r="O66" s="64"/>
+      <c r="O66" s="64">
+        <v>46298</v>
+      </c>
       <c r="P66" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5953,10 +6162,10 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:17">
       <c r="C67" s="35"/>
       <c r="D67" s="46" t="s">
-        <v>245</v>
+        <v>133</v>
       </c>
       <c r="E67" s="37" t="s">
         <v>1</v>
@@ -5971,10 +6180,10 @@
         <v>638</v>
       </c>
       <c r="J67" s="38" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="K67" s="38" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L67" s="38">
         <f t="shared" si="7"/>
@@ -5987,7 +6196,9 @@
       <c r="N67" s="39">
         <v>1</v>
       </c>
-      <c r="O67" s="64"/>
+      <c r="O67" s="64">
+        <v>46298</v>
+      </c>
       <c r="P67" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5997,31 +6208,43 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:17">
       <c r="C68" s="35"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="37"/>
+      <c r="D68" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="E68" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F68" s="37"/>
       <c r="G68" s="37"/>
       <c r="H68" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I68" s="38"/>
-      <c r="J68" s="38"/>
-      <c r="K68" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I68" s="38">
+        <v>60</v>
+      </c>
+      <c r="J68" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="K68" s="38" t="s">
+        <v>56</v>
+      </c>
       <c r="L68" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M68" s="38" t="str">
+        <v>60</v>
+      </c>
+      <c r="M68" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>60</v>
       </c>
       <c r="N68" s="39">
         <v>1</v>
       </c>
-      <c r="O68" s="64"/>
+      <c r="O68" s="64">
+        <v>46298</v>
+      </c>
       <c r="P68" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6031,31 +6254,45 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:17">
       <c r="C69" s="35"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
+      <c r="D69" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="E69" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G69" s="37"/>
       <c r="H69" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I69" s="38"/>
-      <c r="J69" s="38"/>
-      <c r="K69" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I69" s="38">
+        <v>91.5</v>
+      </c>
+      <c r="J69" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K69" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="L69" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M69" s="38" t="str">
+        <v>91.5</v>
+      </c>
+      <c r="M69" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>45.75</v>
       </c>
       <c r="N69" s="39">
         <v>1</v>
       </c>
-      <c r="O69" s="64"/>
+      <c r="O69" s="64">
+        <v>46298</v>
+      </c>
       <c r="P69" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6065,33 +6302,45 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:17">
       <c r="C70" s="35"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="37"/>
+      <c r="D70" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="E70" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F70" s="37"/>
       <c r="G70" s="37"/>
       <c r="H70" s="37">
-        <f t="shared" ref="H70:H101" si="11">COUNTA(E70:G70)</f>
-        <v>0</v>
-      </c>
-      <c r="I70" s="38"/>
-      <c r="J70" s="38"/>
-      <c r="K70" s="38"/>
+        <f t="shared" ref="H70:H99" si="11">COUNTA(E70:G70)</f>
+        <v>1</v>
+      </c>
+      <c r="I70" s="38">
+        <v>-51.5</v>
+      </c>
+      <c r="J70" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="K70" s="38" t="s">
+        <v>115</v>
+      </c>
       <c r="L70" s="38">
-        <f t="shared" ref="L70:L101" si="12">I70/N70</f>
-        <v>0</v>
-      </c>
-      <c r="M70" s="38" t="str">
-        <f t="shared" ref="M70:M101" si="13">IFERROR(L70/H70,"")</f>
-        <v/>
+        <f t="shared" ref="L70:L99" si="12">I70/N70</f>
+        <v>-51.5</v>
+      </c>
+      <c r="M70" s="38">
+        <f t="shared" ref="M70:M99" si="13">IFERROR(L70/H70,"")</f>
+        <v>-51.5</v>
       </c>
       <c r="N70" s="39">
         <v>1</v>
       </c>
-      <c r="O70" s="64"/>
+      <c r="O70" s="64">
+        <v>46298</v>
+      </c>
       <c r="P70" s="64" t="str">
-        <f t="shared" ref="P70:P101" si="14">IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
+        <f t="shared" ref="P70:P99" si="14">IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
         <v/>
       </c>
       <c r="Q70" s="37" t="str">
@@ -6099,31 +6348,43 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:17">
       <c r="C71" s="35"/>
-      <c r="D71" s="46"/>
+      <c r="D71" s="46" t="s">
+        <v>136</v>
+      </c>
       <c r="E71" s="37"/>
-      <c r="F71" s="37"/>
+      <c r="F71" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G71" s="37"/>
       <c r="H71" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I71" s="38"/>
-      <c r="J71" s="38"/>
-      <c r="K71" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I71" s="38">
+        <v>-40</v>
+      </c>
+      <c r="J71" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="K71" s="38" t="s">
+        <v>115</v>
+      </c>
       <c r="L71" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M71" s="38" t="str">
+        <v>-40</v>
+      </c>
+      <c r="M71" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>-40</v>
       </c>
       <c r="N71" s="39">
         <v>1</v>
       </c>
-      <c r="O71" s="64"/>
+      <c r="O71" s="64">
+        <v>46298</v>
+      </c>
       <c r="P71" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6133,31 +6394,43 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:17">
       <c r="C72" s="35"/>
-      <c r="D72" s="46"/>
+      <c r="D72" s="46" t="s">
+        <v>137</v>
+      </c>
       <c r="E72" s="37"/>
       <c r="F72" s="37"/>
-      <c r="G72" s="37"/>
+      <c r="G72" s="37" t="s">
+        <v>33</v>
+      </c>
       <c r="H72" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I72" s="38"/>
-      <c r="J72" s="38"/>
-      <c r="K72" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I72" s="38">
+        <v>53</v>
+      </c>
+      <c r="J72" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K72" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="L72" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M72" s="38" t="str">
+        <v>53</v>
+      </c>
+      <c r="M72" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>53</v>
       </c>
       <c r="N72" s="39">
         <v>1</v>
       </c>
-      <c r="O72" s="64"/>
+      <c r="O72" s="64">
+        <v>46298</v>
+      </c>
       <c r="P72" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6167,31 +6440,43 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:17">
       <c r="C73" s="35"/>
-      <c r="D73" s="46"/>
+      <c r="D73" s="46" t="s">
+        <v>138</v>
+      </c>
       <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
+      <c r="F73" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G73" s="37"/>
       <c r="H73" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I73" s="38"/>
-      <c r="J73" s="38"/>
-      <c r="K73" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I73" s="38">
+        <v>35</v>
+      </c>
+      <c r="J73" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K73" s="38" t="s">
+        <v>62</v>
+      </c>
       <c r="L73" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M73" s="38" t="str">
+        <v>35</v>
+      </c>
+      <c r="M73" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>35</v>
       </c>
       <c r="N73" s="39">
         <v>1</v>
       </c>
-      <c r="O73" s="64"/>
+      <c r="O73" s="64">
+        <v>46298</v>
+      </c>
       <c r="P73" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6201,31 +6486,45 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:17">
       <c r="C74" s="35"/>
-      <c r="D74" s="46"/>
-      <c r="E74" s="37"/>
-      <c r="F74" s="37"/>
+      <c r="D74" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="E74" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G74" s="37"/>
       <c r="H74" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I74" s="38"/>
-      <c r="J74" s="38"/>
-      <c r="K74" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I74" s="38">
+        <v>66</v>
+      </c>
+      <c r="J74" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K74" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="L74" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M74" s="38" t="str">
+        <v>66</v>
+      </c>
+      <c r="M74" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>33</v>
       </c>
       <c r="N74" s="39">
         <v>1</v>
       </c>
-      <c r="O74" s="64"/>
+      <c r="O74" s="64">
+        <v>46298</v>
+      </c>
       <c r="P74" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6235,31 +6534,43 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:17">
       <c r="C75" s="35"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="37"/>
+      <c r="D75" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="E75" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F75" s="37"/>
       <c r="G75" s="37"/>
       <c r="H75" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I75" s="38"/>
-      <c r="J75" s="38"/>
-      <c r="K75" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I75" s="38">
+        <v>-33</v>
+      </c>
+      <c r="J75" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="K75" s="38" t="s">
+        <v>115</v>
+      </c>
       <c r="L75" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M75" s="38" t="str">
+        <v>-33</v>
+      </c>
+      <c r="M75" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>-33</v>
       </c>
       <c r="N75" s="39">
         <v>1</v>
       </c>
-      <c r="O75" s="64"/>
+      <c r="O75" s="64">
+        <v>46298</v>
+      </c>
       <c r="P75" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6269,31 +6580,44 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:17">
       <c r="C76" s="35"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="37"/>
+      <c r="D76" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="E76" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F76" s="37"/>
       <c r="G76" s="37"/>
       <c r="H76" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I76" s="38"/>
-      <c r="J76" s="38"/>
-      <c r="K76" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I76" s="38">
+        <f>(113.71/3)*2</f>
+        <v>75.806666666666658</v>
+      </c>
+      <c r="J76" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K76" s="38" t="s">
+        <v>120</v>
+      </c>
       <c r="L76" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M76" s="38" t="str">
+        <v>75.806666666666658</v>
+      </c>
+      <c r="M76" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>75.806666666666658</v>
       </c>
       <c r="N76" s="39">
         <v>1</v>
       </c>
-      <c r="O76" s="64"/>
+      <c r="O76" s="64">
+        <v>46298</v>
+      </c>
       <c r="P76" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6303,9 +6627,11 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:17">
       <c r="C77" s="35"/>
-      <c r="D77" s="46"/>
+      <c r="D77" s="46" t="s">
+        <v>142</v>
+      </c>
       <c r="E77" s="37"/>
       <c r="F77" s="37"/>
       <c r="G77" s="37"/>
@@ -6313,12 +6639,18 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I77" s="38"/>
-      <c r="J77" s="38"/>
-      <c r="K77" s="38"/>
+      <c r="I77" s="38">
+        <v>37.9</v>
+      </c>
+      <c r="J77" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K77" s="38" t="s">
+        <v>120</v>
+      </c>
       <c r="L77" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>37.9</v>
       </c>
       <c r="M77" s="38" t="str">
         <f t="shared" si="13"/>
@@ -6327,7 +6659,9 @@
       <c r="N77" s="39">
         <v>1</v>
       </c>
-      <c r="O77" s="64"/>
+      <c r="O77" s="64">
+        <v>46298</v>
+      </c>
       <c r="P77" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6337,31 +6671,43 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:17">
       <c r="C78" s="35"/>
-      <c r="D78" s="46"/>
-      <c r="E78" s="37"/>
+      <c r="D78" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="E78" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F78" s="37"/>
       <c r="G78" s="37"/>
       <c r="H78" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I78" s="38"/>
-      <c r="J78" s="38"/>
-      <c r="K78" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I78" s="38">
+        <v>-66</v>
+      </c>
+      <c r="J78" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="K78" s="38" t="s">
+        <v>115</v>
+      </c>
       <c r="L78" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M78" s="38" t="str">
+        <v>-66</v>
+      </c>
+      <c r="M78" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>-66</v>
       </c>
       <c r="N78" s="39">
         <v>1</v>
       </c>
-      <c r="O78" s="64"/>
+      <c r="O78" s="64">
+        <v>46298</v>
+      </c>
       <c r="P78" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6371,31 +6717,45 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:17">
       <c r="C79" s="35"/>
-      <c r="D79" s="46"/>
-      <c r="E79" s="37"/>
-      <c r="F79" s="37"/>
+      <c r="D79" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="E79" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F79" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G79" s="37"/>
       <c r="H79" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I79" s="38"/>
-      <c r="J79" s="38"/>
-      <c r="K79" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I79" s="38">
+        <v>112</v>
+      </c>
+      <c r="J79" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K79" s="38" t="s">
+        <v>145</v>
+      </c>
       <c r="L79" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M79" s="38" t="str">
+        <v>112</v>
+      </c>
+      <c r="M79" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>56</v>
       </c>
       <c r="N79" s="39">
         <v>1</v>
       </c>
-      <c r="O79" s="64"/>
+      <c r="O79" s="64">
+        <v>46298</v>
+      </c>
       <c r="P79" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6405,31 +6765,46 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:17">
       <c r="C80" s="35"/>
-      <c r="D80" s="46"/>
-      <c r="E80" s="37"/>
-      <c r="F80" s="37"/>
+      <c r="D80" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="E80" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G80" s="37"/>
       <c r="H80" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I80" s="38"/>
-      <c r="J80" s="38"/>
-      <c r="K80" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I80" s="38">
+        <f>151.69/2</f>
+        <v>75.844999999999999</v>
+      </c>
+      <c r="J80" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K80" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="L80" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M80" s="38" t="str">
+        <v>75.844999999999999</v>
+      </c>
+      <c r="M80" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>37.922499999999999</v>
       </c>
       <c r="N80" s="39">
         <v>1</v>
       </c>
-      <c r="O80" s="64"/>
+      <c r="O80" s="64">
+        <v>46298</v>
+      </c>
       <c r="P80" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6439,31 +6814,43 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:17">
       <c r="C81" s="35"/>
-      <c r="D81" s="46"/>
-      <c r="E81" s="37"/>
+      <c r="D81" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="E81" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F81" s="37"/>
       <c r="G81" s="37"/>
       <c r="H81" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I81" s="38"/>
-      <c r="J81" s="38"/>
-      <c r="K81" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I81" s="38">
+        <v>-45</v>
+      </c>
+      <c r="J81" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="K81" s="38" t="s">
+        <v>115</v>
+      </c>
       <c r="L81" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M81" s="38" t="str">
+        <v>-45</v>
+      </c>
+      <c r="M81" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>-45</v>
       </c>
       <c r="N81" s="39">
         <v>1</v>
       </c>
-      <c r="O81" s="64"/>
+      <c r="O81" s="64">
+        <v>46298</v>
+      </c>
       <c r="P81" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6473,31 +6860,44 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:17">
       <c r="C82" s="35"/>
-      <c r="D82" s="46"/>
+      <c r="D82" s="46" t="s">
+        <v>146</v>
+      </c>
       <c r="E82" s="37"/>
       <c r="F82" s="37"/>
-      <c r="G82" s="37"/>
+      <c r="G82" s="37" t="s">
+        <v>33</v>
+      </c>
       <c r="H82" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I82" s="38"/>
-      <c r="J82" s="38"/>
-      <c r="K82" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I82" s="38">
+        <f>151.69/2</f>
+        <v>75.844999999999999</v>
+      </c>
+      <c r="J82" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K82" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="L82" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M82" s="38" t="str">
+        <v>75.844999999999999</v>
+      </c>
+      <c r="M82" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>75.844999999999999</v>
       </c>
       <c r="N82" s="39">
         <v>1</v>
       </c>
-      <c r="O82" s="64"/>
+      <c r="O82" s="64">
+        <v>46298</v>
+      </c>
       <c r="P82" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6507,65 +6907,91 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:17">
       <c r="C83" s="35"/>
-      <c r="D83" s="46"/>
-      <c r="E83" s="37"/>
+      <c r="D83" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F83" s="37"/>
       <c r="G83" s="37"/>
       <c r="H83" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I83" s="38"/>
-      <c r="J83" s="38"/>
-      <c r="K83" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I83" s="38">
+        <v>88.1</v>
+      </c>
+      <c r="J83" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K83" s="38" t="s">
+        <v>145</v>
+      </c>
       <c r="L83" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M83" s="38" t="str">
+        <v>88.1</v>
+      </c>
+      <c r="M83" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>88.1</v>
       </c>
       <c r="N83" s="39">
         <v>1</v>
       </c>
-      <c r="O83" s="64"/>
+      <c r="O83" s="64">
+        <v>46298</v>
+      </c>
       <c r="P83" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q83" s="37" t="str">
-        <f t="shared" ref="Q83:Q114" ca="1" si="15">IF(O83&lt;&gt;"",IFERROR(DATEDIF(O83,TODAY(),"m")+1,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q83:Q112" ca="1" si="15">IF(O83&lt;&gt;"",IFERROR(DATEDIF(O83,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="3:17">
       <c r="C84" s="35"/>
-      <c r="D84" s="46"/>
-      <c r="E84" s="37"/>
-      <c r="F84" s="37"/>
+      <c r="D84" s="46" t="s">
+        <v>149</v>
+      </c>
+      <c r="E84" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G84" s="37"/>
       <c r="H84" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I84" s="38"/>
-      <c r="J84" s="38"/>
-      <c r="K84" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I84" s="38">
+        <v>47.81</v>
+      </c>
+      <c r="J84" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K84" s="38" t="s">
+        <v>62</v>
+      </c>
       <c r="L84" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M84" s="38" t="str">
+        <v>47.81</v>
+      </c>
+      <c r="M84" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>23.905000000000001</v>
       </c>
       <c r="N84" s="39">
         <v>1</v>
       </c>
-      <c r="O84" s="64"/>
+      <c r="O84" s="64">
+        <v>46298</v>
+      </c>
       <c r="P84" s="64" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6575,31 +7001,45 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:17">
       <c r="C85" s="35"/>
-      <c r="D85" s="46"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="37"/>
+      <c r="D85" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E85" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G85" s="37"/>
       <c r="H85" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I85" s="38"/>
-      <c r="J85" s="38"/>
-      <c r="K85" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I85" s="38">
+        <v>265</v>
+      </c>
+      <c r="J85" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K85" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="L85" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M85" s="38" t="str">
+        <v>265</v>
+      </c>
+      <c r="M85" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>132.5</v>
       </c>
       <c r="N85" s="39">
         <v>1</v>
       </c>
-      <c r="O85" s="35"/>
+      <c r="O85" s="64">
+        <v>46298</v>
+      </c>
       <c r="P85" s="35" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6609,31 +7049,43 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:17">
       <c r="C86" s="35"/>
-      <c r="D86" s="46"/>
-      <c r="E86" s="37"/>
+      <c r="D86" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="E86" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F86" s="37"/>
       <c r="G86" s="37"/>
       <c r="H86" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I86" s="38"/>
-      <c r="J86" s="38"/>
-      <c r="K86" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I86" s="38">
+        <v>-130</v>
+      </c>
+      <c r="J86" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="K86" s="38" t="s">
+        <v>115</v>
+      </c>
       <c r="L86" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M86" s="38" t="str">
+        <v>-130</v>
+      </c>
+      <c r="M86" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>-130</v>
       </c>
       <c r="N86" s="39">
         <v>1</v>
       </c>
-      <c r="O86" s="35"/>
+      <c r="O86" s="64">
+        <v>46298</v>
+      </c>
       <c r="P86" s="35" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6643,31 +7095,45 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:17">
       <c r="C87" s="35"/>
-      <c r="D87" s="46"/>
-      <c r="E87" s="37"/>
-      <c r="F87" s="37"/>
+      <c r="D87" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="E87" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F87" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G87" s="37"/>
       <c r="H87" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I87" s="38"/>
-      <c r="J87" s="38"/>
-      <c r="K87" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I87" s="38">
+        <v>10</v>
+      </c>
+      <c r="J87" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="K87" s="38" t="s">
+        <v>56</v>
+      </c>
       <c r="L87" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M87" s="38" t="str">
+        <v>10</v>
+      </c>
+      <c r="M87" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="N87" s="39">
         <v>1</v>
       </c>
-      <c r="O87" s="35"/>
+      <c r="O87" s="64">
+        <v>46298</v>
+      </c>
       <c r="P87" s="35" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6677,31 +7143,45 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:17">
       <c r="C88" s="35"/>
-      <c r="D88" s="46"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
+      <c r="D88" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="E88" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F88" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G88" s="37"/>
       <c r="H88" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I88" s="38"/>
-      <c r="J88" s="38"/>
-      <c r="K88" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I88" s="38">
+        <v>64</v>
+      </c>
+      <c r="J88" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K88" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="L88" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M88" s="38" t="str">
+        <v>64</v>
+      </c>
+      <c r="M88" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>32</v>
       </c>
       <c r="N88" s="39">
         <v>1</v>
       </c>
-      <c r="O88" s="35"/>
+      <c r="O88" s="64">
+        <v>46298</v>
+      </c>
       <c r="P88" s="35" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6711,31 +7191,45 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:17">
       <c r="C89" s="35"/>
-      <c r="D89" s="46"/>
-      <c r="E89" s="37"/>
-      <c r="F89" s="37"/>
+      <c r="D89" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="E89" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F89" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G89" s="37"/>
       <c r="H89" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I89" s="38"/>
-      <c r="J89" s="38"/>
-      <c r="K89" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I89" s="38">
+        <v>97</v>
+      </c>
+      <c r="J89" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K89" s="38" t="s">
+        <v>145</v>
+      </c>
       <c r="L89" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M89" s="38" t="str">
+        <v>97</v>
+      </c>
+      <c r="M89" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>48.5</v>
       </c>
       <c r="N89" s="39">
         <v>1</v>
       </c>
-      <c r="O89" s="35"/>
+      <c r="O89" s="64">
+        <v>46298</v>
+      </c>
       <c r="P89" s="35" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6745,31 +7239,43 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:17">
       <c r="C90" s="35"/>
-      <c r="D90" s="46"/>
-      <c r="E90" s="37"/>
+      <c r="D90" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="E90" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F90" s="37"/>
       <c r="G90" s="37"/>
       <c r="H90" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I90" s="38"/>
-      <c r="J90" s="38"/>
-      <c r="K90" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I90" s="38">
+        <v>43.39</v>
+      </c>
+      <c r="J90" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K90" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="L90" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M90" s="38" t="str">
+        <v>43.39</v>
+      </c>
+      <c r="M90" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>43.39</v>
       </c>
       <c r="N90" s="39">
         <v>1</v>
       </c>
-      <c r="O90" s="35"/>
+      <c r="O90" s="64">
+        <v>46298</v>
+      </c>
       <c r="P90" s="35" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6779,31 +7285,43 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:17">
       <c r="C91" s="35"/>
-      <c r="D91" s="46"/>
-      <c r="E91" s="37"/>
+      <c r="D91" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="E91" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F91" s="37"/>
       <c r="G91" s="37"/>
       <c r="H91" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I91" s="38"/>
-      <c r="J91" s="38"/>
-      <c r="K91" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I91" s="38">
+        <v>-45</v>
+      </c>
+      <c r="J91" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="K91" s="38" t="s">
+        <v>115</v>
+      </c>
       <c r="L91" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M91" s="38" t="str">
+        <v>-45</v>
+      </c>
+      <c r="M91" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>-45</v>
       </c>
       <c r="N91" s="39">
         <v>1</v>
       </c>
-      <c r="O91" s="35"/>
+      <c r="O91" s="64">
+        <v>46298</v>
+      </c>
       <c r="P91" s="35" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -6813,9 +7331,11 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:17">
       <c r="C92" s="35"/>
-      <c r="D92" s="46"/>
+      <c r="D92" s="46" t="s">
+        <v>157</v>
+      </c>
       <c r="E92" s="37"/>
       <c r="F92" s="37"/>
       <c r="G92" s="37"/>
@@ -6823,12 +7343,18 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I92" s="38"/>
-      <c r="J92" s="38"/>
-      <c r="K92" s="38"/>
+      <c r="I92" s="38">
+        <v>116.33</v>
+      </c>
+      <c r="J92" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K92" s="38" t="s">
+        <v>158</v>
+      </c>
       <c r="L92" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>116.33</v>
       </c>
       <c r="M92" s="38" t="str">
         <f t="shared" si="13"/>
@@ -6847,9 +7373,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:17">
       <c r="C93" s="35"/>
-      <c r="D93" s="46"/>
+      <c r="D93" s="46" t="s">
+        <v>159</v>
+      </c>
       <c r="E93" s="37"/>
       <c r="F93" s="37"/>
       <c r="G93" s="37"/>
@@ -6857,12 +7385,18 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I93" s="38"/>
-      <c r="J93" s="38"/>
-      <c r="K93" s="38"/>
+      <c r="I93" s="38">
+        <v>116.33</v>
+      </c>
+      <c r="J93" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K93" s="38" t="s">
+        <v>158</v>
+      </c>
       <c r="L93" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>116.33</v>
       </c>
       <c r="M93" s="38" t="str">
         <f t="shared" si="13"/>
@@ -6881,9 +7415,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:17">
       <c r="C94" s="35"/>
-      <c r="D94" s="46"/>
+      <c r="D94" s="46" t="s">
+        <v>160</v>
+      </c>
       <c r="E94" s="37"/>
       <c r="F94" s="37"/>
       <c r="G94" s="37"/>
@@ -6891,12 +7427,18 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I94" s="38"/>
-      <c r="J94" s="38"/>
-      <c r="K94" s="38"/>
+      <c r="I94" s="38">
+        <v>-116.33</v>
+      </c>
+      <c r="J94" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="K94" s="38" t="s">
+        <v>115</v>
+      </c>
       <c r="L94" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>-116.33</v>
       </c>
       <c r="M94" s="38" t="str">
         <f t="shared" si="13"/>
@@ -6915,26 +7457,36 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:17">
       <c r="C95" s="35"/>
-      <c r="D95" s="46"/>
-      <c r="E95" s="37"/>
+      <c r="D95" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E95" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F95" s="37"/>
       <c r="G95" s="37"/>
       <c r="H95" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I95" s="38"/>
-      <c r="J95" s="38"/>
-      <c r="K95" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I95" s="38">
+        <v>60</v>
+      </c>
+      <c r="J95" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K95" s="38" t="s">
+        <v>158</v>
+      </c>
       <c r="L95" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M95" s="38" t="str">
+        <v>60</v>
+      </c>
+      <c r="M95" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>60</v>
       </c>
       <c r="N95" s="39">
         <v>1</v>
@@ -6949,26 +7501,36 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:17">
       <c r="C96" s="35"/>
-      <c r="D96" s="46"/>
-      <c r="E96" s="37"/>
+      <c r="D96" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="E96" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F96" s="37"/>
       <c r="G96" s="37"/>
       <c r="H96" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I96" s="38"/>
-      <c r="J96" s="38"/>
-      <c r="K96" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I96" s="38">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="J96" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K96" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="L96" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M96" s="38" t="str">
+        <v>64.989999999999995</v>
+      </c>
+      <c r="M96" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>64.989999999999995</v>
       </c>
       <c r="N96" s="39">
         <v>1</v>
@@ -6983,26 +7545,36 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:17">
       <c r="C97" s="35"/>
-      <c r="D97" s="46"/>
-      <c r="E97" s="37"/>
+      <c r="D97" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="E97" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F97" s="37"/>
       <c r="G97" s="37"/>
       <c r="H97" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I97" s="38"/>
-      <c r="J97" s="38"/>
-      <c r="K97" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I97" s="38">
+        <v>55</v>
+      </c>
+      <c r="J97" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="K97" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="L97" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M97" s="38" t="str">
+        <v>55</v>
+      </c>
+      <c r="M97" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>55</v>
       </c>
       <c r="N97" s="39">
         <v>1</v>
@@ -7017,7 +7589,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:17">
       <c r="C98" s="35"/>
       <c r="D98" s="46"/>
       <c r="E98" s="37"/>
@@ -7051,7 +7623,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:17">
       <c r="C99" s="35"/>
       <c r="D99" s="46"/>
       <c r="E99" s="37"/>
@@ -7085,25 +7657,25 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:17">
       <c r="C100" s="35"/>
       <c r="D100" s="46"/>
       <c r="E100" s="37"/>
       <c r="F100" s="37"/>
       <c r="G100" s="37"/>
       <c r="H100" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="H100:H128" si="16">COUNTA(E100:G100)</f>
         <v>0</v>
       </c>
       <c r="I100" s="38"/>
       <c r="J100" s="38"/>
       <c r="K100" s="38"/>
       <c r="L100" s="38">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="L100:L128" si="17">I100/N100</f>
         <v>0</v>
       </c>
       <c r="M100" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="M100:M128" si="18">IFERROR(L100/H100,"")</f>
         <v/>
       </c>
       <c r="N100" s="39">
@@ -7111,7 +7683,7 @@
       </c>
       <c r="O100" s="35"/>
       <c r="P100" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="P100:P128" si="19">IF(N100&lt;&gt;1,EDATE(O100,N100-1),"")</f>
         <v/>
       </c>
       <c r="Q100" s="37" t="str">
@@ -7119,25 +7691,25 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:17">
       <c r="C101" s="35"/>
       <c r="D101" s="46"/>
       <c r="E101" s="37"/>
       <c r="F101" s="37"/>
       <c r="G101" s="37"/>
       <c r="H101" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I101" s="38"/>
       <c r="J101" s="38"/>
       <c r="K101" s="38"/>
       <c r="L101" s="38">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M101" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N101" s="39">
@@ -7145,7 +7717,7 @@
       </c>
       <c r="O101" s="35"/>
       <c r="P101" s="35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q101" s="37" t="str">
@@ -7153,25 +7725,25 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:17">
       <c r="C102" s="35"/>
       <c r="D102" s="46"/>
       <c r="E102" s="37"/>
       <c r="F102" s="37"/>
       <c r="G102" s="37"/>
       <c r="H102" s="37">
-        <f t="shared" ref="H102:H133" si="16">COUNTA(E102:G102)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I102" s="38"/>
       <c r="J102" s="38"/>
       <c r="K102" s="38"/>
       <c r="L102" s="38">
-        <f t="shared" ref="L102:L130" si="17">I102/N102</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M102" s="38" t="str">
-        <f t="shared" ref="M102:M133" si="18">IFERROR(L102/H102,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N102" s="39">
@@ -7179,7 +7751,7 @@
       </c>
       <c r="O102" s="35"/>
       <c r="P102" s="35" t="str">
-        <f t="shared" ref="P102:P133" si="19">IF(N102&lt;&gt;1,EDATE(O102,N102-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q102" s="37" t="str">
@@ -7187,7 +7759,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:17">
       <c r="C103" s="35"/>
       <c r="D103" s="46"/>
       <c r="E103" s="37"/>
@@ -7221,7 +7793,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:17">
       <c r="C104" s="35"/>
       <c r="D104" s="46"/>
       <c r="E104" s="37"/>
@@ -7255,7 +7827,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:17">
       <c r="C105" s="35"/>
       <c r="D105" s="46"/>
       <c r="E105" s="37"/>
@@ -7289,7 +7861,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:17">
       <c r="C106" s="35"/>
       <c r="D106" s="46"/>
       <c r="E106" s="37"/>
@@ -7323,7 +7895,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:17">
       <c r="C107" s="35"/>
       <c r="D107" s="46"/>
       <c r="E107" s="37"/>
@@ -7357,7 +7929,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:17">
       <c r="C108" s="35"/>
       <c r="D108" s="46"/>
       <c r="E108" s="37"/>
@@ -7391,7 +7963,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:17">
       <c r="C109" s="35"/>
       <c r="D109" s="46"/>
       <c r="E109" s="37"/>
@@ -7425,7 +7997,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:17">
       <c r="C110" s="35"/>
       <c r="D110" s="46"/>
       <c r="E110" s="37"/>
@@ -7459,7 +8031,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:17">
       <c r="C111" s="35"/>
       <c r="D111" s="46"/>
       <c r="E111" s="37"/>
@@ -7493,7 +8065,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:17">
       <c r="C112" s="35"/>
       <c r="D112" s="46"/>
       <c r="E112" s="37"/>
@@ -7527,7 +8099,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:17">
       <c r="C113" s="35"/>
       <c r="D113" s="46"/>
       <c r="E113" s="37"/>
@@ -7557,11 +8129,11 @@
         <v/>
       </c>
       <c r="Q113" s="37" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="114" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q113:Q128" ca="1" si="20">IF(O113&lt;&gt;"",IFERROR(DATEDIF(O113,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="3:17">
       <c r="C114" s="35"/>
       <c r="D114" s="46"/>
       <c r="E114" s="37"/>
@@ -7591,11 +8163,11 @@
         <v/>
       </c>
       <c r="Q114" s="37" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="3:17">
       <c r="C115" s="35"/>
       <c r="D115" s="46"/>
       <c r="E115" s="37"/>
@@ -7625,11 +8197,11 @@
         <v/>
       </c>
       <c r="Q115" s="37" t="str">
-        <f t="shared" ref="Q115:Q130" ca="1" si="20">IF(O115&lt;&gt;"",IFERROR(DATEDIF(O115,TODAY(),"m")+1,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="3:17">
       <c r="C116" s="35"/>
       <c r="D116" s="46"/>
       <c r="E116" s="37"/>
@@ -7663,7 +8235,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:17">
       <c r="C117" s="35"/>
       <c r="D117" s="46"/>
       <c r="E117" s="37"/>
@@ -7697,7 +8269,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:17">
       <c r="C118" s="35"/>
       <c r="D118" s="46"/>
       <c r="E118" s="37"/>
@@ -7731,7 +8303,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:17">
       <c r="C119" s="35"/>
       <c r="D119" s="46"/>
       <c r="E119" s="37"/>
@@ -7765,7 +8337,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:17">
       <c r="C120" s="35"/>
       <c r="D120" s="46"/>
       <c r="E120" s="37"/>
@@ -7799,7 +8371,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:17">
       <c r="C121" s="35"/>
       <c r="D121" s="46"/>
       <c r="E121" s="37"/>
@@ -7833,7 +8405,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:17">
       <c r="C122" s="35"/>
       <c r="D122" s="46"/>
       <c r="E122" s="37"/>
@@ -7867,7 +8439,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:17">
       <c r="C123" s="35"/>
       <c r="D123" s="46"/>
       <c r="E123" s="37"/>
@@ -7901,7 +8473,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:17">
       <c r="C124" s="35"/>
       <c r="D124" s="46"/>
       <c r="E124" s="37"/>
@@ -7935,7 +8507,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:17">
       <c r="C125" s="35"/>
       <c r="D125" s="46"/>
       <c r="E125" s="37"/>
@@ -7969,7 +8541,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:17">
       <c r="C126" s="35"/>
       <c r="D126" s="46"/>
       <c r="E126" s="37"/>
@@ -8003,7 +8575,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:17">
       <c r="C127" s="35"/>
       <c r="D127" s="46"/>
       <c r="E127" s="37"/>
@@ -8037,7 +8609,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:17">
       <c r="C128" s="35"/>
       <c r="D128" s="46"/>
       <c r="E128" s="37"/>
@@ -8071,107 +8643,79 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C129" s="35"/>
-      <c r="D129" s="46"/>
-      <c r="E129" s="37"/>
-      <c r="F129" s="37"/>
-      <c r="G129" s="37"/>
-      <c r="H129" s="37">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I129" s="38"/>
-      <c r="J129" s="38"/>
-      <c r="K129" s="38"/>
-      <c r="L129" s="38">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M129" s="38" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="N129" s="39">
-        <v>1</v>
-      </c>
-      <c r="O129" s="35"/>
-      <c r="P129" s="35" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="Q129" s="37" t="str">
-        <f t="shared" ca="1" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C130" s="35"/>
-      <c r="D130" s="46"/>
-      <c r="E130" s="37"/>
-      <c r="F130" s="37"/>
-      <c r="G130" s="37"/>
-      <c r="H130" s="37">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I130" s="38"/>
-      <c r="J130" s="38"/>
-      <c r="K130" s="38"/>
-      <c r="L130" s="38">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M130" s="38" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="N130" s="39">
-        <v>1</v>
-      </c>
-      <c r="O130" s="35"/>
-      <c r="P130" s="35" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="Q130" s="37" t="str">
-        <f t="shared" ca="1" si="20"/>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="C5:Q51" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q130">
+  <autoFilter ref="C5:Q128" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q128">
       <sortCondition ref="P5:P51"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="I6:I130">
-    <cfRule type="cellIs" dxfId="15" priority="18" operator="lessThan">
+  <conditionalFormatting sqref="I98:I128 I6:I96">
+    <cfRule type="cellIs" dxfId="29" priority="27" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J130">
-    <cfRule type="cellIs" dxfId="14" priority="17" operator="equal">
+  <conditionalFormatting sqref="J6:J128">
+    <cfRule type="cellIs" dxfId="28" priority="26" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:K130">
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+  <conditionalFormatting sqref="J98:K128 I97:K97 J6:K96">
+    <cfRule type="cellIs" dxfId="27" priority="20" operator="equal">
       <formula>"Parcelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K50">
-    <cfRule type="cellIs" dxfId="12" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="19" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="11" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K66">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="10" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K70:K71">
+    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K75">
+    <cfRule type="cellIs" dxfId="22" priority="7" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K78">
+    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K81">
+    <cfRule type="cellIs" dxfId="20" priority="5" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K86">
+    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K91">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K94">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I97">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8183,7 +8727,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:R20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="36.5703125" customWidth="1"/>
@@ -8196,47 +8740,47 @@
     <col min="18" max="18" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="30" customHeight="1">
       <c r="D2" s="33" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H2" s="34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J2" s="34" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K2" s="34" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M2" s="33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N2" s="33" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O2" s="34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" ht="16.5" customHeight="1">
       <c r="D3" s="54" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" s="36" t="s">
         <v>1</v>
@@ -8272,9 +8816,9 @@
       </c>
       <c r="R3" s="16"/>
     </row>
-    <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:18" ht="16.5" customHeight="1">
       <c r="D4" s="55" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E4" s="56" t="s">
         <v>1</v>
@@ -8310,12 +8854,12 @@
       </c>
       <c r="R4" s="16"/>
     </row>
-    <row r="5" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" ht="16.5" customHeight="1">
       <c r="B5" s="30" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>1</v>
@@ -8329,15 +8873,15 @@
         <v>2</v>
       </c>
       <c r="I5" s="38">
-        <v>330.8</v>
+        <v>440</v>
       </c>
       <c r="J5" s="38">
         <f t="shared" si="0"/>
-        <v>330.8</v>
+        <v>440</v>
       </c>
       <c r="K5" s="38">
         <f t="shared" si="1"/>
-        <v>165.4</v>
+        <v>220</v>
       </c>
       <c r="L5" s="37">
         <f t="shared" si="2"/>
@@ -8351,13 +8895,13 @@
       </c>
       <c r="P5" s="59"/>
     </row>
-    <row r="6" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" ht="16.5" customHeight="1">
       <c r="B6" s="32">
         <f>SUMIF($E$3:$E$34,B5,$K$3:$K$34)</f>
-        <v>2515.7400000000002</v>
+        <v>2570.34</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>1</v>
@@ -8392,10 +8936,10 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" ht="16.5" customHeight="1">
       <c r="B7" s="60"/>
       <c r="D7" s="54" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="E7" s="36" t="s">
         <v>1</v>
@@ -8430,12 +8974,12 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" ht="16.5" customHeight="1">
       <c r="B8" s="30" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="54" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>1</v>
@@ -8470,13 +9014,13 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:18" ht="16.5" customHeight="1">
       <c r="B9" s="61">
         <f>SUMIF($F$3:$F$34,B8,$K$3:$K$34)</f>
-        <v>5807.74</v>
+        <v>5862.34</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="E9" s="36" t="s">
         <v>1</v>
@@ -8512,9 +9056,9 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18">
       <c r="D10" s="54" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="37" t="s">
@@ -8547,9 +9091,9 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18">
       <c r="D11" s="54" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="37" t="s">
@@ -8582,9 +9126,9 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18">
       <c r="D12" s="54" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="E12" s="36"/>
       <c r="F12" s="37" t="s">
@@ -8617,9 +9161,9 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18">
       <c r="D13" s="54" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="E13" s="36" t="s">
         <v>1</v>
@@ -8654,7 +9198,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:18">
       <c r="D14" s="37"/>
       <c r="E14" s="36"/>
       <c r="F14" s="37"/>
@@ -8668,7 +9212,7 @@
       <c r="N14" s="38"/>
       <c r="O14" s="39"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:18">
       <c r="D15" s="37"/>
       <c r="E15" s="36"/>
       <c r="F15" s="37"/>
@@ -8682,7 +9226,7 @@
       <c r="N15" s="38"/>
       <c r="O15" s="39"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18">
       <c r="D16" s="37"/>
       <c r="E16" s="36"/>
       <c r="F16" s="37"/>
@@ -8696,7 +9240,7 @@
       <c r="N16" s="38"/>
       <c r="O16" s="39"/>
     </row>
-    <row r="17" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:15">
       <c r="D17" s="37"/>
       <c r="E17" s="36"/>
       <c r="F17" s="37"/>
@@ -8710,7 +9254,7 @@
       <c r="N17" s="38"/>
       <c r="O17" s="39"/>
     </row>
-    <row r="18" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:15">
       <c r="D18" s="37"/>
       <c r="E18" s="36"/>
       <c r="F18" s="37"/>
@@ -8724,7 +9268,7 @@
       <c r="N18" s="38"/>
       <c r="O18" s="39"/>
     </row>
-    <row r="19" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:15">
       <c r="D19" s="37"/>
       <c r="E19" s="36"/>
       <c r="F19" s="37"/>
@@ -8738,7 +9282,7 @@
       <c r="N19" s="38"/>
       <c r="O19" s="39"/>
     </row>
-    <row r="20" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:15">
       <c r="D20" s="37"/>
       <c r="E20" s="36"/>
       <c r="F20" s="37"/>
@@ -8761,7 +9305,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:O404"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.140625" customWidth="1"/>
@@ -8777,23 +9321,23 @@
     <col min="15" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15">
       <c r="G1" s="2"/>
       <c r="N1" s="47" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" ht="14.25" customHeight="1">
       <c r="G2" s="2"/>
       <c r="N2" s="43"/>
     </row>
-    <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" ht="27.75" customHeight="1">
       <c r="G3" s="2"/>
       <c r="L3" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="M3" s="77" t="s">
-        <v>124</v>
+        <v>174</v>
+      </c>
+      <c r="M3" s="76" t="s">
+        <v>175</v>
       </c>
       <c r="N3" s="43">
         <f>SUM(N5:N21)</f>
@@ -8801,83 +9345,83 @@
       </c>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15">
       <c r="G4" s="2"/>
       <c r="L4" s="48" t="s">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="M4" s="78"/>
       <c r="N4" s="49"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15">
       <c r="B5" s="43"/>
       <c r="C5" s="43"/>
       <c r="F5" s="16"/>
       <c r="G5" s="28"/>
       <c r="L5" t="s">
-        <v>126</v>
+        <v>177</v>
       </c>
       <c r="N5" s="1">
         <v>100</v>
       </c>
       <c r="O5" s="16"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15">
       <c r="G6" s="2"/>
       <c r="L6" t="s">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="N6" s="1">
         <f>97+31</f>
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15">
       <c r="G7" s="2"/>
       <c r="N7" s="73"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15">
       <c r="F8" s="16"/>
       <c r="G8" s="50"/>
       <c r="N8" s="73"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15">
       <c r="F9" s="47" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="G9" s="28"/>
       <c r="N9" s="72"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15">
       <c r="E10" t="s">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="F10" s="16">
         <f>SUM(G11:I11)</f>
-        <v>4520.0000000000036</v>
+        <v>4000.0000000000036</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="H10" s="51" t="s">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="I10" s="51" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
       <c r="N10" s="72"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15">
       <c r="E11" t="s">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="F11" s="16">
         <f>SUM(G11:H11)</f>
-        <v>4520.0000000000036</v>
+        <v>4000.0000000000036</v>
       </c>
       <c r="G11" s="1">
         <f>G12+SUM(G14:G496)</f>
-        <v>4520.0000000000036</v>
+        <v>4000.0000000000036</v>
       </c>
       <c r="H11" s="1">
         <f>H12+SUM(H14:H496)</f>
@@ -8889,36 +9433,36 @@
       </c>
       <c r="N11" s="72"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15">
       <c r="F12" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="G12" s="1">
         <v>15250</v>
       </c>
       <c r="N12" s="72"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15">
       <c r="F13" s="74" t="s">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="G13" s="52"/>
       <c r="H13" s="74"/>
       <c r="I13" s="74"/>
       <c r="N13" s="72"/>
     </row>
-    <row r="14" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" outlineLevel="1">
       <c r="F14" t="s">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="G14" s="53"/>
       <c r="H14" s="53"/>
       <c r="I14" s="53"/>
       <c r="N14" s="43"/>
     </row>
-    <row r="15" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" outlineLevel="1">
       <c r="F15" t="s">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="G15" s="53">
         <v>773.35</v>
@@ -8927,9 +9471,9 @@
       <c r="I15" s="53"/>
       <c r="N15" s="43"/>
     </row>
-    <row r="16" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" outlineLevel="1">
       <c r="F16" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="G16" s="53">
         <v>-5148</v>
@@ -8938,9 +9482,9 @@
       <c r="I16" s="53"/>
       <c r="N16" s="43"/>
     </row>
-    <row r="17" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:14" outlineLevel="1">
       <c r="F17" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="G17" s="53">
         <v>-168</v>
@@ -8949,9 +9493,9 @@
       <c r="I17" s="53"/>
       <c r="N17" s="43"/>
     </row>
-    <row r="18" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="6:14" outlineLevel="1">
       <c r="F18" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="G18" s="53">
         <v>-1700</v>
@@ -8960,9 +9504,9 @@
       <c r="I18" s="53"/>
       <c r="N18" s="43"/>
     </row>
-    <row r="19" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:14" outlineLevel="1">
       <c r="F19" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="G19" s="53">
         <v>5148</v>
@@ -8971,9 +9515,9 @@
       <c r="I19" s="53"/>
       <c r="N19" s="43"/>
     </row>
-    <row r="20" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:14" outlineLevel="1">
       <c r="F20" t="s">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="G20" s="53">
         <v>-4938</v>
@@ -8982,9 +9526,9 @@
       <c r="I20" s="53"/>
       <c r="N20" s="43"/>
     </row>
-    <row r="21" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:14" outlineLevel="1">
       <c r="F21" t="s">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="G21" s="53">
         <v>-1595</v>
@@ -8993,9 +9537,9 @@
       <c r="I21" s="53"/>
       <c r="N21" s="43"/>
     </row>
-    <row r="22" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:14" outlineLevel="1">
       <c r="F22" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="G22" s="53">
         <v>-4677</v>
@@ -9004,9 +9548,9 @@
       <c r="I22" s="53"/>
       <c r="N22" s="43"/>
     </row>
-    <row r="23" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:14" outlineLevel="1">
       <c r="F23" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="G23" s="53">
         <v>-200</v>
@@ -9015,9 +9559,9 @@
       <c r="I23" s="53"/>
       <c r="N23" s="43"/>
     </row>
-    <row r="24" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="6:14" outlineLevel="1">
       <c r="F24" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="G24" s="53">
         <v>4677</v>
@@ -9026,9 +9570,9 @@
       <c r="I24" s="53"/>
       <c r="N24" s="43"/>
     </row>
-    <row r="25" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:14" outlineLevel="1">
       <c r="F25" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="G25" s="53">
         <v>-750</v>
@@ -9037,9 +9581,9 @@
       <c r="I25" s="53"/>
       <c r="N25" s="43"/>
     </row>
-    <row r="26" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:14" outlineLevel="1">
       <c r="F26" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="G26" s="53">
         <v>-652</v>
@@ -9048,9 +9592,9 @@
       <c r="I26" s="53"/>
       <c r="N26" s="43"/>
     </row>
-    <row r="27" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:14" outlineLevel="1">
       <c r="F27" t="s">
-        <v>146</v>
+        <v>197</v>
       </c>
       <c r="G27" s="53">
         <v>11100</v>
@@ -9059,9 +9603,9 @@
       <c r="I27" s="53"/>
       <c r="N27" s="43"/>
     </row>
-    <row r="28" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:14" outlineLevel="1">
       <c r="F28" t="s">
-        <v>147</v>
+        <v>198</v>
       </c>
       <c r="G28" s="53">
         <v>-396</v>
@@ -9070,9 +9614,9 @@
       <c r="I28" s="53"/>
       <c r="N28" s="43"/>
     </row>
-    <row r="29" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="6:14" outlineLevel="1">
       <c r="F29" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="G29" s="53">
         <v>-4211</v>
@@ -9081,9 +9625,9 @@
       <c r="I29" s="53"/>
       <c r="N29" s="43"/>
     </row>
-    <row r="30" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="6:14" outlineLevel="1">
       <c r="F30" t="s">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="G30" s="53">
         <v>-450</v>
@@ -9092,9 +9636,9 @@
       <c r="I30" s="53"/>
       <c r="N30" s="43"/>
     </row>
-    <row r="31" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:14" outlineLevel="1">
       <c r="F31" t="s">
-        <v>149</v>
+        <v>200</v>
       </c>
       <c r="G31" s="53">
         <v>-1197</v>
@@ -9103,9 +9647,9 @@
       <c r="I31" s="53"/>
       <c r="N31" s="43"/>
     </row>
-    <row r="32" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="6:14" outlineLevel="1">
       <c r="F32" t="s">
-        <v>150</v>
+        <v>201</v>
       </c>
       <c r="G32" s="53">
         <v>-315</v>
@@ -9114,9 +9658,9 @@
       <c r="I32" s="53"/>
       <c r="N32" s="43"/>
     </row>
-    <row r="33" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:14" outlineLevel="1">
       <c r="F33" t="s">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="G33" s="53">
         <v>-830</v>
@@ -9125,9 +9669,9 @@
       <c r="I33" s="53"/>
       <c r="N33" s="43"/>
     </row>
-    <row r="34" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:14" outlineLevel="1">
       <c r="F34" t="s">
-        <v>152</v>
+        <v>203</v>
       </c>
       <c r="G34" s="53">
         <v>4211</v>
@@ -9136,9 +9680,9 @@
       <c r="I34" s="53"/>
       <c r="N34" s="43"/>
     </row>
-    <row r="35" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:14" outlineLevel="1">
       <c r="F35" t="s">
-        <v>153</v>
+        <v>204</v>
       </c>
       <c r="G35" s="53">
         <v>-200</v>
@@ -9147,9 +9691,9 @@
       <c r="I35" s="53"/>
       <c r="N35" s="43"/>
     </row>
-    <row r="36" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:14" outlineLevel="1">
       <c r="F36" t="s">
-        <v>154</v>
+        <v>205</v>
       </c>
       <c r="G36" s="53">
         <v>10000</v>
@@ -9158,9 +9702,9 @@
       <c r="I36" s="53"/>
       <c r="N36" s="43"/>
     </row>
-    <row r="37" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:14" outlineLevel="1">
       <c r="F37" t="s">
-        <v>155</v>
+        <v>206</v>
       </c>
       <c r="G37" s="53">
         <v>-200</v>
@@ -9169,9 +9713,9 @@
       <c r="I37" s="53"/>
       <c r="N37" s="43"/>
     </row>
-    <row r="38" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:14" outlineLevel="1">
       <c r="F38" t="s">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="G38" s="53">
         <v>-381</v>
@@ -9180,9 +9724,9 @@
       <c r="I38" s="53"/>
       <c r="N38" s="43"/>
     </row>
-    <row r="39" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:14" outlineLevel="1">
       <c r="F39" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="G39" s="53">
         <v>-4911</v>
@@ -9191,10 +9735,10 @@
       <c r="I39" s="53"/>
       <c r="N39" s="43"/>
     </row>
-    <row r="40" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:14" outlineLevel="1">
       <c r="E40" s="2"/>
       <c r="F40" t="s">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="G40" s="53">
         <v>-5700</v>
@@ -9203,9 +9747,9 @@
       <c r="I40" s="53"/>
       <c r="N40" s="43"/>
     </row>
-    <row r="41" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:14" outlineLevel="1">
       <c r="F41" t="s">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="G41" s="53">
         <v>-400</v>
@@ -9214,9 +9758,9 @@
       <c r="I41" s="53"/>
       <c r="N41" s="43"/>
     </row>
-    <row r="42" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:14" outlineLevel="1">
       <c r="F42" t="s">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="G42" s="53">
         <v>-450</v>
@@ -9225,9 +9769,9 @@
       <c r="I42" s="53"/>
       <c r="N42" s="43"/>
     </row>
-    <row r="43" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:14" outlineLevel="1">
       <c r="F43" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="G43" s="53">
         <v>-640</v>
@@ -9236,10 +9780,10 @@
       <c r="I43" s="53"/>
       <c r="N43" s="43"/>
     </row>
-    <row r="44" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:14" outlineLevel="1">
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>161</v>
+        <v>212</v>
       </c>
       <c r="G44" s="53">
         <v>5700</v>
@@ -9248,9 +9792,9 @@
       <c r="I44" s="53"/>
       <c r="N44" s="43"/>
     </row>
-    <row r="45" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="5:14" outlineLevel="1">
       <c r="F45" t="s">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="G45" s="53">
         <v>-130</v>
@@ -9259,9 +9803,9 @@
       <c r="I45" s="53"/>
       <c r="N45" s="43"/>
     </row>
-    <row r="46" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:14" outlineLevel="1">
       <c r="F46" t="s">
-        <v>163</v>
+        <v>214</v>
       </c>
       <c r="G46" s="53">
         <v>-250</v>
@@ -9270,9 +9814,9 @@
       <c r="I46" s="53"/>
       <c r="N46" s="43"/>
     </row>
-    <row r="47" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:14" outlineLevel="1">
       <c r="F47" t="s">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="G47" s="53">
         <v>-112.2</v>
@@ -9281,9 +9825,9 @@
       <c r="I47" s="53"/>
       <c r="N47" s="43"/>
     </row>
-    <row r="48" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:14" outlineLevel="1">
       <c r="F48" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="G48" s="53">
         <v>4911</v>
@@ -9292,9 +9836,9 @@
       <c r="I48" s="53"/>
       <c r="N48" s="43"/>
     </row>
-    <row r="49" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="6:14" outlineLevel="1">
       <c r="F49" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="G49" s="53">
         <v>-3000</v>
@@ -9303,9 +9847,9 @@
       <c r="I49" s="53"/>
       <c r="N49" s="43"/>
     </row>
-    <row r="50" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="6:14" outlineLevel="1">
       <c r="F50" t="s">
-        <v>166</v>
+        <v>217</v>
       </c>
       <c r="G50" s="53">
         <v>-4000</v>
@@ -9314,9 +9858,9 @@
       <c r="I50" s="53"/>
       <c r="N50" s="43"/>
     </row>
-    <row r="51" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="6:14" outlineLevel="1">
       <c r="F51" t="s">
-        <v>167</v>
+        <v>218</v>
       </c>
       <c r="G51" s="53">
         <v>-200</v>
@@ -9325,9 +9869,9 @@
       <c r="I51" s="53"/>
       <c r="N51" s="43"/>
     </row>
-    <row r="52" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="6:14" outlineLevel="1">
       <c r="F52" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="G52" s="53">
         <v>-4612</v>
@@ -9336,9 +9880,9 @@
       <c r="I52" s="53"/>
       <c r="N52" s="43"/>
     </row>
-    <row r="53" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="6:14" outlineLevel="1">
       <c r="F53" t="s">
-        <v>168</v>
+        <v>219</v>
       </c>
       <c r="G53" s="53">
         <v>-700</v>
@@ -9347,9 +9891,9 @@
       <c r="I53" s="53"/>
       <c r="N53" s="43"/>
     </row>
-    <row r="54" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="6:14" outlineLevel="1">
       <c r="F54" t="s">
-        <v>169</v>
+        <v>220</v>
       </c>
       <c r="G54" s="53">
         <v>-880</v>
@@ -9358,9 +9902,9 @@
       <c r="I54" s="53"/>
       <c r="N54" s="43"/>
     </row>
-    <row r="55" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="6:14" outlineLevel="1">
       <c r="F55" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="G55" s="53">
         <v>-310</v>
@@ -9369,9 +9913,9 @@
       <c r="I55" s="53"/>
       <c r="N55" s="43"/>
     </row>
-    <row r="56" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="6:14">
       <c r="F56" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="G56" s="53">
         <v>-250</v>
@@ -9380,9 +9924,9 @@
       <c r="I56" s="53"/>
       <c r="N56" s="43"/>
     </row>
-    <row r="57" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="6:14">
       <c r="F57" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="G57" s="53">
         <v>4690</v>
@@ -9391,9 +9935,9 @@
       <c r="I57" s="53"/>
       <c r="N57" s="43"/>
     </row>
-    <row r="58" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="6:14">
       <c r="F58" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="G58" s="53">
         <v>-4440</v>
@@ -9402,9 +9946,9 @@
       <c r="I58" s="53"/>
       <c r="N58" s="43"/>
     </row>
-    <row r="59" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="6:14">
       <c r="F59" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="G59" s="53">
         <v>-4697</v>
@@ -9412,9 +9956,9 @@
       <c r="H59" s="53"/>
       <c r="I59" s="53"/>
     </row>
-    <row r="60" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="6:14">
       <c r="F60" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="G60" s="53">
         <v>-2500</v>
@@ -9422,9 +9966,9 @@
       <c r="H60" s="53"/>
       <c r="I60" s="53"/>
     </row>
-    <row r="61" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="6:14">
       <c r="F61" t="s">
-        <v>174</v>
+        <v>225</v>
       </c>
       <c r="G61" s="53">
         <v>-126</v>
@@ -9432,9 +9976,9 @@
       <c r="H61" s="53"/>
       <c r="I61" s="53"/>
     </row>
-    <row r="62" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="6:14">
       <c r="F62" t="s">
-        <v>175</v>
+        <v>226</v>
       </c>
       <c r="G62" s="53">
         <v>4742</v>
@@ -9442,9 +9986,9 @@
       <c r="H62" s="53"/>
       <c r="I62" s="53"/>
     </row>
-    <row r="63" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="6:14">
       <c r="F63" t="s">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="G63" s="53">
         <v>-410</v>
@@ -9452,14 +9996,14 @@
       <c r="H63" s="53"/>
       <c r="I63" s="53"/>
     </row>
-    <row r="64" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="6:14">
       <c r="G64" s="53"/>
       <c r="H64" s="53"/>
       <c r="I64" s="53"/>
     </row>
-    <row r="65" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:9">
       <c r="F65" t="s">
-        <v>176</v>
+        <v>227</v>
       </c>
       <c r="G65" s="53">
         <v>3320</v>
@@ -9467,9 +10011,9 @@
       <c r="H65" s="53"/>
       <c r="I65" s="53"/>
     </row>
-    <row r="66" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:9">
       <c r="F66" t="s">
-        <v>177</v>
+        <v>228</v>
       </c>
       <c r="G66" s="53">
         <v>4090</v>
@@ -9477,9 +10021,9 @@
       <c r="H66" s="53"/>
       <c r="I66" s="53"/>
     </row>
-    <row r="67" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:9">
       <c r="F67" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="G67" s="53">
         <v>-5688</v>
@@ -9487,9 +10031,9 @@
       <c r="H67" s="53"/>
       <c r="I67" s="53"/>
     </row>
-    <row r="68" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:9">
       <c r="F68" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="G68" s="53">
         <v>-4433</v>
@@ -9497,9 +10041,9 @@
       <c r="H68" s="53"/>
       <c r="I68" s="53"/>
     </row>
-    <row r="69" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:9">
       <c r="F69" t="s">
-        <v>179</v>
+        <v>230</v>
       </c>
       <c r="G69" s="53">
         <v>-250</v>
@@ -9507,9 +10051,9 @@
       <c r="H69" s="53"/>
       <c r="I69" s="53"/>
     </row>
-    <row r="70" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:9">
       <c r="F70" t="s">
-        <v>180</v>
+        <v>231</v>
       </c>
       <c r="G70" s="53">
         <v>-99</v>
@@ -9517,9 +10061,9 @@
       <c r="H70" s="53"/>
       <c r="I70" s="53"/>
     </row>
-    <row r="71" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:9">
       <c r="F71" t="s">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="G71" s="53">
         <v>320</v>
@@ -9527,9 +10071,9 @@
       <c r="H71" s="53"/>
       <c r="I71" s="53"/>
     </row>
-    <row r="72" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:9">
       <c r="F72" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="G72" s="53">
         <v>-1572</v>
@@ -9537,14 +10081,14 @@
       <c r="H72" s="53"/>
       <c r="I72" s="53"/>
     </row>
-    <row r="73" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:9">
       <c r="G73" s="53"/>
       <c r="H73" s="53"/>
       <c r="I73" s="53"/>
     </row>
-    <row r="74" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:9">
       <c r="F74" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="G74" s="53">
         <v>4433</v>
@@ -9552,9 +10096,9 @@
       <c r="H74" s="53"/>
       <c r="I74" s="53"/>
     </row>
-    <row r="75" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:9">
       <c r="F75" t="s">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="G75" s="53">
         <v>8000</v>
@@ -9562,9 +10106,9 @@
       <c r="H75" s="53"/>
       <c r="I75" s="53"/>
     </row>
-    <row r="76" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:9">
       <c r="F76" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="G76" s="53">
         <v>-1344</v>
@@ -9572,9 +10116,9 @@
       <c r="H76" s="53"/>
       <c r="I76" s="53"/>
     </row>
-    <row r="77" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="6:9">
       <c r="F77" t="s">
-        <v>185</v>
+        <v>236</v>
       </c>
       <c r="G77" s="53">
         <v>-308</v>
@@ -9582,9 +10126,9 @@
       <c r="H77" s="53"/>
       <c r="I77" s="53"/>
     </row>
-    <row r="78" spans="6:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="6:9" ht="14.25" customHeight="1">
       <c r="F78" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="G78" s="53">
         <v>-4204</v>
@@ -9592,9 +10136,9 @@
       <c r="H78" s="53"/>
       <c r="I78" s="53"/>
     </row>
-    <row r="79" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="6:9">
       <c r="F79" t="s">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="G79" s="53">
         <v>-338</v>
@@ -9602,9 +10146,9 @@
       <c r="H79" s="53"/>
       <c r="I79" s="53"/>
     </row>
-    <row r="80" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="6:9">
       <c r="F80" t="s">
-        <v>187</v>
+        <v>238</v>
       </c>
       <c r="G80" s="53">
         <v>-50</v>
@@ -9612,9 +10156,9 @@
       <c r="H80" s="53"/>
       <c r="I80" s="53"/>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9">
       <c r="F81" t="s">
-        <v>188</v>
+        <v>239</v>
       </c>
       <c r="G81" s="53">
         <v>338</v>
@@ -9622,9 +10166,9 @@
       <c r="H81" s="53"/>
       <c r="I81" s="53"/>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9">
       <c r="F82" t="s">
-        <v>189</v>
+        <v>240</v>
       </c>
       <c r="G82" s="53">
         <v>-540</v>
@@ -9632,9 +10176,9 @@
       <c r="H82" s="53"/>
       <c r="I82" s="53"/>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9">
       <c r="F83" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="G83" s="53">
         <v>-184.31</v>
@@ -9642,11 +10186,11 @@
       <c r="H83" s="53"/>
       <c r="I83" s="53"/>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9">
       <c r="C84" s="53"/>
       <c r="D84" s="53"/>
       <c r="F84" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="G84" s="53">
         <v>-1464.22</v>
@@ -9654,11 +10198,11 @@
       <c r="H84" s="53"/>
       <c r="I84" s="53"/>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9">
       <c r="C85" s="53"/>
       <c r="D85" s="53"/>
       <c r="F85" t="s">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="G85" s="53">
         <v>1005</v>
@@ -9666,11 +10210,11 @@
       <c r="H85" s="53"/>
       <c r="I85" s="53"/>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9">
       <c r="C86" s="53"/>
       <c r="D86" s="53"/>
       <c r="F86" t="s">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="G86" s="53">
         <v>-500</v>
@@ -9678,11 +10222,11 @@
       <c r="H86" s="53"/>
       <c r="I86" s="53"/>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9">
       <c r="C87" s="53"/>
       <c r="D87" s="53"/>
       <c r="F87" t="s">
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="G87" s="53">
         <v>-225</v>
@@ -9690,11 +10234,11 @@
       <c r="H87" s="53"/>
       <c r="I87" s="53"/>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9">
       <c r="C88" s="53"/>
       <c r="D88" s="53"/>
       <c r="F88" t="s">
-        <v>193</v>
+        <v>244</v>
       </c>
       <c r="G88" s="53">
         <v>-516</v>
@@ -9702,11 +10246,11 @@
       <c r="H88" s="53"/>
       <c r="I88" s="53"/>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9">
       <c r="C89" s="53"/>
       <c r="D89" s="53"/>
       <c r="F89" t="s">
-        <v>194</v>
+        <v>245</v>
       </c>
       <c r="G89" s="53">
         <v>4204</v>
@@ -9714,16 +10258,16 @@
       <c r="H89" s="53"/>
       <c r="I89" s="53"/>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9">
       <c r="B90" t="s">
-        <v>195</v>
+        <v>246</v>
       </c>
       <c r="C90" s="53">
         <v>5556.2</v>
       </c>
       <c r="D90" s="53"/>
       <c r="F90" t="s">
-        <v>196</v>
+        <v>247</v>
       </c>
       <c r="G90" s="53">
         <v>-100</v>
@@ -9731,11 +10275,11 @@
       <c r="H90" s="53"/>
       <c r="I90" s="53"/>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9">
       <c r="C91" s="53"/>
       <c r="D91" s="53"/>
       <c r="F91" t="s">
-        <v>197</v>
+        <v>248</v>
       </c>
       <c r="G91" s="53">
         <v>8000</v>
@@ -9743,9 +10287,9 @@
       <c r="H91" s="53"/>
       <c r="I91" s="53"/>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9">
       <c r="B92" t="s">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="C92" s="53">
         <v>1000</v>
@@ -9754,7 +10298,7 @@
         <v>300</v>
       </c>
       <c r="F92" t="s">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="G92" s="53">
         <v>1000</v>
@@ -9762,11 +10306,11 @@
       <c r="H92" s="53"/>
       <c r="I92" s="53"/>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9">
       <c r="C93" s="53"/>
       <c r="D93" s="53"/>
       <c r="F93" t="s">
-        <v>200</v>
+        <v>251</v>
       </c>
       <c r="G93" s="53">
         <v>-12881</v>
@@ -9774,16 +10318,16 @@
       <c r="H93" s="53"/>
       <c r="I93" s="53"/>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9">
       <c r="B94" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="C94" s="53">
         <v>160</v>
       </c>
       <c r="D94" s="53"/>
       <c r="F94" t="s">
-        <v>202</v>
+        <v>253</v>
       </c>
       <c r="G94" s="53">
         <v>-4489.62</v>
@@ -9791,11 +10335,11 @@
       <c r="H94" s="53"/>
       <c r="I94" s="53"/>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9">
       <c r="C95" s="53"/>
       <c r="D95" s="53"/>
       <c r="F95" t="s">
-        <v>203</v>
+        <v>254</v>
       </c>
       <c r="G95" s="53">
         <v>5000</v>
@@ -9803,9 +10347,9 @@
       <c r="H95" s="53"/>
       <c r="I95" s="53"/>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9">
       <c r="B96" t="s">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="C96" s="53">
         <v>2000</v>
@@ -9814,7 +10358,7 @@
         <v>300</v>
       </c>
       <c r="F96" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="G96" s="53">
         <v>-480</v>
@@ -9822,30 +10366,35 @@
       <c r="H96" s="53"/>
       <c r="I96" s="53"/>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9">
       <c r="C97" s="53"/>
       <c r="D97" s="53"/>
-      <c r="G97" s="53"/>
+      <c r="F97" t="s">
+        <v>257</v>
+      </c>
+      <c r="G97" s="53">
+        <v>-520</v>
+      </c>
       <c r="H97" s="53"/>
       <c r="I97" s="53"/>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9">
       <c r="C98" s="53"/>
       <c r="D98" s="53"/>
       <c r="G98" s="53"/>
       <c r="H98" s="53"/>
       <c r="I98" s="53"/>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9">
       <c r="C99" s="53"/>
       <c r="D99" s="53"/>
       <c r="G99" s="53"/>
       <c r="H99" s="53"/>
       <c r="I99" s="53"/>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9">
       <c r="B100" t="s">
-        <v>205</v>
+        <v>258</v>
       </c>
       <c r="C100" s="53">
         <v>2000</v>
@@ -9857,9 +10406,9 @@
       <c r="H100" s="53"/>
       <c r="I100" s="53"/>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9">
       <c r="B101" t="s">
-        <v>206</v>
+        <v>259</v>
       </c>
       <c r="C101" s="53">
         <v>8000</v>
@@ -9869,26 +10418,28 @@
       <c r="H101" s="53"/>
       <c r="I101" s="53"/>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9">
       <c r="B102" t="s">
-        <v>207</v>
-      </c>
-      <c r="C102" s="53"/>
+        <v>260</v>
+      </c>
+      <c r="C102" s="53">
+        <v>4180</v>
+      </c>
       <c r="D102" s="53"/>
       <c r="G102" s="53"/>
       <c r="H102" s="53"/>
       <c r="I102" s="53"/>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9">
       <c r="C103" s="53"/>
       <c r="D103" s="53"/>
       <c r="G103" s="53"/>
       <c r="H103" s="53"/>
       <c r="I103" s="53"/>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9">
       <c r="B104" t="s">
-        <v>208</v>
+        <v>261</v>
       </c>
       <c r="C104" s="53">
         <v>2000</v>
@@ -9900,9 +10451,9 @@
       <c r="H104" s="53"/>
       <c r="I104" s="53"/>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9">
       <c r="B105" t="s">
-        <v>209</v>
+        <v>262</v>
       </c>
       <c r="C105" s="53">
         <v>2000</v>
@@ -9914,9 +10465,9 @@
       <c r="H105" s="53"/>
       <c r="I105" s="53"/>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9">
       <c r="B106" t="s">
-        <v>210</v>
+        <v>263</v>
       </c>
       <c r="C106" s="53">
         <v>2000</v>
@@ -9928,16 +10479,16 @@
       <c r="H106" s="53"/>
       <c r="I106" s="53"/>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9">
       <c r="C107" s="53"/>
       <c r="D107" s="53"/>
       <c r="G107" s="53"/>
       <c r="H107" s="53"/>
       <c r="I107" s="53"/>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9">
       <c r="B108" t="s">
-        <v>211</v>
+        <v>264</v>
       </c>
       <c r="C108" s="53">
         <v>-20000</v>
@@ -9947,16 +10498,16 @@
       <c r="H108" s="53"/>
       <c r="I108" s="53"/>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9">
       <c r="C109" s="53"/>
       <c r="D109" s="53"/>
       <c r="G109" s="53"/>
       <c r="H109" s="53"/>
       <c r="I109" s="53"/>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9">
       <c r="B110" t="s">
-        <v>212</v>
+        <v>265</v>
       </c>
       <c r="C110" s="53">
         <v>2000</v>
@@ -9968,9 +10519,9 @@
       <c r="H110" s="53"/>
       <c r="I110" s="53"/>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9">
       <c r="B111" t="s">
-        <v>213</v>
+        <v>266</v>
       </c>
       <c r="C111" s="53">
         <v>2000</v>
@@ -9982,9 +10533,9 @@
       <c r="H111" s="53"/>
       <c r="I111" s="53"/>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9">
       <c r="B112" t="s">
-        <v>214</v>
+        <v>267</v>
       </c>
       <c r="C112" s="53">
         <v>8000</v>
@@ -9994,9 +10545,9 @@
       <c r="H112" s="53"/>
       <c r="I112" s="53"/>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9">
       <c r="B113" t="s">
-        <v>215</v>
+        <v>268</v>
       </c>
       <c r="C113" s="53">
         <v>2000</v>
@@ -10008,9 +10559,9 @@
       <c r="H113" s="53"/>
       <c r="I113" s="53"/>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9">
       <c r="B114" t="s">
-        <v>216</v>
+        <v>269</v>
       </c>
       <c r="C114" s="53">
         <v>2000</v>
@@ -10022,1178 +10573,1185 @@
       <c r="H114" s="53"/>
       <c r="I114" s="53"/>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9">
       <c r="C115" s="53"/>
       <c r="G115" s="53"/>
       <c r="H115" s="53"/>
       <c r="I115" s="53"/>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9">
       <c r="C116" s="53"/>
       <c r="G116" s="53"/>
       <c r="H116" s="53"/>
       <c r="I116" s="53"/>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9">
       <c r="C117" s="53"/>
       <c r="G117" s="53"/>
       <c r="H117" s="53"/>
       <c r="I117" s="53"/>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9">
       <c r="C118" s="53"/>
       <c r="G118" s="53"/>
       <c r="H118" s="53"/>
       <c r="I118" s="53"/>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9">
       <c r="C119" s="53"/>
       <c r="G119" s="53"/>
       <c r="H119" s="53"/>
       <c r="I119" s="53"/>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9">
       <c r="C120" s="53"/>
       <c r="G120" s="53"/>
       <c r="H120" s="53"/>
       <c r="I120" s="53"/>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9">
       <c r="C121" s="53"/>
       <c r="G121" s="53"/>
       <c r="H121" s="53"/>
       <c r="I121" s="53"/>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9">
       <c r="G122" s="53"/>
+      <c r="H122" s="53"/>
       <c r="I122" s="53"/>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9">
       <c r="G123" s="53"/>
+      <c r="H123" s="53"/>
       <c r="I123" s="53"/>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9">
       <c r="G124" s="53"/>
+      <c r="H124" s="53"/>
       <c r="I124" s="53"/>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9">
       <c r="G125" s="53"/>
+      <c r="H125" s="53"/>
       <c r="I125" s="53"/>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9">
       <c r="G126" s="53"/>
+      <c r="H126" s="53"/>
       <c r="I126" s="53"/>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9">
       <c r="G127" s="53"/>
+      <c r="H127" s="53"/>
       <c r="I127" s="53"/>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9">
       <c r="G128" s="53"/>
+      <c r="H128" s="53"/>
       <c r="I128" s="53"/>
     </row>
-    <row r="129" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:9">
       <c r="G129" s="53"/>
       <c r="H129" s="53"/>
       <c r="I129" s="53"/>
     </row>
-    <row r="130" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:9">
       <c r="G130" s="53"/>
       <c r="H130" s="53"/>
       <c r="I130" s="53"/>
     </row>
-    <row r="131" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:9">
       <c r="G131" s="53"/>
       <c r="H131" s="53"/>
       <c r="I131" s="53"/>
     </row>
-    <row r="132" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:9">
       <c r="G132" s="53"/>
       <c r="H132" s="53"/>
       <c r="I132" s="53"/>
     </row>
-    <row r="133" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:9">
       <c r="G133" s="53"/>
       <c r="H133" s="53"/>
       <c r="I133" s="53"/>
     </row>
-    <row r="134" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:9">
       <c r="G134" s="53"/>
       <c r="H134" s="53"/>
       <c r="I134" s="53"/>
     </row>
-    <row r="135" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:9">
       <c r="G135" s="53"/>
       <c r="H135" s="53"/>
       <c r="I135" s="53"/>
     </row>
-    <row r="136" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:9">
       <c r="G136" s="53"/>
       <c r="H136" s="53"/>
       <c r="I136" s="53"/>
     </row>
-    <row r="137" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:9">
       <c r="G137" s="53"/>
       <c r="H137" s="53"/>
       <c r="I137" s="53"/>
     </row>
-    <row r="138" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:9">
       <c r="G138" s="53"/>
       <c r="H138" s="53"/>
       <c r="I138" s="53"/>
     </row>
-    <row r="139" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:9">
       <c r="G139" s="53"/>
       <c r="H139" s="53"/>
       <c r="I139" s="53"/>
     </row>
-    <row r="140" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:9">
       <c r="G140" s="53"/>
       <c r="H140" s="53"/>
       <c r="I140" s="53"/>
     </row>
-    <row r="141" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:9">
       <c r="G141" s="53"/>
       <c r="H141" s="53"/>
       <c r="I141" s="53"/>
     </row>
-    <row r="142" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:9">
       <c r="G142" s="53"/>
       <c r="H142" s="53"/>
       <c r="I142" s="53"/>
     </row>
-    <row r="143" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:9">
       <c r="G143" s="53"/>
       <c r="H143" s="53"/>
       <c r="I143" s="53"/>
     </row>
-    <row r="144" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:9">
       <c r="G144" s="53"/>
       <c r="H144" s="53"/>
       <c r="I144" s="53"/>
     </row>
-    <row r="145" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:9">
       <c r="G145" s="53"/>
       <c r="H145" s="53"/>
       <c r="I145" s="53"/>
     </row>
-    <row r="146" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:9">
       <c r="G146" s="53"/>
       <c r="H146" s="53"/>
       <c r="I146" s="53"/>
     </row>
-    <row r="147" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:9">
       <c r="G147" s="53"/>
       <c r="H147" s="53"/>
       <c r="I147" s="53"/>
     </row>
-    <row r="148" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:9">
       <c r="G148" s="53"/>
       <c r="H148" s="53"/>
       <c r="I148" s="53"/>
     </row>
-    <row r="149" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:9">
       <c r="G149" s="53"/>
       <c r="H149" s="53"/>
       <c r="I149" s="53"/>
     </row>
-    <row r="150" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:9">
       <c r="G150" s="53"/>
       <c r="H150" s="53"/>
       <c r="I150" s="53"/>
     </row>
-    <row r="151" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:9">
       <c r="G151" s="53"/>
       <c r="H151" s="53"/>
       <c r="I151" s="53"/>
     </row>
-    <row r="152" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:9">
       <c r="G152" s="53"/>
       <c r="H152" s="53"/>
       <c r="I152" s="53"/>
     </row>
-    <row r="153" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:9">
       <c r="G153" s="53"/>
       <c r="H153" s="53"/>
       <c r="I153" s="53"/>
     </row>
-    <row r="154" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:9">
       <c r="G154" s="53"/>
       <c r="H154" s="53"/>
       <c r="I154" s="53"/>
     </row>
-    <row r="155" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:9">
       <c r="G155" s="53"/>
       <c r="H155" s="53"/>
       <c r="I155" s="53"/>
     </row>
-    <row r="156" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:9">
       <c r="G156" s="53"/>
       <c r="H156" s="53"/>
       <c r="I156" s="53"/>
     </row>
-    <row r="157" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:9">
       <c r="G157" s="53"/>
       <c r="H157" s="53"/>
       <c r="I157" s="53"/>
     </row>
-    <row r="158" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:9">
       <c r="G158" s="53"/>
       <c r="H158" s="53"/>
       <c r="I158" s="53"/>
     </row>
-    <row r="159" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:9">
       <c r="G159" s="53"/>
       <c r="H159" s="53"/>
       <c r="I159" s="53"/>
     </row>
-    <row r="160" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:9">
       <c r="G160" s="53"/>
       <c r="H160" s="53"/>
       <c r="I160" s="53"/>
     </row>
-    <row r="161" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:9">
       <c r="G161" s="53"/>
       <c r="H161" s="53"/>
       <c r="I161" s="53"/>
     </row>
-    <row r="162" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:9">
       <c r="G162" s="53"/>
       <c r="H162" s="53"/>
       <c r="I162" s="53"/>
     </row>
-    <row r="163" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:9">
       <c r="G163" s="53"/>
       <c r="H163" s="53"/>
       <c r="I163" s="53"/>
     </row>
-    <row r="164" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:9">
       <c r="G164" s="53"/>
       <c r="H164" s="53"/>
       <c r="I164" s="53"/>
     </row>
-    <row r="165" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:9">
       <c r="G165" s="53"/>
       <c r="H165" s="53"/>
       <c r="I165" s="53"/>
     </row>
-    <row r="166" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:9">
       <c r="G166" s="53"/>
       <c r="H166" s="53"/>
       <c r="I166" s="53"/>
     </row>
-    <row r="167" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:9">
       <c r="G167" s="53"/>
       <c r="H167" s="53"/>
       <c r="I167" s="53"/>
     </row>
-    <row r="168" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:9">
       <c r="G168" s="53"/>
       <c r="H168" s="53"/>
       <c r="I168" s="53"/>
     </row>
-    <row r="169" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:9">
       <c r="G169" s="53"/>
       <c r="H169" s="53"/>
       <c r="I169" s="53"/>
     </row>
-    <row r="170" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:9">
       <c r="G170" s="53"/>
       <c r="H170" s="53"/>
       <c r="I170" s="53"/>
     </row>
-    <row r="171" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:9">
       <c r="G171" s="53"/>
       <c r="H171" s="53"/>
       <c r="I171" s="53"/>
     </row>
-    <row r="172" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:9">
       <c r="G172" s="53"/>
       <c r="H172" s="53"/>
       <c r="I172" s="53"/>
     </row>
-    <row r="173" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:9">
       <c r="G173" s="53"/>
       <c r="H173" s="53"/>
       <c r="I173" s="53"/>
     </row>
-    <row r="174" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:9">
       <c r="G174" s="53"/>
       <c r="H174" s="53"/>
       <c r="I174" s="53"/>
     </row>
-    <row r="175" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:9">
       <c r="G175" s="53"/>
       <c r="H175" s="53"/>
       <c r="I175" s="53"/>
     </row>
-    <row r="176" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:9">
       <c r="G176" s="53"/>
       <c r="H176" s="53"/>
       <c r="I176" s="53"/>
     </row>
-    <row r="177" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:9">
       <c r="G177" s="53"/>
       <c r="H177" s="53"/>
       <c r="I177" s="53"/>
     </row>
-    <row r="178" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:9">
       <c r="G178" s="53"/>
       <c r="H178" s="53"/>
       <c r="I178" s="53"/>
     </row>
-    <row r="179" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:9">
       <c r="G179" s="53"/>
       <c r="H179" s="53"/>
       <c r="I179" s="53"/>
     </row>
-    <row r="180" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:9">
       <c r="G180" s="53"/>
       <c r="H180" s="53"/>
       <c r="I180" s="53"/>
     </row>
-    <row r="181" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:9">
       <c r="G181" s="53"/>
       <c r="H181" s="53"/>
       <c r="I181" s="53"/>
     </row>
-    <row r="182" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:9">
       <c r="G182" s="53"/>
       <c r="H182" s="53"/>
       <c r="I182" s="53"/>
     </row>
-    <row r="183" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:9">
       <c r="G183" s="53"/>
       <c r="H183" s="53"/>
       <c r="I183" s="53"/>
     </row>
-    <row r="184" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:9">
       <c r="G184" s="53"/>
       <c r="H184" s="53"/>
       <c r="I184" s="53"/>
     </row>
-    <row r="185" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:9">
       <c r="G185" s="53"/>
       <c r="H185" s="53"/>
       <c r="I185" s="53"/>
     </row>
-    <row r="186" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:9">
       <c r="G186" s="53"/>
       <c r="H186" s="53"/>
       <c r="I186" s="53"/>
     </row>
-    <row r="187" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:9">
       <c r="G187" s="53"/>
       <c r="H187" s="53"/>
       <c r="I187" s="53"/>
     </row>
-    <row r="188" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:9">
       <c r="G188" s="53"/>
       <c r="H188" s="53"/>
       <c r="I188" s="53"/>
     </row>
-    <row r="189" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:9">
       <c r="G189" s="53"/>
       <c r="H189" s="53"/>
       <c r="I189" s="53"/>
     </row>
-    <row r="190" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:9">
       <c r="G190" s="53"/>
       <c r="H190" s="53"/>
       <c r="I190" s="53"/>
     </row>
-    <row r="191" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:9">
       <c r="G191" s="53"/>
       <c r="H191" s="53"/>
       <c r="I191" s="53"/>
     </row>
-    <row r="192" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:9">
       <c r="G192" s="53"/>
       <c r="H192" s="53"/>
       <c r="I192" s="53"/>
     </row>
-    <row r="193" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:9">
       <c r="G193" s="53"/>
       <c r="H193" s="53"/>
       <c r="I193" s="53"/>
     </row>
-    <row r="194" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:9">
       <c r="G194" s="53"/>
       <c r="H194" s="53"/>
       <c r="I194" s="53"/>
     </row>
-    <row r="195" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:9">
       <c r="G195" s="53"/>
       <c r="H195" s="53"/>
       <c r="I195" s="53"/>
     </row>
-    <row r="196" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:9">
       <c r="G196" s="53"/>
       <c r="H196" s="53"/>
       <c r="I196" s="53"/>
     </row>
-    <row r="197" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:9">
       <c r="G197" s="53"/>
       <c r="H197" s="53"/>
       <c r="I197" s="53"/>
     </row>
-    <row r="198" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:9">
       <c r="G198" s="53"/>
       <c r="H198" s="53"/>
       <c r="I198" s="53"/>
     </row>
-    <row r="199" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:9">
       <c r="G199" s="53"/>
       <c r="H199" s="53"/>
       <c r="I199" s="53"/>
     </row>
-    <row r="200" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:9">
       <c r="G200" s="53"/>
       <c r="H200" s="53"/>
       <c r="I200" s="53"/>
     </row>
-    <row r="201" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:9">
       <c r="G201" s="53"/>
       <c r="H201" s="53"/>
       <c r="I201" s="53"/>
     </row>
-    <row r="202" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:9">
       <c r="G202" s="53"/>
       <c r="H202" s="53"/>
       <c r="I202" s="53"/>
     </row>
-    <row r="203" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:9">
       <c r="G203" s="53"/>
       <c r="H203" s="53"/>
       <c r="I203" s="53"/>
     </row>
-    <row r="204" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:9">
       <c r="G204" s="53"/>
       <c r="H204" s="53"/>
       <c r="I204" s="53"/>
     </row>
-    <row r="205" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:9">
       <c r="G205" s="53"/>
       <c r="H205" s="53"/>
       <c r="I205" s="53"/>
     </row>
-    <row r="206" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:9">
       <c r="G206" s="53"/>
       <c r="H206" s="53"/>
       <c r="I206" s="53"/>
     </row>
-    <row r="207" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:9">
       <c r="G207" s="53"/>
       <c r="H207" s="53"/>
       <c r="I207" s="53"/>
     </row>
-    <row r="208" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:9">
       <c r="G208" s="53"/>
       <c r="H208" s="53"/>
       <c r="I208" s="53"/>
     </row>
-    <row r="209" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:9">
       <c r="G209" s="53"/>
       <c r="H209" s="53"/>
       <c r="I209" s="53"/>
     </row>
-    <row r="210" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:9">
       <c r="G210" s="53"/>
       <c r="H210" s="53"/>
       <c r="I210" s="53"/>
     </row>
-    <row r="211" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:9">
       <c r="G211" s="53"/>
       <c r="H211" s="53"/>
       <c r="I211" s="53"/>
     </row>
-    <row r="212" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:9">
       <c r="G212" s="53"/>
       <c r="H212" s="53"/>
       <c r="I212" s="53"/>
     </row>
-    <row r="213" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:9">
       <c r="G213" s="53"/>
       <c r="H213" s="53"/>
       <c r="I213" s="53"/>
     </row>
-    <row r="214" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:9">
       <c r="G214" s="53"/>
       <c r="H214" s="53"/>
       <c r="I214" s="53"/>
     </row>
-    <row r="215" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:9">
       <c r="G215" s="53"/>
       <c r="H215" s="53"/>
       <c r="I215" s="53"/>
     </row>
-    <row r="216" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:9">
       <c r="G216" s="53"/>
       <c r="H216" s="53"/>
       <c r="I216" s="53"/>
     </row>
-    <row r="217" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:9">
       <c r="G217" s="53"/>
       <c r="H217" s="53"/>
       <c r="I217" s="53"/>
     </row>
-    <row r="218" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:9">
       <c r="G218" s="53"/>
       <c r="H218" s="53"/>
       <c r="I218" s="53"/>
     </row>
-    <row r="219" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:9">
       <c r="G219" s="53"/>
       <c r="H219" s="53"/>
       <c r="I219" s="53"/>
     </row>
-    <row r="220" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:9">
       <c r="G220" s="53"/>
       <c r="H220" s="53"/>
       <c r="I220" s="53"/>
     </row>
-    <row r="221" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:9">
       <c r="G221" s="53"/>
       <c r="H221" s="53"/>
       <c r="I221" s="53"/>
     </row>
-    <row r="222" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:9">
       <c r="G222" s="53"/>
       <c r="H222" s="53"/>
       <c r="I222" s="53"/>
     </row>
-    <row r="223" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:9">
       <c r="G223" s="53"/>
       <c r="H223" s="53"/>
       <c r="I223" s="53"/>
     </row>
-    <row r="224" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:9">
       <c r="G224" s="53"/>
       <c r="H224" s="53"/>
       <c r="I224" s="53"/>
     </row>
-    <row r="225" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:9">
       <c r="G225" s="53"/>
       <c r="H225" s="53"/>
       <c r="I225" s="53"/>
     </row>
-    <row r="226" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:9">
       <c r="G226" s="53"/>
       <c r="H226" s="53"/>
       <c r="I226" s="53"/>
     </row>
-    <row r="227" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:9">
       <c r="G227" s="53"/>
       <c r="H227" s="53"/>
       <c r="I227" s="53"/>
     </row>
-    <row r="228" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:9">
       <c r="G228" s="53"/>
       <c r="H228" s="53"/>
       <c r="I228" s="53"/>
     </row>
-    <row r="229" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:9">
       <c r="G229" s="53"/>
       <c r="H229" s="53"/>
       <c r="I229" s="53"/>
     </row>
-    <row r="230" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:9">
       <c r="G230" s="53"/>
       <c r="H230" s="53"/>
       <c r="I230" s="53"/>
     </row>
-    <row r="231" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:9">
       <c r="G231" s="53"/>
       <c r="H231" s="53"/>
       <c r="I231" s="53"/>
     </row>
-    <row r="232" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:9">
       <c r="G232" s="53"/>
       <c r="H232" s="53"/>
       <c r="I232" s="53"/>
     </row>
-    <row r="233" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:9">
       <c r="G233" s="53"/>
       <c r="H233" s="53"/>
       <c r="I233" s="53"/>
     </row>
-    <row r="234" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:9">
       <c r="G234" s="53"/>
       <c r="H234" s="53"/>
       <c r="I234" s="53"/>
     </row>
-    <row r="235" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:9">
       <c r="G235" s="53"/>
       <c r="H235" s="53"/>
       <c r="I235" s="53"/>
     </row>
-    <row r="236" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:9">
       <c r="G236" s="53"/>
       <c r="H236" s="53"/>
       <c r="I236" s="53"/>
     </row>
-    <row r="237" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:9">
       <c r="G237" s="53"/>
       <c r="H237" s="53"/>
       <c r="I237" s="53"/>
     </row>
-    <row r="238" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:9">
       <c r="G238" s="53"/>
       <c r="H238" s="53"/>
       <c r="I238" s="53"/>
     </row>
-    <row r="239" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:9">
       <c r="G239" s="53"/>
       <c r="H239" s="53"/>
       <c r="I239" s="53"/>
     </row>
-    <row r="240" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:9">
       <c r="G240" s="53"/>
       <c r="H240" s="53"/>
       <c r="I240" s="53"/>
     </row>
-    <row r="241" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:9">
       <c r="G241" s="53"/>
       <c r="H241" s="53"/>
       <c r="I241" s="53"/>
     </row>
-    <row r="242" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:9">
       <c r="G242" s="53"/>
       <c r="H242" s="53"/>
       <c r="I242" s="53"/>
     </row>
-    <row r="243" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:9">
       <c r="G243" s="53"/>
       <c r="H243" s="53"/>
       <c r="I243" s="53"/>
     </row>
-    <row r="244" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:9">
       <c r="G244" s="53"/>
       <c r="H244" s="53"/>
       <c r="I244" s="53"/>
     </row>
-    <row r="245" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:9">
       <c r="G245" s="53"/>
       <c r="H245" s="53"/>
       <c r="I245" s="53"/>
     </row>
-    <row r="246" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:9">
       <c r="G246" s="53"/>
       <c r="H246" s="53"/>
       <c r="I246" s="53"/>
     </row>
-    <row r="247" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:9">
       <c r="G247" s="53"/>
       <c r="H247" s="53"/>
       <c r="I247" s="53"/>
     </row>
-    <row r="248" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:9">
       <c r="G248" s="53"/>
       <c r="H248" s="53"/>
       <c r="I248" s="53"/>
     </row>
-    <row r="249" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:9">
       <c r="G249" s="53"/>
       <c r="H249" s="53"/>
       <c r="I249" s="53"/>
     </row>
-    <row r="250" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:9">
       <c r="G250" s="53"/>
       <c r="H250" s="53"/>
       <c r="I250" s="53"/>
     </row>
-    <row r="251" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:9">
       <c r="G251" s="53"/>
       <c r="H251" s="53"/>
       <c r="I251" s="53"/>
     </row>
-    <row r="252" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:9">
       <c r="G252" s="53"/>
       <c r="H252" s="53"/>
       <c r="I252" s="53"/>
     </row>
-    <row r="253" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:9">
       <c r="G253" s="53"/>
       <c r="H253" s="53"/>
       <c r="I253" s="53"/>
     </row>
-    <row r="254" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:9">
       <c r="G254" s="53"/>
       <c r="H254" s="53"/>
       <c r="I254" s="53"/>
     </row>
-    <row r="255" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:9">
       <c r="G255" s="53"/>
       <c r="H255" s="53"/>
       <c r="I255" s="53"/>
     </row>
-    <row r="256" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:9">
       <c r="G256" s="53"/>
       <c r="H256" s="53"/>
       <c r="I256" s="53"/>
     </row>
-    <row r="257" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:9">
       <c r="G257" s="53"/>
       <c r="H257" s="1"/>
       <c r="I257" s="1"/>
     </row>
-    <row r="258" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:9">
       <c r="G258" s="53"/>
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>
     </row>
-    <row r="259" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:9">
       <c r="G259" s="53"/>
       <c r="H259" s="1"/>
       <c r="I259" s="1"/>
     </row>
-    <row r="260" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:9">
       <c r="G260" s="53"/>
       <c r="H260" s="1"/>
       <c r="I260" s="1"/>
     </row>
-    <row r="261" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:9">
       <c r="G261" s="53"/>
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
     </row>
-    <row r="262" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:9">
       <c r="G262" s="53"/>
       <c r="H262" s="1"/>
       <c r="I262" s="1"/>
     </row>
-    <row r="263" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:9">
       <c r="G263" s="53"/>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
     </row>
-    <row r="264" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:9">
       <c r="G264" s="53"/>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
     </row>
-    <row r="265" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:9">
       <c r="G265" s="53"/>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
     </row>
-    <row r="266" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:9">
       <c r="G266" s="53"/>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
     </row>
-    <row r="267" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:9">
       <c r="G267" s="53"/>
     </row>
-    <row r="268" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:9">
       <c r="G268" s="53"/>
     </row>
-    <row r="269" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:9">
       <c r="G269" s="53"/>
     </row>
-    <row r="270" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:9">
       <c r="G270" s="53"/>
     </row>
-    <row r="271" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:9">
       <c r="G271" s="53"/>
     </row>
-    <row r="272" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:9">
       <c r="G272" s="53"/>
     </row>
-    <row r="273" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:7">
       <c r="G273" s="53"/>
     </row>
-    <row r="274" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:7">
       <c r="G274" s="53"/>
     </row>
-    <row r="275" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:7">
       <c r="G275" s="53"/>
     </row>
-    <row r="276" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:7">
       <c r="G276" s="53"/>
     </row>
-    <row r="277" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:7">
       <c r="G277" s="53"/>
     </row>
-    <row r="278" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:7">
       <c r="G278" s="53"/>
     </row>
-    <row r="279" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:7">
       <c r="G279" s="53"/>
     </row>
-    <row r="280" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:7">
       <c r="G280" s="53"/>
     </row>
-    <row r="281" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:7">
       <c r="G281" s="53"/>
     </row>
-    <row r="282" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:7">
       <c r="G282" s="53"/>
     </row>
-    <row r="283" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:7">
       <c r="G283" s="53"/>
     </row>
-    <row r="284" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:7">
       <c r="G284" s="53"/>
     </row>
-    <row r="285" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:7">
       <c r="G285" s="53"/>
     </row>
-    <row r="286" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:7">
       <c r="G286" s="53"/>
     </row>
-    <row r="287" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:7">
       <c r="G287" s="53"/>
     </row>
-    <row r="288" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:7">
       <c r="G288" s="53"/>
     </row>
-    <row r="289" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:7">
       <c r="G289" s="53"/>
     </row>
-    <row r="290" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:7">
       <c r="G290" s="53"/>
     </row>
-    <row r="291" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:7">
       <c r="G291" s="53"/>
     </row>
-    <row r="292" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:7">
       <c r="G292" s="53"/>
     </row>
-    <row r="293" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:7">
       <c r="G293" s="53"/>
     </row>
-    <row r="294" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:7">
       <c r="G294" s="53"/>
     </row>
-    <row r="295" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:7">
       <c r="G295" s="53"/>
     </row>
-    <row r="296" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:7">
       <c r="G296" s="53"/>
     </row>
-    <row r="297" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:7">
       <c r="G297" s="53"/>
     </row>
-    <row r="298" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:7">
       <c r="G298" s="53"/>
     </row>
-    <row r="299" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:7">
       <c r="G299" s="53"/>
     </row>
-    <row r="300" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:7">
       <c r="G300" s="53"/>
     </row>
-    <row r="301" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:7">
       <c r="G301" s="53"/>
     </row>
-    <row r="302" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:7">
       <c r="G302" s="53"/>
     </row>
-    <row r="303" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:7">
       <c r="G303" s="53"/>
     </row>
-    <row r="304" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:7">
       <c r="G304" s="53"/>
     </row>
-    <row r="305" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:7">
       <c r="G305" s="53"/>
     </row>
-    <row r="306" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:7">
       <c r="G306" s="53"/>
     </row>
-    <row r="307" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:7">
       <c r="G307" s="53"/>
     </row>
-    <row r="308" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:7">
       <c r="G308" s="53"/>
     </row>
-    <row r="309" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:7">
       <c r="G309" s="53"/>
     </row>
-    <row r="310" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:7">
       <c r="G310" s="53"/>
     </row>
-    <row r="311" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:7">
       <c r="G311" s="53"/>
     </row>
-    <row r="312" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:7">
       <c r="G312" s="53"/>
     </row>
-    <row r="313" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:7">
       <c r="G313" s="53"/>
     </row>
-    <row r="314" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:7">
       <c r="G314" s="53"/>
     </row>
-    <row r="315" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:7">
       <c r="G315" s="53"/>
     </row>
-    <row r="316" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:7">
       <c r="G316" s="53"/>
     </row>
-    <row r="317" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:7">
       <c r="G317" s="53"/>
     </row>
-    <row r="318" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:7">
       <c r="G318" s="53"/>
     </row>
-    <row r="319" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:7">
       <c r="G319" s="53"/>
     </row>
-    <row r="320" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:7">
       <c r="G320" s="53"/>
     </row>
-    <row r="321" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:7">
       <c r="G321" s="53"/>
     </row>
-    <row r="322" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:7">
       <c r="G322" s="53"/>
     </row>
-    <row r="323" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:7">
       <c r="G323" s="53"/>
     </row>
-    <row r="324" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:7">
       <c r="G324" s="53"/>
     </row>
-    <row r="325" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:7">
       <c r="G325" s="53"/>
     </row>
-    <row r="326" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:7">
       <c r="G326" s="53"/>
     </row>
-    <row r="327" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:7">
       <c r="G327" s="53"/>
     </row>
-    <row r="328" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:7">
       <c r="G328" s="53"/>
     </row>
-    <row r="329" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:7">
       <c r="G329" s="53"/>
     </row>
-    <row r="330" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:7">
       <c r="G330" s="53"/>
     </row>
-    <row r="331" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:7">
       <c r="G331" s="53"/>
     </row>
-    <row r="332" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:7">
       <c r="G332" s="53"/>
     </row>
-    <row r="333" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:7">
       <c r="G333" s="53"/>
     </row>
-    <row r="334" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:7">
       <c r="G334" s="53"/>
     </row>
-    <row r="335" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:7">
       <c r="G335" s="53"/>
     </row>
-    <row r="336" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:7">
       <c r="G336" s="53"/>
     </row>
-    <row r="337" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="7:7">
       <c r="G337" s="53"/>
     </row>
-    <row r="338" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="7:7">
       <c r="G338" s="53"/>
     </row>
-    <row r="339" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="7:7">
       <c r="G339" s="53"/>
     </row>
-    <row r="340" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="7:7">
       <c r="G340" s="53"/>
     </row>
-    <row r="341" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="7:7">
       <c r="G341" s="53"/>
     </row>
-    <row r="342" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="7:7">
       <c r="G342" s="53"/>
     </row>
-    <row r="343" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="7:7">
       <c r="G343" s="53"/>
     </row>
-    <row r="344" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="7:7">
       <c r="G344" s="53"/>
     </row>
-    <row r="345" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="7:7">
       <c r="G345" s="53"/>
     </row>
-    <row r="346" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="7:7">
       <c r="G346" s="53"/>
     </row>
-    <row r="347" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="7:7">
       <c r="G347" s="53"/>
     </row>
-    <row r="348" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="7:7">
       <c r="G348" s="53"/>
     </row>
-    <row r="349" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="7:7">
       <c r="G349" s="53"/>
     </row>
-    <row r="350" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="7:7">
       <c r="G350" s="53"/>
     </row>
-    <row r="351" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="7:7">
       <c r="G351" s="53"/>
     </row>
-    <row r="352" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="7:7">
       <c r="G352" s="53"/>
     </row>
-    <row r="353" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="7:7">
       <c r="G353" s="53"/>
     </row>
-    <row r="354" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="7:7">
       <c r="G354" s="53"/>
     </row>
-    <row r="355" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="7:7">
       <c r="G355" s="53"/>
     </row>
-    <row r="356" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="7:7">
       <c r="G356" s="53"/>
     </row>
-    <row r="357" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="7:7">
       <c r="G357" s="53"/>
     </row>
-    <row r="358" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="7:7">
       <c r="G358" s="53"/>
     </row>
-    <row r="359" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="7:7">
       <c r="G359" s="53"/>
     </row>
-    <row r="360" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="7:7">
       <c r="G360" s="53"/>
     </row>
-    <row r="361" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="7:7">
       <c r="G361" s="53"/>
     </row>
-    <row r="362" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="7:7">
       <c r="G362" s="53"/>
     </row>
-    <row r="363" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="7:7">
       <c r="G363" s="53"/>
     </row>
-    <row r="364" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="7:7">
       <c r="G364" s="53"/>
     </row>
-    <row r="365" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="7:7">
       <c r="G365" s="53"/>
     </row>
-    <row r="366" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="7:7">
       <c r="G366" s="53"/>
     </row>
-    <row r="367" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="7:7">
       <c r="G367" s="53"/>
     </row>
-    <row r="368" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="7:7">
       <c r="G368" s="53"/>
     </row>
-    <row r="369" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="7:7">
       <c r="G369" s="53"/>
     </row>
-    <row r="370" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="7:7">
       <c r="G370" s="53"/>
     </row>
-    <row r="371" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="7:7">
       <c r="G371" s="53"/>
     </row>
-    <row r="372" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="7:7">
       <c r="G372" s="53"/>
     </row>
-    <row r="373" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="7:7">
       <c r="G373" s="53"/>
     </row>
-    <row r="374" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="7:7">
       <c r="G374" s="53"/>
     </row>
-    <row r="375" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="7:7">
       <c r="G375" s="53"/>
     </row>
-    <row r="376" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="7:7">
       <c r="G376" s="53"/>
     </row>
-    <row r="377" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="7:7">
       <c r="G377" s="53"/>
     </row>
-    <row r="378" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="7:7">
       <c r="G378" s="53"/>
     </row>
-    <row r="379" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="7:7">
       <c r="G379" s="53"/>
     </row>
-    <row r="380" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="7:7">
       <c r="G380" s="53"/>
     </row>
-    <row r="381" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="7:7">
       <c r="G381" s="53"/>
     </row>
-    <row r="382" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="7:7">
       <c r="G382" s="53"/>
     </row>
-    <row r="383" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="7:7">
       <c r="G383" s="53"/>
     </row>
-    <row r="384" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="7:7">
       <c r="G384" s="53"/>
     </row>
-    <row r="385" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="7:7">
       <c r="G385" s="53"/>
     </row>
-    <row r="386" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="7:7">
       <c r="G386" s="53"/>
     </row>
-    <row r="387" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="7:7">
       <c r="G387" s="53"/>
     </row>
-    <row r="388" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="7:7">
       <c r="G388" s="53"/>
     </row>
-    <row r="389" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="7:7">
       <c r="G389" s="53"/>
     </row>
-    <row r="390" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="7:7">
       <c r="G390" s="53"/>
     </row>
-    <row r="391" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="7:7">
       <c r="G391" s="53"/>
     </row>
-    <row r="392" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="7:7">
       <c r="G392" s="53"/>
     </row>
-    <row r="393" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="7:7">
       <c r="G393" s="53"/>
     </row>
-    <row r="394" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="7:7">
       <c r="G394" s="53"/>
     </row>
-    <row r="395" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="7:7">
       <c r="G395" s="53"/>
     </row>
-    <row r="396" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="7:7">
       <c r="G396" s="53"/>
     </row>
-    <row r="397" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="7:7">
       <c r="G397" s="53"/>
     </row>
-    <row r="398" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="7:7">
       <c r="G398" s="53"/>
     </row>
-    <row r="399" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="7:7">
       <c r="G399" s="53"/>
     </row>
-    <row r="400" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="7:7">
       <c r="G400" s="53"/>
     </row>
-    <row r="401" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="7:7">
       <c r="G401" s="53"/>
     </row>
-    <row r="402" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="7:7">
       <c r="G402" s="53"/>
     </row>
-    <row r="403" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="7:7">
       <c r="G403" s="53"/>
     </row>
-    <row r="404" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="7:7">
       <c r="G404" s="53"/>
     </row>
   </sheetData>
@@ -11201,42 +11759,66 @@
     <mergeCell ref="M3:M4"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C84:D114 C115:C121">
-    <cfRule type="cellIs" dxfId="9" priority="173" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="179" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="174" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="180" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G96:H121 G122:G1048576">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="G96:H98 G123:G1048576 G116:H116 H99:H115">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:I95">
-    <cfRule type="cellIs" dxfId="5" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="19" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="14" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H129:I266">
-    <cfRule type="cellIs" dxfId="3" priority="171" operator="greaterThan">
+  <conditionalFormatting sqref="H131:I266 I129:I130">
+    <cfRule type="cellIs" dxfId="9" priority="177" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="172" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="178" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I96:I128">
-    <cfRule type="cellIs" dxfId="1" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="25" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="26" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G99:G115">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G117:H117">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G118:H122 H123:H130">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11248,7 +11830,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:D17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="2" width="26.28515625" customWidth="1"/>
@@ -11256,101 +11838,101 @@
     <col min="4" max="4" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4">
       <c r="B1" s="62" t="s">
-        <v>217</v>
+        <v>270</v>
       </c>
       <c r="C1" s="63" t="s">
-        <v>218</v>
+        <v>271</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4">
       <c r="B2" s="54" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>220</v>
+        <v>273</v>
       </c>
       <c r="D2" s="54"/>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4">
       <c r="B3" s="54" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="D3" s="54"/>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4">
       <c r="B4" s="54" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="D4" s="54"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4">
       <c r="B5" s="54" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>220</v>
+        <v>273</v>
       </c>
       <c r="D5" s="54"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4">
       <c r="B6" s="54" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="D6" s="54"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4">
       <c r="B7" s="54" t="s">
-        <v>222</v>
+        <v>275</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>220</v>
+        <v>273</v>
       </c>
       <c r="D7" s="54"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4">
       <c r="B8" s="54" t="s">
-        <v>223</v>
+        <v>276</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="D8" s="54"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4">
       <c r="B9" s="54" t="s">
-        <v>126</v>
+        <v>177</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
       <c r="B10" s="54" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="D10" s="54"/>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3">
       <c r="C17" s="28"/>
     </row>
   </sheetData>

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="378" documentId="8_{0F9471C2-95A1-4CF9-8CFE-1EF73F0B2DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F13926B-4FCC-494B-AAC4-993FF0A8CA9D}"/>
+  <xr:revisionPtr revIDLastSave="501" documentId="8_{0F9471C2-95A1-4CF9-8CFE-1EF73F0B2DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FCB5A87-9713-4693-8DC4-F62A4D1F5DDC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" firstSheet="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="299">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -141,9 +141,6 @@
     <t>Status pagamento Stella</t>
   </si>
   <si>
-    <t>Em aberto</t>
-  </si>
-  <si>
     <t>Itaú Total</t>
   </si>
   <si>
@@ -519,7 +516,7 @@
     <t>Pagamento Almoço Mr Jones</t>
   </si>
   <si>
-    <t>Airbnb Sorocaba Caio</t>
+    <t>Airbnb Sorocaba</t>
   </si>
   <si>
     <t>Serviços</t>
@@ -540,6 +537,54 @@
     <t>Kadalora</t>
   </si>
   <si>
+    <t>Nerdcon</t>
+  </si>
+  <si>
+    <t>Churrascaria</t>
+  </si>
+  <si>
+    <t>Moonshine Nerdcon</t>
+  </si>
+  <si>
+    <t>99 Degas</t>
+  </si>
+  <si>
+    <t>Degas</t>
+  </si>
+  <si>
+    <t>Vacina e Exame Rennala</t>
+  </si>
+  <si>
+    <t>Pet</t>
+  </si>
+  <si>
+    <t>Pagamento Degas</t>
+  </si>
+  <si>
+    <t>Pagamento Churrascaria</t>
+  </si>
+  <si>
+    <t>PS PLus</t>
+  </si>
+  <si>
+    <t>Carnes</t>
+  </si>
+  <si>
+    <t>Multa</t>
+  </si>
+  <si>
+    <t>Remédios</t>
+  </si>
+  <si>
+    <t>Quero-Quero</t>
+  </si>
+  <si>
+    <t>Cobasi Rennala</t>
+  </si>
+  <si>
+    <t>Pagamento Cobase Rennala e Quero-Quero</t>
+  </si>
+  <si>
     <t>Vivo</t>
   </si>
   <si>
@@ -786,40 +831,37 @@
     <t xml:space="preserve">Devolução Stella </t>
   </si>
   <si>
+    <t>Sanduba do Barba</t>
+  </si>
+  <si>
+    <t>Ilumeo Agosto - 2º PPT</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
+    <t>Passagens - Compradas em agosto</t>
+  </si>
+  <si>
+    <t>Adiantamento Stella Setembro</t>
+  </si>
+  <si>
+    <t>Restituição IR</t>
+  </si>
+  <si>
+    <t>Novembro</t>
+  </si>
+  <si>
+    <t>Psicóloga Atrasada</t>
+  </si>
+  <si>
+    <t>Custos Rennala</t>
+  </si>
+  <si>
     <t>Devolução Stella + Recolhimento</t>
   </si>
   <si>
-    <t>Sanduba do Barba</t>
-  </si>
-  <si>
-    <t>Ilumeo Agosto - 2º PPT</t>
-  </si>
-  <si>
-    <t>Outubro</t>
-  </si>
-  <si>
-    <t>Setembro</t>
-  </si>
-  <si>
-    <t>Passagens - Compradas em agosto</t>
-  </si>
-  <si>
-    <t>Pagamento Control</t>
-  </si>
-  <si>
-    <t>Adiantamento Stella Setembro</t>
-  </si>
-  <si>
-    <t>Restituição IR</t>
-  </si>
-  <si>
-    <t>Novembro</t>
-  </si>
-  <si>
-    <t>Psicóloga Atrasada</t>
-  </si>
-  <si>
-    <t>Custos Rennala</t>
+    <t>Custos Rennala 2</t>
   </si>
   <si>
     <t>Dezembro</t>
@@ -883,6 +925,24 @@
   </si>
   <si>
     <t>Dera</t>
+  </si>
+  <si>
+    <t>Janta Aniversário Stella</t>
+  </si>
+  <si>
+    <t>Adiantamento Parcelas Blood of the Dawnalker</t>
+  </si>
+  <si>
+    <t>Pagamento Janta Aniversário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagamento Adiantamento Dawnwalker </t>
+  </si>
+  <si>
+    <t>Janta Anivsersário</t>
+  </si>
+  <si>
+    <t>Recebido</t>
   </si>
 </sst>
 </file>
@@ -894,7 +954,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1175,7 +1235,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1359,30 +1419,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
+  <dxfs count="32">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1533,7 +1586,28 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1636,6 +1710,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1815,7 +1893,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:F41"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
     <col min="3" max="3" width="19.85546875" style="1" customWidth="1"/>
@@ -1824,9 +1902,9 @@
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" customHeight="1"/>
-    <row r="2" spans="2:6" ht="23.25" customHeight="1">
-      <c r="B2" s="75" t="s">
+    <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="76" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -1837,20 +1915,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="24" customHeight="1">
+    <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="77"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C25+C26+C7+C27</f>
-        <v>1631.7072380952386</v>
+        <v>1851.9222380952388</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E25+E26</f>
-        <v>2330.8541666666661</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="7.5" customHeight="1"/>
-    <row r="5" spans="2:6">
+        <v>1794.9891666666663</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
@@ -1862,21 +1940,21 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-8190.7927619047614</v>
+        <v>-8970.5777619047622</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-7669.1458333333339</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6">
+        <v>-8205.0108333333337</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -1884,7 +1962,7 @@
       <c r="D7" s="9"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
@@ -1898,35 +1976,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>5580.2910952380944</v>
+        <v>6360.0760952380942</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>1806.8058333333333</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6">
+        <v>2342.6708333333331</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>5580.2910952380944</v>
+        <v>6360.0760952380942</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>1806.8058333333333</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6">
+        <v>2342.6708333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
@@ -1940,7 +2018,7 @@
         <v>5862.34</v>
       </c>
     </row>
-    <row r="12" spans="2:6" outlineLevel="1">
+    <row r="12" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
         <v>10</v>
       </c>
@@ -1954,7 +2032,7 @@
         <v>1617.835</v>
       </c>
     </row>
-    <row r="13" spans="2:6" outlineLevel="1">
+    <row r="13" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
@@ -1968,7 +2046,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="2:6" outlineLevel="1">
+    <row r="14" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B14" s="13" t="s">
         <v>12</v>
       </c>
@@ -1983,7 +2061,7 @@
       </c>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="2:6" outlineLevel="1">
+    <row r="15" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="s">
         <v>13</v>
       </c>
@@ -1997,7 +2075,7 @@
         <v>40.619999999999997</v>
       </c>
     </row>
-    <row r="16" spans="2:6" outlineLevel="1">
+    <row r="16" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
         <v>14</v>
       </c>
@@ -2011,7 +2089,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:5" outlineLevel="1">
+    <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
         <v>15</v>
       </c>
@@ -2025,7 +2103,7 @@
         <v>112.38500000000001</v>
       </c>
     </row>
-    <row r="18" spans="2:5" outlineLevel="1">
+    <row r="18" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
         <v>16</v>
       </c>
@@ -2039,7 +2117,7 @@
         <v>333.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" outlineLevel="1">
+    <row r="19" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B19" s="13" t="str">
         <f>Contas!$D10</f>
         <v>Cartão Itaú da Stella</v>
@@ -2051,7 +2129,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="2:5" outlineLevel="1">
+    <row r="20" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B20" s="13" t="str">
         <f>Contas!$D11</f>
         <v>Recolhimento INSS</v>
@@ -2063,7 +2141,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="21" spans="2:5" outlineLevel="1">
+    <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B21" s="13" t="str">
         <f>Contas!$D12</f>
         <v>Empréstimo</v>
@@ -2075,7 +2153,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="22" spans="2:5" outlineLevel="1">
+    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B22" s="17" t="s">
         <v>17</v>
       </c>
@@ -2083,29 +2161,27 @@
       <c r="D22" s="19"/>
       <c r="E22" s="18"/>
     </row>
-    <row r="23" spans="2:5" outlineLevel="1">
+    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B23" s="13"/>
       <c r="C23" s="14"/>
       <c r="D23" s="15"/>
       <c r="E23" s="14"/>
     </row>
-    <row r="24" spans="2:5" outlineLevel="1">
+    <row r="24" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B24" s="13"/>
       <c r="C24" s="14"/>
       <c r="D24" s="15"/>
       <c r="E24" s="14"/>
     </row>
-    <row r="25" spans="2:5">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="8">
-        <v>1000</v>
-      </c>
+      <c r="C25" s="8"/>
       <c r="D25" s="9"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" spans="2:5">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
         <v>19</v>
       </c>
@@ -2119,7 +2195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:5">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="13" t="s">
         <v>20</v>
       </c>
@@ -2130,7 +2206,7 @@
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28" spans="2:5" outlineLevel="1">
+    <row r="28" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B28" s="13" t="s">
         <v>21</v>
       </c>
@@ -2141,7 +2217,7 @@
       <c r="D28" s="15"/>
       <c r="E28" s="14"/>
     </row>
-    <row r="29" spans="2:5" outlineLevel="1">
+    <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B29" s="13" t="s">
         <v>22</v>
       </c>
@@ -2149,7 +2225,7 @@
       <c r="D29" s="20"/>
       <c r="E29" s="21"/>
     </row>
-    <row r="30" spans="2:5" outlineLevel="1">
+    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B30" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L7</f>
         <v xml:space="preserve">       </v>
@@ -2161,7 +2237,7 @@
       <c r="D30" s="20"/>
       <c r="E30" s="21"/>
     </row>
-    <row r="31" spans="2:5" outlineLevel="1">
+    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B31" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L8</f>
         <v xml:space="preserve">       </v>
@@ -2173,7 +2249,7 @@
       <c r="D31" s="20"/>
       <c r="E31" s="21"/>
     </row>
-    <row r="32" spans="2:5" outlineLevel="1">
+    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B32" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L9</f>
         <v xml:space="preserve">       </v>
@@ -2185,7 +2261,7 @@
       <c r="D32" s="20"/>
       <c r="E32" s="21"/>
     </row>
-    <row r="33" spans="2:6" outlineLevel="1">
+    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B33" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L10</f>
         <v xml:space="preserve">       </v>
@@ -2197,7 +2273,7 @@
       <c r="D33" s="20"/>
       <c r="E33" s="21"/>
     </row>
-    <row r="34" spans="2:6" outlineLevel="1">
+    <row r="34" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B34" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L12</f>
         <v xml:space="preserve">       </v>
@@ -2209,7 +2285,7 @@
       <c r="D34" s="20"/>
       <c r="E34" s="21"/>
     </row>
-    <row r="35" spans="2:6" outlineLevel="1">
+    <row r="35" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B35" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L13</f>
         <v xml:space="preserve">       </v>
@@ -2221,7 +2297,7 @@
       <c r="D35" s="20"/>
       <c r="E35" s="21"/>
     </row>
-    <row r="36" spans="2:6" outlineLevel="1">
+    <row r="36" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B36" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L14</f>
         <v xml:space="preserve">       </v>
@@ -2233,7 +2309,7 @@
       <c r="D36" s="20"/>
       <c r="E36" s="21"/>
     </row>
-    <row r="37" spans="2:6" outlineLevel="1">
+    <row r="37" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B37" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L15</f>
         <v xml:space="preserve">       </v>
@@ -2245,7 +2321,7 @@
       <c r="D37" s="20"/>
       <c r="E37" s="21"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L16</f>
         <v xml:space="preserve">       </v>
@@ -2258,7 +2334,7 @@
       <c r="E38" s="21"/>
       <c r="F38" s="16"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L17</f>
         <v xml:space="preserve">       </v>
@@ -2271,7 +2347,7 @@
       <c r="E39" s="21"/>
       <c r="F39" s="16"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L21</f>
         <v xml:space="preserve">       </v>
@@ -2283,7 +2359,7 @@
       <c r="D40" s="20"/>
       <c r="E40" s="21"/>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L22</f>
         <v xml:space="preserve">       </v>
@@ -2307,7 +2383,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:D24"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="31.42578125" customWidth="1"/>
@@ -2316,8 +2392,8 @@
     <col min="5" max="5" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="39" customHeight="1"/>
-    <row r="2" spans="2:4" ht="18.75" customHeight="1">
+    <row r="1" spans="2:4" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="22"/>
       <c r="C2" s="23" t="s">
         <v>2</v>
@@ -2326,7 +2402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
@@ -2339,45 +2415,45 @@
         <v>40.161666666666669</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>1806.8058333333333</v>
+        <v>2342.6708333333331</v>
       </c>
       <c r="D4" s="24">
         <f>Saldo!C9+D5</f>
-        <v>5580.2910952380944</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
+        <v>6360.0760952380942</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="13"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="13"/>
       <c r="C7" s="8"/>
       <c r="D7" s="24"/>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="13"/>
       <c r="C8" s="8"/>
       <c r="D8" s="24"/>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="13"/>
       <c r="C9" s="8"/>
       <c r="D9" s="24"/>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
@@ -2387,7 +2463,7 @@
       </c>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="2:4">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
         <v>23</v>
       </c>
@@ -2397,7 +2473,7 @@
       </c>
       <c r="D11" s="13"/>
     </row>
-    <row r="12" spans="2:4">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="25" t="s">
         <v>24</v>
       </c>
@@ -2407,7 +2483,7 @@
       </c>
       <c r="D12" s="13"/>
     </row>
-    <row r="13" spans="2:4">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
         <v>12</v>
       </c>
@@ -2417,7 +2493,7 @@
       </c>
       <c r="D13" s="13"/>
     </row>
-    <row r="14" spans="2:4">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="13" t="s">
         <v>13</v>
       </c>
@@ -2427,7 +2503,7 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="2:4">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="s">
         <v>14</v>
       </c>
@@ -2437,7 +2513,7 @@
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="2:4">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
         <v>15</v>
       </c>
@@ -2447,7 +2523,7 @@
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
         <v>25</v>
       </c>
@@ -2457,7 +2533,7 @@
       </c>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
         <v>26</v>
       </c>
@@ -2467,33 +2543,31 @@
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="19" spans="2:4">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="13"/>
       <c r="C19" s="14"/>
       <c r="D19" s="13"/>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>5155.1458333333339</v>
+        <v>5691.0108333333337</v>
       </c>
       <c r="D20" s="27"/>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="2:4">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="11">
-        <v>5556.6183333333338</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4">
+      <c r="C22" s="11"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>29</v>
       </c>
@@ -2501,12 +2575,12 @@
         <v>46262</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>30</v>
       </c>
       <c r="C24" s="71" t="s">
-        <v>31</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -2521,7 +2595,7 @@
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
   <dimension ref="C1:Q67"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" style="2" customWidth="1"/>
@@ -2536,9 +2610,9 @@
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
@@ -2547,10 +2621,10 @@
         <v>2</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="31">
         <f>SUM(L5:L21)</f>
         <v>40.161666666666669</v>
@@ -2568,59 +2642,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="3:17" ht="30" customHeight="1">
+    <row r="4" spans="3:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="E4" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="F4" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="G4" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="H4" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="I4" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="J4" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="K4" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="L4" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="34" t="s">
+      <c r="M4" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="M4" s="34" t="s">
+      <c r="N4" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="34" t="s">
+      <c r="O4" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="O4" s="33" t="s">
+      <c r="P4" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="P4" s="33" t="s">
+      <c r="Q4" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="Q4" s="34" t="s">
+    </row>
+    <row r="5" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="69" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="3:17" ht="16.5" customHeight="1">
-      <c r="C5" s="69" t="s">
+      <c r="D5" s="36" t="s">
         <v>49</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>50</v>
       </c>
       <c r="E5" s="37" t="s">
         <v>1</v>
@@ -2635,10 +2709,10 @@
         <v>240.97</v>
       </c>
       <c r="J5" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="37" t="s">
         <v>51</v>
-      </c>
-      <c r="K5" s="37" t="s">
-        <v>52</v>
       </c>
       <c r="L5" s="38">
         <f t="shared" ref="L5:L15" si="1">I5/N5</f>
@@ -2663,7 +2737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="3:17" ht="16.5" customHeight="1">
+    <row r="6" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="37"/>
       <c r="D6" s="36"/>
       <c r="E6" s="37"/>
@@ -2695,7 +2769,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="3:17" ht="16.5" customHeight="1">
+    <row r="7" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="35"/>
       <c r="D7" s="36"/>
       <c r="E7" s="37"/>
@@ -2724,7 +2798,7 @@
       <c r="P7" s="35"/>
       <c r="Q7" s="37"/>
     </row>
-    <row r="8" spans="3:17" ht="16.5" customHeight="1">
+    <row r="8" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="35"/>
       <c r="D8" s="36"/>
       <c r="E8" s="37"/>
@@ -2753,7 +2827,7 @@
       <c r="P8" s="35"/>
       <c r="Q8" s="37"/>
     </row>
-    <row r="9" spans="3:17" ht="16.5" customHeight="1">
+    <row r="9" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="35"/>
       <c r="D9" s="36"/>
       <c r="E9" s="37"/>
@@ -2782,7 +2856,7 @@
       <c r="P9" s="35"/>
       <c r="Q9" s="37"/>
     </row>
-    <row r="10" spans="3:17" ht="16.5" customHeight="1">
+    <row r="10" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="35"/>
       <c r="D10" s="36"/>
       <c r="E10" s="37"/>
@@ -2814,7 +2888,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="3:17" ht="16.5" customHeight="1">
+    <row r="11" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="35"/>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
@@ -2843,7 +2917,7 @@
       <c r="P11" s="35"/>
       <c r="Q11" s="37"/>
     </row>
-    <row r="12" spans="3:17" ht="16.5" customHeight="1">
+    <row r="12" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="37"/>
       <c r="D12" s="36"/>
       <c r="E12" s="37"/>
@@ -2872,7 +2946,7 @@
       <c r="P12" s="35"/>
       <c r="Q12" s="37"/>
     </row>
-    <row r="13" spans="3:17" ht="16.5" customHeight="1">
+    <row r="13" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="37"/>
       <c r="D13" s="36"/>
       <c r="E13" s="37"/>
@@ -2901,7 +2975,7 @@
       <c r="P13" s="35"/>
       <c r="Q13" s="37"/>
     </row>
-    <row r="14" spans="3:17" ht="16.5" customHeight="1">
+    <row r="14" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="37"/>
       <c r="D14" s="36"/>
       <c r="E14" s="37"/>
@@ -2930,7 +3004,7 @@
       <c r="P14" s="35"/>
       <c r="Q14" s="37"/>
     </row>
-    <row r="15" spans="3:17" ht="16.5" customHeight="1">
+    <row r="15" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="37"/>
       <c r="D15" s="36"/>
       <c r="E15" s="37"/>
@@ -2959,7 +3033,7 @@
       <c r="P15" s="35"/>
       <c r="Q15" s="37"/>
     </row>
-    <row r="16" spans="3:17" ht="16.5" customHeight="1">
+    <row r="16" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="37"/>
       <c r="D16" s="36"/>
       <c r="E16" s="37"/>
@@ -2976,7 +3050,7 @@
       <c r="P16" s="35"/>
       <c r="Q16" s="37"/>
     </row>
-    <row r="17" spans="3:17" ht="16.5" customHeight="1">
+    <row r="17" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="35"/>
       <c r="D17" s="36"/>
       <c r="E17" s="37"/>
@@ -2993,7 +3067,7 @@
       <c r="P17" s="35"/>
       <c r="Q17" s="37"/>
     </row>
-    <row r="18" spans="3:17" ht="16.5" customHeight="1">
+    <row r="18" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="35"/>
       <c r="D18" s="36"/>
       <c r="E18" s="37"/>
@@ -3010,7 +3084,7 @@
       <c r="P18" s="35"/>
       <c r="Q18" s="37"/>
     </row>
-    <row r="19" spans="3:17" ht="16.5" customHeight="1">
+    <row r="19" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -3021,198 +3095,198 @@
       <c r="O19" s="41"/>
       <c r="P19" s="41"/>
     </row>
-    <row r="20" spans="3:17">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
       <c r="H20" s="2"/>
       <c r="O20" s="42"/>
       <c r="P20" s="42"/>
     </row>
-    <row r="21" spans="3:17">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
       <c r="H21" s="2"/>
       <c r="O21" s="42"/>
       <c r="P21" s="42"/>
     </row>
-    <row r="22" spans="3:17">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
       <c r="H22" s="2"/>
       <c r="O22" s="42"/>
       <c r="P22" s="42"/>
     </row>
-    <row r="23" spans="3:17">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O23" s="42"/>
       <c r="P23" s="42"/>
     </row>
-    <row r="24" spans="3:17">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O24" s="42"/>
       <c r="P24" s="42"/>
     </row>
-    <row r="25" spans="3:17">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O25" s="42"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="3:17">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O26" s="42"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="3:17">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O27" s="42"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="3:17">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O28" s="42"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="3:17">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O29" s="42"/>
       <c r="P29" s="42"/>
     </row>
-    <row r="30" spans="3:17">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O30" s="42"/>
       <c r="P30" s="42"/>
     </row>
-    <row r="31" spans="3:17">
+    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O31" s="42"/>
       <c r="P31" s="42"/>
     </row>
-    <row r="32" spans="3:17">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O32" s="42"/>
       <c r="P32" s="42"/>
     </row>
-    <row r="33" spans="15:16">
+    <row r="33" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O33" s="42"/>
       <c r="P33" s="42"/>
     </row>
-    <row r="34" spans="15:16">
+    <row r="34" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O34" s="42"/>
       <c r="P34" s="42"/>
     </row>
-    <row r="35" spans="15:16">
+    <row r="35" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O35" s="42"/>
       <c r="P35" s="42"/>
     </row>
-    <row r="36" spans="15:16">
+    <row r="36" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O36" s="42"/>
       <c r="P36" s="42"/>
     </row>
-    <row r="37" spans="15:16">
+    <row r="37" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O37" s="42"/>
       <c r="P37" s="42"/>
     </row>
-    <row r="38" spans="15:16">
+    <row r="38" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O38" s="42"/>
       <c r="P38" s="42"/>
     </row>
-    <row r="39" spans="15:16">
+    <row r="39" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O39" s="42"/>
       <c r="P39" s="42"/>
     </row>
-    <row r="40" spans="15:16">
+    <row r="40" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O40" s="42"/>
       <c r="P40" s="42"/>
     </row>
-    <row r="41" spans="15:16">
+    <row r="41" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O41" s="42"/>
       <c r="P41" s="42"/>
     </row>
-    <row r="42" spans="15:16">
+    <row r="42" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
     </row>
-    <row r="43" spans="15:16">
+    <row r="43" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O43" s="42"/>
       <c r="P43" s="42"/>
     </row>
-    <row r="44" spans="15:16">
+    <row r="44" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O44" s="42"/>
       <c r="P44" s="42"/>
     </row>
-    <row r="45" spans="15:16">
+    <row r="45" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O45" s="42"/>
       <c r="P45" s="42"/>
     </row>
-    <row r="46" spans="15:16">
+    <row r="46" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O46" s="42"/>
       <c r="P46" s="42"/>
     </row>
-    <row r="47" spans="15:16">
+    <row r="47" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O47" s="42"/>
       <c r="P47" s="42"/>
     </row>
-    <row r="48" spans="15:16">
+    <row r="48" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O48" s="42"/>
       <c r="P48" s="42"/>
     </row>
-    <row r="49" spans="15:16">
+    <row r="49" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O49" s="42"/>
       <c r="P49" s="42"/>
     </row>
-    <row r="50" spans="15:16">
+    <row r="50" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O50" s="42"/>
       <c r="P50" s="42"/>
     </row>
-    <row r="51" spans="15:16">
+    <row r="51" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O51" s="42"/>
       <c r="P51" s="42"/>
     </row>
-    <row r="52" spans="15:16">
+    <row r="52" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O52" s="42"/>
       <c r="P52" s="42"/>
     </row>
-    <row r="53" spans="15:16">
+    <row r="53" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O53" s="42"/>
       <c r="P53" s="42"/>
     </row>
-    <row r="54" spans="15:16">
+    <row r="54" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O54" s="42"/>
       <c r="P54" s="42"/>
     </row>
-    <row r="55" spans="15:16">
+    <row r="55" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O55" s="42"/>
       <c r="P55" s="42"/>
     </row>
-    <row r="56" spans="15:16">
+    <row r="56" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O56" s="42"/>
       <c r="P56" s="42"/>
     </row>
-    <row r="57" spans="15:16">
+    <row r="57" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O57" s="42"/>
       <c r="P57" s="42"/>
     </row>
-    <row r="58" spans="15:16">
+    <row r="58" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O58" s="42"/>
       <c r="P58" s="42"/>
     </row>
-    <row r="59" spans="15:16">
+    <row r="59" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O59" s="42"/>
       <c r="P59" s="42"/>
     </row>
-    <row r="60" spans="15:16">
+    <row r="60" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O60" s="42"/>
       <c r="P60" s="42"/>
     </row>
-    <row r="61" spans="15:16">
+    <row r="61" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O61" s="42"/>
       <c r="P61" s="42"/>
     </row>
-    <row r="62" spans="15:16">
+    <row r="62" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O62" s="42"/>
       <c r="P62" s="42"/>
     </row>
-    <row r="63" spans="15:16">
+    <row r="63" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O63" s="42"/>
       <c r="P63" s="42"/>
     </row>
-    <row r="64" spans="15:16">
+    <row r="64" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O64" s="42"/>
       <c r="P64" s="42"/>
     </row>
-    <row r="65" spans="15:16">
+    <row r="65" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O65" s="42"/>
       <c r="P65" s="42"/>
     </row>
-    <row r="66" spans="15:16">
+    <row r="66" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O66" s="42"/>
       <c r="P66" s="42"/>
     </row>
-    <row r="67" spans="15:16">
+    <row r="67" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O67" s="42"/>
       <c r="P67" s="42"/>
     </row>
@@ -3223,7 +3297,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J5:K22">
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"Parcelado/Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3238,7 +3312,7 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="C1:Q128"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" style="2" customWidth="1"/>
@@ -3253,9 +3327,9 @@
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
@@ -3264,23 +3338,23 @@
         <v>2</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L1" s="43"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1">
+    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="45">
         <f>SUM(L6:L266)</f>
-        <v>7733.0669285714293</v>
+        <v>8927.176928571429</v>
       </c>
       <c r="E2" s="32">
         <f>SUMIF($E$6:$E$266,E1,$M$6:$M$266)</f>
-        <v>5580.2910952380944</v>
+        <v>6360.0760952380942</v>
       </c>
       <c r="F2" s="32">
         <f>SUMIF($F$6:$F$266,F1,$M$6:$M$266)</f>
-        <v>1806.8058333333333</v>
+        <v>2342.6708333333331</v>
       </c>
       <c r="G2" s="32">
         <f>SUMIF($G$6:$G$266,G1,$M$6:$M$266)</f>
@@ -3290,62 +3364,62 @@
       <c r="L2" s="43"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="3:17">
+    <row r="3" spans="3:17" x14ac:dyDescent="0.25">
       <c r="L3" s="43"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="3:17">
+    <row r="4" spans="3:17" x14ac:dyDescent="0.25">
       <c r="M4" s="43"/>
     </row>
-    <row r="5" spans="3:17" ht="32.25" customHeight="1">
+    <row r="5" spans="3:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="33"/>
       <c r="D5" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="F5" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="G5" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="H5" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="34" t="s">
+      <c r="I5" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="33" t="s">
-        <v>40</v>
-      </c>
       <c r="J5" s="33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K5" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="M5" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="M5" s="34" t="s">
+      <c r="N5" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="N5" s="34" t="s">
+      <c r="O5" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="O5" s="33" t="s">
+      <c r="P5" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="33" t="s">
+      <c r="Q5" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="Q5" s="34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="3:17">
+    </row>
+    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C6" s="35"/>
       <c r="D6" s="36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E6" s="37" t="s">
         <v>1</v>
@@ -3362,10 +3436,10 @@
         <v>359</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L6" s="38">
         <f t="shared" ref="L6:L37" si="1">I6/N6</f>
@@ -3390,10 +3464,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="3:17">
+    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C7" s="35"/>
       <c r="D7" s="36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" s="37" t="s">
         <v>1</v>
@@ -3408,10 +3482,10 @@
         <v>258</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L7" s="38">
         <f t="shared" si="1"/>
@@ -3436,10 +3510,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="3:17">
+    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C8" s="35"/>
       <c r="D8" s="66" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="37" t="s">
         <v>1</v>
@@ -3454,10 +3528,10 @@
         <v>1909.3</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K8" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L8" s="38">
         <f t="shared" si="1"/>
@@ -3482,10 +3556,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="3:17">
+    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C9" s="35"/>
       <c r="D9" s="66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" s="37" t="s">
         <v>1</v>
@@ -3502,10 +3576,10 @@
         <v>725</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L9" s="38">
         <f t="shared" si="1"/>
@@ -3530,10 +3604,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="3:17">
+    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C10" s="35"/>
       <c r="D10" s="66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>1</v>
@@ -3548,10 +3622,10 @@
         <v>659</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L10" s="38">
         <f t="shared" si="1"/>
@@ -3576,10 +3650,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="3:17">
+    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C11" s="35"/>
       <c r="D11" s="66" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E11" s="37" t="s">
         <v>1</v>
@@ -3594,10 +3668,10 @@
         <v>2319.3000000000002</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L11" s="38">
         <f t="shared" si="1"/>
@@ -3622,10 +3696,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="3:17">
+    <row r="12" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C12" s="35"/>
       <c r="D12" s="66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" s="37" t="s">
         <v>1</v>
@@ -3640,10 +3714,10 @@
         <v>2000</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L12" s="38">
         <f t="shared" si="1"/>
@@ -3668,10 +3742,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="3:17">
+    <row r="13" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C13" s="35"/>
       <c r="D13" s="66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="37" t="s">
         <v>1</v>
@@ -3686,10 +3760,10 @@
         <v>372.43</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L13" s="38">
         <f t="shared" si="1"/>
@@ -3714,10 +3788,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="3:17">
+    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C14" s="35"/>
       <c r="D14" s="66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>1</v>
@@ -3733,10 +3807,10 @@
         <v>-773.04</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L14" s="38">
         <f t="shared" si="1"/>
@@ -3761,10 +3835,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="3:17">
+    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C15" s="35"/>
       <c r="D15" s="66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E15" s="37" t="s">
         <v>1</v>
@@ -3779,10 +3853,10 @@
         <v>531</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K15" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L15" s="38">
         <f t="shared" si="1"/>
@@ -3807,10 +3881,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="3:17">
+    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C16" s="35"/>
       <c r="D16" s="66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16" s="37"/>
       <c r="F16" s="37" t="s">
@@ -3825,10 +3899,10 @@
         <v>161.72999999999999</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L16" s="38">
         <f t="shared" si="1"/>
@@ -3853,10 +3927,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="3:17">
+    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C17" s="35"/>
       <c r="D17" s="66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" s="37" t="s">
         <v>1</v>
@@ -3871,10 +3945,10 @@
         <v>72</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K17" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L17" s="38">
         <f t="shared" si="1"/>
@@ -3899,10 +3973,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="3:17">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C18" s="35"/>
       <c r="D18" s="65" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18" s="37"/>
       <c r="F18" s="37" t="s">
@@ -3917,10 +3991,10 @@
         <v>973.02</v>
       </c>
       <c r="J18" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L18" s="38">
         <f t="shared" si="1"/>
@@ -3945,10 +4019,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="3:17">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C19" s="35"/>
       <c r="D19" s="65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E19" s="37" t="s">
         <v>1</v>
@@ -3963,10 +4037,10 @@
         <v>379</v>
       </c>
       <c r="J19" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K19" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L19" s="38">
         <f t="shared" si="1"/>
@@ -3991,10 +4065,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="3:17">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C20" s="35"/>
       <c r="D20" s="65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>1</v>
@@ -4009,10 +4083,10 @@
         <v>297</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L20" s="38">
         <f t="shared" si="1"/>
@@ -4037,10 +4111,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:17">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C21" s="35"/>
       <c r="D21" s="65" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E21" s="37" t="s">
         <v>1</v>
@@ -4055,10 +4129,10 @@
         <v>326.99</v>
       </c>
       <c r="J21" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L21" s="38">
         <f t="shared" si="1"/>
@@ -4083,10 +4157,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:17">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C22" s="35"/>
       <c r="D22" s="70" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>1</v>
@@ -4103,10 +4177,10 @@
         <v>209.94</v>
       </c>
       <c r="J22" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="K22" s="38" t="s">
         <v>51</v>
-      </c>
-      <c r="K22" s="38" t="s">
-        <v>52</v>
       </c>
       <c r="L22" s="38">
         <f t="shared" si="1"/>
@@ -4131,10 +4205,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:17">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C23" s="35"/>
       <c r="D23" s="70" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E23" s="37" t="s">
         <v>1</v>
@@ -4151,10 +4225,10 @@
         <v>249.5</v>
       </c>
       <c r="J23" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="K23" s="38" t="s">
         <v>51</v>
-      </c>
-      <c r="K23" s="38" t="s">
-        <v>52</v>
       </c>
       <c r="L23" s="38">
         <f t="shared" si="1"/>
@@ -4179,10 +4253,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="3:17">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C24" s="35"/>
       <c r="D24" s="70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" s="37" t="s">
         <v>1</v>
@@ -4199,10 +4273,10 @@
         <v>-209.94</v>
       </c>
       <c r="J24" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="K24" s="38" t="s">
         <v>51</v>
-      </c>
-      <c r="K24" s="38" t="s">
-        <v>52</v>
       </c>
       <c r="L24" s="38">
         <f t="shared" si="1"/>
@@ -4227,10 +4301,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="3:17">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C25" s="35"/>
       <c r="D25" s="46" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E25" s="37" t="s">
         <v>1</v>
@@ -4247,10 +4321,10 @@
         <v>506</v>
       </c>
       <c r="J25" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L25" s="38">
         <f t="shared" si="1"/>
@@ -4272,10 +4346,10 @@
       </c>
       <c r="Q25" s="37"/>
     </row>
-    <row r="26" spans="3:17">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C26" s="35"/>
       <c r="D26" s="46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>1</v>
@@ -4290,10 +4364,10 @@
         <v>399.9</v>
       </c>
       <c r="J26" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L26" s="38">
         <f t="shared" si="1"/>
@@ -4318,10 +4392,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:17">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C27" s="35"/>
       <c r="D27" s="46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E27" s="37" t="s">
         <v>1</v>
@@ -4336,10 +4410,10 @@
         <v>284</v>
       </c>
       <c r="J27" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L27" s="38">
         <f t="shared" si="1"/>
@@ -4364,10 +4438,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="3:17">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C28" s="35"/>
       <c r="D28" s="46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E28" s="37" t="s">
         <v>1</v>
@@ -4382,10 +4456,10 @@
         <v>500</v>
       </c>
       <c r="J28" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L28" s="38">
         <f t="shared" si="1"/>
@@ -4410,10 +4484,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="3:17">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C29" s="35"/>
       <c r="D29" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>1</v>
@@ -4428,10 +4502,10 @@
         <v>300</v>
       </c>
       <c r="J29" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L29" s="38">
         <f t="shared" si="1"/>
@@ -4456,10 +4530,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="3:17">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C30" s="35"/>
       <c r="D30" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>1</v>
@@ -4476,10 +4550,10 @@
         <v>1017.6</v>
       </c>
       <c r="J30" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L30" s="38">
         <f t="shared" si="1"/>
@@ -4504,10 +4578,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="3:17">
+    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C31" s="35"/>
       <c r="D31" s="46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E31" s="37" t="s">
         <v>1</v>
@@ -4522,10 +4596,10 @@
         <v>1900</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L31" s="38">
         <f t="shared" si="1"/>
@@ -4550,10 +4624,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="3:17">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C32" s="35"/>
       <c r="D32" s="46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E32" s="37" t="s">
         <v>1</v>
@@ -4568,10 +4642,10 @@
         <v>474.33</v>
       </c>
       <c r="J32" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K32" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L32" s="38">
         <f t="shared" si="1"/>
@@ -4596,10 +4670,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="3:17">
+    <row r="33" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C33" s="35"/>
       <c r="D33" s="46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E33" s="37" t="s">
         <v>1</v>
@@ -4614,10 +4688,10 @@
         <v>330</v>
       </c>
       <c r="J33" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L33" s="38">
         <f t="shared" si="1"/>
@@ -4642,10 +4716,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="3:17">
+    <row r="34" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C34" s="35"/>
       <c r="D34" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E34" s="37" t="s">
         <v>1</v>
@@ -4662,10 +4736,10 @@
         <v>1780</v>
       </c>
       <c r="J34" s="68" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K34" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L34" s="38">
         <f t="shared" si="1"/>
@@ -4690,10 +4764,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="3:17">
+    <row r="35" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C35" s="35"/>
       <c r="D35" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E35" s="37" t="s">
         <v>1</v>
@@ -4708,10 +4782,10 @@
         <v>286.39</v>
       </c>
       <c r="J35" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L35" s="38">
         <f t="shared" si="1"/>
@@ -4736,10 +4810,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="3:17">
+    <row r="36" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C36" s="35"/>
       <c r="D36" s="46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E36" s="37" t="s">
         <v>1</v>
@@ -4754,10 +4828,10 @@
         <v>1181.1400000000001</v>
       </c>
       <c r="J36" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L36" s="38">
         <f t="shared" si="1"/>
@@ -4782,10 +4856,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="3:17">
+    <row r="37" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C37" s="35"/>
       <c r="D37" s="46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E37" s="37" t="s">
         <v>1</v>
@@ -4802,10 +4876,10 @@
         <v>224.24</v>
       </c>
       <c r="J37" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L37" s="38">
         <f t="shared" si="1"/>
@@ -4830,12 +4904,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="3:17">
+    <row r="38" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C38" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" s="46" t="s">
         <v>95</v>
-      </c>
-      <c r="D38" s="46" t="s">
-        <v>96</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>1</v>
@@ -4850,10 +4924,10 @@
         <v>279</v>
       </c>
       <c r="J38" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K38" s="38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L38" s="38">
         <f t="shared" ref="L38:L69" si="7">I38/N38</f>
@@ -4878,10 +4952,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="3:17">
+    <row r="39" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C39" s="35"/>
       <c r="D39" s="36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E39" s="37" t="s">
         <v>1</v>
@@ -4898,10 +4972,10 @@
         <v>22.45</v>
       </c>
       <c r="J39" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K39" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L39" s="38">
         <f t="shared" si="7"/>
@@ -4924,10 +4998,10 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="3:17">
+    <row r="40" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C40" s="35"/>
       <c r="D40" s="46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E40" s="37" t="s">
         <v>1</v>
@@ -4944,10 +5018,10 @@
         <v>60</v>
       </c>
       <c r="J40" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L40" s="38">
         <f t="shared" si="7"/>
@@ -4970,10 +5044,10 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="3:17">
+    <row r="41" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C41" s="35"/>
       <c r="D41" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E41" s="37" t="s">
         <v>1</v>
@@ -4990,10 +5064,10 @@
         <v>395.54</v>
       </c>
       <c r="J41" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K41" s="37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L41" s="38">
         <f t="shared" si="7"/>
@@ -5016,10 +5090,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="3:17">
+    <row r="42" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C42" s="35"/>
       <c r="D42" s="36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E42" s="37" t="s">
         <v>1</v>
@@ -5036,10 +5110,10 @@
         <v>197</v>
       </c>
       <c r="J42" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L42" s="38">
         <f t="shared" si="7"/>
@@ -5062,10 +5136,10 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="3:17">
+    <row r="43" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C43" s="35"/>
       <c r="D43" s="46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E43" s="37" t="s">
         <v>1</v>
@@ -5082,10 +5156,10 @@
         <v>225</v>
       </c>
       <c r="J43" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K43" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L43" s="38">
         <f t="shared" si="7"/>
@@ -5108,10 +5182,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="3:17">
+    <row r="44" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C44" s="35"/>
       <c r="D44" s="36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E44" s="37" t="s">
         <v>1</v>
@@ -5128,10 +5202,10 @@
         <v>166.15</v>
       </c>
       <c r="J44" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L44" s="38">
         <f t="shared" si="7"/>
@@ -5154,10 +5228,10 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="3:17">
+    <row r="45" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C45" s="35"/>
       <c r="D45" s="36" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E45" s="37" t="s">
         <v>1</v>
@@ -5174,10 +5248,10 @@
         <v>19.899999999999999</v>
       </c>
       <c r="J45" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K45" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L45" s="38">
         <f t="shared" si="7"/>
@@ -5200,10 +5274,10 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="3:17">
+    <row r="46" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C46" s="35"/>
       <c r="D46" s="46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E46" s="37" t="s">
         <v>1</v>
@@ -5218,10 +5292,10 @@
         <v>284.05</v>
       </c>
       <c r="J46" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L46" s="38">
         <f t="shared" si="7"/>
@@ -5244,10 +5318,10 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="3:17">
+    <row r="47" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C47" s="35"/>
       <c r="D47" s="46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E47" s="37" t="s">
         <v>1</v>
@@ -5262,10 +5336,10 @@
         <v>110</v>
       </c>
       <c r="J47" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K47" s="38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L47" s="38">
         <f t="shared" si="7"/>
@@ -5288,10 +5362,10 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="3:17">
+    <row r="48" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C48" s="35"/>
       <c r="D48" s="46" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E48" s="37" t="s">
         <v>1</v>
@@ -5306,10 +5380,10 @@
         <v>118.4</v>
       </c>
       <c r="J48" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K48" s="38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L48" s="38">
         <f t="shared" si="7"/>
@@ -5329,10 +5403,10 @@
       </c>
       <c r="Q48" s="37"/>
     </row>
-    <row r="49" spans="3:17">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C49" s="35"/>
       <c r="D49" s="36" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E49" s="37" t="s">
         <v>1</v>
@@ -5347,10 +5421,10 @@
         <v>26.9</v>
       </c>
       <c r="J49" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K49" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L49" s="38">
         <f t="shared" si="7"/>
@@ -5373,10 +5447,10 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="3:17">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C50" s="35"/>
       <c r="D50" s="46" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E50" s="37" t="s">
         <v>1</v>
@@ -5391,10 +5465,10 @@
         <v>70</v>
       </c>
       <c r="J50" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K50" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L50" s="38">
         <f t="shared" si="7"/>
@@ -5414,10 +5488,10 @@
       </c>
       <c r="Q50" s="37"/>
     </row>
-    <row r="51" spans="3:17">
+    <row r="51" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C51" s="35"/>
       <c r="D51" s="67" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E51" s="37" t="s">
         <v>1</v>
@@ -5432,10 +5506,10 @@
         <v>426</v>
       </c>
       <c r="J51" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K51" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L51" s="38">
         <f t="shared" si="7"/>
@@ -5458,10 +5532,10 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="3:17">
+    <row r="52" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C52" s="35"/>
       <c r="D52" s="46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E52" s="37" t="s">
         <v>1</v>
@@ -5478,10 +5552,10 @@
         <v>-43</v>
       </c>
       <c r="J52" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K52" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L52" s="38">
         <f t="shared" si="7"/>
@@ -5504,10 +5578,10 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="3:17">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C53" s="35"/>
       <c r="D53" s="46" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E53" s="37" t="s">
         <v>1</v>
@@ -5524,10 +5598,10 @@
         <v>217.85</v>
       </c>
       <c r="J53" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K53" s="38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L53" s="38">
         <f t="shared" si="7"/>
@@ -5552,10 +5626,10 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="3:17">
+    <row r="54" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C54" s="35"/>
       <c r="D54" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E54" s="37" t="s">
         <v>1</v>
@@ -5570,10 +5644,10 @@
         <v>300</v>
       </c>
       <c r="J54" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K54" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L54" s="38">
         <f t="shared" si="7"/>
@@ -5598,10 +5672,10 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="3:17">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C55" s="35"/>
       <c r="D55" s="46" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E55" s="37" t="s">
         <v>1</v>
@@ -5617,10 +5691,10 @@
         <v>37.909999999999997</v>
       </c>
       <c r="J55" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K55" s="38" t="s">
         <v>119</v>
-      </c>
-      <c r="K55" s="38" t="s">
-        <v>120</v>
       </c>
       <c r="L55" s="38">
         <f t="shared" si="7"/>
@@ -5645,10 +5719,10 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="3:17">
+    <row r="56" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C56" s="35"/>
       <c r="D56" s="46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E56" s="37" t="s">
         <v>1</v>
@@ -5665,10 +5739,10 @@
         <v>66</v>
       </c>
       <c r="J56" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K56" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L56" s="38">
         <f t="shared" si="7"/>
@@ -5693,10 +5767,10 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="3:17">
+    <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="35"/>
       <c r="D57" s="46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E57" s="37" t="s">
         <v>1</v>
@@ -5713,10 +5787,10 @@
         <v>265</v>
       </c>
       <c r="J57" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K57" s="38" t="s">
         <v>119</v>
-      </c>
-      <c r="K57" s="38" t="s">
-        <v>120</v>
       </c>
       <c r="L57" s="38">
         <f t="shared" si="7"/>
@@ -5741,10 +5815,10 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="3:17">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C58" s="35"/>
       <c r="D58" s="36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E58" s="37" t="s">
         <v>1</v>
@@ -5760,10 +5834,10 @@
         <v>369</v>
       </c>
       <c r="J58" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K58" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L58" s="38">
         <f t="shared" si="7"/>
@@ -5788,10 +5862,10 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="3:17">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C59" s="35"/>
       <c r="D59" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E59" s="37" t="s">
         <v>1</v>
@@ -5808,10 +5882,10 @@
         <v>120</v>
       </c>
       <c r="J59" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K59" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L59" s="38">
         <f t="shared" si="7"/>
@@ -5836,10 +5910,10 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="3:17">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C60" s="35"/>
       <c r="D60" s="46" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E60" s="37" t="s">
         <v>1</v>
@@ -5854,10 +5928,10 @@
         <v>85</v>
       </c>
       <c r="J60" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K60" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L60" s="38">
         <f t="shared" si="7"/>
@@ -5882,10 +5956,10 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="3:17">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C61" s="35"/>
       <c r="D61" s="46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E61" s="37" t="s">
         <v>1</v>
@@ -5903,10 +5977,10 @@
         <v>85.786666666666676</v>
       </c>
       <c r="J61" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K61" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L61" s="38">
         <f t="shared" si="7"/>
@@ -5931,10 +6005,10 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="3:17">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C62" s="35"/>
       <c r="D62" s="46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
@@ -5948,10 +6022,10 @@
         <v>42.895000000000003</v>
       </c>
       <c r="J62" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K62" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L62" s="38">
         <f t="shared" si="7"/>
@@ -5976,10 +6050,10 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="3:17">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C63" s="35"/>
       <c r="D63" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E63" s="37" t="s">
         <v>1</v>
@@ -5996,10 +6070,10 @@
         <v>40</v>
       </c>
       <c r="J63" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K63" s="38" t="s">
         <v>119</v>
-      </c>
-      <c r="K63" s="38" t="s">
-        <v>120</v>
       </c>
       <c r="L63" s="38">
         <f t="shared" si="7"/>
@@ -6024,10 +6098,10 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="3:17">
+    <row r="64" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C64" s="35"/>
       <c r="D64" s="46" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E64" s="37"/>
       <c r="F64" s="37"/>
@@ -6040,10 +6114,10 @@
         <v>20</v>
       </c>
       <c r="J64" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K64" s="38" t="s">
         <v>119</v>
-      </c>
-      <c r="K64" s="38" t="s">
-        <v>120</v>
       </c>
       <c r="L64" s="38">
         <f t="shared" si="7"/>
@@ -6068,10 +6142,10 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="3:17">
+    <row r="65" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C65" s="35"/>
       <c r="D65" s="46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E65" s="37" t="s">
         <v>1</v>
@@ -6088,10 +6162,10 @@
         <v>56.42</v>
       </c>
       <c r="J65" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K65" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L65" s="38">
         <f t="shared" si="7"/>
@@ -6116,10 +6190,10 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="3:17">
+    <row r="66" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C66" s="35"/>
       <c r="D66" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E66" s="37" t="s">
         <v>1</v>
@@ -6134,10 +6208,10 @@
         <v>-338</v>
       </c>
       <c r="J66" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L66" s="38">
         <f t="shared" si="7"/>
@@ -6162,10 +6236,10 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="3:17">
+    <row r="67" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C67" s="35"/>
       <c r="D67" s="46" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E67" s="37" t="s">
         <v>1</v>
@@ -6180,10 +6254,10 @@
         <v>638</v>
       </c>
       <c r="J67" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K67" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L67" s="38">
         <f t="shared" si="7"/>
@@ -6208,10 +6282,10 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="3:17">
+    <row r="68" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C68" s="35"/>
       <c r="D68" s="46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E68" s="37" t="s">
         <v>1</v>
@@ -6226,10 +6300,10 @@
         <v>60</v>
       </c>
       <c r="J68" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K68" s="38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L68" s="38">
         <f t="shared" si="7"/>
@@ -6254,10 +6328,10 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="3:17">
+    <row r="69" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C69" s="35"/>
       <c r="D69" s="46" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E69" s="37" t="s">
         <v>1</v>
@@ -6274,10 +6348,10 @@
         <v>91.5</v>
       </c>
       <c r="J69" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K69" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L69" s="38">
         <f t="shared" si="7"/>
@@ -6302,10 +6376,10 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="3:17">
+    <row r="70" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C70" s="35"/>
       <c r="D70" s="46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E70" s="37" t="s">
         <v>1</v>
@@ -6320,10 +6394,10 @@
         <v>-51.5</v>
       </c>
       <c r="J70" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L70" s="38">
         <f t="shared" ref="L70:L99" si="12">I70/N70</f>
@@ -6348,10 +6422,10 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="3:17">
+    <row r="71" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C71" s="35"/>
       <c r="D71" s="46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E71" s="37"/>
       <c r="F71" s="37" t="s">
@@ -6366,10 +6440,10 @@
         <v>-40</v>
       </c>
       <c r="J71" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K71" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L71" s="38">
         <f t="shared" si="12"/>
@@ -6394,15 +6468,15 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="3:17">
+    <row r="72" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C72" s="35"/>
       <c r="D72" s="46" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E72" s="37"/>
       <c r="F72" s="37"/>
       <c r="G72" s="37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H72" s="37">
         <f t="shared" si="11"/>
@@ -6412,10 +6486,10 @@
         <v>53</v>
       </c>
       <c r="J72" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L72" s="38">
         <f t="shared" si="12"/>
@@ -6440,10 +6514,10 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="3:17">
+    <row r="73" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C73" s="35"/>
       <c r="D73" s="46" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E73" s="37"/>
       <c r="F73" s="37" t="s">
@@ -6458,10 +6532,10 @@
         <v>35</v>
       </c>
       <c r="J73" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K73" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L73" s="38">
         <f t="shared" si="12"/>
@@ -6486,10 +6560,10 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="3:17">
+    <row r="74" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C74" s="35"/>
       <c r="D74" s="46" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E74" s="37" t="s">
         <v>1</v>
@@ -6506,10 +6580,10 @@
         <v>66</v>
       </c>
       <c r="J74" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K74" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L74" s="38">
         <f t="shared" si="12"/>
@@ -6534,10 +6608,10 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="3:17">
+    <row r="75" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C75" s="35"/>
       <c r="D75" s="46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E75" s="37" t="s">
         <v>1</v>
@@ -6552,10 +6626,10 @@
         <v>-33</v>
       </c>
       <c r="J75" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K75" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L75" s="38">
         <f t="shared" si="12"/>
@@ -6580,10 +6654,10 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="3:17">
+    <row r="76" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C76" s="35"/>
       <c r="D76" s="46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E76" s="37" t="s">
         <v>1</v>
@@ -6599,10 +6673,10 @@
         <v>75.806666666666658</v>
       </c>
       <c r="J76" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K76" s="38" t="s">
         <v>119</v>
-      </c>
-      <c r="K76" s="38" t="s">
-        <v>120</v>
       </c>
       <c r="L76" s="38">
         <f t="shared" si="12"/>
@@ -6627,10 +6701,10 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="3:17">
+    <row r="77" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C77" s="35"/>
       <c r="D77" s="46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E77" s="37"/>
       <c r="F77" s="37"/>
@@ -6643,10 +6717,10 @@
         <v>37.9</v>
       </c>
       <c r="J77" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K77" s="38" t="s">
         <v>119</v>
-      </c>
-      <c r="K77" s="38" t="s">
-        <v>120</v>
       </c>
       <c r="L77" s="38">
         <f t="shared" si="12"/>
@@ -6671,10 +6745,10 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="3:17">
+    <row r="78" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C78" s="35"/>
       <c r="D78" s="46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E78" s="37" t="s">
         <v>1</v>
@@ -6689,10 +6763,10 @@
         <v>-66</v>
       </c>
       <c r="J78" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K78" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L78" s="38">
         <f t="shared" si="12"/>
@@ -6717,10 +6791,10 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="3:17">
+    <row r="79" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C79" s="35"/>
       <c r="D79" s="46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E79" s="37" t="s">
         <v>1</v>
@@ -6737,10 +6811,10 @@
         <v>112</v>
       </c>
       <c r="J79" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K79" s="38" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L79" s="38">
         <f t="shared" si="12"/>
@@ -6765,10 +6839,10 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="3:17">
+    <row r="80" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C80" s="35"/>
       <c r="D80" s="46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E80" s="37" t="s">
         <v>1</v>
@@ -6786,10 +6860,10 @@
         <v>75.844999999999999</v>
       </c>
       <c r="J80" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K80" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L80" s="38">
         <f t="shared" si="12"/>
@@ -6814,10 +6888,10 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="3:17">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C81" s="35"/>
       <c r="D81" s="46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E81" s="37" t="s">
         <v>1</v>
@@ -6832,10 +6906,10 @@
         <v>-45</v>
       </c>
       <c r="J81" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K81" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L81" s="38">
         <f t="shared" si="12"/>
@@ -6860,15 +6934,15 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="3:17">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C82" s="35"/>
       <c r="D82" s="46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E82" s="37"/>
       <c r="F82" s="37"/>
       <c r="G82" s="37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H82" s="37">
         <f t="shared" si="11"/>
@@ -6879,10 +6953,10 @@
         <v>75.844999999999999</v>
       </c>
       <c r="J82" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K82" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L82" s="38">
         <f t="shared" si="12"/>
@@ -6907,10 +6981,10 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="3:17">
+    <row r="83" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C83" s="35"/>
       <c r="D83" s="46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E83" s="37" t="s">
         <v>1</v>
@@ -6925,10 +6999,10 @@
         <v>88.1</v>
       </c>
       <c r="J83" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K83" s="38" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L83" s="38">
         <f t="shared" si="12"/>
@@ -6953,10 +7027,10 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="3:17">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C84" s="35"/>
       <c r="D84" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E84" s="37" t="s">
         <v>1</v>
@@ -6973,10 +7047,10 @@
         <v>47.81</v>
       </c>
       <c r="J84" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K84" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L84" s="38">
         <f t="shared" si="12"/>
@@ -7001,10 +7075,10 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="3:17">
+    <row r="85" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C85" s="35"/>
       <c r="D85" s="46" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E85" s="37" t="s">
         <v>1</v>
@@ -7021,10 +7095,10 @@
         <v>265</v>
       </c>
       <c r="J85" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K85" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L85" s="38">
         <f t="shared" si="12"/>
@@ -7049,10 +7123,10 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="3:17">
+    <row r="86" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C86" s="35"/>
       <c r="D86" s="46" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E86" s="37" t="s">
         <v>1</v>
@@ -7067,10 +7141,10 @@
         <v>-130</v>
       </c>
       <c r="J86" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K86" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L86" s="38">
         <f t="shared" si="12"/>
@@ -7095,10 +7169,10 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="3:17">
+    <row r="87" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C87" s="35"/>
       <c r="D87" s="46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E87" s="37" t="s">
         <v>1</v>
@@ -7115,10 +7189,10 @@
         <v>10</v>
       </c>
       <c r="J87" s="38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K87" s="38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L87" s="38">
         <f t="shared" si="12"/>
@@ -7143,10 +7217,10 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="3:17">
+    <row r="88" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C88" s="35"/>
       <c r="D88" s="46" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E88" s="37" t="s">
         <v>1</v>
@@ -7163,10 +7237,10 @@
         <v>64</v>
       </c>
       <c r="J88" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K88" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L88" s="38">
         <f t="shared" si="12"/>
@@ -7191,10 +7265,10 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="3:17">
+    <row r="89" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C89" s="35"/>
       <c r="D89" s="46" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E89" s="37" t="s">
         <v>1</v>
@@ -7211,10 +7285,10 @@
         <v>97</v>
       </c>
       <c r="J89" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K89" s="38" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L89" s="38">
         <f t="shared" si="12"/>
@@ -7239,10 +7313,10 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="3:17">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C90" s="35"/>
       <c r="D90" s="46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E90" s="37" t="s">
         <v>1</v>
@@ -7257,10 +7331,10 @@
         <v>43.39</v>
       </c>
       <c r="J90" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K90" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L90" s="38">
         <f t="shared" si="12"/>
@@ -7285,10 +7359,10 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="3:17">
+    <row r="91" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C91" s="35"/>
       <c r="D91" s="46" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E91" s="37" t="s">
         <v>1</v>
@@ -7303,10 +7377,10 @@
         <v>-45</v>
       </c>
       <c r="J91" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K91" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L91" s="38">
         <f t="shared" si="12"/>
@@ -7331,39 +7405,45 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="3:17">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C92" s="35"/>
       <c r="D92" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="E92" s="37"/>
-      <c r="F92" s="37"/>
+        <v>156</v>
+      </c>
+      <c r="E92" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F92" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G92" s="37"/>
       <c r="H92" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I92" s="38">
         <v>116.33</v>
       </c>
       <c r="J92" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K92" s="38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L92" s="38">
         <f t="shared" si="12"/>
         <v>116.33</v>
       </c>
-      <c r="M92" s="38" t="str">
+      <c r="M92" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>58.164999999999999</v>
       </c>
       <c r="N92" s="39">
         <v>1</v>
       </c>
-      <c r="O92" s="35"/>
+      <c r="O92" s="64">
+        <v>46298</v>
+      </c>
       <c r="P92" s="35" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -7373,10 +7453,10 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="3:17">
+    <row r="93" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C93" s="35"/>
       <c r="D93" s="46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E93" s="37"/>
       <c r="F93" s="37"/>
@@ -7389,10 +7469,10 @@
         <v>116.33</v>
       </c>
       <c r="J93" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K93" s="38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L93" s="38">
         <f t="shared" si="12"/>
@@ -7405,7 +7485,9 @@
       <c r="N93" s="39">
         <v>1</v>
       </c>
-      <c r="O93" s="35"/>
+      <c r="O93" s="64">
+        <v>46298</v>
+      </c>
       <c r="P93" s="35" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -7415,10 +7497,10 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="3:17">
+    <row r="94" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C94" s="35"/>
       <c r="D94" s="46" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E94" s="37"/>
       <c r="F94" s="37"/>
@@ -7431,10 +7513,10 @@
         <v>-116.33</v>
       </c>
       <c r="J94" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K94" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L94" s="38">
         <f t="shared" si="12"/>
@@ -7447,7 +7529,9 @@
       <c r="N94" s="39">
         <v>1</v>
       </c>
-      <c r="O94" s="35"/>
+      <c r="O94" s="64">
+        <v>46298</v>
+      </c>
       <c r="P94" s="35" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -7457,10 +7541,10 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="3:17">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C95" s="35"/>
       <c r="D95" s="46" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E95" s="37" t="s">
         <v>1</v>
@@ -7475,10 +7559,10 @@
         <v>60</v>
       </c>
       <c r="J95" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K95" s="38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L95" s="38">
         <f t="shared" si="12"/>
@@ -7491,7 +7575,9 @@
       <c r="N95" s="39">
         <v>1</v>
       </c>
-      <c r="O95" s="35"/>
+      <c r="O95" s="64">
+        <v>46298</v>
+      </c>
       <c r="P95" s="35" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -7501,10 +7587,10 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="3:17">
+    <row r="96" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C96" s="35"/>
       <c r="D96" s="46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E96" s="37" t="s">
         <v>1</v>
@@ -7519,10 +7605,10 @@
         <v>64.989999999999995</v>
       </c>
       <c r="J96" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K96" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L96" s="38">
         <f t="shared" si="12"/>
@@ -7535,7 +7621,9 @@
       <c r="N96" s="39">
         <v>1</v>
       </c>
-      <c r="O96" s="35"/>
+      <c r="O96" s="64">
+        <v>46298</v>
+      </c>
       <c r="P96" s="35" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -7545,10 +7633,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="3:17">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C97" s="35"/>
       <c r="D97" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E97" s="37" t="s">
         <v>1</v>
@@ -7563,10 +7651,10 @@
         <v>55</v>
       </c>
       <c r="J97" s="38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K97" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L97" s="38">
         <f t="shared" si="12"/>
@@ -7579,7 +7667,9 @@
       <c r="N97" s="39">
         <v>1</v>
       </c>
-      <c r="O97" s="35"/>
+      <c r="O97" s="64">
+        <v>46298</v>
+      </c>
       <c r="P97" s="35" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -7589,60 +7679,86 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="3:17">
+    <row r="98" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C98" s="35"/>
-      <c r="D98" s="46"/>
-      <c r="E98" s="37"/>
-      <c r="F98" s="37"/>
+      <c r="D98" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="E98" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F98" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G98" s="37"/>
       <c r="H98" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I98" s="38"/>
-      <c r="J98" s="38"/>
-      <c r="K98" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I98" s="38">
+        <v>663</v>
+      </c>
+      <c r="J98" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="K98" s="38" t="s">
+        <v>61</v>
+      </c>
       <c r="L98" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M98" s="38" t="str">
+        <v>110.5</v>
+      </c>
+      <c r="M98" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>55.25</v>
       </c>
       <c r="N98" s="39">
-        <v>1</v>
-      </c>
-      <c r="O98" s="35"/>
-      <c r="P98" s="35" t="str">
+        <v>6</v>
+      </c>
+      <c r="O98" s="64">
+        <v>46298</v>
+      </c>
+      <c r="P98" s="35">
         <f t="shared" si="14"/>
-        <v/>
+        <v>46449</v>
       </c>
       <c r="Q98" s="37" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="99" spans="3:17">
+    <row r="99" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C99" s="35"/>
-      <c r="D99" s="46"/>
-      <c r="E99" s="37"/>
-      <c r="F99" s="37"/>
+      <c r="D99" s="46" t="s">
+        <v>164</v>
+      </c>
+      <c r="E99" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F99" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G99" s="37"/>
       <c r="H99" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I99" s="38"/>
-      <c r="J99" s="38"/>
-      <c r="K99" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I99" s="38">
+        <v>320</v>
+      </c>
+      <c r="J99" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K99" s="38" t="s">
+        <v>121</v>
+      </c>
       <c r="L99" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M99" s="38" t="str">
+        <v>320</v>
+      </c>
+      <c r="M99" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>160</v>
       </c>
       <c r="N99" s="39">
         <v>1</v>
@@ -7657,26 +7773,36 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="3:17">
+    <row r="100" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C100" s="35"/>
-      <c r="D100" s="46"/>
-      <c r="E100" s="37"/>
+      <c r="D100" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="E100" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F100" s="37"/>
       <c r="G100" s="37"/>
       <c r="H100" s="37">
         <f t="shared" ref="H100:H128" si="16">COUNTA(E100:G100)</f>
-        <v>0</v>
-      </c>
-      <c r="I100" s="38"/>
-      <c r="J100" s="38"/>
-      <c r="K100" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I100" s="38">
+        <v>72</v>
+      </c>
+      <c r="J100" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K100" s="38" t="s">
+        <v>121</v>
+      </c>
       <c r="L100" s="38">
         <f t="shared" ref="L100:L128" si="17">I100/N100</f>
-        <v>0</v>
-      </c>
-      <c r="M100" s="38" t="str">
+        <v>72</v>
+      </c>
+      <c r="M100" s="38">
         <f t="shared" ref="M100:M128" si="18">IFERROR(L100/H100,"")</f>
-        <v/>
+        <v>72</v>
       </c>
       <c r="N100" s="39">
         <v>1</v>
@@ -7691,26 +7817,36 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C101" s="35"/>
-      <c r="D101" s="46"/>
-      <c r="E101" s="37"/>
+      <c r="D101" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="E101" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F101" s="37"/>
       <c r="G101" s="37"/>
       <c r="H101" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I101" s="38"/>
-      <c r="J101" s="38"/>
-      <c r="K101" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I101" s="38">
+        <v>25</v>
+      </c>
+      <c r="J101" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K101" s="38" t="s">
+        <v>119</v>
+      </c>
       <c r="L101" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M101" s="38" t="str">
+        <v>25</v>
+      </c>
+      <c r="M101" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>25</v>
       </c>
       <c r="N101" s="39">
         <v>1</v>
@@ -7725,9 +7861,11 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C102" s="35"/>
-      <c r="D102" s="46"/>
+      <c r="D102" s="46" t="s">
+        <v>167</v>
+      </c>
       <c r="E102" s="37"/>
       <c r="F102" s="37"/>
       <c r="G102" s="37"/>
@@ -7735,12 +7873,18 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I102" s="38"/>
-      <c r="J102" s="38"/>
-      <c r="K102" s="38"/>
+      <c r="I102" s="38">
+        <v>273.5</v>
+      </c>
+      <c r="J102" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K102" s="38" t="s">
+        <v>121</v>
+      </c>
       <c r="L102" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>273.5</v>
       </c>
       <c r="M102" s="38" t="str">
         <f t="shared" si="18"/>
@@ -7759,26 +7903,38 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C103" s="35"/>
-      <c r="D103" s="46"/>
-      <c r="E103" s="37"/>
-      <c r="F103" s="37"/>
+      <c r="D103" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="E103" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F103" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G103" s="37"/>
       <c r="H103" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I103" s="38"/>
-      <c r="J103" s="38"/>
-      <c r="K103" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I103" s="38">
+        <v>305</v>
+      </c>
+      <c r="J103" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K103" s="38" t="s">
+        <v>169</v>
+      </c>
       <c r="L103" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M103" s="38" t="str">
+        <v>305</v>
+      </c>
+      <c r="M103" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>152.5</v>
       </c>
       <c r="N103" s="39">
         <v>1</v>
@@ -7793,9 +7949,11 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C104" s="35"/>
-      <c r="D104" s="46"/>
+      <c r="D104" s="46" t="s">
+        <v>170</v>
+      </c>
       <c r="E104" s="37"/>
       <c r="F104" s="37"/>
       <c r="G104" s="37"/>
@@ -7803,12 +7961,18 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I104" s="38"/>
-      <c r="J104" s="38"/>
-      <c r="K104" s="38"/>
+      <c r="I104" s="38">
+        <v>-273.5</v>
+      </c>
+      <c r="J104" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="K104" s="38" t="s">
+        <v>114</v>
+      </c>
       <c r="L104" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-273.5</v>
       </c>
       <c r="M104" s="38" t="str">
         <f t="shared" si="18"/>
@@ -7827,26 +7991,37 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C105" s="35"/>
-      <c r="D105" s="46"/>
-      <c r="E105" s="37"/>
+      <c r="D105" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="E105" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F105" s="37"/>
       <c r="G105" s="37"/>
       <c r="H105" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I105" s="38"/>
-      <c r="J105" s="38"/>
-      <c r="K105" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I105" s="38">
+        <f>-80-338+273.5</f>
+        <v>-144.5</v>
+      </c>
+      <c r="J105" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="K105" s="38" t="s">
+        <v>114</v>
+      </c>
       <c r="L105" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M105" s="38" t="str">
+        <v>-144.5</v>
+      </c>
+      <c r="M105" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>-144.5</v>
       </c>
       <c r="N105" s="39">
         <v>1</v>
@@ -7861,26 +8036,38 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="3:17">
+    <row r="106" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C106" s="35"/>
-      <c r="D106" s="46"/>
-      <c r="E106" s="37"/>
-      <c r="F106" s="37"/>
+      <c r="D106" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="E106" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F106" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G106" s="37"/>
       <c r="H106" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I106" s="38"/>
-      <c r="J106" s="38"/>
-      <c r="K106" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I106" s="38">
+        <v>219.9</v>
+      </c>
+      <c r="J106" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K106" s="38" t="s">
+        <v>157</v>
+      </c>
       <c r="L106" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M106" s="38" t="str">
+        <v>219.9</v>
+      </c>
+      <c r="M106" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>109.95</v>
       </c>
       <c r="N106" s="39">
         <v>1</v>
@@ -7895,26 +8082,36 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="3:17">
+    <row r="107" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C107" s="35"/>
-      <c r="D107" s="46"/>
-      <c r="E107" s="37"/>
+      <c r="D107" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="E107" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F107" s="37"/>
       <c r="G107" s="37"/>
       <c r="H107" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I107" s="38"/>
-      <c r="J107" s="38"/>
-      <c r="K107" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I107" s="38">
+        <v>95</v>
+      </c>
+      <c r="J107" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K107" s="38" t="s">
+        <v>157</v>
+      </c>
       <c r="L107" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M107" s="38" t="str">
+        <v>95</v>
+      </c>
+      <c r="M107" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>95</v>
       </c>
       <c r="N107" s="39">
         <v>1</v>
@@ -7929,26 +8126,36 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="3:17">
+    <row r="108" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C108" s="35"/>
-      <c r="D108" s="46"/>
-      <c r="E108" s="37"/>
+      <c r="D108" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E108" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F108" s="37"/>
       <c r="G108" s="37"/>
       <c r="H108" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I108" s="38"/>
-      <c r="J108" s="38"/>
-      <c r="K108" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I108" s="38">
+        <v>65</v>
+      </c>
+      <c r="J108" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K108" s="38" t="s">
+        <v>121</v>
+      </c>
       <c r="L108" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="38" t="str">
+        <v>65</v>
+      </c>
+      <c r="M108" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>65</v>
       </c>
       <c r="N108" s="39">
         <v>1</v>
@@ -7963,26 +8170,36 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="3:17">
+    <row r="109" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C109" s="35"/>
-      <c r="D109" s="46"/>
-      <c r="E109" s="37"/>
+      <c r="D109" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="E109" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F109" s="37"/>
       <c r="G109" s="37"/>
       <c r="H109" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I109" s="38"/>
-      <c r="J109" s="38"/>
-      <c r="K109" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I109" s="38">
+        <v>85.24</v>
+      </c>
+      <c r="J109" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K109" s="38" t="s">
+        <v>157</v>
+      </c>
       <c r="L109" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M109" s="38" t="str">
+        <v>85.24</v>
+      </c>
+      <c r="M109" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>85.24</v>
       </c>
       <c r="N109" s="39">
         <v>1</v>
@@ -7997,26 +8214,36 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="3:17">
+    <row r="110" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C110" s="35"/>
-      <c r="D110" s="46"/>
-      <c r="E110" s="37"/>
+      <c r="D110" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="E110" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F110" s="37"/>
       <c r="G110" s="37"/>
       <c r="H110" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I110" s="38"/>
-      <c r="J110" s="38"/>
-      <c r="K110" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I110" s="38">
+        <v>56.18</v>
+      </c>
+      <c r="J110" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K110" s="38" t="s">
+        <v>70</v>
+      </c>
       <c r="L110" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M110" s="38" t="str">
+        <v>56.18</v>
+      </c>
+      <c r="M110" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>56.18</v>
       </c>
       <c r="N110" s="39">
         <v>1</v>
@@ -8031,9 +8258,11 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="3:17">
+    <row r="111" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C111" s="35"/>
-      <c r="D111" s="46"/>
+      <c r="D111" s="46" t="s">
+        <v>176</v>
+      </c>
       <c r="E111" s="37"/>
       <c r="F111" s="37"/>
       <c r="G111" s="37"/>
@@ -8041,12 +8270,18 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I111" s="38"/>
-      <c r="J111" s="38"/>
-      <c r="K111" s="38"/>
+      <c r="I111" s="38">
+        <v>235.73</v>
+      </c>
+      <c r="J111" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K111" s="38" t="s">
+        <v>121</v>
+      </c>
       <c r="L111" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>235.73</v>
       </c>
       <c r="M111" s="38" t="str">
         <f t="shared" si="18"/>
@@ -8065,9 +8300,11 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="3:17">
+    <row r="112" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C112" s="35"/>
-      <c r="D112" s="46"/>
+      <c r="D112" s="46" t="s">
+        <v>177</v>
+      </c>
       <c r="E112" s="37"/>
       <c r="F112" s="37"/>
       <c r="G112" s="37"/>
@@ -8075,12 +8312,18 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I112" s="38"/>
-      <c r="J112" s="38"/>
-      <c r="K112" s="38"/>
+      <c r="I112" s="38">
+        <v>208.52</v>
+      </c>
+      <c r="J112" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K112" s="38" t="s">
+        <v>144</v>
+      </c>
       <c r="L112" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>208.52</v>
       </c>
       <c r="M112" s="38" t="str">
         <f t="shared" si="18"/>
@@ -8099,9 +8342,11 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="3:17">
+    <row r="113" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C113" s="35"/>
-      <c r="D113" s="46"/>
+      <c r="D113" s="36" t="s">
+        <v>178</v>
+      </c>
       <c r="E113" s="37"/>
       <c r="F113" s="37"/>
       <c r="G113" s="37"/>
@@ -8109,12 +8354,18 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I113" s="38"/>
-      <c r="J113" s="38"/>
-      <c r="K113" s="38"/>
+      <c r="I113" s="38">
+        <v>-450</v>
+      </c>
+      <c r="J113" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="K113" s="38" t="s">
+        <v>114</v>
+      </c>
       <c r="L113" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-450</v>
       </c>
       <c r="M113" s="38" t="str">
         <f t="shared" si="18"/>
@@ -8133,9 +8384,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="3:17">
+    <row r="114" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C114" s="35"/>
-      <c r="D114" s="46"/>
+      <c r="D114" s="46" t="s">
+        <v>293</v>
+      </c>
       <c r="E114" s="37"/>
       <c r="F114" s="37"/>
       <c r="G114" s="37"/>
@@ -8143,12 +8396,18 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I114" s="38"/>
-      <c r="J114" s="38"/>
-      <c r="K114" s="38"/>
+      <c r="I114" s="38">
+        <v>276.54000000000002</v>
+      </c>
+      <c r="J114" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K114" s="38" t="s">
+        <v>121</v>
+      </c>
       <c r="L114" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>276.54000000000002</v>
       </c>
       <c r="M114" s="38" t="str">
         <f t="shared" si="18"/>
@@ -8167,26 +8426,36 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="3:17">
+    <row r="115" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C115" s="35"/>
-      <c r="D115" s="46"/>
-      <c r="E115" s="37"/>
+      <c r="D115" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="E115" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F115" s="37"/>
       <c r="G115" s="37"/>
       <c r="H115" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I115" s="38"/>
-      <c r="J115" s="38"/>
-      <c r="K115" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I115" s="38">
+        <v>150</v>
+      </c>
+      <c r="J115" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="K115" s="38" t="s">
+        <v>61</v>
+      </c>
       <c r="L115" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M115" s="38" t="str">
+        <v>150</v>
+      </c>
+      <c r="M115" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>150</v>
       </c>
       <c r="N115" s="39">
         <v>1</v>
@@ -8201,9 +8470,11 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="3:17">
+    <row r="116" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C116" s="35"/>
-      <c r="D116" s="46"/>
+      <c r="D116" s="46" t="s">
+        <v>295</v>
+      </c>
       <c r="E116" s="37"/>
       <c r="F116" s="37"/>
       <c r="G116" s="37"/>
@@ -8211,12 +8482,18 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I116" s="38"/>
-      <c r="J116" s="38"/>
-      <c r="K116" s="38"/>
+      <c r="I116" s="38">
+        <v>-276</v>
+      </c>
+      <c r="J116" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="K116" s="38" t="s">
+        <v>114</v>
+      </c>
       <c r="L116" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-276</v>
       </c>
       <c r="M116" s="38" t="str">
         <f t="shared" si="18"/>
@@ -8235,26 +8512,36 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="3:17">
+    <row r="117" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C117" s="35"/>
-      <c r="D117" s="46"/>
-      <c r="E117" s="37"/>
+      <c r="D117" s="36" t="s">
+        <v>296</v>
+      </c>
+      <c r="E117" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F117" s="37"/>
       <c r="G117" s="37"/>
       <c r="H117" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I117" s="38"/>
-      <c r="J117" s="38"/>
-      <c r="K117" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I117" s="38">
+        <v>-160</v>
+      </c>
+      <c r="J117" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="K117" s="38" t="s">
+        <v>114</v>
+      </c>
       <c r="L117" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M117" s="38" t="str">
+        <v>-160</v>
+      </c>
+      <c r="M117" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>-160</v>
       </c>
       <c r="N117" s="39">
         <v>1</v>
@@ -8269,7 +8556,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="3:17">
+    <row r="118" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C118" s="35"/>
       <c r="D118" s="46"/>
       <c r="E118" s="37"/>
@@ -8303,7 +8590,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="3:17">
+    <row r="119" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C119" s="35"/>
       <c r="D119" s="46"/>
       <c r="E119" s="37"/>
@@ -8337,7 +8624,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="3:17">
+    <row r="120" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C120" s="35"/>
       <c r="D120" s="46"/>
       <c r="E120" s="37"/>
@@ -8371,7 +8658,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="3:17">
+    <row r="121" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C121" s="35"/>
       <c r="D121" s="46"/>
       <c r="E121" s="37"/>
@@ -8405,7 +8692,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="3:17">
+    <row r="122" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C122" s="35"/>
       <c r="D122" s="46"/>
       <c r="E122" s="37"/>
@@ -8439,7 +8726,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="3:17">
+    <row r="123" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C123" s="35"/>
       <c r="D123" s="46"/>
       <c r="E123" s="37"/>
@@ -8473,7 +8760,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="3:17">
+    <row r="124" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C124" s="35"/>
       <c r="D124" s="46"/>
       <c r="E124" s="37"/>
@@ -8507,7 +8794,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="3:17">
+    <row r="125" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C125" s="35"/>
       <c r="D125" s="46"/>
       <c r="E125" s="37"/>
@@ -8541,7 +8828,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="3:17">
+    <row r="126" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C126" s="35"/>
       <c r="D126" s="46"/>
       <c r="E126" s="37"/>
@@ -8575,7 +8862,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="3:17">
+    <row r="127" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C127" s="35"/>
       <c r="D127" s="46"/>
       <c r="E127" s="37"/>
@@ -8609,7 +8896,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="3:17">
+    <row r="128" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C128" s="35"/>
       <c r="D128" s="46"/>
       <c r="E128" s="37"/>
@@ -8649,73 +8936,88 @@
       <sortCondition ref="P5:P51"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="I98:I128 I6:I96">
-    <cfRule type="cellIs" dxfId="29" priority="27" operator="lessThan">
+  <conditionalFormatting sqref="I6:I96 I98:I128">
+    <cfRule type="cellIs" dxfId="30" priority="30" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J128">
-    <cfRule type="cellIs" dxfId="28" priority="26" operator="equal">
+  <conditionalFormatting sqref="I97">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J98:K128 I97:K97 J6:K96">
-    <cfRule type="cellIs" dxfId="27" priority="20" operator="equal">
+  <conditionalFormatting sqref="J6:J128">
+    <cfRule type="cellIs" dxfId="28" priority="29" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6:K96 I97:K97 J98:K128">
+    <cfRule type="cellIs" dxfId="27" priority="23" operator="equal">
       <formula>"Parcelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K50">
-    <cfRule type="cellIs" dxfId="26" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="22" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52">
-    <cfRule type="cellIs" dxfId="25" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="14" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K66">
-    <cfRule type="cellIs" dxfId="24" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="13" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K70:K71">
-    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="11" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K75">
-    <cfRule type="cellIs" dxfId="22" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="10" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78">
-    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="9" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K81">
-    <cfRule type="cellIs" dxfId="20" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K86">
-    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="7" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K91">
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K94">
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I97">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+  <conditionalFormatting sqref="K104:K105">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K113">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K116:K117">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8727,7 +9029,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:R20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="36.5703125" customWidth="1"/>
@@ -8740,45 +9042,45 @@
     <col min="18" max="18" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="30" customHeight="1">
+    <row r="2" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="G2" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="H2" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="I2" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="33" t="s">
-        <v>40</v>
-      </c>
       <c r="J2" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="L2" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="34" t="s">
+      <c r="M2" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="33" t="s">
+      <c r="N2" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="33" t="s">
+      <c r="O2" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="2:18" ht="16.5" customHeight="1">
+    </row>
+    <row r="3" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="54" t="s">
         <v>23</v>
       </c>
@@ -8816,9 +9118,9 @@
       </c>
       <c r="R3" s="16"/>
     </row>
-    <row r="4" spans="2:18" ht="16.5" customHeight="1">
+    <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="55" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="E4" s="56" t="s">
         <v>1</v>
@@ -8854,12 +9156,12 @@
       </c>
       <c r="R4" s="16"/>
     </row>
-    <row r="5" spans="2:18" ht="16.5" customHeight="1">
+    <row r="5" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="30" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>1</v>
@@ -8895,13 +9197,13 @@
       </c>
       <c r="P5" s="59"/>
     </row>
-    <row r="6" spans="2:18" ht="16.5" customHeight="1">
+    <row r="6" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="32">
         <f>SUMIF($E$3:$E$34,B5,$K$3:$K$34)</f>
         <v>2570.34</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>1</v>
@@ -8936,10 +9238,10 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="16.5" customHeight="1">
+    <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="60"/>
       <c r="D7" s="54" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="E7" s="36" t="s">
         <v>1</v>
@@ -8974,12 +9276,12 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="16.5" customHeight="1">
+    <row r="8" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="30" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>1</v>
@@ -9014,13 +9316,13 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="16.5" customHeight="1">
+    <row r="9" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="61">
         <f>SUMIF($F$3:$F$34,B8,$K$3:$K$34)</f>
         <v>5862.34</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="E9" s="36" t="s">
         <v>1</v>
@@ -9056,9 +9358,9 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="10" spans="2:18">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D10" s="54" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="37" t="s">
@@ -9091,9 +9393,9 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="11" spans="2:18">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D11" s="54" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="37" t="s">
@@ -9126,9 +9428,9 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="12" spans="2:18">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D12" s="54" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="E12" s="36"/>
       <c r="F12" s="37" t="s">
@@ -9161,9 +9463,9 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="13" spans="2:18">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D13" s="54" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="E13" s="36" t="s">
         <v>1</v>
@@ -9198,7 +9500,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="14" spans="2:18">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D14" s="37"/>
       <c r="E14" s="36"/>
       <c r="F14" s="37"/>
@@ -9212,7 +9514,7 @@
       <c r="N14" s="38"/>
       <c r="O14" s="39"/>
     </row>
-    <row r="15" spans="2:18">
+    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D15" s="37"/>
       <c r="E15" s="36"/>
       <c r="F15" s="37"/>
@@ -9226,7 +9528,7 @@
       <c r="N15" s="38"/>
       <c r="O15" s="39"/>
     </row>
-    <row r="16" spans="2:18">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D16" s="37"/>
       <c r="E16" s="36"/>
       <c r="F16" s="37"/>
@@ -9240,7 +9542,7 @@
       <c r="N16" s="38"/>
       <c r="O16" s="39"/>
     </row>
-    <row r="17" spans="4:15">
+    <row r="17" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D17" s="37"/>
       <c r="E17" s="36"/>
       <c r="F17" s="37"/>
@@ -9254,7 +9556,7 @@
       <c r="N17" s="38"/>
       <c r="O17" s="39"/>
     </row>
-    <row r="18" spans="4:15">
+    <row r="18" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D18" s="37"/>
       <c r="E18" s="36"/>
       <c r="F18" s="37"/>
@@ -9268,7 +9570,7 @@
       <c r="N18" s="38"/>
       <c r="O18" s="39"/>
     </row>
-    <row r="19" spans="4:15">
+    <row r="19" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D19" s="37"/>
       <c r="E19" s="36"/>
       <c r="F19" s="37"/>
@@ -9282,7 +9584,7 @@
       <c r="N19" s="38"/>
       <c r="O19" s="39"/>
     </row>
-    <row r="20" spans="4:15">
+    <row r="20" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D20" s="37"/>
       <c r="E20" s="36"/>
       <c r="F20" s="37"/>
@@ -9305,7 +9607,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:O404"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.140625" customWidth="1"/>
@@ -9321,23 +9623,23 @@
     <col min="15" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" s="2"/>
       <c r="N1" s="47" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" ht="14.25" customHeight="1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G2" s="2"/>
       <c r="N2" s="43"/>
     </row>
-    <row r="3" spans="2:15" ht="27.75" customHeight="1">
+    <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G3" s="2"/>
       <c r="L3" s="47" t="s">
-        <v>174</v>
-      </c>
-      <c r="M3" s="76" t="s">
-        <v>175</v>
+        <v>189</v>
+      </c>
+      <c r="M3" s="78" t="s">
+        <v>190</v>
       </c>
       <c r="N3" s="43">
         <f>SUM(N5:N21)</f>
@@ -9345,83 +9647,83 @@
       </c>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" spans="2:15">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G4" s="2"/>
       <c r="L4" s="48" t="s">
-        <v>176</v>
-      </c>
-      <c r="M4" s="78"/>
+        <v>191</v>
+      </c>
+      <c r="M4" s="79"/>
       <c r="N4" s="49"/>
     </row>
-    <row r="5" spans="2:15">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="43"/>
       <c r="C5" s="43"/>
       <c r="F5" s="16"/>
       <c r="G5" s="28"/>
       <c r="L5" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="N5" s="1">
         <v>100</v>
       </c>
       <c r="O5" s="16"/>
     </row>
-    <row r="6" spans="2:15">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G6" s="2"/>
       <c r="L6" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="N6" s="1">
         <f>97+31</f>
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="2:15">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G7" s="2"/>
       <c r="N7" s="73"/>
     </row>
-    <row r="8" spans="2:15">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F8" s="16"/>
       <c r="G8" s="50"/>
       <c r="N8" s="73"/>
     </row>
-    <row r="9" spans="2:15">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F9" s="47" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="G9" s="28"/>
       <c r="N9" s="72"/>
     </row>
-    <row r="10" spans="2:15">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F10" s="16">
         <f>SUM(G11:I11)</f>
-        <v>4000.0000000000036</v>
+        <v>8780.2000000000044</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="H10" s="51" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="I10" s="51" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="N10" s="72"/>
     </row>
-    <row r="11" spans="2:15">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="F11" s="16">
         <f>SUM(G11:H11)</f>
-        <v>4000.0000000000036</v>
+        <v>8780.2000000000044</v>
       </c>
       <c r="G11" s="1">
         <f>G12+SUM(G14:G496)</f>
-        <v>4000.0000000000036</v>
+        <v>8780.2000000000044</v>
       </c>
       <c r="H11" s="1">
         <f>H12+SUM(H14:H496)</f>
@@ -9433,36 +9735,36 @@
       </c>
       <c r="N11" s="72"/>
     </row>
-    <row r="12" spans="2:15">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="G12" s="1">
         <v>15250</v>
       </c>
       <c r="N12" s="72"/>
     </row>
-    <row r="13" spans="2:15">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F13" s="74" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="G13" s="52"/>
       <c r="H13" s="74"/>
       <c r="I13" s="74"/>
       <c r="N13" s="72"/>
     </row>
-    <row r="14" spans="2:15" outlineLevel="1">
+    <row r="14" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="G14" s="53"/>
       <c r="H14" s="53"/>
       <c r="I14" s="53"/>
       <c r="N14" s="43"/>
     </row>
-    <row r="15" spans="2:15" outlineLevel="1">
+    <row r="15" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F15" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="G15" s="53">
         <v>773.35</v>
@@ -9471,9 +9773,9 @@
       <c r="I15" s="53"/>
       <c r="N15" s="43"/>
     </row>
-    <row r="16" spans="2:15" outlineLevel="1">
+    <row r="16" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F16" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="G16" s="53">
         <v>-5148</v>
@@ -9482,9 +9784,9 @@
       <c r="I16" s="53"/>
       <c r="N16" s="43"/>
     </row>
-    <row r="17" spans="6:14" outlineLevel="1">
+    <row r="17" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F17" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="G17" s="53">
         <v>-168</v>
@@ -9493,9 +9795,9 @@
       <c r="I17" s="53"/>
       <c r="N17" s="43"/>
     </row>
-    <row r="18" spans="6:14" outlineLevel="1">
+    <row r="18" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F18" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="G18" s="53">
         <v>-1700</v>
@@ -9504,9 +9806,9 @@
       <c r="I18" s="53"/>
       <c r="N18" s="43"/>
     </row>
-    <row r="19" spans="6:14" outlineLevel="1">
+    <row r="19" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F19" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="G19" s="53">
         <v>5148</v>
@@ -9515,9 +9817,9 @@
       <c r="I19" s="53"/>
       <c r="N19" s="43"/>
     </row>
-    <row r="20" spans="6:14" outlineLevel="1">
+    <row r="20" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F20" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="G20" s="53">
         <v>-4938</v>
@@ -9526,9 +9828,9 @@
       <c r="I20" s="53"/>
       <c r="N20" s="43"/>
     </row>
-    <row r="21" spans="6:14" outlineLevel="1">
+    <row r="21" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F21" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="G21" s="53">
         <v>-1595</v>
@@ -9537,9 +9839,9 @@
       <c r="I21" s="53"/>
       <c r="N21" s="43"/>
     </row>
-    <row r="22" spans="6:14" outlineLevel="1">
+    <row r="22" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="G22" s="53">
         <v>-4677</v>
@@ -9548,9 +9850,9 @@
       <c r="I22" s="53"/>
       <c r="N22" s="43"/>
     </row>
-    <row r="23" spans="6:14" outlineLevel="1">
+    <row r="23" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F23" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="G23" s="53">
         <v>-200</v>
@@ -9559,9 +9861,9 @@
       <c r="I23" s="53"/>
       <c r="N23" s="43"/>
     </row>
-    <row r="24" spans="6:14" outlineLevel="1">
+    <row r="24" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F24" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="G24" s="53">
         <v>4677</v>
@@ -9570,9 +9872,9 @@
       <c r="I24" s="53"/>
       <c r="N24" s="43"/>
     </row>
-    <row r="25" spans="6:14" outlineLevel="1">
+    <row r="25" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F25" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="G25" s="53">
         <v>-750</v>
@@ -9581,9 +9883,9 @@
       <c r="I25" s="53"/>
       <c r="N25" s="43"/>
     </row>
-    <row r="26" spans="6:14" outlineLevel="1">
+    <row r="26" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F26" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="G26" s="53">
         <v>-652</v>
@@ -9592,9 +9894,9 @@
       <c r="I26" s="53"/>
       <c r="N26" s="43"/>
     </row>
-    <row r="27" spans="6:14" outlineLevel="1">
+    <row r="27" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F27" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="G27" s="53">
         <v>11100</v>
@@ -9603,9 +9905,9 @@
       <c r="I27" s="53"/>
       <c r="N27" s="43"/>
     </row>
-    <row r="28" spans="6:14" outlineLevel="1">
+    <row r="28" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F28" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="G28" s="53">
         <v>-396</v>
@@ -9614,9 +9916,9 @@
       <c r="I28" s="53"/>
       <c r="N28" s="43"/>
     </row>
-    <row r="29" spans="6:14" outlineLevel="1">
+    <row r="29" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F29" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="G29" s="53">
         <v>-4211</v>
@@ -9625,9 +9927,9 @@
       <c r="I29" s="53"/>
       <c r="N29" s="43"/>
     </row>
-    <row r="30" spans="6:14" outlineLevel="1">
+    <row r="30" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F30" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="G30" s="53">
         <v>-450</v>
@@ -9636,9 +9938,9 @@
       <c r="I30" s="53"/>
       <c r="N30" s="43"/>
     </row>
-    <row r="31" spans="6:14" outlineLevel="1">
+    <row r="31" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F31" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="G31" s="53">
         <v>-1197</v>
@@ -9647,9 +9949,9 @@
       <c r="I31" s="53"/>
       <c r="N31" s="43"/>
     </row>
-    <row r="32" spans="6:14" outlineLevel="1">
+    <row r="32" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F32" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="G32" s="53">
         <v>-315</v>
@@ -9658,9 +9960,9 @@
       <c r="I32" s="53"/>
       <c r="N32" s="43"/>
     </row>
-    <row r="33" spans="5:14" outlineLevel="1">
+    <row r="33" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F33" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="G33" s="53">
         <v>-830</v>
@@ -9669,9 +9971,9 @@
       <c r="I33" s="53"/>
       <c r="N33" s="43"/>
     </row>
-    <row r="34" spans="5:14" outlineLevel="1">
+    <row r="34" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F34" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="G34" s="53">
         <v>4211</v>
@@ -9680,9 +9982,9 @@
       <c r="I34" s="53"/>
       <c r="N34" s="43"/>
     </row>
-    <row r="35" spans="5:14" outlineLevel="1">
+    <row r="35" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F35" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="G35" s="53">
         <v>-200</v>
@@ -9691,9 +9993,9 @@
       <c r="I35" s="53"/>
       <c r="N35" s="43"/>
     </row>
-    <row r="36" spans="5:14" outlineLevel="1">
+    <row r="36" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F36" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="G36" s="53">
         <v>10000</v>
@@ -9702,9 +10004,9 @@
       <c r="I36" s="53"/>
       <c r="N36" s="43"/>
     </row>
-    <row r="37" spans="5:14" outlineLevel="1">
+    <row r="37" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F37" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="G37" s="53">
         <v>-200</v>
@@ -9713,9 +10015,9 @@
       <c r="I37" s="53"/>
       <c r="N37" s="43"/>
     </row>
-    <row r="38" spans="5:14" outlineLevel="1">
+    <row r="38" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F38" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="G38" s="53">
         <v>-381</v>
@@ -9724,9 +10026,9 @@
       <c r="I38" s="53"/>
       <c r="N38" s="43"/>
     </row>
-    <row r="39" spans="5:14" outlineLevel="1">
+    <row r="39" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="G39" s="53">
         <v>-4911</v>
@@ -9735,10 +10037,10 @@
       <c r="I39" s="53"/>
       <c r="N39" s="43"/>
     </row>
-    <row r="40" spans="5:14" outlineLevel="1">
+    <row r="40" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="G40" s="53">
         <v>-5700</v>
@@ -9747,9 +10049,9 @@
       <c r="I40" s="53"/>
       <c r="N40" s="43"/>
     </row>
-    <row r="41" spans="5:14" outlineLevel="1">
+    <row r="41" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F41" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="G41" s="53">
         <v>-400</v>
@@ -9758,9 +10060,9 @@
       <c r="I41" s="53"/>
       <c r="N41" s="43"/>
     </row>
-    <row r="42" spans="5:14" outlineLevel="1">
+    <row r="42" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F42" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="G42" s="53">
         <v>-450</v>
@@ -9769,9 +10071,9 @@
       <c r="I42" s="53"/>
       <c r="N42" s="43"/>
     </row>
-    <row r="43" spans="5:14" outlineLevel="1">
+    <row r="43" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F43" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="G43" s="53">
         <v>-640</v>
@@ -9780,10 +10082,10 @@
       <c r="I43" s="53"/>
       <c r="N43" s="43"/>
     </row>
-    <row r="44" spans="5:14" outlineLevel="1">
+    <row r="44" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="G44" s="53">
         <v>5700</v>
@@ -9792,9 +10094,9 @@
       <c r="I44" s="53"/>
       <c r="N44" s="43"/>
     </row>
-    <row r="45" spans="5:14" outlineLevel="1">
+    <row r="45" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F45" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="G45" s="53">
         <v>-130</v>
@@ -9803,9 +10105,9 @@
       <c r="I45" s="53"/>
       <c r="N45" s="43"/>
     </row>
-    <row r="46" spans="5:14" outlineLevel="1">
+    <row r="46" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F46" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="G46" s="53">
         <v>-250</v>
@@ -9814,9 +10116,9 @@
       <c r="I46" s="53"/>
       <c r="N46" s="43"/>
     </row>
-    <row r="47" spans="5:14" outlineLevel="1">
+    <row r="47" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F47" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="G47" s="53">
         <v>-112.2</v>
@@ -9825,9 +10127,9 @@
       <c r="I47" s="53"/>
       <c r="N47" s="43"/>
     </row>
-    <row r="48" spans="5:14" outlineLevel="1">
+    <row r="48" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F48" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="G48" s="53">
         <v>4911</v>
@@ -9836,9 +10138,9 @@
       <c r="I48" s="53"/>
       <c r="N48" s="43"/>
     </row>
-    <row r="49" spans="6:14" outlineLevel="1">
+    <row r="49" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F49" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="G49" s="53">
         <v>-3000</v>
@@ -9847,9 +10149,9 @@
       <c r="I49" s="53"/>
       <c r="N49" s="43"/>
     </row>
-    <row r="50" spans="6:14" outlineLevel="1">
+    <row r="50" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F50" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="G50" s="53">
         <v>-4000</v>
@@ -9858,9 +10160,9 @@
       <c r="I50" s="53"/>
       <c r="N50" s="43"/>
     </row>
-    <row r="51" spans="6:14" outlineLevel="1">
+    <row r="51" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F51" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="G51" s="53">
         <v>-200</v>
@@ -9869,9 +10171,9 @@
       <c r="I51" s="53"/>
       <c r="N51" s="43"/>
     </row>
-    <row r="52" spans="6:14" outlineLevel="1">
+    <row r="52" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F52" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="G52" s="53">
         <v>-4612</v>
@@ -9880,9 +10182,9 @@
       <c r="I52" s="53"/>
       <c r="N52" s="43"/>
     </row>
-    <row r="53" spans="6:14" outlineLevel="1">
+    <row r="53" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F53" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="G53" s="53">
         <v>-700</v>
@@ -9891,9 +10193,9 @@
       <c r="I53" s="53"/>
       <c r="N53" s="43"/>
     </row>
-    <row r="54" spans="6:14" outlineLevel="1">
+    <row r="54" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F54" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="G54" s="53">
         <v>-880</v>
@@ -9902,9 +10204,9 @@
       <c r="I54" s="53"/>
       <c r="N54" s="43"/>
     </row>
-    <row r="55" spans="6:14" outlineLevel="1">
+    <row r="55" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F55" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="G55" s="53">
         <v>-310</v>
@@ -9913,9 +10215,9 @@
       <c r="I55" s="53"/>
       <c r="N55" s="43"/>
     </row>
-    <row r="56" spans="6:14">
+    <row r="56" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F56" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="G56" s="53">
         <v>-250</v>
@@ -9924,9 +10226,9 @@
       <c r="I56" s="53"/>
       <c r="N56" s="43"/>
     </row>
-    <row r="57" spans="6:14">
+    <row r="57" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F57" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="G57" s="53">
         <v>4690</v>
@@ -9935,9 +10237,9 @@
       <c r="I57" s="53"/>
       <c r="N57" s="43"/>
     </row>
-    <row r="58" spans="6:14">
+    <row r="58" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F58" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="G58" s="53">
         <v>-4440</v>
@@ -9946,9 +10248,9 @@
       <c r="I58" s="53"/>
       <c r="N58" s="43"/>
     </row>
-    <row r="59" spans="6:14">
+    <row r="59" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F59" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="G59" s="53">
         <v>-4697</v>
@@ -9956,9 +10258,9 @@
       <c r="H59" s="53"/>
       <c r="I59" s="53"/>
     </row>
-    <row r="60" spans="6:14">
+    <row r="60" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F60" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="G60" s="53">
         <v>-2500</v>
@@ -9966,9 +10268,9 @@
       <c r="H60" s="53"/>
       <c r="I60" s="53"/>
     </row>
-    <row r="61" spans="6:14">
+    <row r="61" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F61" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="G61" s="53">
         <v>-126</v>
@@ -9976,9 +10278,9 @@
       <c r="H61" s="53"/>
       <c r="I61" s="53"/>
     </row>
-    <row r="62" spans="6:14">
+    <row r="62" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F62" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="G62" s="53">
         <v>4742</v>
@@ -9986,9 +10288,9 @@
       <c r="H62" s="53"/>
       <c r="I62" s="53"/>
     </row>
-    <row r="63" spans="6:14">
+    <row r="63" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F63" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="G63" s="53">
         <v>-410</v>
@@ -9996,14 +10298,14 @@
       <c r="H63" s="53"/>
       <c r="I63" s="53"/>
     </row>
-    <row r="64" spans="6:14">
+    <row r="64" spans="6:14" x14ac:dyDescent="0.25">
       <c r="G64" s="53"/>
       <c r="H64" s="53"/>
       <c r="I64" s="53"/>
     </row>
-    <row r="65" spans="6:9">
+    <row r="65" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F65" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="G65" s="53">
         <v>3320</v>
@@ -10011,9 +10313,9 @@
       <c r="H65" s="53"/>
       <c r="I65" s="53"/>
     </row>
-    <row r="66" spans="6:9">
+    <row r="66" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F66" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="G66" s="53">
         <v>4090</v>
@@ -10021,9 +10323,9 @@
       <c r="H66" s="53"/>
       <c r="I66" s="53"/>
     </row>
-    <row r="67" spans="6:9">
+    <row r="67" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F67" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="G67" s="53">
         <v>-5688</v>
@@ -10031,9 +10333,9 @@
       <c r="H67" s="53"/>
       <c r="I67" s="53"/>
     </row>
-    <row r="68" spans="6:9">
+    <row r="68" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F68" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="G68" s="53">
         <v>-4433</v>
@@ -10041,9 +10343,9 @@
       <c r="H68" s="53"/>
       <c r="I68" s="53"/>
     </row>
-    <row r="69" spans="6:9">
+    <row r="69" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F69" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="G69" s="53">
         <v>-250</v>
@@ -10051,9 +10353,9 @@
       <c r="H69" s="53"/>
       <c r="I69" s="53"/>
     </row>
-    <row r="70" spans="6:9">
+    <row r="70" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F70" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="G70" s="53">
         <v>-99</v>
@@ -10061,9 +10363,9 @@
       <c r="H70" s="53"/>
       <c r="I70" s="53"/>
     </row>
-    <row r="71" spans="6:9">
+    <row r="71" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F71" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="G71" s="53">
         <v>320</v>
@@ -10071,9 +10373,9 @@
       <c r="H71" s="53"/>
       <c r="I71" s="53"/>
     </row>
-    <row r="72" spans="6:9">
+    <row r="72" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F72" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="G72" s="53">
         <v>-1572</v>
@@ -10081,14 +10383,14 @@
       <c r="H72" s="53"/>
       <c r="I72" s="53"/>
     </row>
-    <row r="73" spans="6:9">
+    <row r="73" spans="6:9" x14ac:dyDescent="0.25">
       <c r="G73" s="53"/>
       <c r="H73" s="53"/>
       <c r="I73" s="53"/>
     </row>
-    <row r="74" spans="6:9">
+    <row r="74" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F74" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="G74" s="53">
         <v>4433</v>
@@ -10096,9 +10398,9 @@
       <c r="H74" s="53"/>
       <c r="I74" s="53"/>
     </row>
-    <row r="75" spans="6:9">
+    <row r="75" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F75" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="G75" s="53">
         <v>8000</v>
@@ -10106,9 +10408,9 @@
       <c r="H75" s="53"/>
       <c r="I75" s="53"/>
     </row>
-    <row r="76" spans="6:9">
+    <row r="76" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F76" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="G76" s="53">
         <v>-1344</v>
@@ -10116,9 +10418,9 @@
       <c r="H76" s="53"/>
       <c r="I76" s="53"/>
     </row>
-    <row r="77" spans="6:9">
+    <row r="77" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F77" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="G77" s="53">
         <v>-308</v>
@@ -10126,9 +10428,9 @@
       <c r="H77" s="53"/>
       <c r="I77" s="53"/>
     </row>
-    <row r="78" spans="6:9" ht="14.25" customHeight="1">
+    <row r="78" spans="6:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F78" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="G78" s="53">
         <v>-4204</v>
@@ -10136,9 +10438,9 @@
       <c r="H78" s="53"/>
       <c r="I78" s="53"/>
     </row>
-    <row r="79" spans="6:9">
+    <row r="79" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F79" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="G79" s="53">
         <v>-338</v>
@@ -10146,9 +10448,9 @@
       <c r="H79" s="53"/>
       <c r="I79" s="53"/>
     </row>
-    <row r="80" spans="6:9">
+    <row r="80" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F80" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="G80" s="53">
         <v>-50</v>
@@ -10156,9 +10458,9 @@
       <c r="H80" s="53"/>
       <c r="I80" s="53"/>
     </row>
-    <row r="81" spans="2:9">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F81" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="G81" s="53">
         <v>338</v>
@@ -10166,9 +10468,9 @@
       <c r="H81" s="53"/>
       <c r="I81" s="53"/>
     </row>
-    <row r="82" spans="2:9">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F82" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="G82" s="53">
         <v>-540</v>
@@ -10176,9 +10478,9 @@
       <c r="H82" s="53"/>
       <c r="I82" s="53"/>
     </row>
-    <row r="83" spans="2:9">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F83" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="G83" s="53">
         <v>-184.31</v>
@@ -10186,11 +10488,11 @@
       <c r="H83" s="53"/>
       <c r="I83" s="53"/>
     </row>
-    <row r="84" spans="2:9">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C84" s="53"/>
       <c r="D84" s="53"/>
       <c r="F84" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="G84" s="53">
         <v>-1464.22</v>
@@ -10198,11 +10500,11 @@
       <c r="H84" s="53"/>
       <c r="I84" s="53"/>
     </row>
-    <row r="85" spans="2:9">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C85" s="53"/>
       <c r="D85" s="53"/>
       <c r="F85" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="G85" s="53">
         <v>1005</v>
@@ -10210,11 +10512,11 @@
       <c r="H85" s="53"/>
       <c r="I85" s="53"/>
     </row>
-    <row r="86" spans="2:9">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C86" s="53"/>
       <c r="D86" s="53"/>
       <c r="F86" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="G86" s="53">
         <v>-500</v>
@@ -10222,11 +10524,11 @@
       <c r="H86" s="53"/>
       <c r="I86" s="53"/>
     </row>
-    <row r="87" spans="2:9">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C87" s="53"/>
       <c r="D87" s="53"/>
       <c r="F87" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="G87" s="53">
         <v>-225</v>
@@ -10234,11 +10536,11 @@
       <c r="H87" s="53"/>
       <c r="I87" s="53"/>
     </row>
-    <row r="88" spans="2:9">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C88" s="53"/>
       <c r="D88" s="53"/>
       <c r="F88" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="G88" s="53">
         <v>-516</v>
@@ -10246,11 +10548,11 @@
       <c r="H88" s="53"/>
       <c r="I88" s="53"/>
     </row>
-    <row r="89" spans="2:9">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C89" s="53"/>
       <c r="D89" s="53"/>
       <c r="F89" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="G89" s="53">
         <v>4204</v>
@@ -10258,16 +10560,11 @@
       <c r="H89" s="53"/>
       <c r="I89" s="53"/>
     </row>
-    <row r="90" spans="2:9">
-      <c r="B90" t="s">
-        <v>246</v>
-      </c>
-      <c r="C90" s="53">
-        <v>5556.2</v>
-      </c>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C90" s="53"/>
       <c r="D90" s="53"/>
       <c r="F90" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="G90" s="53">
         <v>-100</v>
@@ -10275,11 +10572,11 @@
       <c r="H90" s="53"/>
       <c r="I90" s="53"/>
     </row>
-    <row r="91" spans="2:9">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C91" s="53"/>
       <c r="D91" s="53"/>
       <c r="F91" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="G91" s="53">
         <v>8000</v>
@@ -10287,18 +10584,11 @@
       <c r="H91" s="53"/>
       <c r="I91" s="53"/>
     </row>
-    <row r="92" spans="2:9">
-      <c r="B92" t="s">
-        <v>249</v>
-      </c>
-      <c r="C92" s="53">
-        <v>1000</v>
-      </c>
-      <c r="D92" s="53">
-        <v>300</v>
-      </c>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C92" s="53"/>
+      <c r="D92" s="53"/>
       <c r="F92" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="G92" s="53">
         <v>1000</v>
@@ -10306,11 +10596,11 @@
       <c r="H92" s="53"/>
       <c r="I92" s="53"/>
     </row>
-    <row r="93" spans="2:9">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C93" s="53"/>
       <c r="D93" s="53"/>
       <c r="F93" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="G93" s="53">
         <v>-12881</v>
@@ -10318,16 +10608,11 @@
       <c r="H93" s="53"/>
       <c r="I93" s="53"/>
     </row>
-    <row r="94" spans="2:9">
-      <c r="B94" t="s">
-        <v>252</v>
-      </c>
-      <c r="C94" s="53">
-        <v>160</v>
-      </c>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C94" s="53"/>
       <c r="D94" s="53"/>
       <c r="F94" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="G94" s="53">
         <v>-4489.62</v>
@@ -10335,11 +10620,11 @@
       <c r="H94" s="53"/>
       <c r="I94" s="53"/>
     </row>
-    <row r="95" spans="2:9">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C95" s="53"/>
       <c r="D95" s="53"/>
       <c r="F95" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="G95" s="53">
         <v>5000</v>
@@ -10347,9 +10632,9 @@
       <c r="H95" s="53"/>
       <c r="I95" s="53"/>
     </row>
-    <row r="96" spans="2:9">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C96" s="53">
         <v>2000</v>
@@ -10358,7 +10643,7 @@
         <v>300</v>
       </c>
       <c r="F96" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="G96" s="53">
         <v>-480</v>
@@ -10366,11 +10651,11 @@
       <c r="H96" s="53"/>
       <c r="I96" s="53"/>
     </row>
-    <row r="97" spans="2:9">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C97" s="53"/>
       <c r="D97" s="53"/>
       <c r="F97" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="G97" s="53">
         <v>-520</v>
@@ -10378,23 +10663,33 @@
       <c r="H97" s="53"/>
       <c r="I97" s="53"/>
     </row>
-    <row r="98" spans="2:9">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C98" s="53"/>
       <c r="D98" s="53"/>
-      <c r="G98" s="53"/>
+      <c r="F98" t="s">
+        <v>270</v>
+      </c>
+      <c r="G98" s="53">
+        <v>5556.2</v>
+      </c>
       <c r="H98" s="53"/>
       <c r="I98" s="53"/>
     </row>
-    <row r="99" spans="2:9">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C99" s="53"/>
       <c r="D99" s="53"/>
-      <c r="G99" s="53"/>
+      <c r="F99" t="s">
+        <v>271</v>
+      </c>
+      <c r="G99" s="53">
+        <v>-500</v>
+      </c>
       <c r="H99" s="53"/>
       <c r="I99" s="53"/>
     </row>
-    <row r="100" spans="2:9">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="C100" s="53">
         <v>2000</v>
@@ -10402,13 +10697,18 @@
       <c r="D100" s="53">
         <v>300</v>
       </c>
-      <c r="G100" s="53"/>
+      <c r="F100" t="s">
+        <v>297</v>
+      </c>
+      <c r="G100" s="53">
+        <v>-276</v>
+      </c>
       <c r="H100" s="53"/>
       <c r="I100" s="53"/>
     </row>
-    <row r="101" spans="2:9">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="C101" s="53">
         <v>8000</v>
@@ -10418,9 +10718,9 @@
       <c r="H101" s="53"/>
       <c r="I101" s="53"/>
     </row>
-    <row r="102" spans="2:9">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="C102" s="53">
         <v>4180</v>
@@ -10430,16 +10730,16 @@
       <c r="H102" s="53"/>
       <c r="I102" s="53"/>
     </row>
-    <row r="103" spans="2:9">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C103" s="53"/>
       <c r="D103" s="53"/>
       <c r="G103" s="53"/>
       <c r="H103" s="53"/>
       <c r="I103" s="53"/>
     </row>
-    <row r="104" spans="2:9">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="C104" s="53">
         <v>2000</v>
@@ -10451,9 +10751,9 @@
       <c r="H104" s="53"/>
       <c r="I104" s="53"/>
     </row>
-    <row r="105" spans="2:9">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="C105" s="53">
         <v>2000</v>
@@ -10465,9 +10765,9 @@
       <c r="H105" s="53"/>
       <c r="I105" s="53"/>
     </row>
-    <row r="106" spans="2:9">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="C106" s="53">
         <v>2000</v>
@@ -10479,16 +10779,16 @@
       <c r="H106" s="53"/>
       <c r="I106" s="53"/>
     </row>
-    <row r="107" spans="2:9">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C107" s="53"/>
       <c r="D107" s="53"/>
       <c r="G107" s="53"/>
       <c r="H107" s="53"/>
       <c r="I107" s="53"/>
     </row>
-    <row r="108" spans="2:9">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="C108" s="53">
         <v>-20000</v>
@@ -10498,16 +10798,16 @@
       <c r="H108" s="53"/>
       <c r="I108" s="53"/>
     </row>
-    <row r="109" spans="2:9">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C109" s="53"/>
       <c r="D109" s="53"/>
       <c r="G109" s="53"/>
       <c r="H109" s="53"/>
       <c r="I109" s="53"/>
     </row>
-    <row r="110" spans="2:9">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="C110" s="53">
         <v>2000</v>
@@ -10519,9 +10819,9 @@
       <c r="H110" s="53"/>
       <c r="I110" s="53"/>
     </row>
-    <row r="111" spans="2:9">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="C111" s="53">
         <v>2000</v>
@@ -10533,9 +10833,9 @@
       <c r="H111" s="53"/>
       <c r="I111" s="53"/>
     </row>
-    <row r="112" spans="2:9">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="C112" s="53">
         <v>8000</v>
@@ -10545,9 +10845,9 @@
       <c r="H112" s="53"/>
       <c r="I112" s="53"/>
     </row>
-    <row r="113" spans="2:9">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="C113" s="53">
         <v>2000</v>
@@ -10559,9 +10859,9 @@
       <c r="H113" s="53"/>
       <c r="I113" s="53"/>
     </row>
-    <row r="114" spans="2:9">
+    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="C114" s="53">
         <v>2000</v>
@@ -10573,1185 +10873,1185 @@
       <c r="H114" s="53"/>
       <c r="I114" s="53"/>
     </row>
-    <row r="115" spans="2:9">
+    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C115" s="53"/>
       <c r="G115" s="53"/>
       <c r="H115" s="53"/>
       <c r="I115" s="53"/>
     </row>
-    <row r="116" spans="2:9">
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C116" s="53"/>
       <c r="G116" s="53"/>
       <c r="H116" s="53"/>
       <c r="I116" s="53"/>
     </row>
-    <row r="117" spans="2:9">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C117" s="53"/>
       <c r="G117" s="53"/>
       <c r="H117" s="53"/>
       <c r="I117" s="53"/>
     </row>
-    <row r="118" spans="2:9">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C118" s="53"/>
       <c r="G118" s="53"/>
       <c r="H118" s="53"/>
       <c r="I118" s="53"/>
     </row>
-    <row r="119" spans="2:9">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C119" s="53"/>
       <c r="G119" s="53"/>
       <c r="H119" s="53"/>
       <c r="I119" s="53"/>
     </row>
-    <row r="120" spans="2:9">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C120" s="53"/>
       <c r="G120" s="53"/>
       <c r="H120" s="53"/>
       <c r="I120" s="53"/>
     </row>
-    <row r="121" spans="2:9">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C121" s="53"/>
       <c r="G121" s="53"/>
       <c r="H121" s="53"/>
       <c r="I121" s="53"/>
     </row>
-    <row r="122" spans="2:9">
+    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G122" s="53"/>
-      <c r="H122" s="53"/>
+      <c r="H122" s="75"/>
       <c r="I122" s="53"/>
     </row>
-    <row r="123" spans="2:9">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G123" s="53"/>
-      <c r="H123" s="53"/>
+      <c r="H123" s="75"/>
       <c r="I123" s="53"/>
     </row>
-    <row r="124" spans="2:9">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G124" s="53"/>
-      <c r="H124" s="53"/>
+      <c r="H124" s="75"/>
       <c r="I124" s="53"/>
     </row>
-    <row r="125" spans="2:9">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G125" s="53"/>
-      <c r="H125" s="53"/>
+      <c r="H125" s="75"/>
       <c r="I125" s="53"/>
     </row>
-    <row r="126" spans="2:9">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G126" s="53"/>
-      <c r="H126" s="53"/>
+      <c r="H126" s="75"/>
       <c r="I126" s="53"/>
     </row>
-    <row r="127" spans="2:9">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G127" s="53"/>
-      <c r="H127" s="53"/>
+      <c r="H127" s="75"/>
       <c r="I127" s="53"/>
     </row>
-    <row r="128" spans="2:9">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G128" s="53"/>
-      <c r="H128" s="53"/>
+      <c r="H128" s="75"/>
       <c r="I128" s="53"/>
     </row>
-    <row r="129" spans="7:9">
+    <row r="129" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G129" s="53"/>
       <c r="H129" s="53"/>
       <c r="I129" s="53"/>
     </row>
-    <row r="130" spans="7:9">
+    <row r="130" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G130" s="53"/>
       <c r="H130" s="53"/>
       <c r="I130" s="53"/>
     </row>
-    <row r="131" spans="7:9">
+    <row r="131" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G131" s="53"/>
       <c r="H131" s="53"/>
       <c r="I131" s="53"/>
     </row>
-    <row r="132" spans="7:9">
+    <row r="132" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G132" s="53"/>
       <c r="H132" s="53"/>
       <c r="I132" s="53"/>
     </row>
-    <row r="133" spans="7:9">
+    <row r="133" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G133" s="53"/>
       <c r="H133" s="53"/>
       <c r="I133" s="53"/>
     </row>
-    <row r="134" spans="7:9">
+    <row r="134" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G134" s="53"/>
       <c r="H134" s="53"/>
       <c r="I134" s="53"/>
     </row>
-    <row r="135" spans="7:9">
+    <row r="135" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G135" s="53"/>
       <c r="H135" s="53"/>
       <c r="I135" s="53"/>
     </row>
-    <row r="136" spans="7:9">
+    <row r="136" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G136" s="53"/>
       <c r="H136" s="53"/>
       <c r="I136" s="53"/>
     </row>
-    <row r="137" spans="7:9">
+    <row r="137" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G137" s="53"/>
       <c r="H137" s="53"/>
       <c r="I137" s="53"/>
     </row>
-    <row r="138" spans="7:9">
+    <row r="138" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G138" s="53"/>
       <c r="H138" s="53"/>
       <c r="I138" s="53"/>
     </row>
-    <row r="139" spans="7:9">
+    <row r="139" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G139" s="53"/>
       <c r="H139" s="53"/>
       <c r="I139" s="53"/>
     </row>
-    <row r="140" spans="7:9">
+    <row r="140" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G140" s="53"/>
       <c r="H140" s="53"/>
       <c r="I140" s="53"/>
     </row>
-    <row r="141" spans="7:9">
+    <row r="141" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G141" s="53"/>
       <c r="H141" s="53"/>
       <c r="I141" s="53"/>
     </row>
-    <row r="142" spans="7:9">
+    <row r="142" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G142" s="53"/>
       <c r="H142" s="53"/>
       <c r="I142" s="53"/>
     </row>
-    <row r="143" spans="7:9">
+    <row r="143" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G143" s="53"/>
       <c r="H143" s="53"/>
       <c r="I143" s="53"/>
     </row>
-    <row r="144" spans="7:9">
+    <row r="144" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G144" s="53"/>
       <c r="H144" s="53"/>
       <c r="I144" s="53"/>
     </row>
-    <row r="145" spans="7:9">
+    <row r="145" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G145" s="53"/>
       <c r="H145" s="53"/>
       <c r="I145" s="53"/>
     </row>
-    <row r="146" spans="7:9">
+    <row r="146" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G146" s="53"/>
       <c r="H146" s="53"/>
       <c r="I146" s="53"/>
     </row>
-    <row r="147" spans="7:9">
+    <row r="147" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G147" s="53"/>
       <c r="H147" s="53"/>
       <c r="I147" s="53"/>
     </row>
-    <row r="148" spans="7:9">
+    <row r="148" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G148" s="53"/>
       <c r="H148" s="53"/>
       <c r="I148" s="53"/>
     </row>
-    <row r="149" spans="7:9">
+    <row r="149" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G149" s="53"/>
       <c r="H149" s="53"/>
       <c r="I149" s="53"/>
     </row>
-    <row r="150" spans="7:9">
+    <row r="150" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G150" s="53"/>
       <c r="H150" s="53"/>
       <c r="I150" s="53"/>
     </row>
-    <row r="151" spans="7:9">
+    <row r="151" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G151" s="53"/>
       <c r="H151" s="53"/>
       <c r="I151" s="53"/>
     </row>
-    <row r="152" spans="7:9">
+    <row r="152" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G152" s="53"/>
       <c r="H152" s="53"/>
       <c r="I152" s="53"/>
     </row>
-    <row r="153" spans="7:9">
+    <row r="153" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G153" s="53"/>
       <c r="H153" s="53"/>
       <c r="I153" s="53"/>
     </row>
-    <row r="154" spans="7:9">
+    <row r="154" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G154" s="53"/>
       <c r="H154" s="53"/>
       <c r="I154" s="53"/>
     </row>
-    <row r="155" spans="7:9">
+    <row r="155" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G155" s="53"/>
       <c r="H155" s="53"/>
       <c r="I155" s="53"/>
     </row>
-    <row r="156" spans="7:9">
+    <row r="156" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G156" s="53"/>
       <c r="H156" s="53"/>
       <c r="I156" s="53"/>
     </row>
-    <row r="157" spans="7:9">
+    <row r="157" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G157" s="53"/>
       <c r="H157" s="53"/>
       <c r="I157" s="53"/>
     </row>
-    <row r="158" spans="7:9">
+    <row r="158" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G158" s="53"/>
       <c r="H158" s="53"/>
       <c r="I158" s="53"/>
     </row>
-    <row r="159" spans="7:9">
+    <row r="159" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G159" s="53"/>
       <c r="H159" s="53"/>
       <c r="I159" s="53"/>
     </row>
-    <row r="160" spans="7:9">
+    <row r="160" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G160" s="53"/>
       <c r="H160" s="53"/>
       <c r="I160" s="53"/>
     </row>
-    <row r="161" spans="7:9">
+    <row r="161" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G161" s="53"/>
       <c r="H161" s="53"/>
       <c r="I161" s="53"/>
     </row>
-    <row r="162" spans="7:9">
+    <row r="162" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G162" s="53"/>
       <c r="H162" s="53"/>
       <c r="I162" s="53"/>
     </row>
-    <row r="163" spans="7:9">
+    <row r="163" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G163" s="53"/>
       <c r="H163" s="53"/>
       <c r="I163" s="53"/>
     </row>
-    <row r="164" spans="7:9">
+    <row r="164" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G164" s="53"/>
       <c r="H164" s="53"/>
       <c r="I164" s="53"/>
     </row>
-    <row r="165" spans="7:9">
+    <row r="165" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G165" s="53"/>
       <c r="H165" s="53"/>
       <c r="I165" s="53"/>
     </row>
-    <row r="166" spans="7:9">
+    <row r="166" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G166" s="53"/>
       <c r="H166" s="53"/>
       <c r="I166" s="53"/>
     </row>
-    <row r="167" spans="7:9">
+    <row r="167" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G167" s="53"/>
       <c r="H167" s="53"/>
       <c r="I167" s="53"/>
     </row>
-    <row r="168" spans="7:9">
+    <row r="168" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G168" s="53"/>
       <c r="H168" s="53"/>
       <c r="I168" s="53"/>
     </row>
-    <row r="169" spans="7:9">
+    <row r="169" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G169" s="53"/>
       <c r="H169" s="53"/>
       <c r="I169" s="53"/>
     </row>
-    <row r="170" spans="7:9">
+    <row r="170" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G170" s="53"/>
       <c r="H170" s="53"/>
       <c r="I170" s="53"/>
     </row>
-    <row r="171" spans="7:9">
+    <row r="171" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G171" s="53"/>
       <c r="H171" s="53"/>
       <c r="I171" s="53"/>
     </row>
-    <row r="172" spans="7:9">
+    <row r="172" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G172" s="53"/>
       <c r="H172" s="53"/>
       <c r="I172" s="53"/>
     </row>
-    <row r="173" spans="7:9">
+    <row r="173" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G173" s="53"/>
       <c r="H173" s="53"/>
       <c r="I173" s="53"/>
     </row>
-    <row r="174" spans="7:9">
+    <row r="174" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G174" s="53"/>
       <c r="H174" s="53"/>
       <c r="I174" s="53"/>
     </row>
-    <row r="175" spans="7:9">
+    <row r="175" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G175" s="53"/>
       <c r="H175" s="53"/>
       <c r="I175" s="53"/>
     </row>
-    <row r="176" spans="7:9">
+    <row r="176" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G176" s="53"/>
       <c r="H176" s="53"/>
       <c r="I176" s="53"/>
     </row>
-    <row r="177" spans="7:9">
+    <row r="177" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G177" s="53"/>
       <c r="H177" s="53"/>
       <c r="I177" s="53"/>
     </row>
-    <row r="178" spans="7:9">
+    <row r="178" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G178" s="53"/>
       <c r="H178" s="53"/>
       <c r="I178" s="53"/>
     </row>
-    <row r="179" spans="7:9">
+    <row r="179" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G179" s="53"/>
       <c r="H179" s="53"/>
       <c r="I179" s="53"/>
     </row>
-    <row r="180" spans="7:9">
+    <row r="180" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G180" s="53"/>
       <c r="H180" s="53"/>
       <c r="I180" s="53"/>
     </row>
-    <row r="181" spans="7:9">
+    <row r="181" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G181" s="53"/>
       <c r="H181" s="53"/>
       <c r="I181" s="53"/>
     </row>
-    <row r="182" spans="7:9">
+    <row r="182" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G182" s="53"/>
       <c r="H182" s="53"/>
       <c r="I182" s="53"/>
     </row>
-    <row r="183" spans="7:9">
+    <row r="183" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G183" s="53"/>
       <c r="H183" s="53"/>
       <c r="I183" s="53"/>
     </row>
-    <row r="184" spans="7:9">
+    <row r="184" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G184" s="53"/>
       <c r="H184" s="53"/>
       <c r="I184" s="53"/>
     </row>
-    <row r="185" spans="7:9">
+    <row r="185" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G185" s="53"/>
       <c r="H185" s="53"/>
       <c r="I185" s="53"/>
     </row>
-    <row r="186" spans="7:9">
+    <row r="186" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G186" s="53"/>
       <c r="H186" s="53"/>
       <c r="I186" s="53"/>
     </row>
-    <row r="187" spans="7:9">
+    <row r="187" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G187" s="53"/>
       <c r="H187" s="53"/>
       <c r="I187" s="53"/>
     </row>
-    <row r="188" spans="7:9">
+    <row r="188" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G188" s="53"/>
       <c r="H188" s="53"/>
       <c r="I188" s="53"/>
     </row>
-    <row r="189" spans="7:9">
+    <row r="189" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G189" s="53"/>
       <c r="H189" s="53"/>
       <c r="I189" s="53"/>
     </row>
-    <row r="190" spans="7:9">
+    <row r="190" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G190" s="53"/>
       <c r="H190" s="53"/>
       <c r="I190" s="53"/>
     </row>
-    <row r="191" spans="7:9">
+    <row r="191" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G191" s="53"/>
       <c r="H191" s="53"/>
       <c r="I191" s="53"/>
     </row>
-    <row r="192" spans="7:9">
+    <row r="192" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G192" s="53"/>
       <c r="H192" s="53"/>
       <c r="I192" s="53"/>
     </row>
-    <row r="193" spans="7:9">
+    <row r="193" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G193" s="53"/>
       <c r="H193" s="53"/>
       <c r="I193" s="53"/>
     </row>
-    <row r="194" spans="7:9">
+    <row r="194" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G194" s="53"/>
       <c r="H194" s="53"/>
       <c r="I194" s="53"/>
     </row>
-    <row r="195" spans="7:9">
+    <row r="195" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G195" s="53"/>
       <c r="H195" s="53"/>
       <c r="I195" s="53"/>
     </row>
-    <row r="196" spans="7:9">
+    <row r="196" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G196" s="53"/>
       <c r="H196" s="53"/>
       <c r="I196" s="53"/>
     </row>
-    <row r="197" spans="7:9">
+    <row r="197" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G197" s="53"/>
       <c r="H197" s="53"/>
       <c r="I197" s="53"/>
     </row>
-    <row r="198" spans="7:9">
+    <row r="198" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G198" s="53"/>
       <c r="H198" s="53"/>
       <c r="I198" s="53"/>
     </row>
-    <row r="199" spans="7:9">
+    <row r="199" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G199" s="53"/>
       <c r="H199" s="53"/>
       <c r="I199" s="53"/>
     </row>
-    <row r="200" spans="7:9">
+    <row r="200" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G200" s="53"/>
       <c r="H200" s="53"/>
       <c r="I200" s="53"/>
     </row>
-    <row r="201" spans="7:9">
+    <row r="201" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G201" s="53"/>
       <c r="H201" s="53"/>
       <c r="I201" s="53"/>
     </row>
-    <row r="202" spans="7:9">
+    <row r="202" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G202" s="53"/>
       <c r="H202" s="53"/>
       <c r="I202" s="53"/>
     </row>
-    <row r="203" spans="7:9">
+    <row r="203" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G203" s="53"/>
       <c r="H203" s="53"/>
       <c r="I203" s="53"/>
     </row>
-    <row r="204" spans="7:9">
+    <row r="204" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G204" s="53"/>
       <c r="H204" s="53"/>
       <c r="I204" s="53"/>
     </row>
-    <row r="205" spans="7:9">
+    <row r="205" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G205" s="53"/>
       <c r="H205" s="53"/>
       <c r="I205" s="53"/>
     </row>
-    <row r="206" spans="7:9">
+    <row r="206" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G206" s="53"/>
       <c r="H206" s="53"/>
       <c r="I206" s="53"/>
     </row>
-    <row r="207" spans="7:9">
+    <row r="207" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G207" s="53"/>
       <c r="H207" s="53"/>
       <c r="I207" s="53"/>
     </row>
-    <row r="208" spans="7:9">
+    <row r="208" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G208" s="53"/>
       <c r="H208" s="53"/>
       <c r="I208" s="53"/>
     </row>
-    <row r="209" spans="7:9">
+    <row r="209" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G209" s="53"/>
       <c r="H209" s="53"/>
       <c r="I209" s="53"/>
     </row>
-    <row r="210" spans="7:9">
+    <row r="210" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G210" s="53"/>
       <c r="H210" s="53"/>
       <c r="I210" s="53"/>
     </row>
-    <row r="211" spans="7:9">
+    <row r="211" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G211" s="53"/>
       <c r="H211" s="53"/>
       <c r="I211" s="53"/>
     </row>
-    <row r="212" spans="7:9">
+    <row r="212" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G212" s="53"/>
       <c r="H212" s="53"/>
       <c r="I212" s="53"/>
     </row>
-    <row r="213" spans="7:9">
+    <row r="213" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G213" s="53"/>
       <c r="H213" s="53"/>
       <c r="I213" s="53"/>
     </row>
-    <row r="214" spans="7:9">
+    <row r="214" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G214" s="53"/>
       <c r="H214" s="53"/>
       <c r="I214" s="53"/>
     </row>
-    <row r="215" spans="7:9">
+    <row r="215" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G215" s="53"/>
       <c r="H215" s="53"/>
       <c r="I215" s="53"/>
     </row>
-    <row r="216" spans="7:9">
+    <row r="216" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G216" s="53"/>
       <c r="H216" s="53"/>
       <c r="I216" s="53"/>
     </row>
-    <row r="217" spans="7:9">
+    <row r="217" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G217" s="53"/>
       <c r="H217" s="53"/>
       <c r="I217" s="53"/>
     </row>
-    <row r="218" spans="7:9">
+    <row r="218" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G218" s="53"/>
       <c r="H218" s="53"/>
       <c r="I218" s="53"/>
     </row>
-    <row r="219" spans="7:9">
+    <row r="219" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G219" s="53"/>
       <c r="H219" s="53"/>
       <c r="I219" s="53"/>
     </row>
-    <row r="220" spans="7:9">
+    <row r="220" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G220" s="53"/>
       <c r="H220" s="53"/>
       <c r="I220" s="53"/>
     </row>
-    <row r="221" spans="7:9">
+    <row r="221" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G221" s="53"/>
       <c r="H221" s="53"/>
       <c r="I221" s="53"/>
     </row>
-    <row r="222" spans="7:9">
+    <row r="222" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G222" s="53"/>
       <c r="H222" s="53"/>
       <c r="I222" s="53"/>
     </row>
-    <row r="223" spans="7:9">
+    <row r="223" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G223" s="53"/>
       <c r="H223" s="53"/>
       <c r="I223" s="53"/>
     </row>
-    <row r="224" spans="7:9">
+    <row r="224" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G224" s="53"/>
       <c r="H224" s="53"/>
       <c r="I224" s="53"/>
     </row>
-    <row r="225" spans="7:9">
+    <row r="225" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G225" s="53"/>
       <c r="H225" s="53"/>
       <c r="I225" s="53"/>
     </row>
-    <row r="226" spans="7:9">
+    <row r="226" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G226" s="53"/>
       <c r="H226" s="53"/>
       <c r="I226" s="53"/>
     </row>
-    <row r="227" spans="7:9">
+    <row r="227" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G227" s="53"/>
       <c r="H227" s="53"/>
       <c r="I227" s="53"/>
     </row>
-    <row r="228" spans="7:9">
+    <row r="228" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G228" s="53"/>
       <c r="H228" s="53"/>
       <c r="I228" s="53"/>
     </row>
-    <row r="229" spans="7:9">
+    <row r="229" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G229" s="53"/>
       <c r="H229" s="53"/>
       <c r="I229" s="53"/>
     </row>
-    <row r="230" spans="7:9">
+    <row r="230" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G230" s="53"/>
       <c r="H230" s="53"/>
       <c r="I230" s="53"/>
     </row>
-    <row r="231" spans="7:9">
+    <row r="231" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G231" s="53"/>
       <c r="H231" s="53"/>
       <c r="I231" s="53"/>
     </row>
-    <row r="232" spans="7:9">
+    <row r="232" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G232" s="53"/>
       <c r="H232" s="53"/>
       <c r="I232" s="53"/>
     </row>
-    <row r="233" spans="7:9">
+    <row r="233" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G233" s="53"/>
       <c r="H233" s="53"/>
       <c r="I233" s="53"/>
     </row>
-    <row r="234" spans="7:9">
+    <row r="234" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G234" s="53"/>
       <c r="H234" s="53"/>
       <c r="I234" s="53"/>
     </row>
-    <row r="235" spans="7:9">
+    <row r="235" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G235" s="53"/>
       <c r="H235" s="53"/>
       <c r="I235" s="53"/>
     </row>
-    <row r="236" spans="7:9">
+    <row r="236" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G236" s="53"/>
       <c r="H236" s="53"/>
       <c r="I236" s="53"/>
     </row>
-    <row r="237" spans="7:9">
+    <row r="237" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G237" s="53"/>
       <c r="H237" s="53"/>
       <c r="I237" s="53"/>
     </row>
-    <row r="238" spans="7:9">
+    <row r="238" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G238" s="53"/>
       <c r="H238" s="53"/>
       <c r="I238" s="53"/>
     </row>
-    <row r="239" spans="7:9">
+    <row r="239" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G239" s="53"/>
       <c r="H239" s="53"/>
       <c r="I239" s="53"/>
     </row>
-    <row r="240" spans="7:9">
+    <row r="240" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G240" s="53"/>
       <c r="H240" s="53"/>
       <c r="I240" s="53"/>
     </row>
-    <row r="241" spans="7:9">
+    <row r="241" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G241" s="53"/>
       <c r="H241" s="53"/>
       <c r="I241" s="53"/>
     </row>
-    <row r="242" spans="7:9">
+    <row r="242" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G242" s="53"/>
       <c r="H242" s="53"/>
       <c r="I242" s="53"/>
     </row>
-    <row r="243" spans="7:9">
+    <row r="243" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G243" s="53"/>
       <c r="H243" s="53"/>
       <c r="I243" s="53"/>
     </row>
-    <row r="244" spans="7:9">
+    <row r="244" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G244" s="53"/>
       <c r="H244" s="53"/>
       <c r="I244" s="53"/>
     </row>
-    <row r="245" spans="7:9">
+    <row r="245" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G245" s="53"/>
       <c r="H245" s="53"/>
       <c r="I245" s="53"/>
     </row>
-    <row r="246" spans="7:9">
+    <row r="246" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G246" s="53"/>
       <c r="H246" s="53"/>
       <c r="I246" s="53"/>
     </row>
-    <row r="247" spans="7:9">
+    <row r="247" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G247" s="53"/>
       <c r="H247" s="53"/>
       <c r="I247" s="53"/>
     </row>
-    <row r="248" spans="7:9">
+    <row r="248" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G248" s="53"/>
       <c r="H248" s="53"/>
       <c r="I248" s="53"/>
     </row>
-    <row r="249" spans="7:9">
+    <row r="249" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G249" s="53"/>
       <c r="H249" s="53"/>
       <c r="I249" s="53"/>
     </row>
-    <row r="250" spans="7:9">
+    <row r="250" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G250" s="53"/>
       <c r="H250" s="53"/>
       <c r="I250" s="53"/>
     </row>
-    <row r="251" spans="7:9">
+    <row r="251" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G251" s="53"/>
       <c r="H251" s="53"/>
       <c r="I251" s="53"/>
     </row>
-    <row r="252" spans="7:9">
+    <row r="252" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G252" s="53"/>
       <c r="H252" s="53"/>
       <c r="I252" s="53"/>
     </row>
-    <row r="253" spans="7:9">
+    <row r="253" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G253" s="53"/>
       <c r="H253" s="53"/>
       <c r="I253" s="53"/>
     </row>
-    <row r="254" spans="7:9">
+    <row r="254" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G254" s="53"/>
       <c r="H254" s="53"/>
       <c r="I254" s="53"/>
     </row>
-    <row r="255" spans="7:9">
+    <row r="255" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G255" s="53"/>
       <c r="H255" s="53"/>
       <c r="I255" s="53"/>
     </row>
-    <row r="256" spans="7:9">
+    <row r="256" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G256" s="53"/>
       <c r="H256" s="53"/>
       <c r="I256" s="53"/>
     </row>
-    <row r="257" spans="7:9">
+    <row r="257" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G257" s="53"/>
       <c r="H257" s="1"/>
       <c r="I257" s="1"/>
     </row>
-    <row r="258" spans="7:9">
+    <row r="258" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G258" s="53"/>
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>
     </row>
-    <row r="259" spans="7:9">
+    <row r="259" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G259" s="53"/>
       <c r="H259" s="1"/>
       <c r="I259" s="1"/>
     </row>
-    <row r="260" spans="7:9">
+    <row r="260" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G260" s="53"/>
       <c r="H260" s="1"/>
       <c r="I260" s="1"/>
     </row>
-    <row r="261" spans="7:9">
+    <row r="261" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G261" s="53"/>
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
     </row>
-    <row r="262" spans="7:9">
+    <row r="262" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G262" s="53"/>
       <c r="H262" s="1"/>
       <c r="I262" s="1"/>
     </row>
-    <row r="263" spans="7:9">
+    <row r="263" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G263" s="53"/>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
     </row>
-    <row r="264" spans="7:9">
+    <row r="264" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G264" s="53"/>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
     </row>
-    <row r="265" spans="7:9">
+    <row r="265" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G265" s="53"/>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
     </row>
-    <row r="266" spans="7:9">
+    <row r="266" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G266" s="53"/>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
     </row>
-    <row r="267" spans="7:9">
+    <row r="267" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G267" s="53"/>
     </row>
-    <row r="268" spans="7:9">
+    <row r="268" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G268" s="53"/>
     </row>
-    <row r="269" spans="7:9">
+    <row r="269" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G269" s="53"/>
     </row>
-    <row r="270" spans="7:9">
+    <row r="270" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G270" s="53"/>
     </row>
-    <row r="271" spans="7:9">
+    <row r="271" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G271" s="53"/>
     </row>
-    <row r="272" spans="7:9">
+    <row r="272" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G272" s="53"/>
     </row>
-    <row r="273" spans="7:7">
+    <row r="273" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G273" s="53"/>
     </row>
-    <row r="274" spans="7:7">
+    <row r="274" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G274" s="53"/>
     </row>
-    <row r="275" spans="7:7">
+    <row r="275" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G275" s="53"/>
     </row>
-    <row r="276" spans="7:7">
+    <row r="276" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G276" s="53"/>
     </row>
-    <row r="277" spans="7:7">
+    <row r="277" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G277" s="53"/>
     </row>
-    <row r="278" spans="7:7">
+    <row r="278" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G278" s="53"/>
     </row>
-    <row r="279" spans="7:7">
+    <row r="279" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G279" s="53"/>
     </row>
-    <row r="280" spans="7:7">
+    <row r="280" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G280" s="53"/>
     </row>
-    <row r="281" spans="7:7">
+    <row r="281" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G281" s="53"/>
     </row>
-    <row r="282" spans="7:7">
+    <row r="282" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G282" s="53"/>
     </row>
-    <row r="283" spans="7:7">
+    <row r="283" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G283" s="53"/>
     </row>
-    <row r="284" spans="7:7">
+    <row r="284" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G284" s="53"/>
     </row>
-    <row r="285" spans="7:7">
+    <row r="285" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G285" s="53"/>
     </row>
-    <row r="286" spans="7:7">
+    <row r="286" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G286" s="53"/>
     </row>
-    <row r="287" spans="7:7">
+    <row r="287" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G287" s="53"/>
     </row>
-    <row r="288" spans="7:7">
+    <row r="288" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G288" s="53"/>
     </row>
-    <row r="289" spans="7:7">
+    <row r="289" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G289" s="53"/>
     </row>
-    <row r="290" spans="7:7">
+    <row r="290" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G290" s="53"/>
     </row>
-    <row r="291" spans="7:7">
+    <row r="291" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G291" s="53"/>
     </row>
-    <row r="292" spans="7:7">
+    <row r="292" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G292" s="53"/>
     </row>
-    <row r="293" spans="7:7">
+    <row r="293" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G293" s="53"/>
     </row>
-    <row r="294" spans="7:7">
+    <row r="294" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G294" s="53"/>
     </row>
-    <row r="295" spans="7:7">
+    <row r="295" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G295" s="53"/>
     </row>
-    <row r="296" spans="7:7">
+    <row r="296" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G296" s="53"/>
     </row>
-    <row r="297" spans="7:7">
+    <row r="297" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G297" s="53"/>
     </row>
-    <row r="298" spans="7:7">
+    <row r="298" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G298" s="53"/>
     </row>
-    <row r="299" spans="7:7">
+    <row r="299" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G299" s="53"/>
     </row>
-    <row r="300" spans="7:7">
+    <row r="300" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G300" s="53"/>
     </row>
-    <row r="301" spans="7:7">
+    <row r="301" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G301" s="53"/>
     </row>
-    <row r="302" spans="7:7">
+    <row r="302" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G302" s="53"/>
     </row>
-    <row r="303" spans="7:7">
+    <row r="303" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G303" s="53"/>
     </row>
-    <row r="304" spans="7:7">
+    <row r="304" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G304" s="53"/>
     </row>
-    <row r="305" spans="7:7">
+    <row r="305" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G305" s="53"/>
     </row>
-    <row r="306" spans="7:7">
+    <row r="306" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G306" s="53"/>
     </row>
-    <row r="307" spans="7:7">
+    <row r="307" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G307" s="53"/>
     </row>
-    <row r="308" spans="7:7">
+    <row r="308" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G308" s="53"/>
     </row>
-    <row r="309" spans="7:7">
+    <row r="309" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G309" s="53"/>
     </row>
-    <row r="310" spans="7:7">
+    <row r="310" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G310" s="53"/>
     </row>
-    <row r="311" spans="7:7">
+    <row r="311" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G311" s="53"/>
     </row>
-    <row r="312" spans="7:7">
+    <row r="312" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G312" s="53"/>
     </row>
-    <row r="313" spans="7:7">
+    <row r="313" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G313" s="53"/>
     </row>
-    <row r="314" spans="7:7">
+    <row r="314" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G314" s="53"/>
     </row>
-    <row r="315" spans="7:7">
+    <row r="315" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G315" s="53"/>
     </row>
-    <row r="316" spans="7:7">
+    <row r="316" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G316" s="53"/>
     </row>
-    <row r="317" spans="7:7">
+    <row r="317" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G317" s="53"/>
     </row>
-    <row r="318" spans="7:7">
+    <row r="318" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G318" s="53"/>
     </row>
-    <row r="319" spans="7:7">
+    <row r="319" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G319" s="53"/>
     </row>
-    <row r="320" spans="7:7">
+    <row r="320" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G320" s="53"/>
     </row>
-    <row r="321" spans="7:7">
+    <row r="321" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G321" s="53"/>
     </row>
-    <row r="322" spans="7:7">
+    <row r="322" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G322" s="53"/>
     </row>
-    <row r="323" spans="7:7">
+    <row r="323" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G323" s="53"/>
     </row>
-    <row r="324" spans="7:7">
+    <row r="324" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G324" s="53"/>
     </row>
-    <row r="325" spans="7:7">
+    <row r="325" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G325" s="53"/>
     </row>
-    <row r="326" spans="7:7">
+    <row r="326" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G326" s="53"/>
     </row>
-    <row r="327" spans="7:7">
+    <row r="327" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G327" s="53"/>
     </row>
-    <row r="328" spans="7:7">
+    <row r="328" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G328" s="53"/>
     </row>
-    <row r="329" spans="7:7">
+    <row r="329" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G329" s="53"/>
     </row>
-    <row r="330" spans="7:7">
+    <row r="330" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G330" s="53"/>
     </row>
-    <row r="331" spans="7:7">
+    <row r="331" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G331" s="53"/>
     </row>
-    <row r="332" spans="7:7">
+    <row r="332" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G332" s="53"/>
     </row>
-    <row r="333" spans="7:7">
+    <row r="333" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G333" s="53"/>
     </row>
-    <row r="334" spans="7:7">
+    <row r="334" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G334" s="53"/>
     </row>
-    <row r="335" spans="7:7">
+    <row r="335" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G335" s="53"/>
     </row>
-    <row r="336" spans="7:7">
+    <row r="336" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G336" s="53"/>
     </row>
-    <row r="337" spans="7:7">
+    <row r="337" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G337" s="53"/>
     </row>
-    <row r="338" spans="7:7">
+    <row r="338" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G338" s="53"/>
     </row>
-    <row r="339" spans="7:7">
+    <row r="339" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G339" s="53"/>
     </row>
-    <row r="340" spans="7:7">
+    <row r="340" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G340" s="53"/>
     </row>
-    <row r="341" spans="7:7">
+    <row r="341" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G341" s="53"/>
     </row>
-    <row r="342" spans="7:7">
+    <row r="342" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G342" s="53"/>
     </row>
-    <row r="343" spans="7:7">
+    <row r="343" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G343" s="53"/>
     </row>
-    <row r="344" spans="7:7">
+    <row r="344" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G344" s="53"/>
     </row>
-    <row r="345" spans="7:7">
+    <row r="345" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G345" s="53"/>
     </row>
-    <row r="346" spans="7:7">
+    <row r="346" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G346" s="53"/>
     </row>
-    <row r="347" spans="7:7">
+    <row r="347" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G347" s="53"/>
     </row>
-    <row r="348" spans="7:7">
+    <row r="348" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G348" s="53"/>
     </row>
-    <row r="349" spans="7:7">
+    <row r="349" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G349" s="53"/>
     </row>
-    <row r="350" spans="7:7">
+    <row r="350" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G350" s="53"/>
     </row>
-    <row r="351" spans="7:7">
+    <row r="351" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G351" s="53"/>
     </row>
-    <row r="352" spans="7:7">
+    <row r="352" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G352" s="53"/>
     </row>
-    <row r="353" spans="7:7">
+    <row r="353" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G353" s="53"/>
     </row>
-    <row r="354" spans="7:7">
+    <row r="354" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G354" s="53"/>
     </row>
-    <row r="355" spans="7:7">
+    <row r="355" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G355" s="53"/>
     </row>
-    <row r="356" spans="7:7">
+    <row r="356" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G356" s="53"/>
     </row>
-    <row r="357" spans="7:7">
+    <row r="357" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G357" s="53"/>
     </row>
-    <row r="358" spans="7:7">
+    <row r="358" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G358" s="53"/>
     </row>
-    <row r="359" spans="7:7">
+    <row r="359" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G359" s="53"/>
     </row>
-    <row r="360" spans="7:7">
+    <row r="360" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G360" s="53"/>
     </row>
-    <row r="361" spans="7:7">
+    <row r="361" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G361" s="53"/>
     </row>
-    <row r="362" spans="7:7">
+    <row r="362" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G362" s="53"/>
     </row>
-    <row r="363" spans="7:7">
+    <row r="363" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G363" s="53"/>
     </row>
-    <row r="364" spans="7:7">
+    <row r="364" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G364" s="53"/>
     </row>
-    <row r="365" spans="7:7">
+    <row r="365" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G365" s="53"/>
     </row>
-    <row r="366" spans="7:7">
+    <row r="366" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G366" s="53"/>
     </row>
-    <row r="367" spans="7:7">
+    <row r="367" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G367" s="53"/>
     </row>
-    <row r="368" spans="7:7">
+    <row r="368" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G368" s="53"/>
     </row>
-    <row r="369" spans="7:7">
+    <row r="369" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G369" s="53"/>
     </row>
-    <row r="370" spans="7:7">
+    <row r="370" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G370" s="53"/>
     </row>
-    <row r="371" spans="7:7">
+    <row r="371" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G371" s="53"/>
     </row>
-    <row r="372" spans="7:7">
+    <row r="372" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G372" s="53"/>
     </row>
-    <row r="373" spans="7:7">
+    <row r="373" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G373" s="53"/>
     </row>
-    <row r="374" spans="7:7">
+    <row r="374" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G374" s="53"/>
     </row>
-    <row r="375" spans="7:7">
+    <row r="375" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G375" s="53"/>
     </row>
-    <row r="376" spans="7:7">
+    <row r="376" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G376" s="53"/>
     </row>
-    <row r="377" spans="7:7">
+    <row r="377" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G377" s="53"/>
     </row>
-    <row r="378" spans="7:7">
+    <row r="378" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G378" s="53"/>
     </row>
-    <row r="379" spans="7:7">
+    <row r="379" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G379" s="53"/>
     </row>
-    <row r="380" spans="7:7">
+    <row r="380" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G380" s="53"/>
     </row>
-    <row r="381" spans="7:7">
+    <row r="381" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G381" s="53"/>
     </row>
-    <row r="382" spans="7:7">
+    <row r="382" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G382" s="53"/>
     </row>
-    <row r="383" spans="7:7">
+    <row r="383" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G383" s="53"/>
     </row>
-    <row r="384" spans="7:7">
+    <row r="384" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G384" s="53"/>
     </row>
-    <row r="385" spans="7:7">
+    <row r="385" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G385" s="53"/>
     </row>
-    <row r="386" spans="7:7">
+    <row r="386" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G386" s="53"/>
     </row>
-    <row r="387" spans="7:7">
+    <row r="387" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G387" s="53"/>
     </row>
-    <row r="388" spans="7:7">
+    <row r="388" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G388" s="53"/>
     </row>
-    <row r="389" spans="7:7">
+    <row r="389" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G389" s="53"/>
     </row>
-    <row r="390" spans="7:7">
+    <row r="390" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G390" s="53"/>
     </row>
-    <row r="391" spans="7:7">
+    <row r="391" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G391" s="53"/>
     </row>
-    <row r="392" spans="7:7">
+    <row r="392" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G392" s="53"/>
     </row>
-    <row r="393" spans="7:7">
+    <row r="393" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G393" s="53"/>
     </row>
-    <row r="394" spans="7:7">
+    <row r="394" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G394" s="53"/>
     </row>
-    <row r="395" spans="7:7">
+    <row r="395" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G395" s="53"/>
     </row>
-    <row r="396" spans="7:7">
+    <row r="396" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G396" s="53"/>
     </row>
-    <row r="397" spans="7:7">
+    <row r="397" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G397" s="53"/>
     </row>
-    <row r="398" spans="7:7">
+    <row r="398" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G398" s="53"/>
     </row>
-    <row r="399" spans="7:7">
+    <row r="399" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G399" s="53"/>
     </row>
-    <row r="400" spans="7:7">
+    <row r="400" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G400" s="53"/>
     </row>
-    <row r="401" spans="7:7">
+    <row r="401" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G401" s="53"/>
     </row>
-    <row r="402" spans="7:7">
+    <row r="402" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G402" s="53"/>
     </row>
-    <row r="403" spans="7:7">
+    <row r="403" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G403" s="53"/>
     </row>
-    <row r="404" spans="7:7">
+    <row r="404" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G404" s="53"/>
     </row>
   </sheetData>
@@ -11759,66 +12059,58 @@
     <mergeCell ref="M3:M4"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C84:D114 C115:C121">
-    <cfRule type="cellIs" dxfId="15" priority="179" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="181" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="182" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G96:H98 G123:G1048576 G116:H116 H99:H115">
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="greaterThan">
+  <conditionalFormatting sqref="G123:G1048576">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G96:H122">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:I95">
-    <cfRule type="cellIs" dxfId="11" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="21" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="22" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H131:I266 I129:I130">
-    <cfRule type="cellIs" dxfId="9" priority="177" operator="greaterThan">
+  <conditionalFormatting sqref="H123:H130">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="178" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I96:I128">
-    <cfRule type="cellIs" dxfId="7" priority="25" operator="greaterThan">
+  <conditionalFormatting sqref="H131:I266">
+    <cfRule type="cellIs" dxfId="3" priority="179" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="26" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="180" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G99:G115">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
+  <conditionalFormatting sqref="I96:I130">
+    <cfRule type="cellIs" dxfId="1" priority="27" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G117:H117">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G118:H122 H123:H130">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="28" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11830,7 +12122,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:D17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="2" width="26.28515625" customWidth="1"/>
@@ -11838,101 +12130,101 @@
     <col min="4" max="4" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" s="62" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="C1" s="63" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="54" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="D2" s="54"/>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="54" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="D3" s="54"/>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="54" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="D4" s="54"/>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="54" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="D5" s="54"/>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="54" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="D6" s="54"/>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="54" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="D7" s="54"/>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="54" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="D8" s="54"/>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="54" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="54" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="D10" s="54"/>
     </row>
-    <row r="17" spans="3:3">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" s="28"/>
     </row>
   </sheetData>

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="501" documentId="8_{0F9471C2-95A1-4CF9-8CFE-1EF73F0B2DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FCB5A87-9713-4693-8DC4-F62A4D1F5DDC}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_C0E26E8C2FF3658481E6AE6DE74C74B31A2D8B7D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87AB67AE-89AD-4869-A5B6-44A3B39CBF8F}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -25,11 +25,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Itaú!$C$4:$Q$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NuBank!$C$5:$Q$128</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -46,17 +43,65 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="306">
+  <si>
+    <t>Stella</t>
+  </si>
+  <si>
+    <t>Guilherme</t>
+  </si>
+  <si>
+    <t>Cartão Itaú</t>
+  </si>
+  <si>
+    <t>Cartão NuBank</t>
+  </si>
+  <si>
+    <t>Contas</t>
+  </si>
+  <si>
+    <t>Aluguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Vivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Luz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Água</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Gás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Verisure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Seguranças+Câmeras+Seguro+Edilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Recolhimento INSS</t>
+  </si>
+  <si>
+    <t>Stella tem que transferir:</t>
+  </si>
+  <si>
+    <t>Valor fixado (Stella)</t>
+  </si>
+  <si>
+    <t>Data de fixação</t>
+  </si>
+  <si>
+    <t>Status pagamento Stella</t>
+  </si>
+  <si>
+    <t>Aguardando</t>
+  </si>
   <si>
     <t>Valor para o mês</t>
   </si>
   <si>
-    <t>Guilherme</t>
-  </si>
-  <si>
-    <t>Stella</t>
-  </si>
-  <si>
     <t>Salário</t>
   </si>
   <si>
@@ -66,36 +111,15 @@
     <t>Resto o mês anterior</t>
   </si>
   <si>
-    <t>Cartão Itaú</t>
-  </si>
-  <si>
-    <t>Cartão NuBank</t>
-  </si>
-  <si>
     <t>Compensasão no NuBank</t>
   </si>
   <si>
-    <t>Contas</t>
-  </si>
-  <si>
     <t xml:space="preserve">        Aluguel</t>
   </si>
   <si>
     <t xml:space="preserve">        Internet</t>
   </si>
   <si>
-    <t xml:space="preserve">        Luz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Água</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Gás</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Verisure</t>
-  </si>
-  <si>
     <t xml:space="preserve">        Seguranças+Câmera+Seguro+Edilson</t>
   </si>
   <si>
@@ -117,30 +141,6 @@
     <t xml:space="preserve">       Seguro</t>
   </si>
   <si>
-    <t>Aluguel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Vivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Seguranças+Câmeras+Seguro+Edilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Recolhimento INSS</t>
-  </si>
-  <si>
-    <t>Stella tem que transferir:</t>
-  </si>
-  <si>
-    <t>Valor fixado (Stella)</t>
-  </si>
-  <si>
-    <t>Data de fixação</t>
-  </si>
-  <si>
-    <t>Status pagamento Stella</t>
-  </si>
-  <si>
     <t>Itaú Total</t>
   </si>
   <si>
@@ -585,6 +585,36 @@
     <t>Pagamento Cobase Rennala e Quero-Quero</t>
   </si>
   <si>
+    <t>Janta Aniversário Stella</t>
+  </si>
+  <si>
+    <t>Adiantamento Parcelas Blood of the Dawnalker</t>
+  </si>
+  <si>
+    <t>Pagamento Janta Aniversário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagamento Adiantamento Dawnwalker </t>
+  </si>
+  <si>
+    <t>Bonfas</t>
+  </si>
+  <si>
+    <t>GAsolina</t>
+  </si>
+  <si>
+    <t>Mr Jones</t>
+  </si>
+  <si>
+    <t>Uber Scanntech</t>
+  </si>
+  <si>
+    <t>Pagamento Mr Jones e Bonfas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUtros </t>
+  </si>
+  <si>
     <t>Vivo</t>
   </si>
   <si>
@@ -849,27 +879,33 @@
     <t>Restituição IR</t>
   </si>
   <si>
+    <t>Psicóloga Atrasada</t>
+  </si>
+  <si>
+    <t>Custos Rennala</t>
+  </si>
+  <si>
+    <t>Devolução Stella + Recolhimento</t>
+  </si>
+  <si>
     <t>Novembro</t>
   </si>
   <si>
-    <t>Psicóloga Atrasada</t>
-  </si>
-  <si>
-    <t>Custos Rennala</t>
-  </si>
-  <si>
-    <t>Devolução Stella + Recolhimento</t>
-  </si>
-  <si>
     <t>Custos Rennala 2</t>
   </si>
   <si>
     <t>Dezembro</t>
   </si>
   <si>
+    <t>Janta Anivsersário</t>
+  </si>
+  <si>
     <t>Ilumeo Dezembro - 3º PPT</t>
   </si>
   <si>
+    <t>mr Jones e bonfas</t>
+  </si>
+  <si>
     <t>Segunda Parcela 13º</t>
   </si>
   <si>
@@ -925,24 +961,6 @@
   </si>
   <si>
     <t>Dera</t>
-  </si>
-  <si>
-    <t>Janta Aniversário Stella</t>
-  </si>
-  <si>
-    <t>Adiantamento Parcelas Blood of the Dawnalker</t>
-  </si>
-  <si>
-    <t>Pagamento Janta Aniversário</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagamento Adiantamento Dawnwalker </t>
-  </si>
-  <si>
-    <t>Janta Anivsersário</t>
-  </si>
-  <si>
-    <t>Recebido</t>
   </si>
 </sst>
 </file>
@@ -954,7 +972,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1062,6 +1080,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1235,7 +1261,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1418,10 +1444,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1430,6 +1456,9 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1712,10 +1741,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
@@ -1893,78 +1918,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:F41"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="76" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="77"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C25+C26+C7+C27</f>
-        <v>1851.9222380952388</v>
+        <v>1717.3872380952389</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E25+E26</f>
-        <v>1794.9891666666663</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+        <v>1898.7241666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C5" s="8">
-        <v>10400</v>
+        <v>10528</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="8">
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-8970.5777619047622</v>
+        <v>-9233.112761904762</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-8205.0108333333337</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+        <v>-8101.2758333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="9"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8" s="8">
         <f>Itaú!E2</f>
@@ -1976,37 +2001,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>6360.0760952380942</v>
+        <v>6622.6110952380941</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>2342.6708333333331</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+        <v>2488.935833333333</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="10" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>6360.0760952380942</v>
+        <v>6622.6110952380941</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>2342.6708333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+        <v>2488.935833333333</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" s="8">
         <f>Contas!B6</f>
@@ -2015,12 +2040,12 @@
       <c r="D11" s="9"/>
       <c r="E11" s="8">
         <f>Contas!B9</f>
-        <v>5862.34</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+        <v>5612.34</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C12" s="14">
         <f>Contas!K3</f>
@@ -2032,9 +2057,9 @@
         <v>1617.835</v>
       </c>
     </row>
-    <row r="13" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C13" s="14">
         <f>Contas!K4</f>
@@ -2046,9 +2071,9 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C14" s="14">
         <f>Contas!K5</f>
@@ -2061,9 +2086,9 @@
       </c>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C15" s="14">
         <f>Contas!K6</f>
@@ -2075,9 +2100,9 @@
         <v>40.619999999999997</v>
       </c>
     </row>
-    <row r="16" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C16" s="14">
         <f>Contas!K7</f>
@@ -2089,9 +2114,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C17" s="14">
         <f>Contas!K8</f>
@@ -2103,9 +2128,9 @@
         <v>112.38500000000001</v>
       </c>
     </row>
-    <row r="18" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
         <f>Contas!$K9+Contas!$K13</f>
@@ -2117,7 +2142,7 @@
         <v>333.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="str">
         <f>Contas!$D10</f>
         <v>Cartão Itaú da Stella</v>
@@ -2129,7 +2154,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="str">
         <f>Contas!$D11</f>
         <v>Recolhimento INSS</v>
@@ -2138,10 +2163,10 @@
       <c r="D20" s="15"/>
       <c r="E20" s="14">
         <f>Contas!K11</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B21" s="13" t="str">
         <f>Contas!$D12</f>
         <v>Empréstimo</v>
@@ -2153,37 +2178,37 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B22" s="17" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C22" s="18"/>
       <c r="D22" s="19"/>
       <c r="E22" s="18"/>
     </row>
-    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B23" s="13"/>
       <c r="C23" s="14"/>
       <c r="D23" s="15"/>
       <c r="E23" s="14"/>
     </row>
-    <row r="24" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B24" s="13"/>
       <c r="C24" s="14"/>
       <c r="D24" s="15"/>
       <c r="E24" s="14"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="9"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C26" s="8">
         <f>SUM(C28:C39)</f>
@@ -2195,9 +2220,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="13" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C27" s="8">
         <f>(338/4)*5</f>
@@ -2206,9 +2231,9 @@
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B28" s="13" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C28" s="14" t="str">
         <f>IF('NuConta e Poupança'!M5="Sim",'NuConta e Poupança'!N5,"")</f>
@@ -2217,15 +2242,15 @@
       <c r="D28" s="15"/>
       <c r="E28" s="14"/>
     </row>
-    <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B29" s="13" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="20"/>
       <c r="E29" s="21"/>
     </row>
-    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B30" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L7</f>
         <v xml:space="preserve">       </v>
@@ -2237,7 +2262,7 @@
       <c r="D30" s="20"/>
       <c r="E30" s="21"/>
     </row>
-    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B31" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L8</f>
         <v xml:space="preserve">       </v>
@@ -2249,7 +2274,7 @@
       <c r="D31" s="20"/>
       <c r="E31" s="21"/>
     </row>
-    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B32" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L9</f>
         <v xml:space="preserve">       </v>
@@ -2261,7 +2286,7 @@
       <c r="D32" s="20"/>
       <c r="E32" s="21"/>
     </row>
-    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B33" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L10</f>
         <v xml:space="preserve">       </v>
@@ -2273,7 +2298,7 @@
       <c r="D33" s="20"/>
       <c r="E33" s="21"/>
     </row>
-    <row r="34" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L12</f>
         <v xml:space="preserve">       </v>
@@ -2285,7 +2310,7 @@
       <c r="D34" s="20"/>
       <c r="E34" s="21"/>
     </row>
-    <row r="35" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B35" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L13</f>
         <v xml:space="preserve">       </v>
@@ -2297,7 +2322,7 @@
       <c r="D35" s="20"/>
       <c r="E35" s="21"/>
     </row>
-    <row r="36" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B36" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L14</f>
         <v xml:space="preserve">       </v>
@@ -2309,7 +2334,7 @@
       <c r="D36" s="20"/>
       <c r="E36" s="21"/>
     </row>
-    <row r="37" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B37" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L15</f>
         <v xml:space="preserve">       </v>
@@ -2321,7 +2346,7 @@
       <c r="D37" s="20"/>
       <c r="E37" s="21"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L16</f>
         <v xml:space="preserve">       </v>
@@ -2334,7 +2359,7 @@
       <c r="E38" s="21"/>
       <c r="F38" s="16"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L17</f>
         <v xml:space="preserve">       </v>
@@ -2347,7 +2372,7 @@
       <c r="E39" s="21"/>
       <c r="F39" s="16"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L21</f>
         <v xml:space="preserve">       </v>
@@ -2359,7 +2384,7 @@
       <c r="D40" s="20"/>
       <c r="E40" s="21"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L22</f>
         <v xml:space="preserve">       </v>
@@ -2383,28 +2408,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:D24"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="31.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" ht="39" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="22"/>
       <c r="C2" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="7" t="s">
         <v>2</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="7" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="8">
         <f>Saldo!E8</f>
@@ -2415,57 +2440,57 @@
         <v>40.161666666666669</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>2342.6708333333331</v>
+        <v>2488.935833333333</v>
       </c>
       <c r="D4" s="24">
         <f>Saldo!C9+D5</f>
-        <v>6360.0760952380942</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+        <v>6622.6110952380941</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="13"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="13"/>
       <c r="C7" s="8"/>
       <c r="D7" s="24"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="13"/>
       <c r="C8" s="8"/>
       <c r="D8" s="24"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="13"/>
       <c r="C9" s="8"/>
       <c r="D9" s="24"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" s="8">
         <f>SUM(C11,C13:C18)</f>
-        <v>3348.34</v>
+        <v>3098.34</v>
       </c>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C11" s="14">
         <f>Saldo!E12</f>
@@ -2473,9 +2498,9 @@
       </c>
       <c r="D11" s="13"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B12" s="25" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C12" s="26">
         <f>Contas!K4</f>
@@ -2483,9 +2508,9 @@
       </c>
       <c r="D12" s="13"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" s="14">
         <f>Contas!K5</f>
@@ -2493,9 +2518,9 @@
       </c>
       <c r="D13" s="13"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C14" s="14">
         <f>Contas!K6</f>
@@ -2503,9 +2528,9 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C15" s="14">
         <f>Contas!K7</f>
@@ -2513,9 +2538,9 @@
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C16" s="14">
         <f>Contas!K8</f>
@@ -2523,9 +2548,9 @@
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C17" s="14">
         <f>Saldo!E18</f>
@@ -2533,54 +2558,56 @@
       </c>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C18" s="14">
         <f>Saldo!E20</f>
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="13"/>
       <c r="C19" s="14"/>
       <c r="D19" s="13"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="10" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C20" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>5691.0108333333337</v>
+        <v>5587.2758333333331</v>
       </c>
       <c r="D20" s="27"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="11"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="C22" s="80">
+        <v>5587.2758333333331</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C23" s="71">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C24" s="71" t="s">
-        <v>298</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2595,36 +2622,36 @@
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
   <dimension ref="C1:Q67"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="35.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="41" customWidth="1"/>
-    <col min="5" max="6" width="22.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" customWidth="1"/>
-    <col min="8" max="9" width="13.5703125" customWidth="1"/>
+    <col min="5" max="6" width="22.5546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.5546875" customWidth="1"/>
+    <col min="8" max="9" width="13.5546875" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" customWidth="1"/>
-    <col min="12" max="16" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" customWidth="1"/>
+    <col min="12" max="16" width="13.5546875" customWidth="1"/>
     <col min="17" max="17" width="17" style="2" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D1" s="29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D2" s="31">
         <f>SUM(L5:L21)</f>
         <v>40.161666666666669</v>
@@ -2642,59 +2669,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="3:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M4" s="34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O4" s="33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P4" s="33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q4" s="34" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="69" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="37" t="s">
         <v>1</v>
@@ -2709,10 +2736,10 @@
         <v>240.97</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L5" s="38">
         <f t="shared" ref="L5:L15" si="1">I5/N5</f>
@@ -2737,7 +2764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="37"/>
       <c r="D6" s="36"/>
       <c r="E6" s="37"/>
@@ -2769,7 +2796,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="35"/>
       <c r="D7" s="36"/>
       <c r="E7" s="37"/>
@@ -2798,7 +2825,7 @@
       <c r="P7" s="35"/>
       <c r="Q7" s="37"/>
     </row>
-    <row r="8" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="35"/>
       <c r="D8" s="36"/>
       <c r="E8" s="37"/>
@@ -2827,7 +2854,7 @@
       <c r="P8" s="35"/>
       <c r="Q8" s="37"/>
     </row>
-    <row r="9" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="35"/>
       <c r="D9" s="36"/>
       <c r="E9" s="37"/>
@@ -2856,7 +2883,7 @@
       <c r="P9" s="35"/>
       <c r="Q9" s="37"/>
     </row>
-    <row r="10" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="35"/>
       <c r="D10" s="36"/>
       <c r="E10" s="37"/>
@@ -2888,7 +2915,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="35"/>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
@@ -2917,7 +2944,7 @@
       <c r="P11" s="35"/>
       <c r="Q11" s="37"/>
     </row>
-    <row r="12" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="37"/>
       <c r="D12" s="36"/>
       <c r="E12" s="37"/>
@@ -2946,7 +2973,7 @@
       <c r="P12" s="35"/>
       <c r="Q12" s="37"/>
     </row>
-    <row r="13" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="37"/>
       <c r="D13" s="36"/>
       <c r="E13" s="37"/>
@@ -2975,7 +3002,7 @@
       <c r="P13" s="35"/>
       <c r="Q13" s="37"/>
     </row>
-    <row r="14" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="37"/>
       <c r="D14" s="36"/>
       <c r="E14" s="37"/>
@@ -3004,7 +3031,7 @@
       <c r="P14" s="35"/>
       <c r="Q14" s="37"/>
     </row>
-    <row r="15" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="37"/>
       <c r="D15" s="36"/>
       <c r="E15" s="37"/>
@@ -3033,7 +3060,7 @@
       <c r="P15" s="35"/>
       <c r="Q15" s="37"/>
     </row>
-    <row r="16" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="37"/>
       <c r="D16" s="36"/>
       <c r="E16" s="37"/>
@@ -3050,7 +3077,7 @@
       <c r="P16" s="35"/>
       <c r="Q16" s="37"/>
     </row>
-    <row r="17" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="35"/>
       <c r="D17" s="36"/>
       <c r="E17" s="37"/>
@@ -3067,7 +3094,7 @@
       <c r="P17" s="35"/>
       <c r="Q17" s="37"/>
     </row>
-    <row r="18" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="35"/>
       <c r="D18" s="36"/>
       <c r="E18" s="37"/>
@@ -3084,7 +3111,7 @@
       <c r="P18" s="35"/>
       <c r="Q18" s="37"/>
     </row>
-    <row r="19" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -3095,198 +3122,198 @@
       <c r="O19" s="41"/>
       <c r="P19" s="41"/>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.3">
       <c r="H20" s="2"/>
       <c r="O20" s="42"/>
       <c r="P20" s="42"/>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.3">
       <c r="H21" s="2"/>
       <c r="O21" s="42"/>
       <c r="P21" s="42"/>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.3">
       <c r="H22" s="2"/>
       <c r="O22" s="42"/>
       <c r="P22" s="42"/>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O23" s="42"/>
       <c r="P23" s="42"/>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O24" s="42"/>
       <c r="P24" s="42"/>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O25" s="42"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O26" s="42"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O27" s="42"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O28" s="42"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O29" s="42"/>
       <c r="P29" s="42"/>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O30" s="42"/>
       <c r="P30" s="42"/>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O31" s="42"/>
       <c r="P31" s="42"/>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O32" s="42"/>
       <c r="P32" s="42"/>
     </row>
-    <row r="33" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O33" s="42"/>
       <c r="P33" s="42"/>
     </row>
-    <row r="34" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O34" s="42"/>
       <c r="P34" s="42"/>
     </row>
-    <row r="35" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O35" s="42"/>
       <c r="P35" s="42"/>
     </row>
-    <row r="36" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O36" s="42"/>
       <c r="P36" s="42"/>
     </row>
-    <row r="37" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O37" s="42"/>
       <c r="P37" s="42"/>
     </row>
-    <row r="38" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O38" s="42"/>
       <c r="P38" s="42"/>
     </row>
-    <row r="39" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O39" s="42"/>
       <c r="P39" s="42"/>
     </row>
-    <row r="40" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O40" s="42"/>
       <c r="P40" s="42"/>
     </row>
-    <row r="41" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O41" s="42"/>
       <c r="P41" s="42"/>
     </row>
-    <row r="42" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
     </row>
-    <row r="43" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O43" s="42"/>
       <c r="P43" s="42"/>
     </row>
-    <row r="44" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O44" s="42"/>
       <c r="P44" s="42"/>
     </row>
-    <row r="45" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O45" s="42"/>
       <c r="P45" s="42"/>
     </row>
-    <row r="46" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O46" s="42"/>
       <c r="P46" s="42"/>
     </row>
-    <row r="47" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O47" s="42"/>
       <c r="P47" s="42"/>
     </row>
-    <row r="48" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O48" s="42"/>
       <c r="P48" s="42"/>
     </row>
-    <row r="49" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O49" s="42"/>
       <c r="P49" s="42"/>
     </row>
-    <row r="50" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O50" s="42"/>
       <c r="P50" s="42"/>
     </row>
-    <row r="51" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O51" s="42"/>
       <c r="P51" s="42"/>
     </row>
-    <row r="52" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O52" s="42"/>
       <c r="P52" s="42"/>
     </row>
-    <row r="53" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O53" s="42"/>
       <c r="P53" s="42"/>
     </row>
-    <row r="54" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O54" s="42"/>
       <c r="P54" s="42"/>
     </row>
-    <row r="55" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O55" s="42"/>
       <c r="P55" s="42"/>
     </row>
-    <row r="56" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O56" s="42"/>
       <c r="P56" s="42"/>
     </row>
-    <row r="57" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O57" s="42"/>
       <c r="P57" s="42"/>
     </row>
-    <row r="58" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O58" s="42"/>
       <c r="P58" s="42"/>
     </row>
-    <row r="59" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O59" s="42"/>
       <c r="P59" s="42"/>
     </row>
-    <row r="60" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O60" s="42"/>
       <c r="P60" s="42"/>
     </row>
-    <row r="61" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O61" s="42"/>
       <c r="P61" s="42"/>
     </row>
-    <row r="62" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O62" s="42"/>
       <c r="P62" s="42"/>
     </row>
-    <row r="63" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O63" s="42"/>
       <c r="P63" s="42"/>
     </row>
-    <row r="64" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O64" s="42"/>
       <c r="P64" s="42"/>
     </row>
-    <row r="65" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O65" s="42"/>
       <c r="P65" s="42"/>
     </row>
-    <row r="66" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O66" s="42"/>
       <c r="P66" s="42"/>
     </row>
-    <row r="67" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O67" s="42"/>
       <c r="P67" s="42"/>
     </row>
@@ -3312,49 +3339,49 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="C1:Q128"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" customWidth="1"/>
-    <col min="5" max="7" width="20.5703125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" style="43" customWidth="1"/>
-    <col min="10" max="10" width="20.42578125" style="43" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" customWidth="1"/>
-    <col min="12" max="16" width="13.5703125" customWidth="1"/>
-    <col min="17" max="17" width="21.85546875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="36.5546875" customWidth="1"/>
+    <col min="5" max="7" width="20.5546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5546875" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" style="43" customWidth="1"/>
+    <col min="10" max="10" width="20.44140625" style="43" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" customWidth="1"/>
+    <col min="12" max="16" width="13.5546875" customWidth="1"/>
+    <col min="17" max="17" width="21.88671875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D1" s="44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" s="43"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D2" s="45">
         <f>SUM(L6:L266)</f>
-        <v>8927.176928571429</v>
+        <v>9219.6469285714302</v>
       </c>
       <c r="E2" s="32">
         <f>SUMIF($E$6:$E$266,E1,$M$6:$M$266)</f>
-        <v>6360.0760952380942</v>
+        <v>6622.6110952380941</v>
       </c>
       <c r="F2" s="32">
         <f>SUMIF($F$6:$F$266,F1,$M$6:$M$266)</f>
-        <v>2342.6708333333331</v>
+        <v>2488.935833333333</v>
       </c>
       <c r="G2" s="32">
         <f>SUMIF($G$6:$G$266,G1,$M$6:$M$266)</f>
@@ -3364,68 +3391,68 @@
       <c r="L2" s="43"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:17" x14ac:dyDescent="0.3">
       <c r="L3" s="43"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:17" x14ac:dyDescent="0.3">
       <c r="M4" s="43"/>
     </row>
-    <row r="5" spans="3:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="33"/>
       <c r="D5" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M5" s="34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N5" s="34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O5" s="33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P5" s="33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q5" s="34" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C6" s="35"/>
       <c r="D6" s="36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37">
@@ -3436,10 +3463,10 @@
         <v>359</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L6" s="38">
         <f t="shared" ref="L6:L37" si="1">I6/N6</f>
@@ -3464,10 +3491,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C7" s="35"/>
       <c r="D7" s="36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" s="37" t="s">
         <v>1</v>
@@ -3482,10 +3509,10 @@
         <v>258</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L7" s="38">
         <f t="shared" si="1"/>
@@ -3510,10 +3537,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C8" s="35"/>
       <c r="D8" s="66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" s="37" t="s">
         <v>1</v>
@@ -3528,10 +3555,10 @@
         <v>1909.3</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K8" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L8" s="38">
         <f t="shared" si="1"/>
@@ -3556,16 +3583,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C9" s="35"/>
       <c r="D9" s="66" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E9" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="37"/>
       <c r="H9" s="37">
@@ -3576,10 +3603,10 @@
         <v>725</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L9" s="38">
         <f t="shared" si="1"/>
@@ -3604,10 +3631,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C10" s="35"/>
       <c r="D10" s="66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>1</v>
@@ -3622,10 +3649,10 @@
         <v>659</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L10" s="38">
         <f t="shared" si="1"/>
@@ -3650,10 +3677,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C11" s="35"/>
       <c r="D11" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E11" s="37" t="s">
         <v>1</v>
@@ -3668,10 +3695,10 @@
         <v>2319.3000000000002</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L11" s="38">
         <f t="shared" si="1"/>
@@ -3696,10 +3723,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C12" s="35"/>
       <c r="D12" s="66" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E12" s="37" t="s">
         <v>1</v>
@@ -3714,10 +3741,10 @@
         <v>2000</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L12" s="38">
         <f t="shared" si="1"/>
@@ -3742,10 +3769,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C13" s="35"/>
       <c r="D13" s="66" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E13" s="37" t="s">
         <v>1</v>
@@ -3760,10 +3787,10 @@
         <v>372.43</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L13" s="38">
         <f t="shared" si="1"/>
@@ -3788,10 +3815,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C14" s="35"/>
       <c r="D14" s="66" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>1</v>
@@ -3807,10 +3834,10 @@
         <v>-773.04</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L14" s="38">
         <f t="shared" si="1"/>
@@ -3835,10 +3862,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C15" s="35"/>
       <c r="D15" s="66" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E15" s="37" t="s">
         <v>1</v>
@@ -3853,10 +3880,10 @@
         <v>531</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K15" s="38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L15" s="38">
         <f t="shared" si="1"/>
@@ -3881,14 +3908,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C16" s="35"/>
       <c r="D16" s="66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" s="37"/>
       <c r="F16" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="37"/>
       <c r="H16" s="37">
@@ -3899,10 +3926,10 @@
         <v>161.72999999999999</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L16" s="38">
         <f t="shared" si="1"/>
@@ -3927,10 +3954,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C17" s="35"/>
       <c r="D17" s="66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E17" s="37" t="s">
         <v>1</v>
@@ -3945,10 +3972,10 @@
         <v>72</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K17" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L17" s="38">
         <f t="shared" si="1"/>
@@ -3973,14 +4000,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C18" s="35"/>
       <c r="D18" s="65" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E18" s="37"/>
       <c r="F18" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" s="37"/>
       <c r="H18" s="37">
@@ -3991,10 +4018,10 @@
         <v>973.02</v>
       </c>
       <c r="J18" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L18" s="38">
         <f t="shared" si="1"/>
@@ -4019,10 +4046,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C19" s="35"/>
       <c r="D19" s="65" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E19" s="37" t="s">
         <v>1</v>
@@ -4037,10 +4064,10 @@
         <v>379</v>
       </c>
       <c r="J19" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K19" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L19" s="38">
         <f t="shared" si="1"/>
@@ -4065,10 +4092,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C20" s="35"/>
       <c r="D20" s="65" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>1</v>
@@ -4083,10 +4110,10 @@
         <v>297</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L20" s="38">
         <f t="shared" si="1"/>
@@ -4111,10 +4138,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C21" s="35"/>
       <c r="D21" s="65" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E21" s="37" t="s">
         <v>1</v>
@@ -4129,10 +4156,10 @@
         <v>326.99</v>
       </c>
       <c r="J21" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L21" s="38">
         <f t="shared" si="1"/>
@@ -4157,16 +4184,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C22" s="35"/>
       <c r="D22" s="70" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" s="37"/>
       <c r="H22" s="37">
@@ -4177,10 +4204,10 @@
         <v>209.94</v>
       </c>
       <c r="J22" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L22" s="38">
         <f t="shared" si="1"/>
@@ -4205,16 +4232,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C23" s="35"/>
       <c r="D23" s="70" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E23" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="37"/>
       <c r="H23" s="37">
@@ -4225,10 +4252,10 @@
         <v>249.5</v>
       </c>
       <c r="J23" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L23" s="38">
         <f t="shared" si="1"/>
@@ -4253,16 +4280,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C24" s="35"/>
       <c r="D24" s="70" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E24" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" s="37"/>
       <c r="H24" s="37">
@@ -4273,10 +4300,10 @@
         <v>-209.94</v>
       </c>
       <c r="J24" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L24" s="38">
         <f t="shared" si="1"/>
@@ -4301,16 +4328,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C25" s="35"/>
       <c r="D25" s="46" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E25" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="37"/>
       <c r="H25" s="37">
@@ -4321,10 +4348,10 @@
         <v>506</v>
       </c>
       <c r="J25" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L25" s="38">
         <f t="shared" si="1"/>
@@ -4346,10 +4373,10 @@
       </c>
       <c r="Q25" s="37"/>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C26" s="35"/>
       <c r="D26" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>1</v>
@@ -4364,10 +4391,10 @@
         <v>399.9</v>
       </c>
       <c r="J26" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L26" s="38">
         <f t="shared" si="1"/>
@@ -4392,10 +4419,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C27" s="35"/>
       <c r="D27" s="46" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E27" s="37" t="s">
         <v>1</v>
@@ -4410,10 +4437,10 @@
         <v>284</v>
       </c>
       <c r="J27" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L27" s="38">
         <f t="shared" si="1"/>
@@ -4438,10 +4465,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C28" s="35"/>
       <c r="D28" s="46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E28" s="37" t="s">
         <v>1</v>
@@ -4456,10 +4483,10 @@
         <v>500</v>
       </c>
       <c r="J28" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L28" s="38">
         <f t="shared" si="1"/>
@@ -4484,10 +4511,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C29" s="35"/>
       <c r="D29" s="46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>1</v>
@@ -4502,10 +4529,10 @@
         <v>300</v>
       </c>
       <c r="J29" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L29" s="38">
         <f t="shared" si="1"/>
@@ -4530,16 +4557,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C30" s="35"/>
       <c r="D30" s="36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30" s="37"/>
       <c r="H30" s="37">
@@ -4550,10 +4577,10 @@
         <v>1017.6</v>
       </c>
       <c r="J30" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L30" s="38">
         <f t="shared" si="1"/>
@@ -4578,10 +4605,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C31" s="35"/>
       <c r="D31" s="46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E31" s="37" t="s">
         <v>1</v>
@@ -4596,10 +4623,10 @@
         <v>1900</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L31" s="38">
         <f t="shared" si="1"/>
@@ -4624,10 +4651,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C32" s="35"/>
       <c r="D32" s="46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E32" s="37" t="s">
         <v>1</v>
@@ -4642,10 +4669,10 @@
         <v>474.33</v>
       </c>
       <c r="J32" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K32" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L32" s="38">
         <f t="shared" si="1"/>
@@ -4670,10 +4697,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C33" s="35"/>
       <c r="D33" s="46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E33" s="37" t="s">
         <v>1</v>
@@ -4688,10 +4715,10 @@
         <v>330</v>
       </c>
       <c r="J33" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L33" s="38">
         <f t="shared" si="1"/>
@@ -4716,16 +4743,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C34" s="35"/>
       <c r="D34" s="46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E34" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" s="37"/>
       <c r="H34" s="37">
@@ -4736,10 +4763,10 @@
         <v>1780</v>
       </c>
       <c r="J34" s="68" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K34" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L34" s="38">
         <f t="shared" si="1"/>
@@ -4764,10 +4791,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C35" s="35"/>
       <c r="D35" s="46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E35" s="37" t="s">
         <v>1</v>
@@ -4782,10 +4809,10 @@
         <v>286.39</v>
       </c>
       <c r="J35" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L35" s="38">
         <f t="shared" si="1"/>
@@ -4810,10 +4837,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C36" s="35"/>
       <c r="D36" s="46" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E36" s="37" t="s">
         <v>1</v>
@@ -4828,10 +4855,10 @@
         <v>1181.1400000000001</v>
       </c>
       <c r="J36" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L36" s="38">
         <f t="shared" si="1"/>
@@ -4856,16 +4883,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C37" s="35"/>
       <c r="D37" s="46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E37" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" s="37"/>
       <c r="H37" s="37">
@@ -4876,10 +4903,10 @@
         <v>224.24</v>
       </c>
       <c r="J37" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L37" s="38">
         <f t="shared" si="1"/>
@@ -4904,12 +4931,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C38" s="35" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D38" s="46" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>1</v>
@@ -4924,10 +4951,10 @@
         <v>279</v>
       </c>
       <c r="J38" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K38" s="38" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L38" s="38">
         <f t="shared" ref="L38:L69" si="7">I38/N38</f>
@@ -4952,16 +4979,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C39" s="35"/>
       <c r="D39" s="36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E39" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" s="37"/>
       <c r="H39" s="37">
@@ -4972,10 +4999,10 @@
         <v>22.45</v>
       </c>
       <c r="J39" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K39" s="37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L39" s="38">
         <f t="shared" si="7"/>
@@ -4998,16 +5025,16 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C40" s="35"/>
       <c r="D40" s="46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E40" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G40" s="37"/>
       <c r="H40" s="37">
@@ -5018,10 +5045,10 @@
         <v>60</v>
       </c>
       <c r="J40" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L40" s="38">
         <f t="shared" si="7"/>
@@ -5044,16 +5071,16 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C41" s="35"/>
       <c r="D41" s="36" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E41" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G41" s="37"/>
       <c r="H41" s="37">
@@ -5064,10 +5091,10 @@
         <v>395.54</v>
       </c>
       <c r="J41" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K41" s="37" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L41" s="38">
         <f t="shared" si="7"/>
@@ -5090,16 +5117,16 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C42" s="35"/>
       <c r="D42" s="36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E42" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G42" s="37"/>
       <c r="H42" s="37">
@@ -5110,10 +5137,10 @@
         <v>197</v>
       </c>
       <c r="J42" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L42" s="38">
         <f t="shared" si="7"/>
@@ -5136,16 +5163,16 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C43" s="35"/>
       <c r="D43" s="46" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E43" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G43" s="37"/>
       <c r="H43" s="37">
@@ -5156,10 +5183,10 @@
         <v>225</v>
       </c>
       <c r="J43" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K43" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L43" s="38">
         <f t="shared" si="7"/>
@@ -5182,16 +5209,16 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C44" s="35"/>
       <c r="D44" s="36" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E44" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G44" s="37"/>
       <c r="H44" s="37">
@@ -5202,10 +5229,10 @@
         <v>166.15</v>
       </c>
       <c r="J44" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L44" s="38">
         <f t="shared" si="7"/>
@@ -5228,16 +5255,16 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C45" s="35"/>
       <c r="D45" s="36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E45" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G45" s="37"/>
       <c r="H45" s="37">
@@ -5248,10 +5275,10 @@
         <v>19.899999999999999</v>
       </c>
       <c r="J45" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K45" s="37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L45" s="38">
         <f t="shared" si="7"/>
@@ -5274,10 +5301,10 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C46" s="35"/>
       <c r="D46" s="46" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E46" s="37" t="s">
         <v>1</v>
@@ -5292,10 +5319,10 @@
         <v>284.05</v>
       </c>
       <c r="J46" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L46" s="38">
         <f t="shared" si="7"/>
@@ -5318,10 +5345,10 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C47" s="35"/>
       <c r="D47" s="46" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E47" s="37" t="s">
         <v>1</v>
@@ -5336,10 +5363,10 @@
         <v>110</v>
       </c>
       <c r="J47" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K47" s="38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L47" s="38">
         <f t="shared" si="7"/>
@@ -5362,10 +5389,10 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C48" s="35"/>
       <c r="D48" s="46" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E48" s="37" t="s">
         <v>1</v>
@@ -5380,10 +5407,10 @@
         <v>118.4</v>
       </c>
       <c r="J48" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K48" s="38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L48" s="38">
         <f t="shared" si="7"/>
@@ -5403,10 +5430,10 @@
       </c>
       <c r="Q48" s="37"/>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C49" s="35"/>
       <c r="D49" s="36" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E49" s="37" t="s">
         <v>1</v>
@@ -5421,10 +5448,10 @@
         <v>26.9</v>
       </c>
       <c r="J49" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K49" s="37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L49" s="38">
         <f t="shared" si="7"/>
@@ -5447,10 +5474,10 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C50" s="35"/>
       <c r="D50" s="46" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E50" s="37" t="s">
         <v>1</v>
@@ -5465,10 +5492,10 @@
         <v>70</v>
       </c>
       <c r="J50" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K50" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L50" s="38">
         <f t="shared" si="7"/>
@@ -5488,10 +5515,10 @@
       </c>
       <c r="Q50" s="37"/>
     </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C51" s="35"/>
       <c r="D51" s="67" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E51" s="37" t="s">
         <v>1</v>
@@ -5506,10 +5533,10 @@
         <v>426</v>
       </c>
       <c r="J51" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K51" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L51" s="38">
         <f t="shared" si="7"/>
@@ -5532,16 +5559,16 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C52" s="35"/>
       <c r="D52" s="46" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E52" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G52" s="37"/>
       <c r="H52" s="37">
@@ -5552,10 +5579,10 @@
         <v>-43</v>
       </c>
       <c r="J52" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K52" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L52" s="38">
         <f t="shared" si="7"/>
@@ -5578,16 +5605,16 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C53" s="35"/>
       <c r="D53" s="46" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E53" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G53" s="37"/>
       <c r="H53" s="37">
@@ -5598,10 +5625,10 @@
         <v>217.85</v>
       </c>
       <c r="J53" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K53" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L53" s="38">
         <f t="shared" si="7"/>
@@ -5626,10 +5653,10 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C54" s="35"/>
       <c r="D54" s="46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E54" s="37" t="s">
         <v>1</v>
@@ -5644,10 +5671,10 @@
         <v>300</v>
       </c>
       <c r="J54" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K54" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L54" s="38">
         <f t="shared" si="7"/>
@@ -5672,10 +5699,10 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C55" s="35"/>
       <c r="D55" s="46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E55" s="37" t="s">
         <v>1</v>
@@ -5691,10 +5718,10 @@
         <v>37.909999999999997</v>
       </c>
       <c r="J55" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K55" s="38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L55" s="38">
         <f t="shared" si="7"/>
@@ -5719,16 +5746,16 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C56" s="35"/>
       <c r="D56" s="46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E56" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G56" s="37"/>
       <c r="H56" s="37">
@@ -5739,10 +5766,10 @@
         <v>66</v>
       </c>
       <c r="J56" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K56" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L56" s="38">
         <f t="shared" si="7"/>
@@ -5767,16 +5794,16 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C57" s="35"/>
       <c r="D57" s="46" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E57" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G57" s="37"/>
       <c r="H57" s="37">
@@ -5787,10 +5814,10 @@
         <v>265</v>
       </c>
       <c r="J57" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K57" s="38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L57" s="38">
         <f t="shared" si="7"/>
@@ -5815,10 +5842,10 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C58" s="35"/>
       <c r="D58" s="36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E58" s="37" t="s">
         <v>1</v>
@@ -5834,10 +5861,10 @@
         <v>369</v>
       </c>
       <c r="J58" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K58" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L58" s="38">
         <f t="shared" si="7"/>
@@ -5862,16 +5889,16 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C59" s="35"/>
       <c r="D59" s="46" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E59" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G59" s="37"/>
       <c r="H59" s="37">
@@ -5882,10 +5909,10 @@
         <v>120</v>
       </c>
       <c r="J59" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K59" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L59" s="38">
         <f t="shared" si="7"/>
@@ -5910,10 +5937,10 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C60" s="35"/>
       <c r="D60" s="46" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E60" s="37" t="s">
         <v>1</v>
@@ -5928,10 +5955,10 @@
         <v>85</v>
       </c>
       <c r="J60" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K60" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L60" s="38">
         <f t="shared" si="7"/>
@@ -5956,16 +5983,16 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C61" s="35"/>
       <c r="D61" s="46" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E61" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G61" s="37"/>
       <c r="H61" s="37">
@@ -5977,10 +6004,10 @@
         <v>85.786666666666676</v>
       </c>
       <c r="J61" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K61" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L61" s="38">
         <f t="shared" si="7"/>
@@ -6005,10 +6032,10 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C62" s="35"/>
       <c r="D62" s="46" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
@@ -6022,10 +6049,10 @@
         <v>42.895000000000003</v>
       </c>
       <c r="J62" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K62" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L62" s="38">
         <f t="shared" si="7"/>
@@ -6050,16 +6077,16 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C63" s="35"/>
       <c r="D63" s="46" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E63" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G63" s="37"/>
       <c r="H63" s="37">
@@ -6070,10 +6097,10 @@
         <v>40</v>
       </c>
       <c r="J63" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K63" s="38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L63" s="38">
         <f t="shared" si="7"/>
@@ -6098,10 +6125,10 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C64" s="35"/>
       <c r="D64" s="46" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E64" s="37"/>
       <c r="F64" s="37"/>
@@ -6114,10 +6141,10 @@
         <v>20</v>
       </c>
       <c r="J64" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L64" s="38">
         <f t="shared" si="7"/>
@@ -6142,16 +6169,16 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C65" s="35"/>
       <c r="D65" s="46" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E65" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G65" s="37"/>
       <c r="H65" s="37">
@@ -6162,10 +6189,10 @@
         <v>56.42</v>
       </c>
       <c r="J65" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K65" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L65" s="38">
         <f t="shared" si="7"/>
@@ -6190,10 +6217,10 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C66" s="35"/>
       <c r="D66" s="46" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E66" s="37" t="s">
         <v>1</v>
@@ -6208,10 +6235,10 @@
         <v>-338</v>
       </c>
       <c r="J66" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L66" s="38">
         <f t="shared" si="7"/>
@@ -6236,10 +6263,10 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C67" s="35"/>
       <c r="D67" s="46" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E67" s="37" t="s">
         <v>1</v>
@@ -6254,10 +6281,10 @@
         <v>638</v>
       </c>
       <c r="J67" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K67" s="38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L67" s="38">
         <f t="shared" si="7"/>
@@ -6282,10 +6309,10 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C68" s="35"/>
       <c r="D68" s="46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E68" s="37" t="s">
         <v>1</v>
@@ -6300,10 +6327,10 @@
         <v>60</v>
       </c>
       <c r="J68" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K68" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L68" s="38">
         <f t="shared" si="7"/>
@@ -6328,16 +6355,16 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C69" s="35"/>
       <c r="D69" s="46" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E69" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G69" s="37"/>
       <c r="H69" s="37">
@@ -6348,10 +6375,10 @@
         <v>91.5</v>
       </c>
       <c r="J69" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K69" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L69" s="38">
         <f t="shared" si="7"/>
@@ -6376,10 +6403,10 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C70" s="35"/>
       <c r="D70" s="46" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E70" s="37" t="s">
         <v>1</v>
@@ -6387,24 +6414,24 @@
       <c r="F70" s="37"/>
       <c r="G70" s="37"/>
       <c r="H70" s="37">
-        <f t="shared" ref="H70:H99" si="11">COUNTA(E70:G70)</f>
+        <f t="shared" ref="H70:H101" si="11">COUNTA(E70:G70)</f>
         <v>1</v>
       </c>
       <c r="I70" s="38">
         <v>-51.5</v>
       </c>
       <c r="J70" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L70" s="38">
-        <f t="shared" ref="L70:L99" si="12">I70/N70</f>
+        <f t="shared" ref="L70:L101" si="12">I70/N70</f>
         <v>-51.5</v>
       </c>
       <c r="M70" s="38">
-        <f t="shared" ref="M70:M99" si="13">IFERROR(L70/H70,"")</f>
+        <f t="shared" ref="M70:M101" si="13">IFERROR(L70/H70,"")</f>
         <v>-51.5</v>
       </c>
       <c r="N70" s="39">
@@ -6414,7 +6441,7 @@
         <v>46298</v>
       </c>
       <c r="P70" s="64" t="str">
-        <f t="shared" ref="P70:P99" si="14">IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
+        <f t="shared" ref="P70:P101" si="14">IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
         <v/>
       </c>
       <c r="Q70" s="37" t="str">
@@ -6422,14 +6449,14 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C71" s="35"/>
       <c r="D71" s="46" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E71" s="37"/>
       <c r="F71" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G71" s="37"/>
       <c r="H71" s="37">
@@ -6440,10 +6467,10 @@
         <v>-40</v>
       </c>
       <c r="J71" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K71" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L71" s="38">
         <f t="shared" si="12"/>
@@ -6468,15 +6495,15 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C72" s="35"/>
       <c r="D72" s="46" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E72" s="37"/>
       <c r="F72" s="37"/>
       <c r="G72" s="37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H72" s="37">
         <f t="shared" si="11"/>
@@ -6486,10 +6513,10 @@
         <v>53</v>
       </c>
       <c r="J72" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L72" s="38">
         <f t="shared" si="12"/>
@@ -6514,14 +6541,14 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C73" s="35"/>
       <c r="D73" s="46" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E73" s="37"/>
       <c r="F73" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G73" s="37"/>
       <c r="H73" s="37">
@@ -6532,10 +6559,10 @@
         <v>35</v>
       </c>
       <c r="J73" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K73" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L73" s="38">
         <f t="shared" si="12"/>
@@ -6560,16 +6587,16 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C74" s="35"/>
       <c r="D74" s="46" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E74" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F74" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G74" s="37"/>
       <c r="H74" s="37">
@@ -6580,10 +6607,10 @@
         <v>66</v>
       </c>
       <c r="J74" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K74" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L74" s="38">
         <f t="shared" si="12"/>
@@ -6608,10 +6635,10 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C75" s="35"/>
       <c r="D75" s="46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E75" s="37" t="s">
         <v>1</v>
@@ -6626,10 +6653,10 @@
         <v>-33</v>
       </c>
       <c r="J75" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K75" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L75" s="38">
         <f t="shared" si="12"/>
@@ -6654,10 +6681,10 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C76" s="35"/>
       <c r="D76" s="46" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E76" s="37" t="s">
         <v>1</v>
@@ -6673,10 +6700,10 @@
         <v>75.806666666666658</v>
       </c>
       <c r="J76" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K76" s="38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L76" s="38">
         <f t="shared" si="12"/>
@@ -6701,10 +6728,10 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C77" s="35"/>
       <c r="D77" s="46" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E77" s="37"/>
       <c r="F77" s="37"/>
@@ -6717,10 +6744,10 @@
         <v>37.9</v>
       </c>
       <c r="J77" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K77" s="38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L77" s="38">
         <f t="shared" si="12"/>
@@ -6745,10 +6772,10 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C78" s="35"/>
       <c r="D78" s="46" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E78" s="37" t="s">
         <v>1</v>
@@ -6763,10 +6790,10 @@
         <v>-66</v>
       </c>
       <c r="J78" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K78" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L78" s="38">
         <f t="shared" si="12"/>
@@ -6791,16 +6818,16 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C79" s="35"/>
       <c r="D79" s="46" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E79" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F79" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G79" s="37"/>
       <c r="H79" s="37">
@@ -6811,10 +6838,10 @@
         <v>112</v>
       </c>
       <c r="J79" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K79" s="38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L79" s="38">
         <f t="shared" si="12"/>
@@ -6839,16 +6866,16 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C80" s="35"/>
       <c r="D80" s="46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E80" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F80" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G80" s="37"/>
       <c r="H80" s="37">
@@ -6860,10 +6887,10 @@
         <v>75.844999999999999</v>
       </c>
       <c r="J80" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K80" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L80" s="38">
         <f t="shared" si="12"/>
@@ -6888,10 +6915,10 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C81" s="35"/>
       <c r="D81" s="46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E81" s="37" t="s">
         <v>1</v>
@@ -6906,10 +6933,10 @@
         <v>-45</v>
       </c>
       <c r="J81" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K81" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L81" s="38">
         <f t="shared" si="12"/>
@@ -6934,15 +6961,15 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C82" s="35"/>
       <c r="D82" s="46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E82" s="37"/>
       <c r="F82" s="37"/>
       <c r="G82" s="37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H82" s="37">
         <f t="shared" si="11"/>
@@ -6953,10 +6980,10 @@
         <v>75.844999999999999</v>
       </c>
       <c r="J82" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K82" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L82" s="38">
         <f t="shared" si="12"/>
@@ -6981,10 +7008,10 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C83" s="35"/>
       <c r="D83" s="46" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E83" s="37" t="s">
         <v>1</v>
@@ -6999,10 +7026,10 @@
         <v>88.1</v>
       </c>
       <c r="J83" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K83" s="38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L83" s="38">
         <f t="shared" si="12"/>
@@ -7023,20 +7050,20 @@
         <v/>
       </c>
       <c r="Q83" s="37" t="str">
-        <f t="shared" ref="Q83:Q112" ca="1" si="15">IF(O83&lt;&gt;"",IFERROR(DATEDIF(O83,TODAY(),"m")+1,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q83:Q114" ca="1" si="15">IF(O83&lt;&gt;"",IFERROR(DATEDIF(O83,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C84" s="35"/>
       <c r="D84" s="46" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E84" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F84" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G84" s="37"/>
       <c r="H84" s="37">
@@ -7047,10 +7074,10 @@
         <v>47.81</v>
       </c>
       <c r="J84" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K84" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L84" s="38">
         <f t="shared" si="12"/>
@@ -7075,16 +7102,16 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C85" s="35"/>
       <c r="D85" s="46" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E85" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G85" s="37"/>
       <c r="H85" s="37">
@@ -7095,10 +7122,10 @@
         <v>265</v>
       </c>
       <c r="J85" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K85" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L85" s="38">
         <f t="shared" si="12"/>
@@ -7123,10 +7150,10 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C86" s="35"/>
       <c r="D86" s="46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E86" s="37" t="s">
         <v>1</v>
@@ -7141,10 +7168,10 @@
         <v>-130</v>
       </c>
       <c r="J86" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K86" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L86" s="38">
         <f t="shared" si="12"/>
@@ -7169,16 +7196,16 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C87" s="35"/>
       <c r="D87" s="46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E87" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F87" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G87" s="37"/>
       <c r="H87" s="37">
@@ -7189,10 +7216,10 @@
         <v>10</v>
       </c>
       <c r="J87" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K87" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L87" s="38">
         <f t="shared" si="12"/>
@@ -7217,16 +7244,16 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C88" s="35"/>
       <c r="D88" s="46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E88" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F88" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G88" s="37"/>
       <c r="H88" s="37">
@@ -7237,10 +7264,10 @@
         <v>64</v>
       </c>
       <c r="J88" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K88" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L88" s="38">
         <f t="shared" si="12"/>
@@ -7265,16 +7292,16 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C89" s="35"/>
       <c r="D89" s="46" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E89" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F89" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G89" s="37"/>
       <c r="H89" s="37">
@@ -7285,10 +7312,10 @@
         <v>97</v>
       </c>
       <c r="J89" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K89" s="38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L89" s="38">
         <f t="shared" si="12"/>
@@ -7313,10 +7340,10 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C90" s="35"/>
       <c r="D90" s="46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E90" s="37" t="s">
         <v>1</v>
@@ -7331,10 +7358,10 @@
         <v>43.39</v>
       </c>
       <c r="J90" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K90" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L90" s="38">
         <f t="shared" si="12"/>
@@ -7359,10 +7386,10 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C91" s="35"/>
       <c r="D91" s="46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E91" s="37" t="s">
         <v>1</v>
@@ -7377,10 +7404,10 @@
         <v>-45</v>
       </c>
       <c r="J91" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K91" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L91" s="38">
         <f t="shared" si="12"/>
@@ -7405,16 +7432,16 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C92" s="35"/>
       <c r="D92" s="46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E92" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F92" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G92" s="37"/>
       <c r="H92" s="37">
@@ -7425,10 +7452,10 @@
         <v>116.33</v>
       </c>
       <c r="J92" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K92" s="38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L92" s="38">
         <f t="shared" si="12"/>
@@ -7453,34 +7480,38 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C93" s="35"/>
       <c r="D93" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="E93" s="37"/>
-      <c r="F93" s="37"/>
+        <v>159</v>
+      </c>
+      <c r="E93" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F93" s="37" t="s">
+        <v>0</v>
+      </c>
       <c r="G93" s="37"/>
       <c r="H93" s="37">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" s="38">
         <v>116.33</v>
       </c>
       <c r="J93" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K93" s="38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L93" s="38">
         <f t="shared" si="12"/>
         <v>116.33</v>
       </c>
-      <c r="M93" s="38" t="str">
+      <c r="M93" s="38">
         <f t="shared" si="13"/>
-        <v/>
+        <v>58.164999999999999</v>
       </c>
       <c r="N93" s="39">
         <v>1</v>
@@ -7497,10 +7528,10 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C94" s="35"/>
       <c r="D94" s="46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E94" s="37"/>
       <c r="F94" s="37"/>
@@ -7513,10 +7544,10 @@
         <v>-116.33</v>
       </c>
       <c r="J94" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K94" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L94" s="38">
         <f t="shared" si="12"/>
@@ -7541,10 +7572,10 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C95" s="35"/>
       <c r="D95" s="46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E95" s="37" t="s">
         <v>1</v>
@@ -7559,10 +7590,10 @@
         <v>60</v>
       </c>
       <c r="J95" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K95" s="38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L95" s="38">
         <f t="shared" si="12"/>
@@ -7587,10 +7618,10 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C96" s="35"/>
       <c r="D96" s="46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E96" s="37" t="s">
         <v>1</v>
@@ -7605,10 +7636,10 @@
         <v>64.989999999999995</v>
       </c>
       <c r="J96" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K96" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L96" s="38">
         <f t="shared" si="12"/>
@@ -7633,10 +7664,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C97" s="35"/>
       <c r="D97" s="46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E97" s="37" t="s">
         <v>1</v>
@@ -7651,10 +7682,10 @@
         <v>55</v>
       </c>
       <c r="J97" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K97" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L97" s="38">
         <f t="shared" si="12"/>
@@ -7679,16 +7710,16 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C98" s="35"/>
       <c r="D98" s="46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E98" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F98" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G98" s="37"/>
       <c r="H98" s="37">
@@ -7699,10 +7730,10 @@
         <v>663</v>
       </c>
       <c r="J98" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K98" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L98" s="38">
         <f t="shared" si="12"/>
@@ -7727,16 +7758,16 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C99" s="35"/>
       <c r="D99" s="46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E99" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F99" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G99" s="37"/>
       <c r="H99" s="37">
@@ -7747,10 +7778,10 @@
         <v>320</v>
       </c>
       <c r="J99" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K99" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L99" s="38">
         <f t="shared" si="12"/>
@@ -7773,10 +7804,10 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C100" s="35"/>
       <c r="D100" s="46" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E100" s="37" t="s">
         <v>1</v>
@@ -7784,24 +7815,24 @@
       <c r="F100" s="37"/>
       <c r="G100" s="37"/>
       <c r="H100" s="37">
-        <f t="shared" ref="H100:H128" si="16">COUNTA(E100:G100)</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="I100" s="38">
         <v>72</v>
       </c>
       <c r="J100" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K100" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L100" s="38">
-        <f t="shared" ref="L100:L128" si="17">I100/N100</f>
+        <f t="shared" si="12"/>
         <v>72</v>
       </c>
       <c r="M100" s="38">
-        <f t="shared" ref="M100:M128" si="18">IFERROR(L100/H100,"")</f>
+        <f t="shared" si="13"/>
         <v>72</v>
       </c>
       <c r="N100" s="39">
@@ -7809,7 +7840,7 @@
       </c>
       <c r="O100" s="35"/>
       <c r="P100" s="35" t="str">
-        <f t="shared" ref="P100:P128" si="19">IF(N100&lt;&gt;1,EDATE(O100,N100-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q100" s="37" t="str">
@@ -7817,10 +7848,10 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C101" s="35"/>
       <c r="D101" s="46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E101" s="37" t="s">
         <v>1</v>
@@ -7828,24 +7859,24 @@
       <c r="F101" s="37"/>
       <c r="G101" s="37"/>
       <c r="H101" s="37">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="I101" s="38">
         <v>25</v>
       </c>
       <c r="J101" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K101" s="38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L101" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>25</v>
       </c>
       <c r="M101" s="38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>25</v>
       </c>
       <c r="N101" s="39">
@@ -7853,7 +7884,7 @@
       </c>
       <c r="O101" s="35"/>
       <c r="P101" s="35" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q101" s="37" t="str">
@@ -7861,33 +7892,33 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C102" s="35"/>
       <c r="D102" s="46" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E102" s="37"/>
       <c r="F102" s="37"/>
       <c r="G102" s="37"/>
       <c r="H102" s="37">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="H102:H133" si="16">COUNTA(E102:G102)</f>
         <v>0</v>
       </c>
       <c r="I102" s="38">
         <v>273.5</v>
       </c>
       <c r="J102" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K102" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L102" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="L102:L128" si="17">I102/N102</f>
         <v>273.5</v>
       </c>
       <c r="M102" s="38" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="M102:M133" si="18">IFERROR(L102/H102,"")</f>
         <v/>
       </c>
       <c r="N102" s="39">
@@ -7895,7 +7926,7 @@
       </c>
       <c r="O102" s="35"/>
       <c r="P102" s="35" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="P102:P133" si="19">IF(N102&lt;&gt;1,EDATE(O102,N102-1),"")</f>
         <v/>
       </c>
       <c r="Q102" s="37" t="str">
@@ -7903,16 +7934,16 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C103" s="35"/>
       <c r="D103" s="46" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E103" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F103" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G103" s="37"/>
       <c r="H103" s="37">
@@ -7923,10 +7954,10 @@
         <v>305</v>
       </c>
       <c r="J103" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K103" s="38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L103" s="38">
         <f t="shared" si="17"/>
@@ -7949,10 +7980,10 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C104" s="35"/>
       <c r="D104" s="46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E104" s="37"/>
       <c r="F104" s="37"/>
@@ -7965,10 +7996,10 @@
         <v>-273.5</v>
       </c>
       <c r="J104" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K104" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L104" s="38">
         <f t="shared" si="17"/>
@@ -7991,10 +8022,10 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C105" s="35"/>
       <c r="D105" s="46" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E105" s="37" t="s">
         <v>1</v>
@@ -8010,10 +8041,10 @@
         <v>-144.5</v>
       </c>
       <c r="J105" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K105" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L105" s="38">
         <f t="shared" si="17"/>
@@ -8036,16 +8067,16 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C106" s="35"/>
       <c r="D106" s="46" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E106" s="37" t="s">
         <v>1</v>
       </c>
       <c r="F106" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G106" s="37"/>
       <c r="H106" s="37">
@@ -8056,10 +8087,10 @@
         <v>219.9</v>
       </c>
       <c r="J106" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K106" s="38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L106" s="38">
         <f t="shared" si="17"/>
@@ -8082,10 +8113,10 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C107" s="35"/>
       <c r="D107" s="46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E107" s="37" t="s">
         <v>1</v>
@@ -8100,10 +8131,10 @@
         <v>95</v>
       </c>
       <c r="J107" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K107" s="38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L107" s="38">
         <f t="shared" si="17"/>
@@ -8126,10 +8157,10 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C108" s="35"/>
       <c r="D108" s="46" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E108" s="37" t="s">
         <v>1</v>
@@ -8144,10 +8175,10 @@
         <v>65</v>
       </c>
       <c r="J108" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K108" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L108" s="38">
         <f t="shared" si="17"/>
@@ -8170,10 +8201,10 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C109" s="35"/>
       <c r="D109" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E109" s="37" t="s">
         <v>1</v>
@@ -8188,10 +8219,10 @@
         <v>85.24</v>
       </c>
       <c r="J109" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K109" s="38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L109" s="38">
         <f t="shared" si="17"/>
@@ -8214,10 +8245,10 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C110" s="35"/>
       <c r="D110" s="46" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E110" s="37" t="s">
         <v>1</v>
@@ -8232,10 +8263,10 @@
         <v>56.18</v>
       </c>
       <c r="J110" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K110" s="38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L110" s="38">
         <f t="shared" si="17"/>
@@ -8258,10 +8289,10 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C111" s="35"/>
       <c r="D111" s="46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E111" s="37"/>
       <c r="F111" s="37"/>
@@ -8274,10 +8305,10 @@
         <v>235.73</v>
       </c>
       <c r="J111" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K111" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L111" s="38">
         <f t="shared" si="17"/>
@@ -8300,10 +8331,10 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C112" s="35"/>
       <c r="D112" s="46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E112" s="37"/>
       <c r="F112" s="37"/>
@@ -8316,10 +8347,10 @@
         <v>208.52</v>
       </c>
       <c r="J112" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K112" s="38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L112" s="38">
         <f t="shared" si="17"/>
@@ -8342,10 +8373,10 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C113" s="35"/>
       <c r="D113" s="36" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E113" s="37"/>
       <c r="F113" s="37"/>
@@ -8358,10 +8389,10 @@
         <v>-450</v>
       </c>
       <c r="J113" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K113" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L113" s="38">
         <f t="shared" si="17"/>
@@ -8380,14 +8411,14 @@
         <v/>
       </c>
       <c r="Q113" s="37" t="str">
-        <f t="shared" ref="Q113:Q128" ca="1" si="20">IF(O113&lt;&gt;"",IFERROR(DATEDIF(O113,TODAY(),"m")+1,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C114" s="35"/>
       <c r="D114" s="46" t="s">
-        <v>293</v>
+        <v>180</v>
       </c>
       <c r="E114" s="37"/>
       <c r="F114" s="37"/>
@@ -8400,10 +8431,10 @@
         <v>276.54000000000002</v>
       </c>
       <c r="J114" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K114" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L114" s="38">
         <f t="shared" si="17"/>
@@ -8422,14 +8453,14 @@
         <v/>
       </c>
       <c r="Q114" s="37" t="str">
-        <f t="shared" ca="1" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C115" s="35"/>
       <c r="D115" s="36" t="s">
-        <v>294</v>
+        <v>181</v>
       </c>
       <c r="E115" s="37" t="s">
         <v>1</v>
@@ -8444,10 +8475,10 @@
         <v>150</v>
       </c>
       <c r="J115" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K115" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L115" s="38">
         <f t="shared" si="17"/>
@@ -8466,14 +8497,14 @@
         <v/>
       </c>
       <c r="Q115" s="37" t="str">
-        <f t="shared" ca="1" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q115:Q128" ca="1" si="20">IF(O115&lt;&gt;"",IFERROR(DATEDIF(O115,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C116" s="35"/>
       <c r="D116" s="46" t="s">
-        <v>295</v>
+        <v>182</v>
       </c>
       <c r="E116" s="37"/>
       <c r="F116" s="37"/>
@@ -8486,10 +8517,10 @@
         <v>-276</v>
       </c>
       <c r="J116" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K116" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L116" s="38">
         <f t="shared" si="17"/>
@@ -8512,10 +8543,10 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C117" s="35"/>
       <c r="D117" s="36" t="s">
-        <v>296</v>
+        <v>183</v>
       </c>
       <c r="E117" s="37" t="s">
         <v>1</v>
@@ -8530,10 +8561,10 @@
         <v>-160</v>
       </c>
       <c r="J117" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K117" s="38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L117" s="38">
         <f t="shared" si="17"/>
@@ -8556,26 +8587,34 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C118" s="35"/>
-      <c r="D118" s="46"/>
-      <c r="E118" s="37"/>
-      <c r="F118" s="37"/>
+      <c r="D118" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E118" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F118" s="37" t="s">
+        <v>0</v>
+      </c>
       <c r="G118" s="37"/>
       <c r="H118" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I118" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I118" s="38">
+        <v>60.2</v>
+      </c>
       <c r="J118" s="38"/>
       <c r="K118" s="38"/>
       <c r="L118" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M118" s="38" t="str">
+        <v>60.2</v>
+      </c>
+      <c r="M118" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>30.1</v>
       </c>
       <c r="N118" s="39">
         <v>1</v>
@@ -8590,26 +8629,32 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C119" s="35"/>
-      <c r="D119" s="46"/>
-      <c r="E119" s="37"/>
+      <c r="D119" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="E119" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F119" s="37"/>
       <c r="G119" s="37"/>
       <c r="H119" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I119" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I119" s="38">
+        <v>75</v>
+      </c>
       <c r="J119" s="38"/>
       <c r="K119" s="38"/>
       <c r="L119" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M119" s="38" t="str">
+        <v>75</v>
+      </c>
+      <c r="M119" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>75</v>
       </c>
       <c r="N119" s="39">
         <v>1</v>
@@ -8624,26 +8669,34 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C120" s="35"/>
-      <c r="D120" s="46"/>
-      <c r="E120" s="37"/>
-      <c r="F120" s="37"/>
+      <c r="D120" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="E120" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F120" s="37" t="s">
+        <v>0</v>
+      </c>
       <c r="G120" s="37"/>
       <c r="H120" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I120" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I120" s="38">
+        <v>81</v>
+      </c>
       <c r="J120" s="38"/>
       <c r="K120" s="38"/>
       <c r="L120" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M120" s="38" t="str">
+        <v>81</v>
+      </c>
+      <c r="M120" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>40.5</v>
       </c>
       <c r="N120" s="39">
         <v>1</v>
@@ -8658,26 +8711,34 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C121" s="35"/>
-      <c r="D121" s="46"/>
-      <c r="E121" s="37"/>
-      <c r="F121" s="37"/>
+      <c r="D121" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="E121" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F121" s="37" t="s">
+        <v>0</v>
+      </c>
       <c r="G121" s="37"/>
       <c r="H121" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I121" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I121" s="38">
+        <v>35</v>
+      </c>
       <c r="J121" s="38"/>
       <c r="K121" s="38"/>
       <c r="L121" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M121" s="38" t="str">
+        <v>35</v>
+      </c>
+      <c r="M121" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>17.5</v>
       </c>
       <c r="N121" s="39">
         <v>1</v>
@@ -8692,9 +8753,11 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C122" s="35"/>
-      <c r="D122" s="46"/>
+      <c r="D122" s="46" t="s">
+        <v>186</v>
+      </c>
       <c r="E122" s="37"/>
       <c r="F122" s="37"/>
       <c r="G122" s="37"/>
@@ -8702,12 +8765,14 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I122" s="38"/>
+      <c r="I122" s="38">
+        <v>116</v>
+      </c>
       <c r="J122" s="38"/>
       <c r="K122" s="38"/>
       <c r="L122" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="M122" s="38" t="str">
         <f t="shared" si="18"/>
@@ -8726,26 +8791,33 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C123" s="35"/>
-      <c r="D123" s="46"/>
-      <c r="E123" s="37"/>
+      <c r="D123" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="E123" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F123" s="37"/>
       <c r="G123" s="37"/>
       <c r="H123" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I123" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I123" s="38">
+        <f>23.95+30.95</f>
+        <v>54.9</v>
+      </c>
       <c r="J123" s="38"/>
       <c r="K123" s="38"/>
       <c r="L123" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M123" s="38" t="str">
+        <v>54.9</v>
+      </c>
+      <c r="M123" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>54.9</v>
       </c>
       <c r="N123" s="39">
         <v>1</v>
@@ -8760,9 +8832,11 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C124" s="35"/>
-      <c r="D124" s="46"/>
+      <c r="D124" s="46" t="s">
+        <v>184</v>
+      </c>
       <c r="E124" s="37"/>
       <c r="F124" s="37"/>
       <c r="G124" s="37"/>
@@ -8770,12 +8844,14 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I124" s="38"/>
+      <c r="I124" s="38">
+        <v>120.37</v>
+      </c>
       <c r="J124" s="38"/>
       <c r="K124" s="38"/>
       <c r="L124" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>120.37</v>
       </c>
       <c r="M124" s="38" t="str">
         <f t="shared" si="18"/>
@@ -8794,9 +8870,11 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C125" s="35"/>
-      <c r="D125" s="46"/>
+      <c r="D125" s="46" t="s">
+        <v>188</v>
+      </c>
       <c r="E125" s="37"/>
       <c r="F125" s="37"/>
       <c r="G125" s="37"/>
@@ -8804,12 +8882,14 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I125" s="38"/>
+      <c r="I125" s="38">
+        <v>-236.37</v>
+      </c>
       <c r="J125" s="38"/>
       <c r="K125" s="38"/>
       <c r="L125" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-236.37</v>
       </c>
       <c r="M125" s="38" t="str">
         <f t="shared" si="18"/>
@@ -8828,26 +8908,32 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C126" s="35"/>
-      <c r="D126" s="46"/>
-      <c r="E126" s="37"/>
+      <c r="D126" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="E126" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F126" s="37"/>
       <c r="G126" s="37"/>
       <c r="H126" s="37">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I126" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I126" s="38">
+        <v>-13.63</v>
+      </c>
       <c r="J126" s="38"/>
       <c r="K126" s="38"/>
       <c r="L126" s="38">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="M126" s="38" t="str">
+        <v>-13.63</v>
+      </c>
+      <c r="M126" s="38">
         <f t="shared" si="18"/>
-        <v/>
+        <v>-13.63</v>
       </c>
       <c r="N126" s="39">
         <v>1</v>
@@ -8862,7 +8948,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C127" s="35"/>
       <c r="D127" s="46"/>
       <c r="E127" s="37"/>
@@ -8896,7 +8982,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C128" s="35"/>
       <c r="D128" s="46"/>
       <c r="E128" s="37"/>
@@ -9029,66 +9115,66 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:R20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" customWidth="1"/>
-    <col min="4" max="4" width="33.85546875" customWidth="1"/>
-    <col min="5" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" customWidth="1"/>
-    <col min="12" max="15" width="13.5703125" customWidth="1"/>
-    <col min="16" max="16" width="53.42578125" customWidth="1"/>
-    <col min="18" max="18" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="36.5546875" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="4" max="4" width="33.88671875" customWidth="1"/>
+    <col min="5" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" customWidth="1"/>
+    <col min="12" max="15" width="13.5546875" customWidth="1"/>
+    <col min="16" max="16" width="53.44140625" customWidth="1"/>
+    <col min="18" max="18" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D2" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H2" s="34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J2" s="34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K2" s="34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M2" s="33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N2" s="33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O2" s="34" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D3" s="54" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E3" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="37"/>
       <c r="H3" s="37">
@@ -9118,15 +9204,15 @@
       </c>
       <c r="R3" s="16"/>
     </row>
-    <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D4" s="55" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="E4" s="56" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" s="37"/>
       <c r="H4" s="57">
@@ -9156,18 +9242,18 @@
       </c>
       <c r="R4" s="16"/>
     </row>
-    <row r="5" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="30" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="37"/>
       <c r="H5" s="37">
@@ -9197,19 +9283,19 @@
       </c>
       <c r="P5" s="59"/>
     </row>
-    <row r="6" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="32">
         <f>SUMIF($E$3:$E$34,B5,$K$3:$K$34)</f>
         <v>2570.34</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37">
@@ -9238,16 +9324,16 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="60"/>
       <c r="D7" s="54" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="E7" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="37"/>
       <c r="H7" s="37">
@@ -9276,18 +9362,18 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="30" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="54" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="37"/>
       <c r="H8" s="37">
@@ -9316,19 +9402,19 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="61">
         <f>SUMIF($F$3:$F$34,B8,$K$3:$K$34)</f>
-        <v>5862.34</v>
+        <v>5612.34</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="E9" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="37"/>
       <c r="H9" s="37">
@@ -9358,13 +9444,13 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D10" s="54" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" s="37"/>
       <c r="H10" s="37">
@@ -9393,13 +9479,13 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D11" s="54" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="37"/>
       <c r="H11" s="37">
@@ -9407,15 +9493,15 @@
         <v>1</v>
       </c>
       <c r="I11" s="38">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="J11" s="38">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="K11" s="38">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="L11" s="37">
         <f t="shared" si="2"/>
@@ -9428,13 +9514,13 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D12" s="54" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="E12" s="36"/>
       <c r="F12" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="37"/>
       <c r="H12" s="37">
@@ -9463,15 +9549,15 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D13" s="54" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="E13" s="36" t="s">
         <v>1</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="37"/>
       <c r="H13" s="37">
@@ -9500,7 +9586,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D14" s="37"/>
       <c r="E14" s="36"/>
       <c r="F14" s="37"/>
@@ -9514,7 +9600,7 @@
       <c r="N14" s="38"/>
       <c r="O14" s="39"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D15" s="37"/>
       <c r="E15" s="36"/>
       <c r="F15" s="37"/>
@@ -9528,7 +9614,7 @@
       <c r="N15" s="38"/>
       <c r="O15" s="39"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D16" s="37"/>
       <c r="E16" s="36"/>
       <c r="F16" s="37"/>
@@ -9542,7 +9628,7 @@
       <c r="N16" s="38"/>
       <c r="O16" s="39"/>
     </row>
-    <row r="17" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D17" s="37"/>
       <c r="E17" s="36"/>
       <c r="F17" s="37"/>
@@ -9556,7 +9642,7 @@
       <c r="N17" s="38"/>
       <c r="O17" s="39"/>
     </row>
-    <row r="18" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D18" s="37"/>
       <c r="E18" s="36"/>
       <c r="F18" s="37"/>
@@ -9570,7 +9656,7 @@
       <c r="N18" s="38"/>
       <c r="O18" s="39"/>
     </row>
-    <row r="19" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D19" s="37"/>
       <c r="E19" s="36"/>
       <c r="F19" s="37"/>
@@ -9584,7 +9670,7 @@
       <c r="N19" s="38"/>
       <c r="O19" s="39"/>
     </row>
-    <row r="20" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D20" s="37"/>
       <c r="E20" s="36"/>
       <c r="F20" s="37"/>
@@ -9607,39 +9693,39 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:O404"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
-    <col min="6" max="6" width="39.7109375" customWidth="1"/>
-    <col min="7" max="7" width="35.42578125" style="1" customWidth="1"/>
-    <col min="8" max="10" width="35.42578125" customWidth="1"/>
-    <col min="12" max="12" width="35.85546875" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" customWidth="1"/>
+    <col min="6" max="6" width="39.6640625" customWidth="1"/>
+    <col min="7" max="7" width="35.44140625" style="1" customWidth="1"/>
+    <col min="8" max="10" width="35.44140625" customWidth="1"/>
+    <col min="12" max="12" width="35.88671875" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
     <col min="14" max="14" width="24" customWidth="1"/>
     <col min="15" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.3">
       <c r="G1" s="2"/>
       <c r="N1" s="47" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G2" s="2"/>
       <c r="N2" s="43"/>
     </row>
-    <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G3" s="2"/>
       <c r="L3" s="47" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="M3" s="78" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="N3" s="43">
         <f>SUM(N5:N21)</f>
@@ -9647,83 +9733,83 @@
       </c>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
       <c r="G4" s="2"/>
       <c r="L4" s="48" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="M4" s="79"/>
       <c r="N4" s="49"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="43"/>
       <c r="C5" s="43"/>
       <c r="F5" s="16"/>
       <c r="G5" s="28"/>
       <c r="L5" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="N5" s="1">
         <v>100</v>
       </c>
       <c r="O5" s="16"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="G6" s="2"/>
       <c r="L6" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="N6" s="1">
         <f>97+31</f>
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="G7" s="2"/>
       <c r="N7" s="73"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F8" s="16"/>
       <c r="G8" s="50"/>
       <c r="N8" s="73"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F9" s="47" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G9" s="28"/>
       <c r="N9" s="72"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="E10" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="F10" s="16">
         <f>SUM(G11:I11)</f>
-        <v>8780.2000000000044</v>
+        <v>8530.2000000000044</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="H10" s="51" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="I10" s="51" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N10" s="72"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="E11" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F11" s="16">
         <f>SUM(G11:H11)</f>
-        <v>8780.2000000000044</v>
+        <v>8530.2000000000044</v>
       </c>
       <c r="G11" s="1">
         <f>G12+SUM(G14:G496)</f>
-        <v>8780.2000000000044</v>
+        <v>8530.2000000000044</v>
       </c>
       <c r="H11" s="1">
         <f>H12+SUM(H14:H496)</f>
@@ -9735,36 +9821,36 @@
       </c>
       <c r="N11" s="72"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F12" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="G12" s="1">
         <v>15250</v>
       </c>
       <c r="N12" s="72"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F13" s="74" t="s">
-        <v>191</v>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="F13" s="75" t="s">
+        <v>202</v>
       </c>
       <c r="G13" s="52"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
       <c r="N13" s="72"/>
     </row>
-    <row r="14" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F14" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="G14" s="53"/>
       <c r="H14" s="53"/>
       <c r="I14" s="53"/>
       <c r="N14" s="43"/>
     </row>
-    <row r="15" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F15" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="G15" s="53">
         <v>773.35</v>
@@ -9773,9 +9859,9 @@
       <c r="I15" s="53"/>
       <c r="N15" s="43"/>
     </row>
-    <row r="16" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F16" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="G16" s="53">
         <v>-5148</v>
@@ -9784,9 +9870,9 @@
       <c r="I16" s="53"/>
       <c r="N16" s="43"/>
     </row>
-    <row r="17" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F17" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="G17" s="53">
         <v>-168</v>
@@ -9795,9 +9881,9 @@
       <c r="I17" s="53"/>
       <c r="N17" s="43"/>
     </row>
-    <row r="18" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F18" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="G18" s="53">
         <v>-1700</v>
@@ -9806,9 +9892,9 @@
       <c r="I18" s="53"/>
       <c r="N18" s="43"/>
     </row>
-    <row r="19" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F19" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="G19" s="53">
         <v>5148</v>
@@ -9817,9 +9903,9 @@
       <c r="I19" s="53"/>
       <c r="N19" s="43"/>
     </row>
-    <row r="20" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F20" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="G20" s="53">
         <v>-4938</v>
@@ -9828,9 +9914,9 @@
       <c r="I20" s="53"/>
       <c r="N20" s="43"/>
     </row>
-    <row r="21" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F21" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="G21" s="53">
         <v>-1595</v>
@@ -9839,9 +9925,9 @@
       <c r="I21" s="53"/>
       <c r="N21" s="43"/>
     </row>
-    <row r="22" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F22" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="G22" s="53">
         <v>-4677</v>
@@ -9850,9 +9936,9 @@
       <c r="I22" s="53"/>
       <c r="N22" s="43"/>
     </row>
-    <row r="23" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F23" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="G23" s="53">
         <v>-200</v>
@@ -9861,9 +9947,9 @@
       <c r="I23" s="53"/>
       <c r="N23" s="43"/>
     </row>
-    <row r="24" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F24" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="G24" s="53">
         <v>4677</v>
@@ -9872,9 +9958,9 @@
       <c r="I24" s="53"/>
       <c r="N24" s="43"/>
     </row>
-    <row r="25" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F25" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G25" s="53">
         <v>-750</v>
@@ -9883,9 +9969,9 @@
       <c r="I25" s="53"/>
       <c r="N25" s="43"/>
     </row>
-    <row r="26" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F26" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="G26" s="53">
         <v>-652</v>
@@ -9894,9 +9980,9 @@
       <c r="I26" s="53"/>
       <c r="N26" s="43"/>
     </row>
-    <row r="27" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F27" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="G27" s="53">
         <v>11100</v>
@@ -9905,9 +9991,9 @@
       <c r="I27" s="53"/>
       <c r="N27" s="43"/>
     </row>
-    <row r="28" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F28" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="G28" s="53">
         <v>-396</v>
@@ -9916,9 +10002,9 @@
       <c r="I28" s="53"/>
       <c r="N28" s="43"/>
     </row>
-    <row r="29" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F29" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="G29" s="53">
         <v>-4211</v>
@@ -9927,9 +10013,9 @@
       <c r="I29" s="53"/>
       <c r="N29" s="43"/>
     </row>
-    <row r="30" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F30" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="G30" s="53">
         <v>-450</v>
@@ -9938,9 +10024,9 @@
       <c r="I30" s="53"/>
       <c r="N30" s="43"/>
     </row>
-    <row r="31" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F31" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="G31" s="53">
         <v>-1197</v>
@@ -9949,9 +10035,9 @@
       <c r="I31" s="53"/>
       <c r="N31" s="43"/>
     </row>
-    <row r="32" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F32" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="G32" s="53">
         <v>-315</v>
@@ -9960,9 +10046,9 @@
       <c r="I32" s="53"/>
       <c r="N32" s="43"/>
     </row>
-    <row r="33" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F33" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="G33" s="53">
         <v>-830</v>
@@ -9971,9 +10057,9 @@
       <c r="I33" s="53"/>
       <c r="N33" s="43"/>
     </row>
-    <row r="34" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F34" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="G34" s="53">
         <v>4211</v>
@@ -9982,9 +10068,9 @@
       <c r="I34" s="53"/>
       <c r="N34" s="43"/>
     </row>
-    <row r="35" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F35" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="G35" s="53">
         <v>-200</v>
@@ -9993,9 +10079,9 @@
       <c r="I35" s="53"/>
       <c r="N35" s="43"/>
     </row>
-    <row r="36" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F36" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="G36" s="53">
         <v>10000</v>
@@ -10004,9 +10090,9 @@
       <c r="I36" s="53"/>
       <c r="N36" s="43"/>
     </row>
-    <row r="37" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F37" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="G37" s="53">
         <v>-200</v>
@@ -10015,9 +10101,9 @@
       <c r="I37" s="53"/>
       <c r="N37" s="43"/>
     </row>
-    <row r="38" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F38" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="G38" s="53">
         <v>-381</v>
@@ -10026,9 +10112,9 @@
       <c r="I38" s="53"/>
       <c r="N38" s="43"/>
     </row>
-    <row r="39" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F39" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="G39" s="53">
         <v>-4911</v>
@@ -10037,10 +10123,10 @@
       <c r="I39" s="53"/>
       <c r="N39" s="43"/>
     </row>
-    <row r="40" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="E40" s="2"/>
       <c r="F40" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="G40" s="53">
         <v>-5700</v>
@@ -10049,9 +10135,9 @@
       <c r="I40" s="53"/>
       <c r="N40" s="43"/>
     </row>
-    <row r="41" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F41" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="G41" s="53">
         <v>-400</v>
@@ -10060,9 +10146,9 @@
       <c r="I41" s="53"/>
       <c r="N41" s="43"/>
     </row>
-    <row r="42" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F42" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="G42" s="53">
         <v>-450</v>
@@ -10071,9 +10157,9 @@
       <c r="I42" s="53"/>
       <c r="N42" s="43"/>
     </row>
-    <row r="43" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F43" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G43" s="53">
         <v>-640</v>
@@ -10082,10 +10168,10 @@
       <c r="I43" s="53"/>
       <c r="N43" s="43"/>
     </row>
-    <row r="44" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="G44" s="53">
         <v>5700</v>
@@ -10094,9 +10180,9 @@
       <c r="I44" s="53"/>
       <c r="N44" s="43"/>
     </row>
-    <row r="45" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F45" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="G45" s="53">
         <v>-130</v>
@@ -10105,9 +10191,9 @@
       <c r="I45" s="53"/>
       <c r="N45" s="43"/>
     </row>
-    <row r="46" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F46" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="G46" s="53">
         <v>-250</v>
@@ -10116,9 +10202,9 @@
       <c r="I46" s="53"/>
       <c r="N46" s="43"/>
     </row>
-    <row r="47" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F47" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="G47" s="53">
         <v>-112.2</v>
@@ -10127,9 +10213,9 @@
       <c r="I47" s="53"/>
       <c r="N47" s="43"/>
     </row>
-    <row r="48" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F48" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="G48" s="53">
         <v>4911</v>
@@ -10138,9 +10224,9 @@
       <c r="I48" s="53"/>
       <c r="N48" s="43"/>
     </row>
-    <row r="49" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F49" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="G49" s="53">
         <v>-3000</v>
@@ -10149,9 +10235,9 @@
       <c r="I49" s="53"/>
       <c r="N49" s="43"/>
     </row>
-    <row r="50" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F50" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="G50" s="53">
         <v>-4000</v>
@@ -10160,9 +10246,9 @@
       <c r="I50" s="53"/>
       <c r="N50" s="43"/>
     </row>
-    <row r="51" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F51" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G51" s="53">
         <v>-200</v>
@@ -10171,9 +10257,9 @@
       <c r="I51" s="53"/>
       <c r="N51" s="43"/>
     </row>
-    <row r="52" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F52" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="G52" s="53">
         <v>-4612</v>
@@ -10182,9 +10268,9 @@
       <c r="I52" s="53"/>
       <c r="N52" s="43"/>
     </row>
-    <row r="53" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F53" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G53" s="53">
         <v>-700</v>
@@ -10193,9 +10279,9 @@
       <c r="I53" s="53"/>
       <c r="N53" s="43"/>
     </row>
-    <row r="54" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F54" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="G54" s="53">
         <v>-880</v>
@@ -10204,9 +10290,9 @@
       <c r="I54" s="53"/>
       <c r="N54" s="43"/>
     </row>
-    <row r="55" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F55" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="G55" s="53">
         <v>-310</v>
@@ -10215,9 +10301,9 @@
       <c r="I55" s="53"/>
       <c r="N55" s="43"/>
     </row>
-    <row r="56" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F56" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G56" s="53">
         <v>-250</v>
@@ -10226,9 +10312,9 @@
       <c r="I56" s="53"/>
       <c r="N56" s="43"/>
     </row>
-    <row r="57" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F57" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="G57" s="53">
         <v>4690</v>
@@ -10237,9 +10323,9 @@
       <c r="I57" s="53"/>
       <c r="N57" s="43"/>
     </row>
-    <row r="58" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F58" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="G58" s="53">
         <v>-4440</v>
@@ -10248,9 +10334,9 @@
       <c r="I58" s="53"/>
       <c r="N58" s="43"/>
     </row>
-    <row r="59" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F59" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="G59" s="53">
         <v>-4697</v>
@@ -10258,9 +10344,9 @@
       <c r="H59" s="53"/>
       <c r="I59" s="53"/>
     </row>
-    <row r="60" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F60" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G60" s="53">
         <v>-2500</v>
@@ -10268,9 +10354,9 @@
       <c r="H60" s="53"/>
       <c r="I60" s="53"/>
     </row>
-    <row r="61" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F61" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="G61" s="53">
         <v>-126</v>
@@ -10278,9 +10364,9 @@
       <c r="H61" s="53"/>
       <c r="I61" s="53"/>
     </row>
-    <row r="62" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F62" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G62" s="53">
         <v>4742</v>
@@ -10288,9 +10374,9 @@
       <c r="H62" s="53"/>
       <c r="I62" s="53"/>
     </row>
-    <row r="63" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F63" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="G63" s="53">
         <v>-410</v>
@@ -10298,14 +10384,14 @@
       <c r="H63" s="53"/>
       <c r="I63" s="53"/>
     </row>
-    <row r="64" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="6:14" x14ac:dyDescent="0.3">
       <c r="G64" s="53"/>
       <c r="H64" s="53"/>
       <c r="I64" s="53"/>
     </row>
-    <row r="65" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F65" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="G65" s="53">
         <v>3320</v>
@@ -10313,9 +10399,9 @@
       <c r="H65" s="53"/>
       <c r="I65" s="53"/>
     </row>
-    <row r="66" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F66" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="G66" s="53">
         <v>4090</v>
@@ -10323,9 +10409,9 @@
       <c r="H66" s="53"/>
       <c r="I66" s="53"/>
     </row>
-    <row r="67" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F67" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="G67" s="53">
         <v>-5688</v>
@@ -10333,9 +10419,9 @@
       <c r="H67" s="53"/>
       <c r="I67" s="53"/>
     </row>
-    <row r="68" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F68" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="G68" s="53">
         <v>-4433</v>
@@ -10343,9 +10429,9 @@
       <c r="H68" s="53"/>
       <c r="I68" s="53"/>
     </row>
-    <row r="69" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F69" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G69" s="53">
         <v>-250</v>
@@ -10353,9 +10439,9 @@
       <c r="H69" s="53"/>
       <c r="I69" s="53"/>
     </row>
-    <row r="70" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F70" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="G70" s="53">
         <v>-99</v>
@@ -10363,9 +10449,9 @@
       <c r="H70" s="53"/>
       <c r="I70" s="53"/>
     </row>
-    <row r="71" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F71" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="G71" s="53">
         <v>320</v>
@@ -10373,9 +10459,9 @@
       <c r="H71" s="53"/>
       <c r="I71" s="53"/>
     </row>
-    <row r="72" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F72" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="G72" s="53">
         <v>-1572</v>
@@ -10383,14 +10469,14 @@
       <c r="H72" s="53"/>
       <c r="I72" s="53"/>
     </row>
-    <row r="73" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:9" x14ac:dyDescent="0.3">
       <c r="G73" s="53"/>
       <c r="H73" s="53"/>
       <c r="I73" s="53"/>
     </row>
-    <row r="74" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F74" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="G74" s="53">
         <v>4433</v>
@@ -10398,9 +10484,9 @@
       <c r="H74" s="53"/>
       <c r="I74" s="53"/>
     </row>
-    <row r="75" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F75" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="G75" s="53">
         <v>8000</v>
@@ -10408,9 +10494,9 @@
       <c r="H75" s="53"/>
       <c r="I75" s="53"/>
     </row>
-    <row r="76" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F76" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="G76" s="53">
         <v>-1344</v>
@@ -10418,9 +10504,9 @@
       <c r="H76" s="53"/>
       <c r="I76" s="53"/>
     </row>
-    <row r="77" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F77" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="G77" s="53">
         <v>-308</v>
@@ -10428,9 +10514,9 @@
       <c r="H77" s="53"/>
       <c r="I77" s="53"/>
     </row>
-    <row r="78" spans="6:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="6:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F78" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="G78" s="53">
         <v>-4204</v>
@@ -10438,9 +10524,9 @@
       <c r="H78" s="53"/>
       <c r="I78" s="53"/>
     </row>
-    <row r="79" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F79" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="G79" s="53">
         <v>-338</v>
@@ -10448,9 +10534,9 @@
       <c r="H79" s="53"/>
       <c r="I79" s="53"/>
     </row>
-    <row r="80" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F80" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="G80" s="53">
         <v>-50</v>
@@ -10458,9 +10544,9 @@
       <c r="H80" s="53"/>
       <c r="I80" s="53"/>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F81" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="G81" s="53">
         <v>338</v>
@@ -10468,9 +10554,9 @@
       <c r="H81" s="53"/>
       <c r="I81" s="53"/>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F82" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="G82" s="53">
         <v>-540</v>
@@ -10478,9 +10564,9 @@
       <c r="H82" s="53"/>
       <c r="I82" s="53"/>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F83" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="G83" s="53">
         <v>-184.31</v>
@@ -10488,11 +10574,9 @@
       <c r="H83" s="53"/>
       <c r="I83" s="53"/>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C84" s="53"/>
-      <c r="D84" s="53"/>
+    <row r="84" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F84" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="G84" s="53">
         <v>-1464.22</v>
@@ -10500,11 +10584,9 @@
       <c r="H84" s="53"/>
       <c r="I84" s="53"/>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C85" s="53"/>
-      <c r="D85" s="53"/>
+    <row r="85" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F85" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="G85" s="53">
         <v>1005</v>
@@ -10512,11 +10594,9 @@
       <c r="H85" s="53"/>
       <c r="I85" s="53"/>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C86" s="53"/>
-      <c r="D86" s="53"/>
+    <row r="86" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F86" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="G86" s="53">
         <v>-500</v>
@@ -10524,11 +10604,9 @@
       <c r="H86" s="53"/>
       <c r="I86" s="53"/>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C87" s="53"/>
-      <c r="D87" s="53"/>
+    <row r="87" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F87" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="G87" s="53">
         <v>-225</v>
@@ -10536,11 +10614,9 @@
       <c r="H87" s="53"/>
       <c r="I87" s="53"/>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C88" s="53"/>
-      <c r="D88" s="53"/>
+    <row r="88" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F88" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="G88" s="53">
         <v>-516</v>
@@ -10548,11 +10624,9 @@
       <c r="H88" s="53"/>
       <c r="I88" s="53"/>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C89" s="53"/>
-      <c r="D89" s="53"/>
+    <row r="89" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F89" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="G89" s="53">
         <v>4204</v>
@@ -10560,11 +10634,9 @@
       <c r="H89" s="53"/>
       <c r="I89" s="53"/>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C90" s="53"/>
-      <c r="D90" s="53"/>
+    <row r="90" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F90" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="G90" s="53">
         <v>-100</v>
@@ -10572,11 +10644,9 @@
       <c r="H90" s="53"/>
       <c r="I90" s="53"/>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C91" s="53"/>
-      <c r="D91" s="53"/>
+    <row r="91" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F91" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="G91" s="53">
         <v>8000</v>
@@ -10584,11 +10654,9 @@
       <c r="H91" s="53"/>
       <c r="I91" s="53"/>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C92" s="53"/>
-      <c r="D92" s="53"/>
+    <row r="92" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F92" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="G92" s="53">
         <v>1000</v>
@@ -10596,11 +10664,9 @@
       <c r="H92" s="53"/>
       <c r="I92" s="53"/>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C93" s="53"/>
-      <c r="D93" s="53"/>
+    <row r="93" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F93" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="G93" s="53">
         <v>-12881</v>
@@ -10608,11 +10674,9 @@
       <c r="H93" s="53"/>
       <c r="I93" s="53"/>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C94" s="53"/>
-      <c r="D94" s="53"/>
+    <row r="94" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F94" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="G94" s="53">
         <v>-4489.62</v>
@@ -10620,11 +10684,9 @@
       <c r="H94" s="53"/>
       <c r="I94" s="53"/>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C95" s="53"/>
-      <c r="D95" s="53"/>
+    <row r="95" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F95" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="G95" s="53">
         <v>5000</v>
@@ -10632,18 +10694,9 @@
       <c r="H95" s="53"/>
       <c r="I95" s="53"/>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B96" t="s">
-        <v>267</v>
-      </c>
-      <c r="C96" s="53">
-        <v>2000</v>
-      </c>
-      <c r="D96" s="53">
-        <v>300</v>
-      </c>
+    <row r="96" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F96" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="G96" s="53">
         <v>-480</v>
@@ -10651,11 +10704,11 @@
       <c r="H96" s="53"/>
       <c r="I96" s="53"/>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C97" s="53"/>
       <c r="D97" s="53"/>
       <c r="F97" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="G97" s="53">
         <v>-520</v>
@@ -10663,11 +10716,11 @@
       <c r="H97" s="53"/>
       <c r="I97" s="53"/>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C98" s="53"/>
       <c r="D98" s="53"/>
       <c r="F98" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G98" s="53">
         <v>5556.2</v>
@@ -10675,11 +10728,18 @@
       <c r="H98" s="53"/>
       <c r="I98" s="53"/>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C99" s="53"/>
-      <c r="D99" s="53"/>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B99" t="s">
+        <v>281</v>
+      </c>
+      <c r="C99" s="53">
+        <v>2000</v>
+      </c>
+      <c r="D99" s="53">
+        <v>300</v>
+      </c>
       <c r="F99" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="G99" s="53">
         <v>-500</v>
@@ -10687,9 +10747,9 @@
       <c r="H99" s="53"/>
       <c r="I99" s="53"/>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="C100" s="53">
         <v>2000</v>
@@ -10698,7 +10758,7 @@
         <v>300</v>
       </c>
       <c r="F100" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="G100" s="53">
         <v>-276</v>
@@ -10706,21 +10766,26 @@
       <c r="H100" s="53"/>
       <c r="I100" s="53"/>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C101" s="53">
         <v>8000</v>
       </c>
       <c r="D101" s="53"/>
-      <c r="G101" s="53"/>
+      <c r="F101" t="s">
+        <v>286</v>
+      </c>
+      <c r="G101" s="53">
+        <v>-250</v>
+      </c>
       <c r="H101" s="53"/>
       <c r="I101" s="53"/>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="C102" s="53">
         <v>4180</v>
@@ -10730,16 +10795,16 @@
       <c r="H102" s="53"/>
       <c r="I102" s="53"/>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C103" s="53"/>
       <c r="D103" s="53"/>
       <c r="G103" s="53"/>
       <c r="H103" s="53"/>
       <c r="I103" s="53"/>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="C104" s="53">
         <v>2000</v>
@@ -10751,9 +10816,9 @@
       <c r="H104" s="53"/>
       <c r="I104" s="53"/>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="C105" s="53">
         <v>2000</v>
@@ -10765,9 +10830,9 @@
       <c r="H105" s="53"/>
       <c r="I105" s="53"/>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="C106" s="53">
         <v>2000</v>
@@ -10779,16 +10844,16 @@
       <c r="H106" s="53"/>
       <c r="I106" s="53"/>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C107" s="53"/>
       <c r="D107" s="53"/>
       <c r="G107" s="53"/>
       <c r="H107" s="53"/>
       <c r="I107" s="53"/>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="C108" s="53">
         <v>-20000</v>
@@ -10798,16 +10863,16 @@
       <c r="H108" s="53"/>
       <c r="I108" s="53"/>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C109" s="53"/>
       <c r="D109" s="53"/>
       <c r="G109" s="53"/>
       <c r="H109" s="53"/>
       <c r="I109" s="53"/>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="C110" s="53">
         <v>2000</v>
@@ -10819,9 +10884,9 @@
       <c r="H110" s="53"/>
       <c r="I110" s="53"/>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C111" s="53">
         <v>2000</v>
@@ -10833,9 +10898,9 @@
       <c r="H111" s="53"/>
       <c r="I111" s="53"/>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="C112" s="53">
         <v>8000</v>
@@ -10845,9 +10910,9 @@
       <c r="H112" s="53"/>
       <c r="I112" s="53"/>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B113" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="C113" s="53">
         <v>2000</v>
@@ -10859,9 +10924,9 @@
       <c r="H113" s="53"/>
       <c r="I113" s="53"/>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="C114" s="53">
         <v>2000</v>
@@ -10873,1204 +10938,1204 @@
       <c r="H114" s="53"/>
       <c r="I114" s="53"/>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C115" s="53"/>
       <c r="G115" s="53"/>
       <c r="H115" s="53"/>
       <c r="I115" s="53"/>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C116" s="53"/>
       <c r="G116" s="53"/>
       <c r="H116" s="53"/>
       <c r="I116" s="53"/>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C117" s="53"/>
       <c r="G117" s="53"/>
       <c r="H117" s="53"/>
       <c r="I117" s="53"/>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C118" s="53"/>
       <c r="G118" s="53"/>
       <c r="H118" s="53"/>
       <c r="I118" s="53"/>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C119" s="53"/>
       <c r="G119" s="53"/>
       <c r="H119" s="53"/>
       <c r="I119" s="53"/>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C120" s="53"/>
       <c r="G120" s="53"/>
       <c r="H120" s="53"/>
       <c r="I120" s="53"/>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C121" s="53"/>
       <c r="G121" s="53"/>
       <c r="H121" s="53"/>
       <c r="I121" s="53"/>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G122" s="53"/>
-      <c r="H122" s="75"/>
+      <c r="H122" s="74"/>
       <c r="I122" s="53"/>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G123" s="53"/>
-      <c r="H123" s="75"/>
+      <c r="H123" s="74"/>
       <c r="I123" s="53"/>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G124" s="53"/>
-      <c r="H124" s="75"/>
+      <c r="H124" s="74"/>
       <c r="I124" s="53"/>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G125" s="53"/>
-      <c r="H125" s="75"/>
+      <c r="H125" s="74"/>
       <c r="I125" s="53"/>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G126" s="53"/>
-      <c r="H126" s="75"/>
+      <c r="H126" s="74"/>
       <c r="I126" s="53"/>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G127" s="53"/>
-      <c r="H127" s="75"/>
+      <c r="H127" s="74"/>
       <c r="I127" s="53"/>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G128" s="53"/>
-      <c r="H128" s="75"/>
+      <c r="H128" s="74"/>
       <c r="I128" s="53"/>
     </row>
-    <row r="129" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G129" s="53"/>
       <c r="H129" s="53"/>
       <c r="I129" s="53"/>
     </row>
-    <row r="130" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G130" s="53"/>
       <c r="H130" s="53"/>
       <c r="I130" s="53"/>
     </row>
-    <row r="131" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G131" s="53"/>
       <c r="H131" s="53"/>
       <c r="I131" s="53"/>
     </row>
-    <row r="132" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G132" s="53"/>
       <c r="H132" s="53"/>
       <c r="I132" s="53"/>
     </row>
-    <row r="133" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G133" s="53"/>
       <c r="H133" s="53"/>
       <c r="I133" s="53"/>
     </row>
-    <row r="134" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G134" s="53"/>
       <c r="H134" s="53"/>
       <c r="I134" s="53"/>
     </row>
-    <row r="135" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G135" s="53"/>
       <c r="H135" s="53"/>
       <c r="I135" s="53"/>
     </row>
-    <row r="136" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G136" s="53"/>
       <c r="H136" s="53"/>
       <c r="I136" s="53"/>
     </row>
-    <row r="137" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G137" s="53"/>
       <c r="H137" s="53"/>
       <c r="I137" s="53"/>
     </row>
-    <row r="138" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G138" s="53"/>
       <c r="H138" s="53"/>
       <c r="I138" s="53"/>
     </row>
-    <row r="139" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G139" s="53"/>
       <c r="H139" s="53"/>
       <c r="I139" s="53"/>
     </row>
-    <row r="140" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G140" s="53"/>
       <c r="H140" s="53"/>
       <c r="I140" s="53"/>
     </row>
-    <row r="141" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G141" s="53"/>
       <c r="H141" s="53"/>
       <c r="I141" s="53"/>
     </row>
-    <row r="142" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G142" s="53"/>
       <c r="H142" s="53"/>
       <c r="I142" s="53"/>
     </row>
-    <row r="143" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G143" s="53"/>
       <c r="H143" s="53"/>
       <c r="I143" s="53"/>
     </row>
-    <row r="144" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G144" s="53"/>
       <c r="H144" s="53"/>
       <c r="I144" s="53"/>
     </row>
-    <row r="145" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G145" s="53"/>
       <c r="H145" s="53"/>
       <c r="I145" s="53"/>
     </row>
-    <row r="146" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G146" s="53"/>
       <c r="H146" s="53"/>
       <c r="I146" s="53"/>
     </row>
-    <row r="147" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G147" s="53"/>
       <c r="H147" s="53"/>
       <c r="I147" s="53"/>
     </row>
-    <row r="148" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G148" s="53"/>
       <c r="H148" s="53"/>
       <c r="I148" s="53"/>
     </row>
-    <row r="149" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G149" s="53"/>
       <c r="H149" s="53"/>
       <c r="I149" s="53"/>
     </row>
-    <row r="150" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G150" s="53"/>
       <c r="H150" s="53"/>
       <c r="I150" s="53"/>
     </row>
-    <row r="151" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G151" s="53"/>
       <c r="H151" s="53"/>
       <c r="I151" s="53"/>
     </row>
-    <row r="152" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G152" s="53"/>
       <c r="H152" s="53"/>
       <c r="I152" s="53"/>
     </row>
-    <row r="153" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G153" s="53"/>
       <c r="H153" s="53"/>
       <c r="I153" s="53"/>
     </row>
-    <row r="154" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G154" s="53"/>
       <c r="H154" s="53"/>
       <c r="I154" s="53"/>
     </row>
-    <row r="155" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G155" s="53"/>
       <c r="H155" s="53"/>
       <c r="I155" s="53"/>
     </row>
-    <row r="156" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G156" s="53"/>
       <c r="H156" s="53"/>
       <c r="I156" s="53"/>
     </row>
-    <row r="157" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G157" s="53"/>
       <c r="H157" s="53"/>
       <c r="I157" s="53"/>
     </row>
-    <row r="158" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G158" s="53"/>
       <c r="H158" s="53"/>
       <c r="I158" s="53"/>
     </row>
-    <row r="159" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G159" s="53"/>
       <c r="H159" s="53"/>
       <c r="I159" s="53"/>
     </row>
-    <row r="160" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G160" s="53"/>
       <c r="H160" s="53"/>
       <c r="I160" s="53"/>
     </row>
-    <row r="161" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G161" s="53"/>
       <c r="H161" s="53"/>
       <c r="I161" s="53"/>
     </row>
-    <row r="162" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G162" s="53"/>
       <c r="H162" s="53"/>
       <c r="I162" s="53"/>
     </row>
-    <row r="163" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G163" s="53"/>
       <c r="H163" s="53"/>
       <c r="I163" s="53"/>
     </row>
-    <row r="164" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G164" s="53"/>
       <c r="H164" s="53"/>
       <c r="I164" s="53"/>
     </row>
-    <row r="165" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G165" s="53"/>
       <c r="H165" s="53"/>
       <c r="I165" s="53"/>
     </row>
-    <row r="166" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G166" s="53"/>
       <c r="H166" s="53"/>
       <c r="I166" s="53"/>
     </row>
-    <row r="167" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G167" s="53"/>
       <c r="H167" s="53"/>
       <c r="I167" s="53"/>
     </row>
-    <row r="168" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G168" s="53"/>
       <c r="H168" s="53"/>
       <c r="I168" s="53"/>
     </row>
-    <row r="169" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G169" s="53"/>
       <c r="H169" s="53"/>
       <c r="I169" s="53"/>
     </row>
-    <row r="170" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G170" s="53"/>
       <c r="H170" s="53"/>
       <c r="I170" s="53"/>
     </row>
-    <row r="171" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G171" s="53"/>
       <c r="H171" s="53"/>
       <c r="I171" s="53"/>
     </row>
-    <row r="172" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G172" s="53"/>
       <c r="H172" s="53"/>
       <c r="I172" s="53"/>
     </row>
-    <row r="173" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G173" s="53"/>
       <c r="H173" s="53"/>
       <c r="I173" s="53"/>
     </row>
-    <row r="174" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G174" s="53"/>
       <c r="H174" s="53"/>
       <c r="I174" s="53"/>
     </row>
-    <row r="175" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G175" s="53"/>
       <c r="H175" s="53"/>
       <c r="I175" s="53"/>
     </row>
-    <row r="176" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G176" s="53"/>
       <c r="H176" s="53"/>
       <c r="I176" s="53"/>
     </row>
-    <row r="177" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G177" s="53"/>
       <c r="H177" s="53"/>
       <c r="I177" s="53"/>
     </row>
-    <row r="178" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G178" s="53"/>
       <c r="H178" s="53"/>
       <c r="I178" s="53"/>
     </row>
-    <row r="179" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G179" s="53"/>
       <c r="H179" s="53"/>
       <c r="I179" s="53"/>
     </row>
-    <row r="180" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G180" s="53"/>
       <c r="H180" s="53"/>
       <c r="I180" s="53"/>
     </row>
-    <row r="181" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G181" s="53"/>
       <c r="H181" s="53"/>
       <c r="I181" s="53"/>
     </row>
-    <row r="182" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G182" s="53"/>
       <c r="H182" s="53"/>
       <c r="I182" s="53"/>
     </row>
-    <row r="183" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G183" s="53"/>
       <c r="H183" s="53"/>
       <c r="I183" s="53"/>
     </row>
-    <row r="184" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G184" s="53"/>
       <c r="H184" s="53"/>
       <c r="I184" s="53"/>
     </row>
-    <row r="185" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G185" s="53"/>
       <c r="H185" s="53"/>
       <c r="I185" s="53"/>
     </row>
-    <row r="186" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G186" s="53"/>
       <c r="H186" s="53"/>
       <c r="I186" s="53"/>
     </row>
-    <row r="187" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G187" s="53"/>
       <c r="H187" s="53"/>
       <c r="I187" s="53"/>
     </row>
-    <row r="188" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G188" s="53"/>
       <c r="H188" s="53"/>
       <c r="I188" s="53"/>
     </row>
-    <row r="189" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G189" s="53"/>
       <c r="H189" s="53"/>
       <c r="I189" s="53"/>
     </row>
-    <row r="190" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G190" s="53"/>
       <c r="H190" s="53"/>
       <c r="I190" s="53"/>
     </row>
-    <row r="191" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G191" s="53"/>
       <c r="H191" s="53"/>
       <c r="I191" s="53"/>
     </row>
-    <row r="192" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G192" s="53"/>
       <c r="H192" s="53"/>
       <c r="I192" s="53"/>
     </row>
-    <row r="193" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G193" s="53"/>
       <c r="H193" s="53"/>
       <c r="I193" s="53"/>
     </row>
-    <row r="194" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G194" s="53"/>
       <c r="H194" s="53"/>
       <c r="I194" s="53"/>
     </row>
-    <row r="195" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G195" s="53"/>
       <c r="H195" s="53"/>
       <c r="I195" s="53"/>
     </row>
-    <row r="196" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G196" s="53"/>
       <c r="H196" s="53"/>
       <c r="I196" s="53"/>
     </row>
-    <row r="197" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G197" s="53"/>
       <c r="H197" s="53"/>
       <c r="I197" s="53"/>
     </row>
-    <row r="198" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G198" s="53"/>
       <c r="H198" s="53"/>
       <c r="I198" s="53"/>
     </row>
-    <row r="199" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G199" s="53"/>
       <c r="H199" s="53"/>
       <c r="I199" s="53"/>
     </row>
-    <row r="200" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G200" s="53"/>
       <c r="H200" s="53"/>
       <c r="I200" s="53"/>
     </row>
-    <row r="201" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G201" s="53"/>
       <c r="H201" s="53"/>
       <c r="I201" s="53"/>
     </row>
-    <row r="202" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G202" s="53"/>
       <c r="H202" s="53"/>
       <c r="I202" s="53"/>
     </row>
-    <row r="203" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G203" s="53"/>
       <c r="H203" s="53"/>
       <c r="I203" s="53"/>
     </row>
-    <row r="204" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G204" s="53"/>
       <c r="H204" s="53"/>
       <c r="I204" s="53"/>
     </row>
-    <row r="205" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G205" s="53"/>
       <c r="H205" s="53"/>
       <c r="I205" s="53"/>
     </row>
-    <row r="206" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G206" s="53"/>
       <c r="H206" s="53"/>
       <c r="I206" s="53"/>
     </row>
-    <row r="207" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G207" s="53"/>
       <c r="H207" s="53"/>
       <c r="I207" s="53"/>
     </row>
-    <row r="208" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G208" s="53"/>
       <c r="H208" s="53"/>
       <c r="I208" s="53"/>
     </row>
-    <row r="209" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G209" s="53"/>
       <c r="H209" s="53"/>
       <c r="I209" s="53"/>
     </row>
-    <row r="210" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G210" s="53"/>
       <c r="H210" s="53"/>
       <c r="I210" s="53"/>
     </row>
-    <row r="211" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G211" s="53"/>
       <c r="H211" s="53"/>
       <c r="I211" s="53"/>
     </row>
-    <row r="212" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G212" s="53"/>
       <c r="H212" s="53"/>
       <c r="I212" s="53"/>
     </row>
-    <row r="213" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G213" s="53"/>
       <c r="H213" s="53"/>
       <c r="I213" s="53"/>
     </row>
-    <row r="214" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G214" s="53"/>
       <c r="H214" s="53"/>
       <c r="I214" s="53"/>
     </row>
-    <row r="215" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G215" s="53"/>
       <c r="H215" s="53"/>
       <c r="I215" s="53"/>
     </row>
-    <row r="216" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G216" s="53"/>
       <c r="H216" s="53"/>
       <c r="I216" s="53"/>
     </row>
-    <row r="217" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G217" s="53"/>
       <c r="H217" s="53"/>
       <c r="I217" s="53"/>
     </row>
-    <row r="218" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G218" s="53"/>
       <c r="H218" s="53"/>
       <c r="I218" s="53"/>
     </row>
-    <row r="219" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G219" s="53"/>
       <c r="H219" s="53"/>
       <c r="I219" s="53"/>
     </row>
-    <row r="220" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G220" s="53"/>
       <c r="H220" s="53"/>
       <c r="I220" s="53"/>
     </row>
-    <row r="221" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G221" s="53"/>
       <c r="H221" s="53"/>
       <c r="I221" s="53"/>
     </row>
-    <row r="222" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G222" s="53"/>
       <c r="H222" s="53"/>
       <c r="I222" s="53"/>
     </row>
-    <row r="223" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G223" s="53"/>
       <c r="H223" s="53"/>
       <c r="I223" s="53"/>
     </row>
-    <row r="224" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G224" s="53"/>
       <c r="H224" s="53"/>
       <c r="I224" s="53"/>
     </row>
-    <row r="225" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G225" s="53"/>
       <c r="H225" s="53"/>
       <c r="I225" s="53"/>
     </row>
-    <row r="226" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G226" s="53"/>
       <c r="H226" s="53"/>
       <c r="I226" s="53"/>
     </row>
-    <row r="227" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G227" s="53"/>
       <c r="H227" s="53"/>
       <c r="I227" s="53"/>
     </row>
-    <row r="228" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G228" s="53"/>
       <c r="H228" s="53"/>
       <c r="I228" s="53"/>
     </row>
-    <row r="229" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G229" s="53"/>
       <c r="H229" s="53"/>
       <c r="I229" s="53"/>
     </row>
-    <row r="230" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G230" s="53"/>
       <c r="H230" s="53"/>
       <c r="I230" s="53"/>
     </row>
-    <row r="231" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G231" s="53"/>
       <c r="H231" s="53"/>
       <c r="I231" s="53"/>
     </row>
-    <row r="232" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G232" s="53"/>
       <c r="H232" s="53"/>
       <c r="I232" s="53"/>
     </row>
-    <row r="233" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G233" s="53"/>
       <c r="H233" s="53"/>
       <c r="I233" s="53"/>
     </row>
-    <row r="234" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G234" s="53"/>
       <c r="H234" s="53"/>
       <c r="I234" s="53"/>
     </row>
-    <row r="235" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G235" s="53"/>
       <c r="H235" s="53"/>
       <c r="I235" s="53"/>
     </row>
-    <row r="236" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G236" s="53"/>
       <c r="H236" s="53"/>
       <c r="I236" s="53"/>
     </row>
-    <row r="237" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G237" s="53"/>
       <c r="H237" s="53"/>
       <c r="I237" s="53"/>
     </row>
-    <row r="238" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G238" s="53"/>
       <c r="H238" s="53"/>
       <c r="I238" s="53"/>
     </row>
-    <row r="239" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G239" s="53"/>
       <c r="H239" s="53"/>
       <c r="I239" s="53"/>
     </row>
-    <row r="240" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G240" s="53"/>
       <c r="H240" s="53"/>
       <c r="I240" s="53"/>
     </row>
-    <row r="241" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G241" s="53"/>
       <c r="H241" s="53"/>
       <c r="I241" s="53"/>
     </row>
-    <row r="242" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G242" s="53"/>
       <c r="H242" s="53"/>
       <c r="I242" s="53"/>
     </row>
-    <row r="243" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G243" s="53"/>
       <c r="H243" s="53"/>
       <c r="I243" s="53"/>
     </row>
-    <row r="244" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G244" s="53"/>
       <c r="H244" s="53"/>
       <c r="I244" s="53"/>
     </row>
-    <row r="245" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G245" s="53"/>
       <c r="H245" s="53"/>
       <c r="I245" s="53"/>
     </row>
-    <row r="246" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G246" s="53"/>
       <c r="H246" s="53"/>
       <c r="I246" s="53"/>
     </row>
-    <row r="247" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G247" s="53"/>
       <c r="H247" s="53"/>
       <c r="I247" s="53"/>
     </row>
-    <row r="248" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G248" s="53"/>
       <c r="H248" s="53"/>
       <c r="I248" s="53"/>
     </row>
-    <row r="249" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G249" s="53"/>
       <c r="H249" s="53"/>
       <c r="I249" s="53"/>
     </row>
-    <row r="250" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G250" s="53"/>
       <c r="H250" s="53"/>
       <c r="I250" s="53"/>
     </row>
-    <row r="251" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G251" s="53"/>
       <c r="H251" s="53"/>
       <c r="I251" s="53"/>
     </row>
-    <row r="252" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G252" s="53"/>
       <c r="H252" s="53"/>
       <c r="I252" s="53"/>
     </row>
-    <row r="253" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G253" s="53"/>
       <c r="H253" s="53"/>
       <c r="I253" s="53"/>
     </row>
-    <row r="254" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G254" s="53"/>
       <c r="H254" s="53"/>
       <c r="I254" s="53"/>
     </row>
-    <row r="255" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G255" s="53"/>
       <c r="H255" s="53"/>
       <c r="I255" s="53"/>
     </row>
-    <row r="256" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G256" s="53"/>
       <c r="H256" s="53"/>
       <c r="I256" s="53"/>
     </row>
-    <row r="257" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G257" s="53"/>
       <c r="H257" s="1"/>
       <c r="I257" s="1"/>
     </row>
-    <row r="258" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G258" s="53"/>
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>
     </row>
-    <row r="259" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G259" s="53"/>
       <c r="H259" s="1"/>
       <c r="I259" s="1"/>
     </row>
-    <row r="260" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G260" s="53"/>
       <c r="H260" s="1"/>
       <c r="I260" s="1"/>
     </row>
-    <row r="261" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G261" s="53"/>
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
     </row>
-    <row r="262" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G262" s="53"/>
       <c r="H262" s="1"/>
       <c r="I262" s="1"/>
     </row>
-    <row r="263" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G263" s="53"/>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
     </row>
-    <row r="264" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G264" s="53"/>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
     </row>
-    <row r="265" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G265" s="53"/>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
     </row>
-    <row r="266" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G266" s="53"/>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
     </row>
-    <row r="267" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G267" s="53"/>
     </row>
-    <row r="268" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G268" s="53"/>
     </row>
-    <row r="269" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G269" s="53"/>
     </row>
-    <row r="270" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G270" s="53"/>
     </row>
-    <row r="271" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G271" s="53"/>
     </row>
-    <row r="272" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G272" s="53"/>
     </row>
-    <row r="273" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G273" s="53"/>
     </row>
-    <row r="274" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G274" s="53"/>
     </row>
-    <row r="275" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G275" s="53"/>
     </row>
-    <row r="276" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G276" s="53"/>
     </row>
-    <row r="277" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G277" s="53"/>
     </row>
-    <row r="278" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G278" s="53"/>
     </row>
-    <row r="279" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G279" s="53"/>
     </row>
-    <row r="280" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G280" s="53"/>
     </row>
-    <row r="281" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G281" s="53"/>
     </row>
-    <row r="282" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G282" s="53"/>
     </row>
-    <row r="283" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G283" s="53"/>
     </row>
-    <row r="284" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G284" s="53"/>
     </row>
-    <row r="285" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G285" s="53"/>
     </row>
-    <row r="286" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G286" s="53"/>
     </row>
-    <row r="287" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G287" s="53"/>
     </row>
-    <row r="288" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G288" s="53"/>
     </row>
-    <row r="289" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G289" s="53"/>
     </row>
-    <row r="290" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G290" s="53"/>
     </row>
-    <row r="291" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G291" s="53"/>
     </row>
-    <row r="292" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G292" s="53"/>
     </row>
-    <row r="293" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G293" s="53"/>
     </row>
-    <row r="294" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G294" s="53"/>
     </row>
-    <row r="295" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G295" s="53"/>
     </row>
-    <row r="296" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G296" s="53"/>
     </row>
-    <row r="297" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G297" s="53"/>
     </row>
-    <row r="298" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G298" s="53"/>
     </row>
-    <row r="299" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G299" s="53"/>
     </row>
-    <row r="300" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G300" s="53"/>
     </row>
-    <row r="301" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G301" s="53"/>
     </row>
-    <row r="302" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G302" s="53"/>
     </row>
-    <row r="303" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G303" s="53"/>
     </row>
-    <row r="304" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G304" s="53"/>
     </row>
-    <row r="305" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G305" s="53"/>
     </row>
-    <row r="306" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G306" s="53"/>
     </row>
-    <row r="307" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G307" s="53"/>
     </row>
-    <row r="308" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G308" s="53"/>
     </row>
-    <row r="309" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G309" s="53"/>
     </row>
-    <row r="310" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G310" s="53"/>
     </row>
-    <row r="311" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G311" s="53"/>
     </row>
-    <row r="312" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G312" s="53"/>
     </row>
-    <row r="313" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G313" s="53"/>
     </row>
-    <row r="314" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G314" s="53"/>
     </row>
-    <row r="315" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G315" s="53"/>
     </row>
-    <row r="316" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G316" s="53"/>
     </row>
-    <row r="317" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G317" s="53"/>
     </row>
-    <row r="318" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G318" s="53"/>
     </row>
-    <row r="319" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G319" s="53"/>
     </row>
-    <row r="320" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G320" s="53"/>
     </row>
-    <row r="321" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G321" s="53"/>
     </row>
-    <row r="322" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G322" s="53"/>
     </row>
-    <row r="323" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G323" s="53"/>
     </row>
-    <row r="324" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G324" s="53"/>
     </row>
-    <row r="325" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G325" s="53"/>
     </row>
-    <row r="326" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G326" s="53"/>
     </row>
-    <row r="327" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G327" s="53"/>
     </row>
-    <row r="328" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G328" s="53"/>
     </row>
-    <row r="329" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G329" s="53"/>
     </row>
-    <row r="330" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G330" s="53"/>
     </row>
-    <row r="331" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G331" s="53"/>
     </row>
-    <row r="332" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G332" s="53"/>
     </row>
-    <row r="333" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G333" s="53"/>
     </row>
-    <row r="334" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G334" s="53"/>
     </row>
-    <row r="335" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G335" s="53"/>
     </row>
-    <row r="336" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G336" s="53"/>
     </row>
-    <row r="337" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G337" s="53"/>
     </row>
-    <row r="338" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G338" s="53"/>
     </row>
-    <row r="339" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G339" s="53"/>
     </row>
-    <row r="340" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G340" s="53"/>
     </row>
-    <row r="341" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G341" s="53"/>
     </row>
-    <row r="342" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G342" s="53"/>
     </row>
-    <row r="343" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G343" s="53"/>
     </row>
-    <row r="344" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G344" s="53"/>
     </row>
-    <row r="345" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G345" s="53"/>
     </row>
-    <row r="346" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G346" s="53"/>
     </row>
-    <row r="347" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G347" s="53"/>
     </row>
-    <row r="348" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G348" s="53"/>
     </row>
-    <row r="349" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G349" s="53"/>
     </row>
-    <row r="350" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G350" s="53"/>
     </row>
-    <row r="351" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G351" s="53"/>
     </row>
-    <row r="352" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G352" s="53"/>
     </row>
-    <row r="353" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G353" s="53"/>
     </row>
-    <row r="354" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G354" s="53"/>
     </row>
-    <row r="355" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G355" s="53"/>
     </row>
-    <row r="356" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G356" s="53"/>
     </row>
-    <row r="357" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G357" s="53"/>
     </row>
-    <row r="358" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G358" s="53"/>
     </row>
-    <row r="359" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G359" s="53"/>
     </row>
-    <row r="360" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G360" s="53"/>
     </row>
-    <row r="361" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G361" s="53"/>
     </row>
-    <row r="362" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G362" s="53"/>
     </row>
-    <row r="363" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G363" s="53"/>
     </row>
-    <row r="364" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G364" s="53"/>
     </row>
-    <row r="365" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G365" s="53"/>
     </row>
-    <row r="366" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G366" s="53"/>
     </row>
-    <row r="367" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G367" s="53"/>
     </row>
-    <row r="368" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G368" s="53"/>
     </row>
-    <row r="369" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G369" s="53"/>
     </row>
-    <row r="370" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G370" s="53"/>
     </row>
-    <row r="371" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G371" s="53"/>
     </row>
-    <row r="372" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G372" s="53"/>
     </row>
-    <row r="373" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G373" s="53"/>
     </row>
-    <row r="374" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G374" s="53"/>
     </row>
-    <row r="375" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G375" s="53"/>
     </row>
-    <row r="376" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G376" s="53"/>
     </row>
-    <row r="377" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G377" s="53"/>
     </row>
-    <row r="378" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G378" s="53"/>
     </row>
-    <row r="379" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G379" s="53"/>
     </row>
-    <row r="380" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G380" s="53"/>
     </row>
-    <row r="381" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G381" s="53"/>
     </row>
-    <row r="382" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G382" s="53"/>
     </row>
-    <row r="383" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G383" s="53"/>
     </row>
-    <row r="384" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G384" s="53"/>
     </row>
-    <row r="385" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G385" s="53"/>
     </row>
-    <row r="386" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G386" s="53"/>
     </row>
-    <row r="387" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G387" s="53"/>
     </row>
-    <row r="388" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G388" s="53"/>
     </row>
-    <row r="389" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G389" s="53"/>
     </row>
-    <row r="390" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G390" s="53"/>
     </row>
-    <row r="391" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G391" s="53"/>
     </row>
-    <row r="392" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G392" s="53"/>
     </row>
-    <row r="393" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G393" s="53"/>
     </row>
-    <row r="394" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G394" s="53"/>
     </row>
-    <row r="395" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G395" s="53"/>
     </row>
-    <row r="396" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G396" s="53"/>
     </row>
-    <row r="397" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G397" s="53"/>
     </row>
-    <row r="398" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G398" s="53"/>
     </row>
-    <row r="399" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G399" s="53"/>
     </row>
-    <row r="400" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G400" s="53"/>
     </row>
-    <row r="401" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G401" s="53"/>
     </row>
-    <row r="402" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G402" s="53"/>
     </row>
-    <row r="403" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G403" s="53"/>
     </row>
-    <row r="404" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G404" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="M3:M4"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C84:D114 C115:C121">
-    <cfRule type="cellIs" dxfId="13" priority="181" operator="greaterThan">
+  <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C97:D114 C115:C121">
+    <cfRule type="cellIs" dxfId="13" priority="189" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="182" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="190" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G123:G1048576">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="17" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12083,34 +12148,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:I95">
-    <cfRule type="cellIs" dxfId="7" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="29" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="30" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H123:H130">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="12" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H131:I266">
-    <cfRule type="cellIs" dxfId="3" priority="179" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="187" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="180" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="188" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I96:I130">
-    <cfRule type="cellIs" dxfId="1" priority="27" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="35" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="28" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="36" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12122,109 +12187,109 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:D17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="47.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B1" s="62" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="C1" s="63" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" s="54" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="D2" s="54"/>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="54" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D3" s="54"/>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="54" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D4" s="54"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="54" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="D5" s="54"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="54" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D6" s="54"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="54" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="D7" s="54"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="54" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D8" s="54"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="54" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="54" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D10" s="54"/>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C17" s="28"/>
     </row>
   </sheetData>

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="11_C0E26E8C2FF3658481E6AE6DE74C74B31A2D8B7D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4296527D-666C-41B8-A631-91D907291824}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="11_C0E26E8C2FF3658481E6AE6DE74C74B31A2D8B7D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C2A6E34-B88C-4799-A709-C607474C06A7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Itaú!$C$4:$Q$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NuBank!$C$5:$Q$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NuBank!$C$5:$Q$47</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="246">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -264,9 +264,6 @@
     <t>Vans Loafer</t>
   </si>
   <si>
-    <t>Blood of the Dawnwalker</t>
-  </si>
-  <si>
     <t>Clube Literatura Clássica</t>
   </si>
   <si>
@@ -378,6 +375,63 @@
     <t>Pet</t>
   </si>
   <si>
+    <t>Vinhos Rappi</t>
+  </si>
+  <si>
+    <t>Comida</t>
+  </si>
+  <si>
+    <t>Pagamento Vinhos Rappi</t>
+  </si>
+  <si>
+    <t>PAGAMENTO</t>
+  </si>
+  <si>
+    <t>Alemão</t>
+  </si>
+  <si>
+    <t>Alemão parte que vou assumir</t>
+  </si>
+  <si>
+    <t>Serviços</t>
+  </si>
+  <si>
+    <t>Gasolina</t>
+  </si>
+  <si>
+    <t>Rappi</t>
+  </si>
+  <si>
+    <t>Pagamento Gasolina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bifinhos </t>
+  </si>
+  <si>
+    <t>Pets</t>
+  </si>
+  <si>
+    <t>Brinquedos Rennala</t>
+  </si>
+  <si>
+    <t>Organizador de Fios</t>
+  </si>
+  <si>
+    <t>Pote de Reção</t>
+  </si>
+  <si>
+    <t>Case ZFold</t>
+  </si>
+  <si>
+    <t>Croma Beer</t>
+  </si>
+  <si>
+    <t>Uber Croma</t>
+  </si>
+  <si>
+    <t>Pagamento Croma Beer</t>
+  </si>
+  <si>
     <t>Vivo</t>
   </si>
   <si>
@@ -486,9 +540,6 @@
     <t>SiSenor</t>
   </si>
   <si>
-    <t>Alemão</t>
-  </si>
-  <si>
     <t>GPS Moto</t>
   </si>
   <si>
@@ -684,6 +735,9 @@
     <t>Fevereiro</t>
   </si>
   <si>
+    <t>Aniversário</t>
+  </si>
+  <si>
     <t>Março</t>
   </si>
   <si>
@@ -730,18 +784,6 @@
   </si>
   <si>
     <t>Dera</t>
-  </si>
-  <si>
-    <t>Vinhos Rappi</t>
-  </si>
-  <si>
-    <t>Comida</t>
-  </si>
-  <si>
-    <t>PAGAMENTO</t>
-  </si>
-  <si>
-    <t>Pagamento Vinhos Rappi</t>
   </si>
 </sst>
 </file>
@@ -753,7 +795,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1225,21 +1267,12 @@
     <xf numFmtId="4" fontId="15" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1252,18 +1285,30 @@
     <xf numFmtId="1" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="30">
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79989013336588644"/>
-        </patternFill>
-      </fill>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1334,6 +1379,50 @@
       <font>
         <color rgb="FF00B050"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1634,7 +1723,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:F41"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
     <col min="3" max="3" width="19.85546875" style="1" customWidth="1"/>
@@ -1643,9 +1732,9 @@
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="77" t="s">
+    <row r="1" spans="2:6" ht="15.75" customHeight="1"/>
+    <row r="2" spans="2:6" ht="23.25" customHeight="1">
+      <c r="B2" s="81" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -1656,46 +1745,46 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="78"/>
+    <row r="3" spans="2:6" ht="24" customHeight="1">
+      <c r="B3" s="82"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C25+C26+C7+C27</f>
-        <v>2062.4889047619045</v>
+        <v>2193.3489047619041</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E25+E26</f>
-        <v>3253.2116666666661</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+        <v>3060.4566666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="7.5" customHeight="1"/>
+    <row r="5" spans="2:6">
       <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="8">
-        <v>10000</v>
+        <v>10500</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="8">
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6">
       <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-5937.5110952380955</v>
+        <v>-6306.6510952380959</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-6746.7883333333339</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+        <v>-6939.5433333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -1703,7 +1792,7 @@
       <c r="D7" s="9"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6">
       <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
@@ -1717,35 +1806,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6">
       <c r="B9" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>3367.1710952380954</v>
+        <v>3736.3110952380957</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>1134.4483333333335</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+        <v>1327.2033333333334</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>3367.1710952380954</v>
+        <v>3736.3110952380957</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>1134.4483333333335</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+        <v>1327.2033333333334</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
@@ -1759,7 +1848,7 @@
         <v>5612.34</v>
       </c>
     </row>
-    <row r="12" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" outlineLevel="1">
       <c r="B12" s="13" t="s">
         <v>10</v>
       </c>
@@ -1773,7 +1862,7 @@
         <v>1617.835</v>
       </c>
     </row>
-    <row r="13" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" outlineLevel="1">
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
@@ -1787,7 +1876,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" outlineLevel="1">
       <c r="B14" s="13" t="s">
         <v>12</v>
       </c>
@@ -1802,7 +1891,7 @@
       </c>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" outlineLevel="1">
       <c r="B15" s="13" t="s">
         <v>13</v>
       </c>
@@ -1816,7 +1905,7 @@
         <v>40.619999999999997</v>
       </c>
     </row>
-    <row r="16" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" outlineLevel="1">
       <c r="B16" s="13" t="s">
         <v>14</v>
       </c>
@@ -1830,7 +1919,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" outlineLevel="1">
       <c r="B17" s="13" t="s">
         <v>15</v>
       </c>
@@ -1844,7 +1933,7 @@
         <v>112.38500000000001</v>
       </c>
     </row>
-    <row r="18" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" outlineLevel="1">
       <c r="B18" s="13" t="s">
         <v>16</v>
       </c>
@@ -1858,7 +1947,7 @@
         <v>333.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" outlineLevel="1">
       <c r="B19" s="13" t="str">
         <f>Contas!$D10</f>
         <v>Cartão Itaú da Stella</v>
@@ -1870,7 +1959,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" outlineLevel="1">
       <c r="B20" s="13" t="str">
         <f>Contas!$D11</f>
         <v>Recolhimento INSS</v>
@@ -1882,7 +1971,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" outlineLevel="1">
       <c r="B21" s="13" t="str">
         <f>Contas!$D12</f>
         <v>Empréstimo</v>
@@ -1894,7 +1983,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" outlineLevel="1">
       <c r="B22" s="17" t="s">
         <v>17</v>
       </c>
@@ -1902,19 +1991,19 @@
       <c r="D22" s="19"/>
       <c r="E22" s="18"/>
     </row>
-    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" outlineLevel="1">
       <c r="B23" s="13"/>
       <c r="C23" s="14"/>
       <c r="D23" s="15"/>
       <c r="E23" s="14"/>
     </row>
-    <row r="24" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" outlineLevel="1">
       <c r="B24" s="13"/>
       <c r="C24" s="14"/>
       <c r="D24" s="15"/>
       <c r="E24" s="14"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5">
       <c r="B25" s="7" t="s">
         <v>18</v>
       </c>
@@ -1924,7 +2013,7 @@
       <c r="D25" s="9"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5">
       <c r="B26" s="7" t="s">
         <v>19</v>
       </c>
@@ -1938,7 +2027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5">
       <c r="B27" s="13" t="s">
         <v>20</v>
       </c>
@@ -1946,7 +2035,7 @@
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" outlineLevel="1">
       <c r="B28" s="13" t="s">
         <v>21</v>
       </c>
@@ -1957,7 +2046,7 @@
       <c r="D28" s="15"/>
       <c r="E28" s="14"/>
     </row>
-    <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" outlineLevel="1">
       <c r="B29" s="13" t="s">
         <v>22</v>
       </c>
@@ -1965,7 +2054,7 @@
       <c r="D29" s="20"/>
       <c r="E29" s="21"/>
     </row>
-    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" outlineLevel="1">
       <c r="B30" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L7</f>
         <v xml:space="preserve">       </v>
@@ -1977,7 +2066,7 @@
       <c r="D30" s="20"/>
       <c r="E30" s="21"/>
     </row>
-    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" outlineLevel="1">
       <c r="B31" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L8</f>
         <v xml:space="preserve">       </v>
@@ -1989,7 +2078,7 @@
       <c r="D31" s="20"/>
       <c r="E31" s="21"/>
     </row>
-    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" outlineLevel="1">
       <c r="B32" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L9</f>
         <v xml:space="preserve">       </v>
@@ -2001,7 +2090,7 @@
       <c r="D32" s="20"/>
       <c r="E32" s="21"/>
     </row>
-    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" outlineLevel="1">
       <c r="B33" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L10</f>
         <v xml:space="preserve">       </v>
@@ -2013,7 +2102,7 @@
       <c r="D33" s="20"/>
       <c r="E33" s="21"/>
     </row>
-    <row r="34" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" outlineLevel="1">
       <c r="B34" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L12</f>
         <v xml:space="preserve">       </v>
@@ -2025,7 +2114,7 @@
       <c r="D34" s="20"/>
       <c r="E34" s="21"/>
     </row>
-    <row r="35" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" outlineLevel="1">
       <c r="B35" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L13</f>
         <v xml:space="preserve">       </v>
@@ -2037,7 +2126,7 @@
       <c r="D35" s="20"/>
       <c r="E35" s="21"/>
     </row>
-    <row r="36" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" outlineLevel="1">
       <c r="B36" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L14</f>
         <v xml:space="preserve">       </v>
@@ -2049,7 +2138,7 @@
       <c r="D36" s="20"/>
       <c r="E36" s="21"/>
     </row>
-    <row r="37" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" outlineLevel="1">
       <c r="B37" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L15</f>
         <v xml:space="preserve">       </v>
@@ -2061,7 +2150,7 @@
       <c r="D37" s="20"/>
       <c r="E37" s="21"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6">
       <c r="B38" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L16</f>
         <v xml:space="preserve">       </v>
@@ -2074,7 +2163,7 @@
       <c r="E38" s="21"/>
       <c r="F38" s="16"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6">
       <c r="B39" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L17</f>
         <v xml:space="preserve">       </v>
@@ -2087,7 +2176,7 @@
       <c r="E39" s="21"/>
       <c r="F39" s="16"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6">
       <c r="B40" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L21</f>
         <v xml:space="preserve">       </v>
@@ -2099,7 +2188,7 @@
       <c r="D40" s="20"/>
       <c r="E40" s="21"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:6">
       <c r="B41" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L22</f>
         <v xml:space="preserve">       </v>
@@ -2123,7 +2212,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:D24"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="31.42578125" customWidth="1"/>
@@ -2132,8 +2221,8 @@
     <col min="5" max="5" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" ht="39" customHeight="1"/>
+    <row r="2" spans="2:4" ht="18.75" customHeight="1">
       <c r="B2" s="22"/>
       <c r="C2" s="23" t="s">
         <v>2</v>
@@ -2142,7 +2231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4">
       <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
@@ -2155,45 +2244,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4">
       <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>1134.4483333333335</v>
+        <v>1327.2033333333334</v>
       </c>
       <c r="D4" s="24">
         <f>Saldo!C9+D5</f>
-        <v>3367.1710952380954</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+        <v>3736.3110952380957</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4">
       <c r="B6" s="13"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4">
       <c r="B7" s="13"/>
       <c r="C7" s="8"/>
       <c r="D7" s="24"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4">
       <c r="B8" s="13"/>
       <c r="C8" s="8"/>
       <c r="D8" s="24"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4">
       <c r="B9" s="13"/>
       <c r="C9" s="8"/>
       <c r="D9" s="24"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4">
       <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
@@ -2203,7 +2292,7 @@
       </c>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4">
       <c r="B11" s="13" t="s">
         <v>23</v>
       </c>
@@ -2213,7 +2302,7 @@
       </c>
       <c r="D11" s="13"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4">
       <c r="B12" s="25" t="s">
         <v>24</v>
       </c>
@@ -2223,7 +2312,7 @@
       </c>
       <c r="D12" s="13"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4">
       <c r="B13" s="13" t="s">
         <v>12</v>
       </c>
@@ -2233,7 +2322,7 @@
       </c>
       <c r="D13" s="13"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4">
       <c r="B14" s="13" t="s">
         <v>13</v>
       </c>
@@ -2243,7 +2332,7 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4">
       <c r="B15" s="13" t="s">
         <v>14</v>
       </c>
@@ -2253,7 +2342,7 @@
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4">
       <c r="B16" s="13" t="s">
         <v>15</v>
       </c>
@@ -2263,7 +2352,7 @@
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4">
       <c r="B17" s="13" t="s">
         <v>25</v>
       </c>
@@ -2273,7 +2362,7 @@
       </c>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4">
       <c r="B18" s="13" t="s">
         <v>26</v>
       </c>
@@ -2283,25 +2372,25 @@
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4">
       <c r="B19" s="13"/>
       <c r="C19" s="14"/>
       <c r="D19" s="13"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4">
       <c r="B20" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>4232.7883333333339</v>
+        <v>4425.5433333333331</v>
       </c>
       <c r="D20" s="27"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4">
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4">
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -2309,7 +2398,7 @@
         <v>5587.2758333333331</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4">
       <c r="B23" t="s">
         <v>29</v>
       </c>
@@ -2317,7 +2406,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4">
       <c r="B24" t="s">
         <v>30</v>
       </c>
@@ -2337,7 +2426,7 @@
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
   <dimension ref="C1:Q67"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" style="2" customWidth="1"/>
@@ -2352,7 +2441,7 @@
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1">
       <c r="D1" s="29" t="s">
         <v>32</v>
       </c>
@@ -2366,7 +2455,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:17" ht="19.5" customHeight="1">
       <c r="D2" s="31">
         <f>SUM(L5:L21)</f>
         <v>0</v>
@@ -2384,7 +2473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="3:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:17" ht="30" customHeight="1">
       <c r="C4" s="33" t="s">
         <v>34</v>
       </c>
@@ -2431,7 +2520,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:17" ht="16.5" customHeight="1">
       <c r="C5" s="68"/>
       <c r="D5" s="36"/>
       <c r="E5" s="37"/>
@@ -2448,7 +2537,7 @@
       <c r="P5" s="64"/>
       <c r="Q5" s="37"/>
     </row>
-    <row r="6" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:17" ht="16.5" customHeight="1">
       <c r="C6" s="37"/>
       <c r="D6" s="36"/>
       <c r="E6" s="37"/>
@@ -2480,7 +2569,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:17" ht="16.5" customHeight="1">
       <c r="C7" s="35"/>
       <c r="D7" s="36"/>
       <c r="E7" s="37"/>
@@ -2509,7 +2598,7 @@
       <c r="P7" s="35"/>
       <c r="Q7" s="37"/>
     </row>
-    <row r="8" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:17" ht="16.5" customHeight="1">
       <c r="C8" s="35"/>
       <c r="D8" s="36"/>
       <c r="E8" s="37"/>
@@ -2538,7 +2627,7 @@
       <c r="P8" s="35"/>
       <c r="Q8" s="37"/>
     </row>
-    <row r="9" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:17" ht="16.5" customHeight="1">
       <c r="C9" s="35"/>
       <c r="D9" s="36"/>
       <c r="E9" s="37"/>
@@ -2567,7 +2656,7 @@
       <c r="P9" s="35"/>
       <c r="Q9" s="37"/>
     </row>
-    <row r="10" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:17" ht="16.5" customHeight="1">
       <c r="C10" s="35"/>
       <c r="D10" s="36"/>
       <c r="E10" s="37"/>
@@ -2599,7 +2688,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:17" ht="16.5" customHeight="1">
       <c r="C11" s="35"/>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
@@ -2628,7 +2717,7 @@
       <c r="P11" s="35"/>
       <c r="Q11" s="37"/>
     </row>
-    <row r="12" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:17" ht="16.5" customHeight="1">
       <c r="C12" s="37"/>
       <c r="D12" s="36"/>
       <c r="E12" s="37"/>
@@ -2657,7 +2746,7 @@
       <c r="P12" s="35"/>
       <c r="Q12" s="37"/>
     </row>
-    <row r="13" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:17" ht="16.5" customHeight="1">
       <c r="C13" s="37"/>
       <c r="D13" s="36"/>
       <c r="E13" s="37"/>
@@ -2686,7 +2775,7 @@
       <c r="P13" s="35"/>
       <c r="Q13" s="37"/>
     </row>
-    <row r="14" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:17" ht="16.5" customHeight="1">
       <c r="C14" s="37"/>
       <c r="D14" s="36"/>
       <c r="E14" s="37"/>
@@ -2715,7 +2804,7 @@
       <c r="P14" s="35"/>
       <c r="Q14" s="37"/>
     </row>
-    <row r="15" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:17" ht="16.5" customHeight="1">
       <c r="C15" s="37"/>
       <c r="D15" s="36"/>
       <c r="E15" s="37"/>
@@ -2744,7 +2833,7 @@
       <c r="P15" s="35"/>
       <c r="Q15" s="37"/>
     </row>
-    <row r="16" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:17" ht="16.5" customHeight="1">
       <c r="C16" s="37"/>
       <c r="D16" s="36"/>
       <c r="E16" s="37"/>
@@ -2761,7 +2850,7 @@
       <c r="P16" s="35"/>
       <c r="Q16" s="37"/>
     </row>
-    <row r="17" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:17" ht="16.5" customHeight="1">
       <c r="C17" s="35"/>
       <c r="D17" s="36"/>
       <c r="E17" s="37"/>
@@ -2778,7 +2867,7 @@
       <c r="P17" s="35"/>
       <c r="Q17" s="37"/>
     </row>
-    <row r="18" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:17" ht="16.5" customHeight="1">
       <c r="C18" s="35"/>
       <c r="D18" s="36"/>
       <c r="E18" s="37"/>
@@ -2795,7 +2884,7 @@
       <c r="P18" s="35"/>
       <c r="Q18" s="37"/>
     </row>
-    <row r="19" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:17" ht="16.5" customHeight="1">
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -2806,198 +2895,198 @@
       <c r="O19" s="41"/>
       <c r="P19" s="41"/>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:17">
       <c r="H20" s="2"/>
       <c r="O20" s="42"/>
       <c r="P20" s="42"/>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:17">
       <c r="H21" s="2"/>
       <c r="O21" s="42"/>
       <c r="P21" s="42"/>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:17">
       <c r="H22" s="2"/>
       <c r="O22" s="42"/>
       <c r="P22" s="42"/>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:17">
       <c r="O23" s="42"/>
       <c r="P23" s="42"/>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:17">
       <c r="O24" s="42"/>
       <c r="P24" s="42"/>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:17">
       <c r="O25" s="42"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:17">
       <c r="O26" s="42"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:17">
       <c r="O27" s="42"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:17">
       <c r="O28" s="42"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:17">
       <c r="O29" s="42"/>
       <c r="P29" s="42"/>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:17">
       <c r="O30" s="42"/>
       <c r="P30" s="42"/>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:17">
       <c r="O31" s="42"/>
       <c r="P31" s="42"/>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:17">
       <c r="O32" s="42"/>
       <c r="P32" s="42"/>
     </row>
-    <row r="33" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="15:16">
       <c r="O33" s="42"/>
       <c r="P33" s="42"/>
     </row>
-    <row r="34" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="15:16">
       <c r="O34" s="42"/>
       <c r="P34" s="42"/>
     </row>
-    <row r="35" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="15:16">
       <c r="O35" s="42"/>
       <c r="P35" s="42"/>
     </row>
-    <row r="36" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="15:16">
       <c r="O36" s="42"/>
       <c r="P36" s="42"/>
     </row>
-    <row r="37" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="15:16">
       <c r="O37" s="42"/>
       <c r="P37" s="42"/>
     </row>
-    <row r="38" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="15:16">
       <c r="O38" s="42"/>
       <c r="P38" s="42"/>
     </row>
-    <row r="39" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="15:16">
       <c r="O39" s="42"/>
       <c r="P39" s="42"/>
     </row>
-    <row r="40" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="15:16">
       <c r="O40" s="42"/>
       <c r="P40" s="42"/>
     </row>
-    <row r="41" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="15:16">
       <c r="O41" s="42"/>
       <c r="P41" s="42"/>
     </row>
-    <row r="42" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="15:16">
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
     </row>
-    <row r="43" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="15:16">
       <c r="O43" s="42"/>
       <c r="P43" s="42"/>
     </row>
-    <row r="44" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="15:16">
       <c r="O44" s="42"/>
       <c r="P44" s="42"/>
     </row>
-    <row r="45" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="15:16">
       <c r="O45" s="42"/>
       <c r="P45" s="42"/>
     </row>
-    <row r="46" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="15:16">
       <c r="O46" s="42"/>
       <c r="P46" s="42"/>
     </row>
-    <row r="47" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="15:16">
       <c r="O47" s="42"/>
       <c r="P47" s="42"/>
     </row>
-    <row r="48" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="15:16">
       <c r="O48" s="42"/>
       <c r="P48" s="42"/>
     </row>
-    <row r="49" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="15:16">
       <c r="O49" s="42"/>
       <c r="P49" s="42"/>
     </row>
-    <row r="50" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="15:16">
       <c r="O50" s="42"/>
       <c r="P50" s="42"/>
     </row>
-    <row r="51" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="15:16">
       <c r="O51" s="42"/>
       <c r="P51" s="42"/>
     </row>
-    <row r="52" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="15:16">
       <c r="O52" s="42"/>
       <c r="P52" s="42"/>
     </row>
-    <row r="53" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="15:16">
       <c r="O53" s="42"/>
       <c r="P53" s="42"/>
     </row>
-    <row r="54" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="15:16">
       <c r="O54" s="42"/>
       <c r="P54" s="42"/>
     </row>
-    <row r="55" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="15:16">
       <c r="O55" s="42"/>
       <c r="P55" s="42"/>
     </row>
-    <row r="56" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="15:16">
       <c r="O56" s="42"/>
       <c r="P56" s="42"/>
     </row>
-    <row r="57" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="15:16">
       <c r="O57" s="42"/>
       <c r="P57" s="42"/>
     </row>
-    <row r="58" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="15:16">
       <c r="O58" s="42"/>
       <c r="P58" s="42"/>
     </row>
-    <row r="59" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="15:16">
       <c r="O59" s="42"/>
       <c r="P59" s="42"/>
     </row>
-    <row r="60" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="15:16">
       <c r="O60" s="42"/>
       <c r="P60" s="42"/>
     </row>
-    <row r="61" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="15:16">
       <c r="O61" s="42"/>
       <c r="P61" s="42"/>
     </row>
-    <row r="62" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="15:16">
       <c r="O62" s="42"/>
       <c r="P62" s="42"/>
     </row>
-    <row r="63" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="15:16">
       <c r="O63" s="42"/>
       <c r="P63" s="42"/>
     </row>
-    <row r="64" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="15:16">
       <c r="O64" s="42"/>
       <c r="P64" s="42"/>
     </row>
-    <row r="65" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="15:16">
       <c r="O65" s="42"/>
       <c r="P65" s="42"/>
     </row>
-    <row r="66" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="15:16">
       <c r="O66" s="42"/>
       <c r="P66" s="42"/>
     </row>
-    <row r="67" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="15:16">
       <c r="O67" s="42"/>
       <c r="P67" s="42"/>
     </row>
@@ -3008,7 +3097,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J5:K22">
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
       <formula>"Parcelado/Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3022,8 +3111,8 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="C1:Q143"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C1:Q142"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" style="2" customWidth="1"/>
@@ -3038,7 +3127,7 @@
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1">
       <c r="D1" s="44" t="s">
         <v>49</v>
       </c>
@@ -3054,35 +3143,35 @@
       <c r="L1" s="43"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:17" ht="19.5" customHeight="1">
       <c r="D2" s="45">
-        <f>SUM(L6:L185)</f>
-        <v>6621.6194285714291</v>
+        <f>SUM(L6:L184)</f>
+        <v>7063.5144285714287</v>
       </c>
       <c r="E2" s="32">
-        <f>SUMIF($E$6:$E$185,E1,$M$6:$M$185)</f>
-        <v>3367.1710952380954</v>
+        <f>SUMIF($E$6:$E$184,E1,$M$6:$M$184)</f>
+        <v>3736.3110952380957</v>
       </c>
       <c r="F2" s="32">
-        <f>SUMIF($F$6:$F$185,F1,$M$6:$M$185)</f>
-        <v>1134.4483333333335</v>
+        <f>SUMIF($F$6:$F$184,F1,$M$6:$M$184)</f>
+        <v>1327.2033333333334</v>
       </c>
       <c r="G2" s="32">
-        <f>SUMIF($G$6:$G$185,G1,$M$6:$M$185)</f>
+        <f>SUMIF($G$6:$G$184,G1,$M$6:$M$184)</f>
         <v>0</v>
       </c>
       <c r="H2" s="16"/>
       <c r="L2" s="43"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:17">
       <c r="L3" s="43"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:17">
       <c r="M4" s="43"/>
     </row>
-    <row r="5" spans="3:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:17" ht="32.25" customHeight="1">
       <c r="C5" s="33"/>
       <c r="D5" s="33" t="s">
         <v>35</v>
@@ -3127,7 +3216,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:17">
       <c r="C6" s="35"/>
       <c r="D6" s="36" t="s">
         <v>51</v>
@@ -3140,7 +3229,7 @@
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37">
-        <f t="shared" ref="H6:H48" si="0">COUNTA(E6:G6)</f>
+        <f t="shared" ref="H6:H47" si="0">COUNTA(E6:G6)</f>
         <v>2</v>
       </c>
       <c r="I6" s="38">
@@ -3153,11 +3242,11 @@
         <v>53</v>
       </c>
       <c r="L6" s="38">
-        <f t="shared" ref="L6:L48" si="1">I6/N6</f>
+        <f t="shared" ref="L6:L47" si="1">I6/N6</f>
         <v>179.5</v>
       </c>
       <c r="M6" s="38">
-        <f t="shared" ref="M6:M48" si="2">IFERROR(L6/H6,"")</f>
+        <f t="shared" ref="M6:M47" si="2">IFERROR(L6/H6,"")</f>
         <v>89.75</v>
       </c>
       <c r="N6" s="39">
@@ -3167,7 +3256,7 @@
         <v>46056</v>
       </c>
       <c r="P6" s="64">
-        <f t="shared" ref="P6:P48" si="3">IF(N6&lt;&gt;1,EDATE(O6,N6-1),"")</f>
+        <f t="shared" ref="P6:P47" si="3">IF(N6&lt;&gt;1,EDATE(O6,N6-1),"")</f>
         <v>46084</v>
       </c>
       <c r="Q6" s="37">
@@ -3175,7 +3264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:17">
       <c r="C7" s="35"/>
       <c r="D7" s="36" t="s">
         <v>54</v>
@@ -3221,9 +3310,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:17">
       <c r="C8" s="35"/>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="74" t="s">
         <v>56</v>
       </c>
       <c r="E8" s="37"/>
@@ -3267,9 +3356,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:17">
       <c r="C9" s="35"/>
-      <c r="D9" s="75" t="s">
+      <c r="D9" s="74" t="s">
         <v>58</v>
       </c>
       <c r="E9" s="37" t="s">
@@ -3313,9 +3402,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:17">
       <c r="C10" s="35"/>
-      <c r="D10" s="75" t="s">
+      <c r="D10" s="74" t="s">
         <v>60</v>
       </c>
       <c r="E10" s="37" t="s">
@@ -3359,9 +3448,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:17">
       <c r="C11" s="35"/>
-      <c r="D11" s="75" t="s">
+      <c r="D11" s="74" t="s">
         <v>61</v>
       </c>
       <c r="E11" s="37" t="s">
@@ -3405,9 +3494,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:17">
       <c r="C12" s="35"/>
-      <c r="D12" s="75" t="s">
+      <c r="D12" s="74" t="s">
         <v>62</v>
       </c>
       <c r="E12" s="37" t="s">
@@ -3453,7 +3542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:17">
       <c r="C13" s="35"/>
       <c r="D13" s="65" t="s">
         <v>63</v>
@@ -3501,7 +3590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:17">
       <c r="C14" s="35"/>
       <c r="D14" s="65" t="s">
         <v>65</v>
@@ -3549,7 +3638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:17">
       <c r="C15" s="35"/>
       <c r="D15" s="65" t="s">
         <v>66</v>
@@ -3597,9 +3686,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:17">
       <c r="C16" s="35"/>
-      <c r="D16" s="76" t="s">
+      <c r="D16" s="75" t="s">
         <v>67</v>
       </c>
       <c r="E16" s="37" t="s">
@@ -3642,9 +3731,9 @@
       </c>
       <c r="Q16" s="37"/>
     </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:17">
       <c r="C17" s="35"/>
-      <c r="D17" s="76" t="s">
+      <c r="D17" s="75" t="s">
         <v>68</v>
       </c>
       <c r="E17" s="37" t="s">
@@ -3684,13 +3773,13 @@
         <v>46390</v>
       </c>
       <c r="Q17" s="37">
-        <f t="shared" ref="Q17:Q40" ca="1" si="5">IF(O17&lt;&gt;"",IFERROR(DATEDIF(O17,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ref="Q17:Q39" ca="1" si="5">IF(O17&lt;&gt;"",IFERROR(DATEDIF(O17,TODAY(),"m")+1,""),"")</f>
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:17">
       <c r="C18" s="35"/>
-      <c r="D18" s="76" t="s">
+      <c r="D18" s="75" t="s">
         <v>70</v>
       </c>
       <c r="E18" s="37" t="s">
@@ -3734,9 +3823,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:17">
       <c r="C19" s="35"/>
-      <c r="D19" s="76" t="s">
+      <c r="D19" s="75" t="s">
         <v>71</v>
       </c>
       <c r="E19" s="37" t="s">
@@ -3780,90 +3869,90 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:17">
       <c r="C20" s="35"/>
-      <c r="D20" s="76" t="s">
+      <c r="D20" s="36" t="s">
         <v>72</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F20" s="37"/>
+      <c r="F20" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G20" s="37"/>
       <c r="H20" s="37">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="38">
-        <v>300</v>
+        <v>1017.6</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="K20" s="38" t="s">
-        <v>59</v>
+        <v>55</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>55</v>
       </c>
       <c r="L20" s="38">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>84.8</v>
       </c>
       <c r="M20" s="38">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>42.4</v>
       </c>
       <c r="N20" s="39">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O20" s="64">
-        <v>46237</v>
+        <v>46084</v>
       </c>
       <c r="P20" s="64">
         <f t="shared" si="3"/>
-        <v>46390</v>
+        <v>46421</v>
       </c>
       <c r="Q20" s="37">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17">
       <c r="C21" s="35"/>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="46" t="s">
         <v>73</v>
       </c>
       <c r="E21" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F21" s="37" t="s">
-        <v>2</v>
-      </c>
+      <c r="F21" s="37"/>
       <c r="G21" s="37"/>
       <c r="H21" s="37">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="38">
-        <v>1017.6</v>
+        <v>1900</v>
       </c>
       <c r="J21" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="K21" s="37" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="K21" s="38" t="s">
+        <v>59</v>
       </c>
       <c r="L21" s="38">
         <f t="shared" si="1"/>
-        <v>84.8</v>
+        <v>190</v>
       </c>
       <c r="M21" s="38">
         <f t="shared" si="2"/>
-        <v>42.4</v>
+        <v>190</v>
       </c>
       <c r="N21" s="39">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O21" s="64">
-        <v>46084</v>
+        <v>46145</v>
       </c>
       <c r="P21" s="64">
         <f t="shared" si="3"/>
@@ -3871,10 +3960,10 @@
       </c>
       <c r="Q21" s="37">
         <f t="shared" ca="1" si="5"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17">
       <c r="C22" s="35"/>
       <c r="D22" s="46" t="s">
         <v>74</v>
@@ -3889,7 +3978,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="38">
-        <v>1900</v>
+        <v>474.33</v>
       </c>
       <c r="J22" s="38" t="s">
         <v>52</v>
@@ -3899,17 +3988,17 @@
       </c>
       <c r="L22" s="38">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>52.703333333333333</v>
       </c>
       <c r="M22" s="38">
         <f t="shared" si="2"/>
-        <v>190</v>
+        <v>52.703333333333333</v>
       </c>
       <c r="N22" s="39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O22" s="64">
-        <v>46145</v>
+        <v>46176</v>
       </c>
       <c r="P22" s="64">
         <f t="shared" si="3"/>
@@ -3917,10 +4006,10 @@
       </c>
       <c r="Q22" s="37">
         <f t="shared" ca="1" si="5"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17">
       <c r="C23" s="35"/>
       <c r="D23" s="46" t="s">
         <v>75</v>
@@ -3935,7 +4024,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="38">
-        <v>474.33</v>
+        <v>330</v>
       </c>
       <c r="J23" s="38" t="s">
         <v>52</v>
@@ -3945,17 +4034,17 @@
       </c>
       <c r="L23" s="38">
         <f t="shared" si="1"/>
-        <v>52.703333333333333</v>
+        <v>55</v>
       </c>
       <c r="M23" s="38">
         <f t="shared" si="2"/>
-        <v>52.703333333333333</v>
+        <v>55</v>
       </c>
       <c r="N23" s="39">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O23" s="64">
-        <v>46176</v>
+        <v>46268</v>
       </c>
       <c r="P23" s="64">
         <f t="shared" si="3"/>
@@ -3963,10 +4052,10 @@
       </c>
       <c r="Q23" s="37">
         <f t="shared" ca="1" si="5"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17">
       <c r="C24" s="35"/>
       <c r="D24" s="46" t="s">
         <v>76</v>
@@ -3974,16 +4063,18 @@
       <c r="E24" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F24" s="37"/>
+      <c r="F24" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G24" s="37"/>
       <c r="H24" s="37">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="38">
-        <v>330</v>
-      </c>
-      <c r="J24" s="38" t="s">
+        <v>1780</v>
+      </c>
+      <c r="J24" s="67" t="s">
         <v>52</v>
       </c>
       <c r="K24" s="38" t="s">
@@ -3991,28 +4082,28 @@
       </c>
       <c r="L24" s="38">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>222.5</v>
       </c>
       <c r="M24" s="38">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>111.25</v>
       </c>
       <c r="N24" s="39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O24" s="64">
-        <v>46268</v>
+        <v>46237</v>
       </c>
       <c r="P24" s="64">
         <f t="shared" si="3"/>
-        <v>46421</v>
+        <v>46449</v>
       </c>
       <c r="Q24" s="37">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17">
       <c r="C25" s="35"/>
       <c r="D25" s="46" t="s">
         <v>77</v>
@@ -4020,18 +4111,16 @@
       <c r="E25" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F25" s="37" t="s">
-        <v>2</v>
-      </c>
+      <c r="F25" s="37"/>
       <c r="G25" s="37"/>
       <c r="H25" s="37">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" s="38">
-        <v>1780</v>
-      </c>
-      <c r="J25" s="67" t="s">
+        <v>286.39</v>
+      </c>
+      <c r="J25" s="38" t="s">
         <v>52</v>
       </c>
       <c r="K25" s="38" t="s">
@@ -4039,17 +4128,17 @@
       </c>
       <c r="L25" s="38">
         <f t="shared" si="1"/>
-        <v>222.5</v>
+        <v>28.638999999999999</v>
       </c>
       <c r="M25" s="38">
         <f t="shared" si="2"/>
-        <v>111.25</v>
+        <v>28.638999999999999</v>
       </c>
       <c r="N25" s="39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O25" s="64">
-        <v>46237</v>
+        <v>46176</v>
       </c>
       <c r="P25" s="64">
         <f t="shared" si="3"/>
@@ -4057,10 +4146,10 @@
       </c>
       <c r="Q25" s="37">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17">
       <c r="C26" s="35"/>
       <c r="D26" s="46" t="s">
         <v>78</v>
@@ -4075,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="38">
-        <v>286.39</v>
+        <v>300</v>
       </c>
       <c r="J26" s="38" t="s">
         <v>52</v>
@@ -4085,17 +4174,17 @@
       </c>
       <c r="L26" s="38">
         <f t="shared" si="1"/>
-        <v>28.638999999999999</v>
+        <v>50</v>
       </c>
       <c r="M26" s="38">
         <f t="shared" si="2"/>
-        <v>28.638999999999999</v>
+        <v>50</v>
       </c>
       <c r="N26" s="39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O26" s="64">
-        <v>46176</v>
+        <v>46298</v>
       </c>
       <c r="P26" s="64">
         <f t="shared" si="3"/>
@@ -4103,10 +4192,10 @@
       </c>
       <c r="Q26" s="37">
         <f t="shared" ca="1" si="5"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17">
       <c r="C27" s="35"/>
       <c r="D27" s="46" t="s">
         <v>79</v>
@@ -4114,14 +4203,16 @@
       <c r="E27" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F27" s="37"/>
+      <c r="F27" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G27" s="37"/>
       <c r="H27" s="37">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="38">
-        <v>300</v>
+        <v>663</v>
       </c>
       <c r="J27" s="38" t="s">
         <v>52</v>
@@ -4131,11 +4222,11 @@
       </c>
       <c r="L27" s="38">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>110.5</v>
       </c>
       <c r="M27" s="38">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>55.25</v>
       </c>
       <c r="N27" s="39">
         <v>6</v>
@@ -4143,7 +4234,7 @@
       <c r="O27" s="64">
         <v>46298</v>
       </c>
-      <c r="P27" s="64">
+      <c r="P27" s="35">
         <f t="shared" si="3"/>
         <v>46449</v>
       </c>
@@ -4152,7 +4243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:17">
       <c r="C28" s="35"/>
       <c r="D28" s="46" t="s">
         <v>80</v>
@@ -4160,16 +4251,14 @@
       <c r="E28" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F28" s="37" t="s">
-        <v>2</v>
-      </c>
+      <c r="F28" s="37"/>
       <c r="G28" s="37"/>
       <c r="H28" s="37">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="38">
-        <v>663</v>
+        <v>1181.1400000000001</v>
       </c>
       <c r="J28" s="38" t="s">
         <v>52</v>
@@ -4179,28 +4268,28 @@
       </c>
       <c r="L28" s="38">
         <f t="shared" si="1"/>
-        <v>110.5</v>
+        <v>118.114</v>
       </c>
       <c r="M28" s="38">
         <f t="shared" si="2"/>
-        <v>55.25</v>
+        <v>118.114</v>
       </c>
       <c r="N28" s="39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O28" s="64">
-        <v>46298</v>
-      </c>
-      <c r="P28" s="35">
+        <v>46206</v>
+      </c>
+      <c r="P28" s="64">
         <f t="shared" si="3"/>
-        <v>46449</v>
+        <v>46480</v>
       </c>
       <c r="Q28" s="37">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17">
       <c r="C29" s="35"/>
       <c r="D29" s="46" t="s">
         <v>81</v>
@@ -4208,82 +4297,84 @@
       <c r="E29" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F29" s="37"/>
+      <c r="F29" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G29" s="37"/>
       <c r="H29" s="37">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="38">
-        <v>1181.1400000000001</v>
+        <v>224.24</v>
       </c>
       <c r="J29" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="K29" s="38" t="s">
-        <v>59</v>
+        <v>55</v>
+      </c>
+      <c r="K29" s="37" t="s">
+        <v>55</v>
       </c>
       <c r="L29" s="38">
         <f t="shared" si="1"/>
-        <v>118.114</v>
+        <v>18.686666666666667</v>
       </c>
       <c r="M29" s="38">
         <f t="shared" si="2"/>
-        <v>118.114</v>
+        <v>9.3433333333333337</v>
       </c>
       <c r="N29" s="39">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O29" s="64">
-        <v>46206</v>
+        <v>46176</v>
       </c>
       <c r="P29" s="64">
         <f t="shared" si="3"/>
-        <v>46480</v>
+        <v>46510</v>
       </c>
       <c r="Q29" s="37">
         <f t="shared" ca="1" si="5"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C30" s="35"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17">
+      <c r="C30" s="35" t="s">
+        <v>82</v>
+      </c>
       <c r="D30" s="46" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F30" s="37" t="s">
-        <v>2</v>
-      </c>
+      <c r="F30" s="37"/>
       <c r="G30" s="37"/>
       <c r="H30" s="37">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="38">
-        <v>224.24</v>
+        <v>279</v>
       </c>
       <c r="J30" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="K30" s="37" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="K30" s="38" t="s">
+        <v>84</v>
       </c>
       <c r="L30" s="38">
         <f t="shared" si="1"/>
-        <v>18.686666666666667</v>
+        <v>27.9</v>
       </c>
       <c r="M30" s="38">
         <f t="shared" si="2"/>
-        <v>9.3433333333333337</v>
+        <v>27.9</v>
       </c>
       <c r="N30" s="39">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O30" s="64">
-        <v>46176</v>
+        <v>46237</v>
       </c>
       <c r="P30" s="64">
         <f t="shared" si="3"/>
@@ -4291,61 +4382,59 @@
       </c>
       <c r="Q30" s="37">
         <f t="shared" ca="1" si="5"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C31" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" s="46" t="s">
-        <v>84</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17">
+      <c r="C31" s="35"/>
+      <c r="D31" s="36" t="s">
+        <v>85</v>
       </c>
       <c r="E31" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F31" s="37"/>
+      <c r="F31" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G31" s="37"/>
       <c r="H31" s="37">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="38">
-        <v>279</v>
+        <v>22.45</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="K31" s="38" t="s">
-        <v>85</v>
+        <v>55</v>
+      </c>
+      <c r="K31" s="37" t="s">
+        <v>86</v>
       </c>
       <c r="L31" s="38">
         <f t="shared" si="1"/>
-        <v>27.9</v>
+        <v>22.45</v>
       </c>
       <c r="M31" s="38">
         <f t="shared" si="2"/>
-        <v>27.9</v>
+        <v>11.225</v>
       </c>
       <c r="N31" s="39">
-        <v>10</v>
-      </c>
-      <c r="O31" s="64">
-        <v>46237</v>
-      </c>
-      <c r="P31" s="64">
+        <v>1</v>
+      </c>
+      <c r="O31" s="64"/>
+      <c r="P31" s="64" t="str">
         <f t="shared" si="3"/>
-        <v>46510</v>
-      </c>
-      <c r="Q31" s="37">
+        <v/>
+      </c>
+      <c r="Q31" s="37" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="3:17">
       <c r="C32" s="35"/>
-      <c r="D32" s="36" t="s">
-        <v>86</v>
+      <c r="D32" s="46" t="s">
+        <v>87</v>
       </c>
       <c r="E32" s="37" t="s">
         <v>1</v>
@@ -4359,21 +4448,21 @@
         <v>2</v>
       </c>
       <c r="I32" s="38">
-        <v>22.45</v>
+        <v>60</v>
       </c>
       <c r="J32" s="38" t="s">
         <v>55</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="L32" s="38">
         <f t="shared" si="1"/>
-        <v>22.45</v>
+        <v>60</v>
       </c>
       <c r="M32" s="38">
         <f t="shared" si="2"/>
-        <v>11.225</v>
+        <v>30</v>
       </c>
       <c r="N32" s="39">
         <v>1</v>
@@ -4388,9 +4477,9 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:17">
       <c r="C33" s="35"/>
-      <c r="D33" s="46" t="s">
+      <c r="D33" s="36" t="s">
         <v>88</v>
       </c>
       <c r="E33" s="37" t="s">
@@ -4405,21 +4494,21 @@
         <v>2</v>
       </c>
       <c r="I33" s="38">
-        <v>60</v>
+        <v>395.54</v>
       </c>
       <c r="J33" s="38" t="s">
         <v>55</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="L33" s="38">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>395.54</v>
       </c>
       <c r="M33" s="38">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>197.77</v>
       </c>
       <c r="N33" s="39">
         <v>1</v>
@@ -4434,10 +4523,10 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:17">
       <c r="C34" s="35"/>
       <c r="D34" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34" s="37" t="s">
         <v>1</v>
@@ -4451,21 +4540,21 @@
         <v>2</v>
       </c>
       <c r="I34" s="38">
-        <v>395.54</v>
+        <v>170</v>
       </c>
       <c r="J34" s="38" t="s">
         <v>55</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="L34" s="38">
         <f t="shared" si="1"/>
-        <v>395.54</v>
+        <v>170</v>
       </c>
       <c r="M34" s="38">
         <f t="shared" si="2"/>
-        <v>197.77</v>
+        <v>85</v>
       </c>
       <c r="N34" s="39">
         <v>1</v>
@@ -4480,9 +4569,9 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:17">
       <c r="C35" s="35"/>
-      <c r="D35" s="36" t="s">
+      <c r="D35" s="46" t="s">
         <v>91</v>
       </c>
       <c r="E35" s="37" t="s">
@@ -4497,7 +4586,7 @@
         <v>2</v>
       </c>
       <c r="I35" s="38">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="J35" s="38" t="s">
         <v>55</v>
@@ -4507,11 +4596,11 @@
       </c>
       <c r="L35" s="38">
         <f t="shared" si="1"/>
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="M35" s="38">
         <f t="shared" si="2"/>
-        <v>98.5</v>
+        <v>112.5</v>
       </c>
       <c r="N35" s="39">
         <v>1</v>
@@ -4526,9 +4615,9 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:17">
       <c r="C36" s="35"/>
-      <c r="D36" s="46" t="s">
+      <c r="D36" s="36" t="s">
         <v>92</v>
       </c>
       <c r="E36" s="37" t="s">
@@ -4543,7 +4632,7 @@
         <v>2</v>
       </c>
       <c r="I36" s="38">
-        <v>225</v>
+        <v>166.15</v>
       </c>
       <c r="J36" s="38" t="s">
         <v>55</v>
@@ -4553,11 +4642,11 @@
       </c>
       <c r="L36" s="38">
         <f t="shared" si="1"/>
-        <v>225</v>
+        <v>166.15</v>
       </c>
       <c r="M36" s="38">
         <f t="shared" si="2"/>
-        <v>112.5</v>
+        <v>83.075000000000003</v>
       </c>
       <c r="N36" s="39">
         <v>1</v>
@@ -4572,7 +4661,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:17">
       <c r="C37" s="35"/>
       <c r="D37" s="36" t="s">
         <v>93</v>
@@ -4589,21 +4678,21 @@
         <v>2</v>
       </c>
       <c r="I37" s="38">
-        <v>166.15</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="J37" s="38" t="s">
         <v>55</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="L37" s="38">
         <f t="shared" si="1"/>
-        <v>166.15</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="M37" s="38">
         <f t="shared" si="2"/>
-        <v>83.075000000000003</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="N37" s="39">
         <v>1</v>
@@ -4618,38 +4707,36 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:17">
       <c r="C38" s="35"/>
-      <c r="D38" s="36" t="s">
+      <c r="D38" s="46" t="s">
         <v>94</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F38" s="37" t="s">
-        <v>2</v>
-      </c>
+      <c r="F38" s="37"/>
       <c r="G38" s="37"/>
       <c r="H38" s="37">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="38">
-        <v>19.899999999999999</v>
+        <v>284.05</v>
       </c>
       <c r="J38" s="38" t="s">
         <v>55</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L38" s="38">
         <f t="shared" si="1"/>
-        <v>19.899999999999999</v>
+        <v>284.05</v>
       </c>
       <c r="M38" s="38">
         <f t="shared" si="2"/>
-        <v>9.9499999999999993</v>
+        <v>284.05</v>
       </c>
       <c r="N38" s="39">
         <v>1</v>
@@ -4664,7 +4751,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:17">
       <c r="C39" s="35"/>
       <c r="D39" s="46" t="s">
         <v>95</v>
@@ -4679,21 +4766,21 @@
         <v>1</v>
       </c>
       <c r="I39" s="38">
-        <v>284.05</v>
+        <v>110</v>
       </c>
       <c r="J39" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="K39" s="37" t="s">
-        <v>90</v>
+      <c r="K39" s="38" t="s">
+        <v>96</v>
       </c>
       <c r="L39" s="38">
         <f t="shared" si="1"/>
-        <v>284.05</v>
+        <v>110</v>
       </c>
       <c r="M39" s="38">
         <f t="shared" si="2"/>
-        <v>284.05</v>
+        <v>110</v>
       </c>
       <c r="N39" s="39">
         <v>1</v>
@@ -4708,10 +4795,10 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:17">
       <c r="C40" s="35"/>
       <c r="D40" s="46" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E40" s="37" t="s">
         <v>1</v>
@@ -4723,21 +4810,21 @@
         <v>1</v>
       </c>
       <c r="I40" s="38">
-        <v>110</v>
+        <v>118.4</v>
       </c>
       <c r="J40" s="38" t="s">
         <v>55</v>
       </c>
       <c r="K40" s="38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L40" s="38">
         <f t="shared" si="1"/>
-        <v>110</v>
+        <v>118.4</v>
       </c>
       <c r="M40" s="38">
         <f t="shared" si="2"/>
-        <v>110</v>
+        <v>118.4</v>
       </c>
       <c r="N40" s="39">
         <v>1</v>
@@ -4747,14 +4834,11 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q40" s="37" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="Q40" s="37"/>
+    </row>
+    <row r="41" spans="3:17">
       <c r="C41" s="35"/>
-      <c r="D41" s="46" t="s">
+      <c r="D41" s="36" t="s">
         <v>98</v>
       </c>
       <c r="E41" s="37" t="s">
@@ -4767,21 +4851,21 @@
         <v>1</v>
       </c>
       <c r="I41" s="38">
-        <v>118.4</v>
+        <v>26.9</v>
       </c>
       <c r="J41" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="K41" s="38" t="s">
-        <v>97</v>
+      <c r="K41" s="37" t="s">
+        <v>86</v>
       </c>
       <c r="L41" s="38">
         <f t="shared" si="1"/>
-        <v>118.4</v>
+        <v>26.9</v>
       </c>
       <c r="M41" s="38">
         <f t="shared" si="2"/>
-        <v>118.4</v>
+        <v>26.9</v>
       </c>
       <c r="N41" s="39">
         <v>1</v>
@@ -4791,11 +4875,14 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q41" s="37"/>
-    </row>
-    <row r="42" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="Q41" s="37" t="str">
+        <f ca="1">IF(O41&lt;&gt;"",IFERROR(DATEDIF(O41,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="3:17">
       <c r="C42" s="35"/>
-      <c r="D42" s="36" t="s">
+      <c r="D42" s="46" t="s">
         <v>99</v>
       </c>
       <c r="E42" s="37" t="s">
@@ -4808,21 +4895,21 @@
         <v>1</v>
       </c>
       <c r="I42" s="38">
-        <v>26.9</v>
+        <v>70</v>
       </c>
       <c r="J42" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="K42" s="37" t="s">
-        <v>87</v>
+      <c r="K42" s="38" t="s">
+        <v>55</v>
       </c>
       <c r="L42" s="38">
         <f t="shared" si="1"/>
-        <v>26.9</v>
+        <v>70</v>
       </c>
       <c r="M42" s="38">
         <f t="shared" si="2"/>
-        <v>26.9</v>
+        <v>70</v>
       </c>
       <c r="N42" s="39">
         <v>1</v>
@@ -4832,14 +4919,11 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q42" s="37" t="str">
-        <f ca="1">IF(O42&lt;&gt;"",IFERROR(DATEDIF(O42,TODAY(),"m")+1,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="Q42" s="37"/>
+    </row>
+    <row r="43" spans="3:17">
       <c r="C43" s="35"/>
-      <c r="D43" s="46" t="s">
+      <c r="D43" s="66" t="s">
         <v>100</v>
       </c>
       <c r="E43" s="37" t="s">
@@ -4852,21 +4936,21 @@
         <v>1</v>
       </c>
       <c r="I43" s="38">
-        <v>70</v>
+        <v>426</v>
       </c>
       <c r="J43" s="38" t="s">
         <v>55</v>
       </c>
       <c r="K43" s="38" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="L43" s="38">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>426</v>
       </c>
       <c r="M43" s="38">
         <f t="shared" si="2"/>
-        <v>70</v>
+        <v>426</v>
       </c>
       <c r="N43" s="39">
         <v>1</v>
@@ -4876,12 +4960,15 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q43" s="37"/>
-    </row>
-    <row r="44" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="Q43" s="37" t="str">
+        <f ca="1">IF(O43&lt;&gt;"",IFERROR(DATEDIF(O43,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="3:17">
       <c r="C44" s="35"/>
-      <c r="D44" s="66" t="s">
-        <v>101</v>
+      <c r="D44" s="46" t="s">
+        <v>102</v>
       </c>
       <c r="E44" s="37" t="s">
         <v>1</v>
@@ -4893,36 +4980,38 @@
         <v>1</v>
       </c>
       <c r="I44" s="38">
-        <v>426</v>
+        <v>60</v>
       </c>
       <c r="J44" s="38" t="s">
         <v>55</v>
       </c>
       <c r="K44" s="38" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="L44" s="38">
         <f t="shared" si="1"/>
-        <v>426</v>
+        <v>60</v>
       </c>
       <c r="M44" s="38">
         <f t="shared" si="2"/>
-        <v>426</v>
+        <v>60</v>
       </c>
       <c r="N44" s="39">
         <v>1</v>
       </c>
-      <c r="O44" s="64"/>
+      <c r="O44" s="64">
+        <v>46298</v>
+      </c>
       <c r="P44" s="64" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q44" s="37" t="str">
+      <c r="Q44" s="37">
         <f ca="1">IF(O44&lt;&gt;"",IFERROR(DATEDIF(O44,TODAY(),"m")+1,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="3:17" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="3:17">
       <c r="C45" s="35"/>
       <c r="D45" s="46" t="s">
         <v>103</v>
@@ -4930,14 +5019,16 @@
       <c r="E45" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F45" s="37"/>
+      <c r="F45" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G45" s="37"/>
       <c r="H45" s="37">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" s="38">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="J45" s="38" t="s">
         <v>55</v>
@@ -4947,11 +5038,11 @@
       </c>
       <c r="L45" s="38">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="M45" s="38">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="N45" s="39">
         <v>1</v>
@@ -4968,7 +5059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:17">
       <c r="C46" s="35"/>
       <c r="D46" s="46" t="s">
         <v>104</v>
@@ -4976,76 +5067,76 @@
       <c r="E46" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F46" s="37" t="s">
-        <v>2</v>
-      </c>
+      <c r="F46" s="37"/>
       <c r="G46" s="37"/>
       <c r="H46" s="37">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" s="38">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="J46" s="38" t="s">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="K46" s="38" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="L46" s="38">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="M46" s="38">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="N46" s="39">
         <v>1</v>
       </c>
       <c r="O46" s="64">
-        <v>46298</v>
-      </c>
-      <c r="P46" s="35" t="str">
+        <v>46329</v>
+      </c>
+      <c r="P46" s="64" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q46" s="37">
+      <c r="Q46" s="37" t="str">
         <f ca="1">IF(O46&lt;&gt;"",IFERROR(DATEDIF(O46,TODAY(),"m")+1,""),"")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="3:17" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="3:17">
       <c r="C47" s="35"/>
       <c r="D47" s="46" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E47" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F47" s="37"/>
+      <c r="F47" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G47" s="37"/>
       <c r="H47" s="37">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" s="38">
-        <v>90</v>
+        <v>172.8</v>
       </c>
       <c r="J47" s="38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K47" s="38" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L47" s="38">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>172.8</v>
       </c>
       <c r="M47" s="38">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>86.4</v>
       </c>
       <c r="N47" s="39">
         <v>1</v>
@@ -5053,7 +5144,7 @@
       <c r="O47" s="64">
         <v>46329</v>
       </c>
-      <c r="P47" s="35" t="str">
+      <c r="P47" s="64" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5062,56 +5153,56 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:17">
       <c r="C48" s="35"/>
       <c r="D48" s="46" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E48" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F48" s="37" t="s">
-        <v>2</v>
-      </c>
+      <c r="F48" s="37"/>
       <c r="G48" s="37"/>
       <c r="H48" s="37">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" ref="H48:H109" si="6">COUNTA(E48:G48)</f>
+        <v>1</v>
       </c>
       <c r="I48" s="38">
-        <v>172.8</v>
+        <v>98</v>
       </c>
       <c r="J48" s="38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K48" s="38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L48" s="38">
-        <f t="shared" si="1"/>
-        <v>172.8</v>
+        <f t="shared" ref="L48:L109" si="7">I48/N48</f>
+        <v>98</v>
       </c>
       <c r="M48" s="38">
-        <f t="shared" si="2"/>
-        <v>86.4</v>
+        <f t="shared" ref="M48:M109" si="8">IFERROR(L48/H48,"")</f>
+        <v>98</v>
       </c>
       <c r="N48" s="39">
         <v>1</v>
       </c>
-      <c r="O48" s="35"/>
-      <c r="P48" s="35" t="str">
-        <f t="shared" si="3"/>
+      <c r="O48" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P48" s="64" t="str">
+        <f t="shared" ref="P48:P109" si="9">IF(N48&lt;&gt;1,EDATE(O48,N48-1),"")</f>
         <v/>
       </c>
       <c r="Q48" s="37" t="str">
-        <f ca="1">IF(O48&lt;&gt;"",IFERROR(DATEDIF(O48,TODAY(),"m")+1,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q48:Q109" ca="1" si="10">IF(O48&lt;&gt;"",IFERROR(DATEDIF(O48,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="3:17">
       <c r="C49" s="35"/>
       <c r="D49" s="46" t="s">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="E49" s="37" t="s">
         <v>1</v>
@@ -5119,147 +5210,167 @@
       <c r="F49" s="37"/>
       <c r="G49" s="37"/>
       <c r="H49" s="37">
-        <f t="shared" ref="H49:H110" si="6">COUNTA(E49:G49)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I49" s="38">
-        <v>98</v>
+        <v>-45</v>
       </c>
       <c r="J49" s="38" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K49" s="38" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="L49" s="38">
-        <f t="shared" ref="L49:L110" si="7">I49/N49</f>
-        <v>98</v>
-      </c>
-      <c r="M49" s="38">
-        <f t="shared" ref="M49:M110" si="8">IFERROR(L49/H49,"")</f>
-        <v>98</v>
-      </c>
-      <c r="N49" s="39">
-        <v>1</v>
-      </c>
-      <c r="O49" s="35"/>
-      <c r="P49" s="35" t="str">
-        <f t="shared" ref="P49:P110" si="9">IF(N49&lt;&gt;1,EDATE(O49,N49-1),"")</f>
-        <v/>
-      </c>
-      <c r="Q49" s="37" t="str">
-        <f t="shared" ref="Q49:Q110" ca="1" si="10">IF(O49&lt;&gt;"",IFERROR(DATEDIF(O49,TODAY(),"m")+1,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C50" s="35"/>
-      <c r="D50" s="46" t="s">
-        <v>231</v>
-      </c>
-      <c r="E50" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="37">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="I50" s="38">
-        <v>-45</v>
-      </c>
-      <c r="J50" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="K50" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="L50" s="38">
         <f t="shared" si="7"/>
         <v>-45</v>
       </c>
-      <c r="M50" s="38">
+      <c r="M49" s="38">
         <f t="shared" si="8"/>
         <v>-45</v>
       </c>
-      <c r="N50" s="39">
-        <v>1</v>
-      </c>
-      <c r="O50" s="35"/>
-      <c r="P50" s="35" t="str">
+      <c r="N49" s="39">
+        <v>1</v>
+      </c>
+      <c r="O49" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P49" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q50" s="37" t="str">
+      <c r="Q49" s="37" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C51" s="81"/>
-      <c r="D51" s="66" t="s">
-        <v>146</v>
-      </c>
-      <c r="E51" s="82"/>
-      <c r="F51" s="82"/>
-      <c r="G51" s="82"/>
-      <c r="H51" s="82">
+    <row r="50" spans="3:17">
+      <c r="C50" s="76"/>
+      <c r="D50" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="E50" s="77"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="77">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I51" s="83">
-        <v>2120</v>
-      </c>
-      <c r="J51" s="83"/>
-      <c r="K51" s="83"/>
-      <c r="L51" s="83">
+      <c r="I50" s="78">
+        <v>2000</v>
+      </c>
+      <c r="J50" s="78"/>
+      <c r="K50" s="78"/>
+      <c r="L50" s="78">
         <f t="shared" si="7"/>
-        <v>2120</v>
-      </c>
-      <c r="M51" s="83" t="str">
+        <v>2000</v>
+      </c>
+      <c r="M50" s="78" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N51" s="84">
-        <v>1</v>
-      </c>
-      <c r="O51" s="81"/>
-      <c r="P51" s="81" t="str">
+      <c r="N50" s="79">
+        <v>1</v>
+      </c>
+      <c r="O50" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P50" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q51" s="82" t="str">
+      <c r="Q50" s="77" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:17">
+      <c r="C51" s="35"/>
+      <c r="D51" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="E51" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="37">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="I51" s="38">
+        <v>120</v>
+      </c>
+      <c r="J51" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K51" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="L51" s="38">
+        <f t="shared" si="7"/>
+        <v>120</v>
+      </c>
+      <c r="M51" s="38">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="N51" s="39">
+        <v>1</v>
+      </c>
+      <c r="O51" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P51" s="64" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="Q51" s="37" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="3:17">
       <c r="C52" s="35"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
+      <c r="D52" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="E52" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G52" s="37"/>
       <c r="H52" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I52" s="38"/>
-      <c r="J52" s="38"/>
-      <c r="K52" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I52" s="38">
+        <v>150</v>
+      </c>
+      <c r="J52" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K52" s="38" t="s">
+        <v>106</v>
+      </c>
       <c r="L52" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M52" s="38" t="str">
+        <v>150</v>
+      </c>
+      <c r="M52" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>75</v>
       </c>
       <c r="N52" s="39">
         <v>1</v>
       </c>
-      <c r="O52" s="35"/>
-      <c r="P52" s="35" t="str">
+      <c r="O52" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P52" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5268,32 +5379,44 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:17">
       <c r="C53" s="35"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="37"/>
+      <c r="D53" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="E53" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F53" s="37"/>
       <c r="G53" s="37"/>
       <c r="H53" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I53" s="38"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I53" s="38">
+        <v>60</v>
+      </c>
+      <c r="J53" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K53" s="38" t="s">
+        <v>110</v>
+      </c>
       <c r="L53" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M53" s="38" t="str">
+        <v>60</v>
+      </c>
+      <c r="M53" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>60</v>
       </c>
       <c r="N53" s="39">
         <v>1</v>
       </c>
-      <c r="O53" s="35"/>
-      <c r="P53" s="35" t="str">
+      <c r="O53" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P53" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5302,32 +5425,44 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:17">
       <c r="C54" s="35"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="37"/>
+      <c r="D54" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="E54" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F54" s="37"/>
       <c r="G54" s="37"/>
       <c r="H54" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I54" s="38"/>
-      <c r="J54" s="38"/>
-      <c r="K54" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I54" s="38">
+        <v>-75</v>
+      </c>
+      <c r="J54" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="K54" s="38" t="s">
+        <v>112</v>
+      </c>
       <c r="L54" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M54" s="38" t="str">
+        <v>-75</v>
+      </c>
+      <c r="M54" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-75</v>
       </c>
       <c r="N54" s="39">
         <v>1</v>
       </c>
-      <c r="O54" s="35"/>
-      <c r="P54" s="35" t="str">
+      <c r="O54" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P54" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5336,32 +5471,46 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:17">
       <c r="C55" s="35"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="37"/>
+      <c r="D55" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="E55" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G55" s="37"/>
       <c r="H55" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I55" s="38"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I55" s="38">
+        <v>60</v>
+      </c>
+      <c r="J55" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K55" s="38" t="s">
+        <v>120</v>
+      </c>
       <c r="L55" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M55" s="38" t="str">
+        <v>60</v>
+      </c>
+      <c r="M55" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>30</v>
       </c>
       <c r="N55" s="39">
         <v>1</v>
       </c>
-      <c r="O55" s="35"/>
-      <c r="P55" s="35" t="str">
+      <c r="O55" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P55" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5370,168 +5519,235 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:17">
       <c r="C56" s="35"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
+      <c r="D56" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G56" s="37"/>
       <c r="H56" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="38"/>
-      <c r="J56" s="38"/>
-      <c r="K56" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I56" s="38">
+        <f>39.89+219.13</f>
+        <v>259.02</v>
+      </c>
+      <c r="J56" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="K56" s="38" t="s">
+        <v>120</v>
+      </c>
       <c r="L56" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M56" s="38" t="str">
+        <v>129.51</v>
+      </c>
+      <c r="M56" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>64.754999999999995</v>
       </c>
       <c r="N56" s="39">
-        <v>1</v>
-      </c>
-      <c r="O56" s="35"/>
-      <c r="P56" s="35" t="str">
+        <v>2</v>
+      </c>
+      <c r="O56" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P56" s="64">
         <f t="shared" si="9"/>
-        <v/>
+        <v>46359</v>
       </c>
       <c r="Q56" s="37" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:17">
       <c r="C57" s="35"/>
-      <c r="D57" s="46"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
+      <c r="D57" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="E57" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G57" s="37"/>
       <c r="H57" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I57" s="38"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I57" s="38">
+        <v>68</v>
+      </c>
+      <c r="J57" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="K57" s="38" t="s">
+        <v>120</v>
+      </c>
       <c r="L57" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M57" s="38" t="str">
+        <v>34</v>
+      </c>
+      <c r="M57" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>17</v>
       </c>
       <c r="N57" s="39">
-        <v>1</v>
-      </c>
-      <c r="O57" s="35"/>
-      <c r="P57" s="35" t="str">
+        <v>2</v>
+      </c>
+      <c r="O57" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P57" s="64">
         <f t="shared" si="9"/>
-        <v/>
+        <v>46359</v>
       </c>
       <c r="Q57" s="37" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:17">
       <c r="C58" s="35"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
+      <c r="D58" s="46" t="s">
+        <v>123</v>
+      </c>
+      <c r="E58" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G58" s="37"/>
       <c r="H58" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="38"/>
-      <c r="J58" s="38"/>
-      <c r="K58" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I58" s="38">
+        <v>78</v>
+      </c>
+      <c r="J58" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="K58" s="38" t="s">
+        <v>120</v>
+      </c>
       <c r="L58" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M58" s="38" t="str">
+        <v>39</v>
+      </c>
+      <c r="M58" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>19.5</v>
       </c>
       <c r="N58" s="39">
-        <v>1</v>
-      </c>
-      <c r="O58" s="35"/>
-      <c r="P58" s="35" t="str">
+        <v>2</v>
+      </c>
+      <c r="O58" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P58" s="64">
         <f t="shared" si="9"/>
-        <v/>
+        <v>46359</v>
       </c>
       <c r="Q58" s="37" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:17">
       <c r="C59" s="35"/>
-      <c r="D59" s="46"/>
-      <c r="E59" s="37"/>
+      <c r="D59" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F59" s="37"/>
       <c r="G59" s="37"/>
       <c r="H59" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I59" s="38"/>
-      <c r="J59" s="38"/>
-      <c r="K59" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I59" s="38">
+        <v>197.43</v>
+      </c>
+      <c r="J59" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="K59" s="38" t="s">
+        <v>59</v>
+      </c>
       <c r="L59" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M59" s="38" t="str">
+        <v>32.905000000000001</v>
+      </c>
+      <c r="M59" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>32.905000000000001</v>
       </c>
       <c r="N59" s="39">
-        <v>1</v>
-      </c>
-      <c r="O59" s="35"/>
-      <c r="P59" s="35" t="str">
+        <v>6</v>
+      </c>
+      <c r="O59" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P59" s="64">
         <f t="shared" si="9"/>
-        <v/>
+        <v>46480</v>
       </c>
       <c r="Q59" s="37" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:17">
       <c r="C60" s="35"/>
-      <c r="D60" s="46"/>
-      <c r="E60" s="37"/>
+      <c r="D60" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="E60" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F60" s="37"/>
       <c r="G60" s="37"/>
       <c r="H60" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I60" s="38"/>
-      <c r="J60" s="38"/>
-      <c r="K60" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I60" s="38">
+        <v>421.48</v>
+      </c>
+      <c r="J60" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K60" s="38" t="s">
+        <v>110</v>
+      </c>
       <c r="L60" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M60" s="38" t="str">
+        <v>421.48</v>
+      </c>
+      <c r="M60" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>421.48</v>
       </c>
       <c r="N60" s="39">
         <v>1</v>
       </c>
-      <c r="O60" s="35"/>
-      <c r="P60" s="35" t="str">
+      <c r="O60" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P60" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5540,32 +5756,44 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:17">
       <c r="C61" s="35"/>
-      <c r="D61" s="46"/>
-      <c r="E61" s="37"/>
+      <c r="D61" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F61" s="37"/>
       <c r="G61" s="37"/>
       <c r="H61" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I61" s="38"/>
-      <c r="J61" s="38"/>
-      <c r="K61" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I61" s="38">
+        <v>37</v>
+      </c>
+      <c r="J61" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K61" s="38" t="s">
+        <v>106</v>
+      </c>
       <c r="L61" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M61" s="38" t="str">
+        <v>37</v>
+      </c>
+      <c r="M61" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>37</v>
       </c>
       <c r="N61" s="39">
         <v>1</v>
       </c>
-      <c r="O61" s="35"/>
-      <c r="P61" s="35" t="str">
+      <c r="O61" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P61" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5574,32 +5802,44 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:17">
       <c r="C62" s="35"/>
-      <c r="D62" s="46"/>
-      <c r="E62" s="37"/>
+      <c r="D62" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="E62" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F62" s="37"/>
       <c r="G62" s="37"/>
       <c r="H62" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I62" s="38"/>
-      <c r="J62" s="38"/>
-      <c r="K62" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I62" s="38">
+        <v>-370</v>
+      </c>
+      <c r="J62" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K62" s="38" t="s">
+        <v>110</v>
+      </c>
       <c r="L62" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M62" s="38" t="str">
+        <v>-370</v>
+      </c>
+      <c r="M62" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-370</v>
       </c>
       <c r="N62" s="39">
         <v>1</v>
       </c>
-      <c r="O62" s="35"/>
-      <c r="P62" s="35" t="str">
+      <c r="O62" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P62" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5608,7 +5848,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:17">
       <c r="C63" s="35"/>
       <c r="D63" s="46"/>
       <c r="E63" s="37"/>
@@ -5642,7 +5882,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:17">
       <c r="C64" s="35"/>
       <c r="D64" s="46"/>
       <c r="E64" s="37"/>
@@ -5676,7 +5916,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:17">
       <c r="C65" s="35"/>
       <c r="D65" s="46"/>
       <c r="E65" s="37"/>
@@ -5710,7 +5950,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:17">
       <c r="C66" s="35"/>
       <c r="D66" s="46"/>
       <c r="E66" s="37"/>
@@ -5744,7 +5984,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:17">
       <c r="C67" s="35"/>
       <c r="D67" s="46"/>
       <c r="E67" s="37"/>
@@ -5778,7 +6018,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:17">
       <c r="C68" s="35"/>
       <c r="D68" s="46"/>
       <c r="E68" s="37"/>
@@ -5812,7 +6052,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:17">
       <c r="C69" s="35"/>
       <c r="D69" s="46"/>
       <c r="E69" s="37"/>
@@ -5846,7 +6086,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:17">
       <c r="C70" s="35"/>
       <c r="D70" s="46"/>
       <c r="E70" s="37"/>
@@ -5880,7 +6120,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:17">
       <c r="C71" s="35"/>
       <c r="D71" s="46"/>
       <c r="E71" s="37"/>
@@ -5914,7 +6154,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:17">
       <c r="C72" s="35"/>
       <c r="D72" s="46"/>
       <c r="E72" s="37"/>
@@ -5948,7 +6188,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:17">
       <c r="C73" s="35"/>
       <c r="D73" s="46"/>
       <c r="E73" s="37"/>
@@ -5982,7 +6222,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:17">
       <c r="C74" s="35"/>
       <c r="D74" s="46"/>
       <c r="E74" s="37"/>
@@ -6016,7 +6256,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:17">
       <c r="C75" s="35"/>
       <c r="D75" s="46"/>
       <c r="E75" s="37"/>
@@ -6050,7 +6290,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:17">
       <c r="C76" s="35"/>
       <c r="D76" s="46"/>
       <c r="E76" s="37"/>
@@ -6084,7 +6324,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:17">
       <c r="C77" s="35"/>
       <c r="D77" s="46"/>
       <c r="E77" s="37"/>
@@ -6118,7 +6358,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:17">
       <c r="C78" s="35"/>
       <c r="D78" s="46"/>
       <c r="E78" s="37"/>
@@ -6152,7 +6392,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:17">
       <c r="C79" s="35"/>
       <c r="D79" s="46"/>
       <c r="E79" s="37"/>
@@ -6186,7 +6426,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:17">
       <c r="C80" s="35"/>
       <c r="D80" s="46"/>
       <c r="E80" s="37"/>
@@ -6220,7 +6460,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:17">
       <c r="C81" s="35"/>
       <c r="D81" s="46"/>
       <c r="E81" s="37"/>
@@ -6254,7 +6494,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:17">
       <c r="C82" s="35"/>
       <c r="D82" s="46"/>
       <c r="E82" s="37"/>
@@ -6288,7 +6528,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:17">
       <c r="C83" s="35"/>
       <c r="D83" s="46"/>
       <c r="E83" s="37"/>
@@ -6322,7 +6562,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:17">
       <c r="C84" s="35"/>
       <c r="D84" s="46"/>
       <c r="E84" s="37"/>
@@ -6356,7 +6596,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:17">
       <c r="C85" s="35"/>
       <c r="D85" s="46"/>
       <c r="E85" s="37"/>
@@ -6390,7 +6630,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:17">
       <c r="C86" s="35"/>
       <c r="D86" s="46"/>
       <c r="E86" s="37"/>
@@ -6424,7 +6664,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:17">
       <c r="C87" s="35"/>
       <c r="D87" s="46"/>
       <c r="E87" s="37"/>
@@ -6458,7 +6698,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:17">
       <c r="C88" s="35"/>
       <c r="D88" s="46"/>
       <c r="E88" s="37"/>
@@ -6492,7 +6732,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:17">
       <c r="C89" s="35"/>
       <c r="D89" s="46"/>
       <c r="E89" s="37"/>
@@ -6526,7 +6766,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:17">
       <c r="C90" s="35"/>
       <c r="D90" s="46"/>
       <c r="E90" s="37"/>
@@ -6560,7 +6800,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:17">
       <c r="C91" s="35"/>
       <c r="D91" s="46"/>
       <c r="E91" s="37"/>
@@ -6594,7 +6834,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:17">
       <c r="C92" s="35"/>
       <c r="D92" s="46"/>
       <c r="E92" s="37"/>
@@ -6628,7 +6868,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:17">
       <c r="C93" s="35"/>
       <c r="D93" s="46"/>
       <c r="E93" s="37"/>
@@ -6662,7 +6902,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:17">
       <c r="C94" s="35"/>
       <c r="D94" s="46"/>
       <c r="E94" s="37"/>
@@ -6696,7 +6936,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:17">
       <c r="C95" s="35"/>
       <c r="D95" s="46"/>
       <c r="E95" s="37"/>
@@ -6730,7 +6970,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:17">
       <c r="C96" s="35"/>
       <c r="D96" s="46"/>
       <c r="E96" s="37"/>
@@ -6764,7 +7004,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:17">
       <c r="C97" s="35"/>
       <c r="D97" s="46"/>
       <c r="E97" s="37"/>
@@ -6798,7 +7038,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:17">
       <c r="C98" s="35"/>
       <c r="D98" s="46"/>
       <c r="E98" s="37"/>
@@ -6832,7 +7072,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:17">
       <c r="C99" s="35"/>
       <c r="D99" s="46"/>
       <c r="E99" s="37"/>
@@ -6866,7 +7106,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:17">
       <c r="C100" s="35"/>
       <c r="D100" s="46"/>
       <c r="E100" s="37"/>
@@ -6900,7 +7140,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:17">
       <c r="C101" s="35"/>
       <c r="D101" s="46"/>
       <c r="E101" s="37"/>
@@ -6934,7 +7174,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:17">
       <c r="C102" s="35"/>
       <c r="D102" s="46"/>
       <c r="E102" s="37"/>
@@ -6968,7 +7208,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:17">
       <c r="C103" s="35"/>
       <c r="D103" s="46"/>
       <c r="E103" s="37"/>
@@ -7002,7 +7242,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:17">
       <c r="C104" s="35"/>
       <c r="D104" s="46"/>
       <c r="E104" s="37"/>
@@ -7036,7 +7276,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:17">
       <c r="C105" s="35"/>
       <c r="D105" s="46"/>
       <c r="E105" s="37"/>
@@ -7070,7 +7310,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:17">
       <c r="C106" s="35"/>
       <c r="D106" s="46"/>
       <c r="E106" s="37"/>
@@ -7104,7 +7344,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:17">
       <c r="C107" s="35"/>
       <c r="D107" s="46"/>
       <c r="E107" s="37"/>
@@ -7138,7 +7378,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:17">
       <c r="C108" s="35"/>
       <c r="D108" s="46"/>
       <c r="E108" s="37"/>
@@ -7172,7 +7412,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:17">
       <c r="C109" s="35"/>
       <c r="D109" s="46"/>
       <c r="E109" s="37"/>
@@ -7206,25 +7446,25 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:17">
       <c r="C110" s="35"/>
       <c r="D110" s="46"/>
       <c r="E110" s="37"/>
       <c r="F110" s="37"/>
       <c r="G110" s="37"/>
       <c r="H110" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="H110:H142" si="11">COUNTA(E110:G110)</f>
         <v>0</v>
       </c>
       <c r="I110" s="38"/>
       <c r="J110" s="38"/>
       <c r="K110" s="38"/>
       <c r="L110" s="38">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="L110:L142" si="12">I110/N110</f>
         <v>0</v>
       </c>
       <c r="M110" s="38" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="M110:M142" si="13">IFERROR(L110/H110,"")</f>
         <v/>
       </c>
       <c r="N110" s="39">
@@ -7232,33 +7472,33 @@
       </c>
       <c r="O110" s="35"/>
       <c r="P110" s="35" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="P110:P142" si="14">IF(N110&lt;&gt;1,EDATE(O110,N110-1),"")</f>
         <v/>
       </c>
       <c r="Q110" s="37" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="111" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q110:Q142" ca="1" si="15">IF(O110&lt;&gt;"",IFERROR(DATEDIF(O110,TODAY(),"m")+1,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="3:17">
       <c r="C111" s="35"/>
       <c r="D111" s="46"/>
       <c r="E111" s="37"/>
       <c r="F111" s="37"/>
       <c r="G111" s="37"/>
       <c r="H111" s="37">
-        <f t="shared" ref="H111:H143" si="11">COUNTA(E111:G111)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I111" s="38"/>
       <c r="J111" s="38"/>
       <c r="K111" s="38"/>
       <c r="L111" s="38">
-        <f t="shared" ref="L111:L143" si="12">I111/N111</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M111" s="38" t="str">
-        <f t="shared" ref="M111:M143" si="13">IFERROR(L111/H111,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N111" s="39">
@@ -7266,15 +7506,15 @@
       </c>
       <c r="O111" s="35"/>
       <c r="P111" s="35" t="str">
-        <f t="shared" ref="P111:P143" si="14">IF(N111&lt;&gt;1,EDATE(O111,N111-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q111" s="37" t="str">
-        <f t="shared" ref="Q111:Q143" ca="1" si="15">IF(O111&lt;&gt;"",IFERROR(DATEDIF(O111,TODAY(),"m")+1,""),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="3:17" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="3:17">
       <c r="C112" s="35"/>
       <c r="D112" s="46"/>
       <c r="E112" s="37"/>
@@ -7308,7 +7548,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:17">
       <c r="C113" s="35"/>
       <c r="D113" s="46"/>
       <c r="E113" s="37"/>
@@ -7342,7 +7582,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:17">
       <c r="C114" s="35"/>
       <c r="D114" s="46"/>
       <c r="E114" s="37"/>
@@ -7376,7 +7616,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:17">
       <c r="C115" s="35"/>
       <c r="D115" s="46"/>
       <c r="E115" s="37"/>
@@ -7410,7 +7650,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:17">
       <c r="C116" s="35"/>
       <c r="D116" s="46"/>
       <c r="E116" s="37"/>
@@ -7444,7 +7684,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:17">
       <c r="C117" s="35"/>
       <c r="D117" s="46"/>
       <c r="E117" s="37"/>
@@ -7478,7 +7718,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:17">
       <c r="C118" s="35"/>
       <c r="D118" s="46"/>
       <c r="E118" s="37"/>
@@ -7512,7 +7752,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:17">
       <c r="C119" s="35"/>
       <c r="D119" s="46"/>
       <c r="E119" s="37"/>
@@ -7546,7 +7786,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:17">
       <c r="C120" s="35"/>
       <c r="D120" s="46"/>
       <c r="E120" s="37"/>
@@ -7580,7 +7820,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:17">
       <c r="C121" s="35"/>
       <c r="D121" s="46"/>
       <c r="E121" s="37"/>
@@ -7614,7 +7854,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:17">
       <c r="C122" s="35"/>
       <c r="D122" s="46"/>
       <c r="E122" s="37"/>
@@ -7648,7 +7888,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:17">
       <c r="C123" s="35"/>
       <c r="D123" s="46"/>
       <c r="E123" s="37"/>
@@ -7682,7 +7922,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:17">
       <c r="C124" s="35"/>
       <c r="D124" s="46"/>
       <c r="E124" s="37"/>
@@ -7716,7 +7956,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:17">
       <c r="C125" s="35"/>
       <c r="D125" s="46"/>
       <c r="E125" s="37"/>
@@ -7750,7 +7990,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:17">
       <c r="C126" s="35"/>
       <c r="D126" s="46"/>
       <c r="E126" s="37"/>
@@ -7784,7 +8024,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:17">
       <c r="C127" s="35"/>
       <c r="D127" s="46"/>
       <c r="E127" s="37"/>
@@ -7818,7 +8058,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:17">
       <c r="C128" s="35"/>
       <c r="D128" s="46"/>
       <c r="E128" s="37"/>
@@ -7852,7 +8092,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:17">
       <c r="C129" s="35"/>
       <c r="D129" s="46"/>
       <c r="E129" s="37"/>
@@ -7886,7 +8126,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:17">
       <c r="C130" s="35"/>
       <c r="D130" s="46"/>
       <c r="E130" s="37"/>
@@ -7920,7 +8160,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:17">
       <c r="C131" s="35"/>
       <c r="D131" s="46"/>
       <c r="E131" s="37"/>
@@ -7954,7 +8194,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:17">
       <c r="C132" s="35"/>
       <c r="D132" s="46"/>
       <c r="E132" s="37"/>
@@ -7988,7 +8228,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:17">
       <c r="C133" s="35"/>
       <c r="D133" s="46"/>
       <c r="E133" s="37"/>
@@ -8022,7 +8262,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:17">
       <c r="C134" s="35"/>
       <c r="D134" s="46"/>
       <c r="E134" s="37"/>
@@ -8056,7 +8296,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:17">
       <c r="C135" s="35"/>
       <c r="D135" s="46"/>
       <c r="E135" s="37"/>
@@ -8090,7 +8330,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:17">
       <c r="C136" s="35"/>
       <c r="D136" s="46"/>
       <c r="E136" s="37"/>
@@ -8124,7 +8364,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:17">
       <c r="C137" s="35"/>
       <c r="D137" s="46"/>
       <c r="E137" s="37"/>
@@ -8158,7 +8398,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:17">
       <c r="C138" s="35"/>
       <c r="D138" s="46"/>
       <c r="E138" s="37"/>
@@ -8192,7 +8432,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:17">
       <c r="C139" s="35"/>
       <c r="D139" s="46"/>
       <c r="E139" s="37"/>
@@ -8226,7 +8466,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:17">
       <c r="C140" s="35"/>
       <c r="D140" s="46"/>
       <c r="E140" s="37"/>
@@ -8260,7 +8500,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:17">
       <c r="C141" s="35"/>
       <c r="D141" s="46"/>
       <c r="E141" s="37"/>
@@ -8294,7 +8534,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:17">
       <c r="C142" s="35"/>
       <c r="D142" s="46"/>
       <c r="E142" s="37"/>
@@ -8328,73 +8568,44 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C143" s="35"/>
-      <c r="D143" s="46"/>
-      <c r="E143" s="37"/>
-      <c r="F143" s="37"/>
-      <c r="G143" s="37"/>
-      <c r="H143" s="37">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I143" s="38"/>
-      <c r="J143" s="38"/>
-      <c r="K143" s="38"/>
-      <c r="L143" s="38">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M143" s="38" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="N143" s="39">
-        <v>1</v>
-      </c>
-      <c r="O143" s="35"/>
-      <c r="P143" s="35" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Q143" s="37" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="C5:Q48" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q48">
-      <sortCondition ref="P5:P48"/>
+  <autoFilter ref="C5:Q142" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q47">
+      <sortCondition ref="P5:P47"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="I6:I143">
-    <cfRule type="cellIs" dxfId="19" priority="31" operator="lessThan">
+  <conditionalFormatting sqref="I6:I142">
+    <cfRule type="cellIs" dxfId="28" priority="32" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J143">
-    <cfRule type="cellIs" dxfId="18" priority="5" operator="equal">
+  <conditionalFormatting sqref="J6:J142">
+    <cfRule type="cellIs" dxfId="27" priority="6" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:K143">
-    <cfRule type="cellIs" dxfId="17" priority="24" operator="equal">
+  <conditionalFormatting sqref="J6:K142">
+    <cfRule type="cellIs" dxfId="26" priority="25" operator="equal">
       <formula>"Parcelado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K40">
-    <cfRule type="cellIs" dxfId="16" priority="23" operator="equal">
+  <conditionalFormatting sqref="K39">
+    <cfRule type="cellIs" dxfId="25" priority="24" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K42">
-    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
+  <conditionalFormatting sqref="K41">
+    <cfRule type="cellIs" dxfId="24" priority="16" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K50">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="K49">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+      <formula>"Assinatura"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K54">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8406,7 +8617,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:R20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="36.5703125" customWidth="1"/>
@@ -8419,7 +8630,7 @@
     <col min="18" max="18" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="30" customHeight="1">
       <c r="D2" s="33" t="s">
         <v>35</v>
       </c>
@@ -8457,7 +8668,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" ht="16.5" customHeight="1">
       <c r="D3" s="54" t="s">
         <v>23</v>
       </c>
@@ -8495,9 +8706,9 @@
       </c>
       <c r="R3" s="16"/>
     </row>
-    <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:18" ht="16.5" customHeight="1">
       <c r="D4" s="55" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E4" s="56" t="s">
         <v>1</v>
@@ -8533,12 +8744,12 @@
       </c>
       <c r="R4" s="16"/>
     </row>
-    <row r="5" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" ht="16.5" customHeight="1">
       <c r="B5" s="30" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>1</v>
@@ -8574,13 +8785,13 @@
       </c>
       <c r="P5" s="59"/>
     </row>
-    <row r="6" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" ht="16.5" customHeight="1">
       <c r="B6" s="32">
         <f>SUMIF($E$3:$E$34,B5,$K$3:$K$34)</f>
         <v>2570.34</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>1</v>
@@ -8615,10 +8826,10 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" ht="16.5" customHeight="1">
       <c r="B7" s="60"/>
       <c r="D7" s="54" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="E7" s="36" t="s">
         <v>1</v>
@@ -8653,12 +8864,12 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" ht="16.5" customHeight="1">
       <c r="B8" s="30" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>1</v>
@@ -8693,13 +8904,13 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:18" ht="16.5" customHeight="1">
       <c r="B9" s="61">
         <f>SUMIF($F$3:$F$34,B8,$K$3:$K$34)</f>
         <v>5612.34</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="E9" s="36" t="s">
         <v>1</v>
@@ -8735,9 +8946,9 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18">
       <c r="D10" s="54" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="37" t="s">
@@ -8770,9 +8981,9 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18">
       <c r="D11" s="54" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="37" t="s">
@@ -8805,9 +9016,9 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18">
       <c r="D12" s="54" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="E12" s="36"/>
       <c r="F12" s="37" t="s">
@@ -8840,9 +9051,9 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18">
       <c r="D13" s="54" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="E13" s="36" t="s">
         <v>1</v>
@@ -8877,7 +9088,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:18">
       <c r="D14" s="37"/>
       <c r="E14" s="36"/>
       <c r="F14" s="37"/>
@@ -8891,7 +9102,7 @@
       <c r="N14" s="38"/>
       <c r="O14" s="39"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:18">
       <c r="D15" s="37"/>
       <c r="E15" s="36"/>
       <c r="F15" s="37"/>
@@ -8905,7 +9116,7 @@
       <c r="N15" s="38"/>
       <c r="O15" s="39"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18">
       <c r="D16" s="37"/>
       <c r="E16" s="36"/>
       <c r="F16" s="37"/>
@@ -8919,7 +9130,7 @@
       <c r="N16" s="38"/>
       <c r="O16" s="39"/>
     </row>
-    <row r="17" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:15">
       <c r="D17" s="37"/>
       <c r="E17" s="36"/>
       <c r="F17" s="37"/>
@@ -8933,7 +9144,7 @@
       <c r="N17" s="38"/>
       <c r="O17" s="39"/>
     </row>
-    <row r="18" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:15">
       <c r="D18" s="37"/>
       <c r="E18" s="36"/>
       <c r="F18" s="37"/>
@@ -8947,7 +9158,7 @@
       <c r="N18" s="38"/>
       <c r="O18" s="39"/>
     </row>
-    <row r="19" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:15">
       <c r="D19" s="37"/>
       <c r="E19" s="36"/>
       <c r="F19" s="37"/>
@@ -8961,7 +9172,7 @@
       <c r="N19" s="38"/>
       <c r="O19" s="39"/>
     </row>
-    <row r="20" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:15">
       <c r="D20" s="37"/>
       <c r="E20" s="36"/>
       <c r="F20" s="37"/>
@@ -8984,7 +9195,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:O404"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.140625" customWidth="1"/>
@@ -9000,23 +9211,23 @@
     <col min="15" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15">
       <c r="G1" s="2"/>
       <c r="N1" s="47" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" ht="14.25" customHeight="1">
       <c r="G2" s="2"/>
       <c r="N2" s="43"/>
     </row>
-    <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" ht="27.75" customHeight="1">
       <c r="G3" s="2"/>
       <c r="L3" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="M3" s="79" t="s">
-        <v>121</v>
+        <v>138</v>
+      </c>
+      <c r="M3" s="83" t="s">
+        <v>139</v>
       </c>
       <c r="N3" s="43">
         <f>SUM(N5:N21)</f>
@@ -9024,82 +9235,82 @@
       </c>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15">
       <c r="G4" s="2"/>
       <c r="L4" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="M4" s="80"/>
+        <v>140</v>
+      </c>
+      <c r="M4" s="84"/>
       <c r="N4" s="49"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15">
       <c r="B5" s="43"/>
       <c r="C5" s="43"/>
       <c r="F5" s="16"/>
       <c r="G5" s="28"/>
       <c r="L5" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="N5" s="1">
         <v>100</v>
       </c>
       <c r="O5" s="16"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15">
       <c r="G6" s="2"/>
       <c r="L6" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="N6" s="1">
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15">
       <c r="G7" s="2"/>
       <c r="N7" s="71"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15">
       <c r="F8" s="16"/>
       <c r="G8" s="50"/>
       <c r="N8" s="71"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15">
       <c r="F9" s="47" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="G9" s="28"/>
       <c r="N9" s="70"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15">
       <c r="E10" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="F10" s="16">
         <f>SUM(G11:I11)</f>
-        <v>3370.1200000000044</v>
+        <v>3000.1200000000044</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="H10" s="51" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="I10" s="51" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="N10" s="70"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15">
       <c r="E11" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="F11" s="16">
         <f>SUM(G11:H11)</f>
-        <v>3370.1200000000044</v>
+        <v>3000.1200000000044</v>
       </c>
       <c r="G11" s="1">
         <f>G12+SUM(G14:G496)</f>
-        <v>3370.1200000000044</v>
+        <v>3000.1200000000044</v>
       </c>
       <c r="H11" s="1">
         <f>H12+SUM(H14:H496)</f>
@@ -9111,36 +9322,36 @@
       </c>
       <c r="N11" s="70"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15">
       <c r="F12" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="G12" s="1">
         <v>15250</v>
       </c>
       <c r="N12" s="70"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F13" s="74" t="s">
-        <v>122</v>
+    <row r="13" spans="2:15">
+      <c r="F13" s="80" t="s">
+        <v>140</v>
       </c>
       <c r="G13" s="52"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
       <c r="N13" s="70"/>
     </row>
-    <row r="14" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" outlineLevel="1">
       <c r="F14" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="G14" s="53"/>
       <c r="H14" s="53"/>
       <c r="I14" s="53"/>
       <c r="N14" s="43"/>
     </row>
-    <row r="15" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" outlineLevel="1">
       <c r="F15" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="G15" s="53">
         <v>773.35</v>
@@ -9149,9 +9360,9 @@
       <c r="I15" s="53"/>
       <c r="N15" s="43"/>
     </row>
-    <row r="16" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" outlineLevel="1">
       <c r="F16" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G16" s="53">
         <v>-5148</v>
@@ -9160,9 +9371,9 @@
       <c r="I16" s="53"/>
       <c r="N16" s="43"/>
     </row>
-    <row r="17" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:14" outlineLevel="1">
       <c r="F17" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="G17" s="53">
         <v>-168</v>
@@ -9171,9 +9382,9 @@
       <c r="I17" s="53"/>
       <c r="N17" s="43"/>
     </row>
-    <row r="18" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="6:14" outlineLevel="1">
       <c r="F18" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G18" s="53">
         <v>-1700</v>
@@ -9182,9 +9393,9 @@
       <c r="I18" s="53"/>
       <c r="N18" s="43"/>
     </row>
-    <row r="19" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:14" outlineLevel="1">
       <c r="F19" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="G19" s="53">
         <v>5148</v>
@@ -9193,9 +9404,9 @@
       <c r="I19" s="53"/>
       <c r="N19" s="43"/>
     </row>
-    <row r="20" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:14" outlineLevel="1">
       <c r="F20" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="G20" s="53">
         <v>-4938</v>
@@ -9204,9 +9415,9 @@
       <c r="I20" s="53"/>
       <c r="N20" s="43"/>
     </row>
-    <row r="21" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:14" outlineLevel="1">
       <c r="F21" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="G21" s="53">
         <v>-1595</v>
@@ -9215,9 +9426,9 @@
       <c r="I21" s="53"/>
       <c r="N21" s="43"/>
     </row>
-    <row r="22" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:14" outlineLevel="1">
       <c r="F22" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="G22" s="53">
         <v>-4677</v>
@@ -9226,9 +9437,9 @@
       <c r="I22" s="53"/>
       <c r="N22" s="43"/>
     </row>
-    <row r="23" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:14" outlineLevel="1">
       <c r="F23" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="G23" s="53">
         <v>-200</v>
@@ -9237,9 +9448,9 @@
       <c r="I23" s="53"/>
       <c r="N23" s="43"/>
     </row>
-    <row r="24" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="6:14" outlineLevel="1">
       <c r="F24" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="G24" s="53">
         <v>4677</v>
@@ -9248,9 +9459,9 @@
       <c r="I24" s="53"/>
       <c r="N24" s="43"/>
     </row>
-    <row r="25" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:14" outlineLevel="1">
       <c r="F25" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="G25" s="53">
         <v>-750</v>
@@ -9259,9 +9470,9 @@
       <c r="I25" s="53"/>
       <c r="N25" s="43"/>
     </row>
-    <row r="26" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:14" outlineLevel="1">
       <c r="F26" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G26" s="53">
         <v>-652</v>
@@ -9270,9 +9481,9 @@
       <c r="I26" s="53"/>
       <c r="N26" s="43"/>
     </row>
-    <row r="27" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:14" outlineLevel="1">
       <c r="F27" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="G27" s="53">
         <v>11100</v>
@@ -9281,9 +9492,9 @@
       <c r="I27" s="53"/>
       <c r="N27" s="43"/>
     </row>
-    <row r="28" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:14" outlineLevel="1">
       <c r="F28" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="G28" s="53">
         <v>-396</v>
@@ -9292,9 +9503,9 @@
       <c r="I28" s="53"/>
       <c r="N28" s="43"/>
     </row>
-    <row r="29" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="6:14" outlineLevel="1">
       <c r="F29" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="G29" s="53">
         <v>-4211</v>
@@ -9303,9 +9514,9 @@
       <c r="I29" s="53"/>
       <c r="N29" s="43"/>
     </row>
-    <row r="30" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="6:14" outlineLevel="1">
       <c r="F30" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="G30" s="53">
         <v>-450</v>
@@ -9314,9 +9525,9 @@
       <c r="I30" s="53"/>
       <c r="N30" s="43"/>
     </row>
-    <row r="31" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:14" outlineLevel="1">
       <c r="F31" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="G31" s="53">
         <v>-1197</v>
@@ -9325,9 +9536,9 @@
       <c r="I31" s="53"/>
       <c r="N31" s="43"/>
     </row>
-    <row r="32" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="6:14" outlineLevel="1">
       <c r="F32" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="G32" s="53">
         <v>-315</v>
@@ -9336,9 +9547,9 @@
       <c r="I32" s="53"/>
       <c r="N32" s="43"/>
     </row>
-    <row r="33" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:14" outlineLevel="1">
       <c r="F33" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="G33" s="53">
         <v>-830</v>
@@ -9347,9 +9558,9 @@
       <c r="I33" s="53"/>
       <c r="N33" s="43"/>
     </row>
-    <row r="34" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:14" outlineLevel="1">
       <c r="F34" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="G34" s="53">
         <v>4211</v>
@@ -9358,9 +9569,9 @@
       <c r="I34" s="53"/>
       <c r="N34" s="43"/>
     </row>
-    <row r="35" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:14" outlineLevel="1">
       <c r="F35" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="G35" s="53">
         <v>-200</v>
@@ -9369,9 +9580,9 @@
       <c r="I35" s="53"/>
       <c r="N35" s="43"/>
     </row>
-    <row r="36" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:14" outlineLevel="1">
       <c r="F36" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="G36" s="53">
         <v>10000</v>
@@ -9380,9 +9591,9 @@
       <c r="I36" s="53"/>
       <c r="N36" s="43"/>
     </row>
-    <row r="37" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:14" outlineLevel="1">
       <c r="F37" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="G37" s="53">
         <v>-200</v>
@@ -9391,9 +9602,9 @@
       <c r="I37" s="53"/>
       <c r="N37" s="43"/>
     </row>
-    <row r="38" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:14" outlineLevel="1">
       <c r="F38" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="G38" s="53">
         <v>-381</v>
@@ -9402,9 +9613,9 @@
       <c r="I38" s="53"/>
       <c r="N38" s="43"/>
     </row>
-    <row r="39" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:14" outlineLevel="1">
       <c r="F39" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="G39" s="53">
         <v>-4911</v>
@@ -9413,10 +9624,10 @@
       <c r="I39" s="53"/>
       <c r="N39" s="43"/>
     </row>
-    <row r="40" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:14" outlineLevel="1">
       <c r="E40" s="2"/>
       <c r="F40" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="G40" s="53">
         <v>-5700</v>
@@ -9425,9 +9636,9 @@
       <c r="I40" s="53"/>
       <c r="N40" s="43"/>
     </row>
-    <row r="41" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:14" outlineLevel="1">
       <c r="F41" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="G41" s="53">
         <v>-400</v>
@@ -9436,9 +9647,9 @@
       <c r="I41" s="53"/>
       <c r="N41" s="43"/>
     </row>
-    <row r="42" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:14" outlineLevel="1">
       <c r="F42" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="G42" s="53">
         <v>-450</v>
@@ -9447,9 +9658,9 @@
       <c r="I42" s="53"/>
       <c r="N42" s="43"/>
     </row>
-    <row r="43" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:14" outlineLevel="1">
       <c r="F43" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="G43" s="53">
         <v>-640</v>
@@ -9458,10 +9669,10 @@
       <c r="I43" s="53"/>
       <c r="N43" s="43"/>
     </row>
-    <row r="44" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:14" outlineLevel="1">
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="G44" s="53">
         <v>5700</v>
@@ -9470,9 +9681,9 @@
       <c r="I44" s="53"/>
       <c r="N44" s="43"/>
     </row>
-    <row r="45" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="5:14" outlineLevel="1">
       <c r="F45" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="G45" s="53">
         <v>-130</v>
@@ -9481,9 +9692,9 @@
       <c r="I45" s="53"/>
       <c r="N45" s="43"/>
     </row>
-    <row r="46" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:14" outlineLevel="1">
       <c r="F46" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="G46" s="53">
         <v>-250</v>
@@ -9492,9 +9703,9 @@
       <c r="I46" s="53"/>
       <c r="N46" s="43"/>
     </row>
-    <row r="47" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:14" outlineLevel="1">
       <c r="F47" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="G47" s="53">
         <v>-112.2</v>
@@ -9503,9 +9714,9 @@
       <c r="I47" s="53"/>
       <c r="N47" s="43"/>
     </row>
-    <row r="48" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:14" outlineLevel="1">
       <c r="F48" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="G48" s="53">
         <v>4911</v>
@@ -9514,9 +9725,9 @@
       <c r="I48" s="53"/>
       <c r="N48" s="43"/>
     </row>
-    <row r="49" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="6:14" outlineLevel="1">
       <c r="F49" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="G49" s="53">
         <v>-3000</v>
@@ -9525,9 +9736,9 @@
       <c r="I49" s="53"/>
       <c r="N49" s="43"/>
     </row>
-    <row r="50" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="6:14" outlineLevel="1">
       <c r="F50" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="G50" s="53">
         <v>-4000</v>
@@ -9536,9 +9747,9 @@
       <c r="I50" s="53"/>
       <c r="N50" s="43"/>
     </row>
-    <row r="51" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="6:14" outlineLevel="1">
       <c r="F51" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="G51" s="53">
         <v>-200</v>
@@ -9547,9 +9758,9 @@
       <c r="I51" s="53"/>
       <c r="N51" s="43"/>
     </row>
-    <row r="52" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="6:14" outlineLevel="1">
       <c r="F52" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="G52" s="53">
         <v>-4612</v>
@@ -9558,9 +9769,9 @@
       <c r="I52" s="53"/>
       <c r="N52" s="43"/>
     </row>
-    <row r="53" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="6:14" outlineLevel="1">
       <c r="F53" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="G53" s="53">
         <v>-700</v>
@@ -9569,9 +9780,9 @@
       <c r="I53" s="53"/>
       <c r="N53" s="43"/>
     </row>
-    <row r="54" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="6:14" outlineLevel="1">
       <c r="F54" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="G54" s="53">
         <v>-880</v>
@@ -9580,9 +9791,9 @@
       <c r="I54" s="53"/>
       <c r="N54" s="43"/>
     </row>
-    <row r="55" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="6:14" outlineLevel="1">
       <c r="F55" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="G55" s="53">
         <v>-310</v>
@@ -9591,9 +9802,9 @@
       <c r="I55" s="53"/>
       <c r="N55" s="43"/>
     </row>
-    <row r="56" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="6:14">
       <c r="F56" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="G56" s="53">
         <v>-250</v>
@@ -9602,9 +9813,9 @@
       <c r="I56" s="53"/>
       <c r="N56" s="43"/>
     </row>
-    <row r="57" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="6:14">
       <c r="F57" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="G57" s="53">
         <v>4690</v>
@@ -9613,9 +9824,9 @@
       <c r="I57" s="53"/>
       <c r="N57" s="43"/>
     </row>
-    <row r="58" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="6:14">
       <c r="F58" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="G58" s="53">
         <v>-4440</v>
@@ -9624,9 +9835,9 @@
       <c r="I58" s="53"/>
       <c r="N58" s="43"/>
     </row>
-    <row r="59" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="6:14">
       <c r="F59" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="G59" s="53">
         <v>-4697</v>
@@ -9634,9 +9845,9 @@
       <c r="H59" s="53"/>
       <c r="I59" s="53"/>
     </row>
-    <row r="60" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="6:14">
       <c r="F60" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="G60" s="53">
         <v>-2500</v>
@@ -9644,9 +9855,9 @@
       <c r="H60" s="53"/>
       <c r="I60" s="53"/>
     </row>
-    <row r="61" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="6:14">
       <c r="F61" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G61" s="53">
         <v>-126</v>
@@ -9654,9 +9865,9 @@
       <c r="H61" s="53"/>
       <c r="I61" s="53"/>
     </row>
-    <row r="62" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="6:14">
       <c r="F62" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="G62" s="53">
         <v>4742</v>
@@ -9664,9 +9875,9 @@
       <c r="H62" s="53"/>
       <c r="I62" s="53"/>
     </row>
-    <row r="63" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="6:14">
       <c r="F63" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="G63" s="53">
         <v>-410</v>
@@ -9674,14 +9885,14 @@
       <c r="H63" s="53"/>
       <c r="I63" s="53"/>
     </row>
-    <row r="64" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="6:14">
       <c r="G64" s="53"/>
       <c r="H64" s="53"/>
       <c r="I64" s="53"/>
     </row>
-    <row r="65" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:9">
       <c r="F65" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="G65" s="53">
         <v>3320</v>
@@ -9689,9 +9900,9 @@
       <c r="H65" s="53"/>
       <c r="I65" s="53"/>
     </row>
-    <row r="66" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:9">
       <c r="F66" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="G66" s="53">
         <v>4090</v>
@@ -9699,9 +9910,9 @@
       <c r="H66" s="53"/>
       <c r="I66" s="53"/>
     </row>
-    <row r="67" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:9">
       <c r="F67" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="G67" s="53">
         <v>-5688</v>
@@ -9709,9 +9920,9 @@
       <c r="H67" s="53"/>
       <c r="I67" s="53"/>
     </row>
-    <row r="68" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:9">
       <c r="F68" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="G68" s="53">
         <v>-4433</v>
@@ -9719,9 +9930,9 @@
       <c r="H68" s="53"/>
       <c r="I68" s="53"/>
     </row>
-    <row r="69" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:9">
       <c r="F69" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="G69" s="53">
         <v>-250</v>
@@ -9729,9 +9940,9 @@
       <c r="H69" s="53"/>
       <c r="I69" s="53"/>
     </row>
-    <row r="70" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:9">
       <c r="F70" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="G70" s="53">
         <v>-99</v>
@@ -9739,9 +9950,9 @@
       <c r="H70" s="53"/>
       <c r="I70" s="53"/>
     </row>
-    <row r="71" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:9">
       <c r="F71" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="G71" s="53">
         <v>320</v>
@@ -9749,9 +9960,9 @@
       <c r="H71" s="53"/>
       <c r="I71" s="53"/>
     </row>
-    <row r="72" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:9">
       <c r="F72" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="G72" s="53">
         <v>-1572</v>
@@ -9759,14 +9970,14 @@
       <c r="H72" s="53"/>
       <c r="I72" s="53"/>
     </row>
-    <row r="73" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:9">
       <c r="G73" s="53"/>
       <c r="H73" s="53"/>
       <c r="I73" s="53"/>
     </row>
-    <row r="74" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:9">
       <c r="F74" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="G74" s="53">
         <v>4433</v>
@@ -9774,9 +9985,9 @@
       <c r="H74" s="53"/>
       <c r="I74" s="53"/>
     </row>
-    <row r="75" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:9">
       <c r="F75" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="G75" s="53">
         <v>8000</v>
@@ -9784,9 +9995,9 @@
       <c r="H75" s="53"/>
       <c r="I75" s="53"/>
     </row>
-    <row r="76" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:9">
       <c r="F76" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="G76" s="53">
         <v>-1344</v>
@@ -9794,9 +10005,9 @@
       <c r="H76" s="53"/>
       <c r="I76" s="53"/>
     </row>
-    <row r="77" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="6:9">
       <c r="F77" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="G77" s="53">
         <v>-308</v>
@@ -9804,9 +10015,9 @@
       <c r="H77" s="53"/>
       <c r="I77" s="53"/>
     </row>
-    <row r="78" spans="6:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="6:9" ht="14.25" customHeight="1">
       <c r="F78" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="G78" s="53">
         <v>-4204</v>
@@ -9814,9 +10025,9 @@
       <c r="H78" s="53"/>
       <c r="I78" s="53"/>
     </row>
-    <row r="79" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="6:9">
       <c r="F79" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="G79" s="53">
         <v>-338</v>
@@ -9824,9 +10035,9 @@
       <c r="H79" s="53"/>
       <c r="I79" s="53"/>
     </row>
-    <row r="80" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="6:9">
       <c r="F80" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="G80" s="53">
         <v>-50</v>
@@ -9834,9 +10045,9 @@
       <c r="H80" s="53"/>
       <c r="I80" s="53"/>
     </row>
-    <row r="81" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="6:9">
       <c r="F81" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="G81" s="53">
         <v>338</v>
@@ -9844,9 +10055,9 @@
       <c r="H81" s="53"/>
       <c r="I81" s="53"/>
     </row>
-    <row r="82" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="6:9">
       <c r="F82" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="G82" s="53">
         <v>-540</v>
@@ -9854,9 +10065,9 @@
       <c r="H82" s="53"/>
       <c r="I82" s="53"/>
     </row>
-    <row r="83" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="6:9">
       <c r="F83" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="G83" s="53">
         <v>-184.31</v>
@@ -9864,9 +10075,9 @@
       <c r="H83" s="53"/>
       <c r="I83" s="53"/>
     </row>
-    <row r="84" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="6:9">
       <c r="F84" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="G84" s="53">
         <v>-1464.22</v>
@@ -9874,9 +10085,9 @@
       <c r="H84" s="53"/>
       <c r="I84" s="53"/>
     </row>
-    <row r="85" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="6:9">
       <c r="F85" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="G85" s="53">
         <v>1005</v>
@@ -9884,9 +10095,9 @@
       <c r="H85" s="53"/>
       <c r="I85" s="53"/>
     </row>
-    <row r="86" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="6:9">
       <c r="F86" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="G86" s="53">
         <v>-500</v>
@@ -9894,9 +10105,9 @@
       <c r="H86" s="53"/>
       <c r="I86" s="53"/>
     </row>
-    <row r="87" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="6:9">
       <c r="F87" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="G87" s="53">
         <v>-225</v>
@@ -9904,9 +10115,9 @@
       <c r="H87" s="53"/>
       <c r="I87" s="53"/>
     </row>
-    <row r="88" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="6:9">
       <c r="F88" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="G88" s="53">
         <v>-516</v>
@@ -9914,9 +10125,9 @@
       <c r="H88" s="53"/>
       <c r="I88" s="53"/>
     </row>
-    <row r="89" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="6:9">
       <c r="F89" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="G89" s="53">
         <v>4204</v>
@@ -9924,9 +10135,9 @@
       <c r="H89" s="53"/>
       <c r="I89" s="53"/>
     </row>
-    <row r="90" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="6:9">
       <c r="F90" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="G90" s="53">
         <v>-100</v>
@@ -9934,9 +10145,9 @@
       <c r="H90" s="53"/>
       <c r="I90" s="53"/>
     </row>
-    <row r="91" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="6:9">
       <c r="F91" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="G91" s="53">
         <v>8000</v>
@@ -9944,9 +10155,9 @@
       <c r="H91" s="53"/>
       <c r="I91" s="53"/>
     </row>
-    <row r="92" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="6:9">
       <c r="F92" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="G92" s="53">
         <v>1000</v>
@@ -9954,9 +10165,9 @@
       <c r="H92" s="53"/>
       <c r="I92" s="53"/>
     </row>
-    <row r="93" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="6:9">
       <c r="F93" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="G93" s="53">
         <v>-12881</v>
@@ -9964,9 +10175,9 @@
       <c r="H93" s="53"/>
       <c r="I93" s="53"/>
     </row>
-    <row r="94" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="6:9">
       <c r="F94" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="G94" s="53">
         <v>-4489.62</v>
@@ -9974,9 +10185,9 @@
       <c r="H94" s="53"/>
       <c r="I94" s="53"/>
     </row>
-    <row r="95" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="6:9">
       <c r="F95" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="G95" s="53">
         <v>5000</v>
@@ -9984,9 +10195,9 @@
       <c r="H95" s="53"/>
       <c r="I95" s="53"/>
     </row>
-    <row r="96" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="6:9">
       <c r="F96" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="G96" s="53">
         <v>-480</v>
@@ -9994,16 +10205,16 @@
       <c r="H96" s="53"/>
       <c r="I96" s="53"/>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9">
       <c r="B97" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="C97" s="53">
         <v>-750</v>
       </c>
       <c r="D97" s="53"/>
       <c r="F97" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="G97" s="53">
         <v>-520</v>
@@ -10011,16 +10222,16 @@
       <c r="H97" s="53"/>
       <c r="I97" s="53"/>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9">
       <c r="B98" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="C98" s="53">
         <v>5587.28</v>
       </c>
       <c r="D98" s="53"/>
       <c r="F98" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="G98" s="53">
         <v>5556.2</v>
@@ -10028,14 +10239,14 @@
       <c r="H98" s="53"/>
       <c r="I98" s="53"/>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9">
       <c r="B99" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C99" s="53"/>
       <c r="D99" s="53"/>
       <c r="F99" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G99" s="53">
         <v>-500</v>
@@ -10043,9 +10254,9 @@
       <c r="H99" s="53"/>
       <c r="I99" s="53"/>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9">
       <c r="B100" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C100" s="53">
         <v>2000</v>
@@ -10054,7 +10265,7 @@
         <v>300</v>
       </c>
       <c r="F100" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="G100" s="53">
         <v>-276</v>
@@ -10062,16 +10273,16 @@
       <c r="H100" s="53"/>
       <c r="I100" s="53"/>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9">
       <c r="B101" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C101" s="53">
         <v>8000</v>
       </c>
       <c r="D101" s="53"/>
       <c r="F101" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="G101" s="53">
         <v>-250</v>
@@ -10079,16 +10290,16 @@
       <c r="H101" s="53"/>
       <c r="I101" s="53"/>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9">
       <c r="B102" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C102" s="53">
         <v>4180</v>
       </c>
       <c r="D102" s="53"/>
       <c r="F102" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="G102" s="53">
         <v>-4837.28</v>
@@ -10096,11 +10307,11 @@
       <c r="H102" s="53"/>
       <c r="I102" s="53"/>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9">
       <c r="C103" s="53"/>
       <c r="D103" s="53"/>
       <c r="F103" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G103" s="53">
         <v>-150</v>
@@ -10108,9 +10319,9 @@
       <c r="H103" s="53"/>
       <c r="I103" s="53"/>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9">
       <c r="B104" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C104" s="53">
         <v>2000</v>
@@ -10119,7 +10330,7 @@
         <v>300</v>
       </c>
       <c r="F104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G104" s="53">
         <v>-172.8</v>
@@ -10127,9 +10338,9 @@
       <c r="H104" s="53"/>
       <c r="I104" s="53"/>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9">
       <c r="B105" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C105" s="53">
         <v>2000</v>
@@ -10137,13 +10348,18 @@
       <c r="D105" s="53">
         <v>300</v>
       </c>
-      <c r="G105" s="53"/>
+      <c r="F105" t="s">
+        <v>229</v>
+      </c>
+      <c r="G105" s="53">
+        <v>-370</v>
+      </c>
       <c r="H105" s="53"/>
       <c r="I105" s="53"/>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9">
       <c r="B106" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="C106" s="53">
         <v>2000</v>
@@ -10155,16 +10371,16 @@
       <c r="H106" s="53"/>
       <c r="I106" s="53"/>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9">
       <c r="C107" s="53"/>
       <c r="D107" s="53"/>
       <c r="G107" s="53"/>
       <c r="H107" s="53"/>
       <c r="I107" s="53"/>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9">
       <c r="B108" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="C108" s="53">
         <v>-20000</v>
@@ -10174,16 +10390,16 @@
       <c r="H108" s="53"/>
       <c r="I108" s="53"/>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9">
       <c r="C109" s="53"/>
       <c r="D109" s="53"/>
       <c r="G109" s="53"/>
       <c r="H109" s="53"/>
       <c r="I109" s="53"/>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9">
       <c r="B110" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="C110" s="53">
         <v>2000</v>
@@ -10195,9 +10411,9 @@
       <c r="H110" s="53"/>
       <c r="I110" s="53"/>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9">
       <c r="B111" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="C111" s="53">
         <v>2000</v>
@@ -10209,9 +10425,9 @@
       <c r="H111" s="53"/>
       <c r="I111" s="53"/>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9">
       <c r="B112" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="C112" s="53">
         <v>8000</v>
@@ -10221,9 +10437,9 @@
       <c r="H112" s="53"/>
       <c r="I112" s="53"/>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9">
       <c r="B113" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="C113" s="53">
         <v>2000</v>
@@ -10235,9 +10451,9 @@
       <c r="H113" s="53"/>
       <c r="I113" s="53"/>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9">
       <c r="B114" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C114" s="53">
         <v>2000</v>
@@ -10249,1185 +10465,1185 @@
       <c r="H114" s="53"/>
       <c r="I114" s="53"/>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9">
       <c r="C115" s="53"/>
       <c r="G115" s="53"/>
       <c r="H115" s="53"/>
       <c r="I115" s="53"/>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9">
       <c r="C116" s="53"/>
       <c r="G116" s="53"/>
       <c r="H116" s="53"/>
       <c r="I116" s="53"/>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9">
       <c r="C117" s="53"/>
       <c r="G117" s="53"/>
       <c r="H117" s="53"/>
       <c r="I117" s="53"/>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9">
       <c r="C118" s="53"/>
       <c r="G118" s="53"/>
       <c r="H118" s="53"/>
       <c r="I118" s="53"/>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9">
       <c r="C119" s="53"/>
       <c r="G119" s="53"/>
       <c r="H119" s="53"/>
       <c r="I119" s="53"/>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9">
       <c r="C120" s="53"/>
       <c r="G120" s="53"/>
       <c r="H120" s="53"/>
       <c r="I120" s="53"/>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9">
       <c r="C121" s="53"/>
       <c r="G121" s="53"/>
       <c r="H121" s="53"/>
       <c r="I121" s="53"/>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9">
       <c r="G122" s="53"/>
       <c r="H122" s="72"/>
       <c r="I122" s="53"/>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9">
       <c r="G123" s="53"/>
       <c r="H123" s="72"/>
       <c r="I123" s="53"/>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9">
       <c r="G124" s="53"/>
       <c r="H124" s="72"/>
       <c r="I124" s="53"/>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9">
       <c r="G125" s="53"/>
       <c r="H125" s="72"/>
       <c r="I125" s="53"/>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9">
       <c r="G126" s="53"/>
       <c r="H126" s="72"/>
       <c r="I126" s="53"/>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9">
       <c r="G127" s="53"/>
       <c r="H127" s="72"/>
       <c r="I127" s="53"/>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9">
       <c r="G128" s="53"/>
       <c r="H128" s="72"/>
       <c r="I128" s="53"/>
     </row>
-    <row r="129" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:9">
       <c r="G129" s="53"/>
       <c r="H129" s="53"/>
       <c r="I129" s="53"/>
     </row>
-    <row r="130" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:9">
       <c r="G130" s="53"/>
       <c r="H130" s="53"/>
       <c r="I130" s="53"/>
     </row>
-    <row r="131" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:9">
       <c r="G131" s="53"/>
       <c r="H131" s="53"/>
       <c r="I131" s="53"/>
     </row>
-    <row r="132" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:9">
       <c r="G132" s="53"/>
       <c r="H132" s="53"/>
       <c r="I132" s="53"/>
     </row>
-    <row r="133" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:9">
       <c r="G133" s="53"/>
       <c r="H133" s="53"/>
       <c r="I133" s="53"/>
     </row>
-    <row r="134" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:9">
       <c r="G134" s="53"/>
       <c r="H134" s="53"/>
       <c r="I134" s="53"/>
     </row>
-    <row r="135" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:9">
       <c r="G135" s="53"/>
       <c r="H135" s="53"/>
       <c r="I135" s="53"/>
     </row>
-    <row r="136" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:9">
       <c r="G136" s="53"/>
       <c r="H136" s="53"/>
       <c r="I136" s="53"/>
     </row>
-    <row r="137" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:9">
       <c r="G137" s="53"/>
       <c r="H137" s="53"/>
       <c r="I137" s="53"/>
     </row>
-    <row r="138" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:9">
       <c r="G138" s="53"/>
       <c r="H138" s="53"/>
       <c r="I138" s="53"/>
     </row>
-    <row r="139" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:9">
       <c r="G139" s="53"/>
       <c r="H139" s="53"/>
       <c r="I139" s="53"/>
     </row>
-    <row r="140" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:9">
       <c r="G140" s="53"/>
       <c r="H140" s="53"/>
       <c r="I140" s="53"/>
     </row>
-    <row r="141" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:9">
       <c r="G141" s="53"/>
       <c r="H141" s="53"/>
       <c r="I141" s="53"/>
     </row>
-    <row r="142" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:9">
       <c r="G142" s="53"/>
       <c r="H142" s="53"/>
       <c r="I142" s="53"/>
     </row>
-    <row r="143" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:9">
       <c r="G143" s="53"/>
       <c r="H143" s="53"/>
       <c r="I143" s="53"/>
     </row>
-    <row r="144" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:9">
       <c r="G144" s="53"/>
       <c r="H144" s="53"/>
       <c r="I144" s="53"/>
     </row>
-    <row r="145" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:9">
       <c r="G145" s="53"/>
       <c r="H145" s="53"/>
       <c r="I145" s="53"/>
     </row>
-    <row r="146" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:9">
       <c r="G146" s="53"/>
       <c r="H146" s="53"/>
       <c r="I146" s="53"/>
     </row>
-    <row r="147" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:9">
       <c r="G147" s="53"/>
       <c r="H147" s="53"/>
       <c r="I147" s="53"/>
     </row>
-    <row r="148" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:9">
       <c r="G148" s="53"/>
       <c r="H148" s="53"/>
       <c r="I148" s="53"/>
     </row>
-    <row r="149" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:9">
       <c r="G149" s="53"/>
       <c r="H149" s="53"/>
       <c r="I149" s="53"/>
     </row>
-    <row r="150" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:9">
       <c r="G150" s="53"/>
       <c r="H150" s="53"/>
       <c r="I150" s="53"/>
     </row>
-    <row r="151" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:9">
       <c r="G151" s="53"/>
       <c r="H151" s="53"/>
       <c r="I151" s="53"/>
     </row>
-    <row r="152" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:9">
       <c r="G152" s="53"/>
       <c r="H152" s="53"/>
       <c r="I152" s="53"/>
     </row>
-    <row r="153" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:9">
       <c r="G153" s="53"/>
       <c r="H153" s="53"/>
       <c r="I153" s="53"/>
     </row>
-    <row r="154" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:9">
       <c r="G154" s="53"/>
       <c r="H154" s="53"/>
       <c r="I154" s="53"/>
     </row>
-    <row r="155" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:9">
       <c r="G155" s="53"/>
       <c r="H155" s="53"/>
       <c r="I155" s="53"/>
     </row>
-    <row r="156" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:9">
       <c r="G156" s="53"/>
       <c r="H156" s="53"/>
       <c r="I156" s="53"/>
     </row>
-    <row r="157" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:9">
       <c r="G157" s="53"/>
       <c r="H157" s="53"/>
       <c r="I157" s="53"/>
     </row>
-    <row r="158" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:9">
       <c r="G158" s="53"/>
       <c r="H158" s="53"/>
       <c r="I158" s="53"/>
     </row>
-    <row r="159" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:9">
       <c r="G159" s="53"/>
       <c r="H159" s="53"/>
       <c r="I159" s="53"/>
     </row>
-    <row r="160" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:9">
       <c r="G160" s="53"/>
       <c r="H160" s="53"/>
       <c r="I160" s="53"/>
     </row>
-    <row r="161" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:9">
       <c r="G161" s="53"/>
       <c r="H161" s="53"/>
       <c r="I161" s="53"/>
     </row>
-    <row r="162" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:9">
       <c r="G162" s="53"/>
       <c r="H162" s="53"/>
       <c r="I162" s="53"/>
     </row>
-    <row r="163" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:9">
       <c r="G163" s="53"/>
       <c r="H163" s="53"/>
       <c r="I163" s="53"/>
     </row>
-    <row r="164" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:9">
       <c r="G164" s="53"/>
       <c r="H164" s="53"/>
       <c r="I164" s="53"/>
     </row>
-    <row r="165" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:9">
       <c r="G165" s="53"/>
       <c r="H165" s="53"/>
       <c r="I165" s="53"/>
     </row>
-    <row r="166" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:9">
       <c r="G166" s="53"/>
       <c r="H166" s="53"/>
       <c r="I166" s="53"/>
     </row>
-    <row r="167" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:9">
       <c r="G167" s="53"/>
       <c r="H167" s="53"/>
       <c r="I167" s="53"/>
     </row>
-    <row r="168" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:9">
       <c r="G168" s="53"/>
       <c r="H168" s="53"/>
       <c r="I168" s="53"/>
     </row>
-    <row r="169" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:9">
       <c r="G169" s="53"/>
       <c r="H169" s="53"/>
       <c r="I169" s="53"/>
     </row>
-    <row r="170" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:9">
       <c r="G170" s="53"/>
       <c r="H170" s="53"/>
       <c r="I170" s="53"/>
     </row>
-    <row r="171" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:9">
       <c r="G171" s="53"/>
       <c r="H171" s="53"/>
       <c r="I171" s="53"/>
     </row>
-    <row r="172" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:9">
       <c r="G172" s="53"/>
       <c r="H172" s="53"/>
       <c r="I172" s="53"/>
     </row>
-    <row r="173" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:9">
       <c r="G173" s="53"/>
       <c r="H173" s="53"/>
       <c r="I173" s="53"/>
     </row>
-    <row r="174" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:9">
       <c r="G174" s="53"/>
       <c r="H174" s="53"/>
       <c r="I174" s="53"/>
     </row>
-    <row r="175" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:9">
       <c r="G175" s="53"/>
       <c r="H175" s="53"/>
       <c r="I175" s="53"/>
     </row>
-    <row r="176" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:9">
       <c r="G176" s="53"/>
       <c r="H176" s="53"/>
       <c r="I176" s="53"/>
     </row>
-    <row r="177" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:9">
       <c r="G177" s="53"/>
       <c r="H177" s="53"/>
       <c r="I177" s="53"/>
     </row>
-    <row r="178" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:9">
       <c r="G178" s="53"/>
       <c r="H178" s="53"/>
       <c r="I178" s="53"/>
     </row>
-    <row r="179" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:9">
       <c r="G179" s="53"/>
       <c r="H179" s="53"/>
       <c r="I179" s="53"/>
     </row>
-    <row r="180" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:9">
       <c r="G180" s="53"/>
       <c r="H180" s="53"/>
       <c r="I180" s="53"/>
     </row>
-    <row r="181" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:9">
       <c r="G181" s="53"/>
       <c r="H181" s="53"/>
       <c r="I181" s="53"/>
     </row>
-    <row r="182" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:9">
       <c r="G182" s="53"/>
       <c r="H182" s="53"/>
       <c r="I182" s="53"/>
     </row>
-    <row r="183" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:9">
       <c r="G183" s="53"/>
       <c r="H183" s="53"/>
       <c r="I183" s="53"/>
     </row>
-    <row r="184" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:9">
       <c r="G184" s="53"/>
       <c r="H184" s="53"/>
       <c r="I184" s="53"/>
     </row>
-    <row r="185" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:9">
       <c r="G185" s="53"/>
       <c r="H185" s="53"/>
       <c r="I185" s="53"/>
     </row>
-    <row r="186" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:9">
       <c r="G186" s="53"/>
       <c r="H186" s="53"/>
       <c r="I186" s="53"/>
     </row>
-    <row r="187" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:9">
       <c r="G187" s="53"/>
       <c r="H187" s="53"/>
       <c r="I187" s="53"/>
     </row>
-    <row r="188" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:9">
       <c r="G188" s="53"/>
       <c r="H188" s="53"/>
       <c r="I188" s="53"/>
     </row>
-    <row r="189" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:9">
       <c r="G189" s="53"/>
       <c r="H189" s="53"/>
       <c r="I189" s="53"/>
     </row>
-    <row r="190" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:9">
       <c r="G190" s="53"/>
       <c r="H190" s="53"/>
       <c r="I190" s="53"/>
     </row>
-    <row r="191" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:9">
       <c r="G191" s="53"/>
       <c r="H191" s="53"/>
       <c r="I191" s="53"/>
     </row>
-    <row r="192" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:9">
       <c r="G192" s="53"/>
       <c r="H192" s="53"/>
       <c r="I192" s="53"/>
     </row>
-    <row r="193" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:9">
       <c r="G193" s="53"/>
       <c r="H193" s="53"/>
       <c r="I193" s="53"/>
     </row>
-    <row r="194" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:9">
       <c r="G194" s="53"/>
       <c r="H194" s="53"/>
       <c r="I194" s="53"/>
     </row>
-    <row r="195" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:9">
       <c r="G195" s="53"/>
       <c r="H195" s="53"/>
       <c r="I195" s="53"/>
     </row>
-    <row r="196" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:9">
       <c r="G196" s="53"/>
       <c r="H196" s="53"/>
       <c r="I196" s="53"/>
     </row>
-    <row r="197" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:9">
       <c r="G197" s="53"/>
       <c r="H197" s="53"/>
       <c r="I197" s="53"/>
     </row>
-    <row r="198" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:9">
       <c r="G198" s="53"/>
       <c r="H198" s="53"/>
       <c r="I198" s="53"/>
     </row>
-    <row r="199" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:9">
       <c r="G199" s="53"/>
       <c r="H199" s="53"/>
       <c r="I199" s="53"/>
     </row>
-    <row r="200" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:9">
       <c r="G200" s="53"/>
       <c r="H200" s="53"/>
       <c r="I200" s="53"/>
     </row>
-    <row r="201" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:9">
       <c r="G201" s="53"/>
       <c r="H201" s="53"/>
       <c r="I201" s="53"/>
     </row>
-    <row r="202" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:9">
       <c r="G202" s="53"/>
       <c r="H202" s="53"/>
       <c r="I202" s="53"/>
     </row>
-    <row r="203" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:9">
       <c r="G203" s="53"/>
       <c r="H203" s="53"/>
       <c r="I203" s="53"/>
     </row>
-    <row r="204" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:9">
       <c r="G204" s="53"/>
       <c r="H204" s="53"/>
       <c r="I204" s="53"/>
     </row>
-    <row r="205" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:9">
       <c r="G205" s="53"/>
       <c r="H205" s="53"/>
       <c r="I205" s="53"/>
     </row>
-    <row r="206" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:9">
       <c r="G206" s="53"/>
       <c r="H206" s="53"/>
       <c r="I206" s="53"/>
     </row>
-    <row r="207" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:9">
       <c r="G207" s="53"/>
       <c r="H207" s="53"/>
       <c r="I207" s="53"/>
     </row>
-    <row r="208" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:9">
       <c r="G208" s="53"/>
       <c r="H208" s="53"/>
       <c r="I208" s="53"/>
     </row>
-    <row r="209" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:9">
       <c r="G209" s="53"/>
       <c r="H209" s="53"/>
       <c r="I209" s="53"/>
     </row>
-    <row r="210" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:9">
       <c r="G210" s="53"/>
       <c r="H210" s="53"/>
       <c r="I210" s="53"/>
     </row>
-    <row r="211" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:9">
       <c r="G211" s="53"/>
       <c r="H211" s="53"/>
       <c r="I211" s="53"/>
     </row>
-    <row r="212" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:9">
       <c r="G212" s="53"/>
       <c r="H212" s="53"/>
       <c r="I212" s="53"/>
     </row>
-    <row r="213" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:9">
       <c r="G213" s="53"/>
       <c r="H213" s="53"/>
       <c r="I213" s="53"/>
     </row>
-    <row r="214" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:9">
       <c r="G214" s="53"/>
       <c r="H214" s="53"/>
       <c r="I214" s="53"/>
     </row>
-    <row r="215" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:9">
       <c r="G215" s="53"/>
       <c r="H215" s="53"/>
       <c r="I215" s="53"/>
     </row>
-    <row r="216" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:9">
       <c r="G216" s="53"/>
       <c r="H216" s="53"/>
       <c r="I216" s="53"/>
     </row>
-    <row r="217" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:9">
       <c r="G217" s="53"/>
       <c r="H217" s="53"/>
       <c r="I217" s="53"/>
     </row>
-    <row r="218" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:9">
       <c r="G218" s="53"/>
       <c r="H218" s="53"/>
       <c r="I218" s="53"/>
     </row>
-    <row r="219" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:9">
       <c r="G219" s="53"/>
       <c r="H219" s="53"/>
       <c r="I219" s="53"/>
     </row>
-    <row r="220" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:9">
       <c r="G220" s="53"/>
       <c r="H220" s="53"/>
       <c r="I220" s="53"/>
     </row>
-    <row r="221" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:9">
       <c r="G221" s="53"/>
       <c r="H221" s="53"/>
       <c r="I221" s="53"/>
     </row>
-    <row r="222" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:9">
       <c r="G222" s="53"/>
       <c r="H222" s="53"/>
       <c r="I222" s="53"/>
     </row>
-    <row r="223" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:9">
       <c r="G223" s="53"/>
       <c r="H223" s="53"/>
       <c r="I223" s="53"/>
     </row>
-    <row r="224" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:9">
       <c r="G224" s="53"/>
       <c r="H224" s="53"/>
       <c r="I224" s="53"/>
     </row>
-    <row r="225" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:9">
       <c r="G225" s="53"/>
       <c r="H225" s="53"/>
       <c r="I225" s="53"/>
     </row>
-    <row r="226" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:9">
       <c r="G226" s="53"/>
       <c r="H226" s="53"/>
       <c r="I226" s="53"/>
     </row>
-    <row r="227" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:9">
       <c r="G227" s="53"/>
       <c r="H227" s="53"/>
       <c r="I227" s="53"/>
     </row>
-    <row r="228" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:9">
       <c r="G228" s="53"/>
       <c r="H228" s="53"/>
       <c r="I228" s="53"/>
     </row>
-    <row r="229" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:9">
       <c r="G229" s="53"/>
       <c r="H229" s="53"/>
       <c r="I229" s="53"/>
     </row>
-    <row r="230" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:9">
       <c r="G230" s="53"/>
       <c r="H230" s="53"/>
       <c r="I230" s="53"/>
     </row>
-    <row r="231" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:9">
       <c r="G231" s="53"/>
       <c r="H231" s="53"/>
       <c r="I231" s="53"/>
     </row>
-    <row r="232" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:9">
       <c r="G232" s="53"/>
       <c r="H232" s="53"/>
       <c r="I232" s="53"/>
     </row>
-    <row r="233" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:9">
       <c r="G233" s="53"/>
       <c r="H233" s="53"/>
       <c r="I233" s="53"/>
     </row>
-    <row r="234" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:9">
       <c r="G234" s="53"/>
       <c r="H234" s="53"/>
       <c r="I234" s="53"/>
     </row>
-    <row r="235" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:9">
       <c r="G235" s="53"/>
       <c r="H235" s="53"/>
       <c r="I235" s="53"/>
     </row>
-    <row r="236" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:9">
       <c r="G236" s="53"/>
       <c r="H236" s="53"/>
       <c r="I236" s="53"/>
     </row>
-    <row r="237" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:9">
       <c r="G237" s="53"/>
       <c r="H237" s="53"/>
       <c r="I237" s="53"/>
     </row>
-    <row r="238" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:9">
       <c r="G238" s="53"/>
       <c r="H238" s="53"/>
       <c r="I238" s="53"/>
     </row>
-    <row r="239" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:9">
       <c r="G239" s="53"/>
       <c r="H239" s="53"/>
       <c r="I239" s="53"/>
     </row>
-    <row r="240" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:9">
       <c r="G240" s="53"/>
       <c r="H240" s="53"/>
       <c r="I240" s="53"/>
     </row>
-    <row r="241" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:9">
       <c r="G241" s="53"/>
       <c r="H241" s="53"/>
       <c r="I241" s="53"/>
     </row>
-    <row r="242" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:9">
       <c r="G242" s="53"/>
       <c r="H242" s="53"/>
       <c r="I242" s="53"/>
     </row>
-    <row r="243" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:9">
       <c r="G243" s="53"/>
       <c r="H243" s="53"/>
       <c r="I243" s="53"/>
     </row>
-    <row r="244" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:9">
       <c r="G244" s="53"/>
       <c r="H244" s="53"/>
       <c r="I244" s="53"/>
     </row>
-    <row r="245" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:9">
       <c r="G245" s="53"/>
       <c r="H245" s="53"/>
       <c r="I245" s="53"/>
     </row>
-    <row r="246" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:9">
       <c r="G246" s="53"/>
       <c r="H246" s="53"/>
       <c r="I246" s="53"/>
     </row>
-    <row r="247" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:9">
       <c r="G247" s="53"/>
       <c r="H247" s="53"/>
       <c r="I247" s="53"/>
     </row>
-    <row r="248" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:9">
       <c r="G248" s="53"/>
       <c r="H248" s="53"/>
       <c r="I248" s="53"/>
     </row>
-    <row r="249" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:9">
       <c r="G249" s="53"/>
       <c r="H249" s="53"/>
       <c r="I249" s="53"/>
     </row>
-    <row r="250" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:9">
       <c r="G250" s="53"/>
       <c r="H250" s="53"/>
       <c r="I250" s="53"/>
     </row>
-    <row r="251" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:9">
       <c r="G251" s="53"/>
       <c r="H251" s="53"/>
       <c r="I251" s="53"/>
     </row>
-    <row r="252" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:9">
       <c r="G252" s="53"/>
       <c r="H252" s="53"/>
       <c r="I252" s="53"/>
     </row>
-    <row r="253" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:9">
       <c r="G253" s="53"/>
       <c r="H253" s="53"/>
       <c r="I253" s="53"/>
     </row>
-    <row r="254" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:9">
       <c r="G254" s="53"/>
       <c r="H254" s="53"/>
       <c r="I254" s="53"/>
     </row>
-    <row r="255" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:9">
       <c r="G255" s="53"/>
       <c r="H255" s="53"/>
       <c r="I255" s="53"/>
     </row>
-    <row r="256" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:9">
       <c r="G256" s="53"/>
       <c r="H256" s="53"/>
       <c r="I256" s="53"/>
     </row>
-    <row r="257" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:9">
       <c r="G257" s="53"/>
       <c r="H257" s="1"/>
       <c r="I257" s="1"/>
     </row>
-    <row r="258" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:9">
       <c r="G258" s="53"/>
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>
     </row>
-    <row r="259" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:9">
       <c r="G259" s="53"/>
       <c r="H259" s="1"/>
       <c r="I259" s="1"/>
     </row>
-    <row r="260" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:9">
       <c r="G260" s="53"/>
       <c r="H260" s="1"/>
       <c r="I260" s="1"/>
     </row>
-    <row r="261" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:9">
       <c r="G261" s="53"/>
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
     </row>
-    <row r="262" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:9">
       <c r="G262" s="53"/>
       <c r="H262" s="1"/>
       <c r="I262" s="1"/>
     </row>
-    <row r="263" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:9">
       <c r="G263" s="53"/>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
     </row>
-    <row r="264" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:9">
       <c r="G264" s="53"/>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
     </row>
-    <row r="265" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:9">
       <c r="G265" s="53"/>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
     </row>
-    <row r="266" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:9">
       <c r="G266" s="53"/>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
     </row>
-    <row r="267" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:9">
       <c r="G267" s="53"/>
     </row>
-    <row r="268" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:9">
       <c r="G268" s="53"/>
     </row>
-    <row r="269" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:9">
       <c r="G269" s="53"/>
     </row>
-    <row r="270" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:9">
       <c r="G270" s="53"/>
     </row>
-    <row r="271" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:9">
       <c r="G271" s="53"/>
     </row>
-    <row r="272" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:9">
       <c r="G272" s="53"/>
     </row>
-    <row r="273" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:7">
       <c r="G273" s="53"/>
     </row>
-    <row r="274" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:7">
       <c r="G274" s="53"/>
     </row>
-    <row r="275" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:7">
       <c r="G275" s="53"/>
     </row>
-    <row r="276" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:7">
       <c r="G276" s="53"/>
     </row>
-    <row r="277" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:7">
       <c r="G277" s="53"/>
     </row>
-    <row r="278" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:7">
       <c r="G278" s="53"/>
     </row>
-    <row r="279" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:7">
       <c r="G279" s="53"/>
     </row>
-    <row r="280" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:7">
       <c r="G280" s="53"/>
     </row>
-    <row r="281" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:7">
       <c r="G281" s="53"/>
     </row>
-    <row r="282" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:7">
       <c r="G282" s="53"/>
     </row>
-    <row r="283" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:7">
       <c r="G283" s="53"/>
     </row>
-    <row r="284" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:7">
       <c r="G284" s="53"/>
     </row>
-    <row r="285" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:7">
       <c r="G285" s="53"/>
     </row>
-    <row r="286" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:7">
       <c r="G286" s="53"/>
     </row>
-    <row r="287" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:7">
       <c r="G287" s="53"/>
     </row>
-    <row r="288" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:7">
       <c r="G288" s="53"/>
     </row>
-    <row r="289" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:7">
       <c r="G289" s="53"/>
     </row>
-    <row r="290" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:7">
       <c r="G290" s="53"/>
     </row>
-    <row r="291" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:7">
       <c r="G291" s="53"/>
     </row>
-    <row r="292" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:7">
       <c r="G292" s="53"/>
     </row>
-    <row r="293" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:7">
       <c r="G293" s="53"/>
     </row>
-    <row r="294" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:7">
       <c r="G294" s="53"/>
     </row>
-    <row r="295" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:7">
       <c r="G295" s="53"/>
     </row>
-    <row r="296" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:7">
       <c r="G296" s="53"/>
     </row>
-    <row r="297" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:7">
       <c r="G297" s="53"/>
     </row>
-    <row r="298" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:7">
       <c r="G298" s="53"/>
     </row>
-    <row r="299" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:7">
       <c r="G299" s="53"/>
     </row>
-    <row r="300" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:7">
       <c r="G300" s="53"/>
     </row>
-    <row r="301" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:7">
       <c r="G301" s="53"/>
     </row>
-    <row r="302" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:7">
       <c r="G302" s="53"/>
     </row>
-    <row r="303" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:7">
       <c r="G303" s="53"/>
     </row>
-    <row r="304" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:7">
       <c r="G304" s="53"/>
     </row>
-    <row r="305" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:7">
       <c r="G305" s="53"/>
     </row>
-    <row r="306" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:7">
       <c r="G306" s="53"/>
     </row>
-    <row r="307" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:7">
       <c r="G307" s="53"/>
     </row>
-    <row r="308" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:7">
       <c r="G308" s="53"/>
     </row>
-    <row r="309" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:7">
       <c r="G309" s="53"/>
     </row>
-    <row r="310" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:7">
       <c r="G310" s="53"/>
     </row>
-    <row r="311" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:7">
       <c r="G311" s="53"/>
     </row>
-    <row r="312" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:7">
       <c r="G312" s="53"/>
     </row>
-    <row r="313" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:7">
       <c r="G313" s="53"/>
     </row>
-    <row r="314" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:7">
       <c r="G314" s="53"/>
     </row>
-    <row r="315" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:7">
       <c r="G315" s="53"/>
     </row>
-    <row r="316" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:7">
       <c r="G316" s="53"/>
     </row>
-    <row r="317" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:7">
       <c r="G317" s="53"/>
     </row>
-    <row r="318" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:7">
       <c r="G318" s="53"/>
     </row>
-    <row r="319" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:7">
       <c r="G319" s="53"/>
     </row>
-    <row r="320" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:7">
       <c r="G320" s="53"/>
     </row>
-    <row r="321" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:7">
       <c r="G321" s="53"/>
     </row>
-    <row r="322" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:7">
       <c r="G322" s="53"/>
     </row>
-    <row r="323" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:7">
       <c r="G323" s="53"/>
     </row>
-    <row r="324" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:7">
       <c r="G324" s="53"/>
     </row>
-    <row r="325" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:7">
       <c r="G325" s="53"/>
     </row>
-    <row r="326" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:7">
       <c r="G326" s="53"/>
     </row>
-    <row r="327" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:7">
       <c r="G327" s="53"/>
     </row>
-    <row r="328" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:7">
       <c r="G328" s="53"/>
     </row>
-    <row r="329" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:7">
       <c r="G329" s="53"/>
     </row>
-    <row r="330" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:7">
       <c r="G330" s="53"/>
     </row>
-    <row r="331" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:7">
       <c r="G331" s="53"/>
     </row>
-    <row r="332" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:7">
       <c r="G332" s="53"/>
     </row>
-    <row r="333" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:7">
       <c r="G333" s="53"/>
     </row>
-    <row r="334" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:7">
       <c r="G334" s="53"/>
     </row>
-    <row r="335" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:7">
       <c r="G335" s="53"/>
     </row>
-    <row r="336" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:7">
       <c r="G336" s="53"/>
     </row>
-    <row r="337" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="7:7">
       <c r="G337" s="53"/>
     </row>
-    <row r="338" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="7:7">
       <c r="G338" s="53"/>
     </row>
-    <row r="339" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="7:7">
       <c r="G339" s="53"/>
     </row>
-    <row r="340" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="7:7">
       <c r="G340" s="53"/>
     </row>
-    <row r="341" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="7:7">
       <c r="G341" s="53"/>
     </row>
-    <row r="342" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="7:7">
       <c r="G342" s="53"/>
     </row>
-    <row r="343" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="7:7">
       <c r="G343" s="53"/>
     </row>
-    <row r="344" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="7:7">
       <c r="G344" s="53"/>
     </row>
-    <row r="345" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="7:7">
       <c r="G345" s="53"/>
     </row>
-    <row r="346" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="7:7">
       <c r="G346" s="53"/>
     </row>
-    <row r="347" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="7:7">
       <c r="G347" s="53"/>
     </row>
-    <row r="348" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="7:7">
       <c r="G348" s="53"/>
     </row>
-    <row r="349" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="7:7">
       <c r="G349" s="53"/>
     </row>
-    <row r="350" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="7:7">
       <c r="G350" s="53"/>
     </row>
-    <row r="351" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="7:7">
       <c r="G351" s="53"/>
     </row>
-    <row r="352" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="7:7">
       <c r="G352" s="53"/>
     </row>
-    <row r="353" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="7:7">
       <c r="G353" s="53"/>
     </row>
-    <row r="354" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="7:7">
       <c r="G354" s="53"/>
     </row>
-    <row r="355" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="7:7">
       <c r="G355" s="53"/>
     </row>
-    <row r="356" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="7:7">
       <c r="G356" s="53"/>
     </row>
-    <row r="357" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="7:7">
       <c r="G357" s="53"/>
     </row>
-    <row r="358" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="7:7">
       <c r="G358" s="53"/>
     </row>
-    <row r="359" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="7:7">
       <c r="G359" s="53"/>
     </row>
-    <row r="360" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="7:7">
       <c r="G360" s="53"/>
     </row>
-    <row r="361" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="7:7">
       <c r="G361" s="53"/>
     </row>
-    <row r="362" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="7:7">
       <c r="G362" s="53"/>
     </row>
-    <row r="363" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="7:7">
       <c r="G363" s="53"/>
     </row>
-    <row r="364" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="7:7">
       <c r="G364" s="53"/>
     </row>
-    <row r="365" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="7:7">
       <c r="G365" s="53"/>
     </row>
-    <row r="366" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="7:7">
       <c r="G366" s="53"/>
     </row>
-    <row r="367" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="7:7">
       <c r="G367" s="53"/>
     </row>
-    <row r="368" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="7:7">
       <c r="G368" s="53"/>
     </row>
-    <row r="369" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="7:7">
       <c r="G369" s="53"/>
     </row>
-    <row r="370" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="7:7">
       <c r="G370" s="53"/>
     </row>
-    <row r="371" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="7:7">
       <c r="G371" s="53"/>
     </row>
-    <row r="372" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="7:7">
       <c r="G372" s="53"/>
     </row>
-    <row r="373" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="7:7">
       <c r="G373" s="53"/>
     </row>
-    <row r="374" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="7:7">
       <c r="G374" s="53"/>
     </row>
-    <row r="375" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="7:7">
       <c r="G375" s="53"/>
     </row>
-    <row r="376" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="7:7">
       <c r="G376" s="53"/>
     </row>
-    <row r="377" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="7:7">
       <c r="G377" s="53"/>
     </row>
-    <row r="378" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="7:7">
       <c r="G378" s="53"/>
     </row>
-    <row r="379" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="7:7">
       <c r="G379" s="53"/>
     </row>
-    <row r="380" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="7:7">
       <c r="G380" s="53"/>
     </row>
-    <row r="381" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="7:7">
       <c r="G381" s="53"/>
     </row>
-    <row r="382" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="7:7">
       <c r="G382" s="53"/>
     </row>
-    <row r="383" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="7:7">
       <c r="G383" s="53"/>
     </row>
-    <row r="384" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="7:7">
       <c r="G384" s="53"/>
     </row>
-    <row r="385" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="7:7">
       <c r="G385" s="53"/>
     </row>
-    <row r="386" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="7:7">
       <c r="G386" s="53"/>
     </row>
-    <row r="387" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="7:7">
       <c r="G387" s="53"/>
     </row>
-    <row r="388" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="7:7">
       <c r="G388" s="53"/>
     </row>
-    <row r="389" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="7:7">
       <c r="G389" s="53"/>
     </row>
-    <row r="390" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="7:7">
       <c r="G390" s="53"/>
     </row>
-    <row r="391" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="7:7">
       <c r="G391" s="53"/>
     </row>
-    <row r="392" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="7:7">
       <c r="G392" s="53"/>
     </row>
-    <row r="393" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="7:7">
       <c r="G393" s="53"/>
     </row>
-    <row r="394" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="7:7">
       <c r="G394" s="53"/>
     </row>
-    <row r="395" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="7:7">
       <c r="G395" s="53"/>
     </row>
-    <row r="396" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="7:7">
       <c r="G396" s="53"/>
     </row>
-    <row r="397" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="7:7">
       <c r="G397" s="53"/>
     </row>
-    <row r="398" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="7:7">
       <c r="G398" s="53"/>
     </row>
-    <row r="399" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="7:7">
       <c r="G399" s="53"/>
     </row>
-    <row r="400" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="7:7">
       <c r="G400" s="53"/>
     </row>
-    <row r="401" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="7:7">
       <c r="G401" s="53"/>
     </row>
-    <row r="402" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="7:7">
       <c r="G402" s="53"/>
     </row>
-    <row r="403" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="7:7">
       <c r="G403" s="53"/>
     </row>
-    <row r="404" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="7:7">
       <c r="G404" s="53"/>
     </row>
   </sheetData>
@@ -11435,58 +11651,90 @@
     <mergeCell ref="M3:M4"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C97:D114 C115:C121">
-    <cfRule type="cellIs" dxfId="14" priority="191" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="199" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="192" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="200" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G123:G1048576">
-    <cfRule type="cellIs" dxfId="12" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="27" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="28" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G96:H122">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="G96:H105 G122:H122">
+    <cfRule type="cellIs" dxfId="17" priority="9" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="10" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:I95">
-    <cfRule type="cellIs" dxfId="10" priority="31" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="39" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="32" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="40" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H123:H130">
-    <cfRule type="cellIs" dxfId="8" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="21" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="14" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="22" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H131:I266">
-    <cfRule type="cellIs" dxfId="6" priority="189" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="197" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="190" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="198" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I96:I130">
-    <cfRule type="cellIs" dxfId="4" priority="37" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="38" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="46" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G106:H107">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G108:H111">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G112:H116">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G117:H121">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11498,7 +11746,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:D17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="2" width="26.28515625" customWidth="1"/>
@@ -11506,101 +11754,101 @@
     <col min="4" max="4" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4">
       <c r="B1" s="62" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="C1" s="63" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4">
       <c r="B2" s="54" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="D2" s="54"/>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4">
       <c r="B3" s="54" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="D3" s="54"/>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4">
       <c r="B4" s="54" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="D4" s="54"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4">
       <c r="B5" s="54" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="D5" s="54"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4">
       <c r="B6" s="54" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="D6" s="54"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4">
       <c r="B7" s="54" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="D7" s="54"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4">
       <c r="B8" s="54" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="D8" s="54"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4">
       <c r="B9" s="54" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
       <c r="B10" s="54" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="D10" s="54"/>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3">
       <c r="C17" s="28"/>
     </row>
   </sheetData>

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="11_C0E26E8C2FF3658481E6AE6DE74C74B31A2D8B7D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C2A6E34-B88C-4799-A709-C607474C06A7}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="11_C0E26E8C2FF3658481E6AE6DE74C74B31A2D8B7D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A6D1C18-61D5-427D-BB7D-B4DE6023E9A2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="254">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -784,6 +784,30 @@
   </si>
   <si>
     <t>Dera</t>
+  </si>
+  <si>
+    <t>Psicóloga</t>
+  </si>
+  <si>
+    <t>Saúde</t>
+  </si>
+  <si>
+    <t>Pizza</t>
+  </si>
+  <si>
+    <t>Uber Galpãozin</t>
+  </si>
+  <si>
+    <t>Parrilla</t>
+  </si>
+  <si>
+    <t>Empanadas</t>
+  </si>
+  <si>
+    <t>Pagamento Galpãozin</t>
+  </si>
+  <si>
+    <t>Pagamento Empanadas</t>
   </si>
 </sst>
 </file>
@@ -795,7 +819,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1289,57 +1313,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1546,6 +1530,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
@@ -1723,7 +1711,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:F41"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
     <col min="3" max="3" width="19.85546875" style="1" customWidth="1"/>
@@ -1732,8 +1720,8 @@
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" customHeight="1"/>
-    <row r="2" spans="2:6" ht="23.25" customHeight="1">
+    <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
         <v>0</v>
       </c>
@@ -1745,20 +1733,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="24" customHeight="1">
+    <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="82"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C25+C26+C7+C27</f>
-        <v>2193.3489047619041</v>
+        <v>1899.0389047619037</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E25+E26</f>
-        <v>3060.4566666666669</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="7.5" customHeight="1"/>
-    <row r="5" spans="2:6">
+        <v>2716.1166666666668</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
@@ -1770,21 +1758,21 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-6306.6510952380959</v>
+        <v>-6938.9610952380963</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-6939.5433333333331</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6">
+        <v>-7283.8833333333332</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -1792,7 +1780,7 @@
       <c r="D7" s="9"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
@@ -1806,35 +1794,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>3736.3110952380957</v>
+        <v>4368.6210952380961</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>1327.2033333333334</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6">
+        <v>1671.5433333333335</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>3736.3110952380957</v>
+        <v>4368.6210952380961</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>1327.2033333333334</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6">
+        <v>1671.5433333333335</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
@@ -1848,7 +1836,7 @@
         <v>5612.34</v>
       </c>
     </row>
-    <row r="12" spans="2:6" outlineLevel="1">
+    <row r="12" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
         <v>10</v>
       </c>
@@ -1862,7 +1850,7 @@
         <v>1617.835</v>
       </c>
     </row>
-    <row r="13" spans="2:6" outlineLevel="1">
+    <row r="13" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
@@ -1876,7 +1864,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="2:6" outlineLevel="1">
+    <row r="14" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B14" s="13" t="s">
         <v>12</v>
       </c>
@@ -1891,7 +1879,7 @@
       </c>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="2:6" outlineLevel="1">
+    <row r="15" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="s">
         <v>13</v>
       </c>
@@ -1905,7 +1893,7 @@
         <v>40.619999999999997</v>
       </c>
     </row>
-    <row r="16" spans="2:6" outlineLevel="1">
+    <row r="16" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
         <v>14</v>
       </c>
@@ -1919,7 +1907,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:5" outlineLevel="1">
+    <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
         <v>15</v>
       </c>
@@ -1933,7 +1921,7 @@
         <v>112.38500000000001</v>
       </c>
     </row>
-    <row r="18" spans="2:5" outlineLevel="1">
+    <row r="18" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
         <v>16</v>
       </c>
@@ -1947,7 +1935,7 @@
         <v>333.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" outlineLevel="1">
+    <row r="19" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B19" s="13" t="str">
         <f>Contas!$D10</f>
         <v>Cartão Itaú da Stella</v>
@@ -1959,7 +1947,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="2:5" outlineLevel="1">
+    <row r="20" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B20" s="13" t="str">
         <f>Contas!$D11</f>
         <v>Recolhimento INSS</v>
@@ -1971,7 +1959,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="21" spans="2:5" outlineLevel="1">
+    <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B21" s="13" t="str">
         <f>Contas!$D12</f>
         <v>Empréstimo</v>
@@ -1983,7 +1971,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="22" spans="2:5" outlineLevel="1">
+    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B22" s="17" t="s">
         <v>17</v>
       </c>
@@ -1991,19 +1979,19 @@
       <c r="D22" s="19"/>
       <c r="E22" s="18"/>
     </row>
-    <row r="23" spans="2:5" outlineLevel="1">
+    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B23" s="13"/>
       <c r="C23" s="14"/>
       <c r="D23" s="15"/>
       <c r="E23" s="14"/>
     </row>
-    <row r="24" spans="2:5" outlineLevel="1">
+    <row r="24" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B24" s="13"/>
       <c r="C24" s="14"/>
       <c r="D24" s="15"/>
       <c r="E24" s="14"/>
     </row>
-    <row r="25" spans="2:5">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
         <v>18</v>
       </c>
@@ -2013,7 +2001,7 @@
       <c r="D25" s="9"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" spans="2:5">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
         <v>19</v>
       </c>
@@ -2027,15 +2015,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:5">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="8"/>
+      <c r="C27" s="8">
+        <v>338</v>
+      </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28" spans="2:5" outlineLevel="1">
+    <row r="28" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B28" s="13" t="s">
         <v>21</v>
       </c>
@@ -2046,7 +2036,7 @@
       <c r="D28" s="15"/>
       <c r="E28" s="14"/>
     </row>
-    <row r="29" spans="2:5" outlineLevel="1">
+    <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B29" s="13" t="s">
         <v>22</v>
       </c>
@@ -2054,7 +2044,7 @@
       <c r="D29" s="20"/>
       <c r="E29" s="21"/>
     </row>
-    <row r="30" spans="2:5" outlineLevel="1">
+    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B30" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L7</f>
         <v xml:space="preserve">       </v>
@@ -2066,7 +2056,7 @@
       <c r="D30" s="20"/>
       <c r="E30" s="21"/>
     </row>
-    <row r="31" spans="2:5" outlineLevel="1">
+    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B31" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L8</f>
         <v xml:space="preserve">       </v>
@@ -2078,7 +2068,7 @@
       <c r="D31" s="20"/>
       <c r="E31" s="21"/>
     </row>
-    <row r="32" spans="2:5" outlineLevel="1">
+    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B32" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L9</f>
         <v xml:space="preserve">       </v>
@@ -2090,7 +2080,7 @@
       <c r="D32" s="20"/>
       <c r="E32" s="21"/>
     </row>
-    <row r="33" spans="2:6" outlineLevel="1">
+    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B33" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L10</f>
         <v xml:space="preserve">       </v>
@@ -2102,7 +2092,7 @@
       <c r="D33" s="20"/>
       <c r="E33" s="21"/>
     </row>
-    <row r="34" spans="2:6" outlineLevel="1">
+    <row r="34" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B34" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L12</f>
         <v xml:space="preserve">       </v>
@@ -2114,7 +2104,7 @@
       <c r="D34" s="20"/>
       <c r="E34" s="21"/>
     </row>
-    <row r="35" spans="2:6" outlineLevel="1">
+    <row r="35" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B35" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L13</f>
         <v xml:space="preserve">       </v>
@@ -2126,7 +2116,7 @@
       <c r="D35" s="20"/>
       <c r="E35" s="21"/>
     </row>
-    <row r="36" spans="2:6" outlineLevel="1">
+    <row r="36" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B36" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L14</f>
         <v xml:space="preserve">       </v>
@@ -2138,7 +2128,7 @@
       <c r="D36" s="20"/>
       <c r="E36" s="21"/>
     </row>
-    <row r="37" spans="2:6" outlineLevel="1">
+    <row r="37" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B37" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L15</f>
         <v xml:space="preserve">       </v>
@@ -2150,7 +2140,7 @@
       <c r="D37" s="20"/>
       <c r="E37" s="21"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L16</f>
         <v xml:space="preserve">       </v>
@@ -2163,7 +2153,7 @@
       <c r="E38" s="21"/>
       <c r="F38" s="16"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L17</f>
         <v xml:space="preserve">       </v>
@@ -2176,7 +2166,7 @@
       <c r="E39" s="21"/>
       <c r="F39" s="16"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L21</f>
         <v xml:space="preserve">       </v>
@@ -2188,7 +2178,7 @@
       <c r="D40" s="20"/>
       <c r="E40" s="21"/>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L22</f>
         <v xml:space="preserve">       </v>
@@ -2212,7 +2202,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:D24"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="31.42578125" customWidth="1"/>
@@ -2221,8 +2211,8 @@
     <col min="5" max="5" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="39" customHeight="1"/>
-    <row r="2" spans="2:4" ht="18.75" customHeight="1">
+    <row r="1" spans="2:4" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="22"/>
       <c r="C2" s="23" t="s">
         <v>2</v>
@@ -2231,7 +2221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
@@ -2244,45 +2234,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>1327.2033333333334</v>
+        <v>1671.5433333333335</v>
       </c>
       <c r="D4" s="24">
         <f>Saldo!C9+D5</f>
-        <v>3736.3110952380957</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
+        <v>4368.6210952380961</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="13"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="13"/>
       <c r="C7" s="8"/>
       <c r="D7" s="24"/>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="13"/>
       <c r="C8" s="8"/>
       <c r="D8" s="24"/>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="13"/>
       <c r="C9" s="8"/>
       <c r="D9" s="24"/>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
@@ -2292,7 +2282,7 @@
       </c>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="2:4">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
         <v>23</v>
       </c>
@@ -2302,7 +2292,7 @@
       </c>
       <c r="D11" s="13"/>
     </row>
-    <row r="12" spans="2:4">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="25" t="s">
         <v>24</v>
       </c>
@@ -2312,7 +2302,7 @@
       </c>
       <c r="D12" s="13"/>
     </row>
-    <row r="13" spans="2:4">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
         <v>12</v>
       </c>
@@ -2322,7 +2312,7 @@
       </c>
       <c r="D13" s="13"/>
     </row>
-    <row r="14" spans="2:4">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="13" t="s">
         <v>13</v>
       </c>
@@ -2332,7 +2322,7 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="2:4">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="s">
         <v>14</v>
       </c>
@@ -2342,7 +2332,7 @@
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="2:4">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
         <v>15</v>
       </c>
@@ -2352,7 +2342,7 @@
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
         <v>25</v>
       </c>
@@ -2362,7 +2352,7 @@
       </c>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
         <v>26</v>
       </c>
@@ -2372,25 +2362,25 @@
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="19" spans="2:4">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="13"/>
       <c r="C19" s="14"/>
       <c r="D19" s="13"/>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>4425.5433333333331</v>
+        <v>4769.8833333333332</v>
       </c>
       <c r="D20" s="27"/>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="2:4">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>28</v>
       </c>
@@ -2398,7 +2388,7 @@
         <v>5587.2758333333331</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>29</v>
       </c>
@@ -2406,7 +2396,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>30</v>
       </c>
@@ -2426,7 +2416,7 @@
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
   <dimension ref="C1:Q67"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" style="2" customWidth="1"/>
@@ -2441,7 +2431,7 @@
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="29" t="s">
         <v>32</v>
       </c>
@@ -2455,7 +2445,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1">
+    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="31">
         <f>SUM(L5:L21)</f>
         <v>0</v>
@@ -2473,7 +2463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="3:17" ht="30" customHeight="1">
+    <row r="4" spans="3:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="33" t="s">
         <v>34</v>
       </c>
@@ -2520,7 +2510,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="3:17" ht="16.5" customHeight="1">
+    <row r="5" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="68"/>
       <c r="D5" s="36"/>
       <c r="E5" s="37"/>
@@ -2537,7 +2527,7 @@
       <c r="P5" s="64"/>
       <c r="Q5" s="37"/>
     </row>
-    <row r="6" spans="3:17" ht="16.5" customHeight="1">
+    <row r="6" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="37"/>
       <c r="D6" s="36"/>
       <c r="E6" s="37"/>
@@ -2569,7 +2559,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="3:17" ht="16.5" customHeight="1">
+    <row r="7" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="35"/>
       <c r="D7" s="36"/>
       <c r="E7" s="37"/>
@@ -2598,7 +2588,7 @@
       <c r="P7" s="35"/>
       <c r="Q7" s="37"/>
     </row>
-    <row r="8" spans="3:17" ht="16.5" customHeight="1">
+    <row r="8" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="35"/>
       <c r="D8" s="36"/>
       <c r="E8" s="37"/>
@@ -2627,7 +2617,7 @@
       <c r="P8" s="35"/>
       <c r="Q8" s="37"/>
     </row>
-    <row r="9" spans="3:17" ht="16.5" customHeight="1">
+    <row r="9" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="35"/>
       <c r="D9" s="36"/>
       <c r="E9" s="37"/>
@@ -2656,7 +2646,7 @@
       <c r="P9" s="35"/>
       <c r="Q9" s="37"/>
     </row>
-    <row r="10" spans="3:17" ht="16.5" customHeight="1">
+    <row r="10" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="35"/>
       <c r="D10" s="36"/>
       <c r="E10" s="37"/>
@@ -2688,7 +2678,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="3:17" ht="16.5" customHeight="1">
+    <row r="11" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="35"/>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
@@ -2717,7 +2707,7 @@
       <c r="P11" s="35"/>
       <c r="Q11" s="37"/>
     </row>
-    <row r="12" spans="3:17" ht="16.5" customHeight="1">
+    <row r="12" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="37"/>
       <c r="D12" s="36"/>
       <c r="E12" s="37"/>
@@ -2746,7 +2736,7 @@
       <c r="P12" s="35"/>
       <c r="Q12" s="37"/>
     </row>
-    <row r="13" spans="3:17" ht="16.5" customHeight="1">
+    <row r="13" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="37"/>
       <c r="D13" s="36"/>
       <c r="E13" s="37"/>
@@ -2775,7 +2765,7 @@
       <c r="P13" s="35"/>
       <c r="Q13" s="37"/>
     </row>
-    <row r="14" spans="3:17" ht="16.5" customHeight="1">
+    <row r="14" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="37"/>
       <c r="D14" s="36"/>
       <c r="E14" s="37"/>
@@ -2804,7 +2794,7 @@
       <c r="P14" s="35"/>
       <c r="Q14" s="37"/>
     </row>
-    <row r="15" spans="3:17" ht="16.5" customHeight="1">
+    <row r="15" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="37"/>
       <c r="D15" s="36"/>
       <c r="E15" s="37"/>
@@ -2833,7 +2823,7 @@
       <c r="P15" s="35"/>
       <c r="Q15" s="37"/>
     </row>
-    <row r="16" spans="3:17" ht="16.5" customHeight="1">
+    <row r="16" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="37"/>
       <c r="D16" s="36"/>
       <c r="E16" s="37"/>
@@ -2850,7 +2840,7 @@
       <c r="P16" s="35"/>
       <c r="Q16" s="37"/>
     </row>
-    <row r="17" spans="3:17" ht="16.5" customHeight="1">
+    <row r="17" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="35"/>
       <c r="D17" s="36"/>
       <c r="E17" s="37"/>
@@ -2867,7 +2857,7 @@
       <c r="P17" s="35"/>
       <c r="Q17" s="37"/>
     </row>
-    <row r="18" spans="3:17" ht="16.5" customHeight="1">
+    <row r="18" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="35"/>
       <c r="D18" s="36"/>
       <c r="E18" s="37"/>
@@ -2884,7 +2874,7 @@
       <c r="P18" s="35"/>
       <c r="Q18" s="37"/>
     </row>
-    <row r="19" spans="3:17" ht="16.5" customHeight="1">
+    <row r="19" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -2895,198 +2885,198 @@
       <c r="O19" s="41"/>
       <c r="P19" s="41"/>
     </row>
-    <row r="20" spans="3:17">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
       <c r="H20" s="2"/>
       <c r="O20" s="42"/>
       <c r="P20" s="42"/>
     </row>
-    <row r="21" spans="3:17">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
       <c r="H21" s="2"/>
       <c r="O21" s="42"/>
       <c r="P21" s="42"/>
     </row>
-    <row r="22" spans="3:17">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
       <c r="H22" s="2"/>
       <c r="O22" s="42"/>
       <c r="P22" s="42"/>
     </row>
-    <row r="23" spans="3:17">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O23" s="42"/>
       <c r="P23" s="42"/>
     </row>
-    <row r="24" spans="3:17">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O24" s="42"/>
       <c r="P24" s="42"/>
     </row>
-    <row r="25" spans="3:17">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O25" s="42"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="3:17">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O26" s="42"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="3:17">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O27" s="42"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="3:17">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O28" s="42"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="3:17">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O29" s="42"/>
       <c r="P29" s="42"/>
     </row>
-    <row r="30" spans="3:17">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O30" s="42"/>
       <c r="P30" s="42"/>
     </row>
-    <row r="31" spans="3:17">
+    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O31" s="42"/>
       <c r="P31" s="42"/>
     </row>
-    <row r="32" spans="3:17">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O32" s="42"/>
       <c r="P32" s="42"/>
     </row>
-    <row r="33" spans="15:16">
+    <row r="33" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O33" s="42"/>
       <c r="P33" s="42"/>
     </row>
-    <row r="34" spans="15:16">
+    <row r="34" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O34" s="42"/>
       <c r="P34" s="42"/>
     </row>
-    <row r="35" spans="15:16">
+    <row r="35" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O35" s="42"/>
       <c r="P35" s="42"/>
     </row>
-    <row r="36" spans="15:16">
+    <row r="36" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O36" s="42"/>
       <c r="P36" s="42"/>
     </row>
-    <row r="37" spans="15:16">
+    <row r="37" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O37" s="42"/>
       <c r="P37" s="42"/>
     </row>
-    <row r="38" spans="15:16">
+    <row r="38" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O38" s="42"/>
       <c r="P38" s="42"/>
     </row>
-    <row r="39" spans="15:16">
+    <row r="39" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O39" s="42"/>
       <c r="P39" s="42"/>
     </row>
-    <row r="40" spans="15:16">
+    <row r="40" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O40" s="42"/>
       <c r="P40" s="42"/>
     </row>
-    <row r="41" spans="15:16">
+    <row r="41" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O41" s="42"/>
       <c r="P41" s="42"/>
     </row>
-    <row r="42" spans="15:16">
+    <row r="42" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
     </row>
-    <row r="43" spans="15:16">
+    <row r="43" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O43" s="42"/>
       <c r="P43" s="42"/>
     </row>
-    <row r="44" spans="15:16">
+    <row r="44" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O44" s="42"/>
       <c r="P44" s="42"/>
     </row>
-    <row r="45" spans="15:16">
+    <row r="45" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O45" s="42"/>
       <c r="P45" s="42"/>
     </row>
-    <row r="46" spans="15:16">
+    <row r="46" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O46" s="42"/>
       <c r="P46" s="42"/>
     </row>
-    <row r="47" spans="15:16">
+    <row r="47" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O47" s="42"/>
       <c r="P47" s="42"/>
     </row>
-    <row r="48" spans="15:16">
+    <row r="48" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O48" s="42"/>
       <c r="P48" s="42"/>
     </row>
-    <row r="49" spans="15:16">
+    <row r="49" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O49" s="42"/>
       <c r="P49" s="42"/>
     </row>
-    <row r="50" spans="15:16">
+    <row r="50" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O50" s="42"/>
       <c r="P50" s="42"/>
     </row>
-    <row r="51" spans="15:16">
+    <row r="51" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O51" s="42"/>
       <c r="P51" s="42"/>
     </row>
-    <row r="52" spans="15:16">
+    <row r="52" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O52" s="42"/>
       <c r="P52" s="42"/>
     </row>
-    <row r="53" spans="15:16">
+    <row r="53" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O53" s="42"/>
       <c r="P53" s="42"/>
     </row>
-    <row r="54" spans="15:16">
+    <row r="54" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O54" s="42"/>
       <c r="P54" s="42"/>
     </row>
-    <row r="55" spans="15:16">
+    <row r="55" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O55" s="42"/>
       <c r="P55" s="42"/>
     </row>
-    <row r="56" spans="15:16">
+    <row r="56" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O56" s="42"/>
       <c r="P56" s="42"/>
     </row>
-    <row r="57" spans="15:16">
+    <row r="57" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O57" s="42"/>
       <c r="P57" s="42"/>
     </row>
-    <row r="58" spans="15:16">
+    <row r="58" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O58" s="42"/>
       <c r="P58" s="42"/>
     </row>
-    <row r="59" spans="15:16">
+    <row r="59" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O59" s="42"/>
       <c r="P59" s="42"/>
     </row>
-    <row r="60" spans="15:16">
+    <row r="60" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O60" s="42"/>
       <c r="P60" s="42"/>
     </row>
-    <row r="61" spans="15:16">
+    <row r="61" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O61" s="42"/>
       <c r="P61" s="42"/>
     </row>
-    <row r="62" spans="15:16">
+    <row r="62" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O62" s="42"/>
       <c r="P62" s="42"/>
     </row>
-    <row r="63" spans="15:16">
+    <row r="63" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O63" s="42"/>
       <c r="P63" s="42"/>
     </row>
-    <row r="64" spans="15:16">
+    <row r="64" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O64" s="42"/>
       <c r="P64" s="42"/>
     </row>
-    <row r="65" spans="15:16">
+    <row r="65" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O65" s="42"/>
       <c r="P65" s="42"/>
     </row>
-    <row r="66" spans="15:16">
+    <row r="66" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O66" s="42"/>
       <c r="P66" s="42"/>
     </row>
-    <row r="67" spans="15:16">
+    <row r="67" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O67" s="42"/>
       <c r="P67" s="42"/>
     </row>
@@ -3097,7 +3087,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J5:K22">
-    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
       <formula>"Parcelado/Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3112,7 +3102,7 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="C1:Q142"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" style="2" customWidth="1"/>
@@ -3127,7 +3117,7 @@
     <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="44" t="s">
         <v>49</v>
       </c>
@@ -3143,18 +3133,18 @@
       <c r="L1" s="43"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1">
+    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="45">
         <f>SUM(L6:L184)</f>
-        <v>7063.5144285714287</v>
+        <v>8040.1644285714283</v>
       </c>
       <c r="E2" s="32">
         <f>SUMIF($E$6:$E$184,E1,$M$6:$M$184)</f>
-        <v>3736.3110952380957</v>
+        <v>4368.6210952380961</v>
       </c>
       <c r="F2" s="32">
         <f>SUMIF($F$6:$F$184,F1,$M$6:$M$184)</f>
-        <v>1327.2033333333334</v>
+        <v>1671.5433333333335</v>
       </c>
       <c r="G2" s="32">
         <f>SUMIF($G$6:$G$184,G1,$M$6:$M$184)</f>
@@ -3164,14 +3154,14 @@
       <c r="L2" s="43"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="3:17">
+    <row r="3" spans="3:17" x14ac:dyDescent="0.25">
       <c r="L3" s="43"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="3:17">
+    <row r="4" spans="3:17" x14ac:dyDescent="0.25">
       <c r="M4" s="43"/>
     </row>
-    <row r="5" spans="3:17" ht="32.25" customHeight="1">
+    <row r="5" spans="3:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="33"/>
       <c r="D5" s="33" t="s">
         <v>35</v>
@@ -3216,7 +3206,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="3:17">
+    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C6" s="35"/>
       <c r="D6" s="36" t="s">
         <v>51</v>
@@ -3264,7 +3254,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="3:17">
+    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C7" s="35"/>
       <c r="D7" s="36" t="s">
         <v>54</v>
@@ -3310,7 +3300,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="3:17">
+    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C8" s="35"/>
       <c r="D8" s="74" t="s">
         <v>56</v>
@@ -3356,7 +3346,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="3:17">
+    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C9" s="35"/>
       <c r="D9" s="74" t="s">
         <v>58</v>
@@ -3402,7 +3392,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="3:17">
+    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C10" s="35"/>
       <c r="D10" s="74" t="s">
         <v>60</v>
@@ -3448,7 +3438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="3:17">
+    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C11" s="35"/>
       <c r="D11" s="74" t="s">
         <v>61</v>
@@ -3494,7 +3484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="3:17">
+    <row r="12" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C12" s="35"/>
       <c r="D12" s="74" t="s">
         <v>62</v>
@@ -3542,7 +3532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:17">
+    <row r="13" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C13" s="35"/>
       <c r="D13" s="65" t="s">
         <v>63</v>
@@ -3590,7 +3580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="3:17">
+    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C14" s="35"/>
       <c r="D14" s="65" t="s">
         <v>65</v>
@@ -3638,7 +3628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="3:17">
+    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C15" s="35"/>
       <c r="D15" s="65" t="s">
         <v>66</v>
@@ -3686,7 +3676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="3:17">
+    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C16" s="35"/>
       <c r="D16" s="75" t="s">
         <v>67</v>
@@ -3731,7 +3721,7 @@
       </c>
       <c r="Q16" s="37"/>
     </row>
-    <row r="17" spans="3:17">
+    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C17" s="35"/>
       <c r="D17" s="75" t="s">
         <v>68</v>
@@ -3777,7 +3767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="3:17">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C18" s="35"/>
       <c r="D18" s="75" t="s">
         <v>70</v>
@@ -3823,7 +3813,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:17">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C19" s="35"/>
       <c r="D19" s="75" t="s">
         <v>71</v>
@@ -3869,7 +3859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="3:17">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C20" s="35"/>
       <c r="D20" s="36" t="s">
         <v>72</v>
@@ -3917,7 +3907,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:17">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C21" s="35"/>
       <c r="D21" s="46" t="s">
         <v>73</v>
@@ -3963,7 +3953,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="3:17">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C22" s="35"/>
       <c r="D22" s="46" t="s">
         <v>74</v>
@@ -4009,7 +3999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:17">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C23" s="35"/>
       <c r="D23" s="46" t="s">
         <v>75</v>
@@ -4055,7 +4045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="3:17">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C24" s="35"/>
       <c r="D24" s="46" t="s">
         <v>76</v>
@@ -4103,7 +4093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:17">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C25" s="35"/>
       <c r="D25" s="46" t="s">
         <v>77</v>
@@ -4149,7 +4139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="3:17">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C26" s="35"/>
       <c r="D26" s="46" t="s">
         <v>78</v>
@@ -4195,7 +4185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="3:17">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C27" s="35"/>
       <c r="D27" s="46" t="s">
         <v>79</v>
@@ -4243,7 +4233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="3:17">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C28" s="35"/>
       <c r="D28" s="46" t="s">
         <v>80</v>
@@ -4289,7 +4279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="3:17">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C29" s="35"/>
       <c r="D29" s="46" t="s">
         <v>81</v>
@@ -4337,7 +4327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="3:17">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C30" s="35" t="s">
         <v>82</v>
       </c>
@@ -4385,7 +4375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="3:17">
+    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C31" s="35"/>
       <c r="D31" s="36" t="s">
         <v>85</v>
@@ -4431,7 +4421,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="3:17">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C32" s="35"/>
       <c r="D32" s="46" t="s">
         <v>87</v>
@@ -4477,7 +4467,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="3:17">
+    <row r="33" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C33" s="35"/>
       <c r="D33" s="36" t="s">
         <v>88</v>
@@ -4523,7 +4513,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="3:17">
+    <row r="34" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C34" s="35"/>
       <c r="D34" s="36" t="s">
         <v>90</v>
@@ -4569,7 +4559,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="3:17">
+    <row r="35" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C35" s="35"/>
       <c r="D35" s="46" t="s">
         <v>91</v>
@@ -4615,7 +4605,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="3:17">
+    <row r="36" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C36" s="35"/>
       <c r="D36" s="36" t="s">
         <v>92</v>
@@ -4661,7 +4651,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="3:17">
+    <row r="37" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C37" s="35"/>
       <c r="D37" s="36" t="s">
         <v>93</v>
@@ -4707,7 +4697,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="3:17">
+    <row r="38" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C38" s="35"/>
       <c r="D38" s="46" t="s">
         <v>94</v>
@@ -4751,7 +4741,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="3:17">
+    <row r="39" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C39" s="35"/>
       <c r="D39" s="46" t="s">
         <v>95</v>
@@ -4795,7 +4785,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="3:17">
+    <row r="40" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C40" s="35"/>
       <c r="D40" s="46" t="s">
         <v>97</v>
@@ -4836,7 +4826,7 @@
       </c>
       <c r="Q40" s="37"/>
     </row>
-    <row r="41" spans="3:17">
+    <row r="41" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C41" s="35"/>
       <c r="D41" s="36" t="s">
         <v>98</v>
@@ -4880,7 +4870,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="3:17">
+    <row r="42" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C42" s="35"/>
       <c r="D42" s="46" t="s">
         <v>99</v>
@@ -4921,7 +4911,7 @@
       </c>
       <c r="Q42" s="37"/>
     </row>
-    <row r="43" spans="3:17">
+    <row r="43" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C43" s="35"/>
       <c r="D43" s="66" t="s">
         <v>100</v>
@@ -4965,7 +4955,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="3:17">
+    <row r="44" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C44" s="35"/>
       <c r="D44" s="46" t="s">
         <v>102</v>
@@ -5011,7 +5001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="3:17">
+    <row r="45" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C45" s="35"/>
       <c r="D45" s="46" t="s">
         <v>103</v>
@@ -5059,7 +5049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="3:17">
+    <row r="46" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C46" s="35"/>
       <c r="D46" s="46" t="s">
         <v>104</v>
@@ -5105,7 +5095,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="3:17">
+    <row r="47" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C47" s="35"/>
       <c r="D47" s="46" t="s">
         <v>107</v>
@@ -5153,7 +5143,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="3:17">
+    <row r="48" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C48" s="35"/>
       <c r="D48" s="46" t="s">
         <v>109</v>
@@ -5199,7 +5189,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="3:17">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C49" s="35"/>
       <c r="D49" s="46" t="s">
         <v>111</v>
@@ -5245,7 +5235,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="3:17">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C50" s="76"/>
       <c r="D50" s="66" t="s">
         <v>113</v>
@@ -5285,7 +5275,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="3:17">
+    <row r="51" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C51" s="35"/>
       <c r="D51" s="46" t="s">
         <v>114</v>
@@ -5331,7 +5321,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="3:17">
+    <row r="52" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C52" s="35"/>
       <c r="D52" s="46" t="s">
         <v>116</v>
@@ -5379,7 +5369,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="3:17">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C53" s="35"/>
       <c r="D53" s="46" t="s">
         <v>117</v>
@@ -5425,7 +5415,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="3:17">
+    <row r="54" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C54" s="35"/>
       <c r="D54" s="46" t="s">
         <v>118</v>
@@ -5471,7 +5461,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="3:17">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C55" s="35"/>
       <c r="D55" s="46" t="s">
         <v>119</v>
@@ -5519,7 +5509,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="3:17">
+    <row r="56" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C56" s="35"/>
       <c r="D56" s="46" t="s">
         <v>121</v>
@@ -5568,7 +5558,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="3:17">
+    <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="35"/>
       <c r="D57" s="46" t="s">
         <v>122</v>
@@ -5616,7 +5606,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="3:17">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C58" s="35"/>
       <c r="D58" s="46" t="s">
         <v>123</v>
@@ -5664,7 +5654,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="3:17">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C59" s="35"/>
       <c r="D59" s="46" t="s">
         <v>124</v>
@@ -5710,7 +5700,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="3:17">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C60" s="35"/>
       <c r="D60" s="46" t="s">
         <v>125</v>
@@ -5756,7 +5746,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="3:17">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C61" s="35"/>
       <c r="D61" s="46" t="s">
         <v>126</v>
@@ -5802,7 +5792,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="3:17">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C62" s="35"/>
       <c r="D62" s="46" t="s">
         <v>127</v>
@@ -5848,31 +5838,43 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="3:17">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C63" s="35"/>
-      <c r="D63" s="46"/>
-      <c r="E63" s="37"/>
+      <c r="D63" s="46" t="s">
+        <v>246</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F63" s="37"/>
       <c r="G63" s="37"/>
       <c r="H63" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I63" s="38"/>
-      <c r="J63" s="38"/>
-      <c r="K63" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I63" s="38">
+        <v>520</v>
+      </c>
+      <c r="J63" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K63" s="38" t="s">
+        <v>247</v>
+      </c>
       <c r="L63" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M63" s="38" t="str">
+        <v>520</v>
+      </c>
+      <c r="M63" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>520</v>
       </c>
       <c r="N63" s="39">
         <v>1</v>
       </c>
-      <c r="O63" s="35"/>
+      <c r="O63" s="64">
+        <v>46329</v>
+      </c>
       <c r="P63" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5882,26 +5884,38 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="3:17">
+    <row r="64" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C64" s="35"/>
-      <c r="D64" s="46"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
+      <c r="D64" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="E64" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G64" s="37"/>
       <c r="H64" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I64" s="38"/>
-      <c r="J64" s="38"/>
-      <c r="K64" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I64" s="38">
+        <v>91.8</v>
+      </c>
+      <c r="J64" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K64" s="38" t="s">
+        <v>110</v>
+      </c>
       <c r="L64" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M64" s="38" t="str">
+        <v>91.8</v>
+      </c>
+      <c r="M64" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>45.9</v>
       </c>
       <c r="N64" s="39">
         <v>1</v>
@@ -5916,26 +5930,38 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="3:17">
+    <row r="65" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C65" s="35"/>
-      <c r="D65" s="46"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="37"/>
+      <c r="D65" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G65" s="37"/>
       <c r="H65" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I65" s="38"/>
-      <c r="J65" s="38"/>
-      <c r="K65" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I65" s="38">
+        <v>117.28</v>
+      </c>
+      <c r="J65" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K65" s="38" t="s">
+        <v>106</v>
+      </c>
       <c r="L65" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M65" s="38" t="str">
+        <v>117.28</v>
+      </c>
+      <c r="M65" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>58.64</v>
       </c>
       <c r="N65" s="39">
         <v>1</v>
@@ -5950,26 +5976,36 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="3:17">
+    <row r="66" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C66" s="35"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="37"/>
+      <c r="D66" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="E66" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F66" s="37"/>
       <c r="G66" s="37"/>
       <c r="H66" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I66" s="38"/>
-      <c r="J66" s="38"/>
-      <c r="K66" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I66" s="38">
+        <v>25.97</v>
+      </c>
+      <c r="J66" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K66" s="38" t="s">
+        <v>106</v>
+      </c>
       <c r="L66" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M66" s="38" t="str">
+        <v>25.97</v>
+      </c>
+      <c r="M66" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>25.97</v>
       </c>
       <c r="N66" s="39">
         <v>1</v>
@@ -5984,26 +6020,39 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="3:17">
+    <row r="67" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C67" s="35"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="37"/>
+      <c r="D67" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G67" s="37"/>
       <c r="H67" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I67" s="38"/>
-      <c r="J67" s="38"/>
-      <c r="K67" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I67" s="38">
+        <f>108+95</f>
+        <v>203</v>
+      </c>
+      <c r="J67" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K67" s="38" t="s">
+        <v>110</v>
+      </c>
       <c r="L67" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M67" s="38" t="str">
+        <v>203</v>
+      </c>
+      <c r="M67" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>101.5</v>
       </c>
       <c r="N67" s="39">
         <v>1</v>
@@ -6018,26 +6067,36 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="3:17">
+    <row r="68" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C68" s="35"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="37"/>
+      <c r="D68" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="E68" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F68" s="37"/>
       <c r="G68" s="37"/>
       <c r="H68" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I68" s="38"/>
-      <c r="J68" s="38"/>
-      <c r="K68" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I68" s="38">
+        <v>52</v>
+      </c>
+      <c r="J68" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K68" s="38" t="s">
+        <v>110</v>
+      </c>
       <c r="L68" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M68" s="38" t="str">
+        <v>52</v>
+      </c>
+      <c r="M68" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>52</v>
       </c>
       <c r="N68" s="39">
         <v>1</v>
@@ -6052,26 +6111,38 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="3:17">
+    <row r="69" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C69" s="35"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
+      <c r="D69" s="46" t="s">
+        <v>250</v>
+      </c>
+      <c r="E69" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G69" s="37"/>
       <c r="H69" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I69" s="38"/>
-      <c r="J69" s="38"/>
-      <c r="K69" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I69" s="38">
+        <v>101.6</v>
+      </c>
+      <c r="J69" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K69" s="38" t="s">
+        <v>110</v>
+      </c>
       <c r="L69" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M69" s="38" t="str">
+        <v>101.6</v>
+      </c>
+      <c r="M69" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>50.8</v>
       </c>
       <c r="N69" s="39">
         <v>1</v>
@@ -6086,26 +6157,38 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="3:17">
+    <row r="70" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C70" s="35"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
+      <c r="D70" s="46" t="s">
+        <v>251</v>
+      </c>
+      <c r="E70" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G70" s="37"/>
       <c r="H70" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I70" s="38"/>
-      <c r="J70" s="38"/>
-      <c r="K70" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I70" s="38">
+        <v>175</v>
+      </c>
+      <c r="J70" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K70" s="38" t="s">
+        <v>110</v>
+      </c>
       <c r="L70" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M70" s="38" t="str">
+        <v>175</v>
+      </c>
+      <c r="M70" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>87.5</v>
       </c>
       <c r="N70" s="39">
         <v>1</v>
@@ -6120,26 +6203,36 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="3:17">
+    <row r="71" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C71" s="35"/>
-      <c r="D71" s="46"/>
-      <c r="E71" s="37"/>
+      <c r="D71" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="E71" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F71" s="37"/>
       <c r="G71" s="37"/>
       <c r="H71" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I71" s="38"/>
-      <c r="J71" s="38"/>
-      <c r="K71" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I71" s="38">
+        <v>-60</v>
+      </c>
+      <c r="J71" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="K71" s="38" t="s">
+        <v>112</v>
+      </c>
       <c r="L71" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M71" s="38" t="str">
+        <v>-60</v>
+      </c>
+      <c r="M71" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-60</v>
       </c>
       <c r="N71" s="39">
         <v>1</v>
@@ -6154,26 +6247,36 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="3:17">
+    <row r="72" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C72" s="35"/>
-      <c r="D72" s="46"/>
-      <c r="E72" s="37"/>
+      <c r="D72" s="46" t="s">
+        <v>252</v>
+      </c>
+      <c r="E72" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F72" s="37"/>
       <c r="G72" s="37"/>
       <c r="H72" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I72" s="38"/>
-      <c r="J72" s="38"/>
-      <c r="K72" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I72" s="38">
+        <v>-150</v>
+      </c>
+      <c r="J72" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="K72" s="38" t="s">
+        <v>112</v>
+      </c>
       <c r="L72" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M72" s="38" t="str">
+        <v>-150</v>
+      </c>
+      <c r="M72" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-150</v>
       </c>
       <c r="N72" s="39">
         <v>1</v>
@@ -6188,26 +6291,36 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="3:17">
+    <row r="73" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C73" s="35"/>
-      <c r="D73" s="46"/>
-      <c r="E73" s="37"/>
+      <c r="D73" s="46" t="s">
+        <v>253</v>
+      </c>
+      <c r="E73" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F73" s="37"/>
       <c r="G73" s="37"/>
       <c r="H73" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I73" s="38"/>
-      <c r="J73" s="38"/>
-      <c r="K73" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I73" s="38">
+        <v>-100</v>
+      </c>
+      <c r="J73" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="K73" s="38" t="s">
+        <v>112</v>
+      </c>
       <c r="L73" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M73" s="38" t="str">
+        <v>-100</v>
+      </c>
+      <c r="M73" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-100</v>
       </c>
       <c r="N73" s="39">
         <v>1</v>
@@ -6222,7 +6335,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="3:17">
+    <row r="74" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C74" s="35"/>
       <c r="D74" s="46"/>
       <c r="E74" s="37"/>
@@ -6256,7 +6369,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="3:17">
+    <row r="75" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C75" s="35"/>
       <c r="D75" s="46"/>
       <c r="E75" s="37"/>
@@ -6290,7 +6403,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="3:17">
+    <row r="76" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C76" s="35"/>
       <c r="D76" s="46"/>
       <c r="E76" s="37"/>
@@ -6324,7 +6437,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="3:17">
+    <row r="77" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C77" s="35"/>
       <c r="D77" s="46"/>
       <c r="E77" s="37"/>
@@ -6358,7 +6471,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="3:17">
+    <row r="78" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C78" s="35"/>
       <c r="D78" s="46"/>
       <c r="E78" s="37"/>
@@ -6392,7 +6505,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="3:17">
+    <row r="79" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C79" s="35"/>
       <c r="D79" s="46"/>
       <c r="E79" s="37"/>
@@ -6426,7 +6539,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="3:17">
+    <row r="80" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C80" s="35"/>
       <c r="D80" s="46"/>
       <c r="E80" s="37"/>
@@ -6460,7 +6573,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="3:17">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C81" s="35"/>
       <c r="D81" s="46"/>
       <c r="E81" s="37"/>
@@ -6494,7 +6607,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="3:17">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C82" s="35"/>
       <c r="D82" s="46"/>
       <c r="E82" s="37"/>
@@ -6528,7 +6641,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="3:17">
+    <row r="83" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C83" s="35"/>
       <c r="D83" s="46"/>
       <c r="E83" s="37"/>
@@ -6562,7 +6675,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="3:17">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C84" s="35"/>
       <c r="D84" s="46"/>
       <c r="E84" s="37"/>
@@ -6596,7 +6709,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="3:17">
+    <row r="85" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C85" s="35"/>
       <c r="D85" s="46"/>
       <c r="E85" s="37"/>
@@ -6630,7 +6743,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="3:17">
+    <row r="86" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C86" s="35"/>
       <c r="D86" s="46"/>
       <c r="E86" s="37"/>
@@ -6664,7 +6777,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="3:17">
+    <row r="87" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C87" s="35"/>
       <c r="D87" s="46"/>
       <c r="E87" s="37"/>
@@ -6698,7 +6811,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="3:17">
+    <row r="88" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C88" s="35"/>
       <c r="D88" s="46"/>
       <c r="E88" s="37"/>
@@ -6732,7 +6845,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="3:17">
+    <row r="89" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C89" s="35"/>
       <c r="D89" s="46"/>
       <c r="E89" s="37"/>
@@ -6766,7 +6879,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="3:17">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C90" s="35"/>
       <c r="D90" s="46"/>
       <c r="E90" s="37"/>
@@ -6800,7 +6913,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="3:17">
+    <row r="91" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C91" s="35"/>
       <c r="D91" s="46"/>
       <c r="E91" s="37"/>
@@ -6834,7 +6947,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="3:17">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C92" s="35"/>
       <c r="D92" s="46"/>
       <c r="E92" s="37"/>
@@ -6868,7 +6981,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="3:17">
+    <row r="93" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C93" s="35"/>
       <c r="D93" s="46"/>
       <c r="E93" s="37"/>
@@ -6902,7 +7015,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="3:17">
+    <row r="94" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C94" s="35"/>
       <c r="D94" s="46"/>
       <c r="E94" s="37"/>
@@ -6936,7 +7049,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="3:17">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C95" s="35"/>
       <c r="D95" s="46"/>
       <c r="E95" s="37"/>
@@ -6970,7 +7083,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="3:17">
+    <row r="96" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C96" s="35"/>
       <c r="D96" s="46"/>
       <c r="E96" s="37"/>
@@ -7004,7 +7117,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="3:17">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C97" s="35"/>
       <c r="D97" s="46"/>
       <c r="E97" s="37"/>
@@ -7038,7 +7151,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="3:17">
+    <row r="98" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C98" s="35"/>
       <c r="D98" s="46"/>
       <c r="E98" s="37"/>
@@ -7072,7 +7185,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="3:17">
+    <row r="99" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C99" s="35"/>
       <c r="D99" s="46"/>
       <c r="E99" s="37"/>
@@ -7106,7 +7219,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="3:17">
+    <row r="100" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C100" s="35"/>
       <c r="D100" s="46"/>
       <c r="E100" s="37"/>
@@ -7140,7 +7253,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C101" s="35"/>
       <c r="D101" s="46"/>
       <c r="E101" s="37"/>
@@ -7174,7 +7287,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C102" s="35"/>
       <c r="D102" s="46"/>
       <c r="E102" s="37"/>
@@ -7208,7 +7321,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C103" s="35"/>
       <c r="D103" s="46"/>
       <c r="E103" s="37"/>
@@ -7242,7 +7355,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C104" s="35"/>
       <c r="D104" s="46"/>
       <c r="E104" s="37"/>
@@ -7276,7 +7389,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C105" s="35"/>
       <c r="D105" s="46"/>
       <c r="E105" s="37"/>
@@ -7310,7 +7423,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="3:17">
+    <row r="106" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C106" s="35"/>
       <c r="D106" s="46"/>
       <c r="E106" s="37"/>
@@ -7344,7 +7457,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="3:17">
+    <row r="107" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C107" s="35"/>
       <c r="D107" s="46"/>
       <c r="E107" s="37"/>
@@ -7378,7 +7491,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="3:17">
+    <row r="108" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C108" s="35"/>
       <c r="D108" s="46"/>
       <c r="E108" s="37"/>
@@ -7412,7 +7525,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="3:17">
+    <row r="109" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C109" s="35"/>
       <c r="D109" s="46"/>
       <c r="E109" s="37"/>
@@ -7446,7 +7559,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="3:17">
+    <row r="110" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C110" s="35"/>
       <c r="D110" s="46"/>
       <c r="E110" s="37"/>
@@ -7480,7 +7593,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="3:17">
+    <row r="111" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C111" s="35"/>
       <c r="D111" s="46"/>
       <c r="E111" s="37"/>
@@ -7514,7 +7627,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="3:17">
+    <row r="112" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C112" s="35"/>
       <c r="D112" s="46"/>
       <c r="E112" s="37"/>
@@ -7548,7 +7661,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="3:17">
+    <row r="113" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C113" s="35"/>
       <c r="D113" s="46"/>
       <c r="E113" s="37"/>
@@ -7582,7 +7695,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="3:17">
+    <row r="114" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C114" s="35"/>
       <c r="D114" s="46"/>
       <c r="E114" s="37"/>
@@ -7616,7 +7729,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="3:17">
+    <row r="115" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C115" s="35"/>
       <c r="D115" s="46"/>
       <c r="E115" s="37"/>
@@ -7650,7 +7763,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="3:17">
+    <row r="116" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C116" s="35"/>
       <c r="D116" s="46"/>
       <c r="E116" s="37"/>
@@ -7684,7 +7797,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="3:17">
+    <row r="117" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C117" s="35"/>
       <c r="D117" s="46"/>
       <c r="E117" s="37"/>
@@ -7718,7 +7831,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="3:17">
+    <row r="118" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C118" s="35"/>
       <c r="D118" s="46"/>
       <c r="E118" s="37"/>
@@ -7752,7 +7865,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="3:17">
+    <row r="119" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C119" s="35"/>
       <c r="D119" s="46"/>
       <c r="E119" s="37"/>
@@ -7786,7 +7899,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="3:17">
+    <row r="120" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C120" s="35"/>
       <c r="D120" s="46"/>
       <c r="E120" s="37"/>
@@ -7820,7 +7933,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="3:17">
+    <row r="121" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C121" s="35"/>
       <c r="D121" s="46"/>
       <c r="E121" s="37"/>
@@ -7854,7 +7967,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="3:17">
+    <row r="122" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C122" s="35"/>
       <c r="D122" s="46"/>
       <c r="E122" s="37"/>
@@ -7888,7 +8001,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="3:17">
+    <row r="123" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C123" s="35"/>
       <c r="D123" s="46"/>
       <c r="E123" s="37"/>
@@ -7922,7 +8035,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="3:17">
+    <row r="124" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C124" s="35"/>
       <c r="D124" s="46"/>
       <c r="E124" s="37"/>
@@ -7956,7 +8069,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="3:17">
+    <row r="125" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C125" s="35"/>
       <c r="D125" s="46"/>
       <c r="E125" s="37"/>
@@ -7990,7 +8103,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="3:17">
+    <row r="126" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C126" s="35"/>
       <c r="D126" s="46"/>
       <c r="E126" s="37"/>
@@ -8024,7 +8137,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="3:17">
+    <row r="127" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C127" s="35"/>
       <c r="D127" s="46"/>
       <c r="E127" s="37"/>
@@ -8058,7 +8171,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="3:17">
+    <row r="128" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C128" s="35"/>
       <c r="D128" s="46"/>
       <c r="E128" s="37"/>
@@ -8092,7 +8205,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="3:17">
+    <row r="129" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C129" s="35"/>
       <c r="D129" s="46"/>
       <c r="E129" s="37"/>
@@ -8126,7 +8239,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="3:17">
+    <row r="130" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C130" s="35"/>
       <c r="D130" s="46"/>
       <c r="E130" s="37"/>
@@ -8160,7 +8273,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="3:17">
+    <row r="131" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C131" s="35"/>
       <c r="D131" s="46"/>
       <c r="E131" s="37"/>
@@ -8194,7 +8307,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="3:17">
+    <row r="132" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C132" s="35"/>
       <c r="D132" s="46"/>
       <c r="E132" s="37"/>
@@ -8228,7 +8341,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="3:17">
+    <row r="133" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C133" s="35"/>
       <c r="D133" s="46"/>
       <c r="E133" s="37"/>
@@ -8262,7 +8375,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="3:17">
+    <row r="134" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C134" s="35"/>
       <c r="D134" s="46"/>
       <c r="E134" s="37"/>
@@ -8296,7 +8409,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="3:17">
+    <row r="135" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C135" s="35"/>
       <c r="D135" s="46"/>
       <c r="E135" s="37"/>
@@ -8330,7 +8443,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="3:17">
+    <row r="136" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C136" s="35"/>
       <c r="D136" s="46"/>
       <c r="E136" s="37"/>
@@ -8364,7 +8477,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="3:17">
+    <row r="137" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C137" s="35"/>
       <c r="D137" s="46"/>
       <c r="E137" s="37"/>
@@ -8398,7 +8511,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="3:17">
+    <row r="138" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C138" s="35"/>
       <c r="D138" s="46"/>
       <c r="E138" s="37"/>
@@ -8432,7 +8545,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="3:17">
+    <row r="139" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C139" s="35"/>
       <c r="D139" s="46"/>
       <c r="E139" s="37"/>
@@ -8466,7 +8579,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="3:17">
+    <row r="140" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C140" s="35"/>
       <c r="D140" s="46"/>
       <c r="E140" s="37"/>
@@ -8500,7 +8613,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="3:17">
+    <row r="141" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C141" s="35"/>
       <c r="D141" s="46"/>
       <c r="E141" s="37"/>
@@ -8534,7 +8647,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="3:17">
+    <row r="142" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C142" s="35"/>
       <c r="D142" s="46"/>
       <c r="E142" s="37"/>
@@ -8575,37 +8688,37 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="I6:I142">
-    <cfRule type="cellIs" dxfId="28" priority="32" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="32" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J142">
-    <cfRule type="cellIs" dxfId="27" priority="6" operator="equal">
+  <conditionalFormatting sqref="J71:K73 J6:J142">
+    <cfRule type="cellIs" dxfId="19" priority="6" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:K142">
-    <cfRule type="cellIs" dxfId="26" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="25" operator="equal">
       <formula>"Parcelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="cellIs" dxfId="25" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="24" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="cellIs" dxfId="24" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="16" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K49">
-    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K54">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8617,7 +8730,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:R20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="36.5703125" customWidth="1"/>
@@ -8630,7 +8743,7 @@
     <col min="18" max="18" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="30" customHeight="1">
+    <row r="2" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="33" t="s">
         <v>35</v>
       </c>
@@ -8668,7 +8781,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="16.5" customHeight="1">
+    <row r="3" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="54" t="s">
         <v>23</v>
       </c>
@@ -8706,7 +8819,7 @@
       </c>
       <c r="R3" s="16"/>
     </row>
-    <row r="4" spans="2:18" ht="16.5" customHeight="1">
+    <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="55" t="s">
         <v>128</v>
       </c>
@@ -8744,7 +8857,7 @@
       </c>
       <c r="R4" s="16"/>
     </row>
-    <row r="5" spans="2:18" ht="16.5" customHeight="1">
+    <row r="5" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="30" t="s">
         <v>1</v>
       </c>
@@ -8785,7 +8898,7 @@
       </c>
       <c r="P5" s="59"/>
     </row>
-    <row r="6" spans="2:18" ht="16.5" customHeight="1">
+    <row r="6" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="32">
         <f>SUMIF($E$3:$E$34,B5,$K$3:$K$34)</f>
         <v>2570.34</v>
@@ -8826,7 +8939,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="16.5" customHeight="1">
+    <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="60"/>
       <c r="D7" s="54" t="s">
         <v>131</v>
@@ -8864,7 +8977,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="16.5" customHeight="1">
+    <row r="8" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="30" t="s">
         <v>2</v>
       </c>
@@ -8904,7 +9017,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="16.5" customHeight="1">
+    <row r="9" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="61">
         <f>SUMIF($F$3:$F$34,B8,$K$3:$K$34)</f>
         <v>5612.34</v>
@@ -8946,7 +9059,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="10" spans="2:18">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D10" s="54" t="s">
         <v>133</v>
       </c>
@@ -8981,7 +9094,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="11" spans="2:18">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D11" s="54" t="s">
         <v>134</v>
       </c>
@@ -9016,7 +9129,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="12" spans="2:18">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D12" s="54" t="s">
         <v>135</v>
       </c>
@@ -9051,7 +9164,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="13" spans="2:18">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D13" s="54" t="s">
         <v>136</v>
       </c>
@@ -9088,7 +9201,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="14" spans="2:18">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D14" s="37"/>
       <c r="E14" s="36"/>
       <c r="F14" s="37"/>
@@ -9102,7 +9215,7 @@
       <c r="N14" s="38"/>
       <c r="O14" s="39"/>
     </row>
-    <row r="15" spans="2:18">
+    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D15" s="37"/>
       <c r="E15" s="36"/>
       <c r="F15" s="37"/>
@@ -9116,7 +9229,7 @@
       <c r="N15" s="38"/>
       <c r="O15" s="39"/>
     </row>
-    <row r="16" spans="2:18">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D16" s="37"/>
       <c r="E16" s="36"/>
       <c r="F16" s="37"/>
@@ -9130,7 +9243,7 @@
       <c r="N16" s="38"/>
       <c r="O16" s="39"/>
     </row>
-    <row r="17" spans="4:15">
+    <row r="17" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D17" s="37"/>
       <c r="E17" s="36"/>
       <c r="F17" s="37"/>
@@ -9144,7 +9257,7 @@
       <c r="N17" s="38"/>
       <c r="O17" s="39"/>
     </row>
-    <row r="18" spans="4:15">
+    <row r="18" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D18" s="37"/>
       <c r="E18" s="36"/>
       <c r="F18" s="37"/>
@@ -9158,7 +9271,7 @@
       <c r="N18" s="38"/>
       <c r="O18" s="39"/>
     </row>
-    <row r="19" spans="4:15">
+    <row r="19" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D19" s="37"/>
       <c r="E19" s="36"/>
       <c r="F19" s="37"/>
@@ -9172,7 +9285,7 @@
       <c r="N19" s="38"/>
       <c r="O19" s="39"/>
     </row>
-    <row r="20" spans="4:15">
+    <row r="20" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D20" s="37"/>
       <c r="E20" s="36"/>
       <c r="F20" s="37"/>
@@ -9195,7 +9308,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:O404"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.140625" customWidth="1"/>
@@ -9211,17 +9324,17 @@
     <col min="15" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" s="2"/>
       <c r="N1" s="47" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="2:15" ht="14.25" customHeight="1">
+    <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G2" s="2"/>
       <c r="N2" s="43"/>
     </row>
-    <row r="3" spans="2:15" ht="27.75" customHeight="1">
+    <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G3" s="2"/>
       <c r="L3" s="47" t="s">
         <v>138</v>
@@ -9235,7 +9348,7 @@
       </c>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" spans="2:15">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G4" s="2"/>
       <c r="L4" s="48" t="s">
         <v>140</v>
@@ -9243,7 +9356,7 @@
       <c r="M4" s="84"/>
       <c r="N4" s="49"/>
     </row>
-    <row r="5" spans="2:15">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="43"/>
       <c r="C5" s="43"/>
       <c r="F5" s="16"/>
@@ -9256,7 +9369,7 @@
       </c>
       <c r="O5" s="16"/>
     </row>
-    <row r="6" spans="2:15">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G6" s="2"/>
       <c r="L6" t="s">
         <v>142</v>
@@ -9265,23 +9378,23 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="2:15">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G7" s="2"/>
       <c r="N7" s="71"/>
     </row>
-    <row r="8" spans="2:15">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F8" s="16"/>
       <c r="G8" s="50"/>
       <c r="N8" s="71"/>
     </row>
-    <row r="9" spans="2:15">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F9" s="47" t="s">
         <v>143</v>
       </c>
       <c r="G9" s="28"/>
       <c r="N9" s="70"/>
     </row>
-    <row r="10" spans="2:15">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
         <v>144</v>
       </c>
@@ -9300,7 +9413,7 @@
       </c>
       <c r="N10" s="70"/>
     </row>
-    <row r="11" spans="2:15">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
         <v>148</v>
       </c>
@@ -9322,7 +9435,7 @@
       </c>
       <c r="N11" s="70"/>
     </row>
-    <row r="12" spans="2:15">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
         <v>138</v>
       </c>
@@ -9331,7 +9444,7 @@
       </c>
       <c r="N12" s="70"/>
     </row>
-    <row r="13" spans="2:15">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F13" s="80" t="s">
         <v>140</v>
       </c>
@@ -9340,7 +9453,7 @@
       <c r="I13" s="80"/>
       <c r="N13" s="70"/>
     </row>
-    <row r="14" spans="2:15" outlineLevel="1">
+    <row r="14" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
         <v>149</v>
       </c>
@@ -9349,7 +9462,7 @@
       <c r="I14" s="53"/>
       <c r="N14" s="43"/>
     </row>
-    <row r="15" spans="2:15" outlineLevel="1">
+    <row r="15" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F15" t="s">
         <v>150</v>
       </c>
@@ -9360,7 +9473,7 @@
       <c r="I15" s="53"/>
       <c r="N15" s="43"/>
     </row>
-    <row r="16" spans="2:15" outlineLevel="1">
+    <row r="16" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F16" t="s">
         <v>151</v>
       </c>
@@ -9371,7 +9484,7 @@
       <c r="I16" s="53"/>
       <c r="N16" s="43"/>
     </row>
-    <row r="17" spans="6:14" outlineLevel="1">
+    <row r="17" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F17" t="s">
         <v>152</v>
       </c>
@@ -9382,7 +9495,7 @@
       <c r="I17" s="53"/>
       <c r="N17" s="43"/>
     </row>
-    <row r="18" spans="6:14" outlineLevel="1">
+    <row r="18" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F18" t="s">
         <v>153</v>
       </c>
@@ -9393,7 +9506,7 @@
       <c r="I18" s="53"/>
       <c r="N18" s="43"/>
     </row>
-    <row r="19" spans="6:14" outlineLevel="1">
+    <row r="19" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F19" t="s">
         <v>154</v>
       </c>
@@ -9404,7 +9517,7 @@
       <c r="I19" s="53"/>
       <c r="N19" s="43"/>
     </row>
-    <row r="20" spans="6:14" outlineLevel="1">
+    <row r="20" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F20" t="s">
         <v>155</v>
       </c>
@@ -9415,7 +9528,7 @@
       <c r="I20" s="53"/>
       <c r="N20" s="43"/>
     </row>
-    <row r="21" spans="6:14" outlineLevel="1">
+    <row r="21" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F21" t="s">
         <v>156</v>
       </c>
@@ -9426,7 +9539,7 @@
       <c r="I21" s="53"/>
       <c r="N21" s="43"/>
     </row>
-    <row r="22" spans="6:14" outlineLevel="1">
+    <row r="22" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
         <v>157</v>
       </c>
@@ -9437,7 +9550,7 @@
       <c r="I22" s="53"/>
       <c r="N22" s="43"/>
     </row>
-    <row r="23" spans="6:14" outlineLevel="1">
+    <row r="23" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F23" t="s">
         <v>158</v>
       </c>
@@ -9448,7 +9561,7 @@
       <c r="I23" s="53"/>
       <c r="N23" s="43"/>
     </row>
-    <row r="24" spans="6:14" outlineLevel="1">
+    <row r="24" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F24" t="s">
         <v>154</v>
       </c>
@@ -9459,7 +9572,7 @@
       <c r="I24" s="53"/>
       <c r="N24" s="43"/>
     </row>
-    <row r="25" spans="6:14" outlineLevel="1">
+    <row r="25" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F25" t="s">
         <v>159</v>
       </c>
@@ -9470,7 +9583,7 @@
       <c r="I25" s="53"/>
       <c r="N25" s="43"/>
     </row>
-    <row r="26" spans="6:14" outlineLevel="1">
+    <row r="26" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F26" t="s">
         <v>160</v>
       </c>
@@ -9481,7 +9594,7 @@
       <c r="I26" s="53"/>
       <c r="N26" s="43"/>
     </row>
-    <row r="27" spans="6:14" outlineLevel="1">
+    <row r="27" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F27" t="s">
         <v>161</v>
       </c>
@@ -9492,7 +9605,7 @@
       <c r="I27" s="53"/>
       <c r="N27" s="43"/>
     </row>
-    <row r="28" spans="6:14" outlineLevel="1">
+    <row r="28" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F28" t="s">
         <v>162</v>
       </c>
@@ -9503,7 +9616,7 @@
       <c r="I28" s="53"/>
       <c r="N28" s="43"/>
     </row>
-    <row r="29" spans="6:14" outlineLevel="1">
+    <row r="29" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F29" t="s">
         <v>157</v>
       </c>
@@ -9514,7 +9627,7 @@
       <c r="I29" s="53"/>
       <c r="N29" s="43"/>
     </row>
-    <row r="30" spans="6:14" outlineLevel="1">
+    <row r="30" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F30" t="s">
         <v>163</v>
       </c>
@@ -9525,7 +9638,7 @@
       <c r="I30" s="53"/>
       <c r="N30" s="43"/>
     </row>
-    <row r="31" spans="6:14" outlineLevel="1">
+    <row r="31" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F31" t="s">
         <v>113</v>
       </c>
@@ -9536,7 +9649,7 @@
       <c r="I31" s="53"/>
       <c r="N31" s="43"/>
     </row>
-    <row r="32" spans="6:14" outlineLevel="1">
+    <row r="32" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F32" t="s">
         <v>164</v>
       </c>
@@ -9547,7 +9660,7 @@
       <c r="I32" s="53"/>
       <c r="N32" s="43"/>
     </row>
-    <row r="33" spans="5:14" outlineLevel="1">
+    <row r="33" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F33" t="s">
         <v>165</v>
       </c>
@@ -9558,7 +9671,7 @@
       <c r="I33" s="53"/>
       <c r="N33" s="43"/>
     </row>
-    <row r="34" spans="5:14" outlineLevel="1">
+    <row r="34" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F34" t="s">
         <v>166</v>
       </c>
@@ -9569,7 +9682,7 @@
       <c r="I34" s="53"/>
       <c r="N34" s="43"/>
     </row>
-    <row r="35" spans="5:14" outlineLevel="1">
+    <row r="35" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F35" t="s">
         <v>167</v>
       </c>
@@ -9580,7 +9693,7 @@
       <c r="I35" s="53"/>
       <c r="N35" s="43"/>
     </row>
-    <row r="36" spans="5:14" outlineLevel="1">
+    <row r="36" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F36" t="s">
         <v>168</v>
       </c>
@@ -9591,7 +9704,7 @@
       <c r="I36" s="53"/>
       <c r="N36" s="43"/>
     </row>
-    <row r="37" spans="5:14" outlineLevel="1">
+    <row r="37" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F37" t="s">
         <v>169</v>
       </c>
@@ -9602,7 +9715,7 @@
       <c r="I37" s="53"/>
       <c r="N37" s="43"/>
     </row>
-    <row r="38" spans="5:14" outlineLevel="1">
+    <row r="38" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F38" t="s">
         <v>170</v>
       </c>
@@ -9613,7 +9726,7 @@
       <c r="I38" s="53"/>
       <c r="N38" s="43"/>
     </row>
-    <row r="39" spans="5:14" outlineLevel="1">
+    <row r="39" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
         <v>157</v>
       </c>
@@ -9624,7 +9737,7 @@
       <c r="I39" s="53"/>
       <c r="N39" s="43"/>
     </row>
-    <row r="40" spans="5:14" outlineLevel="1">
+    <row r="40" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" t="s">
         <v>171</v>
@@ -9636,7 +9749,7 @@
       <c r="I40" s="53"/>
       <c r="N40" s="43"/>
     </row>
-    <row r="41" spans="5:14" outlineLevel="1">
+    <row r="41" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F41" t="s">
         <v>172</v>
       </c>
@@ -9647,7 +9760,7 @@
       <c r="I41" s="53"/>
       <c r="N41" s="43"/>
     </row>
-    <row r="42" spans="5:14" outlineLevel="1">
+    <row r="42" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F42" t="s">
         <v>173</v>
       </c>
@@ -9658,7 +9771,7 @@
       <c r="I42" s="53"/>
       <c r="N42" s="43"/>
     </row>
-    <row r="43" spans="5:14" outlineLevel="1">
+    <row r="43" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F43" t="s">
         <v>174</v>
       </c>
@@ -9669,7 +9782,7 @@
       <c r="I43" s="53"/>
       <c r="N43" s="43"/>
     </row>
-    <row r="44" spans="5:14" outlineLevel="1">
+    <row r="44" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="E44" s="2"/>
       <c r="F44" t="s">
         <v>175</v>
@@ -9681,7 +9794,7 @@
       <c r="I44" s="53"/>
       <c r="N44" s="43"/>
     </row>
-    <row r="45" spans="5:14" outlineLevel="1">
+    <row r="45" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F45" t="s">
         <v>176</v>
       </c>
@@ -9692,7 +9805,7 @@
       <c r="I45" s="53"/>
       <c r="N45" s="43"/>
     </row>
-    <row r="46" spans="5:14" outlineLevel="1">
+    <row r="46" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F46" t="s">
         <v>177</v>
       </c>
@@ -9703,7 +9816,7 @@
       <c r="I46" s="53"/>
       <c r="N46" s="43"/>
     </row>
-    <row r="47" spans="5:14" outlineLevel="1">
+    <row r="47" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F47" t="s">
         <v>178</v>
       </c>
@@ -9714,7 +9827,7 @@
       <c r="I47" s="53"/>
       <c r="N47" s="43"/>
     </row>
-    <row r="48" spans="5:14" outlineLevel="1">
+    <row r="48" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F48" t="s">
         <v>154</v>
       </c>
@@ -9725,7 +9838,7 @@
       <c r="I48" s="53"/>
       <c r="N48" s="43"/>
     </row>
-    <row r="49" spans="6:14" outlineLevel="1">
+    <row r="49" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F49" t="s">
         <v>179</v>
       </c>
@@ -9736,7 +9849,7 @@
       <c r="I49" s="53"/>
       <c r="N49" s="43"/>
     </row>
-    <row r="50" spans="6:14" outlineLevel="1">
+    <row r="50" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F50" t="s">
         <v>180</v>
       </c>
@@ -9747,7 +9860,7 @@
       <c r="I50" s="53"/>
       <c r="N50" s="43"/>
     </row>
-    <row r="51" spans="6:14" outlineLevel="1">
+    <row r="51" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F51" t="s">
         <v>181</v>
       </c>
@@ -9758,7 +9871,7 @@
       <c r="I51" s="53"/>
       <c r="N51" s="43"/>
     </row>
-    <row r="52" spans="6:14" outlineLevel="1">
+    <row r="52" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F52" t="s">
         <v>157</v>
       </c>
@@ -9769,7 +9882,7 @@
       <c r="I52" s="53"/>
       <c r="N52" s="43"/>
     </row>
-    <row r="53" spans="6:14" outlineLevel="1">
+    <row r="53" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F53" t="s">
         <v>182</v>
       </c>
@@ -9780,7 +9893,7 @@
       <c r="I53" s="53"/>
       <c r="N53" s="43"/>
     </row>
-    <row r="54" spans="6:14" outlineLevel="1">
+    <row r="54" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F54" t="s">
         <v>183</v>
       </c>
@@ -9791,7 +9904,7 @@
       <c r="I54" s="53"/>
       <c r="N54" s="43"/>
     </row>
-    <row r="55" spans="6:14" outlineLevel="1">
+    <row r="55" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F55" t="s">
         <v>184</v>
       </c>
@@ -9802,7 +9915,7 @@
       <c r="I55" s="53"/>
       <c r="N55" s="43"/>
     </row>
-    <row r="56" spans="6:14">
+    <row r="56" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F56" t="s">
         <v>185</v>
       </c>
@@ -9813,7 +9926,7 @@
       <c r="I56" s="53"/>
       <c r="N56" s="43"/>
     </row>
-    <row r="57" spans="6:14">
+    <row r="57" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F57" t="s">
         <v>154</v>
       </c>
@@ -9824,7 +9937,7 @@
       <c r="I57" s="53"/>
       <c r="N57" s="43"/>
     </row>
-    <row r="58" spans="6:14">
+    <row r="58" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F58" t="s">
         <v>157</v>
       </c>
@@ -9835,7 +9948,7 @@
       <c r="I58" s="53"/>
       <c r="N58" s="43"/>
     </row>
-    <row r="59" spans="6:14">
+    <row r="59" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F59" t="s">
         <v>186</v>
       </c>
@@ -9845,7 +9958,7 @@
       <c r="H59" s="53"/>
       <c r="I59" s="53"/>
     </row>
-    <row r="60" spans="6:14">
+    <row r="60" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F60" t="s">
         <v>187</v>
       </c>
@@ -9855,7 +9968,7 @@
       <c r="H60" s="53"/>
       <c r="I60" s="53"/>
     </row>
-    <row r="61" spans="6:14">
+    <row r="61" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F61" t="s">
         <v>188</v>
       </c>
@@ -9865,7 +9978,7 @@
       <c r="H61" s="53"/>
       <c r="I61" s="53"/>
     </row>
-    <row r="62" spans="6:14">
+    <row r="62" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F62" t="s">
         <v>189</v>
       </c>
@@ -9875,7 +9988,7 @@
       <c r="H62" s="53"/>
       <c r="I62" s="53"/>
     </row>
-    <row r="63" spans="6:14">
+    <row r="63" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F63" t="s">
         <v>170</v>
       </c>
@@ -9885,12 +9998,12 @@
       <c r="H63" s="53"/>
       <c r="I63" s="53"/>
     </row>
-    <row r="64" spans="6:14">
+    <row r="64" spans="6:14" x14ac:dyDescent="0.25">
       <c r="G64" s="53"/>
       <c r="H64" s="53"/>
       <c r="I64" s="53"/>
     </row>
-    <row r="65" spans="6:9">
+    <row r="65" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F65" t="s">
         <v>190</v>
       </c>
@@ -9900,7 +10013,7 @@
       <c r="H65" s="53"/>
       <c r="I65" s="53"/>
     </row>
-    <row r="66" spans="6:9">
+    <row r="66" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F66" t="s">
         <v>191</v>
       </c>
@@ -9910,7 +10023,7 @@
       <c r="H66" s="53"/>
       <c r="I66" s="53"/>
     </row>
-    <row r="67" spans="6:9">
+    <row r="67" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F67" t="s">
         <v>192</v>
       </c>
@@ -9920,7 +10033,7 @@
       <c r="H67" s="53"/>
       <c r="I67" s="53"/>
     </row>
-    <row r="68" spans="6:9">
+    <row r="68" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F68" t="s">
         <v>157</v>
       </c>
@@ -9930,7 +10043,7 @@
       <c r="H68" s="53"/>
       <c r="I68" s="53"/>
     </row>
-    <row r="69" spans="6:9">
+    <row r="69" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F69" t="s">
         <v>193</v>
       </c>
@@ -9940,7 +10053,7 @@
       <c r="H69" s="53"/>
       <c r="I69" s="53"/>
     </row>
-    <row r="70" spans="6:9">
+    <row r="70" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F70" t="s">
         <v>194</v>
       </c>
@@ -9950,7 +10063,7 @@
       <c r="H70" s="53"/>
       <c r="I70" s="53"/>
     </row>
-    <row r="71" spans="6:9">
+    <row r="71" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F71" t="s">
         <v>195</v>
       </c>
@@ -9960,7 +10073,7 @@
       <c r="H71" s="53"/>
       <c r="I71" s="53"/>
     </row>
-    <row r="72" spans="6:9">
+    <row r="72" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F72" t="s">
         <v>196</v>
       </c>
@@ -9970,12 +10083,12 @@
       <c r="H72" s="53"/>
       <c r="I72" s="53"/>
     </row>
-    <row r="73" spans="6:9">
+    <row r="73" spans="6:9" x14ac:dyDescent="0.25">
       <c r="G73" s="53"/>
       <c r="H73" s="53"/>
       <c r="I73" s="53"/>
     </row>
-    <row r="74" spans="6:9">
+    <row r="74" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F74" t="s">
         <v>154</v>
       </c>
@@ -9985,7 +10098,7 @@
       <c r="H74" s="53"/>
       <c r="I74" s="53"/>
     </row>
-    <row r="75" spans="6:9">
+    <row r="75" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F75" t="s">
         <v>197</v>
       </c>
@@ -9995,7 +10108,7 @@
       <c r="H75" s="53"/>
       <c r="I75" s="53"/>
     </row>
-    <row r="76" spans="6:9">
+    <row r="76" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F76" t="s">
         <v>198</v>
       </c>
@@ -10005,7 +10118,7 @@
       <c r="H76" s="53"/>
       <c r="I76" s="53"/>
     </row>
-    <row r="77" spans="6:9">
+    <row r="77" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F77" t="s">
         <v>199</v>
       </c>
@@ -10015,7 +10128,7 @@
       <c r="H77" s="53"/>
       <c r="I77" s="53"/>
     </row>
-    <row r="78" spans="6:9" ht="14.25" customHeight="1">
+    <row r="78" spans="6:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F78" t="s">
         <v>157</v>
       </c>
@@ -10025,7 +10138,7 @@
       <c r="H78" s="53"/>
       <c r="I78" s="53"/>
     </row>
-    <row r="79" spans="6:9">
+    <row r="79" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F79" t="s">
         <v>200</v>
       </c>
@@ -10035,7 +10148,7 @@
       <c r="H79" s="53"/>
       <c r="I79" s="53"/>
     </row>
-    <row r="80" spans="6:9">
+    <row r="80" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F80" t="s">
         <v>201</v>
       </c>
@@ -10045,7 +10158,7 @@
       <c r="H80" s="53"/>
       <c r="I80" s="53"/>
     </row>
-    <row r="81" spans="6:9">
+    <row r="81" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F81" t="s">
         <v>202</v>
       </c>
@@ -10055,7 +10168,7 @@
       <c r="H81" s="53"/>
       <c r="I81" s="53"/>
     </row>
-    <row r="82" spans="6:9">
+    <row r="82" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F82" t="s">
         <v>203</v>
       </c>
@@ -10065,7 +10178,7 @@
       <c r="H82" s="53"/>
       <c r="I82" s="53"/>
     </row>
-    <row r="83" spans="6:9">
+    <row r="83" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F83" t="s">
         <v>204</v>
       </c>
@@ -10075,7 +10188,7 @@
       <c r="H83" s="53"/>
       <c r="I83" s="53"/>
     </row>
-    <row r="84" spans="6:9">
+    <row r="84" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F84" t="s">
         <v>196</v>
       </c>
@@ -10085,7 +10198,7 @@
       <c r="H84" s="53"/>
       <c r="I84" s="53"/>
     </row>
-    <row r="85" spans="6:9">
+    <row r="85" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F85" t="s">
         <v>195</v>
       </c>
@@ -10095,7 +10208,7 @@
       <c r="H85" s="53"/>
       <c r="I85" s="53"/>
     </row>
-    <row r="86" spans="6:9">
+    <row r="86" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F86" t="s">
         <v>205</v>
       </c>
@@ -10105,7 +10218,7 @@
       <c r="H86" s="53"/>
       <c r="I86" s="53"/>
     </row>
-    <row r="87" spans="6:9">
+    <row r="87" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F87" t="s">
         <v>206</v>
       </c>
@@ -10115,7 +10228,7 @@
       <c r="H87" s="53"/>
       <c r="I87" s="53"/>
     </row>
-    <row r="88" spans="6:9">
+    <row r="88" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F88" t="s">
         <v>207</v>
       </c>
@@ -10125,7 +10238,7 @@
       <c r="H88" s="53"/>
       <c r="I88" s="53"/>
     </row>
-    <row r="89" spans="6:9">
+    <row r="89" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F89" t="s">
         <v>208</v>
       </c>
@@ -10135,7 +10248,7 @@
       <c r="H89" s="53"/>
       <c r="I89" s="53"/>
     </row>
-    <row r="90" spans="6:9">
+    <row r="90" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F90" t="s">
         <v>209</v>
       </c>
@@ -10145,7 +10258,7 @@
       <c r="H90" s="53"/>
       <c r="I90" s="53"/>
     </row>
-    <row r="91" spans="6:9">
+    <row r="91" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F91" t="s">
         <v>210</v>
       </c>
@@ -10155,7 +10268,7 @@
       <c r="H91" s="53"/>
       <c r="I91" s="53"/>
     </row>
-    <row r="92" spans="6:9">
+    <row r="92" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F92" t="s">
         <v>211</v>
       </c>
@@ -10165,7 +10278,7 @@
       <c r="H92" s="53"/>
       <c r="I92" s="53"/>
     </row>
-    <row r="93" spans="6:9">
+    <row r="93" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F93" t="s">
         <v>212</v>
       </c>
@@ -10175,7 +10288,7 @@
       <c r="H93" s="53"/>
       <c r="I93" s="53"/>
     </row>
-    <row r="94" spans="6:9">
+    <row r="94" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F94" t="s">
         <v>213</v>
       </c>
@@ -10185,7 +10298,7 @@
       <c r="H94" s="53"/>
       <c r="I94" s="53"/>
     </row>
-    <row r="95" spans="6:9">
+    <row r="95" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F95" t="s">
         <v>214</v>
       </c>
@@ -10195,7 +10308,7 @@
       <c r="H95" s="53"/>
       <c r="I95" s="53"/>
     </row>
-    <row r="96" spans="6:9">
+    <row r="96" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F96" t="s">
         <v>215</v>
       </c>
@@ -10205,7 +10318,7 @@
       <c r="H96" s="53"/>
       <c r="I96" s="53"/>
     </row>
-    <row r="97" spans="2:9">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>216</v>
       </c>
@@ -10222,7 +10335,7 @@
       <c r="H97" s="53"/>
       <c r="I97" s="53"/>
     </row>
-    <row r="98" spans="2:9">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>154</v>
       </c>
@@ -10239,7 +10352,7 @@
       <c r="H98" s="53"/>
       <c r="I98" s="53"/>
     </row>
-    <row r="99" spans="2:9">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>219</v>
       </c>
@@ -10254,7 +10367,7 @@
       <c r="H99" s="53"/>
       <c r="I99" s="53"/>
     </row>
-    <row r="100" spans="2:9">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>221</v>
       </c>
@@ -10273,7 +10386,7 @@
       <c r="H100" s="53"/>
       <c r="I100" s="53"/>
     </row>
-    <row r="101" spans="2:9">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>223</v>
       </c>
@@ -10290,7 +10403,7 @@
       <c r="H101" s="53"/>
       <c r="I101" s="53"/>
     </row>
-    <row r="102" spans="2:9">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>225</v>
       </c>
@@ -10307,7 +10420,7 @@
       <c r="H102" s="53"/>
       <c r="I102" s="53"/>
     </row>
-    <row r="103" spans="2:9">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C103" s="53"/>
       <c r="D103" s="53"/>
       <c r="F103" t="s">
@@ -10319,7 +10432,7 @@
       <c r="H103" s="53"/>
       <c r="I103" s="53"/>
     </row>
-    <row r="104" spans="2:9">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>227</v>
       </c>
@@ -10338,7 +10451,7 @@
       <c r="H104" s="53"/>
       <c r="I104" s="53"/>
     </row>
-    <row r="105" spans="2:9">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>228</v>
       </c>
@@ -10357,7 +10470,7 @@
       <c r="H105" s="53"/>
       <c r="I105" s="53"/>
     </row>
-    <row r="106" spans="2:9">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>230</v>
       </c>
@@ -10371,14 +10484,14 @@
       <c r="H106" s="53"/>
       <c r="I106" s="53"/>
     </row>
-    <row r="107" spans="2:9">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C107" s="53"/>
       <c r="D107" s="53"/>
       <c r="G107" s="53"/>
       <c r="H107" s="53"/>
       <c r="I107" s="53"/>
     </row>
-    <row r="108" spans="2:9">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>231</v>
       </c>
@@ -10390,14 +10503,14 @@
       <c r="H108" s="53"/>
       <c r="I108" s="53"/>
     </row>
-    <row r="109" spans="2:9">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C109" s="53"/>
       <c r="D109" s="53"/>
       <c r="G109" s="53"/>
       <c r="H109" s="53"/>
       <c r="I109" s="53"/>
     </row>
-    <row r="110" spans="2:9">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>232</v>
       </c>
@@ -10411,7 +10524,7 @@
       <c r="H110" s="53"/>
       <c r="I110" s="53"/>
     </row>
-    <row r="111" spans="2:9">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>233</v>
       </c>
@@ -10425,7 +10538,7 @@
       <c r="H111" s="53"/>
       <c r="I111" s="53"/>
     </row>
-    <row r="112" spans="2:9">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>234</v>
       </c>
@@ -10437,7 +10550,7 @@
       <c r="H112" s="53"/>
       <c r="I112" s="53"/>
     </row>
-    <row r="113" spans="2:9">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>235</v>
       </c>
@@ -10451,7 +10564,7 @@
       <c r="H113" s="53"/>
       <c r="I113" s="53"/>
     </row>
-    <row r="114" spans="2:9">
+    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>236</v>
       </c>
@@ -10465,1185 +10578,1185 @@
       <c r="H114" s="53"/>
       <c r="I114" s="53"/>
     </row>
-    <row r="115" spans="2:9">
+    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C115" s="53"/>
       <c r="G115" s="53"/>
       <c r="H115" s="53"/>
       <c r="I115" s="53"/>
     </row>
-    <row r="116" spans="2:9">
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C116" s="53"/>
       <c r="G116" s="53"/>
       <c r="H116" s="53"/>
       <c r="I116" s="53"/>
     </row>
-    <row r="117" spans="2:9">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C117" s="53"/>
       <c r="G117" s="53"/>
       <c r="H117" s="53"/>
       <c r="I117" s="53"/>
     </row>
-    <row r="118" spans="2:9">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C118" s="53"/>
       <c r="G118" s="53"/>
       <c r="H118" s="53"/>
       <c r="I118" s="53"/>
     </row>
-    <row r="119" spans="2:9">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C119" s="53"/>
       <c r="G119" s="53"/>
       <c r="H119" s="53"/>
       <c r="I119" s="53"/>
     </row>
-    <row r="120" spans="2:9">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C120" s="53"/>
       <c r="G120" s="53"/>
       <c r="H120" s="53"/>
       <c r="I120" s="53"/>
     </row>
-    <row r="121" spans="2:9">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C121" s="53"/>
       <c r="G121" s="53"/>
       <c r="H121" s="53"/>
       <c r="I121" s="53"/>
     </row>
-    <row r="122" spans="2:9">
+    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G122" s="53"/>
       <c r="H122" s="72"/>
       <c r="I122" s="53"/>
     </row>
-    <row r="123" spans="2:9">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G123" s="53"/>
       <c r="H123" s="72"/>
       <c r="I123" s="53"/>
     </row>
-    <row r="124" spans="2:9">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G124" s="53"/>
       <c r="H124" s="72"/>
       <c r="I124" s="53"/>
     </row>
-    <row r="125" spans="2:9">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G125" s="53"/>
       <c r="H125" s="72"/>
       <c r="I125" s="53"/>
     </row>
-    <row r="126" spans="2:9">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G126" s="53"/>
       <c r="H126" s="72"/>
       <c r="I126" s="53"/>
     </row>
-    <row r="127" spans="2:9">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G127" s="53"/>
       <c r="H127" s="72"/>
       <c r="I127" s="53"/>
     </row>
-    <row r="128" spans="2:9">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G128" s="53"/>
       <c r="H128" s="72"/>
       <c r="I128" s="53"/>
     </row>
-    <row r="129" spans="7:9">
+    <row r="129" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G129" s="53"/>
       <c r="H129" s="53"/>
       <c r="I129" s="53"/>
     </row>
-    <row r="130" spans="7:9">
+    <row r="130" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G130" s="53"/>
       <c r="H130" s="53"/>
       <c r="I130" s="53"/>
     </row>
-    <row r="131" spans="7:9">
+    <row r="131" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G131" s="53"/>
       <c r="H131" s="53"/>
       <c r="I131" s="53"/>
     </row>
-    <row r="132" spans="7:9">
+    <row r="132" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G132" s="53"/>
       <c r="H132" s="53"/>
       <c r="I132" s="53"/>
     </row>
-    <row r="133" spans="7:9">
+    <row r="133" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G133" s="53"/>
       <c r="H133" s="53"/>
       <c r="I133" s="53"/>
     </row>
-    <row r="134" spans="7:9">
+    <row r="134" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G134" s="53"/>
       <c r="H134" s="53"/>
       <c r="I134" s="53"/>
     </row>
-    <row r="135" spans="7:9">
+    <row r="135" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G135" s="53"/>
       <c r="H135" s="53"/>
       <c r="I135" s="53"/>
     </row>
-    <row r="136" spans="7:9">
+    <row r="136" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G136" s="53"/>
       <c r="H136" s="53"/>
       <c r="I136" s="53"/>
     </row>
-    <row r="137" spans="7:9">
+    <row r="137" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G137" s="53"/>
       <c r="H137" s="53"/>
       <c r="I137" s="53"/>
     </row>
-    <row r="138" spans="7:9">
+    <row r="138" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G138" s="53"/>
       <c r="H138" s="53"/>
       <c r="I138" s="53"/>
     </row>
-    <row r="139" spans="7:9">
+    <row r="139" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G139" s="53"/>
       <c r="H139" s="53"/>
       <c r="I139" s="53"/>
     </row>
-    <row r="140" spans="7:9">
+    <row r="140" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G140" s="53"/>
       <c r="H140" s="53"/>
       <c r="I140" s="53"/>
     </row>
-    <row r="141" spans="7:9">
+    <row r="141" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G141" s="53"/>
       <c r="H141" s="53"/>
       <c r="I141" s="53"/>
     </row>
-    <row r="142" spans="7:9">
+    <row r="142" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G142" s="53"/>
       <c r="H142" s="53"/>
       <c r="I142" s="53"/>
     </row>
-    <row r="143" spans="7:9">
+    <row r="143" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G143" s="53"/>
       <c r="H143" s="53"/>
       <c r="I143" s="53"/>
     </row>
-    <row r="144" spans="7:9">
+    <row r="144" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G144" s="53"/>
       <c r="H144" s="53"/>
       <c r="I144" s="53"/>
     </row>
-    <row r="145" spans="7:9">
+    <row r="145" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G145" s="53"/>
       <c r="H145" s="53"/>
       <c r="I145" s="53"/>
     </row>
-    <row r="146" spans="7:9">
+    <row r="146" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G146" s="53"/>
       <c r="H146" s="53"/>
       <c r="I146" s="53"/>
     </row>
-    <row r="147" spans="7:9">
+    <row r="147" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G147" s="53"/>
       <c r="H147" s="53"/>
       <c r="I147" s="53"/>
     </row>
-    <row r="148" spans="7:9">
+    <row r="148" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G148" s="53"/>
       <c r="H148" s="53"/>
       <c r="I148" s="53"/>
     </row>
-    <row r="149" spans="7:9">
+    <row r="149" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G149" s="53"/>
       <c r="H149" s="53"/>
       <c r="I149" s="53"/>
     </row>
-    <row r="150" spans="7:9">
+    <row r="150" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G150" s="53"/>
       <c r="H150" s="53"/>
       <c r="I150" s="53"/>
     </row>
-    <row r="151" spans="7:9">
+    <row r="151" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G151" s="53"/>
       <c r="H151" s="53"/>
       <c r="I151" s="53"/>
     </row>
-    <row r="152" spans="7:9">
+    <row r="152" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G152" s="53"/>
       <c r="H152" s="53"/>
       <c r="I152" s="53"/>
     </row>
-    <row r="153" spans="7:9">
+    <row r="153" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G153" s="53"/>
       <c r="H153" s="53"/>
       <c r="I153" s="53"/>
     </row>
-    <row r="154" spans="7:9">
+    <row r="154" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G154" s="53"/>
       <c r="H154" s="53"/>
       <c r="I154" s="53"/>
     </row>
-    <row r="155" spans="7:9">
+    <row r="155" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G155" s="53"/>
       <c r="H155" s="53"/>
       <c r="I155" s="53"/>
     </row>
-    <row r="156" spans="7:9">
+    <row r="156" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G156" s="53"/>
       <c r="H156" s="53"/>
       <c r="I156" s="53"/>
     </row>
-    <row r="157" spans="7:9">
+    <row r="157" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G157" s="53"/>
       <c r="H157" s="53"/>
       <c r="I157" s="53"/>
     </row>
-    <row r="158" spans="7:9">
+    <row r="158" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G158" s="53"/>
       <c r="H158" s="53"/>
       <c r="I158" s="53"/>
     </row>
-    <row r="159" spans="7:9">
+    <row r="159" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G159" s="53"/>
       <c r="H159" s="53"/>
       <c r="I159" s="53"/>
     </row>
-    <row r="160" spans="7:9">
+    <row r="160" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G160" s="53"/>
       <c r="H160" s="53"/>
       <c r="I160" s="53"/>
     </row>
-    <row r="161" spans="7:9">
+    <row r="161" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G161" s="53"/>
       <c r="H161" s="53"/>
       <c r="I161" s="53"/>
     </row>
-    <row r="162" spans="7:9">
+    <row r="162" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G162" s="53"/>
       <c r="H162" s="53"/>
       <c r="I162" s="53"/>
     </row>
-    <row r="163" spans="7:9">
+    <row r="163" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G163" s="53"/>
       <c r="H163" s="53"/>
       <c r="I163" s="53"/>
     </row>
-    <row r="164" spans="7:9">
+    <row r="164" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G164" s="53"/>
       <c r="H164" s="53"/>
       <c r="I164" s="53"/>
     </row>
-    <row r="165" spans="7:9">
+    <row r="165" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G165" s="53"/>
       <c r="H165" s="53"/>
       <c r="I165" s="53"/>
     </row>
-    <row r="166" spans="7:9">
+    <row r="166" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G166" s="53"/>
       <c r="H166" s="53"/>
       <c r="I166" s="53"/>
     </row>
-    <row r="167" spans="7:9">
+    <row r="167" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G167" s="53"/>
       <c r="H167" s="53"/>
       <c r="I167" s="53"/>
     </row>
-    <row r="168" spans="7:9">
+    <row r="168" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G168" s="53"/>
       <c r="H168" s="53"/>
       <c r="I168" s="53"/>
     </row>
-    <row r="169" spans="7:9">
+    <row r="169" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G169" s="53"/>
       <c r="H169" s="53"/>
       <c r="I169" s="53"/>
     </row>
-    <row r="170" spans="7:9">
+    <row r="170" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G170" s="53"/>
       <c r="H170" s="53"/>
       <c r="I170" s="53"/>
     </row>
-    <row r="171" spans="7:9">
+    <row r="171" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G171" s="53"/>
       <c r="H171" s="53"/>
       <c r="I171" s="53"/>
     </row>
-    <row r="172" spans="7:9">
+    <row r="172" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G172" s="53"/>
       <c r="H172" s="53"/>
       <c r="I172" s="53"/>
     </row>
-    <row r="173" spans="7:9">
+    <row r="173" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G173" s="53"/>
       <c r="H173" s="53"/>
       <c r="I173" s="53"/>
     </row>
-    <row r="174" spans="7:9">
+    <row r="174" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G174" s="53"/>
       <c r="H174" s="53"/>
       <c r="I174" s="53"/>
     </row>
-    <row r="175" spans="7:9">
+    <row r="175" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G175" s="53"/>
       <c r="H175" s="53"/>
       <c r="I175" s="53"/>
     </row>
-    <row r="176" spans="7:9">
+    <row r="176" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G176" s="53"/>
       <c r="H176" s="53"/>
       <c r="I176" s="53"/>
     </row>
-    <row r="177" spans="7:9">
+    <row r="177" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G177" s="53"/>
       <c r="H177" s="53"/>
       <c r="I177" s="53"/>
     </row>
-    <row r="178" spans="7:9">
+    <row r="178" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G178" s="53"/>
       <c r="H178" s="53"/>
       <c r="I178" s="53"/>
     </row>
-    <row r="179" spans="7:9">
+    <row r="179" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G179" s="53"/>
       <c r="H179" s="53"/>
       <c r="I179" s="53"/>
     </row>
-    <row r="180" spans="7:9">
+    <row r="180" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G180" s="53"/>
       <c r="H180" s="53"/>
       <c r="I180" s="53"/>
     </row>
-    <row r="181" spans="7:9">
+    <row r="181" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G181" s="53"/>
       <c r="H181" s="53"/>
       <c r="I181" s="53"/>
     </row>
-    <row r="182" spans="7:9">
+    <row r="182" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G182" s="53"/>
       <c r="H182" s="53"/>
       <c r="I182" s="53"/>
     </row>
-    <row r="183" spans="7:9">
+    <row r="183" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G183" s="53"/>
       <c r="H183" s="53"/>
       <c r="I183" s="53"/>
     </row>
-    <row r="184" spans="7:9">
+    <row r="184" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G184" s="53"/>
       <c r="H184" s="53"/>
       <c r="I184" s="53"/>
     </row>
-    <row r="185" spans="7:9">
+    <row r="185" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G185" s="53"/>
       <c r="H185" s="53"/>
       <c r="I185" s="53"/>
     </row>
-    <row r="186" spans="7:9">
+    <row r="186" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G186" s="53"/>
       <c r="H186" s="53"/>
       <c r="I186" s="53"/>
     </row>
-    <row r="187" spans="7:9">
+    <row r="187" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G187" s="53"/>
       <c r="H187" s="53"/>
       <c r="I187" s="53"/>
     </row>
-    <row r="188" spans="7:9">
+    <row r="188" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G188" s="53"/>
       <c r="H188" s="53"/>
       <c r="I188" s="53"/>
     </row>
-    <row r="189" spans="7:9">
+    <row r="189" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G189" s="53"/>
       <c r="H189" s="53"/>
       <c r="I189" s="53"/>
     </row>
-    <row r="190" spans="7:9">
+    <row r="190" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G190" s="53"/>
       <c r="H190" s="53"/>
       <c r="I190" s="53"/>
     </row>
-    <row r="191" spans="7:9">
+    <row r="191" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G191" s="53"/>
       <c r="H191" s="53"/>
       <c r="I191" s="53"/>
     </row>
-    <row r="192" spans="7:9">
+    <row r="192" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G192" s="53"/>
       <c r="H192" s="53"/>
       <c r="I192" s="53"/>
     </row>
-    <row r="193" spans="7:9">
+    <row r="193" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G193" s="53"/>
       <c r="H193" s="53"/>
       <c r="I193" s="53"/>
     </row>
-    <row r="194" spans="7:9">
+    <row r="194" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G194" s="53"/>
       <c r="H194" s="53"/>
       <c r="I194" s="53"/>
     </row>
-    <row r="195" spans="7:9">
+    <row r="195" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G195" s="53"/>
       <c r="H195" s="53"/>
       <c r="I195" s="53"/>
     </row>
-    <row r="196" spans="7:9">
+    <row r="196" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G196" s="53"/>
       <c r="H196" s="53"/>
       <c r="I196" s="53"/>
     </row>
-    <row r="197" spans="7:9">
+    <row r="197" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G197" s="53"/>
       <c r="H197" s="53"/>
       <c r="I197" s="53"/>
     </row>
-    <row r="198" spans="7:9">
+    <row r="198" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G198" s="53"/>
       <c r="H198" s="53"/>
       <c r="I198" s="53"/>
     </row>
-    <row r="199" spans="7:9">
+    <row r="199" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G199" s="53"/>
       <c r="H199" s="53"/>
       <c r="I199" s="53"/>
     </row>
-    <row r="200" spans="7:9">
+    <row r="200" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G200" s="53"/>
       <c r="H200" s="53"/>
       <c r="I200" s="53"/>
     </row>
-    <row r="201" spans="7:9">
+    <row r="201" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G201" s="53"/>
       <c r="H201" s="53"/>
       <c r="I201" s="53"/>
     </row>
-    <row r="202" spans="7:9">
+    <row r="202" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G202" s="53"/>
       <c r="H202" s="53"/>
       <c r="I202" s="53"/>
     </row>
-    <row r="203" spans="7:9">
+    <row r="203" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G203" s="53"/>
       <c r="H203" s="53"/>
       <c r="I203" s="53"/>
     </row>
-    <row r="204" spans="7:9">
+    <row r="204" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G204" s="53"/>
       <c r="H204" s="53"/>
       <c r="I204" s="53"/>
     </row>
-    <row r="205" spans="7:9">
+    <row r="205" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G205" s="53"/>
       <c r="H205" s="53"/>
       <c r="I205" s="53"/>
     </row>
-    <row r="206" spans="7:9">
+    <row r="206" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G206" s="53"/>
       <c r="H206" s="53"/>
       <c r="I206" s="53"/>
     </row>
-    <row r="207" spans="7:9">
+    <row r="207" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G207" s="53"/>
       <c r="H207" s="53"/>
       <c r="I207" s="53"/>
     </row>
-    <row r="208" spans="7:9">
+    <row r="208" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G208" s="53"/>
       <c r="H208" s="53"/>
       <c r="I208" s="53"/>
     </row>
-    <row r="209" spans="7:9">
+    <row r="209" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G209" s="53"/>
       <c r="H209" s="53"/>
       <c r="I209" s="53"/>
     </row>
-    <row r="210" spans="7:9">
+    <row r="210" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G210" s="53"/>
       <c r="H210" s="53"/>
       <c r="I210" s="53"/>
     </row>
-    <row r="211" spans="7:9">
+    <row r="211" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G211" s="53"/>
       <c r="H211" s="53"/>
       <c r="I211" s="53"/>
     </row>
-    <row r="212" spans="7:9">
+    <row r="212" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G212" s="53"/>
       <c r="H212" s="53"/>
       <c r="I212" s="53"/>
     </row>
-    <row r="213" spans="7:9">
+    <row r="213" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G213" s="53"/>
       <c r="H213" s="53"/>
       <c r="I213" s="53"/>
     </row>
-    <row r="214" spans="7:9">
+    <row r="214" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G214" s="53"/>
       <c r="H214" s="53"/>
       <c r="I214" s="53"/>
     </row>
-    <row r="215" spans="7:9">
+    <row r="215" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G215" s="53"/>
       <c r="H215" s="53"/>
       <c r="I215" s="53"/>
     </row>
-    <row r="216" spans="7:9">
+    <row r="216" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G216" s="53"/>
       <c r="H216" s="53"/>
       <c r="I216" s="53"/>
     </row>
-    <row r="217" spans="7:9">
+    <row r="217" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G217" s="53"/>
       <c r="H217" s="53"/>
       <c r="I217" s="53"/>
     </row>
-    <row r="218" spans="7:9">
+    <row r="218" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G218" s="53"/>
       <c r="H218" s="53"/>
       <c r="I218" s="53"/>
     </row>
-    <row r="219" spans="7:9">
+    <row r="219" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G219" s="53"/>
       <c r="H219" s="53"/>
       <c r="I219" s="53"/>
     </row>
-    <row r="220" spans="7:9">
+    <row r="220" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G220" s="53"/>
       <c r="H220" s="53"/>
       <c r="I220" s="53"/>
     </row>
-    <row r="221" spans="7:9">
+    <row r="221" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G221" s="53"/>
       <c r="H221" s="53"/>
       <c r="I221" s="53"/>
     </row>
-    <row r="222" spans="7:9">
+    <row r="222" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G222" s="53"/>
       <c r="H222" s="53"/>
       <c r="I222" s="53"/>
     </row>
-    <row r="223" spans="7:9">
+    <row r="223" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G223" s="53"/>
       <c r="H223" s="53"/>
       <c r="I223" s="53"/>
     </row>
-    <row r="224" spans="7:9">
+    <row r="224" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G224" s="53"/>
       <c r="H224" s="53"/>
       <c r="I224" s="53"/>
     </row>
-    <row r="225" spans="7:9">
+    <row r="225" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G225" s="53"/>
       <c r="H225" s="53"/>
       <c r="I225" s="53"/>
     </row>
-    <row r="226" spans="7:9">
+    <row r="226" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G226" s="53"/>
       <c r="H226" s="53"/>
       <c r="I226" s="53"/>
     </row>
-    <row r="227" spans="7:9">
+    <row r="227" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G227" s="53"/>
       <c r="H227" s="53"/>
       <c r="I227" s="53"/>
     </row>
-    <row r="228" spans="7:9">
+    <row r="228" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G228" s="53"/>
       <c r="H228" s="53"/>
       <c r="I228" s="53"/>
     </row>
-    <row r="229" spans="7:9">
+    <row r="229" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G229" s="53"/>
       <c r="H229" s="53"/>
       <c r="I229" s="53"/>
     </row>
-    <row r="230" spans="7:9">
+    <row r="230" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G230" s="53"/>
       <c r="H230" s="53"/>
       <c r="I230" s="53"/>
     </row>
-    <row r="231" spans="7:9">
+    <row r="231" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G231" s="53"/>
       <c r="H231" s="53"/>
       <c r="I231" s="53"/>
     </row>
-    <row r="232" spans="7:9">
+    <row r="232" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G232" s="53"/>
       <c r="H232" s="53"/>
       <c r="I232" s="53"/>
     </row>
-    <row r="233" spans="7:9">
+    <row r="233" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G233" s="53"/>
       <c r="H233" s="53"/>
       <c r="I233" s="53"/>
     </row>
-    <row r="234" spans="7:9">
+    <row r="234" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G234" s="53"/>
       <c r="H234" s="53"/>
       <c r="I234" s="53"/>
     </row>
-    <row r="235" spans="7:9">
+    <row r="235" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G235" s="53"/>
       <c r="H235" s="53"/>
       <c r="I235" s="53"/>
     </row>
-    <row r="236" spans="7:9">
+    <row r="236" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G236" s="53"/>
       <c r="H236" s="53"/>
       <c r="I236" s="53"/>
     </row>
-    <row r="237" spans="7:9">
+    <row r="237" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G237" s="53"/>
       <c r="H237" s="53"/>
       <c r="I237" s="53"/>
     </row>
-    <row r="238" spans="7:9">
+    <row r="238" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G238" s="53"/>
       <c r="H238" s="53"/>
       <c r="I238" s="53"/>
     </row>
-    <row r="239" spans="7:9">
+    <row r="239" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G239" s="53"/>
       <c r="H239" s="53"/>
       <c r="I239" s="53"/>
     </row>
-    <row r="240" spans="7:9">
+    <row r="240" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G240" s="53"/>
       <c r="H240" s="53"/>
       <c r="I240" s="53"/>
     </row>
-    <row r="241" spans="7:9">
+    <row r="241" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G241" s="53"/>
       <c r="H241" s="53"/>
       <c r="I241" s="53"/>
     </row>
-    <row r="242" spans="7:9">
+    <row r="242" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G242" s="53"/>
       <c r="H242" s="53"/>
       <c r="I242" s="53"/>
     </row>
-    <row r="243" spans="7:9">
+    <row r="243" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G243" s="53"/>
       <c r="H243" s="53"/>
       <c r="I243" s="53"/>
     </row>
-    <row r="244" spans="7:9">
+    <row r="244" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G244" s="53"/>
       <c r="H244" s="53"/>
       <c r="I244" s="53"/>
     </row>
-    <row r="245" spans="7:9">
+    <row r="245" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G245" s="53"/>
       <c r="H245" s="53"/>
       <c r="I245" s="53"/>
     </row>
-    <row r="246" spans="7:9">
+    <row r="246" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G246" s="53"/>
       <c r="H246" s="53"/>
       <c r="I246" s="53"/>
     </row>
-    <row r="247" spans="7:9">
+    <row r="247" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G247" s="53"/>
       <c r="H247" s="53"/>
       <c r="I247" s="53"/>
     </row>
-    <row r="248" spans="7:9">
+    <row r="248" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G248" s="53"/>
       <c r="H248" s="53"/>
       <c r="I248" s="53"/>
     </row>
-    <row r="249" spans="7:9">
+    <row r="249" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G249" s="53"/>
       <c r="H249" s="53"/>
       <c r="I249" s="53"/>
     </row>
-    <row r="250" spans="7:9">
+    <row r="250" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G250" s="53"/>
       <c r="H250" s="53"/>
       <c r="I250" s="53"/>
     </row>
-    <row r="251" spans="7:9">
+    <row r="251" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G251" s="53"/>
       <c r="H251" s="53"/>
       <c r="I251" s="53"/>
     </row>
-    <row r="252" spans="7:9">
+    <row r="252" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G252" s="53"/>
       <c r="H252" s="53"/>
       <c r="I252" s="53"/>
     </row>
-    <row r="253" spans="7:9">
+    <row r="253" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G253" s="53"/>
       <c r="H253" s="53"/>
       <c r="I253" s="53"/>
     </row>
-    <row r="254" spans="7:9">
+    <row r="254" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G254" s="53"/>
       <c r="H254" s="53"/>
       <c r="I254" s="53"/>
     </row>
-    <row r="255" spans="7:9">
+    <row r="255" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G255" s="53"/>
       <c r="H255" s="53"/>
       <c r="I255" s="53"/>
     </row>
-    <row r="256" spans="7:9">
+    <row r="256" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G256" s="53"/>
       <c r="H256" s="53"/>
       <c r="I256" s="53"/>
     </row>
-    <row r="257" spans="7:9">
+    <row r="257" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G257" s="53"/>
       <c r="H257" s="1"/>
       <c r="I257" s="1"/>
     </row>
-    <row r="258" spans="7:9">
+    <row r="258" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G258" s="53"/>
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>
     </row>
-    <row r="259" spans="7:9">
+    <row r="259" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G259" s="53"/>
       <c r="H259" s="1"/>
       <c r="I259" s="1"/>
     </row>
-    <row r="260" spans="7:9">
+    <row r="260" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G260" s="53"/>
       <c r="H260" s="1"/>
       <c r="I260" s="1"/>
     </row>
-    <row r="261" spans="7:9">
+    <row r="261" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G261" s="53"/>
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
     </row>
-    <row r="262" spans="7:9">
+    <row r="262" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G262" s="53"/>
       <c r="H262" s="1"/>
       <c r="I262" s="1"/>
     </row>
-    <row r="263" spans="7:9">
+    <row r="263" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G263" s="53"/>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
     </row>
-    <row r="264" spans="7:9">
+    <row r="264" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G264" s="53"/>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
     </row>
-    <row r="265" spans="7:9">
+    <row r="265" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G265" s="53"/>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
     </row>
-    <row r="266" spans="7:9">
+    <row r="266" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G266" s="53"/>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
     </row>
-    <row r="267" spans="7:9">
+    <row r="267" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G267" s="53"/>
     </row>
-    <row r="268" spans="7:9">
+    <row r="268" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G268" s="53"/>
     </row>
-    <row r="269" spans="7:9">
+    <row r="269" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G269" s="53"/>
     </row>
-    <row r="270" spans="7:9">
+    <row r="270" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G270" s="53"/>
     </row>
-    <row r="271" spans="7:9">
+    <row r="271" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G271" s="53"/>
     </row>
-    <row r="272" spans="7:9">
+    <row r="272" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G272" s="53"/>
     </row>
-    <row r="273" spans="7:7">
+    <row r="273" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G273" s="53"/>
     </row>
-    <row r="274" spans="7:7">
+    <row r="274" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G274" s="53"/>
     </row>
-    <row r="275" spans="7:7">
+    <row r="275" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G275" s="53"/>
     </row>
-    <row r="276" spans="7:7">
+    <row r="276" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G276" s="53"/>
     </row>
-    <row r="277" spans="7:7">
+    <row r="277" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G277" s="53"/>
     </row>
-    <row r="278" spans="7:7">
+    <row r="278" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G278" s="53"/>
     </row>
-    <row r="279" spans="7:7">
+    <row r="279" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G279" s="53"/>
     </row>
-    <row r="280" spans="7:7">
+    <row r="280" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G280" s="53"/>
     </row>
-    <row r="281" spans="7:7">
+    <row r="281" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G281" s="53"/>
     </row>
-    <row r="282" spans="7:7">
+    <row r="282" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G282" s="53"/>
     </row>
-    <row r="283" spans="7:7">
+    <row r="283" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G283" s="53"/>
     </row>
-    <row r="284" spans="7:7">
+    <row r="284" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G284" s="53"/>
     </row>
-    <row r="285" spans="7:7">
+    <row r="285" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G285" s="53"/>
     </row>
-    <row r="286" spans="7:7">
+    <row r="286" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G286" s="53"/>
     </row>
-    <row r="287" spans="7:7">
+    <row r="287" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G287" s="53"/>
     </row>
-    <row r="288" spans="7:7">
+    <row r="288" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G288" s="53"/>
     </row>
-    <row r="289" spans="7:7">
+    <row r="289" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G289" s="53"/>
     </row>
-    <row r="290" spans="7:7">
+    <row r="290" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G290" s="53"/>
     </row>
-    <row r="291" spans="7:7">
+    <row r="291" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G291" s="53"/>
     </row>
-    <row r="292" spans="7:7">
+    <row r="292" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G292" s="53"/>
     </row>
-    <row r="293" spans="7:7">
+    <row r="293" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G293" s="53"/>
     </row>
-    <row r="294" spans="7:7">
+    <row r="294" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G294" s="53"/>
     </row>
-    <row r="295" spans="7:7">
+    <row r="295" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G295" s="53"/>
     </row>
-    <row r="296" spans="7:7">
+    <row r="296" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G296" s="53"/>
     </row>
-    <row r="297" spans="7:7">
+    <row r="297" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G297" s="53"/>
     </row>
-    <row r="298" spans="7:7">
+    <row r="298" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G298" s="53"/>
     </row>
-    <row r="299" spans="7:7">
+    <row r="299" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G299" s="53"/>
     </row>
-    <row r="300" spans="7:7">
+    <row r="300" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G300" s="53"/>
     </row>
-    <row r="301" spans="7:7">
+    <row r="301" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G301" s="53"/>
     </row>
-    <row r="302" spans="7:7">
+    <row r="302" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G302" s="53"/>
     </row>
-    <row r="303" spans="7:7">
+    <row r="303" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G303" s="53"/>
     </row>
-    <row r="304" spans="7:7">
+    <row r="304" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G304" s="53"/>
     </row>
-    <row r="305" spans="7:7">
+    <row r="305" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G305" s="53"/>
     </row>
-    <row r="306" spans="7:7">
+    <row r="306" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G306" s="53"/>
     </row>
-    <row r="307" spans="7:7">
+    <row r="307" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G307" s="53"/>
     </row>
-    <row r="308" spans="7:7">
+    <row r="308" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G308" s="53"/>
     </row>
-    <row r="309" spans="7:7">
+    <row r="309" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G309" s="53"/>
     </row>
-    <row r="310" spans="7:7">
+    <row r="310" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G310" s="53"/>
     </row>
-    <row r="311" spans="7:7">
+    <row r="311" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G311" s="53"/>
     </row>
-    <row r="312" spans="7:7">
+    <row r="312" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G312" s="53"/>
     </row>
-    <row r="313" spans="7:7">
+    <row r="313" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G313" s="53"/>
     </row>
-    <row r="314" spans="7:7">
+    <row r="314" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G314" s="53"/>
     </row>
-    <row r="315" spans="7:7">
+    <row r="315" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G315" s="53"/>
     </row>
-    <row r="316" spans="7:7">
+    <row r="316" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G316" s="53"/>
     </row>
-    <row r="317" spans="7:7">
+    <row r="317" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G317" s="53"/>
     </row>
-    <row r="318" spans="7:7">
+    <row r="318" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G318" s="53"/>
     </row>
-    <row r="319" spans="7:7">
+    <row r="319" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G319" s="53"/>
     </row>
-    <row r="320" spans="7:7">
+    <row r="320" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G320" s="53"/>
     </row>
-    <row r="321" spans="7:7">
+    <row r="321" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G321" s="53"/>
     </row>
-    <row r="322" spans="7:7">
+    <row r="322" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G322" s="53"/>
     </row>
-    <row r="323" spans="7:7">
+    <row r="323" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G323" s="53"/>
     </row>
-    <row r="324" spans="7:7">
+    <row r="324" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G324" s="53"/>
     </row>
-    <row r="325" spans="7:7">
+    <row r="325" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G325" s="53"/>
     </row>
-    <row r="326" spans="7:7">
+    <row r="326" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G326" s="53"/>
     </row>
-    <row r="327" spans="7:7">
+    <row r="327" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G327" s="53"/>
     </row>
-    <row r="328" spans="7:7">
+    <row r="328" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G328" s="53"/>
     </row>
-    <row r="329" spans="7:7">
+    <row r="329" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G329" s="53"/>
     </row>
-    <row r="330" spans="7:7">
+    <row r="330" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G330" s="53"/>
     </row>
-    <row r="331" spans="7:7">
+    <row r="331" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G331" s="53"/>
     </row>
-    <row r="332" spans="7:7">
+    <row r="332" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G332" s="53"/>
     </row>
-    <row r="333" spans="7:7">
+    <row r="333" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G333" s="53"/>
     </row>
-    <row r="334" spans="7:7">
+    <row r="334" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G334" s="53"/>
     </row>
-    <row r="335" spans="7:7">
+    <row r="335" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G335" s="53"/>
     </row>
-    <row r="336" spans="7:7">
+    <row r="336" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G336" s="53"/>
     </row>
-    <row r="337" spans="7:7">
+    <row r="337" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G337" s="53"/>
     </row>
-    <row r="338" spans="7:7">
+    <row r="338" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G338" s="53"/>
     </row>
-    <row r="339" spans="7:7">
+    <row r="339" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G339" s="53"/>
     </row>
-    <row r="340" spans="7:7">
+    <row r="340" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G340" s="53"/>
     </row>
-    <row r="341" spans="7:7">
+    <row r="341" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G341" s="53"/>
     </row>
-    <row r="342" spans="7:7">
+    <row r="342" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G342" s="53"/>
     </row>
-    <row r="343" spans="7:7">
+    <row r="343" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G343" s="53"/>
     </row>
-    <row r="344" spans="7:7">
+    <row r="344" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G344" s="53"/>
     </row>
-    <row r="345" spans="7:7">
+    <row r="345" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G345" s="53"/>
     </row>
-    <row r="346" spans="7:7">
+    <row r="346" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G346" s="53"/>
     </row>
-    <row r="347" spans="7:7">
+    <row r="347" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G347" s="53"/>
     </row>
-    <row r="348" spans="7:7">
+    <row r="348" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G348" s="53"/>
     </row>
-    <row r="349" spans="7:7">
+    <row r="349" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G349" s="53"/>
     </row>
-    <row r="350" spans="7:7">
+    <row r="350" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G350" s="53"/>
     </row>
-    <row r="351" spans="7:7">
+    <row r="351" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G351" s="53"/>
     </row>
-    <row r="352" spans="7:7">
+    <row r="352" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G352" s="53"/>
     </row>
-    <row r="353" spans="7:7">
+    <row r="353" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G353" s="53"/>
     </row>
-    <row r="354" spans="7:7">
+    <row r="354" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G354" s="53"/>
     </row>
-    <row r="355" spans="7:7">
+    <row r="355" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G355" s="53"/>
     </row>
-    <row r="356" spans="7:7">
+    <row r="356" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G356" s="53"/>
     </row>
-    <row r="357" spans="7:7">
+    <row r="357" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G357" s="53"/>
     </row>
-    <row r="358" spans="7:7">
+    <row r="358" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G358" s="53"/>
     </row>
-    <row r="359" spans="7:7">
+    <row r="359" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G359" s="53"/>
     </row>
-    <row r="360" spans="7:7">
+    <row r="360" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G360" s="53"/>
     </row>
-    <row r="361" spans="7:7">
+    <row r="361" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G361" s="53"/>
     </row>
-    <row r="362" spans="7:7">
+    <row r="362" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G362" s="53"/>
     </row>
-    <row r="363" spans="7:7">
+    <row r="363" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G363" s="53"/>
     </row>
-    <row r="364" spans="7:7">
+    <row r="364" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G364" s="53"/>
     </row>
-    <row r="365" spans="7:7">
+    <row r="365" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G365" s="53"/>
     </row>
-    <row r="366" spans="7:7">
+    <row r="366" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G366" s="53"/>
     </row>
-    <row r="367" spans="7:7">
+    <row r="367" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G367" s="53"/>
     </row>
-    <row r="368" spans="7:7">
+    <row r="368" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G368" s="53"/>
     </row>
-    <row r="369" spans="7:7">
+    <row r="369" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G369" s="53"/>
     </row>
-    <row r="370" spans="7:7">
+    <row r="370" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G370" s="53"/>
     </row>
-    <row r="371" spans="7:7">
+    <row r="371" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G371" s="53"/>
     </row>
-    <row r="372" spans="7:7">
+    <row r="372" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G372" s="53"/>
     </row>
-    <row r="373" spans="7:7">
+    <row r="373" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G373" s="53"/>
     </row>
-    <row r="374" spans="7:7">
+    <row r="374" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G374" s="53"/>
     </row>
-    <row r="375" spans="7:7">
+    <row r="375" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G375" s="53"/>
     </row>
-    <row r="376" spans="7:7">
+    <row r="376" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G376" s="53"/>
     </row>
-    <row r="377" spans="7:7">
+    <row r="377" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G377" s="53"/>
     </row>
-    <row r="378" spans="7:7">
+    <row r="378" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G378" s="53"/>
     </row>
-    <row r="379" spans="7:7">
+    <row r="379" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G379" s="53"/>
     </row>
-    <row r="380" spans="7:7">
+    <row r="380" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G380" s="53"/>
     </row>
-    <row r="381" spans="7:7">
+    <row r="381" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G381" s="53"/>
     </row>
-    <row r="382" spans="7:7">
+    <row r="382" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G382" s="53"/>
     </row>
-    <row r="383" spans="7:7">
+    <row r="383" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G383" s="53"/>
     </row>
-    <row r="384" spans="7:7">
+    <row r="384" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G384" s="53"/>
     </row>
-    <row r="385" spans="7:7">
+    <row r="385" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G385" s="53"/>
     </row>
-    <row r="386" spans="7:7">
+    <row r="386" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G386" s="53"/>
     </row>
-    <row r="387" spans="7:7">
+    <row r="387" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G387" s="53"/>
     </row>
-    <row r="388" spans="7:7">
+    <row r="388" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G388" s="53"/>
     </row>
-    <row r="389" spans="7:7">
+    <row r="389" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G389" s="53"/>
     </row>
-    <row r="390" spans="7:7">
+    <row r="390" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G390" s="53"/>
     </row>
-    <row r="391" spans="7:7">
+    <row r="391" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G391" s="53"/>
     </row>
-    <row r="392" spans="7:7">
+    <row r="392" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G392" s="53"/>
     </row>
-    <row r="393" spans="7:7">
+    <row r="393" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G393" s="53"/>
     </row>
-    <row r="394" spans="7:7">
+    <row r="394" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G394" s="53"/>
     </row>
-    <row r="395" spans="7:7">
+    <row r="395" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G395" s="53"/>
     </row>
-    <row r="396" spans="7:7">
+    <row r="396" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G396" s="53"/>
     </row>
-    <row r="397" spans="7:7">
+    <row r="397" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G397" s="53"/>
     </row>
-    <row r="398" spans="7:7">
+    <row r="398" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G398" s="53"/>
     </row>
-    <row r="399" spans="7:7">
+    <row r="399" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G399" s="53"/>
     </row>
-    <row r="400" spans="7:7">
+    <row r="400" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G400" s="53"/>
     </row>
-    <row r="401" spans="7:7">
+    <row r="401" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G401" s="53"/>
     </row>
-    <row r="402" spans="7:7">
+    <row r="402" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G402" s="53"/>
     </row>
-    <row r="403" spans="7:7">
+    <row r="403" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G403" s="53"/>
     </row>
-    <row r="404" spans="7:7">
+    <row r="404" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G404" s="53"/>
     </row>
   </sheetData>
@@ -11651,90 +11764,58 @@
     <mergeCell ref="M3:M4"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C97:D114 C115:C121">
-    <cfRule type="cellIs" dxfId="21" priority="199" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="199" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="200" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="200" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G123:G1048576">
-    <cfRule type="cellIs" dxfId="19" priority="27" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="27" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="28" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="28" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G96:H105 G122:H122">
-    <cfRule type="cellIs" dxfId="17" priority="9" operator="greaterThan">
+  <conditionalFormatting sqref="G96:H122">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:I95">
-    <cfRule type="cellIs" dxfId="15" priority="39" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="39" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="40" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="40" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H123:H130">
-    <cfRule type="cellIs" dxfId="13" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="21" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="22" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H131:I266">
-    <cfRule type="cellIs" dxfId="11" priority="197" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="197" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="198" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="198" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I96:I130">
-    <cfRule type="cellIs" dxfId="9" priority="45" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="45" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="46" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G106:H107">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G108:H111">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G112:H116">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G117:H121">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="46" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11746,7 +11827,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:D17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="2" width="26.28515625" customWidth="1"/>
@@ -11754,7 +11835,7 @@
     <col min="4" max="4" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" s="62" t="s">
         <v>237</v>
       </c>
@@ -11765,7 +11846,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="2" spans="2:4">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="54" t="s">
         <v>23</v>
       </c>
@@ -11774,7 +11855,7 @@
       </c>
       <c r="D2" s="54"/>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="54" t="s">
         <v>128</v>
       </c>
@@ -11783,7 +11864,7 @@
       </c>
       <c r="D3" s="54"/>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="54" t="s">
         <v>129</v>
       </c>
@@ -11792,7 +11873,7 @@
       </c>
       <c r="D4" s="54"/>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="54" t="s">
         <v>130</v>
       </c>
@@ -11801,7 +11882,7 @@
       </c>
       <c r="D5" s="54"/>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="54" t="s">
         <v>131</v>
       </c>
@@ -11810,7 +11891,7 @@
       </c>
       <c r="D6" s="54"/>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="54" t="s">
         <v>242</v>
       </c>
@@ -11819,7 +11900,7 @@
       </c>
       <c r="D7" s="54"/>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="54" t="s">
         <v>243</v>
       </c>
@@ -11828,7 +11909,7 @@
       </c>
       <c r="D8" s="54"/>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="54" t="s">
         <v>141</v>
       </c>
@@ -11839,7 +11920,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="54" t="s">
         <v>245</v>
       </c>
@@ -11848,7 +11929,7 @@
       </c>
       <c r="D10" s="54"/>
     </row>
-    <row r="17" spans="3:3">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" s="28"/>
     </row>
   </sheetData>

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="218" documentId="11_C0E26E8C2FF3658481E6AE6DE74C74B31A2D8B7D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A6D1C18-61D5-427D-BB7D-B4DE6023E9A2}"/>
+  <xr:revisionPtr revIDLastSave="496" documentId="11_C0E26E8C2FF3658481E6AE6DE74C74B31A2D8B7D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{566CA734-F2FA-494D-AC4A-CE5F73FEA93F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="286">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -129,6 +129,9 @@
     <t xml:space="preserve">        Recolhimento INSS</t>
   </si>
   <si>
+    <t>Soma sem INSS</t>
+  </si>
+  <si>
     <t>Stella tem que transferir:</t>
   </si>
   <si>
@@ -141,7 +144,7 @@
     <t>Status pagamento Stella</t>
   </si>
   <si>
-    <t>Aguardando</t>
+    <t>Pago</t>
   </si>
   <si>
     <t>Itaú Total</t>
@@ -432,6 +435,90 @@
     <t>Pagamento Croma Beer</t>
   </si>
   <si>
+    <t>Psicóloga</t>
+  </si>
+  <si>
+    <t>Saúde</t>
+  </si>
+  <si>
+    <t>Pizza</t>
+  </si>
+  <si>
+    <t>Uber Galpãozin</t>
+  </si>
+  <si>
+    <t>Galpãozin</t>
+  </si>
+  <si>
+    <t>Parrilla</t>
+  </si>
+  <si>
+    <t>Empanadas</t>
+  </si>
+  <si>
+    <t>Pagamento Galpãozin</t>
+  </si>
+  <si>
+    <t>Pagamento Empanadas</t>
+  </si>
+  <si>
+    <t>Calças Stella</t>
+  </si>
+  <si>
+    <t>IPA</t>
+  </si>
+  <si>
+    <t>Vacina</t>
+  </si>
+  <si>
+    <t>BK</t>
+  </si>
+  <si>
+    <t>Guacolombia</t>
+  </si>
+  <si>
+    <t>Grama Sintética</t>
+  </si>
+  <si>
+    <t>Quero-quero</t>
+  </si>
+  <si>
+    <t>Vitoritto</t>
+  </si>
+  <si>
+    <t>Uber Mr Jones</t>
+  </si>
+  <si>
+    <t>Pagamento Quero-Quero+Vitorrito</t>
+  </si>
+  <si>
+    <t>Cervejas</t>
+  </si>
+  <si>
+    <t>Mr Jones</t>
+  </si>
+  <si>
+    <t>Pagamento mr Jones</t>
+  </si>
+  <si>
+    <t>Psiquiatra</t>
+  </si>
+  <si>
+    <t>Estacionamento Eldorado</t>
+  </si>
+  <si>
+    <t>Trasporte</t>
+  </si>
+  <si>
+    <t>Pagamento Quero-Quero</t>
+  </si>
+  <si>
+    <t>Ida e Volta Scanntech</t>
+  </si>
+  <si>
+    <t>Almoço Hotel</t>
+  </si>
+  <si>
     <t>Vivo</t>
   </si>
   <si>
@@ -477,6 +564,12 @@
     <t>Seguro Itaú</t>
   </si>
   <si>
+    <t>Pagamento Psiquiatra</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
@@ -522,9 +615,6 @@
     <t>Adiantamento Stella</t>
   </si>
   <si>
-    <t>Galpãozin</t>
-  </si>
-  <si>
     <t>Fisioterapia Stella</t>
   </si>
   <si>
@@ -696,48 +786,60 @@
     <t>Psicóloga Atrasada</t>
   </si>
   <si>
+    <t>Custos Rennala</t>
+  </si>
+  <si>
+    <t>Devolução Stella - 20/10</t>
+  </si>
+  <si>
+    <t>Devolução Stella + Recolhimento</t>
+  </si>
+  <si>
+    <t>Custos Rennala 2</t>
+  </si>
+  <si>
+    <t>NF</t>
+  </si>
+  <si>
+    <t>Janta Anivsersário</t>
+  </si>
+  <si>
+    <t>mr Jones e bonfas</t>
+  </si>
+  <si>
+    <t>Devolução Stella Novembro - 20/11</t>
+  </si>
+  <si>
+    <t>Adiantamento Stella Outubro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novembro </t>
+  </si>
+  <si>
+    <t>Aniversário</t>
+  </si>
+  <si>
+    <t>NF Stella - Atrasado</t>
+  </si>
+  <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
     <t>NF Stella</t>
   </si>
   <si>
-    <t>Custos Rennala</t>
-  </si>
-  <si>
-    <t>Devolução Stella + Recolhimento</t>
-  </si>
-  <si>
-    <t>Novembro</t>
-  </si>
-  <si>
-    <t>Custos Rennala 2</t>
-  </si>
-  <si>
-    <t>Dezembro</t>
-  </si>
-  <si>
-    <t>Janta Anivsersário</t>
-  </si>
-  <si>
     <t>Ilumeo Dezembro - 3º PPT</t>
   </si>
   <si>
-    <t>mr Jones e bonfas</t>
-  </si>
-  <si>
     <t>Segunda Parcela 13º</t>
   </si>
   <si>
-    <t>Adiantamento Stella Outubro</t>
-  </si>
-  <si>
     <t>Janeiro</t>
   </si>
   <si>
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>Aniversário</t>
-  </si>
-  <si>
     <t>Março</t>
   </si>
   <si>
@@ -786,28 +888,22 @@
     <t>Dera</t>
   </si>
   <si>
-    <t>Psicóloga</t>
-  </si>
-  <si>
-    <t>Saúde</t>
-  </si>
-  <si>
-    <t>Pizza</t>
-  </si>
-  <si>
-    <t>Uber Galpãozin</t>
-  </si>
-  <si>
-    <t>Parrilla</t>
-  </si>
-  <si>
-    <t>Empanadas</t>
-  </si>
-  <si>
-    <t>Pagamento Galpãozin</t>
-  </si>
-  <si>
-    <t>Pagamento Empanadas</t>
+    <t>Dinheiro FIA</t>
+  </si>
+  <si>
+    <t>Bem Gelada</t>
+  </si>
+  <si>
+    <t>Uber Protesto</t>
+  </si>
+  <si>
+    <t>Dinheiro Ps5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Dinheiro PS5</t>
+  </si>
+  <si>
+    <t>Ajuste</t>
   </si>
 </sst>
 </file>
@@ -1108,7 +1204,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1310,6 +1406,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1530,10 +1629,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
@@ -1710,7 +1805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:F41"/>
+  <dimension ref="B1:F42"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
@@ -1722,7 +1817,7 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="82" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -1734,15 +1829,15 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="82"/>
+      <c r="B3" s="83"/>
       <c r="C3" s="6">
-        <f>C5-C8-C10-C11-C25+C26+C7+C27</f>
-        <v>1899.0389047619037</v>
+        <f>C5-C8-C10-C11-C26+C27+C7+C28</f>
+        <v>1692.5772380952367</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
-        <f>E5-E8-E10-E11-E25+E26</f>
-        <v>2716.1166666666668</v>
+        <f>E5-E8-E10-E11-E26+E27</f>
+        <v>2609.5200000000004</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1755,7 +1850,7 @@
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="8">
-        <v>10000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
@@ -1764,12 +1859,12 @@
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-6938.9610952380963</v>
+        <v>-7665.4227619047633</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-7283.8833333333332</v>
+        <v>-8390.48</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -1800,12 +1895,12 @@
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>4368.6210952380961</v>
+        <v>5107.5827619047632</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>1671.5433333333335</v>
+        <v>2490.6400000000003</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -1814,12 +1909,12 @@
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>4368.6210952380961</v>
+        <v>5107.5827619047632</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>1671.5433333333335</v>
+        <v>2490.6400000000003</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
@@ -1828,12 +1923,12 @@
       </c>
       <c r="C11" s="8">
         <f>Contas!B6</f>
-        <v>2570.34</v>
+        <v>2557.84</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="8">
         <f>Contas!B9</f>
-        <v>5612.34</v>
+        <v>5899.84</v>
       </c>
     </row>
     <row r="12" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -1870,12 +1965,12 @@
       </c>
       <c r="C14" s="14">
         <f>Contas!K5</f>
-        <v>220</v>
+        <v>207.5</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="14">
         <f>Contas!K5</f>
-        <v>220</v>
+        <v>207.5</v>
       </c>
       <c r="F14" s="16"/>
     </row>
@@ -1926,12 +2021,12 @@
         <v>16</v>
       </c>
       <c r="C18" s="14">
-        <f>Contas!$K9+Contas!$K13</f>
+        <f>Contas!$K9+Contas!$K14</f>
         <v>333.5</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="14">
-        <f>Contas!$K9+Contas!$K13</f>
+        <f>Contas!$K9+Contas!$K14</f>
         <v>333.5</v>
       </c>
     </row>
@@ -1962,28 +2057,34 @@
     <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B21" s="13" t="str">
         <f>Contas!$D12</f>
-        <v>Empréstimo</v>
+        <v>Dinheiro Ps5</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="15"/>
       <c r="E21" s="14">
         <f>Contas!K12</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="13" t="str">
+        <f>Contas!$D13</f>
+        <v>Empréstimo</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="14">
+        <f>Contas!K13</f>
         <v>1292</v>
       </c>
     </row>
-    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
+    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="18"/>
-    </row>
-    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="13"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="14"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="18"/>
     </row>
     <row r="24" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B24" s="13"/>
@@ -1991,175 +2092,168 @@
       <c r="D24" s="15"/>
       <c r="E24" s="14"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="8"/>
+    <row r="25" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="14"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D26" s="9"/>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="8">
-        <f>SUM(C28:C39)</f>
+      <c r="C27" s="8">
+        <f>SUM(C29:C40)</f>
+        <v>520</v>
+      </c>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8">
+        <f>SUM(E29:E38)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8">
-        <f>SUM(E28:E37)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="13" t="s">
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C28" s="8">
         <v>338</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-    </row>
-    <row r="28" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="14" t="str">
-        <f>IF('NuConta e Poupança'!M5="Sim",'NuConta e Poupança'!N5,"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="14"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="14" t="str">
+        <f>IF('NuConta e Poupança'!M5="Sim",'NuConta e Poupança'!N5,"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="15"/>
+      <c r="E29" s="14"/>
+    </row>
+    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="21"/>
-    </row>
-    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="13" t="str">
-        <f>"       "&amp;'NuConta e Poupança'!L7</f>
-        <v xml:space="preserve">       </v>
-      </c>
-      <c r="C30" s="14" t="str">
-        <f>IF('NuConta e Poupança'!M7="Sim",'NuConta e Poupança'!N7,"")</f>
-        <v/>
-      </c>
+      <c r="C30" s="14"/>
       <c r="D30" s="20"/>
       <c r="E30" s="21"/>
     </row>
     <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B31" s="13" t="str">
-        <f>"       "&amp;'NuConta e Poupança'!L8</f>
-        <v xml:space="preserve">       </v>
-      </c>
-      <c r="C31" s="14" t="str">
-        <f>IF('NuConta e Poupança'!M8="Sim",'NuConta e Poupança'!N8,"")</f>
-        <v/>
+        <f>"       "&amp;'NuConta e Poupança'!L7</f>
+        <v xml:space="preserve">       Pagamento Psiquiatra</v>
+      </c>
+      <c r="C31" s="14">
+        <f>IF('NuConta e Poupança'!M7="Sim",'NuConta e Poupança'!N7,"")</f>
+        <v>280</v>
       </c>
       <c r="D31" s="20"/>
       <c r="E31" s="21"/>
     </row>
     <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B32" s="13" t="str">
+        <f>"       "&amp;'NuConta e Poupança'!L8</f>
+        <v xml:space="preserve">       Dinheiro FIA</v>
+      </c>
+      <c r="C32" s="14">
+        <f>IF('NuConta e Poupança'!M8="Sim",'NuConta e Poupança'!N8,"")</f>
+        <v>240</v>
+      </c>
+      <c r="D32" s="20"/>
+      <c r="E32" s="21"/>
+    </row>
+    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L9</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C32" s="14" t="str">
+      <c r="C33" s="14" t="str">
         <f>IF('NuConta e Poupança'!M9="Sim",'NuConta e Poupança'!N9,"")</f>
         <v/>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="21"/>
-    </row>
-    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="13" t="str">
+      <c r="D33" s="20"/>
+      <c r="E33" s="21"/>
+    </row>
+    <row r="34" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L10</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C33" s="14" t="str">
+      <c r="C34" s="14" t="str">
         <f>IF('NuConta e Poupança'!M10="Sim",'NuConta e Poupança'!N10,"")</f>
         <v/>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="21"/>
-    </row>
-    <row r="34" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="13" t="str">
+      <c r="D34" s="20"/>
+      <c r="E34" s="21"/>
+    </row>
+    <row r="35" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L12</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C34" s="14" t="str">
+      <c r="C35" s="14" t="str">
         <f>IF('NuConta e Poupança'!M12="Sim",'NuConta e Poupança'!N11,"")</f>
         <v/>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="21"/>
-    </row>
-    <row r="35" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="13" t="str">
+      <c r="D35" s="20"/>
+      <c r="E35" s="21"/>
+    </row>
+    <row r="36" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L13</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C35" s="14" t="str">
+      <c r="C36" s="14" t="str">
         <f>IF('NuConta e Poupança'!M13="Sim",'NuConta e Poupança'!N12,"")</f>
         <v/>
       </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="21"/>
-    </row>
-    <row r="36" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="13" t="str">
+      <c r="D36" s="20"/>
+      <c r="E36" s="21"/>
+    </row>
+    <row r="37" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L14</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C36" s="14" t="str">
+      <c r="C37" s="14" t="str">
         <f>IF('NuConta e Poupança'!M14="Sim",'NuConta e Poupança'!N13,"")</f>
         <v/>
       </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="21"/>
-    </row>
-    <row r="37" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="13" t="str">
+      <c r="D37" s="20"/>
+      <c r="E37" s="21"/>
+    </row>
+    <row r="38" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L15</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C37" s="14" t="str">
+      <c r="C38" s="14" t="str">
         <f>IF('NuConta e Poupança'!M15="Sim",'NuConta e Poupança'!N14,"")</f>
         <v/>
       </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="21"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="13" t="str">
+      <c r="D38" s="20"/>
+      <c r="E38" s="21"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L16</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C38" s="14" t="str">
+      <c r="C39" s="14" t="str">
         <f>IF('NuConta e Poupança'!M16="Sim",'NuConta e Poupança'!N15,"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="16"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="13" t="str">
-        <f>"       "&amp;'NuConta e Poupança'!L17</f>
-        <v xml:space="preserve">       </v>
-      </c>
-      <c r="C39" s="14" t="str">
-        <f>IF('NuConta e Poupança'!M17="Sim",'NuConta e Poupança'!N16,"")</f>
         <v/>
       </c>
       <c r="D39" s="20"/>
@@ -2168,27 +2262,40 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="13" t="str">
+        <f>"       "&amp;'NuConta e Poupança'!L17</f>
+        <v xml:space="preserve">       </v>
+      </c>
+      <c r="C40" s="14" t="str">
+        <f>IF('NuConta e Poupança'!M17="Sim",'NuConta e Poupança'!N16,"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="20"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="16"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L21</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C40" s="14" t="str">
+      <c r="C41" s="14" t="str">
         <f>IF('NuConta e Poupança'!M21="Sim",'NuConta e Poupança'!N20,"")</f>
         <v/>
       </c>
-      <c r="D40" s="20"/>
-      <c r="E40" s="21"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B41" s="13" t="str">
+      <c r="D41" s="20"/>
+      <c r="E41" s="21"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B42" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L22</f>
         <v xml:space="preserve">       </v>
       </c>
-      <c r="C41" s="14" t="str">
+      <c r="C42" s="14" t="str">
         <f>IF('NuConta e Poupança'!M22="Sim",'NuConta e Poupança'!N21,"")</f>
         <v/>
       </c>
-      <c r="D41" s="20"/>
-      <c r="E41" s="21"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2201,7 +2308,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:D24"/>
+  <dimension ref="B1:D100"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2240,11 +2347,11 @@
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>1671.5433333333335</v>
+        <v>2490.6400000000003</v>
       </c>
       <c r="D4" s="24">
         <f>Saldo!C9+D5</f>
-        <v>4368.6210952380961</v>
+        <v>5107.5827619047632</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
@@ -2277,8 +2384,8 @@
         <v>9</v>
       </c>
       <c r="C10" s="8">
-        <f>SUM(C11,C13:C18)</f>
-        <v>3098.34</v>
+        <f>SUM(C11,C13:C19)</f>
+        <v>3385.84</v>
       </c>
       <c r="D10" s="7"/>
     </row>
@@ -2308,7 +2415,7 @@
       </c>
       <c r="C13" s="14">
         <f>Contas!K5</f>
-        <v>220</v>
+        <v>207.5</v>
       </c>
       <c r="D13" s="13"/>
     </row>
@@ -2363,45 +2470,66 @@
       <c r="D18" s="13"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="13"/>
-      <c r="C19" s="14"/>
+      <c r="B19" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="C19" s="14">
+        <f>Saldo!E21</f>
+        <v>300</v>
+      </c>
       <c r="D19" s="13"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="14">
+        <f>C21-C18</f>
+        <v>5126.4800000000005</v>
+      </c>
+      <c r="D20" s="13"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>4769.8833333333332</v>
-      </c>
-      <c r="D20" s="27"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="1"/>
+        <v>5876.4800000000005</v>
+      </c>
+      <c r="D21" s="27"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="73">
-        <v>5587.2758333333331</v>
-      </c>
+      <c r="C22" s="1"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="69">
-        <v>46295</v>
+      <c r="C23" s="73">
+        <v>5587.2758333333331</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="69" t="s">
+      <c r="C24" s="69">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
         <v>31</v>
+      </c>
+      <c r="C25" s="69" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C100" s="81" t="str">
+        <f>'Compensasões e Transferências'!C25</f>
+        <v>Pago</v>
       </c>
     </row>
   </sheetData>
@@ -2433,7 +2561,7 @@
   <sheetData>
     <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
@@ -2442,7 +2570,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2465,49 +2593,49 @@
     </row>
     <row r="4" spans="3:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M4" s="34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O4" s="33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P4" s="33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q4" s="34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3119,7 +3247,7 @@
   <sheetData>
     <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>1</v>
@@ -3128,7 +3256,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L1" s="43"/>
       <c r="P1" s="2"/>
@@ -3136,15 +3264,15 @@
     <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="45">
         <f>SUM(L6:L184)</f>
-        <v>8040.1644285714283</v>
+        <v>9598.2227619047608</v>
       </c>
       <c r="E2" s="32">
         <f>SUMIF($E$6:$E$184,E1,$M$6:$M$184)</f>
-        <v>4368.6210952380961</v>
+        <v>5107.5827619047632</v>
       </c>
       <c r="F2" s="32">
         <f>SUMIF($F$6:$F$184,F1,$M$6:$M$184)</f>
-        <v>1671.5433333333335</v>
+        <v>2490.6400000000003</v>
       </c>
       <c r="G2" s="32">
         <f>SUMIF($G$6:$G$184,G1,$M$6:$M$184)</f>
@@ -3164,52 +3292,52 @@
     <row r="5" spans="3:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="33"/>
       <c r="D5" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M5" s="34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N5" s="34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O5" s="33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P5" s="33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q5" s="34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C6" s="35"/>
       <c r="D6" s="36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E6" s="37" t="s">
         <v>1</v>
@@ -3226,10 +3354,10 @@
         <v>359</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L6" s="38">
         <f t="shared" ref="L6:L47" si="1">I6/N6</f>
@@ -3257,7 +3385,7 @@
     <row r="7" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C7" s="35"/>
       <c r="D7" s="36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" s="37" t="s">
         <v>1</v>
@@ -3272,10 +3400,10 @@
         <v>258</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K7" s="37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L7" s="38">
         <f t="shared" si="1"/>
@@ -3303,7 +3431,7 @@
     <row r="8" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C8" s="35"/>
       <c r="D8" s="74" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="37"/>
       <c r="F8" s="37" t="s">
@@ -3318,10 +3446,10 @@
         <v>973.02</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K8" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L8" s="38">
         <f t="shared" si="1"/>
@@ -3349,7 +3477,7 @@
     <row r="9" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C9" s="35"/>
       <c r="D9" s="74" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" s="37" t="s">
         <v>1</v>
@@ -3364,10 +3492,10 @@
         <v>379</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L9" s="38">
         <f t="shared" si="1"/>
@@ -3395,7 +3523,7 @@
     <row r="10" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C10" s="35"/>
       <c r="D10" s="74" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" s="37" t="s">
         <v>1</v>
@@ -3410,10 +3538,10 @@
         <v>297</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L10" s="38">
         <f t="shared" si="1"/>
@@ -3441,7 +3569,7 @@
     <row r="11" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C11" s="35"/>
       <c r="D11" s="74" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E11" s="37" t="s">
         <v>1</v>
@@ -3456,10 +3584,10 @@
         <v>326.99</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L11" s="38">
         <f t="shared" si="1"/>
@@ -3487,7 +3615,7 @@
     <row r="12" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C12" s="35"/>
       <c r="D12" s="74" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E12" s="37" t="s">
         <v>1</v>
@@ -3504,10 +3632,10 @@
         <v>217.85</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L12" s="38">
         <f t="shared" si="1"/>
@@ -3535,7 +3663,7 @@
     <row r="13" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C13" s="35"/>
       <c r="D13" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E13" s="37" t="s">
         <v>1</v>
@@ -3552,10 +3680,10 @@
         <v>209.94</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L13" s="38">
         <f t="shared" si="1"/>
@@ -3583,7 +3711,7 @@
     <row r="14" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C14" s="35"/>
       <c r="D14" s="65" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>1</v>
@@ -3600,10 +3728,10 @@
         <v>249.5</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L14" s="38">
         <f t="shared" si="1"/>
@@ -3631,7 +3759,7 @@
     <row r="15" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C15" s="35"/>
       <c r="D15" s="65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" s="37" t="s">
         <v>1</v>
@@ -3648,10 +3776,10 @@
         <v>-209.94</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K15" s="38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L15" s="38">
         <f t="shared" si="1"/>
@@ -3679,7 +3807,7 @@
     <row r="16" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C16" s="35"/>
       <c r="D16" s="75" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E16" s="37" t="s">
         <v>1</v>
@@ -3696,10 +3824,10 @@
         <v>506</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L16" s="38">
         <f t="shared" si="1"/>
@@ -3724,7 +3852,7 @@
     <row r="17" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C17" s="35"/>
       <c r="D17" s="75" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E17" s="37" t="s">
         <v>1</v>
@@ -3739,10 +3867,10 @@
         <v>399.9</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K17" s="38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L17" s="38">
         <f t="shared" si="1"/>
@@ -3770,7 +3898,7 @@
     <row r="18" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C18" s="35"/>
       <c r="D18" s="75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E18" s="37" t="s">
         <v>1</v>
@@ -3785,10 +3913,10 @@
         <v>284</v>
       </c>
       <c r="J18" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L18" s="38">
         <f t="shared" si="1"/>
@@ -3816,7 +3944,7 @@
     <row r="19" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C19" s="35"/>
       <c r="D19" s="75" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E19" s="37" t="s">
         <v>1</v>
@@ -3831,10 +3959,10 @@
         <v>500</v>
       </c>
       <c r="J19" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K19" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L19" s="38">
         <f t="shared" si="1"/>
@@ -3862,7 +3990,7 @@
     <row r="20" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C20" s="35"/>
       <c r="D20" s="36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>1</v>
@@ -3879,10 +4007,10 @@
         <v>1017.6</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L20" s="38">
         <f t="shared" si="1"/>
@@ -3910,7 +4038,7 @@
     <row r="21" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C21" s="35"/>
       <c r="D21" s="46" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E21" s="37" t="s">
         <v>1</v>
@@ -3925,10 +4053,10 @@
         <v>1900</v>
       </c>
       <c r="J21" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L21" s="38">
         <f t="shared" si="1"/>
@@ -3956,7 +4084,7 @@
     <row r="22" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C22" s="35"/>
       <c r="D22" s="46" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>1</v>
@@ -3971,10 +4099,10 @@
         <v>474.33</v>
       </c>
       <c r="J22" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L22" s="38">
         <f t="shared" si="1"/>
@@ -4002,7 +4130,7 @@
     <row r="23" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C23" s="35"/>
       <c r="D23" s="46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E23" s="37" t="s">
         <v>1</v>
@@ -4017,10 +4145,10 @@
         <v>330</v>
       </c>
       <c r="J23" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L23" s="38">
         <f t="shared" si="1"/>
@@ -4048,7 +4176,7 @@
     <row r="24" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C24" s="35"/>
       <c r="D24" s="46" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E24" s="37" t="s">
         <v>1</v>
@@ -4065,10 +4193,10 @@
         <v>1780</v>
       </c>
       <c r="J24" s="67" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L24" s="38">
         <f t="shared" si="1"/>
@@ -4096,7 +4224,7 @@
     <row r="25" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C25" s="35"/>
       <c r="D25" s="46" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E25" s="37" t="s">
         <v>1</v>
@@ -4111,10 +4239,10 @@
         <v>286.39</v>
       </c>
       <c r="J25" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L25" s="38">
         <f t="shared" si="1"/>
@@ -4142,7 +4270,7 @@
     <row r="26" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C26" s="35"/>
       <c r="D26" s="46" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>1</v>
@@ -4157,10 +4285,10 @@
         <v>300</v>
       </c>
       <c r="J26" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L26" s="38">
         <f t="shared" si="1"/>
@@ -4188,7 +4316,7 @@
     <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C27" s="35"/>
       <c r="D27" s="46" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E27" s="37" t="s">
         <v>1</v>
@@ -4205,10 +4333,10 @@
         <v>663</v>
       </c>
       <c r="J27" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L27" s="38">
         <f t="shared" si="1"/>
@@ -4236,7 +4364,7 @@
     <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C28" s="35"/>
       <c r="D28" s="46" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E28" s="37" t="s">
         <v>1</v>
@@ -4251,10 +4379,10 @@
         <v>1181.1400000000001</v>
       </c>
       <c r="J28" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L28" s="38">
         <f t="shared" si="1"/>
@@ -4282,7 +4410,7 @@
     <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C29" s="35"/>
       <c r="D29" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>1</v>
@@ -4299,10 +4427,10 @@
         <v>224.24</v>
       </c>
       <c r="J29" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K29" s="37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L29" s="38">
         <f t="shared" si="1"/>
@@ -4329,10 +4457,10 @@
     </row>
     <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C30" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D30" s="46" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>1</v>
@@ -4347,10 +4475,10 @@
         <v>279</v>
       </c>
       <c r="J30" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L30" s="38">
         <f t="shared" si="1"/>
@@ -4378,7 +4506,7 @@
     <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C31" s="35"/>
       <c r="D31" s="36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E31" s="37" t="s">
         <v>1</v>
@@ -4395,10 +4523,10 @@
         <v>22.45</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K31" s="37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L31" s="38">
         <f t="shared" si="1"/>
@@ -4424,7 +4552,7 @@
     <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C32" s="35"/>
       <c r="D32" s="46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E32" s="37" t="s">
         <v>1</v>
@@ -4441,10 +4569,10 @@
         <v>60</v>
       </c>
       <c r="J32" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L32" s="38">
         <f t="shared" si="1"/>
@@ -4470,7 +4598,7 @@
     <row r="33" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C33" s="35"/>
       <c r="D33" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E33" s="37" t="s">
         <v>1</v>
@@ -4487,10 +4615,10 @@
         <v>395.54</v>
       </c>
       <c r="J33" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L33" s="38">
         <f t="shared" si="1"/>
@@ -4516,7 +4644,7 @@
     <row r="34" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C34" s="35"/>
       <c r="D34" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E34" s="37" t="s">
         <v>1</v>
@@ -4533,10 +4661,10 @@
         <v>170</v>
       </c>
       <c r="J34" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L34" s="38">
         <f t="shared" si="1"/>
@@ -4562,7 +4690,7 @@
     <row r="35" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C35" s="35"/>
       <c r="D35" s="46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E35" s="37" t="s">
         <v>1</v>
@@ -4579,10 +4707,10 @@
         <v>225</v>
       </c>
       <c r="J35" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K35" s="37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L35" s="38">
         <f t="shared" si="1"/>
@@ -4608,7 +4736,7 @@
     <row r="36" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C36" s="35"/>
       <c r="D36" s="36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E36" s="37" t="s">
         <v>1</v>
@@ -4625,10 +4753,10 @@
         <v>166.15</v>
       </c>
       <c r="J36" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K36" s="37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L36" s="38">
         <f t="shared" si="1"/>
@@ -4654,7 +4782,7 @@
     <row r="37" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C37" s="35"/>
       <c r="D37" s="36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E37" s="37" t="s">
         <v>1</v>
@@ -4671,10 +4799,10 @@
         <v>19.899999999999999</v>
       </c>
       <c r="J37" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L37" s="38">
         <f t="shared" si="1"/>
@@ -4700,7 +4828,7 @@
     <row r="38" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C38" s="35"/>
       <c r="D38" s="46" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>1</v>
@@ -4715,10 +4843,10 @@
         <v>284.05</v>
       </c>
       <c r="J38" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L38" s="38">
         <f t="shared" si="1"/>
@@ -4744,7 +4872,7 @@
     <row r="39" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C39" s="35"/>
       <c r="D39" s="46" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E39" s="37" t="s">
         <v>1</v>
@@ -4759,10 +4887,10 @@
         <v>110</v>
       </c>
       <c r="J39" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K39" s="38" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L39" s="38">
         <f t="shared" si="1"/>
@@ -4788,7 +4916,7 @@
     <row r="40" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C40" s="35"/>
       <c r="D40" s="46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E40" s="37" t="s">
         <v>1</v>
@@ -4803,10 +4931,10 @@
         <v>118.4</v>
       </c>
       <c r="J40" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K40" s="38" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L40" s="38">
         <f t="shared" si="1"/>
@@ -4829,7 +4957,7 @@
     <row r="41" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C41" s="35"/>
       <c r="D41" s="36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E41" s="37" t="s">
         <v>1</v>
@@ -4844,10 +4972,10 @@
         <v>26.9</v>
       </c>
       <c r="J41" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K41" s="37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L41" s="38">
         <f t="shared" si="1"/>
@@ -4873,7 +5001,7 @@
     <row r="42" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C42" s="35"/>
       <c r="D42" s="46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E42" s="37" t="s">
         <v>1</v>
@@ -4888,10 +5016,10 @@
         <v>70</v>
       </c>
       <c r="J42" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K42" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L42" s="38">
         <f t="shared" si="1"/>
@@ -4914,7 +5042,7 @@
     <row r="43" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C43" s="35"/>
       <c r="D43" s="66" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E43" s="37" t="s">
         <v>1</v>
@@ -4926,21 +5054,21 @@
         <v>1</v>
       </c>
       <c r="I43" s="38">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="J43" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K43" s="38" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L43" s="38">
         <f t="shared" si="1"/>
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="M43" s="38">
         <f t="shared" si="2"/>
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="N43" s="39">
         <v>1</v>
@@ -4958,7 +5086,7 @@
     <row r="44" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C44" s="35"/>
       <c r="D44" s="46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E44" s="37" t="s">
         <v>1</v>
@@ -4973,10 +5101,10 @@
         <v>60</v>
       </c>
       <c r="J44" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K44" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L44" s="38">
         <f t="shared" si="1"/>
@@ -5004,7 +5132,7 @@
     <row r="45" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C45" s="35"/>
       <c r="D45" s="46" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E45" s="37" t="s">
         <v>1</v>
@@ -5021,10 +5149,10 @@
         <v>10</v>
       </c>
       <c r="J45" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K45" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L45" s="38">
         <f t="shared" si="1"/>
@@ -5052,7 +5180,7 @@
     <row r="46" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C46" s="35"/>
       <c r="D46" s="46" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E46" s="37" t="s">
         <v>1</v>
@@ -5067,10 +5195,10 @@
         <v>90</v>
       </c>
       <c r="J46" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K46" s="38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L46" s="38">
         <f t="shared" si="1"/>
@@ -5098,7 +5226,7 @@
     <row r="47" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C47" s="35"/>
       <c r="D47" s="46" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E47" s="37" t="s">
         <v>1</v>
@@ -5115,10 +5243,10 @@
         <v>172.8</v>
       </c>
       <c r="J47" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K47" s="38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L47" s="38">
         <f t="shared" si="1"/>
@@ -5146,7 +5274,7 @@
     <row r="48" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C48" s="35"/>
       <c r="D48" s="46" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E48" s="37" t="s">
         <v>1</v>
@@ -5161,10 +5289,10 @@
         <v>98</v>
       </c>
       <c r="J48" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K48" s="38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L48" s="38">
         <f t="shared" ref="L48:L109" si="7">I48/N48</f>
@@ -5192,7 +5320,7 @@
     <row r="49" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C49" s="35"/>
       <c r="D49" s="46" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E49" s="37" t="s">
         <v>1</v>
@@ -5207,10 +5335,10 @@
         <v>-45</v>
       </c>
       <c r="J49" s="38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K49" s="38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L49" s="38">
         <f t="shared" si="7"/>
@@ -5238,7 +5366,7 @@
     <row r="50" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C50" s="76"/>
       <c r="D50" s="66" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E50" s="77"/>
       <c r="F50" s="77"/>
@@ -5278,7 +5406,7 @@
     <row r="51" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C51" s="35"/>
       <c r="D51" s="46" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E51" s="37" t="s">
         <v>1</v>
@@ -5293,10 +5421,10 @@
         <v>120</v>
       </c>
       <c r="J51" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K51" s="38" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L51" s="38">
         <f t="shared" si="7"/>
@@ -5324,7 +5452,7 @@
     <row r="52" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C52" s="35"/>
       <c r="D52" s="46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E52" s="37" t="s">
         <v>1</v>
@@ -5341,10 +5469,10 @@
         <v>150</v>
       </c>
       <c r="J52" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K52" s="38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L52" s="38">
         <f t="shared" si="7"/>
@@ -5372,7 +5500,7 @@
     <row r="53" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C53" s="35"/>
       <c r="D53" s="46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E53" s="37" t="s">
         <v>1</v>
@@ -5387,10 +5515,10 @@
         <v>60</v>
       </c>
       <c r="J53" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K53" s="38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L53" s="38">
         <f t="shared" si="7"/>
@@ -5418,7 +5546,7 @@
     <row r="54" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C54" s="35"/>
       <c r="D54" s="46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E54" s="37" t="s">
         <v>1</v>
@@ -5433,10 +5561,10 @@
         <v>-75</v>
       </c>
       <c r="J54" s="38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K54" s="38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L54" s="38">
         <f t="shared" si="7"/>
@@ -5464,7 +5592,7 @@
     <row r="55" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C55" s="35"/>
       <c r="D55" s="46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E55" s="37" t="s">
         <v>1</v>
@@ -5481,10 +5609,10 @@
         <v>60</v>
       </c>
       <c r="J55" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K55" s="38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L55" s="38">
         <f t="shared" si="7"/>
@@ -5512,7 +5640,7 @@
     <row r="56" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C56" s="35"/>
       <c r="D56" s="46" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E56" s="37" t="s">
         <v>1</v>
@@ -5530,10 +5658,10 @@
         <v>259.02</v>
       </c>
       <c r="J56" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K56" s="38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L56" s="38">
         <f t="shared" si="7"/>
@@ -5561,7 +5689,7 @@
     <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="35"/>
       <c r="D57" s="46" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E57" s="37" t="s">
         <v>1</v>
@@ -5578,10 +5706,10 @@
         <v>68</v>
       </c>
       <c r="J57" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K57" s="38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L57" s="38">
         <f t="shared" si="7"/>
@@ -5609,7 +5737,7 @@
     <row r="58" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C58" s="35"/>
       <c r="D58" s="46" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E58" s="37" t="s">
         <v>1</v>
@@ -5626,10 +5754,10 @@
         <v>78</v>
       </c>
       <c r="J58" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K58" s="38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L58" s="38">
         <f t="shared" si="7"/>
@@ -5657,7 +5785,7 @@
     <row r="59" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C59" s="35"/>
       <c r="D59" s="46" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E59" s="37" t="s">
         <v>1</v>
@@ -5672,10 +5800,10 @@
         <v>197.43</v>
       </c>
       <c r="J59" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K59" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L59" s="38">
         <f t="shared" si="7"/>
@@ -5703,7 +5831,7 @@
     <row r="60" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C60" s="35"/>
       <c r="D60" s="46" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E60" s="37" t="s">
         <v>1</v>
@@ -5718,10 +5846,10 @@
         <v>421.48</v>
       </c>
       <c r="J60" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K60" s="38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L60" s="38">
         <f t="shared" si="7"/>
@@ -5749,7 +5877,7 @@
     <row r="61" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C61" s="35"/>
       <c r="D61" s="46" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E61" s="37" t="s">
         <v>1</v>
@@ -5764,10 +5892,10 @@
         <v>37</v>
       </c>
       <c r="J61" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K61" s="38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L61" s="38">
         <f t="shared" si="7"/>
@@ -5795,7 +5923,7 @@
     <row r="62" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C62" s="35"/>
       <c r="D62" s="46" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E62" s="37" t="s">
         <v>1</v>
@@ -5810,10 +5938,10 @@
         <v>-370</v>
       </c>
       <c r="J62" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K62" s="38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L62" s="38">
         <f t="shared" si="7"/>
@@ -5841,7 +5969,7 @@
     <row r="63" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C63" s="35"/>
       <c r="D63" s="46" t="s">
-        <v>246</v>
+        <v>129</v>
       </c>
       <c r="E63" s="37" t="s">
         <v>1</v>
@@ -5856,10 +5984,10 @@
         <v>520</v>
       </c>
       <c r="J63" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K63" s="38" t="s">
-        <v>247</v>
+        <v>130</v>
       </c>
       <c r="L63" s="38">
         <f t="shared" si="7"/>
@@ -5887,7 +6015,7 @@
     <row r="64" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C64" s="35"/>
       <c r="D64" s="46" t="s">
-        <v>248</v>
+        <v>131</v>
       </c>
       <c r="E64" s="37" t="s">
         <v>1</v>
@@ -5904,10 +6032,10 @@
         <v>91.8</v>
       </c>
       <c r="J64" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L64" s="38">
         <f t="shared" si="7"/>
@@ -5920,7 +6048,9 @@
       <c r="N64" s="39">
         <v>1</v>
       </c>
-      <c r="O64" s="35"/>
+      <c r="O64" s="64">
+        <v>46329</v>
+      </c>
       <c r="P64" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5933,7 +6063,7 @@
     <row r="65" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C65" s="35"/>
       <c r="D65" s="46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E65" s="37" t="s">
         <v>1</v>
@@ -5950,10 +6080,10 @@
         <v>117.28</v>
       </c>
       <c r="J65" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K65" s="38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L65" s="38">
         <f t="shared" si="7"/>
@@ -5966,7 +6096,9 @@
       <c r="N65" s="39">
         <v>1</v>
       </c>
-      <c r="O65" s="35"/>
+      <c r="O65" s="64">
+        <v>46329</v>
+      </c>
       <c r="P65" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5979,7 +6111,7 @@
     <row r="66" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C66" s="35"/>
       <c r="D66" s="46" t="s">
-        <v>249</v>
+        <v>132</v>
       </c>
       <c r="E66" s="37" t="s">
         <v>1</v>
@@ -5994,10 +6126,10 @@
         <v>25.97</v>
       </c>
       <c r="J66" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L66" s="38">
         <f t="shared" si="7"/>
@@ -6010,7 +6142,9 @@
       <c r="N66" s="39">
         <v>1</v>
       </c>
-      <c r="O66" s="35"/>
+      <c r="O66" s="64">
+        <v>46329</v>
+      </c>
       <c r="P66" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6023,7 +6157,7 @@
     <row r="67" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C67" s="35"/>
       <c r="D67" s="46" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="E67" s="37" t="s">
         <v>1</v>
@@ -6041,10 +6175,10 @@
         <v>203</v>
       </c>
       <c r="J67" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K67" s="38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L67" s="38">
         <f t="shared" si="7"/>
@@ -6057,7 +6191,9 @@
       <c r="N67" s="39">
         <v>1</v>
       </c>
-      <c r="O67" s="35"/>
+      <c r="O67" s="64">
+        <v>46329</v>
+      </c>
       <c r="P67" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6070,7 +6206,7 @@
     <row r="68" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C68" s="35"/>
       <c r="D68" s="46" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="E68" s="37" t="s">
         <v>1</v>
@@ -6085,10 +6221,10 @@
         <v>52</v>
       </c>
       <c r="J68" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K68" s="38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L68" s="38">
         <f t="shared" si="7"/>
@@ -6101,7 +6237,9 @@
       <c r="N68" s="39">
         <v>1</v>
       </c>
-      <c r="O68" s="35"/>
+      <c r="O68" s="64">
+        <v>46329</v>
+      </c>
       <c r="P68" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6114,7 +6252,7 @@
     <row r="69" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C69" s="35"/>
       <c r="D69" s="46" t="s">
-        <v>250</v>
+        <v>134</v>
       </c>
       <c r="E69" s="37" t="s">
         <v>1</v>
@@ -6131,10 +6269,10 @@
         <v>101.6</v>
       </c>
       <c r="J69" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K69" s="38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L69" s="38">
         <f t="shared" si="7"/>
@@ -6147,7 +6285,9 @@
       <c r="N69" s="39">
         <v>1</v>
       </c>
-      <c r="O69" s="35"/>
+      <c r="O69" s="64">
+        <v>46329</v>
+      </c>
       <c r="P69" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6160,7 +6300,7 @@
     <row r="70" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C70" s="35"/>
       <c r="D70" s="46" t="s">
-        <v>251</v>
+        <v>135</v>
       </c>
       <c r="E70" s="37" t="s">
         <v>1</v>
@@ -6177,10 +6317,10 @@
         <v>175</v>
       </c>
       <c r="J70" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L70" s="38">
         <f t="shared" si="7"/>
@@ -6193,7 +6333,9 @@
       <c r="N70" s="39">
         <v>1</v>
       </c>
-      <c r="O70" s="35"/>
+      <c r="O70" s="64">
+        <v>46329</v>
+      </c>
       <c r="P70" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6206,7 +6348,7 @@
     <row r="71" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C71" s="35"/>
       <c r="D71" s="46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E71" s="37" t="s">
         <v>1</v>
@@ -6221,10 +6363,10 @@
         <v>-60</v>
       </c>
       <c r="J71" s="38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K71" s="38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L71" s="38">
         <f t="shared" si="7"/>
@@ -6237,7 +6379,9 @@
       <c r="N71" s="39">
         <v>1</v>
       </c>
-      <c r="O71" s="35"/>
+      <c r="O71" s="64">
+        <v>46329</v>
+      </c>
       <c r="P71" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6250,7 +6394,7 @@
     <row r="72" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C72" s="35"/>
       <c r="D72" s="46" t="s">
-        <v>252</v>
+        <v>136</v>
       </c>
       <c r="E72" s="37" t="s">
         <v>1</v>
@@ -6265,10 +6409,10 @@
         <v>-150</v>
       </c>
       <c r="J72" s="38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L72" s="38">
         <f t="shared" si="7"/>
@@ -6281,7 +6425,9 @@
       <c r="N72" s="39">
         <v>1</v>
       </c>
-      <c r="O72" s="35"/>
+      <c r="O72" s="64">
+        <v>46329</v>
+      </c>
       <c r="P72" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6294,7 +6440,7 @@
     <row r="73" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C73" s="35"/>
       <c r="D73" s="46" t="s">
-        <v>253</v>
+        <v>137</v>
       </c>
       <c r="E73" s="37" t="s">
         <v>1</v>
@@ -6309,10 +6455,10 @@
         <v>-100</v>
       </c>
       <c r="J73" s="38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K73" s="38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L73" s="38">
         <f t="shared" si="7"/>
@@ -6325,7 +6471,9 @@
       <c r="N73" s="39">
         <v>1</v>
       </c>
-      <c r="O73" s="35"/>
+      <c r="O73" s="64">
+        <v>46329</v>
+      </c>
       <c r="P73" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6337,32 +6485,46 @@
     </row>
     <row r="74" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C74" s="35"/>
-      <c r="D74" s="46"/>
-      <c r="E74" s="37"/>
-      <c r="F74" s="37"/>
+      <c r="D74" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E74" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G74" s="37"/>
       <c r="H74" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I74" s="38"/>
-      <c r="J74" s="38"/>
-      <c r="K74" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I74" s="38">
+        <v>253.48</v>
+      </c>
+      <c r="J74" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="K74" s="38" t="s">
+        <v>60</v>
+      </c>
       <c r="L74" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M74" s="38" t="str">
+        <v>84.493333333333325</v>
+      </c>
+      <c r="M74" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>42.246666666666663</v>
       </c>
       <c r="N74" s="39">
-        <v>1</v>
-      </c>
-      <c r="O74" s="35"/>
-      <c r="P74" s="35" t="str">
+        <v>3</v>
+      </c>
+      <c r="O74" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P74" s="35">
         <f t="shared" si="9"/>
-        <v/>
+        <v>46390</v>
       </c>
       <c r="Q74" s="37" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -6371,29 +6533,43 @@
     </row>
     <row r="75" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C75" s="35"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
+      <c r="D75" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="E75" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G75" s="37"/>
       <c r="H75" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I75" s="38"/>
-      <c r="J75" s="38"/>
-      <c r="K75" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I75" s="38">
+        <v>41</v>
+      </c>
+      <c r="J75" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K75" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="L75" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M75" s="38" t="str">
+        <v>41</v>
+      </c>
+      <c r="M75" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>20.5</v>
       </c>
       <c r="N75" s="39">
         <v>1</v>
       </c>
-      <c r="O75" s="35"/>
+      <c r="O75" s="64">
+        <v>46329</v>
+      </c>
       <c r="P75" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6405,29 +6581,43 @@
     </row>
     <row r="76" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C76" s="35"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
+      <c r="D76" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="E76" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G76" s="37"/>
       <c r="H76" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I76" s="38"/>
-      <c r="J76" s="38"/>
-      <c r="K76" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I76" s="38">
+        <v>120</v>
+      </c>
+      <c r="J76" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K76" s="38" t="s">
+        <v>121</v>
+      </c>
       <c r="L76" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M76" s="38" t="str">
+        <v>120</v>
+      </c>
+      <c r="M76" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>60</v>
       </c>
       <c r="N76" s="39">
         <v>1</v>
       </c>
-      <c r="O76" s="35"/>
+      <c r="O76" s="64">
+        <v>46329</v>
+      </c>
       <c r="P76" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6439,29 +6629,44 @@
     </row>
     <row r="77" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C77" s="35"/>
-      <c r="D77" s="46"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
+      <c r="D77" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="E77" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G77" s="37"/>
       <c r="H77" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I77" s="38"/>
-      <c r="J77" s="38"/>
-      <c r="K77" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I77" s="38">
+        <f>58.8+52.4</f>
+        <v>111.19999999999999</v>
+      </c>
+      <c r="J77" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K77" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="L77" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M77" s="38" t="str">
+        <v>111.19999999999999</v>
+      </c>
+      <c r="M77" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>55.599999999999994</v>
       </c>
       <c r="N77" s="39">
         <v>1</v>
       </c>
-      <c r="O77" s="35"/>
+      <c r="O77" s="64">
+        <v>46329</v>
+      </c>
       <c r="P77" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6473,29 +6678,41 @@
     </row>
     <row r="78" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C78" s="35"/>
-      <c r="D78" s="46"/>
+      <c r="D78" s="46" t="s">
+        <v>142</v>
+      </c>
       <c r="E78" s="37"/>
-      <c r="F78" s="37"/>
+      <c r="F78" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G78" s="37"/>
       <c r="H78" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I78" s="38"/>
-      <c r="J78" s="38"/>
-      <c r="K78" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I78" s="38">
+        <v>115</v>
+      </c>
+      <c r="J78" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K78" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="L78" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M78" s="38" t="str">
+        <v>115</v>
+      </c>
+      <c r="M78" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>115</v>
       </c>
       <c r="N78" s="39">
         <v>1</v>
       </c>
-      <c r="O78" s="35"/>
+      <c r="O78" s="64">
+        <v>46329</v>
+      </c>
       <c r="P78" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6507,32 +6724,46 @@
     </row>
     <row r="79" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C79" s="35"/>
-      <c r="D79" s="46"/>
-      <c r="E79" s="37"/>
-      <c r="F79" s="37"/>
+      <c r="D79" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="E79" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F79" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G79" s="37"/>
       <c r="H79" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I79" s="38"/>
-      <c r="J79" s="38"/>
-      <c r="K79" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I79" s="38">
+        <v>200</v>
+      </c>
+      <c r="J79" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="K79" s="38" t="s">
+        <v>60</v>
+      </c>
       <c r="L79" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M79" s="38" t="str">
+        <v>50</v>
+      </c>
+      <c r="M79" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>25</v>
       </c>
       <c r="N79" s="39">
-        <v>1</v>
-      </c>
-      <c r="O79" s="35"/>
-      <c r="P79" s="35" t="str">
+        <v>4</v>
+      </c>
+      <c r="O79" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P79" s="35">
         <f t="shared" si="9"/>
-        <v/>
+        <v>46421</v>
       </c>
       <c r="Q79" s="37" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -6541,29 +6772,43 @@
     </row>
     <row r="80" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C80" s="35"/>
-      <c r="D80" s="46"/>
-      <c r="E80" s="37"/>
-      <c r="F80" s="37"/>
+      <c r="D80" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="E80" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F80" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G80" s="37"/>
       <c r="H80" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I80" s="38"/>
-      <c r="J80" s="38"/>
-      <c r="K80" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I80" s="38">
+        <v>136</v>
+      </c>
+      <c r="J80" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K80" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="L80" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M80" s="38" t="str">
+        <v>136</v>
+      </c>
+      <c r="M80" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>68</v>
       </c>
       <c r="N80" s="39">
         <v>1</v>
       </c>
-      <c r="O80" s="35"/>
+      <c r="O80" s="64">
+        <v>46329</v>
+      </c>
       <c r="P80" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6575,29 +6820,43 @@
     </row>
     <row r="81" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C81" s="35"/>
-      <c r="D81" s="46"/>
-      <c r="E81" s="37"/>
-      <c r="F81" s="37"/>
+      <c r="D81" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="E81" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F81" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G81" s="37"/>
       <c r="H81" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I81" s="38"/>
-      <c r="J81" s="38"/>
-      <c r="K81" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I81" s="38">
+        <v>62</v>
+      </c>
+      <c r="J81" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K81" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="L81" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M81" s="38" t="str">
+        <v>62</v>
+      </c>
+      <c r="M81" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>31</v>
       </c>
       <c r="N81" s="39">
         <v>1</v>
       </c>
-      <c r="O81" s="35"/>
+      <c r="O81" s="64">
+        <v>46329</v>
+      </c>
       <c r="P81" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6609,29 +6868,41 @@
     </row>
     <row r="82" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C82" s="35"/>
-      <c r="D82" s="46"/>
-      <c r="E82" s="37"/>
+      <c r="D82" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="E82" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F82" s="37"/>
       <c r="G82" s="37"/>
       <c r="H82" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I82" s="38"/>
-      <c r="J82" s="38"/>
-      <c r="K82" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I82" s="38">
+        <v>20</v>
+      </c>
+      <c r="J82" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K82" s="38" t="s">
+        <v>107</v>
+      </c>
       <c r="L82" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M82" s="38" t="str">
+        <v>20</v>
+      </c>
+      <c r="M82" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>20</v>
       </c>
       <c r="N82" s="39">
         <v>1</v>
       </c>
-      <c r="O82" s="35"/>
+      <c r="O82" s="64">
+        <v>46329</v>
+      </c>
       <c r="P82" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6643,29 +6914,41 @@
     </row>
     <row r="83" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C83" s="35"/>
-      <c r="D83" s="46"/>
-      <c r="E83" s="37"/>
+      <c r="D83" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F83" s="37"/>
       <c r="G83" s="37"/>
       <c r="H83" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I83" s="38"/>
-      <c r="J83" s="38"/>
-      <c r="K83" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I83" s="38">
+        <v>-93</v>
+      </c>
+      <c r="J83" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="K83" s="38" t="s">
+        <v>113</v>
+      </c>
       <c r="L83" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M83" s="38" t="str">
+        <v>-93</v>
+      </c>
+      <c r="M83" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-93</v>
       </c>
       <c r="N83" s="39">
         <v>1</v>
       </c>
-      <c r="O83" s="35"/>
+      <c r="O83" s="64">
+        <v>46329</v>
+      </c>
       <c r="P83" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6677,29 +6960,43 @@
     </row>
     <row r="84" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C84" s="35"/>
-      <c r="D84" s="46"/>
-      <c r="E84" s="37"/>
-      <c r="F84" s="37"/>
+      <c r="D84" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="E84" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G84" s="37"/>
       <c r="H84" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I84" s="38"/>
-      <c r="J84" s="38"/>
-      <c r="K84" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I84" s="38">
+        <v>50</v>
+      </c>
+      <c r="J84" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K84" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="L84" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M84" s="38" t="str">
+        <v>50</v>
+      </c>
+      <c r="M84" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>25</v>
       </c>
       <c r="N84" s="39">
         <v>1</v>
       </c>
-      <c r="O84" s="35"/>
+      <c r="O84" s="64">
+        <v>46329</v>
+      </c>
       <c r="P84" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6711,29 +7008,43 @@
     </row>
     <row r="85" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C85" s="35"/>
-      <c r="D85" s="46"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="37"/>
+      <c r="D85" s="46" t="s">
+        <v>149</v>
+      </c>
+      <c r="E85" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F85" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G85" s="37"/>
       <c r="H85" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I85" s="38"/>
-      <c r="J85" s="38"/>
-      <c r="K85" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I85" s="38">
+        <v>235</v>
+      </c>
+      <c r="J85" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K85" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="L85" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M85" s="38" t="str">
+        <v>235</v>
+      </c>
+      <c r="M85" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>117.5</v>
       </c>
       <c r="N85" s="39">
         <v>1</v>
       </c>
-      <c r="O85" s="35"/>
+      <c r="O85" s="64">
+        <v>46329</v>
+      </c>
       <c r="P85" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6745,29 +7056,41 @@
     </row>
     <row r="86" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C86" s="35"/>
-      <c r="D86" s="46"/>
-      <c r="E86" s="37"/>
+      <c r="D86" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E86" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F86" s="37"/>
       <c r="G86" s="37"/>
       <c r="H86" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I86" s="38"/>
-      <c r="J86" s="38"/>
-      <c r="K86" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I86" s="38">
+        <v>-117.5</v>
+      </c>
+      <c r="J86" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="K86" s="38" t="s">
+        <v>113</v>
+      </c>
       <c r="L86" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M86" s="38" t="str">
+        <v>-117.5</v>
+      </c>
+      <c r="M86" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-117.5</v>
       </c>
       <c r="N86" s="39">
         <v>1</v>
       </c>
-      <c r="O86" s="35"/>
+      <c r="O86" s="64">
+        <v>46329</v>
+      </c>
       <c r="P86" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6779,32 +7102,44 @@
     </row>
     <row r="87" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C87" s="35"/>
-      <c r="D87" s="46"/>
-      <c r="E87" s="37"/>
+      <c r="D87" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="E87" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F87" s="37"/>
       <c r="G87" s="37"/>
       <c r="H87" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I87" s="38"/>
-      <c r="J87" s="38"/>
-      <c r="K87" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I87" s="38">
+        <v>562.73</v>
+      </c>
+      <c r="J87" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="K87" s="38" t="s">
+        <v>130</v>
+      </c>
       <c r="L87" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M87" s="38" t="str">
+        <v>281.36500000000001</v>
+      </c>
+      <c r="M87" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>281.36500000000001</v>
       </c>
       <c r="N87" s="39">
-        <v>1</v>
-      </c>
-      <c r="O87" s="35"/>
-      <c r="P87" s="35" t="str">
+        <v>2</v>
+      </c>
+      <c r="O87" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P87" s="35">
         <f t="shared" si="9"/>
-        <v/>
+        <v>46359</v>
       </c>
       <c r="Q87" s="37" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -6813,24 +7148,34 @@
     </row>
     <row r="88" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C88" s="35"/>
-      <c r="D88" s="46"/>
+      <c r="D88" s="46" t="s">
+        <v>118</v>
+      </c>
       <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
+      <c r="F88" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G88" s="37"/>
       <c r="H88" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I88" s="38"/>
-      <c r="J88" s="38"/>
-      <c r="K88" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I88" s="38">
+        <v>50</v>
+      </c>
+      <c r="J88" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K88" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="L88" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M88" s="38" t="str">
+        <v>50</v>
+      </c>
+      <c r="M88" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>50</v>
       </c>
       <c r="N88" s="39">
         <v>1</v>
@@ -6847,24 +7192,36 @@
     </row>
     <row r="89" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C89" s="35"/>
-      <c r="D89" s="46"/>
-      <c r="E89" s="37"/>
-      <c r="F89" s="37"/>
+      <c r="D89" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="E89" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F89" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G89" s="37"/>
       <c r="H89" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I89" s="38"/>
-      <c r="J89" s="38"/>
-      <c r="K89" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I89" s="38">
+        <v>26</v>
+      </c>
+      <c r="J89" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K89" s="38" t="s">
+        <v>153</v>
+      </c>
       <c r="L89" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M89" s="38" t="str">
+        <v>26</v>
+      </c>
+      <c r="M89" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>13</v>
       </c>
       <c r="N89" s="39">
         <v>1</v>
@@ -6881,24 +7238,36 @@
     </row>
     <row r="90" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C90" s="35"/>
-      <c r="D90" s="46"/>
-      <c r="E90" s="37"/>
-      <c r="F90" s="37"/>
+      <c r="D90" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="E90" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F90" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G90" s="37"/>
       <c r="H90" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I90" s="38"/>
-      <c r="J90" s="38"/>
-      <c r="K90" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I90" s="38">
+        <v>130</v>
+      </c>
+      <c r="J90" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K90" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="L90" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M90" s="38" t="str">
+        <v>130</v>
+      </c>
+      <c r="M90" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>65</v>
       </c>
       <c r="N90" s="39">
         <v>1</v>
@@ -6915,24 +7284,34 @@
     </row>
     <row r="91" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C91" s="35"/>
-      <c r="D91" s="46"/>
-      <c r="E91" s="37"/>
+      <c r="D91" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="E91" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F91" s="37"/>
       <c r="G91" s="37"/>
       <c r="H91" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I91" s="38"/>
-      <c r="J91" s="38"/>
-      <c r="K91" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I91" s="38">
+        <v>-65</v>
+      </c>
+      <c r="J91" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="K91" s="38" t="s">
+        <v>113</v>
+      </c>
       <c r="L91" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M91" s="38" t="str">
+        <v>-65</v>
+      </c>
+      <c r="M91" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-65</v>
       </c>
       <c r="N91" s="39">
         <v>1</v>
@@ -6949,24 +7328,34 @@
     </row>
     <row r="92" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C92" s="35"/>
-      <c r="D92" s="46"/>
-      <c r="E92" s="37"/>
+      <c r="D92" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="E92" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F92" s="37"/>
       <c r="G92" s="37"/>
       <c r="H92" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I92" s="38"/>
-      <c r="J92" s="38"/>
-      <c r="K92" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I92" s="38">
+        <v>82</v>
+      </c>
+      <c r="J92" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K92" s="38" t="s">
+        <v>153</v>
+      </c>
       <c r="L92" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M92" s="38" t="str">
+        <v>82</v>
+      </c>
+      <c r="M92" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>82</v>
       </c>
       <c r="N92" s="39">
         <v>1</v>
@@ -6983,24 +7372,34 @@
     </row>
     <row r="93" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C93" s="35"/>
-      <c r="D93" s="46"/>
-      <c r="E93" s="37"/>
+      <c r="D93" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="E93" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F93" s="37"/>
       <c r="G93" s="37"/>
       <c r="H93" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I93" s="38"/>
-      <c r="J93" s="38"/>
-      <c r="K93" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I93" s="38">
+        <v>58</v>
+      </c>
+      <c r="J93" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K93" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="L93" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M93" s="38" t="str">
+        <v>58</v>
+      </c>
+      <c r="M93" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>58</v>
       </c>
       <c r="N93" s="39">
         <v>1</v>
@@ -7017,24 +7416,32 @@
     </row>
     <row r="94" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C94" s="35"/>
-      <c r="D94" s="46"/>
-      <c r="E94" s="37"/>
-      <c r="F94" s="37"/>
+      <c r="D94" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="E94" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F94" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G94" s="37"/>
       <c r="H94" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I94" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I94" s="38">
+        <v>89</v>
+      </c>
       <c r="J94" s="38"/>
       <c r="K94" s="38"/>
       <c r="L94" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M94" s="38" t="str">
+        <v>89</v>
+      </c>
+      <c r="M94" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>44.5</v>
       </c>
       <c r="N94" s="39">
         <v>1</v>
@@ -7051,24 +7458,31 @@
     </row>
     <row r="95" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C95" s="35"/>
-      <c r="D95" s="46"/>
-      <c r="E95" s="37"/>
+      <c r="D95" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="E95" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F95" s="37"/>
       <c r="G95" s="37"/>
       <c r="H95" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I95" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I95" s="38">
+        <f>58+48+48</f>
+        <v>154</v>
+      </c>
       <c r="J95" s="38"/>
       <c r="K95" s="38"/>
       <c r="L95" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M95" s="38" t="str">
+        <v>154</v>
+      </c>
+      <c r="M95" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>154</v>
       </c>
       <c r="N95" s="39">
         <v>1</v>
@@ -7085,24 +7499,30 @@
     </row>
     <row r="96" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C96" s="35"/>
-      <c r="D96" s="46"/>
+      <c r="D96" s="46" t="s">
+        <v>281</v>
+      </c>
       <c r="E96" s="37"/>
-      <c r="F96" s="37"/>
+      <c r="F96" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G96" s="37"/>
       <c r="H96" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I96" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I96" s="38">
+        <v>48</v>
+      </c>
       <c r="J96" s="38"/>
       <c r="K96" s="38"/>
       <c r="L96" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M96" s="38" t="str">
+        <v>48</v>
+      </c>
+      <c r="M96" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>48</v>
       </c>
       <c r="N96" s="39">
         <v>1</v>
@@ -7119,24 +7539,32 @@
     </row>
     <row r="97" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C97" s="35"/>
-      <c r="D97" s="46"/>
-      <c r="E97" s="37"/>
-      <c r="F97" s="37"/>
+      <c r="D97" s="46" t="s">
+        <v>282</v>
+      </c>
+      <c r="E97" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F97" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G97" s="37"/>
       <c r="H97" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I97" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I97" s="38">
+        <v>40</v>
+      </c>
       <c r="J97" s="38"/>
       <c r="K97" s="38"/>
       <c r="L97" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M97" s="38" t="str">
+        <v>40</v>
+      </c>
+      <c r="M97" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>20</v>
       </c>
       <c r="N97" s="39">
         <v>1</v>
@@ -7153,24 +7581,32 @@
     </row>
     <row r="98" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C98" s="35"/>
-      <c r="D98" s="46"/>
-      <c r="E98" s="37"/>
-      <c r="F98" s="37"/>
+      <c r="D98" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="E98" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F98" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G98" s="37"/>
       <c r="H98" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I98" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I98" s="38">
+        <v>75</v>
+      </c>
       <c r="J98" s="38"/>
       <c r="K98" s="38"/>
       <c r="L98" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M98" s="38" t="str">
+        <v>75</v>
+      </c>
+      <c r="M98" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>37.5</v>
       </c>
       <c r="N98" s="39">
         <v>1</v>
@@ -7187,24 +7623,32 @@
     </row>
     <row r="99" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C99" s="35"/>
-      <c r="D99" s="46"/>
-      <c r="E99" s="37"/>
-      <c r="F99" s="37"/>
+      <c r="D99" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="E99" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F99" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G99" s="37"/>
       <c r="H99" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I99" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I99" s="38">
+        <v>-37.5</v>
+      </c>
       <c r="J99" s="38"/>
       <c r="K99" s="38"/>
       <c r="L99" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M99" s="38" t="str">
+        <v>-37.5</v>
+      </c>
+      <c r="M99" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-18.75</v>
       </c>
       <c r="N99" s="39">
         <v>1</v>
@@ -7221,24 +7665,30 @@
     </row>
     <row r="100" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C100" s="35"/>
-      <c r="D100" s="46"/>
-      <c r="E100" s="37"/>
+      <c r="D100" s="46" t="s">
+        <v>285</v>
+      </c>
+      <c r="E100" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F100" s="37"/>
       <c r="G100" s="37"/>
       <c r="H100" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I100" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I100" s="38">
+        <v>-200</v>
+      </c>
       <c r="J100" s="38"/>
       <c r="K100" s="38"/>
       <c r="L100" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M100" s="38" t="str">
+        <v>-200</v>
+      </c>
+      <c r="M100" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-200</v>
       </c>
       <c r="N100" s="39">
         <v>1</v>
@@ -8692,7 +9142,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J71:K73 J6:J142">
+  <conditionalFormatting sqref="J6:J142 J71:K73 J83:K83 J86:K86 J91:K91">
     <cfRule type="cellIs" dxfId="19" priority="6" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
@@ -8729,7 +9179,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B2:R20"/>
+  <dimension ref="B2:R21"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -8738,47 +9188,48 @@
     <col min="4" max="4" width="33.85546875" customWidth="1"/>
     <col min="5" max="10" width="13.5703125" customWidth="1"/>
     <col min="11" max="11" width="15.5703125" customWidth="1"/>
-    <col min="12" max="15" width="13.5703125" customWidth="1"/>
+    <col min="12" max="14" width="13.5703125" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="53.42578125" customWidth="1"/>
     <col min="18" max="18" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K2" s="34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M2" s="33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N2" s="33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O2" s="34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8800,28 +9251,28 @@
         <v>3235.67</v>
       </c>
       <c r="J3" s="38">
-        <f t="shared" ref="J3:J13" si="0">I3/L3</f>
+        <f t="shared" ref="J3:J14" si="0">I3/L3</f>
         <v>3235.67</v>
       </c>
       <c r="K3" s="38">
-        <f t="shared" ref="K3:K13" si="1">IFERROR(J3/H3,"")</f>
+        <f t="shared" ref="K3:K14" si="1">IFERROR(J3/H3,"")</f>
         <v>1617.835</v>
       </c>
       <c r="L3" s="37">
-        <f t="shared" ref="L3:L13" si="2">(DATEDIF(M3,N3,"m")+1)</f>
+        <f t="shared" ref="L3:L14" si="2">(DATEDIF(M3,N3,"m")+1)</f>
         <v>1</v>
       </c>
       <c r="M3" s="38"/>
       <c r="N3" s="38"/>
       <c r="O3" s="39">
-        <f t="shared" ref="O3:O13" ca="1" si="3">IFERROR(DATEDIF(M3,TODAY(),"m")+1,"")</f>
+        <f t="shared" ref="O3:O14" ca="1" si="3">IFERROR(DATEDIF(M3,TODAY(),"m")+1,"")</f>
         <v>1522</v>
       </c>
       <c r="R3" s="16"/>
     </row>
     <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="55" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="E4" s="56" t="s">
         <v>1</v>
@@ -8862,7 +9313,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>1</v>
@@ -8876,15 +9327,15 @@
         <v>2</v>
       </c>
       <c r="I5" s="38">
-        <v>440</v>
+        <v>415</v>
       </c>
       <c r="J5" s="38">
         <f t="shared" si="0"/>
-        <v>440</v>
+        <v>415</v>
       </c>
       <c r="K5" s="38">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>207.5</v>
       </c>
       <c r="L5" s="37">
         <f t="shared" si="2"/>
@@ -8900,11 +9351,11 @@
     </row>
     <row r="6" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="32">
-        <f>SUMIF($E$3:$E$34,B5,$K$3:$K$34)</f>
-        <v>2570.34</v>
+        <f>SUMIF($E$3:$E$35,B5,$K$3:$K$35)</f>
+        <v>2557.84</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>1</v>
@@ -8942,7 +9393,7 @@
     <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="60"/>
       <c r="D7" s="54" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="E7" s="36" t="s">
         <v>1</v>
@@ -8982,7 +9433,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="54" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>1</v>
@@ -9019,11 +9470,11 @@
     </row>
     <row r="9" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="61">
-        <f>SUMIF($F$3:$F$34,B8,$K$3:$K$34)</f>
-        <v>5612.34</v>
+        <f>SUMIF($F$3:$F$35,B8,$K$3:$K$35)</f>
+        <v>5899.84</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="E9" s="36" t="s">
         <v>1</v>
@@ -9061,7 +9512,7 @@
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D10" s="54" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="37" t="s">
@@ -9096,7 +9547,7 @@
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D11" s="54" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="37" t="s">
@@ -9131,7 +9582,7 @@
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D12" s="54" t="s">
-        <v>135</v>
+        <v>283</v>
       </c>
       <c r="E12" s="36"/>
       <c r="F12" s="37" t="s">
@@ -9143,18 +9594,18 @@
         <v>1</v>
       </c>
       <c r="I12" s="38">
-        <v>1292</v>
+        <v>300</v>
       </c>
       <c r="J12" s="38">
-        <f t="shared" si="0"/>
-        <v>1292</v>
+        <f t="shared" ref="J12" si="4">I12/L12</f>
+        <v>300</v>
       </c>
       <c r="K12" s="38">
-        <f t="shared" si="1"/>
-        <v>1292</v>
+        <f t="shared" ref="K12" si="5">IFERROR(J12/H12,"")</f>
+        <v>300</v>
       </c>
       <c r="L12" s="37">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="L12" si="6">(DATEDIF(M12,N12,"m")+1)</f>
         <v>1</v>
       </c>
       <c r="M12" s="38"/>
@@ -9166,29 +9617,27 @@
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D13" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="E13" s="36" t="s">
-        <v>1</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="E13" s="36"/>
       <c r="F13" s="37" t="s">
         <v>2</v>
       </c>
       <c r="G13" s="37"/>
       <c r="H13" s="37">
         <f>COUNTA(E13:G13)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" s="38">
-        <v>300</v>
+        <v>1292</v>
       </c>
       <c r="J13" s="38">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>1292</v>
       </c>
       <c r="K13" s="38">
         <f t="shared" si="1"/>
-        <v>150</v>
+        <v>1292</v>
       </c>
       <c r="L13" s="37">
         <f t="shared" si="2"/>
@@ -9202,18 +9651,41 @@
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D14" s="37"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="37"/>
+      <c r="D14" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="37"/>
-      <c r="L14" s="37"/>
+      <c r="H14" s="37">
+        <f>COUNTA(E14:G14)</f>
+        <v>2</v>
+      </c>
+      <c r="I14" s="38">
+        <v>300</v>
+      </c>
+      <c r="J14" s="38">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="K14" s="38">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="L14" s="37">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="M14" s="38"/>
       <c r="N14" s="38"/>
-      <c r="O14" s="39"/>
+      <c r="O14" s="39">
+        <f t="shared" ca="1" si="3"/>
+        <v>1522</v>
+      </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D15" s="37"/>
@@ -9298,6 +9770,20 @@
       <c r="M20" s="38"/>
       <c r="N20" s="38"/>
       <c r="O20" s="39"/>
+    </row>
+    <row r="21" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D21" s="37"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="39"/>
     </row>
   </sheetData>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9327,7 +9813,7 @@
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" s="2"/>
       <c r="N1" s="47" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9337,23 +9823,23 @@
     <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G3" s="2"/>
       <c r="L3" s="47" t="s">
-        <v>138</v>
-      </c>
-      <c r="M3" s="83" t="s">
-        <v>139</v>
+        <v>167</v>
+      </c>
+      <c r="M3" s="84" t="s">
+        <v>168</v>
       </c>
       <c r="N3" s="43">
         <f>SUM(N5:N21)</f>
-        <v>237</v>
+        <v>757</v>
       </c>
       <c r="O3" s="16"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G4" s="2"/>
       <c r="L4" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="M4" s="84"/>
+        <v>169</v>
+      </c>
+      <c r="M4" s="85"/>
       <c r="N4" s="49"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
@@ -9362,7 +9848,7 @@
       <c r="F5" s="16"/>
       <c r="G5" s="28"/>
       <c r="L5" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="N5" s="1">
         <v>100</v>
@@ -9372,7 +9858,7 @@
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G6" s="2"/>
       <c r="L6" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="N6" s="1">
         <v>137</v>
@@ -9380,50 +9866,66 @@
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G7" s="2"/>
-      <c r="N7" s="71"/>
+      <c r="L7" t="s">
+        <v>172</v>
+      </c>
+      <c r="M7" t="s">
+        <v>173</v>
+      </c>
+      <c r="N7" s="71">
+        <v>280</v>
+      </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F8" s="16"/>
       <c r="G8" s="50"/>
-      <c r="N8" s="71"/>
+      <c r="L8" t="s">
+        <v>280</v>
+      </c>
+      <c r="M8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N8" s="71">
+        <v>240</v>
+      </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F9" s="47" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="G9" s="28"/>
       <c r="N9" s="70"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F10" s="16">
         <f>SUM(G11:I11)</f>
-        <v>3000.1200000000044</v>
+        <v>6694.4000000000051</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="H10" s="51" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="I10" s="51" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="N10" s="70"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="F11" s="16">
         <f>SUM(G11:H11)</f>
-        <v>3000.1200000000044</v>
+        <v>6694.4000000000051</v>
       </c>
       <c r="G11" s="1">
         <f>G12+SUM(G14:G496)</f>
-        <v>3000.1200000000044</v>
+        <v>6694.4000000000051</v>
       </c>
       <c r="H11" s="1">
         <f>H12+SUM(H14:H496)</f>
@@ -9437,7 +9939,7 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="G12" s="1">
         <v>15250</v>
@@ -9446,7 +9948,7 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F13" s="80" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="G13" s="52"/>
       <c r="H13" s="80"/>
@@ -9455,7 +9957,7 @@
     </row>
     <row r="14" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="G14" s="53"/>
       <c r="H14" s="53"/>
@@ -9464,7 +9966,7 @@
     </row>
     <row r="15" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F15" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="G15" s="53">
         <v>773.35</v>
@@ -9475,7 +9977,7 @@
     </row>
     <row r="16" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F16" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="G16" s="53">
         <v>-5148</v>
@@ -9486,7 +9988,7 @@
     </row>
     <row r="17" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F17" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="G17" s="53">
         <v>-168</v>
@@ -9497,7 +9999,7 @@
     </row>
     <row r="18" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F18" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="G18" s="53">
         <v>-1700</v>
@@ -9508,7 +10010,7 @@
     </row>
     <row r="19" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F19" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="G19" s="53">
         <v>5148</v>
@@ -9519,7 +10021,7 @@
     </row>
     <row r="20" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F20" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="G20" s="53">
         <v>-4938</v>
@@ -9530,7 +10032,7 @@
     </row>
     <row r="21" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F21" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="G21" s="53">
         <v>-1595</v>
@@ -9541,7 +10043,7 @@
     </row>
     <row r="22" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="G22" s="53">
         <v>-4677</v>
@@ -9552,7 +10054,7 @@
     </row>
     <row r="23" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F23" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="G23" s="53">
         <v>-200</v>
@@ -9563,7 +10065,7 @@
     </row>
     <row r="24" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F24" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="G24" s="53">
         <v>4677</v>
@@ -9574,7 +10076,7 @@
     </row>
     <row r="25" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F25" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="G25" s="53">
         <v>-750</v>
@@ -9585,7 +10087,7 @@
     </row>
     <row r="26" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F26" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="G26" s="53">
         <v>-652</v>
@@ -9596,7 +10098,7 @@
     </row>
     <row r="27" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F27" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="G27" s="53">
         <v>11100</v>
@@ -9607,7 +10109,7 @@
     </row>
     <row r="28" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F28" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="G28" s="53">
         <v>-396</v>
@@ -9618,7 +10120,7 @@
     </row>
     <row r="29" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F29" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="G29" s="53">
         <v>-4211</v>
@@ -9629,7 +10131,7 @@
     </row>
     <row r="30" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F30" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="G30" s="53">
         <v>-450</v>
@@ -9640,7 +10142,7 @@
     </row>
     <row r="31" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G31" s="53">
         <v>-1197</v>
@@ -9651,7 +10153,7 @@
     </row>
     <row r="32" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F32" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="G32" s="53">
         <v>-315</v>
@@ -9662,7 +10164,7 @@
     </row>
     <row r="33" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F33" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="G33" s="53">
         <v>-830</v>
@@ -9673,7 +10175,7 @@
     </row>
     <row r="34" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F34" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="G34" s="53">
         <v>4211</v>
@@ -9684,7 +10186,7 @@
     </row>
     <row r="35" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F35" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="G35" s="53">
         <v>-200</v>
@@ -9695,7 +10197,7 @@
     </row>
     <row r="36" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F36" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="G36" s="53">
         <v>10000</v>
@@ -9706,7 +10208,7 @@
     </row>
     <row r="37" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F37" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="G37" s="53">
         <v>-200</v>
@@ -9717,7 +10219,7 @@
     </row>
     <row r="38" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F38" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="G38" s="53">
         <v>-381</v>
@@ -9728,7 +10230,7 @@
     </row>
     <row r="39" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F39" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="G39" s="53">
         <v>-4911</v>
@@ -9740,7 +10242,7 @@
     <row r="40" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="G40" s="53">
         <v>-5700</v>
@@ -9751,7 +10253,7 @@
     </row>
     <row r="41" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F41" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="G41" s="53">
         <v>-400</v>
@@ -9762,7 +10264,7 @@
     </row>
     <row r="42" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F42" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="G42" s="53">
         <v>-450</v>
@@ -9773,7 +10275,7 @@
     </row>
     <row r="43" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F43" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="G43" s="53">
         <v>-640</v>
@@ -9785,7 +10287,7 @@
     <row r="44" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="G44" s="53">
         <v>5700</v>
@@ -9796,7 +10298,7 @@
     </row>
     <row r="45" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F45" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="G45" s="53">
         <v>-130</v>
@@ -9807,7 +10309,7 @@
     </row>
     <row r="46" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F46" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="G46" s="53">
         <v>-250</v>
@@ -9818,7 +10320,7 @@
     </row>
     <row r="47" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F47" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="G47" s="53">
         <v>-112.2</v>
@@ -9829,7 +10331,7 @@
     </row>
     <row r="48" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F48" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="G48" s="53">
         <v>4911</v>
@@ -9840,7 +10342,7 @@
     </row>
     <row r="49" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F49" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="G49" s="53">
         <v>-3000</v>
@@ -9851,7 +10353,7 @@
     </row>
     <row r="50" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F50" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="G50" s="53">
         <v>-4000</v>
@@ -9862,7 +10364,7 @@
     </row>
     <row r="51" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F51" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="G51" s="53">
         <v>-200</v>
@@ -9873,7 +10375,7 @@
     </row>
     <row r="52" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F52" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="G52" s="53">
         <v>-4612</v>
@@ -9884,7 +10386,7 @@
     </row>
     <row r="53" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F53" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="G53" s="53">
         <v>-700</v>
@@ -9895,7 +10397,7 @@
     </row>
     <row r="54" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F54" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="G54" s="53">
         <v>-880</v>
@@ -9906,7 +10408,7 @@
     </row>
     <row r="55" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F55" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="G55" s="53">
         <v>-310</v>
@@ -9917,7 +10419,7 @@
     </row>
     <row r="56" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F56" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="G56" s="53">
         <v>-250</v>
@@ -9928,7 +10430,7 @@
     </row>
     <row r="57" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F57" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="G57" s="53">
         <v>4690</v>
@@ -9939,7 +10441,7 @@
     </row>
     <row r="58" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F58" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="G58" s="53">
         <v>-4440</v>
@@ -9950,7 +10452,7 @@
     </row>
     <row r="59" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F59" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="G59" s="53">
         <v>-4697</v>
@@ -9960,7 +10462,7 @@
     </row>
     <row r="60" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F60" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="G60" s="53">
         <v>-2500</v>
@@ -9970,7 +10472,7 @@
     </row>
     <row r="61" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F61" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="G61" s="53">
         <v>-126</v>
@@ -9980,7 +10482,7 @@
     </row>
     <row r="62" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F62" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="G62" s="53">
         <v>4742</v>
@@ -9990,7 +10492,7 @@
     </row>
     <row r="63" spans="6:14" x14ac:dyDescent="0.25">
       <c r="F63" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="G63" s="53">
         <v>-410</v>
@@ -10005,7 +10507,7 @@
     </row>
     <row r="65" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F65" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="G65" s="53">
         <v>3320</v>
@@ -10015,7 +10517,7 @@
     </row>
     <row r="66" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F66" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="G66" s="53">
         <v>4090</v>
@@ -10025,7 +10527,7 @@
     </row>
     <row r="67" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F67" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="G67" s="53">
         <v>-5688</v>
@@ -10035,7 +10537,7 @@
     </row>
     <row r="68" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F68" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="G68" s="53">
         <v>-4433</v>
@@ -10045,7 +10547,7 @@
     </row>
     <row r="69" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F69" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="G69" s="53">
         <v>-250</v>
@@ -10055,7 +10557,7 @@
     </row>
     <row r="70" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F70" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="G70" s="53">
         <v>-99</v>
@@ -10065,7 +10567,7 @@
     </row>
     <row r="71" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F71" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="G71" s="53">
         <v>320</v>
@@ -10075,7 +10577,7 @@
     </row>
     <row r="72" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F72" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="G72" s="53">
         <v>-1572</v>
@@ -10090,7 +10592,7 @@
     </row>
     <row r="74" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F74" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="G74" s="53">
         <v>4433</v>
@@ -10100,7 +10602,7 @@
     </row>
     <row r="75" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F75" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="G75" s="53">
         <v>8000</v>
@@ -10110,7 +10612,7 @@
     </row>
     <row r="76" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F76" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="G76" s="53">
         <v>-1344</v>
@@ -10120,7 +10622,7 @@
     </row>
     <row r="77" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F77" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="G77" s="53">
         <v>-308</v>
@@ -10130,7 +10632,7 @@
     </row>
     <row r="78" spans="6:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F78" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="G78" s="53">
         <v>-4204</v>
@@ -10140,7 +10642,7 @@
     </row>
     <row r="79" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F79" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="G79" s="53">
         <v>-338</v>
@@ -10150,7 +10652,7 @@
     </row>
     <row r="80" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F80" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="G80" s="53">
         <v>-50</v>
@@ -10158,9 +10660,9 @@
       <c r="H80" s="53"/>
       <c r="I80" s="53"/>
     </row>
-    <row r="81" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F81" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="G81" s="53">
         <v>338</v>
@@ -10168,9 +10670,9 @@
       <c r="H81" s="53"/>
       <c r="I81" s="53"/>
     </row>
-    <row r="82" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F82" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="G82" s="53">
         <v>-540</v>
@@ -10178,9 +10680,9 @@
       <c r="H82" s="53"/>
       <c r="I82" s="53"/>
     </row>
-    <row r="83" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F83" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="G83" s="53">
         <v>-184.31</v>
@@ -10188,9 +10690,9 @@
       <c r="H83" s="53"/>
       <c r="I83" s="53"/>
     </row>
-    <row r="84" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F84" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="G84" s="53">
         <v>-1464.22</v>
@@ -10198,9 +10700,9 @@
       <c r="H84" s="53"/>
       <c r="I84" s="53"/>
     </row>
-    <row r="85" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F85" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="G85" s="53">
         <v>1005</v>
@@ -10208,9 +10710,9 @@
       <c r="H85" s="53"/>
       <c r="I85" s="53"/>
     </row>
-    <row r="86" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F86" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="G86" s="53">
         <v>-500</v>
@@ -10218,9 +10720,9 @@
       <c r="H86" s="53"/>
       <c r="I86" s="53"/>
     </row>
-    <row r="87" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F87" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="G87" s="53">
         <v>-225</v>
@@ -10228,9 +10730,9 @@
       <c r="H87" s="53"/>
       <c r="I87" s="53"/>
     </row>
-    <row r="88" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F88" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="G88" s="53">
         <v>-516</v>
@@ -10238,9 +10740,9 @@
       <c r="H88" s="53"/>
       <c r="I88" s="53"/>
     </row>
-    <row r="89" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F89" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="G89" s="53">
         <v>4204</v>
@@ -10248,9 +10750,9 @@
       <c r="H89" s="53"/>
       <c r="I89" s="53"/>
     </row>
-    <row r="90" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F90" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="G90" s="53">
         <v>-100</v>
@@ -10258,9 +10760,9 @@
       <c r="H90" s="53"/>
       <c r="I90" s="53"/>
     </row>
-    <row r="91" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F91" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="G91" s="53">
         <v>8000</v>
@@ -10268,9 +10770,9 @@
       <c r="H91" s="53"/>
       <c r="I91" s="53"/>
     </row>
-    <row r="92" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F92" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="G92" s="53">
         <v>1000</v>
@@ -10278,9 +10780,9 @@
       <c r="H92" s="53"/>
       <c r="I92" s="53"/>
     </row>
-    <row r="93" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F93" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="G93" s="53">
         <v>-12881</v>
@@ -10288,9 +10790,9 @@
       <c r="H93" s="53"/>
       <c r="I93" s="53"/>
     </row>
-    <row r="94" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F94" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="G94" s="53">
         <v>-4489.62</v>
@@ -10298,9 +10800,9 @@
       <c r="H94" s="53"/>
       <c r="I94" s="53"/>
     </row>
-    <row r="95" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:9" x14ac:dyDescent="0.25">
       <c r="F95" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="G95" s="53">
         <v>5000</v>
@@ -10308,9 +10810,10 @@
       <c r="H95" s="53"/>
       <c r="I95" s="53"/>
     </row>
-    <row r="96" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C96" s="53"/>
       <c r="F96" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G96" s="53">
         <v>-480</v>
@@ -10319,15 +10822,10 @@
       <c r="I96" s="53"/>
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B97" t="s">
-        <v>216</v>
-      </c>
-      <c r="C97" s="53">
-        <v>-750</v>
-      </c>
+      <c r="C97" s="53"/>
       <c r="D97" s="53"/>
       <c r="F97" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="G97" s="53">
         <v>-520</v>
@@ -10336,15 +10834,10 @@
       <c r="I97" s="53"/>
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B98" t="s">
-        <v>154</v>
-      </c>
-      <c r="C98" s="53">
-        <v>5587.28</v>
-      </c>
+      <c r="C98" s="53"/>
       <c r="D98" s="53"/>
       <c r="F98" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="G98" s="53">
         <v>5556.2</v>
@@ -10354,12 +10847,15 @@
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>219</v>
-      </c>
-      <c r="C99" s="53"/>
+        <v>188</v>
+      </c>
+      <c r="C99" s="53">
+        <f>-'Compensasões e Transferências'!C21</f>
+        <v>-5876.4800000000005</v>
+      </c>
       <c r="D99" s="53"/>
       <c r="F99" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="G99" s="53">
         <v>-500</v>
@@ -10369,16 +10865,12 @@
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>221</v>
-      </c>
-      <c r="C100" s="53">
-        <v>2000</v>
-      </c>
-      <c r="D100" s="53">
-        <v>300</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="C100" s="53"/>
+      <c r="D100" s="53"/>
       <c r="F100" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="G100" s="53">
         <v>-276</v>
@@ -10387,15 +10879,10 @@
       <c r="I100" s="53"/>
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C101" s="53">
-        <v>8000</v>
-      </c>
+      <c r="C101" s="53"/>
       <c r="D101" s="53"/>
       <c r="F101" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="G101" s="53">
         <v>-250</v>
@@ -10405,14 +10892,15 @@
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="C102" s="53">
-        <v>4180</v>
+        <f>-C99</f>
+        <v>5876.4800000000005</v>
       </c>
       <c r="D102" s="53"/>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="G102" s="53">
         <v>-4837.28</v>
@@ -10421,10 +10909,15 @@
       <c r="I102" s="53"/>
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>255</v>
+      </c>
       <c r="C103" s="53"/>
-      <c r="D103" s="53"/>
+      <c r="D103" s="53">
+        <v>300</v>
+      </c>
       <c r="F103" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="G103" s="53">
         <v>-150</v>
@@ -10433,17 +10926,10 @@
       <c r="I103" s="53"/>
     </row>
     <row r="104" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B104" t="s">
-        <v>227</v>
-      </c>
-      <c r="C104" s="53">
-        <v>2000</v>
-      </c>
-      <c r="D104" s="53">
-        <v>300</v>
-      </c>
+      <c r="C104" s="53"/>
+      <c r="D104" s="53"/>
       <c r="F104" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G104" s="53">
         <v>-172.8</v>
@@ -10452,17 +10938,10 @@
       <c r="I104" s="53"/>
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B105" t="s">
-        <v>228</v>
-      </c>
-      <c r="C105" s="53">
-        <v>2000</v>
-      </c>
-      <c r="D105" s="53">
-        <v>300</v>
-      </c>
+      <c r="C105" s="53"/>
+      <c r="D105" s="53"/>
       <c r="F105" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="G105" s="53">
         <v>-370</v>
@@ -10471,62 +10950,80 @@
       <c r="I105" s="53"/>
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B106" t="s">
-        <v>230</v>
-      </c>
-      <c r="C106" s="53">
-        <v>2000</v>
-      </c>
-      <c r="D106" s="53">
-        <v>300</v>
-      </c>
-      <c r="G106" s="53"/>
+      <c r="C106" s="53"/>
+      <c r="D106" s="53"/>
+      <c r="F106" t="s">
+        <v>257</v>
+      </c>
+      <c r="G106" s="53">
+        <v>-815</v>
+      </c>
       <c r="H106" s="53"/>
       <c r="I106" s="53"/>
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C107" s="53"/>
-      <c r="D107" s="53"/>
-      <c r="G107" s="53"/>
+      <c r="B107" t="s">
+        <v>258</v>
+      </c>
+      <c r="C107" s="53">
+        <v>2000</v>
+      </c>
+      <c r="D107" s="53">
+        <v>300</v>
+      </c>
+      <c r="F107" t="s">
+        <v>259</v>
+      </c>
+      <c r="G107" s="53">
+        <v>-678</v>
+      </c>
       <c r="H107" s="53"/>
       <c r="I107" s="53"/>
     </row>
     <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="C108" s="53">
-        <v>-20000</v>
+        <v>8000</v>
       </c>
       <c r="D108" s="53"/>
-      <c r="G108" s="53"/>
+      <c r="F108" t="s">
+        <v>285</v>
+      </c>
+      <c r="G108" s="53">
+        <v>-400</v>
+      </c>
       <c r="H108" s="53"/>
       <c r="I108" s="53"/>
     </row>
     <row r="109" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C109" s="53"/>
+      <c r="B109" t="s">
+        <v>261</v>
+      </c>
+      <c r="C109" s="53">
+        <v>4180</v>
+      </c>
       <c r="D109" s="53"/>
-      <c r="G109" s="53"/>
+      <c r="F109" t="s">
+        <v>247</v>
+      </c>
+      <c r="G109" s="53">
+        <v>5587.28</v>
+      </c>
       <c r="H109" s="53"/>
       <c r="I109" s="53"/>
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B110" t="s">
-        <v>232</v>
-      </c>
-      <c r="C110" s="53">
-        <v>2000</v>
-      </c>
-      <c r="D110" s="53">
-        <v>300</v>
-      </c>
+      <c r="C110" s="53"/>
+      <c r="D110" s="53"/>
       <c r="G110" s="53"/>
       <c r="H110" s="53"/>
       <c r="I110" s="53"/>
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="C111" s="53">
         <v>2000</v>
@@ -10540,19 +11037,21 @@
     </row>
     <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="C112" s="53">
-        <v>8000</v>
-      </c>
-      <c r="D112" s="53"/>
+        <v>2000</v>
+      </c>
+      <c r="D112" s="53">
+        <v>300</v>
+      </c>
       <c r="G112" s="53"/>
       <c r="H112" s="53"/>
       <c r="I112" s="53"/>
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="C113" s="53">
         <v>2000</v>
@@ -10565,84 +11064,122 @@
       <c r="I113" s="53"/>
     </row>
     <row r="114" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B114" t="s">
-        <v>236</v>
-      </c>
-      <c r="C114" s="53">
-        <v>2000</v>
-      </c>
-      <c r="D114" s="53">
-        <v>300</v>
-      </c>
+      <c r="C114" s="53"/>
+      <c r="D114" s="53"/>
       <c r="G114" s="53"/>
       <c r="H114" s="53"/>
       <c r="I114" s="53"/>
     </row>
     <row r="115" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C115" s="53"/>
+      <c r="B115" t="s">
+        <v>265</v>
+      </c>
+      <c r="C115" s="53">
+        <v>-20000</v>
+      </c>
+      <c r="D115" s="53"/>
       <c r="G115" s="53"/>
       <c r="H115" s="53"/>
       <c r="I115" s="53"/>
     </row>
     <row r="116" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C116" s="53"/>
+      <c r="D116" s="53"/>
       <c r="G116" s="53"/>
       <c r="H116" s="53"/>
       <c r="I116" s="53"/>
     </row>
     <row r="117" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C117" s="53"/>
+      <c r="B117" t="s">
+        <v>266</v>
+      </c>
+      <c r="C117" s="53">
+        <v>2000</v>
+      </c>
+      <c r="D117" s="53">
+        <v>300</v>
+      </c>
       <c r="G117" s="53"/>
       <c r="H117" s="53"/>
       <c r="I117" s="53"/>
     </row>
     <row r="118" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C118" s="53"/>
+      <c r="B118" t="s">
+        <v>267</v>
+      </c>
+      <c r="C118" s="53">
+        <v>2000</v>
+      </c>
+      <c r="D118" s="53">
+        <v>300</v>
+      </c>
       <c r="G118" s="53"/>
       <c r="H118" s="53"/>
       <c r="I118" s="53"/>
     </row>
     <row r="119" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C119" s="53"/>
+      <c r="B119" t="s">
+        <v>268</v>
+      </c>
+      <c r="C119" s="53">
+        <v>8000</v>
+      </c>
+      <c r="D119" s="53"/>
       <c r="G119" s="53"/>
       <c r="H119" s="53"/>
       <c r="I119" s="53"/>
     </row>
     <row r="120" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C120" s="53"/>
+      <c r="B120" t="s">
+        <v>269</v>
+      </c>
+      <c r="C120" s="53">
+        <v>2000</v>
+      </c>
+      <c r="D120" s="53">
+        <v>300</v>
+      </c>
       <c r="G120" s="53"/>
       <c r="H120" s="53"/>
       <c r="I120" s="53"/>
     </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C121" s="53"/>
+      <c r="B121" t="s">
+        <v>270</v>
+      </c>
+      <c r="C121" s="53">
+        <v>2000</v>
+      </c>
+      <c r="D121" s="53">
+        <v>300</v>
+      </c>
       <c r="G121" s="53"/>
       <c r="H121" s="53"/>
       <c r="I121" s="53"/>
     </row>
     <row r="122" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G122" s="53"/>
-      <c r="H122" s="72"/>
+      <c r="H122" s="53"/>
       <c r="I122" s="53"/>
     </row>
     <row r="123" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G123" s="53"/>
-      <c r="H123" s="72"/>
+      <c r="H123" s="53"/>
       <c r="I123" s="53"/>
     </row>
     <row r="124" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G124" s="53"/>
-      <c r="H124" s="72"/>
+      <c r="H124" s="53"/>
       <c r="I124" s="53"/>
     </row>
     <row r="125" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G125" s="53"/>
-      <c r="H125" s="72"/>
+      <c r="H125" s="53"/>
       <c r="I125" s="53"/>
     </row>
     <row r="126" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G126" s="53"/>
-      <c r="H126" s="72"/>
+      <c r="H126" s="53"/>
       <c r="I126" s="53"/>
     </row>
     <row r="127" spans="2:9" x14ac:dyDescent="0.25">
@@ -10652,7 +11189,7 @@
     </row>
     <row r="128" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G128" s="53"/>
-      <c r="H128" s="72"/>
+      <c r="H128" s="53"/>
       <c r="I128" s="53"/>
     </row>
     <row r="129" spans="7:9" x14ac:dyDescent="0.25">
@@ -11763,59 +12300,59 @@
   <mergeCells count="1">
     <mergeCell ref="M3:M4"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C97:D114 C115:C121">
-    <cfRule type="cellIs" dxfId="13" priority="199" operator="greaterThan">
+  <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C97:D121">
+    <cfRule type="cellIs" dxfId="13" priority="235" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="200" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="236" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G123:G1048576">
-    <cfRule type="cellIs" dxfId="11" priority="27" operator="greaterThan">
+  <conditionalFormatting sqref="C96">
+    <cfRule type="cellIs" dxfId="11" priority="35" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="28" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="36" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G96:H122">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="G133:G1048576">
+    <cfRule type="cellIs" dxfId="9" priority="63" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="64" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I95">
-    <cfRule type="cellIs" dxfId="7" priority="39" operator="greaterThan">
+  <conditionalFormatting sqref="G14:I108 G110:I110 I109 G123:I132 I111:I122">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="40" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H123:H130">
-    <cfRule type="cellIs" dxfId="5" priority="21" operator="greaterThan">
+  <conditionalFormatting sqref="H133:I266">
+    <cfRule type="cellIs" dxfId="5" priority="233" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="234" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H131:I266">
-    <cfRule type="cellIs" dxfId="3" priority="197" operator="greaterThan">
+  <conditionalFormatting sqref="G109:H109">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="198" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I96:I130">
-    <cfRule type="cellIs" dxfId="1" priority="45" operator="greaterThan">
+  <conditionalFormatting sqref="G111:H122">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="46" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11837,13 +12374,13 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" s="62" t="s">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="C1" s="63" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>239</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
@@ -11851,81 +12388,81 @@
         <v>23</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="D2" s="54"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="54" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="D3" s="54"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="54" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="D4" s="54"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="54" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="D5" s="54"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="54" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="D6" s="54"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="54" t="s">
-        <v>242</v>
+        <v>276</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="D7" s="54"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="54" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="D8" s="54"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="54" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>244</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="54" t="s">
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="D10" s="54"/>
     </row>

--- a/financas.xlsx
+++ b/financas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="496" documentId="11_C0E26E8C2FF3658481E6AE6DE74C74B31A2D8B7D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{566CA734-F2FA-494D-AC4A-CE5F73FEA93F}"/>
+  <xr:revisionPtr revIDLastSave="529" documentId="11_C0E26E8C2FF3658481E6AE6DE74C74B31A2D8B7D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAA86987-0795-45F4-B685-7E54E78D2F66}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saldo" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="289">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -904,6 +904,15 @@
   </si>
   <si>
     <t>Ajuste</t>
+  </si>
+  <si>
+    <t>Remédios Geleia</t>
+  </si>
+  <si>
+    <t>Neutrodor+Bite Stop</t>
+  </si>
+  <si>
+    <t>Kadalora</t>
   </si>
 </sst>
 </file>
@@ -1422,27 +1431,7 @@
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1629,6 +1618,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
@@ -1806,17 +1799,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:F42"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="82" t="s">
         <v>0</v>
       </c>
@@ -1828,20 +1821,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="83"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C26+C27+C7+C28</f>
-        <v>1692.5772380952367</v>
+        <v>1510.7772380952374</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E26+E27</f>
-        <v>2609.5200000000004</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+        <v>2477.7199999999993</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
@@ -1853,21 +1846,21 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-7665.4227619047633</v>
+        <v>-7567.2227619047626</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-8390.48</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+        <v>-8522.2800000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
@@ -1875,7 +1868,7 @@
       <c r="D7" s="9"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
@@ -1889,35 +1882,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>5107.5827619047632</v>
+        <v>5009.3827619047624</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>2490.6400000000003</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+        <v>2622.44</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>5107.5827619047632</v>
+        <v>5009.3827619047624</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>2490.6400000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+        <v>2622.44</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
@@ -1931,7 +1924,7 @@
         <v>5899.84</v>
       </c>
     </row>
-    <row r="12" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>10</v>
       </c>
@@ -1945,7 +1938,7 @@
         <v>1617.835</v>
       </c>
     </row>
-    <row r="13" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
@@ -1959,7 +1952,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>12</v>
       </c>
@@ -1974,7 +1967,7 @@
       </c>
       <c r="F14" s="16"/>
     </row>
-    <row r="15" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>13</v>
       </c>
@@ -1988,7 +1981,7 @@
         <v>40.619999999999997</v>
       </c>
     </row>
-    <row r="16" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
         <v>14</v>
       </c>
@@ -2002,7 +1995,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
         <v>15</v>
       </c>
@@ -2016,7 +2009,7 @@
         <v>112.38500000000001</v>
       </c>
     </row>
-    <row r="18" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
         <v>16</v>
       </c>
@@ -2030,7 +2023,7 @@
         <v>333.5</v>
       </c>
     </row>
-    <row r="19" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="str">
         <f>Contas!$D10</f>
         <v>Cartão Itaú da Stella</v>
@@ -2042,7 +2035,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="str">
         <f>Contas!$D11</f>
         <v>Recolhimento INSS</v>
@@ -2054,7 +2047,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B21" s="13" t="str">
         <f>Contas!$D12</f>
         <v>Dinheiro Ps5</v>
@@ -2066,7 +2059,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B22" s="13" t="str">
         <f>Contas!$D13</f>
         <v>Empréstimo</v>
@@ -2078,7 +2071,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B23" s="17" t="s">
         <v>17</v>
       </c>
@@ -2086,19 +2079,19 @@
       <c r="D23" s="19"/>
       <c r="E23" s="18"/>
     </row>
-    <row r="24" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B24" s="13"/>
       <c r="C24" s="14"/>
       <c r="D24" s="15"/>
       <c r="E24" s="14"/>
     </row>
-    <row r="25" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B25" s="13"/>
       <c r="C25" s="14"/>
       <c r="D25" s="15"/>
       <c r="E25" s="14"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
         <v>18</v>
       </c>
@@ -2108,13 +2101,13 @@
       <c r="D26" s="9"/>
       <c r="E26" s="8"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
         <v>19</v>
       </c>
       <c r="C27" s="8">
         <f>SUM(C29:C40)</f>
-        <v>520</v>
+        <v>240</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8">
@@ -2122,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="13" t="s">
         <v>20</v>
       </c>
@@ -2132,7 +2125,7 @@
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
     </row>
-    <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B29" s="13" t="s">
         <v>21</v>
       </c>
@@ -2143,7 +2136,7 @@
       <c r="D29" s="15"/>
       <c r="E29" s="14"/>
     </row>
-    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B30" s="13" t="s">
         <v>22</v>
       </c>
@@ -2151,19 +2144,19 @@
       <c r="D30" s="20"/>
       <c r="E30" s="21"/>
     </row>
-    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B31" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L7</f>
-        <v xml:space="preserve">       Pagamento Psiquiatra</v>
-      </c>
-      <c r="C31" s="14">
+        <v xml:space="preserve">       </v>
+      </c>
+      <c r="C31" s="14" t="str">
         <f>IF('NuConta e Poupança'!M7="Sim",'NuConta e Poupança'!N7,"")</f>
-        <v>280</v>
+        <v/>
       </c>
       <c r="D31" s="20"/>
       <c r="E31" s="21"/>
     </row>
-    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B32" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L8</f>
         <v xml:space="preserve">       Dinheiro FIA</v>
@@ -2175,7 +2168,7 @@
       <c r="D32" s="20"/>
       <c r="E32" s="21"/>
     </row>
-    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B33" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L9</f>
         <v xml:space="preserve">       </v>
@@ -2187,7 +2180,7 @@
       <c r="D33" s="20"/>
       <c r="E33" s="21"/>
     </row>
-    <row r="34" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L10</f>
         <v xml:space="preserve">       </v>
@@ -2199,7 +2192,7 @@
       <c r="D34" s="20"/>
       <c r="E34" s="21"/>
     </row>
-    <row r="35" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B35" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L12</f>
         <v xml:space="preserve">       </v>
@@ -2211,7 +2204,7 @@
       <c r="D35" s="20"/>
       <c r="E35" s="21"/>
     </row>
-    <row r="36" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B36" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L13</f>
         <v xml:space="preserve">       </v>
@@ -2223,7 +2216,7 @@
       <c r="D36" s="20"/>
       <c r="E36" s="21"/>
     </row>
-    <row r="37" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B37" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L14</f>
         <v xml:space="preserve">       </v>
@@ -2235,7 +2228,7 @@
       <c r="D37" s="20"/>
       <c r="E37" s="21"/>
     </row>
-    <row r="38" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B38" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L15</f>
         <v xml:space="preserve">       </v>
@@ -2247,7 +2240,7 @@
       <c r="D38" s="20"/>
       <c r="E38" s="21"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L16</f>
         <v xml:space="preserve">       </v>
@@ -2260,7 +2253,7 @@
       <c r="E39" s="21"/>
       <c r="F39" s="16"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L17</f>
         <v xml:space="preserve">       </v>
@@ -2273,7 +2266,7 @@
       <c r="E40" s="21"/>
       <c r="F40" s="16"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L21</f>
         <v xml:space="preserve">       </v>
@@ -2285,7 +2278,7 @@
       <c r="D41" s="20"/>
       <c r="E41" s="21"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="13" t="str">
         <f>"       "&amp;'NuConta e Poupança'!L22</f>
         <v xml:space="preserve">       </v>
@@ -2309,17 +2302,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:D100"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="31.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" ht="39" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="22"/>
       <c r="C2" s="23" t="s">
         <v>2</v>
@@ -2328,7 +2321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
@@ -2341,45 +2334,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>2490.6400000000003</v>
+        <v>2622.44</v>
       </c>
       <c r="D4" s="24">
         <f>Saldo!C9+D5</f>
-        <v>5107.5827619047632</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+        <v>5009.3827619047624</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="13"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="13"/>
       <c r="C7" s="8"/>
       <c r="D7" s="24"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="13"/>
       <c r="C8" s="8"/>
       <c r="D8" s="24"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="13"/>
       <c r="C9" s="8"/>
       <c r="D9" s="24"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
@@ -2389,7 +2382,7 @@
       </c>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
         <v>23</v>
       </c>
@@ -2399,7 +2392,7 @@
       </c>
       <c r="D11" s="13"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B12" s="25" t="s">
         <v>24</v>
       </c>
@@ -2409,7 +2402,7 @@
       </c>
       <c r="D12" s="13"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>12</v>
       </c>
@@ -2419,7 +2412,7 @@
       </c>
       <c r="D13" s="13"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>13</v>
       </c>
@@ -2429,7 +2422,7 @@
       </c>
       <c r="D14" s="13"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>14</v>
       </c>
@@ -2439,7 +2432,7 @@
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
         <v>15</v>
       </c>
@@ -2449,7 +2442,7 @@
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
         <v>25</v>
       </c>
@@ -2459,7 +2452,7 @@
       </c>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
         <v>26</v>
       </c>
@@ -2469,7 +2462,7 @@
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
         <v>284</v>
       </c>
@@ -2479,30 +2472,30 @@
       </c>
       <c r="D19" s="13"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="14">
         <f>C21-C18</f>
-        <v>5126.4800000000005</v>
+        <v>5258.2800000000007</v>
       </c>
       <c r="D20" s="13"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>5876.4800000000005</v>
+        <v>6008.2800000000007</v>
       </c>
       <c r="D21" s="27"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>29</v>
       </c>
@@ -2510,7 +2503,7 @@
         <v>5587.2758333333331</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>30</v>
       </c>
@@ -2518,7 +2511,7 @@
         <v>46295</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>31</v>
       </c>
@@ -2526,7 +2519,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C100" s="81" t="str">
         <f>'Compensasões e Transferências'!C25</f>
         <v>Pago</v>
@@ -2544,22 +2537,22 @@
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
   <dimension ref="C1:Q67"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="35.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="41" customWidth="1"/>
-    <col min="5" max="6" width="22.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" customWidth="1"/>
-    <col min="8" max="9" width="13.5703125" customWidth="1"/>
+    <col min="5" max="6" width="22.5546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.5546875" customWidth="1"/>
+    <col min="8" max="9" width="13.5546875" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" customWidth="1"/>
-    <col min="12" max="16" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" customWidth="1"/>
+    <col min="12" max="16" width="13.5546875" customWidth="1"/>
     <col min="17" max="17" width="17" style="2" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D1" s="29" t="s">
         <v>33</v>
       </c>
@@ -2573,7 +2566,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D2" s="31">
         <f>SUM(L5:L21)</f>
         <v>0</v>
@@ -2591,7 +2584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="3:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="33" t="s">
         <v>35</v>
       </c>
@@ -2638,7 +2631,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="68"/>
       <c r="D5" s="36"/>
       <c r="E5" s="37"/>
@@ -2655,7 +2648,7 @@
       <c r="P5" s="64"/>
       <c r="Q5" s="37"/>
     </row>
-    <row r="6" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="37"/>
       <c r="D6" s="36"/>
       <c r="E6" s="37"/>
@@ -2687,7 +2680,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="35"/>
       <c r="D7" s="36"/>
       <c r="E7" s="37"/>
@@ -2716,7 +2709,7 @@
       <c r="P7" s="35"/>
       <c r="Q7" s="37"/>
     </row>
-    <row r="8" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="35"/>
       <c r="D8" s="36"/>
       <c r="E8" s="37"/>
@@ -2745,7 +2738,7 @@
       <c r="P8" s="35"/>
       <c r="Q8" s="37"/>
     </row>
-    <row r="9" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="35"/>
       <c r="D9" s="36"/>
       <c r="E9" s="37"/>
@@ -2774,7 +2767,7 @@
       <c r="P9" s="35"/>
       <c r="Q9" s="37"/>
     </row>
-    <row r="10" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="35"/>
       <c r="D10" s="36"/>
       <c r="E10" s="37"/>
@@ -2806,7 +2799,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="35"/>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
@@ -2835,7 +2828,7 @@
       <c r="P11" s="35"/>
       <c r="Q11" s="37"/>
     </row>
-    <row r="12" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="37"/>
       <c r="D12" s="36"/>
       <c r="E12" s="37"/>
@@ -2864,7 +2857,7 @@
       <c r="P12" s="35"/>
       <c r="Q12" s="37"/>
     </row>
-    <row r="13" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="37"/>
       <c r="D13" s="36"/>
       <c r="E13" s="37"/>
@@ -2893,7 +2886,7 @@
       <c r="P13" s="35"/>
       <c r="Q13" s="37"/>
     </row>
-    <row r="14" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="37"/>
       <c r="D14" s="36"/>
       <c r="E14" s="37"/>
@@ -2922,7 +2915,7 @@
       <c r="P14" s="35"/>
       <c r="Q14" s="37"/>
     </row>
-    <row r="15" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="37"/>
       <c r="D15" s="36"/>
       <c r="E15" s="37"/>
@@ -2951,7 +2944,7 @@
       <c r="P15" s="35"/>
       <c r="Q15" s="37"/>
     </row>
-    <row r="16" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="37"/>
       <c r="D16" s="36"/>
       <c r="E16" s="37"/>
@@ -2968,7 +2961,7 @@
       <c r="P16" s="35"/>
       <c r="Q16" s="37"/>
     </row>
-    <row r="17" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="35"/>
       <c r="D17" s="36"/>
       <c r="E17" s="37"/>
@@ -2985,7 +2978,7 @@
       <c r="P17" s="35"/>
       <c r="Q17" s="37"/>
     </row>
-    <row r="18" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="35"/>
       <c r="D18" s="36"/>
       <c r="E18" s="37"/>
@@ -3002,7 +2995,7 @@
       <c r="P18" s="35"/>
       <c r="Q18" s="37"/>
     </row>
-    <row r="19" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -3013,198 +3006,198 @@
       <c r="O19" s="41"/>
       <c r="P19" s="41"/>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.3">
       <c r="H20" s="2"/>
       <c r="O20" s="42"/>
       <c r="P20" s="42"/>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.3">
       <c r="H21" s="2"/>
       <c r="O21" s="42"/>
       <c r="P21" s="42"/>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.3">
       <c r="H22" s="2"/>
       <c r="O22" s="42"/>
       <c r="P22" s="42"/>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O23" s="42"/>
       <c r="P23" s="42"/>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O24" s="42"/>
       <c r="P24" s="42"/>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O25" s="42"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O26" s="42"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O27" s="42"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O28" s="42"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O29" s="42"/>
       <c r="P29" s="42"/>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O30" s="42"/>
       <c r="P30" s="42"/>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O31" s="42"/>
       <c r="P31" s="42"/>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.3">
       <c r="O32" s="42"/>
       <c r="P32" s="42"/>
     </row>
-    <row r="33" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O33" s="42"/>
       <c r="P33" s="42"/>
     </row>
-    <row r="34" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O34" s="42"/>
       <c r="P34" s="42"/>
     </row>
-    <row r="35" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O35" s="42"/>
       <c r="P35" s="42"/>
     </row>
-    <row r="36" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O36" s="42"/>
       <c r="P36" s="42"/>
     </row>
-    <row r="37" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O37" s="42"/>
       <c r="P37" s="42"/>
     </row>
-    <row r="38" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O38" s="42"/>
       <c r="P38" s="42"/>
     </row>
-    <row r="39" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O39" s="42"/>
       <c r="P39" s="42"/>
     </row>
-    <row r="40" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O40" s="42"/>
       <c r="P40" s="42"/>
     </row>
-    <row r="41" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O41" s="42"/>
       <c r="P41" s="42"/>
     </row>
-    <row r="42" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
     </row>
-    <row r="43" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O43" s="42"/>
       <c r="P43" s="42"/>
     </row>
-    <row r="44" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O44" s="42"/>
       <c r="P44" s="42"/>
     </row>
-    <row r="45" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O45" s="42"/>
       <c r="P45" s="42"/>
     </row>
-    <row r="46" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O46" s="42"/>
       <c r="P46" s="42"/>
     </row>
-    <row r="47" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O47" s="42"/>
       <c r="P47" s="42"/>
     </row>
-    <row r="48" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O48" s="42"/>
       <c r="P48" s="42"/>
     </row>
-    <row r="49" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O49" s="42"/>
       <c r="P49" s="42"/>
     </row>
-    <row r="50" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O50" s="42"/>
       <c r="P50" s="42"/>
     </row>
-    <row r="51" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O51" s="42"/>
       <c r="P51" s="42"/>
     </row>
-    <row r="52" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O52" s="42"/>
       <c r="P52" s="42"/>
     </row>
-    <row r="53" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O53" s="42"/>
       <c r="P53" s="42"/>
     </row>
-    <row r="54" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O54" s="42"/>
       <c r="P54" s="42"/>
     </row>
-    <row r="55" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O55" s="42"/>
       <c r="P55" s="42"/>
     </row>
-    <row r="56" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O56" s="42"/>
       <c r="P56" s="42"/>
     </row>
-    <row r="57" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O57" s="42"/>
       <c r="P57" s="42"/>
     </row>
-    <row r="58" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O58" s="42"/>
       <c r="P58" s="42"/>
     </row>
-    <row r="59" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O59" s="42"/>
       <c r="P59" s="42"/>
     </row>
-    <row r="60" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O60" s="42"/>
       <c r="P60" s="42"/>
     </row>
-    <row r="61" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O61" s="42"/>
       <c r="P61" s="42"/>
     </row>
-    <row r="62" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O62" s="42"/>
       <c r="P62" s="42"/>
     </row>
-    <row r="63" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O63" s="42"/>
       <c r="P63" s="42"/>
     </row>
-    <row r="64" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O64" s="42"/>
       <c r="P64" s="42"/>
     </row>
-    <row r="65" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O65" s="42"/>
       <c r="P65" s="42"/>
     </row>
-    <row r="66" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O66" s="42"/>
       <c r="P66" s="42"/>
     </row>
-    <row r="67" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="15:16" x14ac:dyDescent="0.3">
       <c r="O67" s="42"/>
       <c r="P67" s="42"/>
     </row>
@@ -3215,7 +3208,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J5:K22">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"Parcelado/Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3230,22 +3223,22 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="C1:Q142"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" customWidth="1"/>
-    <col min="5" max="7" width="20.5703125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" style="43" customWidth="1"/>
-    <col min="10" max="10" width="20.42578125" style="43" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" customWidth="1"/>
-    <col min="12" max="16" width="13.5703125" customWidth="1"/>
-    <col min="17" max="17" width="21.85546875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="36.5546875" customWidth="1"/>
+    <col min="5" max="7" width="20.5546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5546875" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" style="43" customWidth="1"/>
+    <col min="10" max="10" width="20.44140625" style="43" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" customWidth="1"/>
+    <col min="12" max="16" width="13.5546875" customWidth="1"/>
+    <col min="17" max="17" width="21.88671875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D1" s="44" t="s">
         <v>50</v>
       </c>
@@ -3261,18 +3254,18 @@
       <c r="L1" s="43"/>
       <c r="P1" s="2"/>
     </row>
-    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D2" s="45">
         <f>SUM(L6:L184)</f>
-        <v>9598.2227619047608</v>
+        <v>9631.8227619047593</v>
       </c>
       <c r="E2" s="32">
         <f>SUMIF($E$6:$E$184,E1,$M$6:$M$184)</f>
-        <v>5107.5827619047632</v>
+        <v>5009.3827619047624</v>
       </c>
       <c r="F2" s="32">
         <f>SUMIF($F$6:$F$184,F1,$M$6:$M$184)</f>
-        <v>2490.6400000000003</v>
+        <v>2622.44</v>
       </c>
       <c r="G2" s="32">
         <f>SUMIF($G$6:$G$184,G1,$M$6:$M$184)</f>
@@ -3282,14 +3275,14 @@
       <c r="L2" s="43"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:17" x14ac:dyDescent="0.3">
       <c r="L3" s="43"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:17" x14ac:dyDescent="0.3">
       <c r="M4" s="43"/>
     </row>
-    <row r="5" spans="3:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="33"/>
       <c r="D5" s="33" t="s">
         <v>36</v>
@@ -3334,7 +3327,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C6" s="35"/>
       <c r="D6" s="36" t="s">
         <v>52</v>
@@ -3382,7 +3375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C7" s="35"/>
       <c r="D7" s="36" t="s">
         <v>55</v>
@@ -3428,7 +3421,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C8" s="35"/>
       <c r="D8" s="74" t="s">
         <v>57</v>
@@ -3474,7 +3467,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C9" s="35"/>
       <c r="D9" s="74" t="s">
         <v>59</v>
@@ -3520,7 +3513,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C10" s="35"/>
       <c r="D10" s="74" t="s">
         <v>61</v>
@@ -3566,7 +3559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C11" s="35"/>
       <c r="D11" s="74" t="s">
         <v>62</v>
@@ -3612,7 +3605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C12" s="35"/>
       <c r="D12" s="74" t="s">
         <v>63</v>
@@ -3660,7 +3653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C13" s="35"/>
       <c r="D13" s="65" t="s">
         <v>64</v>
@@ -3708,7 +3701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C14" s="35"/>
       <c r="D14" s="65" t="s">
         <v>66</v>
@@ -3756,7 +3749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C15" s="35"/>
       <c r="D15" s="65" t="s">
         <v>67</v>
@@ -3804,7 +3797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C16" s="35"/>
       <c r="D16" s="75" t="s">
         <v>68</v>
@@ -3849,7 +3842,7 @@
       </c>
       <c r="Q16" s="37"/>
     </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C17" s="35"/>
       <c r="D17" s="75" t="s">
         <v>69</v>
@@ -3895,7 +3888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C18" s="35"/>
       <c r="D18" s="75" t="s">
         <v>71</v>
@@ -3941,7 +3934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C19" s="35"/>
       <c r="D19" s="75" t="s">
         <v>72</v>
@@ -3987,7 +3980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C20" s="35"/>
       <c r="D20" s="36" t="s">
         <v>73</v>
@@ -4035,7 +4028,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C21" s="35"/>
       <c r="D21" s="46" t="s">
         <v>74</v>
@@ -4081,7 +4074,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C22" s="35"/>
       <c r="D22" s="46" t="s">
         <v>75</v>
@@ -4127,7 +4120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C23" s="35"/>
       <c r="D23" s="46" t="s">
         <v>76</v>
@@ -4173,7 +4166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C24" s="35"/>
       <c r="D24" s="46" t="s">
         <v>77</v>
@@ -4221,7 +4214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C25" s="35"/>
       <c r="D25" s="46" t="s">
         <v>78</v>
@@ -4267,7 +4260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C26" s="35"/>
       <c r="D26" s="46" t="s">
         <v>79</v>
@@ -4313,7 +4306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C27" s="35"/>
       <c r="D27" s="46" t="s">
         <v>80</v>
@@ -4361,7 +4354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C28" s="35"/>
       <c r="D28" s="46" t="s">
         <v>81</v>
@@ -4407,7 +4400,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C29" s="35"/>
       <c r="D29" s="46" t="s">
         <v>82</v>
@@ -4455,7 +4448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C30" s="35" t="s">
         <v>83</v>
       </c>
@@ -4503,7 +4496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C31" s="35"/>
       <c r="D31" s="36" t="s">
         <v>86</v>
@@ -4549,7 +4542,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C32" s="35"/>
       <c r="D32" s="46" t="s">
         <v>88</v>
@@ -4595,7 +4588,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C33" s="35"/>
       <c r="D33" s="36" t="s">
         <v>89</v>
@@ -4641,7 +4634,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C34" s="35"/>
       <c r="D34" s="36" t="s">
         <v>91</v>
@@ -4687,7 +4680,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C35" s="35"/>
       <c r="D35" s="46" t="s">
         <v>92</v>
@@ -4733,7 +4726,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C36" s="35"/>
       <c r="D36" s="36" t="s">
         <v>93</v>
@@ -4779,7 +4772,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C37" s="35"/>
       <c r="D37" s="36" t="s">
         <v>94</v>
@@ -4825,7 +4818,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C38" s="35"/>
       <c r="D38" s="46" t="s">
         <v>95</v>
@@ -4869,7 +4862,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C39" s="35"/>
       <c r="D39" s="46" t="s">
         <v>96</v>
@@ -4913,7 +4906,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C40" s="35"/>
       <c r="D40" s="46" t="s">
         <v>98</v>
@@ -4954,7 +4947,7 @@
       </c>
       <c r="Q40" s="37"/>
     </row>
-    <row r="41" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C41" s="35"/>
       <c r="D41" s="36" t="s">
         <v>99</v>
@@ -4998,7 +4991,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C42" s="35"/>
       <c r="D42" s="46" t="s">
         <v>100</v>
@@ -5039,7 +5032,7 @@
       </c>
       <c r="Q42" s="37"/>
     </row>
-    <row r="43" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C43" s="35"/>
       <c r="D43" s="66" t="s">
         <v>101</v>
@@ -5083,7 +5076,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C44" s="35"/>
       <c r="D44" s="46" t="s">
         <v>103</v>
@@ -5129,7 +5122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C45" s="35"/>
       <c r="D45" s="46" t="s">
         <v>104</v>
@@ -5177,7 +5170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C46" s="35"/>
       <c r="D46" s="46" t="s">
         <v>105</v>
@@ -5223,7 +5216,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C47" s="35"/>
       <c r="D47" s="46" t="s">
         <v>108</v>
@@ -5271,7 +5264,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C48" s="35"/>
       <c r="D48" s="46" t="s">
         <v>110</v>
@@ -5317,7 +5310,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C49" s="35"/>
       <c r="D49" s="46" t="s">
         <v>112</v>
@@ -5363,7 +5356,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C50" s="76"/>
       <c r="D50" s="66" t="s">
         <v>114</v>
@@ -5403,7 +5396,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C51" s="35"/>
       <c r="D51" s="46" t="s">
         <v>115</v>
@@ -5449,7 +5442,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C52" s="35"/>
       <c r="D52" s="46" t="s">
         <v>117</v>
@@ -5497,7 +5490,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C53" s="35"/>
       <c r="D53" s="46" t="s">
         <v>118</v>
@@ -5543,7 +5536,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C54" s="35"/>
       <c r="D54" s="46" t="s">
         <v>119</v>
@@ -5589,7 +5582,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C55" s="35"/>
       <c r="D55" s="46" t="s">
         <v>120</v>
@@ -5637,7 +5630,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C56" s="35"/>
       <c r="D56" s="46" t="s">
         <v>122</v>
@@ -5686,7 +5679,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C57" s="35"/>
       <c r="D57" s="46" t="s">
         <v>123</v>
@@ -5734,7 +5727,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C58" s="35"/>
       <c r="D58" s="46" t="s">
         <v>124</v>
@@ -5782,7 +5775,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C59" s="35"/>
       <c r="D59" s="46" t="s">
         <v>125</v>
@@ -5828,7 +5821,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C60" s="35"/>
       <c r="D60" s="46" t="s">
         <v>126</v>
@@ -5874,7 +5867,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C61" s="35"/>
       <c r="D61" s="46" t="s">
         <v>127</v>
@@ -5920,7 +5913,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C62" s="35"/>
       <c r="D62" s="46" t="s">
         <v>128</v>
@@ -5966,7 +5959,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C63" s="35"/>
       <c r="D63" s="46" t="s">
         <v>129</v>
@@ -6012,7 +6005,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C64" s="35"/>
       <c r="D64" s="46" t="s">
         <v>131</v>
@@ -6060,7 +6053,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C65" s="35"/>
       <c r="D65" s="46" t="s">
         <v>117</v>
@@ -6108,7 +6101,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C66" s="35"/>
       <c r="D66" s="46" t="s">
         <v>132</v>
@@ -6154,7 +6147,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C67" s="35"/>
       <c r="D67" s="46" t="s">
         <v>133</v>
@@ -6203,7 +6196,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C68" s="35"/>
       <c r="D68" s="46" t="s">
         <v>133</v>
@@ -6249,7 +6242,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C69" s="35"/>
       <c r="D69" s="46" t="s">
         <v>134</v>
@@ -6297,7 +6290,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C70" s="35"/>
       <c r="D70" s="46" t="s">
         <v>135</v>
@@ -6345,7 +6338,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C71" s="35"/>
       <c r="D71" s="46" t="s">
         <v>119</v>
@@ -6391,7 +6384,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C72" s="35"/>
       <c r="D72" s="46" t="s">
         <v>136</v>
@@ -6437,7 +6430,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C73" s="35"/>
       <c r="D73" s="46" t="s">
         <v>137</v>
@@ -6483,7 +6476,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C74" s="35"/>
       <c r="D74" s="46" t="s">
         <v>138</v>
@@ -6531,7 +6524,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C75" s="35"/>
       <c r="D75" s="46" t="s">
         <v>139</v>
@@ -6579,7 +6572,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C76" s="35"/>
       <c r="D76" s="46" t="s">
         <v>140</v>
@@ -6627,7 +6620,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C77" s="35"/>
       <c r="D77" s="46" t="s">
         <v>141</v>
@@ -6676,7 +6669,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C78" s="35"/>
       <c r="D78" s="46" t="s">
         <v>142</v>
@@ -6722,7 +6715,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C79" s="35"/>
       <c r="D79" s="46" t="s">
         <v>143</v>
@@ -6770,7 +6763,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C80" s="35"/>
       <c r="D80" s="46" t="s">
         <v>144</v>
@@ -6818,7 +6811,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C81" s="35"/>
       <c r="D81" s="46" t="s">
         <v>145</v>
@@ -6866,7 +6859,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C82" s="35"/>
       <c r="D82" s="46" t="s">
         <v>146</v>
@@ -6912,7 +6905,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C83" s="35"/>
       <c r="D83" s="46" t="s">
         <v>147</v>
@@ -6958,7 +6951,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C84" s="35"/>
       <c r="D84" s="46" t="s">
         <v>148</v>
@@ -7006,7 +6999,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C85" s="35"/>
       <c r="D85" s="46" t="s">
         <v>149</v>
@@ -7054,7 +7047,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C86" s="35"/>
       <c r="D86" s="46" t="s">
         <v>150</v>
@@ -7100,7 +7093,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C87" s="35"/>
       <c r="D87" s="46" t="s">
         <v>151</v>
@@ -7146,7 +7139,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C88" s="35"/>
       <c r="D88" s="46" t="s">
         <v>118</v>
@@ -7180,7 +7173,9 @@
       <c r="N88" s="39">
         <v>1</v>
       </c>
-      <c r="O88" s="35"/>
+      <c r="O88" s="64">
+        <v>46329</v>
+      </c>
       <c r="P88" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7190,7 +7185,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C89" s="35"/>
       <c r="D89" s="46" t="s">
         <v>152</v>
@@ -7226,7 +7221,9 @@
       <c r="N89" s="39">
         <v>1</v>
       </c>
-      <c r="O89" s="35"/>
+      <c r="O89" s="64">
+        <v>46329</v>
+      </c>
       <c r="P89" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7236,7 +7233,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C90" s="35"/>
       <c r="D90" s="46" t="s">
         <v>144</v>
@@ -7272,7 +7269,9 @@
       <c r="N90" s="39">
         <v>1</v>
       </c>
-      <c r="O90" s="35"/>
+      <c r="O90" s="64">
+        <v>46329</v>
+      </c>
       <c r="P90" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7282,7 +7281,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C91" s="35"/>
       <c r="D91" s="46" t="s">
         <v>154</v>
@@ -7316,7 +7315,9 @@
       <c r="N91" s="39">
         <v>1</v>
       </c>
-      <c r="O91" s="35"/>
+      <c r="O91" s="64">
+        <v>46329</v>
+      </c>
       <c r="P91" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7326,7 +7327,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C92" s="35"/>
       <c r="D92" s="46" t="s">
         <v>155</v>
@@ -7360,7 +7361,9 @@
       <c r="N92" s="39">
         <v>1</v>
       </c>
-      <c r="O92" s="35"/>
+      <c r="O92" s="64">
+        <v>46329</v>
+      </c>
       <c r="P92" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7370,7 +7373,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C93" s="35"/>
       <c r="D93" s="46" t="s">
         <v>156</v>
@@ -7404,7 +7407,9 @@
       <c r="N93" s="39">
         <v>1</v>
       </c>
-      <c r="O93" s="35"/>
+      <c r="O93" s="64">
+        <v>46329</v>
+      </c>
       <c r="P93" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7414,7 +7419,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C94" s="35"/>
       <c r="D94" s="46" t="s">
         <v>52</v>
@@ -7433,8 +7438,12 @@
       <c r="I94" s="38">
         <v>89</v>
       </c>
-      <c r="J94" s="38"/>
-      <c r="K94" s="38"/>
+      <c r="J94" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K94" s="38" t="s">
+        <v>121</v>
+      </c>
       <c r="L94" s="38">
         <f t="shared" si="7"/>
         <v>89</v>
@@ -7446,7 +7455,9 @@
       <c r="N94" s="39">
         <v>1</v>
       </c>
-      <c r="O94" s="35"/>
+      <c r="O94" s="64">
+        <v>46329</v>
+      </c>
       <c r="P94" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7456,7 +7467,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C95" s="35"/>
       <c r="D95" s="46" t="s">
         <v>281</v>
@@ -7474,8 +7485,12 @@
         <f>58+48+48</f>
         <v>154</v>
       </c>
-      <c r="J95" s="38"/>
-      <c r="K95" s="38"/>
+      <c r="J95" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K95" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="L95" s="38">
         <f t="shared" si="7"/>
         <v>154</v>
@@ -7487,7 +7502,9 @@
       <c r="N95" s="39">
         <v>1</v>
       </c>
-      <c r="O95" s="35"/>
+      <c r="O95" s="64">
+        <v>46329</v>
+      </c>
       <c r="P95" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7497,7 +7514,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C96" s="35"/>
       <c r="D96" s="46" t="s">
         <v>281</v>
@@ -7514,8 +7531,12 @@
       <c r="I96" s="38">
         <v>48</v>
       </c>
-      <c r="J96" s="38"/>
-      <c r="K96" s="38"/>
+      <c r="J96" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K96" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="L96" s="38">
         <f t="shared" si="7"/>
         <v>48</v>
@@ -7527,7 +7548,9 @@
       <c r="N96" s="39">
         <v>1</v>
       </c>
-      <c r="O96" s="35"/>
+      <c r="O96" s="64">
+        <v>46329</v>
+      </c>
       <c r="P96" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7537,7 +7560,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C97" s="35"/>
       <c r="D97" s="46" t="s">
         <v>282</v>
@@ -7556,8 +7579,12 @@
       <c r="I97" s="38">
         <v>40</v>
       </c>
-      <c r="J97" s="38"/>
-      <c r="K97" s="38"/>
+      <c r="J97" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K97" s="38" t="s">
+        <v>107</v>
+      </c>
       <c r="L97" s="38">
         <f t="shared" si="7"/>
         <v>40</v>
@@ -7569,7 +7596,9 @@
       <c r="N97" s="39">
         <v>1</v>
       </c>
-      <c r="O97" s="35"/>
+      <c r="O97" s="64">
+        <v>46329</v>
+      </c>
       <c r="P97" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7579,7 +7608,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C98" s="35"/>
       <c r="D98" s="46" t="s">
         <v>117</v>
@@ -7598,8 +7627,12 @@
       <c r="I98" s="38">
         <v>75</v>
       </c>
-      <c r="J98" s="38"/>
-      <c r="K98" s="38"/>
+      <c r="J98" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K98" s="38" t="s">
+        <v>107</v>
+      </c>
       <c r="L98" s="38">
         <f t="shared" si="7"/>
         <v>75</v>
@@ -7611,7 +7644,9 @@
       <c r="N98" s="39">
         <v>1</v>
       </c>
-      <c r="O98" s="35"/>
+      <c r="O98" s="64">
+        <v>46329</v>
+      </c>
       <c r="P98" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7621,7 +7656,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C99" s="35"/>
       <c r="D99" s="46" t="s">
         <v>119</v>
@@ -7640,8 +7675,12 @@
       <c r="I99" s="38">
         <v>-37.5</v>
       </c>
-      <c r="J99" s="38"/>
-      <c r="K99" s="38"/>
+      <c r="J99" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="K99" s="38" t="s">
+        <v>113</v>
+      </c>
       <c r="L99" s="38">
         <f t="shared" si="7"/>
         <v>-37.5</v>
@@ -7653,7 +7692,9 @@
       <c r="N99" s="39">
         <v>1</v>
       </c>
-      <c r="O99" s="35"/>
+      <c r="O99" s="64">
+        <v>46329</v>
+      </c>
       <c r="P99" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7663,7 +7704,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C100" s="35"/>
       <c r="D100" s="46" t="s">
         <v>285</v>
@@ -7678,22 +7719,28 @@
         <v>1</v>
       </c>
       <c r="I100" s="38">
-        <v>-200</v>
-      </c>
-      <c r="J100" s="38"/>
-      <c r="K100" s="38"/>
+        <v>-150</v>
+      </c>
+      <c r="J100" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="K100" s="38" t="s">
+        <v>113</v>
+      </c>
       <c r="L100" s="38">
         <f t="shared" si="7"/>
-        <v>-200</v>
+        <v>-150</v>
       </c>
       <c r="M100" s="38">
         <f t="shared" si="8"/>
-        <v>-200</v>
+        <v>-150</v>
       </c>
       <c r="N100" s="39">
         <v>1</v>
       </c>
-      <c r="O100" s="35"/>
+      <c r="O100" s="64">
+        <v>46329</v>
+      </c>
       <c r="P100" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7703,65 +7750,93 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C101" s="35"/>
-      <c r="D101" s="46"/>
-      <c r="E101" s="37"/>
-      <c r="F101" s="37"/>
+      <c r="D101" s="46" t="s">
+        <v>286</v>
+      </c>
+      <c r="E101" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F101" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G101" s="37"/>
       <c r="H101" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I101" s="38"/>
-      <c r="J101" s="38"/>
-      <c r="K101" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I101" s="38">
+        <v>165.42</v>
+      </c>
+      <c r="J101" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="K101" s="38" t="s">
+        <v>121</v>
+      </c>
       <c r="L101" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M101" s="38" t="str">
+        <v>82.71</v>
+      </c>
+      <c r="M101" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>41.354999999999997</v>
       </c>
       <c r="N101" s="39">
-        <v>1</v>
-      </c>
-      <c r="O101" s="35"/>
-      <c r="P101" s="35" t="str">
+        <v>2</v>
+      </c>
+      <c r="O101" s="64">
+        <v>46329</v>
+      </c>
+      <c r="P101" s="35">
         <f t="shared" si="9"/>
-        <v/>
+        <v>46359</v>
       </c>
       <c r="Q101" s="37" t="str">
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C102" s="35"/>
-      <c r="D102" s="46"/>
-      <c r="E102" s="37"/>
-      <c r="F102" s="37"/>
+      <c r="D102" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="E102" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F102" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G102" s="37"/>
       <c r="H102" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I102" s="38"/>
-      <c r="J102" s="38"/>
-      <c r="K102" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I102" s="38">
+        <v>67.989999999999995</v>
+      </c>
+      <c r="J102" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K102" s="38" t="s">
+        <v>121</v>
+      </c>
       <c r="L102" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M102" s="38" t="str">
+        <v>67.989999999999995</v>
+      </c>
+      <c r="M102" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>33.994999999999997</v>
       </c>
       <c r="N102" s="39">
         <v>1</v>
       </c>
-      <c r="O102" s="35"/>
+      <c r="O102" s="64">
+        <v>46329</v>
+      </c>
       <c r="P102" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7771,31 +7846,45 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C103" s="35"/>
-      <c r="D103" s="46"/>
-      <c r="E103" s="37"/>
-      <c r="F103" s="37"/>
+      <c r="D103" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="E103" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F103" s="37" t="s">
+        <v>2</v>
+      </c>
       <c r="G103" s="37"/>
       <c r="H103" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I103" s="38"/>
-      <c r="J103" s="38"/>
-      <c r="K103" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="I103" s="38">
+        <v>112.9</v>
+      </c>
+      <c r="J103" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K103" s="38" t="s">
+        <v>111</v>
+      </c>
       <c r="L103" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M103" s="38" t="str">
+        <v>112.9</v>
+      </c>
+      <c r="M103" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>56.45</v>
       </c>
       <c r="N103" s="39">
         <v>1</v>
       </c>
-      <c r="O103" s="35"/>
+      <c r="O103" s="64">
+        <v>46329</v>
+      </c>
       <c r="P103" s="35" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7805,26 +7894,32 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C104" s="35"/>
-      <c r="D104" s="46"/>
-      <c r="E104" s="37"/>
+      <c r="D104" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="E104" s="37" t="s">
+        <v>1</v>
+      </c>
       <c r="F104" s="37"/>
       <c r="G104" s="37"/>
       <c r="H104" s="37">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I104" s="38"/>
+        <v>1</v>
+      </c>
+      <c r="I104" s="38">
+        <v>-280</v>
+      </c>
       <c r="J104" s="38"/>
       <c r="K104" s="38"/>
       <c r="L104" s="38">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M104" s="38" t="str">
+        <v>-280</v>
+      </c>
+      <c r="M104" s="38">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-280</v>
       </c>
       <c r="N104" s="39">
         <v>1</v>
@@ -7839,7 +7934,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C105" s="35"/>
       <c r="D105" s="46"/>
       <c r="E105" s="37"/>
@@ -7873,7 +7968,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C106" s="35"/>
       <c r="D106" s="46"/>
       <c r="E106" s="37"/>
@@ -7907,7 +8002,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C107" s="35"/>
       <c r="D107" s="46"/>
       <c r="E107" s="37"/>
@@ -7941,7 +8036,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C108" s="35"/>
       <c r="D108" s="46"/>
       <c r="E108" s="37"/>
@@ -7975,7 +8070,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C109" s="35"/>
       <c r="D109" s="46"/>
       <c r="E109" s="37"/>
@@ -8009,7 +8104,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C110" s="35"/>
       <c r="D110" s="46"/>
       <c r="E110" s="37"/>
@@ -8043,7 +8138,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C111" s="35"/>
       <c r="D111" s="46"/>
       <c r="E111" s="37"/>
@@ -8077,7 +8172,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C112" s="35"/>
       <c r="D112" s="46"/>
       <c r="E112" s="37"/>
@@ -8111,7 +8206,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C113" s="35"/>
       <c r="D113" s="46"/>
       <c r="E113" s="37"/>
@@ -8145,7 +8240,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C114" s="35"/>
       <c r="D114" s="46"/>
       <c r="E114" s="37"/>
@@ -8179,7 +8274,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C115" s="35"/>
       <c r="D115" s="46"/>
       <c r="E115" s="37"/>
@@ -8213,7 +8308,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C116" s="35"/>
       <c r="D116" s="46"/>
       <c r="E116" s="37"/>
@@ -8247,7 +8342,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C117" s="35"/>
       <c r="D117" s="46"/>
       <c r="E117" s="37"/>
@@ -8281,7 +8376,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C118" s="35"/>
       <c r="D118" s="46"/>
       <c r="E118" s="37"/>
@@ -8315,7 +8410,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C119" s="35"/>
       <c r="D119" s="46"/>
       <c r="E119" s="37"/>
@@ -8349,7 +8444,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C120" s="35"/>
       <c r="D120" s="46"/>
       <c r="E120" s="37"/>
@@ -8383,7 +8478,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C121" s="35"/>
       <c r="D121" s="46"/>
       <c r="E121" s="37"/>
@@ -8417,7 +8512,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C122" s="35"/>
       <c r="D122" s="46"/>
       <c r="E122" s="37"/>
@@ -8451,7 +8546,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C123" s="35"/>
       <c r="D123" s="46"/>
       <c r="E123" s="37"/>
@@ -8485,7 +8580,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C124" s="35"/>
       <c r="D124" s="46"/>
       <c r="E124" s="37"/>
@@ -8519,7 +8614,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C125" s="35"/>
       <c r="D125" s="46"/>
       <c r="E125" s="37"/>
@@ -8553,7 +8648,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C126" s="35"/>
       <c r="D126" s="46"/>
       <c r="E126" s="37"/>
@@ -8587,7 +8682,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C127" s="35"/>
       <c r="D127" s="46"/>
       <c r="E127" s="37"/>
@@ -8621,7 +8716,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C128" s="35"/>
       <c r="D128" s="46"/>
       <c r="E128" s="37"/>
@@ -8655,7 +8750,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C129" s="35"/>
       <c r="D129" s="46"/>
       <c r="E129" s="37"/>
@@ -8689,7 +8784,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C130" s="35"/>
       <c r="D130" s="46"/>
       <c r="E130" s="37"/>
@@ -8723,7 +8818,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C131" s="35"/>
       <c r="D131" s="46"/>
       <c r="E131" s="37"/>
@@ -8757,7 +8852,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C132" s="35"/>
       <c r="D132" s="46"/>
       <c r="E132" s="37"/>
@@ -8791,7 +8886,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C133" s="35"/>
       <c r="D133" s="46"/>
       <c r="E133" s="37"/>
@@ -8825,7 +8920,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C134" s="35"/>
       <c r="D134" s="46"/>
       <c r="E134" s="37"/>
@@ -8859,7 +8954,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C135" s="35"/>
       <c r="D135" s="46"/>
       <c r="E135" s="37"/>
@@ -8893,7 +8988,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C136" s="35"/>
       <c r="D136" s="46"/>
       <c r="E136" s="37"/>
@@ -8927,7 +9022,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C137" s="35"/>
       <c r="D137" s="46"/>
       <c r="E137" s="37"/>
@@ -8961,7 +9056,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C138" s="35"/>
       <c r="D138" s="46"/>
       <c r="E138" s="37"/>
@@ -8995,7 +9090,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C139" s="35"/>
       <c r="D139" s="46"/>
       <c r="E139" s="37"/>
@@ -9029,7 +9124,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C140" s="35"/>
       <c r="D140" s="46"/>
       <c r="E140" s="37"/>
@@ -9063,7 +9158,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C141" s="35"/>
       <c r="D141" s="46"/>
       <c r="E141" s="37"/>
@@ -9097,7 +9192,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C142" s="35"/>
       <c r="D142" s="46"/>
       <c r="E142" s="37"/>
@@ -9138,37 +9233,37 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="I6:I142">
-    <cfRule type="cellIs" dxfId="20" priority="32" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="32" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J142 J71:K73 J83:K83 J86:K86 J91:K91">
-    <cfRule type="cellIs" dxfId="19" priority="6" operator="equal">
+  <conditionalFormatting sqref="J71:K73 J83:K83 J86:K86 J91:K91 J6:J142">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:K142">
-    <cfRule type="cellIs" dxfId="18" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="25" operator="equal">
       <formula>"Parcelado"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="cellIs" dxfId="17" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="24" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="cellIs" dxfId="16" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K49">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K54">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9180,21 +9275,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:R21"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" customWidth="1"/>
-    <col min="4" max="4" width="33.85546875" customWidth="1"/>
-    <col min="5" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" customWidth="1"/>
-    <col min="12" max="14" width="13.5703125" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="53.42578125" customWidth="1"/>
-    <col min="18" max="18" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="36.5546875" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="4" max="4" width="33.88671875" customWidth="1"/>
+    <col min="5" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" customWidth="1"/>
+    <col min="12" max="14" width="13.5546875" customWidth="1"/>
+    <col min="15" max="15" width="13.5546875" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="53.44140625" customWidth="1"/>
+    <col min="18" max="18" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D2" s="33" t="s">
         <v>36</v>
       </c>
@@ -9232,7 +9327,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D3" s="54" t="s">
         <v>23</v>
       </c>
@@ -9270,7 +9365,7 @@
       </c>
       <c r="R3" s="16"/>
     </row>
-    <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D4" s="55" t="s">
         <v>157</v>
       </c>
@@ -9308,7 +9403,7 @@
       </c>
       <c r="R4" s="16"/>
     </row>
-    <row r="5" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="30" t="s">
         <v>1</v>
       </c>
@@ -9349,7 +9444,7 @@
       </c>
       <c r="P5" s="59"/>
     </row>
-    <row r="6" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="32">
         <f>SUMIF($E$3:$E$35,B5,$K$3:$K$35)</f>
         <v>2557.84</v>
@@ -9390,7 +9485,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="60"/>
       <c r="D7" s="54" t="s">
         <v>160</v>
@@ -9428,7 +9523,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="30" t="s">
         <v>2</v>
       </c>
@@ -9468,7 +9563,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="61">
         <f>SUMIF($F$3:$F$35,B8,$K$3:$K$35)</f>
         <v>5899.84</v>
@@ -9484,7 +9579,7 @@
       </c>
       <c r="G9" s="37"/>
       <c r="H9" s="37">
-        <f>COUNTA(E9:G9)</f>
+        <f t="shared" ref="H9:H14" si="4">COUNTA(E9:G9)</f>
         <v>2</v>
       </c>
       <c r="I9" s="38">
@@ -9510,7 +9605,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D10" s="54" t="s">
         <v>162</v>
       </c>
@@ -9520,7 +9615,7 @@
       </c>
       <c r="G10" s="37"/>
       <c r="H10" s="37">
-        <f>COUNTA(E10:G10)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I10" s="38">
@@ -9545,7 +9640,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D11" s="54" t="s">
         <v>163</v>
       </c>
@@ -9555,7 +9650,7 @@
       </c>
       <c r="G11" s="37"/>
       <c r="H11" s="37">
-        <f>COUNTA(E11:G11)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I11" s="38">
@@ -9580,7 +9675,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D12" s="54" t="s">
         <v>283</v>
       </c>
@@ -9590,22 +9685,22 @@
       </c>
       <c r="G12" s="37"/>
       <c r="H12" s="37">
-        <f>COUNTA(E12:G12)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I12" s="38">
         <v>300</v>
       </c>
       <c r="J12" s="38">
-        <f t="shared" ref="J12" si="4">I12/L12</f>
+        <f t="shared" ref="J12" si="5">I12/L12</f>
         <v>300</v>
       </c>
       <c r="K12" s="38">
-        <f t="shared" ref="K12" si="5">IFERROR(J12/H12,"")</f>
+        <f t="shared" ref="K12" si="6">IFERROR(J12/H12,"")</f>
         <v>300</v>
       </c>
       <c r="L12" s="37">
-        <f t="shared" ref="L12" si="6">(DATEDIF(M12,N12,"m")+1)</f>
+        <f t="shared" ref="L12" si="7">(DATEDIF(M12,N12,"m")+1)</f>
         <v>1</v>
       </c>
       <c r="M12" s="38"/>
@@ -9615,7 +9710,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D13" s="54" t="s">
         <v>164</v>
       </c>
@@ -9625,7 +9720,7 @@
       </c>
       <c r="G13" s="37"/>
       <c r="H13" s="37">
-        <f>COUNTA(E13:G13)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I13" s="38">
@@ -9650,7 +9745,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D14" s="54" t="s">
         <v>165</v>
       </c>
@@ -9662,7 +9757,7 @@
       </c>
       <c r="G14" s="37"/>
       <c r="H14" s="37">
-        <f>COUNTA(E14:G14)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="I14" s="38">
@@ -9687,7 +9782,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D15" s="37"/>
       <c r="E15" s="36"/>
       <c r="F15" s="37"/>
@@ -9701,7 +9796,7 @@
       <c r="N15" s="38"/>
       <c r="O15" s="39"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.3">
       <c r="D16" s="37"/>
       <c r="E16" s="36"/>
       <c r="F16" s="37"/>
@@ -9715,7 +9810,7 @@
       <c r="N16" s="38"/>
       <c r="O16" s="39"/>
     </row>
-    <row r="17" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D17" s="37"/>
       <c r="E17" s="36"/>
       <c r="F17" s="37"/>
@@ -9729,7 +9824,7 @@
       <c r="N17" s="38"/>
       <c r="O17" s="39"/>
     </row>
-    <row r="18" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D18" s="37"/>
       <c r="E18" s="36"/>
       <c r="F18" s="37"/>
@@ -9743,7 +9838,7 @@
       <c r="N18" s="38"/>
       <c r="O18" s="39"/>
     </row>
-    <row r="19" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D19" s="37"/>
       <c r="E19" s="36"/>
       <c r="F19" s="37"/>
@@ -9757,7 +9852,7 @@
       <c r="N19" s="38"/>
       <c r="O19" s="39"/>
     </row>
-    <row r="20" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D20" s="37"/>
       <c r="E20" s="36"/>
       <c r="F20" s="37"/>
@@ -9771,7 +9866,7 @@
       <c r="N20" s="38"/>
       <c r="O20" s="39"/>
     </row>
-    <row r="21" spans="4:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:15" x14ac:dyDescent="0.3">
       <c r="D21" s="37"/>
       <c r="E21" s="36"/>
       <c r="F21" s="37"/>
@@ -9794,33 +9889,33 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:O404"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
-    <col min="6" max="6" width="39.7109375" customWidth="1"/>
-    <col min="7" max="7" width="35.42578125" style="1" customWidth="1"/>
-    <col min="8" max="10" width="35.42578125" customWidth="1"/>
-    <col min="12" max="12" width="35.85546875" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" customWidth="1"/>
+    <col min="6" max="6" width="39.6640625" customWidth="1"/>
+    <col min="7" max="7" width="35.44140625" style="1" customWidth="1"/>
+    <col min="8" max="10" width="35.44140625" customWidth="1"/>
+    <col min="12" max="12" width="35.88671875" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
     <col min="14" max="14" width="24" customWidth="1"/>
     <col min="15" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.3">
       <c r="G1" s="2"/>
       <c r="N1" s="47" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G2" s="2"/>
       <c r="N2" s="43"/>
     </row>
-    <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G3" s="2"/>
       <c r="L3" s="47" t="s">
         <v>167</v>
@@ -9830,11 +9925,11 @@
       </c>
       <c r="N3" s="43">
         <f>SUM(N5:N21)</f>
-        <v>757</v>
+        <v>477</v>
       </c>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
       <c r="G4" s="2"/>
       <c r="L4" s="48" t="s">
         <v>169</v>
@@ -9842,7 +9937,7 @@
       <c r="M4" s="85"/>
       <c r="N4" s="49"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="43"/>
       <c r="C5" s="43"/>
       <c r="F5" s="16"/>
@@ -9855,7 +9950,7 @@
       </c>
       <c r="O5" s="16"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="G6" s="2"/>
       <c r="L6" t="s">
         <v>171</v>
@@ -9864,19 +9959,11 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="G7" s="2"/>
-      <c r="L7" t="s">
-        <v>172</v>
-      </c>
-      <c r="M7" t="s">
-        <v>173</v>
-      </c>
-      <c r="N7" s="71">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="N7" s="71"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F8" s="16"/>
       <c r="G8" s="50"/>
       <c r="L8" t="s">
@@ -9889,14 +9976,14 @@
         <v>240</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F9" s="47" t="s">
         <v>174</v>
       </c>
       <c r="G9" s="28"/>
       <c r="N9" s="70"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="E10" t="s">
         <v>175</v>
       </c>
@@ -9915,7 +10002,7 @@
       </c>
       <c r="N10" s="70"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="E11" t="s">
         <v>179</v>
       </c>
@@ -9937,7 +10024,7 @@
       </c>
       <c r="N11" s="70"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F12" t="s">
         <v>167</v>
       </c>
@@ -9946,7 +10033,7 @@
       </c>
       <c r="N12" s="70"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="F13" s="80" t="s">
         <v>169</v>
       </c>
@@ -9955,7 +10042,7 @@
       <c r="I13" s="80"/>
       <c r="N13" s="70"/>
     </row>
-    <row r="14" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F14" t="s">
         <v>180</v>
       </c>
@@ -9964,7 +10051,7 @@
       <c r="I14" s="53"/>
       <c r="N14" s="43"/>
     </row>
-    <row r="15" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F15" t="s">
         <v>181</v>
       </c>
@@ -9975,7 +10062,7 @@
       <c r="I15" s="53"/>
       <c r="N15" s="43"/>
     </row>
-    <row r="16" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F16" t="s">
         <v>182</v>
       </c>
@@ -9986,7 +10073,7 @@
       <c r="I16" s="53"/>
       <c r="N16" s="43"/>
     </row>
-    <row r="17" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F17" t="s">
         <v>183</v>
       </c>
@@ -9997,7 +10084,7 @@
       <c r="I17" s="53"/>
       <c r="N17" s="43"/>
     </row>
-    <row r="18" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F18" t="s">
         <v>184</v>
       </c>
@@ -10008,7 +10095,7 @@
       <c r="I18" s="53"/>
       <c r="N18" s="43"/>
     </row>
-    <row r="19" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F19" t="s">
         <v>185</v>
       </c>
@@ -10019,7 +10106,7 @@
       <c r="I19" s="53"/>
       <c r="N19" s="43"/>
     </row>
-    <row r="20" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F20" t="s">
         <v>186</v>
       </c>
@@ -10030,7 +10117,7 @@
       <c r="I20" s="53"/>
       <c r="N20" s="43"/>
     </row>
-    <row r="21" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F21" t="s">
         <v>187</v>
       </c>
@@ -10041,7 +10128,7 @@
       <c r="I21" s="53"/>
       <c r="N21" s="43"/>
     </row>
-    <row r="22" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F22" t="s">
         <v>188</v>
       </c>
@@ -10052,7 +10139,7 @@
       <c r="I22" s="53"/>
       <c r="N22" s="43"/>
     </row>
-    <row r="23" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F23" t="s">
         <v>133</v>
       </c>
@@ -10063,7 +10150,7 @@
       <c r="I23" s="53"/>
       <c r="N23" s="43"/>
     </row>
-    <row r="24" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F24" t="s">
         <v>185</v>
       </c>
@@ -10074,7 +10161,7 @@
       <c r="I24" s="53"/>
       <c r="N24" s="43"/>
     </row>
-    <row r="25" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F25" t="s">
         <v>189</v>
       </c>
@@ -10085,7 +10172,7 @@
       <c r="I25" s="53"/>
       <c r="N25" s="43"/>
     </row>
-    <row r="26" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F26" t="s">
         <v>190</v>
       </c>
@@ -10096,7 +10183,7 @@
       <c r="I26" s="53"/>
       <c r="N26" s="43"/>
     </row>
-    <row r="27" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F27" t="s">
         <v>191</v>
       </c>
@@ -10107,7 +10194,7 @@
       <c r="I27" s="53"/>
       <c r="N27" s="43"/>
     </row>
-    <row r="28" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F28" t="s">
         <v>192</v>
       </c>
@@ -10118,7 +10205,7 @@
       <c r="I28" s="53"/>
       <c r="N28" s="43"/>
     </row>
-    <row r="29" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F29" t="s">
         <v>188</v>
       </c>
@@ -10129,7 +10216,7 @@
       <c r="I29" s="53"/>
       <c r="N29" s="43"/>
     </row>
-    <row r="30" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F30" t="s">
         <v>193</v>
       </c>
@@ -10140,7 +10227,7 @@
       <c r="I30" s="53"/>
       <c r="N30" s="43"/>
     </row>
-    <row r="31" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F31" t="s">
         <v>114</v>
       </c>
@@ -10151,7 +10238,7 @@
       <c r="I31" s="53"/>
       <c r="N31" s="43"/>
     </row>
-    <row r="32" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F32" t="s">
         <v>194</v>
       </c>
@@ -10162,7 +10249,7 @@
       <c r="I32" s="53"/>
       <c r="N32" s="43"/>
     </row>
-    <row r="33" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F33" t="s">
         <v>195</v>
       </c>
@@ -10173,7 +10260,7 @@
       <c r="I33" s="53"/>
       <c r="N33" s="43"/>
     </row>
-    <row r="34" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F34" t="s">
         <v>196</v>
       </c>
@@ -10184,7 +10271,7 @@
       <c r="I34" s="53"/>
       <c r="N34" s="43"/>
     </row>
-    <row r="35" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F35" t="s">
         <v>197</v>
       </c>
@@ -10195,7 +10282,7 @@
       <c r="I35" s="53"/>
       <c r="N35" s="43"/>
     </row>
-    <row r="36" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F36" t="s">
         <v>198</v>
       </c>
@@ -10206,7 +10293,7 @@
       <c r="I36" s="53"/>
       <c r="N36" s="43"/>
     </row>
-    <row r="37" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F37" t="s">
         <v>199</v>
       </c>
@@ -10217,7 +10304,7 @@
       <c r="I37" s="53"/>
       <c r="N37" s="43"/>
     </row>
-    <row r="38" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F38" t="s">
         <v>200</v>
       </c>
@@ -10228,7 +10315,7 @@
       <c r="I38" s="53"/>
       <c r="N38" s="43"/>
     </row>
-    <row r="39" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F39" t="s">
         <v>188</v>
       </c>
@@ -10239,7 +10326,7 @@
       <c r="I39" s="53"/>
       <c r="N39" s="43"/>
     </row>
-    <row r="40" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="E40" s="2"/>
       <c r="F40" t="s">
         <v>201</v>
@@ -10251,7 +10338,7 @@
       <c r="I40" s="53"/>
       <c r="N40" s="43"/>
     </row>
-    <row r="41" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F41" t="s">
         <v>202</v>
       </c>
@@ -10262,7 +10349,7 @@
       <c r="I41" s="53"/>
       <c r="N41" s="43"/>
     </row>
-    <row r="42" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F42" t="s">
         <v>203</v>
       </c>
@@ -10273,7 +10360,7 @@
       <c r="I42" s="53"/>
       <c r="N42" s="43"/>
     </row>
-    <row r="43" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F43" t="s">
         <v>204</v>
       </c>
@@ -10284,7 +10371,7 @@
       <c r="I43" s="53"/>
       <c r="N43" s="43"/>
     </row>
-    <row r="44" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="E44" s="2"/>
       <c r="F44" t="s">
         <v>205</v>
@@ -10296,7 +10383,7 @@
       <c r="I44" s="53"/>
       <c r="N44" s="43"/>
     </row>
-    <row r="45" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F45" t="s">
         <v>206</v>
       </c>
@@ -10307,7 +10394,7 @@
       <c r="I45" s="53"/>
       <c r="N45" s="43"/>
     </row>
-    <row r="46" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F46" t="s">
         <v>207</v>
       </c>
@@ -10318,7 +10405,7 @@
       <c r="I46" s="53"/>
       <c r="N46" s="43"/>
     </row>
-    <row r="47" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F47" t="s">
         <v>208</v>
       </c>
@@ -10329,7 +10416,7 @@
       <c r="I47" s="53"/>
       <c r="N47" s="43"/>
     </row>
-    <row r="48" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F48" t="s">
         <v>185</v>
       </c>
@@ -10340,7 +10427,7 @@
       <c r="I48" s="53"/>
       <c r="N48" s="43"/>
     </row>
-    <row r="49" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F49" t="s">
         <v>209</v>
       </c>
@@ -10351,7 +10438,7 @@
       <c r="I49" s="53"/>
       <c r="N49" s="43"/>
     </row>
-    <row r="50" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F50" t="s">
         <v>210</v>
       </c>
@@ -10362,7 +10449,7 @@
       <c r="I50" s="53"/>
       <c r="N50" s="43"/>
     </row>
-    <row r="51" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F51" t="s">
         <v>211</v>
       </c>
@@ -10373,7 +10460,7 @@
       <c r="I51" s="53"/>
       <c r="N51" s="43"/>
     </row>
-    <row r="52" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F52" t="s">
         <v>188</v>
       </c>
@@ -10384,7 +10471,7 @@
       <c r="I52" s="53"/>
       <c r="N52" s="43"/>
     </row>
-    <row r="53" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F53" t="s">
         <v>212</v>
       </c>
@@ -10395,7 +10482,7 @@
       <c r="I53" s="53"/>
       <c r="N53" s="43"/>
     </row>
-    <row r="54" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F54" t="s">
         <v>213</v>
       </c>
@@ -10406,7 +10493,7 @@
       <c r="I54" s="53"/>
       <c r="N54" s="43"/>
     </row>
-    <row r="55" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="6:14" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="F55" t="s">
         <v>214</v>
       </c>
@@ -10417,7 +10504,7 @@
       <c r="I55" s="53"/>
       <c r="N55" s="43"/>
     </row>
-    <row r="56" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F56" t="s">
         <v>215</v>
       </c>
@@ -10428,7 +10515,7 @@
       <c r="I56" s="53"/>
       <c r="N56" s="43"/>
     </row>
-    <row r="57" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F57" t="s">
         <v>185</v>
       </c>
@@ -10439,7 +10526,7 @@
       <c r="I57" s="53"/>
       <c r="N57" s="43"/>
     </row>
-    <row r="58" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F58" t="s">
         <v>188</v>
       </c>
@@ -10450,7 +10537,7 @@
       <c r="I58" s="53"/>
       <c r="N58" s="43"/>
     </row>
-    <row r="59" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F59" t="s">
         <v>216</v>
       </c>
@@ -10460,7 +10547,7 @@
       <c r="H59" s="53"/>
       <c r="I59" s="53"/>
     </row>
-    <row r="60" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F60" t="s">
         <v>217</v>
       </c>
@@ -10470,7 +10557,7 @@
       <c r="H60" s="53"/>
       <c r="I60" s="53"/>
     </row>
-    <row r="61" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F61" t="s">
         <v>218</v>
       </c>
@@ -10480,7 +10567,7 @@
       <c r="H61" s="53"/>
       <c r="I61" s="53"/>
     </row>
-    <row r="62" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F62" t="s">
         <v>219</v>
       </c>
@@ -10490,7 +10577,7 @@
       <c r="H62" s="53"/>
       <c r="I62" s="53"/>
     </row>
-    <row r="63" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="6:14" x14ac:dyDescent="0.3">
       <c r="F63" t="s">
         <v>200</v>
       </c>
@@ -10500,12 +10587,12 @@
       <c r="H63" s="53"/>
       <c r="I63" s="53"/>
     </row>
-    <row r="64" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="6:14" x14ac:dyDescent="0.3">
       <c r="G64" s="53"/>
       <c r="H64" s="53"/>
       <c r="I64" s="53"/>
     </row>
-    <row r="65" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F65" t="s">
         <v>220</v>
       </c>
@@ -10515,7 +10602,7 @@
       <c r="H65" s="53"/>
       <c r="I65" s="53"/>
     </row>
-    <row r="66" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F66" t="s">
         <v>221</v>
       </c>
@@ -10525,7 +10612,7 @@
       <c r="H66" s="53"/>
       <c r="I66" s="53"/>
     </row>
-    <row r="67" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F67" t="s">
         <v>222</v>
       </c>
@@ -10535,7 +10622,7 @@
       <c r="H67" s="53"/>
       <c r="I67" s="53"/>
     </row>
-    <row r="68" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F68" t="s">
         <v>188</v>
       </c>
@@ -10545,7 +10632,7 @@
       <c r="H68" s="53"/>
       <c r="I68" s="53"/>
     </row>
-    <row r="69" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F69" t="s">
         <v>223</v>
       </c>
@@ -10555,7 +10642,7 @@
       <c r="H69" s="53"/>
       <c r="I69" s="53"/>
     </row>
-    <row r="70" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F70" t="s">
         <v>224</v>
       </c>
@@ -10565,7 +10652,7 @@
       <c r="H70" s="53"/>
       <c r="I70" s="53"/>
     </row>
-    <row r="71" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F71" t="s">
         <v>225</v>
       </c>
@@ -10575,7 +10662,7 @@
       <c r="H71" s="53"/>
       <c r="I71" s="53"/>
     </row>
-    <row r="72" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F72" t="s">
         <v>226</v>
       </c>
@@ -10585,12 +10672,12 @@
       <c r="H72" s="53"/>
       <c r="I72" s="53"/>
     </row>
-    <row r="73" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:9" x14ac:dyDescent="0.3">
       <c r="G73" s="53"/>
       <c r="H73" s="53"/>
       <c r="I73" s="53"/>
     </row>
-    <row r="74" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F74" t="s">
         <v>185</v>
       </c>
@@ -10600,7 +10687,7 @@
       <c r="H74" s="53"/>
       <c r="I74" s="53"/>
     </row>
-    <row r="75" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F75" t="s">
         <v>227</v>
       </c>
@@ -10610,7 +10697,7 @@
       <c r="H75" s="53"/>
       <c r="I75" s="53"/>
     </row>
-    <row r="76" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F76" t="s">
         <v>228</v>
       </c>
@@ -10620,7 +10707,7 @@
       <c r="H76" s="53"/>
       <c r="I76" s="53"/>
     </row>
-    <row r="77" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F77" t="s">
         <v>229</v>
       </c>
@@ -10630,7 +10717,7 @@
       <c r="H77" s="53"/>
       <c r="I77" s="53"/>
     </row>
-    <row r="78" spans="6:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="6:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F78" t="s">
         <v>188</v>
       </c>
@@ -10640,7 +10727,7 @@
       <c r="H78" s="53"/>
       <c r="I78" s="53"/>
     </row>
-    <row r="79" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F79" t="s">
         <v>230</v>
       </c>
@@ -10650,7 +10737,7 @@
       <c r="H79" s="53"/>
       <c r="I79" s="53"/>
     </row>
-    <row r="80" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F80" t="s">
         <v>231</v>
       </c>
@@ -10660,7 +10747,7 @@
       <c r="H80" s="53"/>
       <c r="I80" s="53"/>
     </row>
-    <row r="81" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F81" t="s">
         <v>232</v>
       </c>
@@ -10670,7 +10757,7 @@
       <c r="H81" s="53"/>
       <c r="I81" s="53"/>
     </row>
-    <row r="82" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F82" t="s">
         <v>233</v>
       </c>
@@ -10680,7 +10767,7 @@
       <c r="H82" s="53"/>
       <c r="I82" s="53"/>
     </row>
-    <row r="83" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F83" t="s">
         <v>234</v>
       </c>
@@ -10690,7 +10777,7 @@
       <c r="H83" s="53"/>
       <c r="I83" s="53"/>
     </row>
-    <row r="84" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F84" t="s">
         <v>226</v>
       </c>
@@ -10700,7 +10787,7 @@
       <c r="H84" s="53"/>
       <c r="I84" s="53"/>
     </row>
-    <row r="85" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F85" t="s">
         <v>225</v>
       </c>
@@ -10710,7 +10797,7 @@
       <c r="H85" s="53"/>
       <c r="I85" s="53"/>
     </row>
-    <row r="86" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F86" t="s">
         <v>235</v>
       </c>
@@ -10720,7 +10807,7 @@
       <c r="H86" s="53"/>
       <c r="I86" s="53"/>
     </row>
-    <row r="87" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F87" t="s">
         <v>236</v>
       </c>
@@ -10730,7 +10817,7 @@
       <c r="H87" s="53"/>
       <c r="I87" s="53"/>
     </row>
-    <row r="88" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F88" t="s">
         <v>237</v>
       </c>
@@ -10740,7 +10827,7 @@
       <c r="H88" s="53"/>
       <c r="I88" s="53"/>
     </row>
-    <row r="89" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F89" t="s">
         <v>238</v>
       </c>
@@ -10750,7 +10837,7 @@
       <c r="H89" s="53"/>
       <c r="I89" s="53"/>
     </row>
-    <row r="90" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F90" t="s">
         <v>239</v>
       </c>
@@ -10760,7 +10847,7 @@
       <c r="H90" s="53"/>
       <c r="I90" s="53"/>
     </row>
-    <row r="91" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F91" t="s">
         <v>240</v>
       </c>
@@ -10770,7 +10857,7 @@
       <c r="H91" s="53"/>
       <c r="I91" s="53"/>
     </row>
-    <row r="92" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F92" t="s">
         <v>241</v>
       </c>
@@ -10780,7 +10867,7 @@
       <c r="H92" s="53"/>
       <c r="I92" s="53"/>
     </row>
-    <row r="93" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F93" t="s">
         <v>242</v>
       </c>
@@ -10790,7 +10877,7 @@
       <c r="H93" s="53"/>
       <c r="I93" s="53"/>
     </row>
-    <row r="94" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F94" t="s">
         <v>243</v>
       </c>
@@ -10800,7 +10887,7 @@
       <c r="H94" s="53"/>
       <c r="I94" s="53"/>
     </row>
-    <row r="95" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:9" x14ac:dyDescent="0.3">
       <c r="F95" t="s">
         <v>244</v>
       </c>
@@ -10810,7 +10897,7 @@
       <c r="H95" s="53"/>
       <c r="I95" s="53"/>
     </row>
-    <row r="96" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C96" s="53"/>
       <c r="F96" t="s">
         <v>245</v>
@@ -10821,7 +10908,7 @@
       <c r="H96" s="53"/>
       <c r="I96" s="53"/>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C97" s="53"/>
       <c r="D97" s="53"/>
       <c r="F97" t="s">
@@ -10833,7 +10920,7 @@
       <c r="H97" s="53"/>
       <c r="I97" s="53"/>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C98" s="53"/>
       <c r="D98" s="53"/>
       <c r="F98" t="s">
@@ -10845,13 +10932,13 @@
       <c r="H98" s="53"/>
       <c r="I98" s="53"/>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>188</v>
       </c>
       <c r="C99" s="53">
         <f>-'Compensasões e Transferências'!C21</f>
-        <v>-5876.4800000000005</v>
+        <v>-6008.2800000000007</v>
       </c>
       <c r="D99" s="53"/>
       <c r="F99" t="s">
@@ -10863,7 +10950,7 @@
       <c r="H99" s="53"/>
       <c r="I99" s="53"/>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>250</v>
       </c>
@@ -10878,7 +10965,7 @@
       <c r="H100" s="53"/>
       <c r="I100" s="53"/>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C101" s="53"/>
       <c r="D101" s="53"/>
       <c r="F101" t="s">
@@ -10890,13 +10977,13 @@
       <c r="H101" s="53"/>
       <c r="I101" s="53"/>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>253</v>
       </c>
       <c r="C102" s="53">
         <f>-C99</f>
-        <v>5876.4800000000005</v>
+        <v>6008.2800000000007</v>
       </c>
       <c r="D102" s="53"/>
       <c r="F102" t="s">
@@ -10908,7 +10995,7 @@
       <c r="H102" s="53"/>
       <c r="I102" s="53"/>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>255</v>
       </c>
@@ -10925,7 +11012,7 @@
       <c r="H103" s="53"/>
       <c r="I103" s="53"/>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C104" s="53"/>
       <c r="D104" s="53"/>
       <c r="F104" t="s">
@@ -10937,7 +11024,7 @@
       <c r="H104" s="53"/>
       <c r="I104" s="53"/>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C105" s="53"/>
       <c r="D105" s="53"/>
       <c r="F105" t="s">
@@ -10949,7 +11036,7 @@
       <c r="H105" s="53"/>
       <c r="I105" s="53"/>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C106" s="53"/>
       <c r="D106" s="53"/>
       <c r="F106" t="s">
@@ -10961,7 +11048,7 @@
       <c r="H106" s="53"/>
       <c r="I106" s="53"/>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
         <v>258</v>
       </c>
@@ -10980,7 +11067,7 @@
       <c r="H107" s="53"/>
       <c r="I107" s="53"/>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>260</v>
       </c>
@@ -10997,7 +11084,7 @@
       <c r="H108" s="53"/>
       <c r="I108" s="53"/>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>261</v>
       </c>
@@ -11014,14 +11101,14 @@
       <c r="H109" s="53"/>
       <c r="I109" s="53"/>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C110" s="53"/>
       <c r="D110" s="53"/>
       <c r="G110" s="53"/>
       <c r="H110" s="53"/>
       <c r="I110" s="53"/>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>262</v>
       </c>
@@ -11035,7 +11122,7 @@
       <c r="H111" s="53"/>
       <c r="I111" s="53"/>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
         <v>263</v>
       </c>
@@ -11049,7 +11136,7 @@
       <c r="H112" s="53"/>
       <c r="I112" s="53"/>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B113" t="s">
         <v>264</v>
       </c>
@@ -11063,14 +11150,14 @@
       <c r="H113" s="53"/>
       <c r="I113" s="53"/>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C114" s="53"/>
       <c r="D114" s="53"/>
       <c r="G114" s="53"/>
       <c r="H114" s="53"/>
       <c r="I114" s="53"/>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
         <v>265</v>
       </c>
@@ -11082,14 +11169,14 @@
       <c r="H115" s="53"/>
       <c r="I115" s="53"/>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C116" s="53"/>
       <c r="D116" s="53"/>
       <c r="G116" s="53"/>
       <c r="H116" s="53"/>
       <c r="I116" s="53"/>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
         <v>266</v>
       </c>
@@ -11103,7 +11190,7 @@
       <c r="H117" s="53"/>
       <c r="I117" s="53"/>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
         <v>267</v>
       </c>
@@ -11117,7 +11204,7 @@
       <c r="H118" s="53"/>
       <c r="I118" s="53"/>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
         <v>268</v>
       </c>
@@ -11129,7 +11216,7 @@
       <c r="H119" s="53"/>
       <c r="I119" s="53"/>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>269</v>
       </c>
@@ -11143,7 +11230,7 @@
       <c r="H120" s="53"/>
       <c r="I120" s="53"/>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>270</v>
       </c>
@@ -11157,1143 +11244,1143 @@
       <c r="H121" s="53"/>
       <c r="I121" s="53"/>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G122" s="53"/>
       <c r="H122" s="53"/>
       <c r="I122" s="53"/>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G123" s="53"/>
       <c r="H123" s="53"/>
       <c r="I123" s="53"/>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G124" s="53"/>
       <c r="H124" s="53"/>
       <c r="I124" s="53"/>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G125" s="53"/>
       <c r="H125" s="53"/>
       <c r="I125" s="53"/>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G126" s="53"/>
       <c r="H126" s="53"/>
       <c r="I126" s="53"/>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G127" s="53"/>
       <c r="H127" s="72"/>
       <c r="I127" s="53"/>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G128" s="53"/>
       <c r="H128" s="53"/>
       <c r="I128" s="53"/>
     </row>
-    <row r="129" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G129" s="53"/>
       <c r="H129" s="53"/>
       <c r="I129" s="53"/>
     </row>
-    <row r="130" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G130" s="53"/>
       <c r="H130" s="53"/>
       <c r="I130" s="53"/>
     </row>
-    <row r="131" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G131" s="53"/>
       <c r="H131" s="53"/>
       <c r="I131" s="53"/>
     </row>
-    <row r="132" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G132" s="53"/>
       <c r="H132" s="53"/>
       <c r="I132" s="53"/>
     </row>
-    <row r="133" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G133" s="53"/>
       <c r="H133" s="53"/>
       <c r="I133" s="53"/>
     </row>
-    <row r="134" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G134" s="53"/>
       <c r="H134" s="53"/>
       <c r="I134" s="53"/>
     </row>
-    <row r="135" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G135" s="53"/>
       <c r="H135" s="53"/>
       <c r="I135" s="53"/>
     </row>
-    <row r="136" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G136" s="53"/>
       <c r="H136" s="53"/>
       <c r="I136" s="53"/>
     </row>
-    <row r="137" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G137" s="53"/>
       <c r="H137" s="53"/>
       <c r="I137" s="53"/>
     </row>
-    <row r="138" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G138" s="53"/>
       <c r="H138" s="53"/>
       <c r="I138" s="53"/>
     </row>
-    <row r="139" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G139" s="53"/>
       <c r="H139" s="53"/>
       <c r="I139" s="53"/>
     </row>
-    <row r="140" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G140" s="53"/>
       <c r="H140" s="53"/>
       <c r="I140" s="53"/>
     </row>
-    <row r="141" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G141" s="53"/>
       <c r="H141" s="53"/>
       <c r="I141" s="53"/>
     </row>
-    <row r="142" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G142" s="53"/>
       <c r="H142" s="53"/>
       <c r="I142" s="53"/>
     </row>
-    <row r="143" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G143" s="53"/>
       <c r="H143" s="53"/>
       <c r="I143" s="53"/>
     </row>
-    <row r="144" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G144" s="53"/>
       <c r="H144" s="53"/>
       <c r="I144" s="53"/>
     </row>
-    <row r="145" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G145" s="53"/>
       <c r="H145" s="53"/>
       <c r="I145" s="53"/>
     </row>
-    <row r="146" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G146" s="53"/>
       <c r="H146" s="53"/>
       <c r="I146" s="53"/>
     </row>
-    <row r="147" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G147" s="53"/>
       <c r="H147" s="53"/>
       <c r="I147" s="53"/>
     </row>
-    <row r="148" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G148" s="53"/>
       <c r="H148" s="53"/>
       <c r="I148" s="53"/>
     </row>
-    <row r="149" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G149" s="53"/>
       <c r="H149" s="53"/>
       <c r="I149" s="53"/>
     </row>
-    <row r="150" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G150" s="53"/>
       <c r="H150" s="53"/>
       <c r="I150" s="53"/>
     </row>
-    <row r="151" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G151" s="53"/>
       <c r="H151" s="53"/>
       <c r="I151" s="53"/>
     </row>
-    <row r="152" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G152" s="53"/>
       <c r="H152" s="53"/>
       <c r="I152" s="53"/>
     </row>
-    <row r="153" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G153" s="53"/>
       <c r="H153" s="53"/>
       <c r="I153" s="53"/>
     </row>
-    <row r="154" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G154" s="53"/>
       <c r="H154" s="53"/>
       <c r="I154" s="53"/>
     </row>
-    <row r="155" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G155" s="53"/>
       <c r="H155" s="53"/>
       <c r="I155" s="53"/>
     </row>
-    <row r="156" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G156" s="53"/>
       <c r="H156" s="53"/>
       <c r="I156" s="53"/>
     </row>
-    <row r="157" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G157" s="53"/>
       <c r="H157" s="53"/>
       <c r="I157" s="53"/>
     </row>
-    <row r="158" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G158" s="53"/>
       <c r="H158" s="53"/>
       <c r="I158" s="53"/>
     </row>
-    <row r="159" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G159" s="53"/>
       <c r="H159" s="53"/>
       <c r="I159" s="53"/>
     </row>
-    <row r="160" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G160" s="53"/>
       <c r="H160" s="53"/>
       <c r="I160" s="53"/>
     </row>
-    <row r="161" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G161" s="53"/>
       <c r="H161" s="53"/>
       <c r="I161" s="53"/>
     </row>
-    <row r="162" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G162" s="53"/>
       <c r="H162" s="53"/>
       <c r="I162" s="53"/>
     </row>
-    <row r="163" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G163" s="53"/>
       <c r="H163" s="53"/>
       <c r="I163" s="53"/>
     </row>
-    <row r="164" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G164" s="53"/>
       <c r="H164" s="53"/>
       <c r="I164" s="53"/>
     </row>
-    <row r="165" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G165" s="53"/>
       <c r="H165" s="53"/>
       <c r="I165" s="53"/>
     </row>
-    <row r="166" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G166" s="53"/>
       <c r="H166" s="53"/>
       <c r="I166" s="53"/>
     </row>
-    <row r="167" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G167" s="53"/>
       <c r="H167" s="53"/>
       <c r="I167" s="53"/>
     </row>
-    <row r="168" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G168" s="53"/>
       <c r="H168" s="53"/>
       <c r="I168" s="53"/>
     </row>
-    <row r="169" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G169" s="53"/>
       <c r="H169" s="53"/>
       <c r="I169" s="53"/>
     </row>
-    <row r="170" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G170" s="53"/>
       <c r="H170" s="53"/>
       <c r="I170" s="53"/>
     </row>
-    <row r="171" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G171" s="53"/>
       <c r="H171" s="53"/>
       <c r="I171" s="53"/>
     </row>
-    <row r="172" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G172" s="53"/>
       <c r="H172" s="53"/>
       <c r="I172" s="53"/>
     </row>
-    <row r="173" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G173" s="53"/>
       <c r="H173" s="53"/>
       <c r="I173" s="53"/>
     </row>
-    <row r="174" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G174" s="53"/>
       <c r="H174" s="53"/>
       <c r="I174" s="53"/>
     </row>
-    <row r="175" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G175" s="53"/>
       <c r="H175" s="53"/>
       <c r="I175" s="53"/>
     </row>
-    <row r="176" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G176" s="53"/>
       <c r="H176" s="53"/>
       <c r="I176" s="53"/>
     </row>
-    <row r="177" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G177" s="53"/>
       <c r="H177" s="53"/>
       <c r="I177" s="53"/>
     </row>
-    <row r="178" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G178" s="53"/>
       <c r="H178" s="53"/>
       <c r="I178" s="53"/>
     </row>
-    <row r="179" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G179" s="53"/>
       <c r="H179" s="53"/>
       <c r="I179" s="53"/>
     </row>
-    <row r="180" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G180" s="53"/>
       <c r="H180" s="53"/>
       <c r="I180" s="53"/>
     </row>
-    <row r="181" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G181" s="53"/>
       <c r="H181" s="53"/>
       <c r="I181" s="53"/>
     </row>
-    <row r="182" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G182" s="53"/>
       <c r="H182" s="53"/>
       <c r="I182" s="53"/>
     </row>
-    <row r="183" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G183" s="53"/>
       <c r="H183" s="53"/>
       <c r="I183" s="53"/>
     </row>
-    <row r="184" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G184" s="53"/>
       <c r="H184" s="53"/>
       <c r="I184" s="53"/>
     </row>
-    <row r="185" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G185" s="53"/>
       <c r="H185" s="53"/>
       <c r="I185" s="53"/>
     </row>
-    <row r="186" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G186" s="53"/>
       <c r="H186" s="53"/>
       <c r="I186" s="53"/>
     </row>
-    <row r="187" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G187" s="53"/>
       <c r="H187" s="53"/>
       <c r="I187" s="53"/>
     </row>
-    <row r="188" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G188" s="53"/>
       <c r="H188" s="53"/>
       <c r="I188" s="53"/>
     </row>
-    <row r="189" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G189" s="53"/>
       <c r="H189" s="53"/>
       <c r="I189" s="53"/>
     </row>
-    <row r="190" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G190" s="53"/>
       <c r="H190" s="53"/>
       <c r="I190" s="53"/>
     </row>
-    <row r="191" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G191" s="53"/>
       <c r="H191" s="53"/>
       <c r="I191" s="53"/>
     </row>
-    <row r="192" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G192" s="53"/>
       <c r="H192" s="53"/>
       <c r="I192" s="53"/>
     </row>
-    <row r="193" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G193" s="53"/>
       <c r="H193" s="53"/>
       <c r="I193" s="53"/>
     </row>
-    <row r="194" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G194" s="53"/>
       <c r="H194" s="53"/>
       <c r="I194" s="53"/>
     </row>
-    <row r="195" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G195" s="53"/>
       <c r="H195" s="53"/>
       <c r="I195" s="53"/>
     </row>
-    <row r="196" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G196" s="53"/>
       <c r="H196" s="53"/>
       <c r="I196" s="53"/>
     </row>
-    <row r="197" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G197" s="53"/>
       <c r="H197" s="53"/>
       <c r="I197" s="53"/>
     </row>
-    <row r="198" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G198" s="53"/>
       <c r="H198" s="53"/>
       <c r="I198" s="53"/>
     </row>
-    <row r="199" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G199" s="53"/>
       <c r="H199" s="53"/>
       <c r="I199" s="53"/>
     </row>
-    <row r="200" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G200" s="53"/>
       <c r="H200" s="53"/>
       <c r="I200" s="53"/>
     </row>
-    <row r="201" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G201" s="53"/>
       <c r="H201" s="53"/>
       <c r="I201" s="53"/>
     </row>
-    <row r="202" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G202" s="53"/>
       <c r="H202" s="53"/>
       <c r="I202" s="53"/>
     </row>
-    <row r="203" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G203" s="53"/>
       <c r="H203" s="53"/>
       <c r="I203" s="53"/>
     </row>
-    <row r="204" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G204" s="53"/>
       <c r="H204" s="53"/>
       <c r="I204" s="53"/>
     </row>
-    <row r="205" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G205" s="53"/>
       <c r="H205" s="53"/>
       <c r="I205" s="53"/>
     </row>
-    <row r="206" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G206" s="53"/>
       <c r="H206" s="53"/>
       <c r="I206" s="53"/>
     </row>
-    <row r="207" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G207" s="53"/>
       <c r="H207" s="53"/>
       <c r="I207" s="53"/>
     </row>
-    <row r="208" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G208" s="53"/>
       <c r="H208" s="53"/>
       <c r="I208" s="53"/>
     </row>
-    <row r="209" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G209" s="53"/>
       <c r="H209" s="53"/>
       <c r="I209" s="53"/>
     </row>
-    <row r="210" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G210" s="53"/>
       <c r="H210" s="53"/>
       <c r="I210" s="53"/>
     </row>
-    <row r="211" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G211" s="53"/>
       <c r="H211" s="53"/>
       <c r="I211" s="53"/>
     </row>
-    <row r="212" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G212" s="53"/>
       <c r="H212" s="53"/>
       <c r="I212" s="53"/>
     </row>
-    <row r="213" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G213" s="53"/>
       <c r="H213" s="53"/>
       <c r="I213" s="53"/>
     </row>
-    <row r="214" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G214" s="53"/>
       <c r="H214" s="53"/>
       <c r="I214" s="53"/>
     </row>
-    <row r="215" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G215" s="53"/>
       <c r="H215" s="53"/>
       <c r="I215" s="53"/>
     </row>
-    <row r="216" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G216" s="53"/>
       <c r="H216" s="53"/>
       <c r="I216" s="53"/>
     </row>
-    <row r="217" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G217" s="53"/>
       <c r="H217" s="53"/>
       <c r="I217" s="53"/>
     </row>
-    <row r="218" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G218" s="53"/>
       <c r="H218" s="53"/>
       <c r="I218" s="53"/>
     </row>
-    <row r="219" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G219" s="53"/>
       <c r="H219" s="53"/>
       <c r="I219" s="53"/>
     </row>
-    <row r="220" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G220" s="53"/>
       <c r="H220" s="53"/>
       <c r="I220" s="53"/>
     </row>
-    <row r="221" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G221" s="53"/>
       <c r="H221" s="53"/>
       <c r="I221" s="53"/>
     </row>
-    <row r="222" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G222" s="53"/>
       <c r="H222" s="53"/>
       <c r="I222" s="53"/>
     </row>
-    <row r="223" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G223" s="53"/>
       <c r="H223" s="53"/>
       <c r="I223" s="53"/>
     </row>
-    <row r="224" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G224" s="53"/>
       <c r="H224" s="53"/>
       <c r="I224" s="53"/>
     </row>
-    <row r="225" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G225" s="53"/>
       <c r="H225" s="53"/>
       <c r="I225" s="53"/>
     </row>
-    <row r="226" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G226" s="53"/>
       <c r="H226" s="53"/>
       <c r="I226" s="53"/>
     </row>
-    <row r="227" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G227" s="53"/>
       <c r="H227" s="53"/>
       <c r="I227" s="53"/>
     </row>
-    <row r="228" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G228" s="53"/>
       <c r="H228" s="53"/>
       <c r="I228" s="53"/>
     </row>
-    <row r="229" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G229" s="53"/>
       <c r="H229" s="53"/>
       <c r="I229" s="53"/>
     </row>
-    <row r="230" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G230" s="53"/>
       <c r="H230" s="53"/>
       <c r="I230" s="53"/>
     </row>
-    <row r="231" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G231" s="53"/>
       <c r="H231" s="53"/>
       <c r="I231" s="53"/>
     </row>
-    <row r="232" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G232" s="53"/>
       <c r="H232" s="53"/>
       <c r="I232" s="53"/>
     </row>
-    <row r="233" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G233" s="53"/>
       <c r="H233" s="53"/>
       <c r="I233" s="53"/>
     </row>
-    <row r="234" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G234" s="53"/>
       <c r="H234" s="53"/>
       <c r="I234" s="53"/>
     </row>
-    <row r="235" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G235" s="53"/>
       <c r="H235" s="53"/>
       <c r="I235" s="53"/>
     </row>
-    <row r="236" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G236" s="53"/>
       <c r="H236" s="53"/>
       <c r="I236" s="53"/>
     </row>
-    <row r="237" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G237" s="53"/>
       <c r="H237" s="53"/>
       <c r="I237" s="53"/>
     </row>
-    <row r="238" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G238" s="53"/>
       <c r="H238" s="53"/>
       <c r="I238" s="53"/>
     </row>
-    <row r="239" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G239" s="53"/>
       <c r="H239" s="53"/>
       <c r="I239" s="53"/>
     </row>
-    <row r="240" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G240" s="53"/>
       <c r="H240" s="53"/>
       <c r="I240" s="53"/>
     </row>
-    <row r="241" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G241" s="53"/>
       <c r="H241" s="53"/>
       <c r="I241" s="53"/>
     </row>
-    <row r="242" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G242" s="53"/>
       <c r="H242" s="53"/>
       <c r="I242" s="53"/>
     </row>
-    <row r="243" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G243" s="53"/>
       <c r="H243" s="53"/>
       <c r="I243" s="53"/>
     </row>
-    <row r="244" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G244" s="53"/>
       <c r="H244" s="53"/>
       <c r="I244" s="53"/>
     </row>
-    <row r="245" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G245" s="53"/>
       <c r="H245" s="53"/>
       <c r="I245" s="53"/>
     </row>
-    <row r="246" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G246" s="53"/>
       <c r="H246" s="53"/>
       <c r="I246" s="53"/>
     </row>
-    <row r="247" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G247" s="53"/>
       <c r="H247" s="53"/>
       <c r="I247" s="53"/>
     </row>
-    <row r="248" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G248" s="53"/>
       <c r="H248" s="53"/>
       <c r="I248" s="53"/>
     </row>
-    <row r="249" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G249" s="53"/>
       <c r="H249" s="53"/>
       <c r="I249" s="53"/>
     </row>
-    <row r="250" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G250" s="53"/>
       <c r="H250" s="53"/>
       <c r="I250" s="53"/>
     </row>
-    <row r="251" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G251" s="53"/>
       <c r="H251" s="53"/>
       <c r="I251" s="53"/>
     </row>
-    <row r="252" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G252" s="53"/>
       <c r="H252" s="53"/>
       <c r="I252" s="53"/>
     </row>
-    <row r="253" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G253" s="53"/>
       <c r="H253" s="53"/>
       <c r="I253" s="53"/>
     </row>
-    <row r="254" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G254" s="53"/>
       <c r="H254" s="53"/>
       <c r="I254" s="53"/>
     </row>
-    <row r="255" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G255" s="53"/>
       <c r="H255" s="53"/>
       <c r="I255" s="53"/>
     </row>
-    <row r="256" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G256" s="53"/>
       <c r="H256" s="53"/>
       <c r="I256" s="53"/>
     </row>
-    <row r="257" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G257" s="53"/>
       <c r="H257" s="1"/>
       <c r="I257" s="1"/>
     </row>
-    <row r="258" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G258" s="53"/>
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>
     </row>
-    <row r="259" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G259" s="53"/>
       <c r="H259" s="1"/>
       <c r="I259" s="1"/>
     </row>
-    <row r="260" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G260" s="53"/>
       <c r="H260" s="1"/>
       <c r="I260" s="1"/>
     </row>
-    <row r="261" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G261" s="53"/>
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
     </row>
-    <row r="262" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G262" s="53"/>
       <c r="H262" s="1"/>
       <c r="I262" s="1"/>
     </row>
-    <row r="263" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G263" s="53"/>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
     </row>
-    <row r="264" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G264" s="53"/>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
     </row>
-    <row r="265" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G265" s="53"/>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
     </row>
-    <row r="266" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G266" s="53"/>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
     </row>
-    <row r="267" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G267" s="53"/>
     </row>
-    <row r="268" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G268" s="53"/>
     </row>
-    <row r="269" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G269" s="53"/>
     </row>
-    <row r="270" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G270" s="53"/>
     </row>
-    <row r="271" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G271" s="53"/>
     </row>
-    <row r="272" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G272" s="53"/>
     </row>
-    <row r="273" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G273" s="53"/>
     </row>
-    <row r="274" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G274" s="53"/>
     </row>
-    <row r="275" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G275" s="53"/>
     </row>
-    <row r="276" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G276" s="53"/>
     </row>
-    <row r="277" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G277" s="53"/>
     </row>
-    <row r="278" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G278" s="53"/>
     </row>
-    <row r="279" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G279" s="53"/>
     </row>
-    <row r="280" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G280" s="53"/>
     </row>
-    <row r="281" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G281" s="53"/>
     </row>
-    <row r="282" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G282" s="53"/>
     </row>
-    <row r="283" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G283" s="53"/>
     </row>
-    <row r="284" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G284" s="53"/>
     </row>
-    <row r="285" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G285" s="53"/>
     </row>
-    <row r="286" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G286" s="53"/>
     </row>
-    <row r="287" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G287" s="53"/>
     </row>
-    <row r="288" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G288" s="53"/>
     </row>
-    <row r="289" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G289" s="53"/>
     </row>
-    <row r="290" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G290" s="53"/>
     </row>
-    <row r="291" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G291" s="53"/>
     </row>
-    <row r="292" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G292" s="53"/>
     </row>
-    <row r="293" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G293" s="53"/>
     </row>
-    <row r="294" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G294" s="53"/>
     </row>
-    <row r="295" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G295" s="53"/>
     </row>
-    <row r="296" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G296" s="53"/>
     </row>
-    <row r="297" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G297" s="53"/>
     </row>
-    <row r="298" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G298" s="53"/>
     </row>
-    <row r="299" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G299" s="53"/>
     </row>
-    <row r="300" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G300" s="53"/>
     </row>
-    <row r="301" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G301" s="53"/>
     </row>
-    <row r="302" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G302" s="53"/>
     </row>
-    <row r="303" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G303" s="53"/>
     </row>
-    <row r="304" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G304" s="53"/>
     </row>
-    <row r="305" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G305" s="53"/>
     </row>
-    <row r="306" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G306" s="53"/>
     </row>
-    <row r="307" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G307" s="53"/>
     </row>
-    <row r="308" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G308" s="53"/>
     </row>
-    <row r="309" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G309" s="53"/>
     </row>
-    <row r="310" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G310" s="53"/>
     </row>
-    <row r="311" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G311" s="53"/>
     </row>
-    <row r="312" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G312" s="53"/>
     </row>
-    <row r="313" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G313" s="53"/>
     </row>
-    <row r="314" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G314" s="53"/>
     </row>
-    <row r="315" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G315" s="53"/>
     </row>
-    <row r="316" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G316" s="53"/>
     </row>
-    <row r="317" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G317" s="53"/>
     </row>
-    <row r="318" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G318" s="53"/>
     </row>
-    <row r="319" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G319" s="53"/>
     </row>
-    <row r="320" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G320" s="53"/>
     </row>
-    <row r="321" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G321" s="53"/>
     </row>
-    <row r="322" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G322" s="53"/>
     </row>
-    <row r="323" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G323" s="53"/>
     </row>
-    <row r="324" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G324" s="53"/>
     </row>
-    <row r="325" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G325" s="53"/>
     </row>
-    <row r="326" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G326" s="53"/>
     </row>
-    <row r="327" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G327" s="53"/>
     </row>
-    <row r="328" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G328" s="53"/>
     </row>
-    <row r="329" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G329" s="53"/>
     </row>
-    <row r="330" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G330" s="53"/>
     </row>
-    <row r="331" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G331" s="53"/>
     </row>
-    <row r="332" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G332" s="53"/>
     </row>
-    <row r="333" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G333" s="53"/>
     </row>
-    <row r="334" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G334" s="53"/>
     </row>
-    <row r="335" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G335" s="53"/>
     </row>
-    <row r="336" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G336" s="53"/>
     </row>
-    <row r="337" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G337" s="53"/>
     </row>
-    <row r="338" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G338" s="53"/>
     </row>
-    <row r="339" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G339" s="53"/>
     </row>
-    <row r="340" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G340" s="53"/>
     </row>
-    <row r="341" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G341" s="53"/>
     </row>
-    <row r="342" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G342" s="53"/>
     </row>
-    <row r="343" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G343" s="53"/>
     </row>
-    <row r="344" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G344" s="53"/>
     </row>
-    <row r="345" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G345" s="53"/>
     </row>
-    <row r="346" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G346" s="53"/>
     </row>
-    <row r="347" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G347" s="53"/>
     </row>
-    <row r="348" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G348" s="53"/>
     </row>
-    <row r="349" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G349" s="53"/>
     </row>
-    <row r="350" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G350" s="53"/>
     </row>
-    <row r="351" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G351" s="53"/>
     </row>
-    <row r="352" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G352" s="53"/>
     </row>
-    <row r="353" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G353" s="53"/>
     </row>
-    <row r="354" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G354" s="53"/>
     </row>
-    <row r="355" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G355" s="53"/>
     </row>
-    <row r="356" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G356" s="53"/>
     </row>
-    <row r="357" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G357" s="53"/>
     </row>
-    <row r="358" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G358" s="53"/>
     </row>
-    <row r="359" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G359" s="53"/>
     </row>
-    <row r="360" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G360" s="53"/>
     </row>
-    <row r="361" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G361" s="53"/>
     </row>
-    <row r="362" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G362" s="53"/>
     </row>
-    <row r="363" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G363" s="53"/>
     </row>
-    <row r="364" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G364" s="53"/>
     </row>
-    <row r="365" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G365" s="53"/>
     </row>
-    <row r="366" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G366" s="53"/>
     </row>
-    <row r="367" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G367" s="53"/>
     </row>
-    <row r="368" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G368" s="53"/>
     </row>
-    <row r="369" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G369" s="53"/>
     </row>
-    <row r="370" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G370" s="53"/>
     </row>
-    <row r="371" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G371" s="53"/>
     </row>
-    <row r="372" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G372" s="53"/>
     </row>
-    <row r="373" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G373" s="53"/>
     </row>
-    <row r="374" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G374" s="53"/>
     </row>
-    <row r="375" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G375" s="53"/>
     </row>
-    <row r="376" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G376" s="53"/>
     </row>
-    <row r="377" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G377" s="53"/>
     </row>
-    <row r="378" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G378" s="53"/>
     </row>
-    <row r="379" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G379" s="53"/>
     </row>
-    <row r="380" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G380" s="53"/>
     </row>
-    <row r="381" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G381" s="53"/>
     </row>
-    <row r="382" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G382" s="53"/>
     </row>
-    <row r="383" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G383" s="53"/>
     </row>
-    <row r="384" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G384" s="53"/>
     </row>
-    <row r="385" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G385" s="53"/>
     </row>
-    <row r="386" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G386" s="53"/>
     </row>
-    <row r="387" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G387" s="53"/>
     </row>
-    <row r="388" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G388" s="53"/>
     </row>
-    <row r="389" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G389" s="53"/>
     </row>
-    <row r="390" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G390" s="53"/>
     </row>
-    <row r="391" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G391" s="53"/>
     </row>
-    <row r="392" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G392" s="53"/>
     </row>
-    <row r="393" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G393" s="53"/>
     </row>
-    <row r="394" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G394" s="53"/>
     </row>
-    <row r="395" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G395" s="53"/>
     </row>
-    <row r="396" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G396" s="53"/>
     </row>
-    <row r="397" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G397" s="53"/>
     </row>
-    <row r="398" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G398" s="53"/>
     </row>
-    <row r="399" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G399" s="53"/>
     </row>
-    <row r="400" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G400" s="53"/>
     </row>
-    <row r="401" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G401" s="53"/>
     </row>
-    <row r="402" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G402" s="53"/>
     </row>
-    <row r="403" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G403" s="53"/>
     </row>
-    <row r="404" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G404" s="53"/>
     </row>
   </sheetData>
@@ -12301,58 +12388,42 @@
     <mergeCell ref="M3:M4"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:C5 C70:D70 C74:D76 C97:D121">
-    <cfRule type="cellIs" dxfId="13" priority="235" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="235" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="236" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="236" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C96">
-    <cfRule type="cellIs" dxfId="11" priority="35" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="35" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="36" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="36" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G133:G1048576">
-    <cfRule type="cellIs" dxfId="9" priority="63" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="63" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="64" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="64" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I108 G110:I110 I109 G123:I132 I111:I122">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThan">
+  <conditionalFormatting sqref="G14:I132">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H133:I266">
-    <cfRule type="cellIs" dxfId="5" priority="233" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="233" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="234" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G109:H109">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G111:H122">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="234" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12364,15 +12435,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:D17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="47.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B1" s="62" t="s">
         <v>271</v>
       </c>
@@ -12383,7 +12454,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" s="54" t="s">
         <v>23</v>
       </c>
@@ -12392,7 +12463,7 @@
       </c>
       <c r="D2" s="54"/>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="54" t="s">
         <v>157</v>
       </c>
@@ -12401,7 +12472,7 @@
       </c>
       <c r="D3" s="54"/>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="54" t="s">
         <v>158</v>
       </c>
@@ -12410,7 +12481,7 @@
       </c>
       <c r="D4" s="54"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="54" t="s">
         <v>159</v>
       </c>
@@ -12419,7 +12490,7 @@
       </c>
       <c r="D5" s="54"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="54" t="s">
         <v>160</v>
       </c>
@@ -12428,7 +12499,7 @@
       </c>
       <c r="D6" s="54"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="54" t="s">
         <v>276</v>
       </c>
@@ -12437,7 +12508,7 @@
       </c>
       <c r="D7" s="54"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="54" t="s">
         <v>277</v>
       </c>
@@ -12446,7 +12517,7 @@
       </c>
       <c r="D8" s="54"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="54" t="s">
         <v>170</v>
       </c>
@@ -12457,7 +12528,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="54" t="s">
         <v>279</v>
       </c>
@@ -12466,7 +12537,7 @@
       </c>
       <c r="D10" s="54"/>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C17" s="28"/>
     </row>
   </sheetData>
